--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証チェックリスト'!$A$1:$G$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経路・運賃・時間データ一覧'!$A$1:$N$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'バス情報整合性チェック'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="E18" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F18" s="55" t="inlineStr">
         <is>
-          <t>大宮・横浜発legの「新宿→茅野」区間が「JR中央線」170分と表示されていたが、新宿発自身の同一区間は「JR特急あずさ」130分で40分の食い違い（同じ茅野ゲートウェイのkirigamineと同型バグ）。あずさ・130分に修正（合計表示は元々整合していたため trainTimeXxx自体は不変）。運賃も茅野ゲートウェイの確立済み増分パターン（+660円）に反して大宮・横浜が528/616円しか増えていなかったため、大宮・横浜とも9,160円に修正。</t>
+          <t>大宮・横浜発legの「新宿→茅野」区間が「JR中央線」170分と表示されていたが、新宿発自身の同一区間は「JR特急あずさ」130分で40分の食い違い（同じ茅野ゲートウェイのkirigamineと同型バグ）。あずさ・130分に修正（合計表示は元々整合していたため trainTimeXxx自体は不変）。運賃も茅野ゲートウェイの確立済み増分パターン（+660円）に反して大宮・横浜が528/616円しか増えていなかったため、大宮・横浜とも9,160円に修正。 ｜【2026-09-25追加修正】茅野ゲートウェイ方式に統一（大宮=立川、横浜=八王子乗換のあずさ） ｜バスは実測（92分・2,600円）に訂正済み</t>
         </is>
       </c>
       <c r="G18" s="37" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="E24" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F24" s="55" t="inlineStr">
         <is>
-          <t>経路・時間は既に正確だった（茅野駅までのJR運賃・南アルプスジオライナー・林道バスの運賃を個別に検算した結果、新宿発8,710円は元々正しかった）。ただし大宮発・横浜発の運賃が新宿発と同額（8,710円）または逆に安い（8,050円）という他の山と同じ逆転・コピペバグがあり、通し運賃で大宮/横浜とも9,040円に修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。</t>
+          <t>経路・時間は既に正確だった（茅野駅までのJR運賃・南アルプスジオライナー・林道バスの運賃を個別に検算した結果、新宿発8,710円は元々正しかった）。ただし大宮発・横浜発の運賃が新宿発と同額（8,710円）または逆に安い（8,050円）という他の山と同じ逆転・コピペバグがあり、通し運賃で大宮/横浜とも9,040円に修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】茅野ゲートウェイ方式に統一（大宮=立川、横浜=八王子乗換のあずさ）</t>
         </is>
       </c>
       <c r="G24" s="37" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="E25" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F25" s="55" t="inlineStr">
         <is>
-          <t>大宮発運賃(8,710円)が新宿発と完全に同額、かつ横浜発(8,050円)がさらに安いという物理的に矛盾した運賃バグを発見。あずさ新宿-茅野実運賃(5,760円)＋バス運賃差分から大宮・横浜とも9,370円に修正。FAQの横浜運賃表記も連動修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。</t>
+          <t>大宮発運賃(8,710円)が新宿発と完全に同額、かつ横浜発(8,050円)がさらに安いという物理的に矛盾した運賃バグを発見。あずさ新宿-茅野実運賃(5,760円)＋バス運賃差分から大宮・横浜とも9,370円に修正。FAQの横浜運賃表記も連動修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】茅野ゲートウェイ方式に統一（大宮=立川、横浜=八王子乗換のあずさ）</t>
         </is>
       </c>
       <c r="G25" s="37" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="E99" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F99" s="55" t="inlineStr">
         <is>
-          <t>重大な経路誤り。noutoriと同一の「甲府→広河原」データが誤って流用されていたが、正しい登山口は「戸台パーク」（新宿→茅野→南アルプスジオライナー経由）。全面再構築。</t>
+          <t>重大な経路誤り。noutoriと同一の「甲府→広河原」データが誤って流用されていたが、正しい登山口は「戸台パーク」（新宿→茅野→南アルプスジオライナー経由）。全面再構築。 ｜【2026-09-25追加修正】茅野ゲートウェイ方式に統一（大宮=立川、横浜=八王子乗換のあずさ）</t>
         </is>
       </c>
       <c r="G99" s="37" t="inlineStr">
@@ -7374,32 +7374,32 @@
         </is>
       </c>
       <c r="G18" s="41" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="H18" s="41" t="n">
-        <v>8500</v>
+        <v>8360</v>
       </c>
       <c r="I18" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[アルピコ交通「霧ヶ峰線」]--&gt; 霧ヶ峰（季節）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[アルピコ交通「霧ヶ峰線」]--&gt; 霧ヶ峰（季節）</t>
         </is>
       </c>
       <c r="J18" s="41" t="n">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="K18" s="41" t="n">
-        <v>9160</v>
+        <v>8360</v>
       </c>
       <c r="L18" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[アルピコ交通「霧ヶ峰線」]--&gt; 霧ヶ峰（季節）</t>
+          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[アルピコ交通「霧ヶ峰線」]--&gt; 霧ヶ峰（季節）</t>
         </is>
       </c>
       <c r="M18" s="41" t="n">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="N18" s="41" t="n">
-        <v>9160</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="19" ht="39" customHeight="1" s="30">
@@ -7698,32 +7698,32 @@
         </is>
       </c>
       <c r="G24" s="41" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H24" s="41" t="n">
         <v>8710</v>
       </c>
       <c r="I24" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
         </is>
       </c>
       <c r="J24" s="41" t="n">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="K24" s="41" t="n">
-        <v>9040</v>
+        <v>8710</v>
       </c>
       <c r="L24" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
+          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
         </is>
       </c>
       <c r="M24" s="41" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="N24" s="41" t="n">
-        <v>9040</v>
+        <v>8050</v>
       </c>
     </row>
     <row r="25" ht="51.75" customHeight="1" s="30">
@@ -7756,32 +7756,32 @@
         </is>
       </c>
       <c r="G25" s="41" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H25" s="41" t="n">
         <v>8710</v>
       </c>
       <c r="I25" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
         </is>
       </c>
       <c r="J25" s="41" t="n">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="K25" s="41" t="n">
-        <v>9370</v>
+        <v>8710</v>
       </c>
       <c r="L25" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
+          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
         </is>
       </c>
       <c r="M25" s="41" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="N25" s="41" t="n">
-        <v>9370</v>
+        <v>8050</v>
       </c>
     </row>
     <row r="26" ht="39" customHeight="1" s="30">
@@ -11904,32 +11904,32 @@
         </is>
       </c>
       <c r="G99" s="41" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H99" s="41" t="n">
         <v>7560</v>
       </c>
       <c r="I99" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[南アルプスジオライナー]--&gt; 戸台パーク（南アルプスマイカー規制のため利用、乗車協力金別途）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[南アルプスジオライナー]--&gt; 戸台パーク（南アルプスマイカー規制のため利用、乗車協力金別途）</t>
         </is>
       </c>
       <c r="J99" s="41" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K99" s="41" t="n">
         <v>7560</v>
       </c>
       <c r="L99" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[南アルプスジオライナー]--&gt; 戸台パーク（南アルプスマイカー規制のため利用、乗車協力金別途）</t>
+          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[南アルプスジオライナー]--&gt; 戸台パーク（南アルプスマイカー規制のため利用、乗車協力金別途）</t>
         </is>
       </c>
       <c r="M99" s="41" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="N99" s="41" t="n">
-        <v>7690</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="100" ht="39" customHeight="1" s="30">
@@ -24237,7 +24237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K191"/>
+  <dimension ref="A1:K196"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -34758,8 +34758,283 @@
         </is>
       </c>
     </row>
+    <row r="192" ht="58.2" customHeight="1" s="30">
+      <c r="A192" s="53" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C192" s="53" t="inlineStr">
+        <is>
+          <t>komagatake</t>
+        </is>
+      </c>
+      <c r="D192" s="54" t="inlineStr">
+        <is>
+          <t>甲斐駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E192" s="54" t="inlineStr">
+        <is>
+          <t>経路・運賃の統一（同一ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="F192" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G192" s="55" t="inlineStr">
+        <is>
+          <t>大宮・横浜：湘南新宿ライン→新宿→あずさ、運賃 大宮9,040/9,370円・横浜同額</t>
+        </is>
+      </c>
+      <c r="H192" s="55" t="inlineStr">
+        <is>
+          <t>大宮：武蔵野線・中央線→立川／横浜：横浜線→八王子乗換のあずさ。運賃 新宿・大宮8,710円／横浜8,050円。あずさ126分（合計 新宿246/大宮277/横浜281分）</t>
+        </is>
+      </c>
+      <c r="I192" s="56" t="inlineStr">
+        <is>
+          <t>駅探（茅野駅までの電車運賃：新宿・大宮5,760円／横浜5,100円）、JRバス関東 南アルプスジオライナー（茅野駅→戸台パーク 1,800円・約65分）、南アルプス林道バス（戸台パーク→北沢峠 約1,150円）</t>
+        </is>
+      </c>
+      <c r="J192" s="55" t="inlineStr">
+        <is>
+          <t>旧新宿発8,710円＝5,760＋1,800＋1,150円で整合。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K192" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="58.2" customHeight="1" s="30">
+      <c r="A193" s="53" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C193" s="53" t="inlineStr">
+        <is>
+          <t>senjogatake</t>
+        </is>
+      </c>
+      <c r="D193" s="54" t="inlineStr">
+        <is>
+          <t>仙丈ヶ岳</t>
+        </is>
+      </c>
+      <c r="E193" s="54" t="inlineStr">
+        <is>
+          <t>経路・運賃の統一（同一ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="F193" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G193" s="55" t="inlineStr">
+        <is>
+          <t>大宮・横浜：湘南新宿ライン→新宿→あずさ、運賃 大宮9,040/9,370円・横浜同額</t>
+        </is>
+      </c>
+      <c r="H193" s="55" t="inlineStr">
+        <is>
+          <t>大宮：武蔵野線・中央線→立川／横浜：横浜線→八王子乗換のあずさ。運賃 新宿・大宮8,710円／横浜8,050円。あずさ126分（合計 新宿246/大宮277/横浜281分）</t>
+        </is>
+      </c>
+      <c r="I193" s="56" t="inlineStr">
+        <is>
+          <t>駅探（茅野駅までの電車運賃：新宿・大宮5,760円／横浜5,100円）、JRバス関東 南アルプスジオライナー（茅野駅→戸台パーク 1,800円・約65分）、南アルプス林道バス（戸台パーク→北沢峠 約1,150円）</t>
+        </is>
+      </c>
+      <c r="J193" s="55" t="inlineStr">
+        <is>
+          <t>旧新宿発8,710円＝5,760＋1,800＋1,150円で整合。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K193" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="58.2" customHeight="1" s="30">
+      <c r="A194" s="53" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C194" s="53" t="inlineStr">
+        <is>
+          <t>nokogiriyama</t>
+        </is>
+      </c>
+      <c r="D194" s="54" t="inlineStr">
+        <is>
+          <t>鋸岳</t>
+        </is>
+      </c>
+      <c r="E194" s="54" t="inlineStr">
+        <is>
+          <t>経路実在性・運賃の統一</t>
+        </is>
+      </c>
+      <c r="F194" s="54" t="inlineStr">
+        <is>
+          <t>trainAccess文・大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G194" s="55" t="inlineStr">
+        <is>
+          <t>trainAccess文が「甲府駅→広河原線（広河原）」（trainRoutes・FAQは茅野駅→戸台パーク）。横浜発7,690円</t>
+        </is>
+      </c>
+      <c r="H194" s="55" t="inlineStr">
+        <is>
+          <t>trainAccess文を茅野駅→ジオライナー→戸台パークに統一。大宮=立川、横浜=八王子乗換。運賃 新宿・大宮7,560円／横浜6,900円（合計 191/222/226分）</t>
+        </is>
+      </c>
+      <c r="I194" s="56" t="inlineStr">
+        <is>
+          <t>駅探（茅野駅までの電車運賃：新宿・大宮5,760円／横浜5,100円）、JRバス関東 南アルプスジオライナー（茅野駅→戸台パーク 1,800円・約65分）、南アルプス林道バス（戸台パーク→北沢峠 約1,150円）</t>
+        </is>
+      </c>
+      <c r="J194" s="55" t="inlineStr">
+        <is>
+          <t>旧新宿発7,560円＝5,760＋1,800円で整合</t>
+        </is>
+      </c>
+      <c r="K194" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="58.2" customHeight="1" s="30">
+      <c r="A195" s="53" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C195" s="53" t="inlineStr">
+        <is>
+          <t>kirigamine</t>
+        </is>
+      </c>
+      <c r="D195" s="54" t="inlineStr">
+        <is>
+          <t>霧ヶ峰</t>
+        </is>
+      </c>
+      <c r="E195" s="54" t="inlineStr">
+        <is>
+          <t>バス時間・経路・運賃の統一</t>
+        </is>
+      </c>
+      <c r="F195" s="54" t="inlineStr">
+        <is>
+          <t>茅野駅→霧ヶ峰</t>
+        </is>
+      </c>
+      <c r="G195" s="55" t="inlineStr">
+        <is>
+          <t>バス「霧ヶ峰線」30分（legsの合計時間は200分で不整合）。大宮・横浜発9,160円</t>
+        </is>
+      </c>
+      <c r="H195" s="55" t="inlineStr">
+        <is>
+          <t>白樺湖・車山高原線（強清水経由）約70分（旧合計時間200分＝あずさ130分＋70分から逆算）。バス種別アイコンをbusに修正。運賃 新宿・大宮8,500円／横浜7,840円（合計 196/227/231分）</t>
+        </is>
+      </c>
+      <c r="I195" s="56" t="inlineStr">
+        <is>
+          <t>アルピコ交通 白樺湖・車山高原線（茅野駅→車山肩 約58分・2,300円）、旧新宿発8,500円の内訳から逆算（バス約2,740円）</t>
+        </is>
+      </c>
+      <c r="J195" s="55" t="inlineStr">
+        <is>
+          <t>旧値から逆算のため一次確認は未了</t>
+        </is>
+      </c>
+      <c r="K195" s="57" t="inlineStr">
+        <is>
+          <t>低〜中</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="58.2" customHeight="1" s="30">
+      <c r="A196" s="53" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C196" s="53" t="inlineStr">
+        <is>
+          <t>kirigamine</t>
+        </is>
+      </c>
+      <c r="D196" s="54" t="inlineStr">
+        <is>
+          <t>霧ヶ峰</t>
+        </is>
+      </c>
+      <c r="E196" s="54" t="inlineStr">
+        <is>
+          <t>バス時間・運賃（実測で訂正）</t>
+        </is>
+      </c>
+      <c r="F196" s="54" t="inlineStr">
+        <is>
+          <t>茅野駅→霧ヶ峰</t>
+        </is>
+      </c>
+      <c r="G196" s="55" t="inlineStr">
+        <is>
+          <t>直前の暫定値：バス70分（逆算）、運賃 新宿・大宮8,500円／横浜7,840円</t>
+        </is>
+      </c>
+      <c r="H196" s="55" t="inlineStr">
+        <is>
+          <t>バス92分・2,600円（ユーザー確認の乗換案内）。運賃 新宿・大宮8,360円／横浜7,700円（合計 218/249/253分）</t>
+        </is>
+      </c>
+      <c r="I196" s="56" t="inlineStr">
+        <is>
+          <t>ユーザー提供の乗換案内（茅野駅→霧ヶ峰 1時間32分・2,600円）、駅探（電車運賃 5,760円／5,100円）</t>
+        </is>
+      </c>
+      <c r="J196" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K196" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K191"/>
+  <autoFilter ref="A1:K196"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証チェックリスト'!$A$1:$G$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経路・運賃・時間データ一覧'!$A$1:$N$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'バス情報整合性チェック'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$208</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -818,7 +818,7 @@
       </c>
       <c r="F2" s="55" t="inlineStr">
         <is>
-          <t>横浜発が「小田急・相鉄直通」(1964年廃止の存在しないルート)だったため全面書き換え。運賃も新価格に更新 ｜【2026-09-25追加修正】渋沢→大倉バスを15分に統一（合計-5分）</t>
+          <t>横浜発が「小田急・相鉄直通」(1964年廃止の存在しないルート)だったため全面書き換え。運賃も新価格に更新 ｜【2026-09-25追加修正】渋沢→大倉バスを15分に統一（合計-5分） ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G2" s="37" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="E3" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F3" s="55" t="inlineStr">
         <is>
-          <t>運賃を新価格に更新（特急富士回遊4200円+バス2000円=6200円）。経路自体はOK</t>
+          <t>運賃を新価格に更新（特急富士回遊4200円+バス2000円=6200円）。経路自体はOK ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E27" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F27" s="55" t="inlineStr">
         <is>
-          <t>経路は実在。新島々駅〜乗鞍高原観光センターのバス時間が「約30分」表示だったが、実際は「約1時間3分」（アルピコ交通「乗鞍高原線」、1,350円）と倍以上の過小表示だった。乗鞍高原〜畳平シャトルバスも「約60分/未記載運賃」だったが正しくは「約50分・1,750円」。運賃も通し運賃で再計算し、新宿9,570円→10,540円、大宮9,680円→10,980円、横浜9,370円→10,980円に修正（横浜が最安という逆転バグも解消）。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。</t>
+          <t>経路は実在。新島々駅〜乗鞍高原観光センターのバス時間が「約30分」表示だったが、実際は「約1時間3分」（アルピコ交通「乗鞍高原線」、1,350円）と倍以上の過小表示だった。乗鞍高原〜畳平シャトルバスも「約60分/未記載運賃」だったが正しくは「約50分・1,750円」。運賃も通し運賃で再計算し、新宿9,570円→10,540円、大宮9,680円→10,980円、横浜9,370円→10,980円に修正（横浜が最安という逆転バグも解消）。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G27" s="37" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="E30" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F30" s="55" t="inlineStr">
         <is>
-          <t>横浜発運賃(8,990円)が新宿発(9,190円)より安いという逆転バグを発見（横浜発は新宿経由でさらに距離が長いため物理的に矛盾）。大宮発運賃(9,300円)と揃え9,300円に修正。FAQの横浜運賃表記も連動修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。</t>
+          <t>横浜発運賃(8,990円)が新宿発(9,190円)より安いという逆転バグを発見（横浜発は新宿経由でさらに距離が長いため物理的に矛盾）。大宮発運賃(9,300円)と揃え9,300円に修正。FAQの横浜運賃表記も連動修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G30" s="37" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="E31" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F31" s="55" t="inlineStr">
         <is>
-          <t>経路・時間はほぼ正確だったが、横浜発の運賃が新宿発より安い（8,990円&lt;9,190円）逆転バグがあった。JR公式あずさ料金表（新宿-松本6,730円指定席）＋松本電鉄（710円）＋新島々-上高地バス（1,450円）で通し運賃を再計算し、新宿8,890円・大宮/横浜9,330円に修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。</t>
+          <t>経路・時間はほぼ正確だったが、横浜発の運賃が新宿発より安い（8,990円&lt;9,190円）逆転バグがあった。JR公式あずさ料金表（新宿-松本6,730円指定席）＋松本電鉄（710円）＋新島々-上高地バス（1,450円）で通し運賃を再計算し、新宿8,890円・大宮/横浜9,330円に修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G31" s="37" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F42" s="56" t="inlineStr">
         <is>
-          <t>**横浜発の経路が「小田急・相鉄直通」という、tanzawa（丹沢山）と全く同じ1964年廃止済みの存在しない直通ルートだった。** tanzawaで確定済みの正しいルート（横浜→相鉄本線特急→海老名→小田急小田原線急行→渋沢）に統一。また渋沢駅〜大倉のバスが「約15分・210円」表示だったが、実際は「約20分・270円」で全経路とも修正。新宿942円→1,002円、大宮1,470円→1,530円、横浜898円→930円（tanzawaの検証済み値を再利用）に修正。**同じバグ（消滅した直通列車）が複数の山に横展開している可能性が高いことが判明したため、小田急線・相鉄線を経由する他の丹沢エリアの山（大山、鍋割山など）も要注意。** ｜【2026-09-25追加修正】渋沢→大倉バス15分・合計-5分</t>
+          <t>**横浜発の経路が「小田急・相鉄直通」という、tanzawa（丹沢山）と全く同じ1964年廃止済みの存在しない直通ルートだった。** tanzawaで確定済みの正しいルート（横浜→相鉄本線特急→海老名→小田急小田原線急行→渋沢）に統一。また渋沢駅〜大倉のバスが「約15分・210円」表示だったが、実際は「約20分・270円」で全経路とも修正。新宿942円→1,002円、大宮1,470円→1,530円、横浜898円→930円（tanzawaの検証済み値を再利用）に修正。**同じバグ（消滅した直通列車）が複数の山に横展開している可能性が高いことが判明したため、小田急線・相鉄線を経由する他の丹沢エリアの山（大山、鍋割山など）も要注意。** ｜【2026-09-25追加修正】渋沢→大倉バス15分・合計-5分 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G42" s="37" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="F43" s="56" t="inlineStr">
         <is>
-          <t>**横浜発の経路がtanzawa・tonosakiと全く同じ「小田急・相鉄直通」(1964年廃止)バグの3件目の横展開だった。** tonosakiで確定済みのルート（横浜→相鉄本線特急→海老名→小田急小田原線急行→渋沢）に統一。渋沢〜大倉のバスも同じく「約15分・210円」→「約20分・270円」に修正。新宿942円→1,002円、大宮1,470円→1,530円、横浜898円→930円（tonosakiの検証済み値を再利用）。**丹沢エリアで大倉尾根を共有する山（大山、鍋割山など）はこのバグの横展開の要注意リストに追加。** ｜【2026-09-25追加修正】渋沢→大倉バス15分・合計-5分</t>
+          <t>**横浜発の経路がtanzawa・tonosakiと全く同じ「小田急・相鉄直通」(1964年廃止)バグの3件目の横展開だった。** tonosakiで確定済みのルート（横浜→相鉄本線特急→海老名→小田急小田原線急行→渋沢）に統一。渋沢〜大倉のバスも同じく「約15分・210円」→「約20分・270円」に修正。新宿942円→1,002円、大宮1,470円→1,530円、横浜898円→930円（tonosakiの検証済み値を再利用）。**丹沢エリアで大倉尾根を共有する山（大山、鍋割山など）はこのバグの横展開の要注意リストに追加。** ｜【2026-09-25追加修正】渋沢→大倉バス15分・合計-5分 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G43" s="37" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="E52" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F52" s="55" t="inlineStr">
         <is>
-          <t>新宿発運賃(6,620円)が実際には「新宿-松本」間の特急あずさ運賃のみに一致しており、その先の松本電鉄上高地線＋アルピコバス（新島々→中の湯）の運賃が完全に欠落した「運賃の構成要素欠落」バグを発見。同一経路を共有するyari（槍ヶ岳）の運賃差分から欠落分(約2,280円)を推定・加算し、新宿8,900円・大宮9,428円・横浜9,516円に修正。FAQも連動修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。</t>
+          <t>新宿発運賃(6,620円)が実際には「新宿-松本」間の特急あずさ運賃のみに一致しており、その先の松本電鉄上高地線＋アルピコバス（新島々→中の湯）の運賃が完全に欠落した「運賃の構成要素欠落」バグを発見。同一経路を共有するyari（槍ヶ岳）の運賃差分から欠落分(約2,280円)を推定・加算し、新宿8,900円・大宮9,428円・横浜9,516円に修正。FAQも連動修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G52" s="37" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="E101" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F101" s="55" t="inlineStr">
         <is>
-          <t>運賃(6,620円/7,148円/7,236円)が、同一経路のyari（槍ヶ岳）の修正前バグ値ではなく、無関係のyakedake（焼岳、松本電鉄+バス運賃が欠落したバグ値）とまったく同じ数値になっていた「他山の誤データが混入」パターンを発見。同一経路を共有するyariの修正後の正しい運賃（9,190円/9,300円/9,300円）に修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。</t>
+          <t>運賃(6,620円/7,148円/7,236円)が、同一経路のyari（槍ヶ岳）の修正前バグ値ではなく、無関係のyakedake（焼岳、松本電鉄+バス運賃が欠落したバグ値）とまったく同じ数値になっていた「他山の誤データが混入」パターンを発見。同一経路を共有するyariの修正後の正しい運賃（9,190円/9,300円/9,300円）に修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G101" s="37" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="F113" s="56" t="inlineStr">
         <is>
-          <t>tanzawa/tonosaki/hirugataと同じ「小田急・相鉄直通」バグ（1964年廃止のサービス）が横浜発ルートに発見された（4件目）。同一の大倉ゲートウェイを共有するsannotouと完全に同一のバグ・同一の数値だった。tonosaki/hirugataの検証済みルート（横浜→海老名 相鉄本線特急28分→渋沢 小田急小田原線急行30分→大倉 バス20分）に統一。あわせて新宿・大宮発のバス区間(15分)も他山の検証済み値(20分)に、大宮発の小田急線区間(90分)も新宿発の実際の値(70分)に統一。運賃・時間ともhirugata/tonosaki基準の90分/1,002円・120分/1,530円・78分/930円に統一。 ｜【2026-09-25追加修正】渋沢→大倉バス15分・合計-5分</t>
+          <t>tanzawa/tonosaki/hirugataと同じ「小田急・相鉄直通」バグ（1964年廃止のサービス）が横浜発ルートに発見された（4件目）。同一の大倉ゲートウェイを共有するsannotouと完全に同一のバグ・同一の数値だった。tonosaki/hirugataの検証済みルート（横浜→海老名 相鉄本線特急28分→渋沢 小田急小田原線急行30分→大倉 バス20分）に統一。あわせて新宿・大宮発のバス区間(15分)も他山の検証済み値(20分)に、大宮発の小田急線区間(90分)も新宿発の実際の値(70分)に統一。運賃・時間ともhirugata/tonosaki基準の90分/1,002円・120分/1,530円・78分/930円に統一。 ｜【2026-09-25追加修正】渋沢→大倉バス15分・合計-5分 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G113" s="37" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="F114" s="56" t="inlineStr">
         <is>
-          <t>nabewariと全く同じ「小田急・相鉄直通」バグ（5件目）。nabewariと同一の大倉ゲートウェイのため、同じ修正（hirugata/tonosaki基準の90分/1,002円・120分/1,530円・78分/930円）を適用。 ｜【2026-09-25追加修正】渋沢→大倉バス15分・合計-5分</t>
+          <t>nabewariと全く同じ「小田急・相鉄直通」バグ（5件目）。nabewariと同一の大倉ゲートウェイのため、同じ修正（hirugata/tonosaki基準の90分/1,002円・120分/1,530円・78分/930円）を適用。 ｜【2026-09-25追加修正】渋沢→大倉バス15分・合計-5分 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G114" s="37" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E146" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F146" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性確認済み、問題なし。</t>
+          <t>経路・時間・運賃とも整合性確認済み、問題なし。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G146" s="37" t="inlineStr">
@@ -6449,7 +6449,7 @@
         <v>85</v>
       </c>
       <c r="H2" s="41" t="n">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="I2" s="44" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>115</v>
       </c>
       <c r="K2" s="41" t="n">
-        <v>1492</v>
+        <v>1500</v>
       </c>
       <c r="L2" s="44" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>200</v>
       </c>
       <c r="K3" s="41" t="n">
-        <v>6730</v>
+        <v>6390</v>
       </c>
       <c r="L3" s="44" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>204</v>
       </c>
       <c r="N3" s="41" t="n">
-        <v>6816</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="4" ht="39" customHeight="1" s="30">
@@ -7897,7 +7897,7 @@
         <v>327</v>
       </c>
       <c r="N27" s="41" t="n">
-        <v>10980</v>
+        <v>10540</v>
       </c>
     </row>
     <row r="28" ht="39" customHeight="1" s="30">
@@ -8060,7 +8060,7 @@
         <v>285</v>
       </c>
       <c r="K30" s="41" t="n">
-        <v>9300</v>
+        <v>9630</v>
       </c>
       <c r="L30" s="44" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>289</v>
       </c>
       <c r="N30" s="41" t="n">
-        <v>9300</v>
+        <v>9190</v>
       </c>
     </row>
     <row r="31" ht="39" customHeight="1" s="30">
@@ -8129,7 +8129,7 @@
         <v>289</v>
       </c>
       <c r="N31" s="41" t="n">
-        <v>9330</v>
+        <v>8890</v>
       </c>
     </row>
     <row r="32" ht="39" customHeight="1" s="30">
@@ -8745,7 +8745,7 @@
         <v>85</v>
       </c>
       <c r="H42" s="41" t="n">
-        <v>1002</v>
+        <v>970</v>
       </c>
       <c r="I42" s="44" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>115</v>
       </c>
       <c r="K42" s="41" t="n">
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="L42" s="44" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>85</v>
       </c>
       <c r="H43" s="41" t="n">
-        <v>1002</v>
+        <v>970</v>
       </c>
       <c r="I43" s="44" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>115</v>
       </c>
       <c r="K43" s="41" t="n">
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="L43" s="44" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>275</v>
       </c>
       <c r="K52" s="41" t="n">
-        <v>9428</v>
+        <v>9340</v>
       </c>
       <c r="L52" s="44" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>279</v>
       </c>
       <c r="N52" s="41" t="n">
-        <v>9516</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="53" ht="39" customHeight="1" s="30">
@@ -12034,7 +12034,7 @@
         <v>285</v>
       </c>
       <c r="K101" s="41" t="n">
-        <v>9300</v>
+        <v>9630</v>
       </c>
       <c r="L101" s="44" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>289</v>
       </c>
       <c r="N101" s="41" t="n">
-        <v>9300</v>
+        <v>9190</v>
       </c>
     </row>
     <row r="102" ht="51.75" customHeight="1" s="30">
@@ -12719,7 +12719,7 @@
         <v>85</v>
       </c>
       <c r="H113" s="41" t="n">
-        <v>1002</v>
+        <v>970</v>
       </c>
       <c r="I113" s="44" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>115</v>
       </c>
       <c r="K113" s="41" t="n">
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="L113" s="44" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>85</v>
       </c>
       <c r="H114" s="41" t="n">
-        <v>1002</v>
+        <v>970</v>
       </c>
       <c r="I114" s="44" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>115</v>
       </c>
       <c r="K114" s="41" t="n">
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="L114" s="44" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>180</v>
       </c>
       <c r="K146" s="41" t="n">
-        <v>4867</v>
+        <v>4529</v>
       </c>
       <c r="L146" s="44" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>184</v>
       </c>
       <c r="N146" s="41" t="n">
-        <v>4955</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="147" ht="26.25" customHeight="1" s="30">
@@ -24237,7 +24237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K196"/>
+  <dimension ref="A1:K208"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -35033,8 +35033,668 @@
         </is>
       </c>
     </row>
+    <row r="197" ht="58.2" customHeight="1" s="30">
+      <c r="A197" s="53" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C197" s="53" t="inlineStr">
+        <is>
+          <t>tanzawa</t>
+        </is>
+      </c>
+      <c r="D197" s="54" t="inlineStr">
+        <is>
+          <t>丹沢山</t>
+        </is>
+      </c>
+      <c r="E197" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F197" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（渋沢駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G197" s="55" t="inlineStr">
+        <is>
+          <t>運賃 962/1,492/930円（丹沢山のみIC運賃、他4山は根拠不明の値）</t>
+        </is>
+      </c>
+      <c r="H197" s="55" t="inlineStr">
+        <is>
+          <t>運賃 970/1,500/930円（新宿→渋沢 きっぷ700円、大宮→渋沢 1,230円、横浜→渋沢 660円＋バス270円）</t>
+        </is>
+      </c>
+      <c r="I197" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→渋沢 700円、大宮→渋沢 1,230円、横浜→渋沢 660円）</t>
+        </is>
+      </c>
+      <c r="J197" s="55" t="inlineStr">
+        <is>
+          <t>5山で同一値に統一。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K197" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="58.2" customHeight="1" s="30">
+      <c r="A198" s="53" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C198" s="53" t="inlineStr">
+        <is>
+          <t>tonosaki</t>
+        </is>
+      </c>
+      <c r="D198" s="54" t="inlineStr">
+        <is>
+          <t>塔ノ岳</t>
+        </is>
+      </c>
+      <c r="E198" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F198" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（渋沢駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G198" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,002/1,530/930円（丹沢山のみIC運賃、他4山は根拠不明の値）</t>
+        </is>
+      </c>
+      <c r="H198" s="55" t="inlineStr">
+        <is>
+          <t>運賃 970/1,500/930円（新宿→渋沢 きっぷ700円、大宮→渋沢 1,230円、横浜→渋沢 660円＋バス270円）</t>
+        </is>
+      </c>
+      <c r="I198" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→渋沢 700円、大宮→渋沢 1,230円、横浜→渋沢 660円）</t>
+        </is>
+      </c>
+      <c r="J198" s="55" t="inlineStr">
+        <is>
+          <t>5山で同一値に統一。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K198" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="58.2" customHeight="1" s="30">
+      <c r="A199" s="53" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C199" s="53" t="inlineStr">
+        <is>
+          <t>hirugata</t>
+        </is>
+      </c>
+      <c r="D199" s="54" t="inlineStr">
+        <is>
+          <t>蛭ヶ岳</t>
+        </is>
+      </c>
+      <c r="E199" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F199" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（渋沢駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G199" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,002/1,530/930円（丹沢山のみIC運賃、他4山は根拠不明の値）</t>
+        </is>
+      </c>
+      <c r="H199" s="55" t="inlineStr">
+        <is>
+          <t>運賃 970/1,500/930円（新宿→渋沢 きっぷ700円、大宮→渋沢 1,230円、横浜→渋沢 660円＋バス270円）</t>
+        </is>
+      </c>
+      <c r="I199" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→渋沢 700円、大宮→渋沢 1,230円、横浜→渋沢 660円）</t>
+        </is>
+      </c>
+      <c r="J199" s="55" t="inlineStr">
+        <is>
+          <t>5山で同一値に統一。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K199" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="58.2" customHeight="1" s="30">
+      <c r="A200" s="53" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C200" s="53" t="inlineStr">
+        <is>
+          <t>nabewari</t>
+        </is>
+      </c>
+      <c r="D200" s="54" t="inlineStr">
+        <is>
+          <t>鍋割山</t>
+        </is>
+      </c>
+      <c r="E200" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F200" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（渋沢駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G200" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,002/1,530/930円（丹沢山のみIC運賃、他4山は根拠不明の値）</t>
+        </is>
+      </c>
+      <c r="H200" s="55" t="inlineStr">
+        <is>
+          <t>運賃 970/1,500/930円（新宿→渋沢 きっぷ700円、大宮→渋沢 1,230円、横浜→渋沢 660円＋バス270円）</t>
+        </is>
+      </c>
+      <c r="I200" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→渋沢 700円、大宮→渋沢 1,230円、横浜→渋沢 660円）</t>
+        </is>
+      </c>
+      <c r="J200" s="55" t="inlineStr">
+        <is>
+          <t>5山で同一値に統一。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K200" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="58.2" customHeight="1" s="30">
+      <c r="A201" s="53" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C201" s="53" t="inlineStr">
+        <is>
+          <t>sannotou</t>
+        </is>
+      </c>
+      <c r="D201" s="54" t="inlineStr">
+        <is>
+          <t>三ノ塔</t>
+        </is>
+      </c>
+      <c r="E201" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F201" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（渋沢駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G201" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,002/1,530/930円（丹沢山のみIC運賃、他4山は根拠不明の値）</t>
+        </is>
+      </c>
+      <c r="H201" s="55" t="inlineStr">
+        <is>
+          <t>運賃 970/1,500/930円（新宿→渋沢 きっぷ700円、大宮→渋沢 1,230円、横浜→渋沢 660円＋バス270円）</t>
+        </is>
+      </c>
+      <c r="I201" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→渋沢 700円、大宮→渋沢 1,230円、横浜→渋沢 660円）</t>
+        </is>
+      </c>
+      <c r="J201" s="55" t="inlineStr">
+        <is>
+          <t>5山で同一値に統一。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K201" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="58.2" customHeight="1" s="30">
+      <c r="A202" s="53" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C202" s="53" t="inlineStr">
+        <is>
+          <t>fuji</t>
+        </is>
+      </c>
+      <c r="D202" s="54" t="inlineStr">
+        <is>
+          <t>富士山</t>
+        </is>
+      </c>
+      <c r="E202" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F202" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（河口湖駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G202" s="55" t="inlineStr">
+        <is>
+          <t>運賃 6,200/6,730/6,816円（大宮+528円・横浜+616円の単純加算）</t>
+        </is>
+      </c>
+      <c r="H202" s="55" t="inlineStr">
+        <is>
+          <t>運賃 6,200/6,390/6,390円（大宮・横浜→河口湖 乗車券2,770円で新宿発2,580円との差は+190円）</t>
+        </is>
+      </c>
+      <c r="I202" s="56" t="inlineStr">
+        <is>
+          <t>駅探（大宮→河口湖・横浜→河口湖 2,770円／新宿→河口湖 2,580円）</t>
+        </is>
+      </c>
+      <c r="J202" s="55" t="inlineStr">
+        <is>
+          <t>十二ヶ岳・三ツ峠山と同じ+190円に統一</t>
+        </is>
+      </c>
+      <c r="K202" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="58.2" customHeight="1" s="30">
+      <c r="A203" s="53" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C203" s="53" t="inlineStr">
+        <is>
+          <t>ishiwariyama</t>
+        </is>
+      </c>
+      <c r="D203" s="54" t="inlineStr">
+        <is>
+          <t>石割山</t>
+        </is>
+      </c>
+      <c r="E203" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F203" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（河口湖駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G203" s="55" t="inlineStr">
+        <is>
+          <t>運賃 4,339/4,867/4,955円（大宮+528円・横浜+616円の単純加算）</t>
+        </is>
+      </c>
+      <c r="H203" s="55" t="inlineStr">
+        <is>
+          <t>運賃 4,339/4,529/4,529円（大宮・横浜→河口湖 乗車券2,770円で新宿発2,580円との差は+190円）</t>
+        </is>
+      </c>
+      <c r="I203" s="56" t="inlineStr">
+        <is>
+          <t>駅探（大宮→河口湖・横浜→河口湖 2,770円／新宿→河口湖 2,580円）</t>
+        </is>
+      </c>
+      <c r="J203" s="55" t="inlineStr">
+        <is>
+          <t>十二ヶ岳・三ツ峠山と同じ+190円に統一</t>
+        </is>
+      </c>
+      <c r="K203" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="58.2" customHeight="1" s="30">
+      <c r="A204" s="53" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C204" s="53" t="inlineStr">
+        <is>
+          <t>norikura</t>
+        </is>
+      </c>
+      <c r="D204" s="54" t="inlineStr">
+        <is>
+          <t>乗鞍岳</t>
+        </is>
+      </c>
+      <c r="E204" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F204" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（新島々駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G204" s="55" t="inlineStr">
+        <is>
+          <t>運賃 10,540/10,980/10,980円（山ごとにバラバラの加算額）</t>
+        </is>
+      </c>
+      <c r="H204" s="55" t="inlineStr">
+        <is>
+          <t>運賃 10,540/10,980/10,540円（新島々発のバス代は据え置き。JR部分：新宿・横浜→松本 乗車券4,180円、大宮 4,620円で大宮+440円・横浜±0円）</t>
+        </is>
+      </c>
+      <c r="I204" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→新島々 4,180＋特急2,550＋松本電鉄710円=7,440円、横浜同額、大宮 乗車券4,620円）</t>
+        </is>
+      </c>
+      <c r="J204" s="55" t="inlineStr">
+        <is>
+          <t>5山で同一のオフセットに統一</t>
+        </is>
+      </c>
+      <c r="K204" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="58.2" customHeight="1" s="30">
+      <c r="A205" s="53" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C205" s="53" t="inlineStr">
+        <is>
+          <t>hotaka</t>
+        </is>
+      </c>
+      <c r="D205" s="54" t="inlineStr">
+        <is>
+          <t>奥穂高岳</t>
+        </is>
+      </c>
+      <c r="E205" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F205" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（新島々駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G205" s="55" t="inlineStr">
+        <is>
+          <t>運賃 8,890/9,330/9,330円（山ごとにバラバラの加算額）</t>
+        </is>
+      </c>
+      <c r="H205" s="55" t="inlineStr">
+        <is>
+          <t>運賃 8,890/9,330/8,890円（新島々発のバス代は据え置き。JR部分：新宿・横浜→松本 乗車券4,180円、大宮 4,620円で大宮+440円・横浜±0円）</t>
+        </is>
+      </c>
+      <c r="I205" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→新島々 4,180＋特急2,550＋松本電鉄710円=7,440円、横浜同額、大宮 乗車券4,620円）</t>
+        </is>
+      </c>
+      <c r="J205" s="55" t="inlineStr">
+        <is>
+          <t>5山で同一のオフセットに統一</t>
+        </is>
+      </c>
+      <c r="K205" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="58.2" customHeight="1" s="30">
+      <c r="A206" s="53" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C206" s="53" t="inlineStr">
+        <is>
+          <t>yari</t>
+        </is>
+      </c>
+      <c r="D206" s="54" t="inlineStr">
+        <is>
+          <t>槍ヶ岳</t>
+        </is>
+      </c>
+      <c r="E206" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F206" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（新島々駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G206" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,190/9,300/9,300円（山ごとにバラバラの加算額）</t>
+        </is>
+      </c>
+      <c r="H206" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,190/9,630/9,190円（新島々発のバス代は据え置き。JR部分：新宿・横浜→松本 乗車券4,180円、大宮 4,620円で大宮+440円・横浜±0円）</t>
+        </is>
+      </c>
+      <c r="I206" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→新島々 4,180＋特急2,550＋松本電鉄710円=7,440円、横浜同額、大宮 乗車券4,620円）</t>
+        </is>
+      </c>
+      <c r="J206" s="55" t="inlineStr">
+        <is>
+          <t>5山で同一のオフセットに統一</t>
+        </is>
+      </c>
+      <c r="K206" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="58.2" customHeight="1" s="30">
+      <c r="A207" s="53" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C207" s="53" t="inlineStr">
+        <is>
+          <t>chogatake</t>
+        </is>
+      </c>
+      <c r="D207" s="54" t="inlineStr">
+        <is>
+          <t>蝶ヶ岳</t>
+        </is>
+      </c>
+      <c r="E207" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F207" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（新島々駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G207" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,190/9,300/9,300円（山ごとにバラバラの加算額）</t>
+        </is>
+      </c>
+      <c r="H207" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,190/9,630/9,190円（新島々発のバス代は据え置き。JR部分：新宿・横浜→松本 乗車券4,180円、大宮 4,620円で大宮+440円・横浜±0円）</t>
+        </is>
+      </c>
+      <c r="I207" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→新島々 4,180＋特急2,550＋松本電鉄710円=7,440円、横浜同額、大宮 乗車券4,620円）</t>
+        </is>
+      </c>
+      <c r="J207" s="55" t="inlineStr">
+        <is>
+          <t>5山で同一のオフセットに統一</t>
+        </is>
+      </c>
+      <c r="K207" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="58.2" customHeight="1" s="30">
+      <c r="A208" s="53" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C208" s="53" t="inlineStr">
+        <is>
+          <t>yakedake</t>
+        </is>
+      </c>
+      <c r="D208" s="54" t="inlineStr">
+        <is>
+          <t>焼岳</t>
+        </is>
+      </c>
+      <c r="E208" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F208" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（新島々駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G208" s="55" t="inlineStr">
+        <is>
+          <t>運賃 8,900/9,428/9,516円（山ごとにバラバラの加算額）</t>
+        </is>
+      </c>
+      <c r="H208" s="55" t="inlineStr">
+        <is>
+          <t>運賃 8,900/9,340/8,900円（新島々発のバス代は据え置き。JR部分：新宿・横浜→松本 乗車券4,180円、大宮 4,620円で大宮+440円・横浜±0円）</t>
+        </is>
+      </c>
+      <c r="I208" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→新島々 4,180＋特急2,550＋松本電鉄710円=7,440円、横浜同額、大宮 乗車券4,620円）</t>
+        </is>
+      </c>
+      <c r="J208" s="55" t="inlineStr">
+        <is>
+          <t>5山で同一のオフセットに統一</t>
+        </is>
+      </c>
+      <c r="K208" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K196"/>
+  <autoFilter ref="A1:K208"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -35355,7 +36015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -36100,6 +36760,126 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="129.1" customHeight="1" s="30">
+      <c r="A36" s="56" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="55" t="inlineStr">
+        <is>
+          <t>ルートの他山コピー</t>
+        </is>
+      </c>
+      <c r="C36" s="55" t="inlineStr">
+        <is>
+          <t>takamizusanzan（雲取山）、nokogiriyama_chiba（高尾山）、kintoki（塔ノ岳）、tenzandake/hiwadayama（棒ノ折山）、mitakesan（大岳山）</t>
+        </is>
+      </c>
+      <c r="D36" s="56" t="inlineStr">
+        <is>
+          <t>check_pages.py セクション9（routes[]の完全一致を検出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="129.1" customHeight="1" s="30">
+      <c r="A37" s="56" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="55" t="inlineStr">
+        <is>
+          <t>文章・legs・合計時間の不一致</t>
+        </is>
+      </c>
+      <c r="C37" s="55" t="inlineStr">
+        <is>
+          <t>バス「20分」と「15分」（渋沢→大倉）、雲取山「15分」と「35分」、霧ヶ峰の合計200分と経路160分など</t>
+        </is>
+      </c>
+      <c r="D37" s="56" t="inlineStr">
+        <is>
+          <t>check_pages.py セクション10（trainTimeとlegs合計、trainAccess文章とlegs）。既知の未解決は check_known_issues.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="129.1" customHeight="1" s="30">
+      <c r="A38" s="56" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="55" t="inlineStr">
+        <is>
+          <t>記事・検索ページの駅名の食い違い</t>
+        </is>
+      </c>
+      <c r="C38" s="55" t="inlineStr">
+        <is>
+          <t>大菩薩嶺「塩山駅」と実際の「甲斐大和駅」（8ファイル）</t>
+        </is>
+      </c>
+      <c r="D38" s="56" t="inlineStr">
+        <is>
+          <t>check_pages.py セクション11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="129.1" customHeight="1" s="30">
+      <c r="A39" s="56" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="55" t="inlineStr">
+        <is>
+          <t>規制中の山の掲載</t>
+        </is>
+      </c>
+      <c r="C39" s="55" t="inlineStr">
+        <is>
+          <t>草津白根山が診断・検索ページ5件のおすすめに掲載</t>
+        </is>
+      </c>
+      <c r="D39" s="56" t="inlineStr">
+        <is>
+          <t>status.level=restricted を付与し、check_pages.py セクション13で検出</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="129.1" customHeight="1" s="30">
+      <c r="A40" s="56" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="55" t="inlineStr">
+        <is>
+          <t>全車指定席の特急に「自由席」</t>
+        </is>
+      </c>
+      <c r="C40" s="55" t="inlineStr">
+        <is>
+          <t>中央線記事の「特急あずさ…自由席狙い」</t>
+        </is>
+      </c>
+      <c r="D40" s="56" t="inlineStr">
+        <is>
+          <t>check_pages.py セクション14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="129.1" customHeight="1" s="30">
+      <c r="A41" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t>コース定数の異常値</t>
+        </is>
+      </c>
+      <c r="C41" s="55" t="inlineStr">
+        <is>
+          <t>大岳山FAQ「15〜132」</t>
+        </is>
+      </c>
+      <c r="D41" s="56" t="inlineStr">
+        <is>
+          <t>check_pages.py セクション12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証チェックリスト'!$A$1:$G$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経路・運賃・時間データ一覧'!$A$1:$N$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'バス情報整合性チェック'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$222</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="F27" s="55" t="inlineStr">
         <is>
-          <t>経路は実在。新島々駅〜乗鞍高原観光センターのバス時間が「約30分」表示だったが、実際は「約1時間3分」（アルピコ交通「乗鞍高原線」、1,350円）と倍以上の過小表示だった。乗鞍高原〜畳平シャトルバスも「約60分/未記載運賃」だったが正しくは「約50分・1,750円」。運賃も通し運賃で再計算し、新宿9,570円→10,540円、大宮9,680円→10,980円、横浜9,370円→10,980円に修正（横浜が最安という逆転バグも解消）。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
+          <t>経路は実在。新島々駅〜乗鞍高原観光センターのバス時間が「約30分」表示だったが、実際は「約1時間3分」（アルピコ交通「乗鞍高原線」、1,350円）と倍以上の過小表示だった。乗鞍高原〜畳平シャトルバスも「約60分/未記載運賃」だったが正しくは「約50分・1,750円」。運賃も通し運賃で再計算し、新宿9,570円→10,540円、大宮9,680円→10,980円、横浜9,370円→10,980円に修正（横浜が最安という逆転バグも解消）。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照） ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G27" s="37" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F30" s="55" t="inlineStr">
         <is>
-          <t>横浜発運賃(8,990円)が新宿発(9,190円)より安いという逆転バグを発見（横浜発は新宿経由でさらに距離が長いため物理的に矛盾）。大宮発運賃(9,300円)と揃え9,300円に修正。FAQの横浜運賃表記も連動修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
+          <t>横浜発運賃(8,990円)が新宿発(9,190円)より安いという逆転バグを発見（横浜発は新宿経由でさらに距離が長いため物理的に矛盾）。大宮発運賃(9,300円)と揃え9,300円に修正。FAQの横浜運賃表記も連動修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照） ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G30" s="37" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="F31" s="55" t="inlineStr">
         <is>
-          <t>経路・時間はほぼ正確だったが、横浜発の運賃が新宿発より安い（8,990円&lt;9,190円）逆転バグがあった。JR公式あずさ料金表（新宿-松本6,730円指定席）＋松本電鉄（710円）＋新島々-上高地バス（1,450円）で通し運賃を再計算し、新宿8,890円・大宮/横浜9,330円に修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
+          <t>経路・時間はほぼ正確だったが、横浜発の運賃が新宿発より安い（8,990円&lt;9,190円）逆転バグがあった。JR公式あずさ料金表（新宿-松本6,730円指定席）＋松本電鉄（710円）＋新島々-上高地バス（1,450円）で通し運賃を再計算し、新宿8,890円・大宮/横浜9,330円に修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照） ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G31" s="37" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F50" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも内部整合性を確認（legの合計と表示時間が一致、運賃も出発地間で妥当な差）。修正不要。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照）</t>
+          <t>経路・時間・運賃とも内部整合性を確認（legの合計と表示時間が一致、運賃も出発地間で妥当な差）。修正不要。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照） ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G50" s="37" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="E51" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F51" s="55" t="inlineStr">
         <is>
-          <t>trainAccess=falseだったが実際は穂高駅からタクシー+徒歩で到達可能と判明（笊ヶ岳と同型バグ）。一ノ沢林道は2024年崩落で通行止め中のため代替ルート構築。trainAccess=trueに変更、trainRoutes新規構築。</t>
+          <t>trainAccess=falseだったが実際は穂高駅からタクシー+徒歩で到達可能と判明（笊ヶ岳と同型バグ）。一ノ沢林道は2024年崩落で通行止め中のため代替ルート構築。trainAccess=trueに変更、trainRoutes新規構築。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G51" s="37" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="F52" s="55" t="inlineStr">
         <is>
-          <t>新宿発運賃(6,620円)が実際には「新宿-松本」間の特急あずさ運賃のみに一致しており、その先の松本電鉄上高地線＋アルピコバス（新島々→中の湯）の運賃が完全に欠落した「運賃の構成要素欠落」バグを発見。同一経路を共有するyari（槍ヶ岳）の運賃差分から欠落分(約2,280円)を推定・加算し、新宿8,900円・大宮9,428円・横浜9,516円に修正。FAQも連動修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
+          <t>新宿発運賃(6,620円)が実際には「新宿-松本」間の特急あずさ運賃のみに一致しており、その先の松本電鉄上高地線＋アルピコバス（新島々→中の湯）の運賃が完全に欠落した「運賃の構成要素欠落」バグを発見。同一経路を共有するyari（槍ヶ岳）の運賃差分から欠落分(約2,280円)を推定・加算し、新宿8,900円・大宮9,428円・横浜9,516円に修正。FAQも連動修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照） ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G52" s="37" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E68" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F68" s="55" t="inlineStr">
         <is>
-          <t>経路・legsum・運賃・FAQ全て整合。修正不要。</t>
+          <t>経路・legsum・運賃・FAQ全て整合。修正不要。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G68" s="37" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="F101" s="55" t="inlineStr">
         <is>
-          <t>運賃(6,620円/7,148円/7,236円)が、同一経路のyari（槍ヶ岳）の修正前バグ値ではなく、無関係のyakedake（焼岳、松本電鉄+バス運賃が欠落したバグ値）とまったく同じ数値になっていた「他山の誤データが混入」パターンを発見。同一経路を共有するyariの修正後の正しい運賃（9,190円/9,300円/9,300円）に修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
+          <t>運賃(6,620円/7,148円/7,236円)が、同一経路のyari（槍ヶ岳）の修正前バグ値ではなく、無関係のyakedake（焼岳、松本電鉄+バス運賃が欠落したバグ値）とまったく同じ数値になっていた「他山の誤データが混入」パターンを発見。同一経路を共有するyariの修正後の正しい運賃（9,190円/9,300円/9,300円）に修正。【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照） ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G101" s="37" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="E102" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F102" s="55" t="inlineStr">
         <is>
-          <t>大宮・横浜発の「新宿→穂高(JR中央線・大糸線、松本乗換)」区間が240分と表示されていたが、新宿発自身の内訳（あずさ160分+大糸線30分=190分）や実際のあずさ5号直通時刻（179分）と大きく食い違っていた（約50分の過大表示）。190分に統一。新宿発のバッファ不整合（+50分）も解消。</t>
+          <t>大宮・横浜発の「新宿→穂高(JR中央線・大糸線、松本乗換)」区間が240分と表示されていたが、新宿発自身の内訳（あずさ160分+大糸線30分=190分）や実際のあずさ5号直通時刻（179分）と大きく食い違っていた（約50分の過大表示）。190分に統一。新宿発のバッファ不整合（+50分）も解消。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G102" s="37" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="F103" s="55" t="inlineStr">
         <is>
-          <t>経路・運賃は妥当。大宮発（legsum290+25分）・横浜発（294+25分）のバッファが新宿発（260+20分）の+20分基準と不揃いだったため+20分に統一（大宮315→310分、横浜319→314分）。 ｜【2026-09-25追加修正】扇沢バス40分</t>
+          <t>経路・運賃は妥当。大宮発（legsum290+25分）・横浜発（294+25分）のバッファが新宿発（260+20分）の+20分基準と不揃いだったため+20分に統一（大宮315→310分、横浜319→314分）。 ｜【2026-09-25追加修正】扇沢バス40分 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G103" s="37" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E104" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F104" s="55" t="inlineStr">
         <is>
-          <t>trainAccess=falseだったが、信濃大町駅から裏銀座登山バス（予約不要・季節運行）で七倉登山口まで直通可能と判明。trueに変更、trainRoutes新規構築。</t>
+          <t>trainAccess=falseだったが、信濃大町駅から裏銀座登山バス（予約不要・季節運行）で七倉登山口まで直通可能と判明。trueに変更、trainRoutes新規構築。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G104" s="37" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="E105" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F105" s="55" t="inlineStr">
         <is>
-          <t>烏帽子岳と共通登山口（高瀬ダム）。同理由でtrainAccess=trueに変更、trainRoutes新規構築。</t>
+          <t>烏帽子岳と共通登山口（高瀬ダム）。同理由でtrainAccess=trueに変更、trainRoutes新規構築。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G105" s="37" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F107" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも内部整合性を確認（legの合計と表示時間が一致、運賃も出発地間で妥当な差）。修正不要。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照）</t>
+          <t>経路・時間・運賃とも内部整合性を確認（legの合計と表示時間が一致、運賃も出発地間で妥当な差）。修正不要。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照） ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G107" s="37" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="E142" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F142" s="55" t="inlineStr">
         <is>
-          <t>大宮発は新宿を経由しない独自の直行ルート（JR埼京線・武蔵野線・中央線経由）を使用しており妥当性を確認。新宿発だけバッファ10分、大宮・横浜発は0分という不揃いを発見、新宿基準に統一（大宮119→129分、横浜99→109分）。運賃の並び（新宿1,974円＞大宮1,905円＞横浜1,787円）は大宮の直行ルートがより短距離である可能性と整合するため据え置き。</t>
+          <t>大宮発は新宿を経由しない独自の直行ルート（JR埼京線・武蔵野線・中央線経由）を使用しており妥当性を確認。新宿発だけバッファ10分、大宮・横浜発は0分という不揃いを発見、新宿基準に統一（大宮119→129分、横浜99→109分）。運賃の並び（新宿1,974円＞大宮1,905円＞横浜1,787円）は大宮の直行ルートがより短距離である可能性と整合するため据え置き。 ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額・大宮発経路を統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G142" s="37" t="inlineStr">
@@ -7879,14 +7879,14 @@
       </c>
       <c r="I27" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス「乗鞍高原線」]--&gt; 乗鞍高原観光センター --[畳平シャトルバス（要予約）]--&gt; 畳平（マイカー規制・7/1〜10/31運行）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス「乗鞍高原線」]--&gt; 乗鞍高原観光センター --[畳平シャトルバス（要予約）]--&gt; 畳平（マイカー規制・7/1〜10/31運行）</t>
         </is>
       </c>
       <c r="J27" s="41" t="n">
         <v>323</v>
       </c>
       <c r="K27" s="41" t="n">
-        <v>10980</v>
+        <v>10230</v>
       </c>
       <c r="L27" s="44" t="inlineStr">
         <is>
@@ -8053,14 +8053,14 @@
       </c>
       <c r="I30" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
         </is>
       </c>
       <c r="J30" s="41" t="n">
         <v>285</v>
       </c>
       <c r="K30" s="41" t="n">
-        <v>9630</v>
+        <v>8880</v>
       </c>
       <c r="L30" s="44" t="inlineStr">
         <is>
@@ -8111,14 +8111,14 @@
       </c>
       <c r="I31" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
         </is>
       </c>
       <c r="J31" s="41" t="n">
         <v>285</v>
       </c>
       <c r="K31" s="41" t="n">
-        <v>9330</v>
+        <v>8580</v>
       </c>
       <c r="L31" s="44" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>119</v>
       </c>
       <c r="K50" s="41" t="n">
-        <v>1305</v>
+        <v>1564</v>
       </c>
       <c r="L50" s="44" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>103</v>
       </c>
       <c r="N50" s="41" t="n">
-        <v>1187</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="30">
@@ -9271,14 +9271,14 @@
       </c>
       <c r="I51" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線(特急あずさ)]--&gt; 穂高駅 --[タクシー]--&gt; 林道崩落箇所 --[徒歩]--&gt; 一ノ沢登山口</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR中央本線(特急あずさ)]--&gt; 穂高駅 --[タクシー]--&gt; 林道崩落箇所 --[徒歩]--&gt; 一ノ沢登山口</t>
         </is>
       </c>
       <c r="J51" s="41" t="n">
         <v>270</v>
       </c>
       <c r="K51" s="41" t="n">
-        <v>12780</v>
+        <v>11890</v>
       </c>
       <c r="L51" s="44" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>274</v>
       </c>
       <c r="N51" s="41" t="n">
-        <v>12780</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="52" ht="39" customHeight="1" s="30">
@@ -9329,14 +9329,14 @@
       </c>
       <c r="I52" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 中の湯バス停（季節）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 中の湯バス停（季節）</t>
         </is>
       </c>
       <c r="J52" s="41" t="n">
         <v>275</v>
       </c>
       <c r="K52" s="41" t="n">
-        <v>9340</v>
+        <v>8590</v>
       </c>
       <c r="L52" s="44" t="inlineStr">
         <is>
@@ -10185,14 +10185,14 @@
       </c>
       <c r="I68" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（夏季）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（夏季）</t>
         </is>
       </c>
       <c r="J68" s="41" t="n">
         <v>275</v>
       </c>
       <c r="K68" s="41" t="n">
-        <v>8928</v>
+        <v>8090</v>
       </c>
       <c r="L68" s="44" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>279</v>
       </c>
       <c r="N68" s="41" t="n">
-        <v>9016</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="30">
@@ -12027,14 +12027,14 @@
       </c>
       <c r="I101" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
         </is>
       </c>
       <c r="J101" s="41" t="n">
         <v>285</v>
       </c>
       <c r="K101" s="41" t="n">
-        <v>9630</v>
+        <v>8880</v>
       </c>
       <c r="L101" s="44" t="inlineStr">
         <is>
@@ -12085,14 +12085,14 @@
       </c>
       <c r="I102" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線・大糸線（松本乗換）]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（燕岳経由で大天井岳へ縦走・夏季運行）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR中央線・大糸線（松本乗換）]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（燕岳経由で大天井岳へ縦走・夏季運行）</t>
         </is>
       </c>
       <c r="J102" s="41" t="n">
         <v>275</v>
       </c>
       <c r="K102" s="41" t="n">
-        <v>10428</v>
+        <v>9590</v>
       </c>
       <c r="L102" s="44" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>279</v>
       </c>
       <c r="N102" s="41" t="n">
-        <v>10516</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="103" ht="39" customHeight="1" s="30">
@@ -12143,14 +12143,14 @@
       </c>
       <c r="I103" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 信濃大町駅 --[アルピコ交通バス「扇沢線」]--&gt; 扇沢（季節運行）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 信濃大町駅 --[アルピコ交通バス「扇沢線」]--&gt; 扇沢（季節運行）</t>
         </is>
       </c>
       <c r="J103" s="41" t="n">
         <v>310</v>
       </c>
       <c r="K103" s="41" t="n">
-        <v>9528</v>
+        <v>8690</v>
       </c>
       <c r="L103" s="44" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>314</v>
       </c>
       <c r="N103" s="41" t="n">
-        <v>9616</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="30">
@@ -12201,14 +12201,14 @@
       </c>
       <c r="I104" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR中央線特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
         </is>
       </c>
       <c r="J104" s="41" t="n">
         <v>259</v>
       </c>
       <c r="K104" s="41" t="n">
-        <v>9780</v>
+        <v>8890</v>
       </c>
       <c r="L104" s="44" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>263</v>
       </c>
       <c r="N104" s="41" t="n">
-        <v>9780</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="30">
@@ -12259,14 +12259,14 @@
       </c>
       <c r="I105" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR中央線特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
         </is>
       </c>
       <c r="J105" s="41" t="n">
         <v>259</v>
       </c>
       <c r="K105" s="41" t="n">
-        <v>9780</v>
+        <v>8890</v>
       </c>
       <c r="L105" s="44" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>263</v>
       </c>
       <c r="N105" s="41" t="n">
-        <v>9780</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="106" ht="26.25" customHeight="1" s="30">
@@ -12382,7 +12382,7 @@
         <v>119</v>
       </c>
       <c r="K107" s="41" t="n">
-        <v>2502</v>
+        <v>2164</v>
       </c>
       <c r="L107" s="44" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>99</v>
       </c>
       <c r="N107" s="41" t="n">
-        <v>2590</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="108" ht="26.25" customHeight="1" s="30">
@@ -14412,7 +14412,7 @@
         <v>129</v>
       </c>
       <c r="K142" s="41" t="n">
-        <v>1905</v>
+        <v>2164</v>
       </c>
       <c r="L142" s="44" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>109</v>
       </c>
       <c r="N142" s="41" t="n">
-        <v>1787</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="143" ht="26.25" customHeight="1" s="30">
@@ -24237,7 +24237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K208"/>
+  <dimension ref="A1:K222"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -35693,8 +35693,778 @@
         </is>
       </c>
     </row>
+    <row r="209" ht="58.2" customHeight="1" s="30">
+      <c r="A209" s="53" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C209" s="53" t="inlineStr">
+        <is>
+          <t>norikura</t>
+        </is>
+      </c>
+      <c r="D209" s="54" t="inlineStr">
+        <is>
+          <t>乗鞍岳</t>
+        </is>
+      </c>
+      <c r="E209" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F209" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G209" s="55" t="inlineStr">
+        <is>
+          <t>運賃 10,540/10,980/10,540円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H209" s="55" t="inlineStr">
+        <is>
+          <t>運賃 10,540/10,230/10,540円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I209" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J209" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K209" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="58.2" customHeight="1" s="30">
+      <c r="A210" s="53" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C210" s="53" t="inlineStr">
+        <is>
+          <t>hotaka</t>
+        </is>
+      </c>
+      <c r="D210" s="54" t="inlineStr">
+        <is>
+          <t>奥穂高岳</t>
+        </is>
+      </c>
+      <c r="E210" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F210" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G210" s="55" t="inlineStr">
+        <is>
+          <t>運賃 8,890/9,330/8,890円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H210" s="55" t="inlineStr">
+        <is>
+          <t>運賃 8,890/8,580/8,890円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I210" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J210" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K210" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="58.2" customHeight="1" s="30">
+      <c r="A211" s="53" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C211" s="53" t="inlineStr">
+        <is>
+          <t>yari</t>
+        </is>
+      </c>
+      <c r="D211" s="54" t="inlineStr">
+        <is>
+          <t>槍ヶ岳</t>
+        </is>
+      </c>
+      <c r="E211" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F211" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G211" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,190/9,630/9,190円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H211" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,190/8,880/9,190円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I211" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J211" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K211" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="58.2" customHeight="1" s="30">
+      <c r="A212" s="53" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C212" s="53" t="inlineStr">
+        <is>
+          <t>chogatake</t>
+        </is>
+      </c>
+      <c r="D212" s="54" t="inlineStr">
+        <is>
+          <t>蝶ヶ岳</t>
+        </is>
+      </c>
+      <c r="E212" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F212" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G212" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,190/9,630/9,190円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H212" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,190/8,880/9,190円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I212" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J212" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K212" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="58.2" customHeight="1" s="30">
+      <c r="A213" s="53" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C213" s="53" t="inlineStr">
+        <is>
+          <t>yakedake</t>
+        </is>
+      </c>
+      <c r="D213" s="54" t="inlineStr">
+        <is>
+          <t>焼岳</t>
+        </is>
+      </c>
+      <c r="E213" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F213" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G213" s="55" t="inlineStr">
+        <is>
+          <t>運賃 8,900/9,340/8,900円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H213" s="55" t="inlineStr">
+        <is>
+          <t>運賃 8,900/8,590/8,900円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I213" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J213" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K213" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="58.2" customHeight="1" s="30">
+      <c r="A214" s="53" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C214" s="53" t="inlineStr">
+        <is>
+          <t>jonengatake</t>
+        </is>
+      </c>
+      <c r="D214" s="54" t="inlineStr">
+        <is>
+          <t>常念岳</t>
+        </is>
+      </c>
+      <c r="E214" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F214" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G214" s="55" t="inlineStr">
+        <is>
+          <t>運賃 12,200/12,780/12,780円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H214" s="55" t="inlineStr">
+        <is>
+          <t>運賃 12,200/11,890/12,200円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I214" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J214" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K214" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="58.2" customHeight="1" s="30">
+      <c r="A215" s="53" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C215" s="53" t="inlineStr">
+        <is>
+          <t>arikayama</t>
+        </is>
+      </c>
+      <c r="D215" s="54" t="inlineStr">
+        <is>
+          <t>有明山</t>
+        </is>
+      </c>
+      <c r="E215" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F215" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G215" s="55" t="inlineStr">
+        <is>
+          <t>運賃 8,400/8,928/9,016円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H215" s="55" t="inlineStr">
+        <is>
+          <t>運賃 8,400/8,090/8,400円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I215" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J215" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K215" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="58.2" customHeight="1" s="30">
+      <c r="A216" s="53" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C216" s="53" t="inlineStr">
+        <is>
+          <t>otenshoudake</t>
+        </is>
+      </c>
+      <c r="D216" s="54" t="inlineStr">
+        <is>
+          <t>大天井岳</t>
+        </is>
+      </c>
+      <c r="E216" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F216" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G216" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,900/10,428/10,516円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H216" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,900/9,590/9,900円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I216" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J216" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K216" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="58.2" customHeight="1" s="30">
+      <c r="A217" s="53" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C217" s="53" t="inlineStr">
+        <is>
+          <t>harinokidake</t>
+        </is>
+      </c>
+      <c r="D217" s="54" t="inlineStr">
+        <is>
+          <t>針ノ木岳</t>
+        </is>
+      </c>
+      <c r="E217" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F217" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G217" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,000/9,528/9,616円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H217" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,000/8,690/9,000円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I217" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J217" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K217" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="58.2" customHeight="1" s="30">
+      <c r="A218" s="53" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C218" s="53" t="inlineStr">
+        <is>
+          <t>eboshidake_kita</t>
+        </is>
+      </c>
+      <c r="D218" s="54" t="inlineStr">
+        <is>
+          <t>烏帽子岳（北ア）</t>
+        </is>
+      </c>
+      <c r="E218" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F218" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G218" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,200/9,780/9,780円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H218" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,200/8,890/9,200円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I218" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J218" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K218" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="58.2" customHeight="1" s="30">
+      <c r="A219" s="53" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C219" s="53" t="inlineStr">
+        <is>
+          <t>noguchigoro</t>
+        </is>
+      </c>
+      <c r="D219" s="54" t="inlineStr">
+        <is>
+          <t>野口五郎岳</t>
+        </is>
+      </c>
+      <c r="E219" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F219" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（松本方面ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G219" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,200/9,780/9,780円（大宮+440〜580円・横浜+0〜616円の混在）。大宮：湘南新宿ライン→新宿→あずさ</t>
+        </is>
+      </c>
+      <c r="H219" s="55" t="inlineStr">
+        <is>
+          <t>運賃 9,200/8,890/9,200円（大宮＝新宿発−310円、横浜＝新宿発と同額）。大宮：武蔵野線・中央線→立川→あずさ（時間は同等）</t>
+        </is>
+      </c>
+      <c r="I219" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→穂高 4,620＋特急2,550=7,170円／横浜 同額／大宮 立川乗車 4,620＋2,240=6,860円、信濃大町 5,060円で同様、新島々も同様）</t>
+        </is>
+      </c>
+      <c r="J219" s="55" t="inlineStr">
+        <is>
+          <t>旧値との差を確認。11山で同一オフセット</t>
+        </is>
+      </c>
+      <c r="K219" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="58.2" customHeight="1" s="30">
+      <c r="A220" s="53" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C220" s="53" t="inlineStr">
+        <is>
+          <t>otake</t>
+        </is>
+      </c>
+      <c r="D220" s="54" t="inlineStr">
+        <is>
+          <t>大岳山</t>
+        </is>
+      </c>
+      <c r="E220" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F220" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（御嶽駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G220" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,374/1,305/1,187円（大宮・横浜が新宿発より安い／単純加算が山ごとにバラバラ）</t>
+        </is>
+      </c>
+      <c r="H220" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,374/1,564/1,744円（大宮＝新宿発+190円、横浜＝+370円）</t>
+        </is>
+      </c>
+      <c r="I220" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→御嶽 1,040円／大宮 1,230円／横浜 1,410円）</t>
+        </is>
+      </c>
+      <c r="J220" s="55" t="inlineStr">
+        <is>
+          <t>奥多摩群の+180/+370円パターンと整合。新宿発の基準値（1,040円）との44円差は未解消</t>
+        </is>
+      </c>
+      <c r="K220" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="58.2" customHeight="1" s="30">
+      <c r="A221" s="53" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C221" s="53" t="inlineStr">
+        <is>
+          <t>mitakesan</t>
+        </is>
+      </c>
+      <c r="D221" s="54" t="inlineStr">
+        <is>
+          <t>御岳山</t>
+        </is>
+      </c>
+      <c r="E221" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F221" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（御嶽駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G221" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,974/2,502/2,590円（大宮・横浜が新宿発より安い／単純加算が山ごとにバラバラ）</t>
+        </is>
+      </c>
+      <c r="H221" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,974/2,164/2,344円（大宮＝新宿発+190円、横浜＝+370円）</t>
+        </is>
+      </c>
+      <c r="I221" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→御嶽 1,040円／大宮 1,230円／横浜 1,410円）</t>
+        </is>
+      </c>
+      <c r="J221" s="55" t="inlineStr">
+        <is>
+          <t>奥多摩群の+180/+370円パターンと整合。新宿発の基準値（1,040円）との44円差は未解消</t>
+        </is>
+      </c>
+      <c r="K221" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="58.2" customHeight="1" s="30">
+      <c r="A222" s="53" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C222" s="53" t="inlineStr">
+        <is>
+          <t>hinodesaan</t>
+        </is>
+      </c>
+      <c r="D222" s="54" t="inlineStr">
+        <is>
+          <t>日の出山</t>
+        </is>
+      </c>
+      <c r="E222" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F222" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜（御嶽駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G222" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,974/1,905/1,787円（大宮・横浜が新宿発より安い／単純加算が山ごとにバラバラ）</t>
+        </is>
+      </c>
+      <c r="H222" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,974/2,164/2,344円（大宮＝新宿発+190円、横浜＝+370円）</t>
+        </is>
+      </c>
+      <c r="I222" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→御嶽 1,040円／大宮 1,230円／横浜 1,410円）</t>
+        </is>
+      </c>
+      <c r="J222" s="55" t="inlineStr">
+        <is>
+          <t>奥多摩群の+180/+370円パターンと整合。新宿発の基準値（1,040円）との44円差は未解消</t>
+        </is>
+      </c>
+      <c r="K222" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K208"/>
+  <autoFilter ref="A1:K222"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証チェックリスト'!$A$1:$G$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経路・運賃・時間データ一覧'!$A$1:$N$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'バス情報整合性チェック'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$232</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -2948,12 +2948,12 @@
       </c>
       <c r="E63" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F63" s="56" t="inlineStr">
         <is>
-          <t>trainRoutesの経路・時間・運賃データは内部整合性あり（legの合計と表示時間が完全一致）。ただし**FAQ本文の所要時間が実データと全く違う値だった**（新宿: FAQ「約3時間55分」vs 実データ160分=2時間40分、75分もの差）。ontakesan・myokoと同じ新パターンのバグ。FAQ文言のみ修正。</t>
+          <t>trainRoutesの経路・時間・運賃データは内部整合性あり（legの合計と表示時間が完全一致）。ただし**FAQ本文の所要時間が実データと全く違う値だった**（新宿: FAQ「約3時間55分」vs 実データ160分=2時間40分、75分もの差）。ontakesan・myokoと同じ新パターンのバグ。FAQ文言のみ修正。 ｜【2026-09-26追加修正】同一ゲートウェイの経路・時間・運賃差額を駅探で再検証し統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G63" s="37" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="E66" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F66" s="55" t="inlineStr">
         <is>
-          <t>FAQが「公共交通機関なし・車必須」と誤案内していたが、実際は早川町乗合バス+予約制乗合タクシーで到達可能（trainRoutesデータは元々正しかった）。タクシー区間20→10分に修正。FAQ全面修正。</t>
+          <t>FAQが「公共交通機関なし・車必須」と誤案内していたが、実際は早川町乗合バス+予約制乗合タクシーで到達可能（trainRoutesデータは元々正しかった）。タクシー区間20→10分に修正。FAQ全面修正。 ｜【2026-09-26追加修正】同一ゲートウェイの経路・時間・運賃差額を駅探で再検証し統一（修正履歴参照） ｜【2026-09-26】乗合タクシーを約20分に訂正</t>
         </is>
       </c>
       <c r="G66" s="37" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E88" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F88" s="55" t="inlineStr">
         <is>
-          <t>trainAccess=falseだったが、静岡駅からバス/タクシー+東海フォレスト送迎バス（要山小屋予約）で椹島まで到達可能と判明。trueに変更、trainRoutes新規構築。</t>
+          <t>trainAccess=falseだったが、静岡駅からバス/タクシー+東海フォレスト送迎バス（要山小屋予約）で椹島まで到達可能と判明。trueに変更、trainRoutes新規構築。 ｜【2026-09-26追加修正】同一ゲートウェイの経路・時間・運賃差額を駅探で再検証し統一（修正履歴参照） ｜【2026-09-26】2026年の運行期間・運賃で注記を更新、新宿発運賃の内訳（5,940＋5,000円）を確認</t>
         </is>
       </c>
       <c r="G88" s="37" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="E89" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F89" s="55" t="inlineStr">
         <is>
-          <t>荒川岳と共通登山口（椹島）。同理由でtrainAccess=trueに変更、trainRoutes新規構築。</t>
+          <t>荒川岳と共通登山口（椹島）。同理由でtrainAccess=trueに変更、trainRoutes新規構築。 ｜【2026-09-26追加修正】同一ゲートウェイの経路・時間・運賃差額を駅探で再検証し統一（修正履歴参照） ｜【2026-09-26】2026年の運行期間・運賃で注記を更新、新宿発運賃の内訳（5,940＋5,000円）を確認</t>
         </is>
       </c>
       <c r="G89" s="37" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="E90" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F90" s="55" t="inlineStr">
         <is>
-          <t>荒川岳・赤石岳と同一の畑薙第一ダム経由（降車地=聖沢登山口）。trainAccess=trueに変更、trainRoutes新規構築。</t>
+          <t>荒川岳・赤石岳と同一の畑薙第一ダム経由（降車地=聖沢登山口）。trainAccess=trueに変更、trainRoutes新規構築。 ｜【2026-09-26追加修正】同一ゲートウェイの経路・時間・運賃差額を駅探で再検証し統一（修正履歴参照） ｜【2026-09-26】2026年の運行期間・運賃で注記を更新、新宿発運賃の内訳（5,940＋5,000円）を確認</t>
         </is>
       </c>
       <c r="G90" s="37" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="E95" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F95" s="55" t="inlineStr">
         <is>
-          <t>重大な経路誤り。nokogiriyamaと同一の「甲府→広河原」データが誤って流用されていたが、正しい登山口は「奈良田」（新宿→身延→はやかわ乗合バス経由）。全面再構築。</t>
+          <t>重大な経路誤り。nokogiriyamaと同一の「甲府→広河原」データが誤って流用されていたが、正しい登山口は「奈良田」（新宿→身延→はやかわ乗合バス経由）。全面再構築。 ｜【2026-09-26追加修正】同一ゲートウェイの経路・時間・運賃差額を駅探で再検証し統一（修正履歴参照）</t>
         </is>
       </c>
       <c r="G95" s="37" t="inlineStr">
@@ -9908,36 +9908,36 @@
       </c>
       <c r="F63" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR特急ふじかわ]--&gt; 身延駅 --[早川町乗合バス]--&gt; 羽衣登山口（季節）</t>
+          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 羽衣登山口（季節）</t>
         </is>
       </c>
       <c r="G63" s="41" t="n">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="H63" s="41" t="n">
         <v>5520</v>
       </c>
       <c r="I63" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR特急ふじかわ]--&gt; 身延駅 --[早川町乗合バス]--&gt; 羽衣登山口（季節）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 羽衣登山口（季節）</t>
         </is>
       </c>
       <c r="J63" s="41" t="n">
-        <v>190</v>
+        <v>248</v>
       </c>
       <c r="K63" s="41" t="n">
-        <v>6048</v>
+        <v>4960</v>
       </c>
       <c r="L63" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR特急ふじかわ]--&gt; 身延駅 --[早川町乗合バス]--&gt; 羽衣登山口（季節）</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 羽衣登山口（季節）</t>
         </is>
       </c>
       <c r="M63" s="41" t="n">
-        <v>194</v>
+        <v>252</v>
       </c>
       <c r="N63" s="41" t="n">
-        <v>6136</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="30">
@@ -10082,36 +10082,36 @@
       </c>
       <c r="F66" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR特急ふじかわ]--&gt; 身延駅 --[早川町乗合バス]--&gt; 大島バス停 --[予約制乗合タクシー]--&gt; 老平登山口</t>
+          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 大島バス停 --[予約制乗合タクシー]--&gt; 老平登山口</t>
         </is>
       </c>
       <c r="G66" s="41" t="n">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="H66" s="41" t="n">
         <v>7520</v>
       </c>
       <c r="I66" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR特急ふじかわ]--&gt; 身延駅 --[早川町乗合バス]--&gt; 大島バス停 --[予約制乗合タクシー]--&gt; 老平登山口</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 大島バス停 --[予約制乗合タクシー]--&gt; 老平登山口</t>
         </is>
       </c>
       <c r="J66" s="41" t="n">
-        <v>220</v>
+        <v>288</v>
       </c>
       <c r="K66" s="41" t="n">
-        <v>8048</v>
+        <v>6960</v>
       </c>
       <c r="L66" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR特急ふじかわ]--&gt; 身延駅 --[早川町乗合バス]--&gt; 大島バス停 --[予約制乗合タクシー]--&gt; 老平登山口</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 大島バス停 --[予約制乗合タクシー]--&gt; 老平登山口</t>
         </is>
       </c>
       <c r="M66" s="41" t="n">
-        <v>224</v>
+        <v>292</v>
       </c>
       <c r="N66" s="41" t="n">
-        <v>8136</v>
+        <v>7520</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="30">
@@ -11266,21 +11266,21 @@
         </is>
       </c>
       <c r="G88" s="41" t="n">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="H88" s="41" t="n">
         <v>10940</v>
       </c>
       <c r="I88" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR山手線]--&gt; 品川駅 --[東海道新幹線ひかり]--&gt; 静岡駅 --[静鉄ジャストライン南アルプス登山線(季節運行)/乗合タクシー]--&gt; 畑薙第一ダム --[特種東海フォレスト送迎バス(要予約・対象宿泊者)]--&gt; 椹島ロッヂ</t>
+          <t>大宮駅 --[JR上野東京ライン]--&gt; 東京駅 --[東海道新幹線ひかり]--&gt; 静岡駅 --[静鉄ジャストライン南アルプス登山線(季節運行)/乗合タクシー]--&gt; 畑薙第一ダム --[特種東海フォレスト送迎バス(要予約・対象宿泊者)]--&gt; 椹島ロッヂ</t>
         </is>
       </c>
       <c r="J88" s="41" t="n">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="K88" s="41" t="n">
-        <v>11520</v>
+        <v>11300</v>
       </c>
       <c r="L88" s="44" t="inlineStr">
         <is>
@@ -11288,10 +11288,10 @@
         </is>
       </c>
       <c r="M88" s="41" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="N88" s="41" t="n">
-        <v>10450</v>
+        <v>10180</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="30">
@@ -11324,21 +11324,21 @@
         </is>
       </c>
       <c r="G89" s="41" t="n">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="H89" s="41" t="n">
         <v>10940</v>
       </c>
       <c r="I89" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR山手線]--&gt; 品川駅 --[東海道新幹線ひかり]--&gt; 静岡駅 --[静鉄ジャストライン南アルプス登山線(季節運行)/乗合タクシー]--&gt; 畑薙第一ダム --[特種東海フォレスト送迎バス(要予約・対象宿泊者)]--&gt; 椹島ロッヂ</t>
+          <t>大宮駅 --[JR上野東京ライン]--&gt; 東京駅 --[東海道新幹線ひかり]--&gt; 静岡駅 --[静鉄ジャストライン南アルプス登山線(季節運行)/乗合タクシー]--&gt; 畑薙第一ダム --[特種東海フォレスト送迎バス(要予約・対象宿泊者)]--&gt; 椹島ロッヂ</t>
         </is>
       </c>
       <c r="J89" s="41" t="n">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="K89" s="41" t="n">
-        <v>11520</v>
+        <v>11300</v>
       </c>
       <c r="L89" s="44" t="inlineStr">
         <is>
@@ -11346,10 +11346,10 @@
         </is>
       </c>
       <c r="M89" s="41" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="N89" s="41" t="n">
-        <v>10450</v>
+        <v>10180</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="30">
@@ -11382,21 +11382,21 @@
         </is>
       </c>
       <c r="G90" s="41" t="n">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="H90" s="41" t="n">
         <v>10940</v>
       </c>
       <c r="I90" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR山手線]--&gt; 品川駅 --[東海道新幹線ひかり]--&gt; 静岡駅 --[静鉄ジャストライン南アルプス登山線(季節運行)/乗合タクシー]--&gt; 畑薙第一ダム --[特種東海フォレスト送迎バス(要予約・対象宿泊者)]--&gt; 聖沢登山口</t>
+          <t>大宮駅 --[JR上野東京ライン]--&gt; 東京駅 --[東海道新幹線ひかり]--&gt; 静岡駅 --[静鉄ジャストライン南アルプス登山線(季節運行)/乗合タクシー]--&gt; 畑薙第一ダム --[特種東海フォレスト送迎バス(要予約・対象宿泊者)]--&gt; 聖沢登山口</t>
         </is>
       </c>
       <c r="J90" s="41" t="n">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K90" s="41" t="n">
-        <v>11520</v>
+        <v>11300</v>
       </c>
       <c r="L90" s="44" t="inlineStr">
         <is>
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="M90" s="41" t="n">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="N90" s="41" t="n">
-        <v>10450</v>
+        <v>10180</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="30">
@@ -11668,36 +11668,36 @@
       </c>
       <c r="F95" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR特急ふじかわ]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 奈良田温泉 --[徒歩]--&gt; 農鳥岳登山口（大門沢登山口）</t>
+          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 奈良田温泉 --[徒歩]--&gt; 農鳥岳登山口（大門沢登山口）</t>
         </is>
       </c>
       <c r="G95" s="41" t="n">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="H95" s="41" t="n">
         <v>6770</v>
       </c>
       <c r="I95" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR特急ふじかわ]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 奈良田温泉 --[徒歩]--&gt; 農鳥岳登山口（大門沢登山口）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 奈良田温泉 --[徒歩]--&gt; 農鳥岳登山口（大門沢登山口）</t>
         </is>
       </c>
       <c r="J95" s="41" t="n">
-        <v>290</v>
+        <v>348</v>
       </c>
       <c r="K95" s="41" t="n">
-        <v>7320</v>
+        <v>6210</v>
       </c>
       <c r="L95" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR特急ふじかわ]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 奈良田温泉 --[徒歩]--&gt; 農鳥岳登山口（大門沢登山口）</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 奈良田温泉 --[徒歩]--&gt; 農鳥岳登山口（大門沢登山口）</t>
         </is>
       </c>
       <c r="M95" s="41" t="n">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="N95" s="41" t="n">
-        <v>7290</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="30">
@@ -24237,7 +24237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K222"/>
+  <dimension ref="A1:K232"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -36463,8 +36463,558 @@
         </is>
       </c>
     </row>
+    <row r="223" ht="58.2" customHeight="1" s="30">
+      <c r="A223" s="53" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C223" s="53" t="inlineStr">
+        <is>
+          <t>nanaitsurasan</t>
+        </is>
+      </c>
+      <c r="D223" s="54" t="inlineStr">
+        <is>
+          <t>七面山</t>
+        </is>
+      </c>
+      <c r="E223" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合・経路実在性</t>
+        </is>
+      </c>
+      <c r="F223" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（身延駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G223" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 5,520/6,048/6,136円・160/190/194分。特急ふじかわ（特急券別途）を前提にした時間で運賃と不整合。大宮・横浜は単純加算（+528/+616円）</t>
+        </is>
+      </c>
+      <c r="H223" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 5,520/4,960/5,520円・218/248/252分。あずさ・かいじ＋身延線（普通、乗換込み107分）に統一。大宮＝立川からのかいじで新宿発−560円、横浜＝新宿発と同額</t>
+        </is>
+      </c>
+      <c r="I223" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→身延 乗車券3,520＋特急1,580=5,100円・3h18、大宮 立川からのかいじ 3,520＋1,020=4,540円）</t>
+        </is>
+      </c>
+      <c r="J223" s="55" t="inlineStr">
+        <is>
+          <t>旧新宿発運賃=5,100円+バス代で整合。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K223" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="58.2" customHeight="1" s="30">
+      <c r="A224" s="53" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C224" s="53" t="inlineStr">
+        <is>
+          <t>yarigatake2</t>
+        </is>
+      </c>
+      <c r="D224" s="54" t="inlineStr">
+        <is>
+          <t>笊ヶ岳</t>
+        </is>
+      </c>
+      <c r="E224" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合・経路実在性</t>
+        </is>
+      </c>
+      <c r="F224" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（身延駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G224" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 7,520/8,048/8,136円・190/220/224分。特急ふじかわ（特急券別途）を前提にした時間で運賃と不整合。大宮・横浜は単純加算（+528/+616円）</t>
+        </is>
+      </c>
+      <c r="H224" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 7,520/6,960/7,520円・248/278/282分。あずさ・かいじ＋身延線（普通、乗換込み107分）に統一。大宮＝立川からのかいじで新宿発−560円、横浜＝新宿発と同額</t>
+        </is>
+      </c>
+      <c r="I224" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→身延 乗車券3,520＋特急1,580=5,100円・3h18、大宮 立川からのかいじ 3,520＋1,020=4,540円）</t>
+        </is>
+      </c>
+      <c r="J224" s="55" t="inlineStr">
+        <is>
+          <t>旧新宿発運賃=5,100円+バス代で整合。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K224" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="58.2" customHeight="1" s="30">
+      <c r="A225" s="53" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C225" s="53" t="inlineStr">
+        <is>
+          <t>noutori</t>
+        </is>
+      </c>
+      <c r="D225" s="54" t="inlineStr">
+        <is>
+          <t>農鳥岳</t>
+        </is>
+      </c>
+      <c r="E225" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合・経路実在性</t>
+        </is>
+      </c>
+      <c r="F225" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（身延駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G225" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 6,770/7,320/7,290円・260/290/294分。特急ふじかわ（特急券別途）を前提にした時間で運賃と不整合。大宮・横浜は単純加算（+528/+616円）。trainAccess文が「甲府駅→広河原線」（広河原）の別経路</t>
+        </is>
+      </c>
+      <c r="H225" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 6,770/6,210/6,770円・318/348/352分。あずさ・かいじ＋身延線（普通、乗換込み107分）に統一。大宮＝立川からのかいじで新宿発−560円、横浜＝新宿発と同額</t>
+        </is>
+      </c>
+      <c r="I225" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→身延 乗車券3,520＋特急1,580=5,100円・3h18、大宮 立川からのかいじ 3,520＋1,020=4,540円）</t>
+        </is>
+      </c>
+      <c r="J225" s="55" t="inlineStr">
+        <is>
+          <t>旧新宿発運賃=5,100円+バス代で整合。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K225" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="58.2" customHeight="1" s="30">
+      <c r="A226" s="53" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C226" s="53" t="inlineStr">
+        <is>
+          <t>arakawadake</t>
+        </is>
+      </c>
+      <c r="D226" s="54" t="inlineStr">
+        <is>
+          <t>荒川岳</t>
+        </is>
+      </c>
+      <c r="E226" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F226" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（静岡駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G226" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 10,940/11,520/10,450円・341/371/323分（大宮+580円・横浜−490円）。大宮：湘南新宿ライン→新宿→山手線→品川</t>
+        </is>
+      </c>
+      <c r="H226" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 10,940/11,300/10,180円・353/379/328分。新宿発は据え置き、大宮＝上野東京ライン→東京→ひかり（+360円）、横浜＝新横浜→ひかり（−760円）、新幹線は乗換込みの所要時間</t>
+        </is>
+      </c>
+      <c r="I226" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→静岡 乗車券3,410＋ひかり自由席2,530=5,940円・1h23／大宮 3,770＋2,530=6,300円・1h49／横浜 2,650＋2,530=5,180円・58分）</t>
+        </is>
+      </c>
+      <c r="J226" s="55" t="inlineStr">
+        <is>
+          <t>新宿発の内訳（自由席基準5,940＋バス）は据え置き。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K226" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="58.2" customHeight="1" s="30">
+      <c r="A227" s="53" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C227" s="53" t="inlineStr">
+        <is>
+          <t>akaisidake</t>
+        </is>
+      </c>
+      <c r="D227" s="54" t="inlineStr">
+        <is>
+          <t>赤石岳</t>
+        </is>
+      </c>
+      <c r="E227" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F227" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（静岡駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G227" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 10,940/11,520/10,450円・341/371/323分（大宮+580円・横浜−490円）。大宮：湘南新宿ライン→新宿→山手線→品川</t>
+        </is>
+      </c>
+      <c r="H227" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 10,940/11,300/10,180円・353/379/328分。新宿発は据え置き、大宮＝上野東京ライン→東京→ひかり（+360円）、横浜＝新横浜→ひかり（−760円）、新幹線は乗換込みの所要時間</t>
+        </is>
+      </c>
+      <c r="I227" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→静岡 乗車券3,410＋ひかり自由席2,530=5,940円・1h23／大宮 3,770＋2,530=6,300円・1h49／横浜 2,650＋2,530=5,180円・58分）</t>
+        </is>
+      </c>
+      <c r="J227" s="55" t="inlineStr">
+        <is>
+          <t>新宿発の内訳（自由席基準5,940＋バス）は据え置き。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K227" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="58.2" customHeight="1" s="30">
+      <c r="A228" s="53" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C228" s="53" t="inlineStr">
+        <is>
+          <t>hijiridade</t>
+        </is>
+      </c>
+      <c r="D228" s="54" t="inlineStr">
+        <is>
+          <t>聖岳</t>
+        </is>
+      </c>
+      <c r="E228" s="54" t="inlineStr">
+        <is>
+          <t>共有ハブ駅の横断的不整合</t>
+        </is>
+      </c>
+      <c r="F228" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜（静岡駅ゲートウェイ）</t>
+        </is>
+      </c>
+      <c r="G228" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 10,940/11,520/10,450円・326/356/308分（大宮+580円・横浜−490円）。大宮：湘南新宿ライン→新宿→山手線→品川</t>
+        </is>
+      </c>
+      <c r="H228" s="55" t="inlineStr">
+        <is>
+          <t>経路・運賃・時間 10,940/11,300/10,180円・338/364/313分。新宿発は据え置き、大宮＝上野東京ライン→東京→ひかり（+360円）、横浜＝新横浜→ひかり（−760円）、新幹線は乗換込みの所要時間</t>
+        </is>
+      </c>
+      <c r="I228" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→静岡 乗車券3,410＋ひかり自由席2,530=5,940円・1h23／大宮 3,770＋2,530=6,300円・1h49／横浜 2,650＋2,530=5,180円・58分）</t>
+        </is>
+      </c>
+      <c r="J228" s="55" t="inlineStr">
+        <is>
+          <t>新宿発の内訳（自由席基準5,940＋バス）は据え置き。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K228" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="58.2" customHeight="1" s="30">
+      <c r="A229" s="53" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C229" s="53" t="inlineStr">
+        <is>
+          <t>yarigatake2</t>
+        </is>
+      </c>
+      <c r="D229" s="54" t="inlineStr">
+        <is>
+          <t>笊ヶ岳</t>
+        </is>
+      </c>
+      <c r="E229" s="54" t="inlineStr">
+        <is>
+          <t>バス/徒歩区間の時間過小表示</t>
+        </is>
+      </c>
+      <c r="F229" s="54" t="inlineStr">
+        <is>
+          <t>大島バス停→老平登山口</t>
+        </is>
+      </c>
+      <c r="G229" s="55" t="inlineStr">
+        <is>
+          <t>予約制乗合タクシー 10分（文章は20分、FAQは10分と食い違い）</t>
+        </is>
+      </c>
+      <c r="H229" s="55" t="inlineStr">
+        <is>
+          <t>乗合タクシー 約20分（停留所「馬場」＝老平登山口）に統一。合計 新宿258/大宮288/横浜292分</t>
+        </is>
+      </c>
+      <c r="I229" s="56" t="inlineStr">
+        <is>
+          <t>早川町乗合タクシー案内（大島→馬場 約20分）、山旅ガイド（馬場停留所は登山口直下）</t>
+        </is>
+      </c>
+      <c r="J229" s="55" t="inlineStr">
+        <is>
+          <t>文章・FAQ・経路データを同期。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K229" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="58.2" customHeight="1" s="30">
+      <c r="A230" s="53" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C230" s="53" t="inlineStr">
+        <is>
+          <t>arakawadake</t>
+        </is>
+      </c>
+      <c r="D230" s="54" t="inlineStr">
+        <is>
+          <t>荒川岳</t>
+        </is>
+      </c>
+      <c r="E230" s="54" t="inlineStr">
+        <is>
+          <t>バス運賃・時間</t>
+        </is>
+      </c>
+      <c r="F230" s="54" t="inlineStr">
+        <is>
+          <t>静岡駅→畑薙第一ダム／畑薙→椹島</t>
+        </is>
+      </c>
+      <c r="G230" s="55" t="inlineStr">
+        <is>
+          <t>注記：バス「7月中旬〜8月中旬」、乗合タクシー「約8,500円」、送迎バス「7/11〜10/13」（2026年の一次情報で未確認）</t>
+        </is>
+      </c>
+      <c r="H230" s="55" t="inlineStr">
+        <is>
+          <t>静鉄バス南アルプス登山線 2026年7/16〜8/16・5,000円・約3時間20分、千代田タクシー乗合 8,500円（7/18〜8/31毎日・9月は日祝）、特種東海フォレスト送迎バス 無料（素泊まり以上の宿泊者のみ）2026年7/11〜10/12。新宿発合計10,940円＝電車5,940円＋バス5,000円で内訳を確認</t>
+        </is>
+      </c>
+      <c r="I230" s="56" t="inlineStr">
+        <is>
+          <t>TRAIN &amp; TRAIL 南アルプス公共交通機関まとめ（2026年版）、千代田タクシー</t>
+        </is>
+      </c>
+      <c r="J230" s="55" t="inlineStr">
+        <is>
+          <t>新宿発の内訳が5,940＋5,000円で整合</t>
+        </is>
+      </c>
+      <c r="K230" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="58.2" customHeight="1" s="30">
+      <c r="A231" s="53" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C231" s="53" t="inlineStr">
+        <is>
+          <t>akaisidake</t>
+        </is>
+      </c>
+      <c r="D231" s="54" t="inlineStr">
+        <is>
+          <t>赤石岳</t>
+        </is>
+      </c>
+      <c r="E231" s="54" t="inlineStr">
+        <is>
+          <t>バス運賃・時間</t>
+        </is>
+      </c>
+      <c r="F231" s="54" t="inlineStr">
+        <is>
+          <t>静岡駅→畑薙第一ダム／畑薙→椹島</t>
+        </is>
+      </c>
+      <c r="G231" s="55" t="inlineStr">
+        <is>
+          <t>注記：バス「7月中旬〜8月中旬」、乗合タクシー「約8,500円」、送迎バス「7/11〜10/13」（2026年の一次情報で未確認）</t>
+        </is>
+      </c>
+      <c r="H231" s="55" t="inlineStr">
+        <is>
+          <t>静鉄バス南アルプス登山線 2026年7/16〜8/16・5,000円・約3時間20分、千代田タクシー乗合 8,500円（7/18〜8/31毎日・9月は日祝）、特種東海フォレスト送迎バス 無料（素泊まり以上の宿泊者のみ）2026年7/11〜10/12。新宿発合計10,940円＝電車5,940円＋バス5,000円で内訳を確認</t>
+        </is>
+      </c>
+      <c r="I231" s="56" t="inlineStr">
+        <is>
+          <t>TRAIN &amp; TRAIL 南アルプス公共交通機関まとめ（2026年版）、千代田タクシー</t>
+        </is>
+      </c>
+      <c r="J231" s="55" t="inlineStr">
+        <is>
+          <t>新宿発の内訳が5,940＋5,000円で整合</t>
+        </is>
+      </c>
+      <c r="K231" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="58.2" customHeight="1" s="30">
+      <c r="A232" s="53" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C232" s="53" t="inlineStr">
+        <is>
+          <t>hijiridade</t>
+        </is>
+      </c>
+      <c r="D232" s="54" t="inlineStr">
+        <is>
+          <t>聖岳</t>
+        </is>
+      </c>
+      <c r="E232" s="54" t="inlineStr">
+        <is>
+          <t>バス運賃・時間</t>
+        </is>
+      </c>
+      <c r="F232" s="54" t="inlineStr">
+        <is>
+          <t>静岡駅→畑薙第一ダム／畑薙→椹島</t>
+        </is>
+      </c>
+      <c r="G232" s="55" t="inlineStr">
+        <is>
+          <t>注記：バス「7月中旬〜8月中旬」、乗合タクシー「約8,500円」、送迎バス「7/11〜10/13」（2026年の一次情報で未確認）</t>
+        </is>
+      </c>
+      <c r="H232" s="55" t="inlineStr">
+        <is>
+          <t>静鉄バス南アルプス登山線 2026年7/16〜8/16・5,000円・約3時間20分、千代田タクシー乗合 8,500円（7/18〜8/31毎日・9月は日祝）、特種東海フォレスト送迎バス 無料（素泊まり以上の宿泊者のみ）2026年7/11〜10/12。新宿発合計10,940円＝電車5,940円＋バス5,000円で内訳を確認</t>
+        </is>
+      </c>
+      <c r="I232" s="56" t="inlineStr">
+        <is>
+          <t>TRAIN &amp; TRAIL 南アルプス公共交通機関まとめ（2026年版）、千代田タクシー</t>
+        </is>
+      </c>
+      <c r="J232" s="55" t="inlineStr">
+        <is>
+          <t>新宿発の内訳が5,940＋5,000円で整合</t>
+        </is>
+      </c>
+      <c r="K232" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K222"/>
+  <autoFilter ref="A1:K232"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証チェックリスト'!$A$1:$G$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経路・運賃・時間データ一覧'!$A$1:$N$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'バス情報整合性チェック'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$247</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E44" s="53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F44" s="55" t="inlineStr">
         <is>
-          <t>時間・運賃は整合性確認済み。noteに「2026年6月改正でバスは土日祝全便運休・平日朝のみ運行」という重大な制約が記載されているにも関わらず、バッジが「年中運行」のままで実態と矛盾していたため、⚠️「バスは平日朝のみ運行」の警告バッジに修正。 ｜【2026-09-25追加修正】藤野→陣馬登山口バスを4分に統一（他ページ9件も）</t>
+          <t>時間・運賃は整合性確認済み。noteに「2026年6月改正でバスは土日祝全便運休・平日朝のみ運行」という重大な制約が記載されているにも関わらず、バッジが「年中運行」のままで実態と矛盾していたため、⚠️「バスは平日朝のみ運行」の警告バッジに修正。 ｜【2026-09-25追加修正】藤野→陣馬登山口バスを4分に統一（他ページ9件も） ｜【2026-09-26】経路・時間・運賃を駅探・公式情報で再検証して更新（修正履歴参照）</t>
         </is>
       </c>
       <c r="G44" s="37" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="E45" s="53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F45" s="55" t="inlineStr">
         <is>
-          <t>横浜発のバッファ（legsum120分+0分）が新宿発（130+30分）・大宮発（160+30分）の+30分基準と不揃いだったため150分（120+30）に統一。FAQ本文の最寄りバス停表記が「仙石原バス停」という誤記だったため正しい「金時神社入口バス停」に修正。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照）</t>
+          <t>横浜発のバッファ（legsum120分+0分）が新宿発（130+30分）・大宮発（160+30分）の+30分基準と不揃いだったため150分（120+30）に統一。FAQ本文の最寄りバス停表記が「仙石原バス停」という誤記だったため正しい「金時神社入口バス停」に修正。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照） ｜【2026-09-26】経路・時間・運賃を駅探・公式情報で再検証して更新（修正履歴参照）</t>
         </is>
       </c>
       <c r="G45" s="37" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="E65" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F65" s="55" t="inlineStr">
         <is>
-          <t>経路・運賃とも整合性を確認、問題なし。大宮・横浜発の所要時間バッファ（+25分）は秩父鉄道方面への複数経路をまとめた表記のため妥当と判断、修正不要。</t>
+          <t>経路・運賃とも整合性を確認、問題なし。大宮・横浜発の所要時間バッファ（+25分）は秩父鉄道方面への複数経路をまとめた表記のため妥当と判断、修正不要。 ｜【2026-09-26】経路・時間・運賃を駅探・公式情報で再検証して更新（修正履歴参照）</t>
         </is>
       </c>
       <c r="G65" s="37" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="E76" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F76" s="55" t="inlineStr">
         <is>
-          <t>横浜発の「東京→上越妙高」区間が124分と表示されていたが、新宿発の同一区間（東京→上越妙高）は105分で19分の食い違い（実際のはくたか最短106分の調査から105分が正）。修正しtrainTimeYokohama 232→206分に、バッファも他区間と統一。FAQの横浜所要時間表記も3時間52分→3時間26分に修正。</t>
+          <t>横浜発の「東京→上越妙高」区間が124分と表示されていたが、新宿発の同一区間（東京→上越妙高）は105分で19分の食い違い（実際のはくたか最短106分の調査から105分が正）。修正しtrainTimeYokohama 232→206分に、バッファも他区間と統一。FAQの横浜所要時間表記も3時間52分→3時間26分に修正。 ｜【2026-09-26】経路・時間・運賃を駅探・公式情報で再検証して更新（修正履歴参照）</t>
         </is>
       </c>
       <c r="G76" s="37" t="inlineStr">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="E122" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F122" s="55" t="inlineStr">
         <is>
-          <t>全156山のYahoo!乗換案内リンク一斉点検でto=パラメータが空になっていたバグを発見（to=岩井駅に修正）。加えて、iyogatakeと同じ岩井駅ゲートウェイを共有する横浜発fareが780円と不自然に安く、115〜135分の電車乗車に対して過小（電車のみでバス不要の区間）。横浜-木更津の実運賃2,090円を基準に2,420円に修正。</t>
+          <t>全156山のYahoo!乗換案内リンク一斉点検でto=パラメータが空になっていたバグを発見（to=岩井駅に修正）。加えて、iyogatakeと同じ岩井駅ゲートウェイを共有する横浜発fareが780円と不自然に安く、115〜135分の電車乗車に対して過小（電車のみでバス不要の区間）。横浜-木更津の実運賃2,090円を基準に2,420円に修正。 ｜【2026-09-26】経路・時間・運賃を駅探・公式情報で再検証して更新（修正履歴参照）</t>
         </is>
       </c>
       <c r="G122" s="37" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E124" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F124" s="55" t="inlineStr">
         <is>
-          <t>横浜発運賃(3,376円)が実際の横浜-湯河原実運賃(1,410円)＋バス代を大幅に超過し、逆に大宮発(3,288円)や新宿発(2,760円)からも運賃の並びが実距離（横浜70km＜新宿89km＜大宮120km）と矛盾していた重度の運賃バグを発見。実際のJR運賃（新宿2,090円・大宮2,420円・横浜1,410円）から逆算し、大宮3,090円・横浜2,080円に修正（新宿は据え置き）。</t>
+          <t>横浜発運賃(3,376円)が実際の横浜-湯河原実運賃(1,410円)＋バス代を大幅に超過し、逆に大宮発(3,288円)や新宿発(2,760円)からも運賃の並びが実距離（横浜70km＜新宿89km＜大宮120km）と矛盾していた重度の運賃バグを発見。実際のJR運賃（新宿2,090円・大宮2,420円・横浜1,410円）から逆算し、大宮3,090円・横浜2,080円に修正（新宿は据え置き）。 ｜【2026-09-26】経路・時間・運賃を駅探・公式情報で再検証して更新（修正履歴参照）</t>
         </is>
       </c>
       <c r="G124" s="37" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="E151" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F151" s="55" t="inlineStr">
         <is>
-          <t>大宮発ルートが本来不要な「新宿経由」で迂回していた（adatara/tanigawa/makihataと同型のバグ）。大宮→宇都宮の直通JR東北本線（宇都宮線）76分・1,410円のルートに再構築。運賃も迂回分過大だった3,168円→1,960円に修正、所要時間も179分→135分（レグ合計111分＋24分バッファ、他区間の慣例に統一）に修正。</t>
+          <t>大宮発ルートが本来不要な「新宿経由」で迂回していた（adatara/tanigawa/makihataと同型のバグ）。大宮→宇都宮の直通JR東北本線（宇都宮線）76分・1,410円のルートに再構築。運賃も迂回分過大だった3,168円→1,960円に修正、所要時間も179分→135分（レグ合計111分＋24分バッファ、他区間の慣例に統一）に修正。 ｜【2026-09-26】経路・時間・運賃を駅探・公式情報で再検証して更新（修正履歴参照）</t>
         </is>
       </c>
       <c r="G151" s="37" t="inlineStr">
@@ -6252,8 +6252,6 @@
         </is>
       </c>
     </row>
-    <row r="158"/>
-    <row r="159"/>
     <row r="160" ht="15" customHeight="1" s="30">
       <c r="A160" s="39" t="inlineStr">
         <is>
@@ -8854,36 +8852,36 @@
       </c>
       <c r="F44" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線]--&gt; 藤野駅 --[神奈川中央交通バス「野08」]--&gt; 陣馬登山口</t>
+          <t>新宿駅 --[JR中央線（高尾乗換込み）]--&gt; 藤野駅 --[神奈川中央交通バス「野08」]--&gt; 陣馬登山口</t>
         </is>
       </c>
       <c r="G44" s="41" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="H44" s="41" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="I44" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線]--&gt; 藤野駅 --[神奈川中央交通バス「野08」]--&gt; 陣馬登山口</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（西国分寺・高尾乗換込み）]--&gt; 藤野駅 --[神奈川中央交通バス「野08」]--&gt; 陣馬登山口</t>
         </is>
       </c>
       <c r="J44" s="41" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="K44" s="41" t="n">
-        <v>1728</v>
+        <v>1440</v>
       </c>
       <c r="L44" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線]--&gt; 藤野駅 --[神奈川中央交通バス「野08」]--&gt; 陣馬登山口</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子・高尾乗換込み）]--&gt; 藤野駅 --[神奈川中央交通バス「野08」]--&gt; 陣馬登山口</t>
         </is>
       </c>
       <c r="M44" s="41" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="N44" s="41" t="n">
-        <v>1816</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="45" ht="26.25" customHeight="1" s="30">
@@ -8912,36 +8910,36 @@
       </c>
       <c r="F45" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[小田急ロマンスカー]--&gt; 箱根湯本駅 --[箱根登山バス]--&gt; 金時神社入口（またはバスタ新宿→高速バス直通）</t>
+          <t>新宿駅（バスタ新宿） --[小田急ハイウェイバス「新宿〜御殿場・箱根線」]--&gt; 金時登山口（金時神社入口・乙女口にも停車）</t>
         </is>
       </c>
       <c r="G45" s="41" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="H45" s="41" t="n">
-        <v>3420</v>
+        <v>1940</v>
       </c>
       <c r="I45" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急ロマンスカー]--&gt; 箱根湯本駅 --[箱根登山バス]--&gt; 金時神社入口</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅（バスタ新宿） --[小田急ハイウェイバス「新宿〜御殿場・箱根線」]--&gt; 金時登山口（金時神社入口・乙女口にも停車）</t>
         </is>
       </c>
       <c r="J45" s="41" t="n">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="K45" s="41" t="n">
-        <v>3948</v>
+        <v>2470</v>
       </c>
       <c r="L45" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線・小田急線]--&gt; 箱根湯本駅 --[箱根登山バス]--&gt; 金時神社入口</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅（バスタ新宿） --[小田急ハイウェイバス「新宿〜御殿場・箱根線」]--&gt; 金時登山口（金時神社入口・乙女口にも停車）</t>
         </is>
       </c>
       <c r="M45" s="41" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="N45" s="41" t="n">
-        <v>4036</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="46" ht="39" customHeight="1" s="30">
@@ -10024,36 +10022,36 @@
       </c>
       <c r="F65" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線・八高線他]--&gt; 秩父駅 --[秩父鉄道]--&gt; 三峰口駅 --[西武観光バス「三峯神社線」]--&gt; 秩父湖バス停</t>
+          <t>新宿駅 --[JR・西武池袋線・秩父鉄道（池袋・飯能・西武秩父乗換込み）]--&gt; 三峰口駅 --[西武観光バス「三峯神社線」]--&gt; 秩父湖バス停</t>
         </is>
       </c>
       <c r="G65" s="41" t="n">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="H65" s="41" t="n">
-        <v>2100</v>
+        <v>2080</v>
       </c>
       <c r="I65" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR八高線他]--&gt; 三峰口駅 --[西武観光バス「三峯神社線」]--&gt; 秩父湖バス停</t>
+          <t>大宮駅 --[JR高崎線・秩父鉄道（熊谷乗換込み）]--&gt; 三峰口駅 --[西武観光バス「三峯神社線」]--&gt; 秩父湖バス停</t>
         </is>
       </c>
       <c r="J65" s="41" t="n">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="K65" s="41" t="n">
-        <v>2628</v>
+        <v>2250</v>
       </c>
       <c r="L65" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン他]--&gt; 三峰口駅 --[西武観光バス「三峯神社線」]--&gt; 秩父湖バス停</t>
+          <t>横浜駅 --[JR・西武池袋線・秩父鉄道（池袋・飯能・西武秩父乗換込み）]--&gt; 三峰口駅 --[西武観光バス「三峯神社線」]--&gt; 秩父湖バス停</t>
         </is>
       </c>
       <c r="M65" s="41" t="n">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="N65" s="41" t="n">
-        <v>2716</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="66" ht="39" customHeight="1" s="30">
@@ -10614,36 +10612,36 @@
       </c>
       <c r="F76" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線はくたか（東京駅乗換）]--&gt; 上越妙高駅 --[えちごトキめき鉄道]--&gt; 妙高高原駅</t>
+          <t>新宿駅 --[JR湘南新宿ライン（大宮乗換込み）]--&gt; 大宮駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 妙高高原駅 --[頸南バス「笹ヶ峰直行バス」]--&gt; 笹ヶ峰（季節運行）</t>
         </is>
       </c>
       <c r="G76" s="41" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="H76" s="41" t="n">
-        <v>10200</v>
+        <v>9200</v>
       </c>
       <c r="I76" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線はくたか]--&gt; 上越妙高駅 --[えちごトキめき鉄道]--&gt; 妙高高原駅</t>
+          <t>大宮駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 妙高高原駅 --[頸南バス「笹ヶ峰直行バス」]--&gt; 笹ヶ峰（季節運行）</t>
         </is>
       </c>
       <c r="J76" s="41" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="K76" s="41" t="n">
-        <v>9830</v>
+        <v>8540</v>
       </c>
       <c r="L76" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線はくたか]--&gt; 上越妙高駅 --[えちごトキめき鉄道]--&gt; 妙高高原駅</t>
+          <t>横浜駅 --[JR上野東京ライン（上野乗換込み）]--&gt; 上野駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 妙高高原駅 --[頸南バス「笹ヶ峰直行バス」]--&gt; 笹ヶ峰（季節運行）</t>
         </is>
       </c>
       <c r="M76" s="41" t="n">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="N76" s="41" t="n">
-        <v>10330</v>
+        <v>9680</v>
       </c>
     </row>
     <row r="77" ht="39" customHeight="1" s="30">
@@ -13234,36 +13232,36 @@
       </c>
       <c r="F122" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線・総武線快速]--&gt; 千葉駅 --[JR内房線]--&gt; 岩井駅 --[徒歩]--&gt; 福満寺（富山登山口）</t>
+          <t>新宿駅 --[JR総武線快速・内房線（千葉・君津乗換込み）]--&gt; 岩井駅 --[徒歩]--&gt; 福満寺（富山登山口）</t>
         </is>
       </c>
       <c r="G122" s="41" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H122" s="41" t="n">
-        <v>1980</v>
+        <v>2090</v>
       </c>
       <c r="I122" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR内房線]--&gt; 岩井駅 --[徒歩]--&gt; 福満寺（富山登山口）</t>
+          <t>大宮駅 --[JR上野東京ライン・総武線快速・内房線（東京・千葉・君津乗換込み）]--&gt; 岩井駅 --[徒歩]--&gt; 福満寺（富山登山口）</t>
         </is>
       </c>
       <c r="J122" s="41" t="n">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="K122" s="41" t="n">
-        <v>2508</v>
+        <v>2750</v>
       </c>
       <c r="L122" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線・総武線・内房線(君津・木更津経由)]--&gt; 岩井駅 --[徒歩]--&gt; 福満寺（富山登山口）</t>
+          <t>横浜駅 --[JR横須賀線・総武線快速・内房線（千葉・君津乗換込み）]--&gt; 岩井駅 --[徒歩]--&gt; 福満寺（富山登山口）</t>
         </is>
       </c>
       <c r="M122" s="41" t="n">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="N122" s="41" t="n">
-        <v>2420</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="123" ht="26.25" customHeight="1" s="30">
@@ -13350,36 +13348,36 @@
       </c>
       <c r="F124" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR湘南新宿ライン・東海道本線]--&gt; 湯河原駅 --[箱根登山バス]--&gt; 宮城野支所前</t>
+          <t>新宿駅 --[小田急小田原線（快速急行）]--&gt; 小田原駅 --[箱根登山バス「桃源台線」]--&gt; 宮城野支所前 --[徒歩]--&gt; 明神ヶ岳登山口（宮城野）</t>
         </is>
       </c>
       <c r="G124" s="41" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H124" s="41" t="n">
-        <v>2760</v>
+        <v>1700</v>
       </c>
       <c r="I124" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 湯河原駅 --[箱根登山バス]--&gt; 宮城野支所前</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急小田原線（快速急行）]--&gt; 小田原駅 --[箱根登山バス「桃源台線」]--&gt; 宮城野支所前 --[徒歩]--&gt; 明神ヶ岳登山口（宮城野）</t>
         </is>
       </c>
       <c r="J124" s="41" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="K124" s="41" t="n">
-        <v>3090</v>
+        <v>2230</v>
       </c>
       <c r="L124" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 湯河原駅 --[箱根登山バス]--&gt; 宮城野支所前</t>
+          <t>横浜駅 --[JR東海道本線]--&gt; 小田原駅 --[箱根登山バス「桃源台線」]--&gt; 宮城野支所前 --[徒歩]--&gt; 明神ヶ岳登山口（宮城野）</t>
         </is>
       </c>
       <c r="M124" s="41" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N124" s="41" t="n">
-        <v>2080</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="125" ht="39" customHeight="1" s="30">
@@ -14916,36 +14914,36 @@
       </c>
       <c r="F151" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR東北本線]--&gt; 宇都宮駅 --[関東バス]--&gt; 古賀志山登山口</t>
+          <t>新宿駅 --[JR湘南新宿ライン・宇都宮線]--&gt; 宇都宮駅 --[関東自動車バス47番]--&gt; 森林公園入口 --[徒歩]--&gt; 宇都宮市森林公園駐車場</t>
         </is>
       </c>
       <c r="G151" s="41" t="n">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="H151" s="41" t="n">
-        <v>2640</v>
+        <v>2730</v>
       </c>
       <c r="I151" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR東北本線（宇都宮線）]--&gt; 宇都宮駅 --[関東バス]--&gt; 古賀志山登山口</t>
+          <t>大宮駅 --[JR宇都宮線（東北本線快速）]--&gt; 宇都宮駅 --[関東自動車バス47番]--&gt; 森林公園入口 --[徒歩]--&gt; 宇都宮市森林公園駐車場</t>
         </is>
       </c>
       <c r="J151" s="41" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="K151" s="41" t="n">
-        <v>1960</v>
+        <v>2050</v>
       </c>
       <c r="L151" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR東北本線]--&gt; 宇都宮駅 --[関東バス]--&gt; 古賀志山登山口</t>
+          <t>横浜駅 --[JR湘南新宿ライン・宇都宮線]--&gt; 宇都宮駅 --[関東自動車バス47番]--&gt; 森林公園入口 --[徒歩]--&gt; 宇都宮市森林公園駐車場</t>
         </is>
       </c>
       <c r="M151" s="41" t="n">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="N151" s="41" t="n">
-        <v>3256</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="152" ht="39" customHeight="1" s="30">
@@ -24237,7 +24235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K232"/>
+  <dimension ref="A1:K247"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -37013,8 +37011,833 @@
         </is>
       </c>
     </row>
+    <row r="233" ht="58.2" customHeight="1" s="30">
+      <c r="A233" s="53" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C233" s="53" t="inlineStr">
+        <is>
+          <t>kintoki</t>
+        </is>
+      </c>
+      <c r="D233" s="54" t="inlineStr">
+        <is>
+          <t>金時山</t>
+        </is>
+      </c>
+      <c r="E233" s="54" t="inlineStr">
+        <is>
+          <t>経路実在性・最適ルート化</t>
+        </is>
+      </c>
+      <c r="F233" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G233" s="55" t="inlineStr">
+        <is>
+          <t>ロマンスカー→箱根湯本→箱根登山バス（3,420/3,948/4,036円・160/190/150分）。検索ページ7件は存在しない「新松田駅→箱根登山バス」</t>
+        </is>
+      </c>
+      <c r="H233" s="55" t="inlineStr">
+        <is>
+          <t>小田急ハイウェイバス バスタ新宿→金時登山口（乗換なし・約125分・1,940円）。大宮・横浜発はJRで新宿へ（1,940/2,470/2,560円・125/157/157分）。電車ルートは注記に併記</t>
+        </is>
+      </c>
+      <c r="I233" s="56" t="inlineStr">
+        <is>
+          <t>TOZAN GUCHI/箱根ナビ（金時登山口 L線約25分、ハイウェイバス1,940円）、駅探（大宮→新宿 530円、横浜→新宿 620円・32分）</t>
+        </is>
+      </c>
+      <c r="J233" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件（時間・駅名の既知の未解決から除外）</t>
+        </is>
+      </c>
+      <c r="K233" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="58.2" customHeight="1" s="30">
+      <c r="A234" s="53" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C234" s="53" t="inlineStr">
+        <is>
+          <t>myojingatake</t>
+        </is>
+      </c>
+      <c r="D234" s="54" t="inlineStr">
+        <is>
+          <t>明神ヶ岳</t>
+        </is>
+      </c>
+      <c r="E234" s="54" t="inlineStr">
+        <is>
+          <t>経路実在性</t>
+        </is>
+      </c>
+      <c r="F234" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G234" s="55" t="inlineStr">
+        <is>
+          <t>湯河原駅→箱根登山バス→宮城野支所前（2,760/3,090/2,080円・126/156/100分）。trailhead/trainInfoは小田原経由と矛盾</t>
+        </is>
+      </c>
+      <c r="H234" s="55" t="inlineStr">
+        <is>
+          <t>小田急で小田原→箱根登山バス桃源台線（約30分・790円）→宮城野支所前→徒歩約10分（1,700/2,230/1,830円・134/166/97分）</t>
+        </is>
+      </c>
+      <c r="I234" s="56" t="inlineStr">
+        <is>
+          <t>登山口ねっと（宮城野・桃源台線 790円）、駅探（新宿→小田原 910円・94分、横浜→小田原 1,040円・57分）</t>
+        </is>
+      </c>
+      <c r="J234" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件（時間・駅名の既知の未解決から除外）</t>
+        </is>
+      </c>
+      <c r="K234" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="58.2" customHeight="1" s="30">
+      <c r="A235" s="53" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C235" s="53" t="inlineStr">
+        <is>
+          <t>jinba</t>
+        </is>
+      </c>
+      <c r="D235" s="54" t="inlineStr">
+        <is>
+          <t>陣馬山</t>
+        </is>
+      </c>
+      <c r="E235" s="54" t="inlineStr">
+        <is>
+          <t>時間・運賃</t>
+        </is>
+      </c>
+      <c r="F235" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G235" s="55" t="inlineStr">
+        <is>
+          <t>経路データの新宿→藤野が33分（表示74分）。運賃 1,200/1,728/1,816円・74/104/108分</t>
+        </is>
+      </c>
+      <c r="H235" s="55" t="inlineStr">
+        <is>
+          <t>1,250/1,440/1,440円・62/93/87分（新宿→藤野 58分・1,040円＋バス210円、大宮 89分・1,230円、横浜 83分・1,230円）</t>
+        </is>
+      </c>
+      <c r="I235" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿→藤野 1,040円・58分／大宮 1,230円・89分／横浜 1,230円・83分）</t>
+        </is>
+      </c>
+      <c r="J235" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件（時間・駅名の既知の未解決から除外）</t>
+        </is>
+      </c>
+      <c r="K235" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="58.2" customHeight="1" s="30">
+      <c r="A236" s="53" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C236" s="53" t="inlineStr">
+        <is>
+          <t>nakawarayama</t>
+        </is>
+      </c>
+      <c r="D236" s="54" t="inlineStr">
+        <is>
+          <t>和名倉山</t>
+        </is>
+      </c>
+      <c r="E236" s="54" t="inlineStr">
+        <is>
+          <t>時間・運賃</t>
+        </is>
+      </c>
+      <c r="F236" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G236" s="55" t="inlineStr">
+        <is>
+          <t>大宮・横浜発の経路データが短すぎ。2,100/2,628/2,716円・165/195/200分</t>
+        </is>
+      </c>
+      <c r="H236" s="55" t="inlineStr">
+        <is>
+          <t>2,100/2,270/2,620円・204/177/242分（新宿 164分1,500円、大宮 熊谷経由 137分1,670円、横浜 202分2,020円＋バス約600円）</t>
+        </is>
+      </c>
+      <c r="I236" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿・大宮・横浜→三峰口）</t>
+        </is>
+      </c>
+      <c r="J236" s="55" t="inlineStr">
+        <is>
+          <t>新宿発運賃は駅探の最安1,500円で整合</t>
+        </is>
+      </c>
+      <c r="K236" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="58.2" customHeight="1" s="30">
+      <c r="A237" s="53" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C237" s="53" t="inlineStr">
+        <is>
+          <t>hiuchi</t>
+        </is>
+      </c>
+      <c r="D237" s="54" t="inlineStr">
+        <is>
+          <t>火打山</t>
+        </is>
+      </c>
+      <c r="E237" s="54" t="inlineStr">
+        <is>
+          <t>経路・時間・運賃</t>
+        </is>
+      </c>
+      <c r="F237" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G237" s="55" t="inlineStr">
+        <is>
+          <t>上越妙高経由（10,200/9,830/10,330円・203/183/206分）。バス30分（実際は約50分・1,000円）</t>
+        </is>
+      </c>
+      <c r="H237" s="55" t="inlineStr">
+        <is>
+          <t>長野経由（北陸新幹線→しなの鉄道北しなの線）に変更。新宿発2時間46分・8,200円、バス50分・1,000円（9,200/8,540/9,680円・216/173/243分）</t>
+        </is>
+      </c>
+      <c r="I237" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿・大宮・横浜→妙高高原）、頸南バス（妙高高原駅〜笹ヶ峰 1,000円・約50分）</t>
+        </is>
+      </c>
+      <c r="J237" s="55" t="inlineStr">
+        <is>
+          <t>指定席基準。大宮発は自由席の駅探値7,010円＋指定席差額530円で換算</t>
+        </is>
+      </c>
+      <c r="K237" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="58.2" customHeight="1" s="30">
+      <c r="A238" s="53" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C238" s="53" t="inlineStr">
+        <is>
+          <t>tomisan</t>
+        </is>
+      </c>
+      <c r="D238" s="54" t="inlineStr">
+        <is>
+          <t>富山</t>
+        </is>
+      </c>
+      <c r="E238" s="54" t="inlineStr">
+        <is>
+          <t>運賃・時間</t>
+        </is>
+      </c>
+      <c r="F238" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G238" s="55" t="inlineStr">
+        <is>
+          <t>運賃 1,980/2,508/2,420円・199/229/224分（新宿発1,980円は旧値。横浜発の経路データが短すぎ）</t>
+        </is>
+      </c>
+      <c r="H238" s="55" t="inlineStr">
+        <is>
+          <t>2,090/2,750/2,750円・197/210/201分（新宿 2,090円・167分、大宮 2,750円・180分、横浜 2,750円・171分＋徒歩30分）</t>
+        </is>
+      </c>
+      <c r="I238" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿・大宮・横浜→岩井駅）</t>
+        </is>
+      </c>
+      <c r="J238" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件（時間・駅名の既知の未解決から除外）</t>
+        </is>
+      </c>
+      <c r="K238" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="58.2" customHeight="1" s="30">
+      <c r="A239" s="53" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C239" s="53" t="inlineStr">
+        <is>
+          <t>kogashiyama</t>
+        </is>
+      </c>
+      <c r="D239" s="54" t="inlineStr">
+        <is>
+          <t>古賀志山</t>
+        </is>
+      </c>
+      <c r="E239" s="54" t="inlineStr">
+        <is>
+          <t>時間・運賃</t>
+        </is>
+      </c>
+      <c r="F239" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G239" s="55" t="inlineStr">
+        <is>
+          <t>新宿→宇都宮が90分（実際112分）、横浜発2,970円未満など。2,640/1,960/3,256円・149/135/183分</t>
+        </is>
+      </c>
+      <c r="H239" s="55" t="inlineStr">
+        <is>
+          <t>2,640/1,960/2,970円・147/100/169分（新宿 湘南新宿ライン・宇都宮線112分、大宮 65分1,410円、横浜 134分2,420円＋バス約550円）</t>
+        </is>
+      </c>
+      <c r="I239" s="56" t="inlineStr">
+        <is>
+          <t>駅探（新宿・大宮・横浜→宇都宮駅）</t>
+        </is>
+      </c>
+      <c r="J239" s="55" t="inlineStr">
+        <is>
+          <t>大宮発の旧運賃1,960円は駅探と整合</t>
+        </is>
+      </c>
+      <c r="K239" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="58.2" customHeight="1" s="30">
+      <c r="A240" s="53" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C240" s="53" t="inlineStr">
+        <is>
+          <t>adatara</t>
+        </is>
+      </c>
+      <c r="D240" s="54" t="inlineStr">
+        <is>
+          <t>安達太良山</t>
+        </is>
+      </c>
+      <c r="E240" s="54" t="inlineStr">
+        <is>
+          <t>時間・運賃（文章の整合）</t>
+        </is>
+      </c>
+      <c r="F240" s="54" t="inlineStr">
+        <is>
+          <t>trainAccess文章（大宮・横浜発）</t>
+        </is>
+      </c>
+      <c r="G240" s="55" t="inlineStr">
+        <is>
+          <t>文章の所要時間が経路データと不一致（65件を一括）</t>
+        </is>
+      </c>
+      <c r="H240" s="55" t="inlineStr">
+        <is>
+          <t>経路データから文章を機械的に再生成（対象42山・65項目）。経路の構造（バス／タクシー等）が経路データと文章で食い違っていた箇所は経路データを正とした</t>
+        </is>
+      </c>
+      <c r="I240" s="56" t="inlineStr">
+        <is>
+          <t>check_pages.py セクション10（連続legの合計・±3分を許容）</t>
+        </is>
+      </c>
+      <c r="J240" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件。既知の未解決（時間）が0件に</t>
+        </is>
+      </c>
+      <c r="K240" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="53" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C241" s="53" t="inlineStr">
+        <is>
+          <t>adatara他4山</t>
+        </is>
+      </c>
+      <c r="D241" s="54" t="inlineStr">
+        <is>
+          <t>あだたら山・大野山・伊予ヶ岳・岩殿山</t>
+        </is>
+      </c>
+      <c r="E241" s="54" t="inlineStr">
+        <is>
+          <t>文章の整合（機械生成の修正）</t>
+        </is>
+      </c>
+      <c r="F241" s="54" t="inlineStr">
+        <is>
+          <t>trainAccess文章</t>
+        </is>
+      </c>
+      <c r="G241" s="55" t="inlineStr">
+        <is>
+          <t>機械再生成で目的地側の注記（バスの運行制限、山北駅→共和バス停→徒歩30分、天神郷→徒歩5分、大月駅→徒歩15分）が欠落。あだたら新宿発は行先が岳温泉のまま</t>
+        </is>
+      </c>
+      <c r="H241" s="55" t="inlineStr">
+        <is>
+          <t>欠落した注記を手作業で復元。安達太良の新宿発は経路データに合わせ奥岳登山口へ。重要情報の機械生成は今後行わない方針</t>
+        </is>
+      </c>
+      <c r="I241" s="56" t="inlineStr">
+        <is>
+          <t>経路データ・登山口情報・注記との照合</t>
+        </is>
+      </c>
+      <c r="J241" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K241" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="53" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C242" s="53" t="inlineStr">
+        <is>
+          <t>keirisan</t>
+        </is>
+      </c>
+      <c r="D242" s="54" t="inlineStr">
+        <is>
+          <t>蓼科山</t>
+        </is>
+      </c>
+      <c r="E242" s="54" t="inlineStr">
+        <is>
+          <t>表記統一</t>
+        </is>
+      </c>
+      <c r="F242" s="54" t="inlineStr">
+        <is>
+          <t>目的地名（女神茶屋/竜源橋）</t>
+        </is>
+      </c>
+      <c r="G242" s="55" t="inlineStr">
+        <is>
+          <t>出発地により目的地名が異なる（竜源橋／女神茶屋）</t>
+        </is>
+      </c>
+      <c r="H242" s="55" t="inlineStr">
+        <is>
+          <t>全出発地・文章・trainAccessHtmlを「蓼科山登山口（竜源橋）」に統一（登山口欄・注記と一致）</t>
+        </is>
+      </c>
+      <c r="I242" s="56" t="inlineStr">
+        <is>
+          <t>trailhead欄・注記</t>
+        </is>
+      </c>
+      <c r="J242" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K242" s="57" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="53" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C243" s="53" t="inlineStr">
+        <is>
+          <t>tomisan</t>
+        </is>
+      </c>
+      <c r="D243" s="54" t="inlineStr">
+        <is>
+          <t>富山</t>
+        </is>
+      </c>
+      <c r="E243" s="54" t="inlineStr">
+        <is>
+          <t>時間の整合</t>
+        </is>
+      </c>
+      <c r="F243" s="54" t="inlineStr">
+        <is>
+          <t>岩井駅→福満寺の徒歩</t>
+        </is>
+      </c>
+      <c r="G243" s="55" t="inlineStr">
+        <is>
+          <t>紹介文・登山口欄は20分、経路データ・注記は30分</t>
+        </is>
+      </c>
+      <c r="H243" s="55" t="inlineStr">
+        <is>
+          <t>紹介文・登山口欄・jr-uchibo-hikingの記述を30分に統一（伊予ヶ岳のバス15分→20分も統一）</t>
+        </is>
+      </c>
+      <c r="I243" s="56" t="inlineStr">
+        <is>
+          <t>経路データ・注記</t>
+        </is>
+      </c>
+      <c r="J243" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K243" s="57" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="53" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C244" s="53" t="inlineStr">
+        <is>
+          <t>shirane_gunma</t>
+        </is>
+      </c>
+      <c r="D244" s="54" t="inlineStr">
+        <is>
+          <t>草津白根山</t>
+        </is>
+      </c>
+      <c r="E244" s="54" t="inlineStr">
+        <is>
+          <t>規制中の山の掲載</t>
+        </is>
+      </c>
+      <c r="F244" s="54" t="inlineStr">
+        <is>
+          <t>search 車アクセス4ページ</t>
+        </is>
+      </c>
+      <c r="G244" s="55" t="inlineStr">
+        <is>
+          <t>立入規制中（restricted）にもかかわらず一覧に掲載</t>
+        </is>
+      </c>
+      <c r="H244" s="55" t="inlineStr">
+        <is>
+          <t>ofuna/yokohama/shinjuku/omiyaの一覧カードを削除し件数（105→104等）を修正</t>
+        </is>
+      </c>
+      <c r="I244" s="56" t="inlineStr">
+        <is>
+          <t>status.level=restricted</t>
+        </is>
+      </c>
+      <c r="J244" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K244" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="53" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C245" s="53" t="inlineStr">
+        <is>
+          <t>kogashiyama</t>
+        </is>
+      </c>
+      <c r="D245" s="54" t="inlineStr">
+        <is>
+          <t>古賀志山</t>
+        </is>
+      </c>
+      <c r="E245" s="54" t="inlineStr">
+        <is>
+          <t>バス区間の一次情報反映</t>
+        </is>
+      </c>
+      <c r="F245" s="54" t="inlineStr">
+        <is>
+          <t>バス・運賃・時間</t>
+        </is>
+      </c>
+      <c r="G245" s="55" t="inlineStr">
+        <is>
+          <t>宇都宮駅→バス約35分→古賀志山登山口（運賃は算出値550円）。2,640/1,960/2,970円・147/100/169分</t>
+        </is>
+      </c>
+      <c r="H245" s="55" t="inlineStr">
+        <is>
+          <t>宇都宮駅西口→関東自動車バス47番→森林公園入口 約33分・640円（平日6便）→登山口まで徒歩。2,730/2,050/3,060円・145/98/167分。FAQ・注記・busLinks更新</t>
+        </is>
+      </c>
+      <c r="I245" s="56" t="inlineStr">
+        <is>
+          <t>関東バス公式（kantobus.info 宇都宮駅→森林公園）</t>
+        </is>
+      </c>
+      <c r="J245" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K245" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="53" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C246" s="53" t="inlineStr">
+        <is>
+          <t>kogashiyama</t>
+        </is>
+      </c>
+      <c r="D246" s="54" t="inlineStr">
+        <is>
+          <t>古賀志山</t>
+        </is>
+      </c>
+      <c r="E246" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・徒歩区間</t>
+        </is>
+      </c>
+      <c r="F246" s="54" t="inlineStr">
+        <is>
+          <t>登山口名・座標・地図リンク・徒歩</t>
+        </is>
+      </c>
+      <c r="G246" s="55" t="inlineStr">
+        <is>
+          <t>登山口「古賀志山登山口（森林公園）」、座標36.6111,139.9206（誤り）、地図リンクも誤位置。徒歩区間なし（145/98/167分）</t>
+        </is>
+      </c>
+      <c r="H246" s="55" t="inlineStr">
+        <is>
+          <t>登山口を「宇都宮市森林公園駐車場」に修正（座標36.6195,139.7935）。Google/Apple地図リンク更新。森林公園入口→徒歩46分の区間を追加（191/144/213分）。FAQ・注記更新</t>
+        </is>
+      </c>
+      <c r="I246" s="56" t="inlineStr">
+        <is>
+          <t>ユーザー提供情報（徒歩46分）、tozanguchinavi・登山口P（駐車場座標36°37'10.1"N 139°47'36.6"E）</t>
+        </is>
+      </c>
+      <c r="J246" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K246" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="53" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C247" s="53" t="inlineStr">
+        <is>
+          <t>nakawarayama</t>
+        </is>
+      </c>
+      <c r="D247" s="54" t="inlineStr">
+        <is>
+          <t>和名倉山</t>
+        </is>
+      </c>
+      <c r="E247" s="54" t="inlineStr">
+        <is>
+          <t>運賃（公式運賃表で確定）</t>
+        </is>
+      </c>
+      <c r="F247" s="54" t="inlineStr">
+        <is>
+          <t>三峰口駅→秩父湖バス</t>
+        </is>
+      </c>
+      <c r="G247" s="55" t="inlineStr">
+        <is>
+          <t>バス600円（算出値）。2,100/2,270/2,620円</t>
+        </is>
+      </c>
+      <c r="H247" s="55" t="inlineStr">
+        <is>
+          <t>バス580円（西武観光バス運賃表）。2,080/2,250/2,600円。注記・FAQの「目安」表記を削除</t>
+        </is>
+      </c>
+      <c r="I247" s="56" t="inlineStr">
+        <is>
+          <t>西武観光バス運賃表（ユーザー提供画像）</t>
+        </is>
+      </c>
+      <c r="J247" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K247" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K232"/>
+  <autoFilter ref="A1:K247"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証チェックリスト'!$A$1:$G$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経路・運賃・時間データ一覧'!$A$1:$N$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'バス情報整合性チェック'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$247</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$254</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -24235,7 +24235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K247"/>
+  <dimension ref="A1:K254"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -37836,8 +37836,393 @@
         </is>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" s="53" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C248" s="53" t="inlineStr">
+        <is>
+          <t>kobotokeshiroyama他3山</t>
+        </is>
+      </c>
+      <c r="D248" s="54" t="inlineStr">
+        <is>
+          <t>小仏城山・草戸山・鳴虫山・御前山</t>
+        </is>
+      </c>
+      <c r="E248" s="54" t="inlineStr">
+        <is>
+          <t>診断用タグの補完</t>
+        </is>
+      </c>
+      <c r="F248" s="54" t="inlineStr">
+        <is>
+          <t>types / vibes</t>
+        </is>
+      </c>
+      <c r="G248" s="55" t="inlineStr">
+        <is>
+          <t>types・vibesが未設定（null／空）で診断のスコアリングに反映されない</t>
+        </is>
+      </c>
+      <c r="H248" s="55" t="inlineStr">
+        <is>
+          <t>紹介文・コース定数・近隣の山の付け方に合わせて設定（小仏城山 easy,casual／草戸山 easy／鳴虫山 easy,casual／御前山 casual,collector）</t>
+        </is>
+      </c>
+      <c r="I248" s="56" t="inlineStr">
+        <is>
+          <t>各山の紹介文・コース定数</t>
+        </is>
+      </c>
+      <c r="J248" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K248" s="57" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="53" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C249" s="53" t="inlineStr">
+        <is>
+          <t>tanzawa</t>
+        </is>
+      </c>
+      <c r="D249" s="54" t="inlineStr">
+        <is>
+          <t>丹沢山</t>
+        </is>
+      </c>
+      <c r="E249" s="54" t="inlineStr">
+        <is>
+          <t>ページ生成の一本化</t>
+        </is>
+      </c>
+      <c r="F249" s="54" t="inlineStr">
+        <is>
+          <t>ページ生成・FAQ</t>
+        </is>
+      </c>
+      <c r="G249" s="55" t="inlineStr">
+        <is>
+          <t>丹沢山だけ手動管理（生成対象外）で、データ更新のたびに手作業で反映が必要。手動版は横浜発ルート等が旧データ</t>
+        </is>
+      </c>
+      <c r="H249" s="55" t="inlineStr">
+        <is>
+          <t>自動生成に統一（EXCLUDED_IDSを空に）。横浜発（相鉄特急→海老名→小田急）・大倉バス停・近くて似た山を最新データに。FAQの駐車場名を大倉駐車場に統一（parking欄と一致）。TouristAttraction形式のJSON-LDは他155山と同じBreadcrumbのみに統一</t>
+        </is>
+      </c>
+      <c r="I249" s="56" t="inlineStr">
+        <is>
+          <t>手動版と生成版の差分検証、JSONの各項目</t>
+        </is>
+      </c>
+      <c r="J249" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K249" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="53" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C250" s="53" t="inlineStr">
+        <is>
+          <t>全山（156山）</t>
+        </is>
+      </c>
+      <c r="D250" s="54" t="inlineStr">
+        <is>
+          <t>診断のおすすめ理由</t>
+        </is>
+      </c>
+      <c r="E250" s="54" t="inlineStr">
+        <is>
+          <t>診断機能の改善</t>
+        </is>
+      </c>
+      <c r="F250" s="54" t="inlineStr">
+        <is>
+          <t>recommendReason（新規）・recommend/index.html getReasons</t>
+        </is>
+      </c>
+      <c r="G250" s="55" t="inlineStr">
+        <is>
+          <t>おすすめ理由が全山ほぼ共通の3行（日帰り／電車・バス／定数による難易度）</t>
+        </is>
+      </c>
+      <c r="H250" s="55" t="inlineStr">
+        <is>
+          <t>山ごとの一言（recommendReason・手書き、紹介文に基づく）＋出発地からの車／電車の実際の所要時間＋選んだ体力とコース定数の比較＋診断タイプに合う特徴（vibes）</t>
+        </is>
+      </c>
+      <c r="I250" s="56" t="inlineStr">
+        <is>
+          <t>各山の紹介文・経路データ</t>
+        </is>
+      </c>
+      <c r="J250" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件・getReasons動作確認</t>
+        </is>
+      </c>
+      <c r="K250" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="53" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C251" s="53" t="inlineStr">
+        <is>
+          <t>48山（vibes補完）</t>
+        </is>
+      </c>
+      <c r="D251" s="54" t="inlineStr">
+        <is>
+          <t>富士山・槍ヶ岳ほか</t>
+        </is>
+      </c>
+      <c r="E251" s="54" t="inlineStr">
+        <is>
+          <t>診断タグの補完・理由文の汎用表示解消</t>
+        </is>
+      </c>
+      <c r="F251" s="54" t="inlineStr">
+        <is>
+          <t>vibes / recommend getReasons</t>
+        </is>
+      </c>
+      <c r="G251" s="55" t="inlineStr">
+        <is>
+          <t>全156山×診断タイプで理由を出して点検。3行目が汎用文「あなたのタイプに合う山」になる山が、A型44山・V型31山。原因は vibes の不足・誤り（富士山と槍ヶ岳が「樹林帯」のみ等）</t>
+        </is>
+      </c>
+      <c r="H251" s="55" t="inlineStr">
+        <is>
+          <t>紹介文に基づき vibes を補完（富士山・槍ヶ岳は樹林帯を外し火山/岩稜等に修正）。タイプに合う特徴がない場合は、その山自身の特徴を出す表示に変更（汎用文を廃止）</t>
+        </is>
+      </c>
+      <c r="I251" s="56" t="inlineStr">
+        <is>
+          <t>各山の紹介文</t>
+        </is>
+      </c>
+      <c r="J251" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件・全山×4タイプで再点検</t>
+        </is>
+      </c>
+      <c r="K251" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="53" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C252" s="53" t="inlineStr">
+        <is>
+          <t>10山（vibes追補）</t>
+        </is>
+      </c>
+      <c r="D252" s="54" t="inlineStr">
+        <is>
+          <t>有明山・高妻山・武尊山・甲武信ヶ岳・皇海山ほか</t>
+        </is>
+      </c>
+      <c r="E252" s="54" t="inlineStr">
+        <is>
+          <t>診断タグの補完（Web確認）</t>
+        </is>
+      </c>
+      <c r="F252" s="54" t="inlineStr">
+        <is>
+          <t>vibes</t>
+        </is>
+      </c>
+      <c r="G252" s="55" t="inlineStr">
+        <is>
+          <t>アクティブ型で「この山の魅力」表示になる山の特徴タグが不足</t>
+        </is>
+      </c>
+      <c r="H252" s="55" t="inlineStr">
+        <is>
+          <t>有明山(岩場・展望)、高妻山(岩場・稜線・展望)、武尊山(岩場・稜線・展望)、甲武信ヶ岳(展望・シャクナゲ)、皇海山(展望)をヤマ情報サイトで確認して追加。安達太良山・白山(活火山)、笊ヶ岳(展望)、荒川岳・針ノ木岳(高山)は紹介文・標高から追加</t>
+        </is>
+      </c>
+      <c r="I252" s="56" t="inlineStr">
+        <is>
+          <t>YAMA HACK・山と溪谷・ヤマレコ・YAMAP各山ページ</t>
+        </is>
+      </c>
+      <c r="J252" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K252" s="57" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="53" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C253" s="53" t="inlineStr">
+        <is>
+          <t>約40山（vibes Web確認）</t>
+        </is>
+      </c>
+      <c r="D253" s="54" t="inlineStr">
+        <is>
+          <t>雲取山・両神山・金峰山・白馬岳・飯豊山・平ヶ岳・雨飾山・荒川岳・光岳ほか</t>
+        </is>
+      </c>
+      <c r="E253" s="54" t="inlineStr">
+        <is>
+          <t>診断タグの補完（Web確認・第2弾）</t>
+        </is>
+      </c>
+      <c r="F253" s="54" t="inlineStr">
+        <is>
+          <t>vibes</t>
+        </is>
+      </c>
+      <c r="G253" s="55" t="inlineStr">
+        <is>
+          <t>診断理由の特徴タグが紹介文だけを根拠にしており不足</t>
+        </is>
+      </c>
+      <c r="H253" s="55" t="inlineStr">
+        <is>
+          <t>YAMA HACK・山と溪谷・ヤマレコ・各自治体観光サイトで特徴を確認し、実在する特徴（花・稜線・湿原・眺望・岩場・信仰）を追加。35タグ追加</t>
+        </is>
+      </c>
+      <c r="I253" s="56" t="inlineStr">
+        <is>
+          <t>各山の登山情報サイト</t>
+        </is>
+      </c>
+      <c r="J253" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K253" s="57" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="53" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C254" s="53" t="inlineStr">
+        <is>
+          <t>47山（vibes Web確認・第3弾）</t>
+        </is>
+      </c>
+      <c r="D254" s="54" t="inlineStr">
+        <is>
+          <t>約100山（富士山〜高尾・奥武蔵の低山まで）</t>
+        </is>
+      </c>
+      <c r="E254" s="54" t="inlineStr">
+        <is>
+          <t>診断タグの補完（Web確認）＋診断理由を実スコア加点ベースに変更</t>
+        </is>
+      </c>
+      <c r="F254" s="54" t="inlineStr">
+        <is>
+          <t>vibes / recommend/index.html scoreDetail・getReasons</t>
+        </is>
+      </c>
+      <c r="G254" s="55" t="inlineStr">
+        <is>
+          <t>診断の3行目が、実際の得点根拠ではなく診断タイプ1軸目だけで特徴を選んでいた。特徴タグもWeb確認前は紹介文のみが根拠</t>
+        </is>
+      </c>
+      <c r="H254" s="55" t="inlineStr">
+        <is>
+          <t>①scoreMountを加点項目別に集計するscoreDetailに変更し、理由の3行目は実際の加点上位2項目（眺望・岩場・稜線・樹林帯・百名山・アクセス等）から生成。②約100山をYAMA HACK・山と溪谷・ヤマレコ・各自治体観光サイトで確認し、実在する特徴タグを77個追加</t>
+        </is>
+      </c>
+      <c r="I254" s="56" t="inlineStr">
+        <is>
+          <t>各山の登山情報サイト（山と溪谷・YAMA HACK・ヤマレコ・YAMAP・自治体観光協会）</t>
+        </is>
+      </c>
+      <c r="J254" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件・全山×診断タイプで再点検</t>
+        </is>
+      </c>
+      <c r="K254" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K247"/>
+  <autoFilter ref="A1:K254"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証チェックリスト'!$A$1:$G$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経路・運賃・時間データ一覧'!$A$1:$N$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'バス情報整合性チェック'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$254</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$255</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -24235,7 +24235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K254"/>
+  <dimension ref="A1:K255"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -38221,8 +38221,63 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" s="53" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C255" s="53" t="inlineStr">
+        <is>
+          <t>34山（vibes Web確認・第4弾）</t>
+        </is>
+      </c>
+      <c r="D255" s="54" t="inlineStr">
+        <is>
+          <t>残り約60山（鋸山・鎌倉アルプス・奥多摩・奥武蔵・南アルプス等）</t>
+        </is>
+      </c>
+      <c r="E255" s="54" t="inlineStr">
+        <is>
+          <t>診断タグの補完（Web確認）／表記ゆれ統一</t>
+        </is>
+      </c>
+      <c r="F255" s="54" t="inlineStr">
+        <is>
+          <t>vibes</t>
+        </is>
+      </c>
+      <c r="G255" s="55" t="inlineStr">
+        <is>
+          <t>約60山が紹介文と既存タグのみで、Web確認が未実施。vibesに historic / historical / history の表記ゆれがあり、診断のスコア（historic のみ加点）で歴史・信仰の山が加点されない山があった</t>
+        </is>
+      </c>
+      <c r="H255" s="55" t="inlineStr">
+        <is>
+          <t>約60山を山と溪谷・YAMA HACK・ヤマレコ・各自治体観光協会で確認し、実在する特徴タグを43個追加。表記ゆれ3山を historic に統一</t>
+        </is>
+      </c>
+      <c r="I255" s="56" t="inlineStr">
+        <is>
+          <t>各山の登山情報サイト</t>
+        </is>
+      </c>
+      <c r="J255" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K255" s="57" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K254"/>
+  <autoFilter ref="A1:K255"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証チェックリスト'!$A$1:$G$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経路・運賃・時間データ一覧'!$A$1:$N$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'バス情報整合性チェック'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$299</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -2388,17 +2388,17 @@
       </c>
       <c r="E47" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F47" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性を確認、問題なし。</t>
+          <t>経路・時間・運賃とも整合性を確認、問題なし。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G47" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>中（バス運賃または一部所要時間が算出値）</t>
         </is>
       </c>
     </row>
@@ -2423,17 +2423,17 @@
       </c>
       <c r="E48" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F48" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性確認済み、問題なし。</t>
+          <t>経路・時間・運賃とも整合性確認済み、問題なし。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G48" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -2598,17 +2598,17 @@
       </c>
       <c r="E53" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F53" s="55" t="inlineStr">
         <is>
-          <t>大宮・横浜発の「新宿→信濃大町」区間のleg時間が150分と表示されていたが、新宿発自身の同一区間は195分で45分の食い違い（実際のあずさ所要時間3時間30〜45分の調査から195分が正と判断）。leg時間のみ修正（合計表示は元から195分想定で計算済みだったため trainTimeXxx自体は変更不要）。</t>
+          <t>大宮・横浜発の「新宿→信濃大町」区間のleg時間が150分と表示されていたが、新宿発自身の同一区間は195分で45分の食い違い（実際のあずさ所要時間3時間30〜45分の調査から195分が正と判断）。leg時間のみ修正（合計表示は元から195分想定で計算済みだったため trainTimeXxx自体は変更不要）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G53" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで現地時刻表・公式サイト等と照合済み）</t>
+          <t>中（バス運賃または一部所要時間が算出値）</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="E57" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F57" s="55" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="G57" s="37" t="inlineStr">
         <is>
-          <t>中（新規構築データにつき、季節運行バスの正確な時刻・運賃は一部概算含む。要フォローアップ）</t>
+          <t>高（2026-09-27 Yahoo!路線情報・事業者公式で運賃・時間を確認）</t>
         </is>
       </c>
     </row>
@@ -2878,17 +2878,17 @@
       </c>
       <c r="E61" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F61" s="55" t="inlineStr">
         <is>
-          <t>経路・運賃は問題なし。FAQの新宿発所要時間が「約2時間54分」と記載されていたが実データは187分(3時間7分)で13分の食い違いを発見、修正。</t>
+          <t>経路・運賃は問題なし。FAQの新宿発所要時間が「約2時間54分」と記載されていたが実データは187分(3時間7分)で13分の食い違いを発見、修正。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G61" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>中（バス運賃または一部所要時間が算出値）</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="E62" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F62" s="55" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G62" s="37" t="inlineStr">
         <is>
-          <t>中（新規構築データにつき、季節運行バスの正確な時刻・運賃は一部概算含む。要フォローアップ）</t>
+          <t>高（2026-09-27 Yahoo!路線情報・事業者公式で運賃・時間を確認）</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="E69" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F69" s="55" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="G69" s="37" t="inlineStr">
         <is>
-          <t>中（新規構築データにつき、季節運行バスの正確な時刻・運賃は一部概算含む。要フォローアップ）</t>
+          <t>高（2026-09-27 Yahoo!路線情報・事業者公式で運賃・時間を確認）</t>
         </is>
       </c>
     </row>
@@ -3368,17 +3368,17 @@
       </c>
       <c r="E75" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F75" s="55" t="inlineStr">
         <is>
-          <t>trainAccess=falseだったが、南小谷駅から小谷村営バスで雨飾荘まで到達可能と判明。trueに変更、trainRoutes新規構築。</t>
+          <t>trainAccess=falseだったが、南小谷駅から小谷村営バスで雨飾荘まで到達可能と判明。trueに変更、trainRoutes新規構築。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G75" s="37" t="inlineStr">
         <is>
-          <t>中（新規構築データにつき、季節運行バスの正確な時刻・運賃は一部概算含む。要フォローアップ）</t>
+          <t>中（バス運賃または一部所要時間が算出値）</t>
         </is>
       </c>
     </row>
@@ -3473,17 +3473,17 @@
       </c>
       <c r="E78" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F78" s="55" t="inlineStr">
         <is>
-          <t>trainAccess=falseだったが、バスタ新宿から濃飛バス・京王バスの通年高速バスが新穂高温泉まで直通していることが判明。trueに変更、trainRoutes新規構築。</t>
+          <t>trainAccess=falseだったが、バスタ新宿から濃飛バス・京王バスの通年高速バスが新穂高温泉まで直通していることが判明。trueに変更、trainRoutes新規構築。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G78" s="37" t="inlineStr">
         <is>
-          <t>中（新規構築データにつき、季節運行バスの正確な時刻・運賃は一部概算含む。要フォローアップ）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -3508,17 +3508,17 @@
       </c>
       <c r="E79" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F79" s="56" t="inlineStr">
         <is>
-          <t>trainRoutesの経路・時間・運賃データ自体は妥当だったが、**FAQ本文の所要時間が実際の表示時間と全く異なっていた**（新宿: FAQ「約3時間30分」vs 実データ330分=5時間30分、横浜: FAQ「約4時間4分」vs 実データ384分=6時間24分、約2時間もの差）。あわせて大宮・横浜発の合計時間のバッファ（+40分）が新宿発（+20分）と不揃いだったため+20分に統一。**新パターン: FAQの「所要時間」記述が実データと丸ごと食い違うケース（運賃だけでなく時間も要チェック）。**【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。</t>
+          <t>trainRoutesの経路・時間・運賃データ自体は妥当だったが、**FAQ本文の所要時間が実際の表示時間と全く異なっていた**（新宿: FAQ「約3時間30分」vs 実データ330分=5時間30分、横浜: FAQ「約4時間4分」vs 実データ384分=6時間24分、約2時間もの差）。あわせて大宮・横浜発の合計時間のバッファ（+40分）が新宿発（+20分）と不揃いだったため+20分に統一。**新パターン: FAQの「所要時間」記述が実データと丸ごと食い違うケース（運賃だけでなく時間も要チェック）。**【追記2026-09-24】バス時刻表リンクが未登録だったため公式サイトのリンクを追加。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G79" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで現地時刻表・公式サイト等と照合済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -3543,17 +3543,17 @@
       </c>
       <c r="E80" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F80" s="55" t="inlineStr">
         <is>
-          <t>経路・legsum・運賃・FAQ全て整合。修正不要。</t>
+          <t>経路・legsum・運賃・FAQ全て整合。修正不要。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G80" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで公式サイト・複数情報源と照合済み）</t>
+          <t>中（バス運賃または一部所要時間が算出値）</t>
         </is>
       </c>
     </row>
@@ -3613,17 +3613,17 @@
       </c>
       <c r="E82" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F82" s="56" t="inlineStr">
         <is>
-          <t>trainRoutesの経路・時間・運賃は内部整合性あり（legsumと表示時間が一致）。ただし新宿→駒ヶ根（JR飯田線経由）の区間所要時間が、同じ駒ヶ根駅を最寄りとするutsugi（空木岳）のデータでは233分なのに対しkisokomaでは255分となっており、**同一区間なのに山ごとに異なる時間が表示される**既知のパターン（奥多摩駅ハブと同種）のバグだった。utsugiの検証済み値233分に統一（大宮348→326分、横浜352→330分）。</t>
+          <t>trainRoutesの経路・時間・運賃は内部整合性あり（legsumと表示時間が一致）。ただし新宿→駒ヶ根（JR飯田線経由）の区間所要時間が、同じ駒ヶ根駅を最寄りとするutsugi（空木岳）のデータでは233分なのに対しkisokomaでは255分となっており、**同一区間なのに山ごとに異なる時間が表示される**既知のパターン（奥多摩駅ハブと同種）のバグだった。utsugiの検証済み値233分に統一（大宮348→326分、横浜352→330分）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G82" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで現地時刻表・公式サイト等と照合済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -3648,17 +3648,17 @@
       </c>
       <c r="E83" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F83" s="55" t="inlineStr">
         <is>
-          <t>大宮・横浜発legの「新宿→松本」区間が250分と表示されていたが、新宿発自身の同一区間は150分で100分もの食い違いを発見（実際のあずさ所要時間から150分が正）。leg修正しtrainTimeOmiya 380→280分、trainTimeYokohama 384→284分に。</t>
+          <t>大宮・横浜発legの「新宿→松本」区間が250分と表示されていたが、新宿発自身の同一区間は150分で100分もの食い違いを発見（実際のあずさ所要時間から150分が正）。leg修正しtrainTimeOmiya 380→280分、trainTimeYokohama 384→284分に。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G83" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで現地時刻表・公式サイト等と照合済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -3718,17 +3718,17 @@
       </c>
       <c r="E85" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F85" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも内部整合性を確認（legの合計と表示時間が一致、運賃も出発地間で妥当な差）。修正不要（新宿→駒ヶ根のJR飯田線経由233分がkisokomaとの横断チェックの基準値として採用された）。</t>
+          <t>経路・時間・運賃とも内部整合性を確認（legの合計と表示時間が一致、運賃も出発地間で妥当な差）。修正不要（新宿→駒ヶ根のJR飯田線経由233分がkisokomaとの横断チェックの基準値として採用された）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G85" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="E87" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F87" s="55" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="G87" s="37" t="inlineStr">
         <is>
-          <t>中（新規構築データにつき、季節運行バスの正確な時刻・運賃は一部概算含む。要フォローアップ）</t>
+          <t>高（2026-09-27 Yahoo!路線情報・事業者公式で運賃・時間を確認）</t>
         </is>
       </c>
     </row>
@@ -4173,17 +4173,17 @@
       </c>
       <c r="E98" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F98" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性を確認、問題なし（塩山駅ゲートウェイ経由でleg合計と表示時間が一致、山梨交通「西沢渓谷線」の経路も実在確認）。</t>
+          <t>経路・時間・運賃とも整合性を確認、問題なし（塩山駅ゲートウェイ経由でleg合計と表示時間が一致、山梨交通「西沢渓谷線」の経路も実在確認）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G98" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="E100" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F100" s="56" t="inlineStr">
         <is>
-          <t>**経路実在性バグ**: 大宮・横浜発が「新宿駅からJR飯田線」208分と案内していたが、JR飯田線は新宿駅を通らないため物理的に不可能（豊橋〜辰野間の路線）。新宿発と同じ高速バス（新宿〜駒ヶ根線、220分）に統一。大宮:2時間35分/6,308円、横浜:2時間39分/6,396円（所要時間のみ修正、運賃は元々妥当だったため据え置き）。</t>
+          <t>**経路実在性バグ**: 大宮・横浜発が「新宿駅からJR飯田線」208分と案内していたが、JR飯田線は新宿駅を通らないため物理的に不可能（豊橋〜辰野間の路線）。新宿発と同じ高速バス（新宿〜駒ヶ根線、220分）に統一。大宮:2時間35分/6,308円、横浜:2時間39分/6,396円（所要時間のみ修正、運賃は元々妥当だったため据え置き）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G100" s="37" t="inlineStr">
         <is>
-          <t>高（現地時刻表・公式サイト等で検算・修正済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -4523,17 +4523,17 @@
       </c>
       <c r="E108" s="53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F108" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性を確認、問題なし（軍畑駅→徒歩30分の登山口アクセスも実際の距離と整合）。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照）</t>
+          <t>経路・時間・運賃とも整合性を確認、問題なし（軍畑駅→徒歩30分の登山口アクセスも実際の距離と整合）。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照） ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G108" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -4593,17 +4593,17 @@
       </c>
       <c r="E110" s="53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F110" s="55" t="inlineStr">
         <is>
-          <t>新宿発のみ5分の余分なバッファがあり他区間と不揃いだったため統一（79→74分）。FAQの新宿発所要時間が「約1時間5分」と記載されていたが実データは74分(1時間14分)で9分の食い違いも発見、修正。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照）</t>
+          <t>新宿発のみ5分の余分なバッファがあり他区間と不揃いだったため統一（79→74分）。FAQの新宿発所要時間が「約1時間5分」と記載されていたが実データは74分(1時間14分)で9分の食い違いも発見、修正。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照） ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G110" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで現地時刻表・公式サイト等と照合済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -4628,17 +4628,17 @@
       </c>
       <c r="E111" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F111" s="56" t="inlineStr">
         <is>
-          <t>trainRoutesの経路・時間は概ね妥当（新宿のみ+5分の不揃いなバッファがあったため0分に統一、94→89分）。**FAQ本文が「池袋から特急ちちぶで約60分」と記載していたが、特急ちちぶ（レッドアロー）は正丸駅に停車しないため物理的に誤り**（実際は急行/各停で約70分）。FAQを正しい経路情報に修正。</t>
+          <t>trainRoutesの経路・時間は概ね妥当（新宿のみ+5分の不揃いなバッファがあったため0分に統一、94→89分）。**FAQ本文が「池袋から特急ちちぶで約60分」と記載していたが、特急ちちぶ（レッドアロー）は正丸駅に停車しないため物理的に誤り**（実際は急行/各停で約70分）。FAQを正しい経路情報に修正。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G111" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで現地時刻表・公式サイト等と照合済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -4838,17 +4838,17 @@
       </c>
       <c r="E117" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F117" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性確認済み、問題なし。</t>
+          <t>経路・時間・運賃とも整合性確認済み、問題なし。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G117" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5223,17 +5223,17 @@
       </c>
       <c r="E128" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F128" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性を確認、問題なし（新宿・大宮・横浜とも相模湖駅ゲートウェイ経由でleg合計と表示時間が一致）。</t>
+          <t>経路・時間・運賃とも整合性を確認、問題なし（新宿・大宮・横浜とも相模湖駅ゲートウェイ経由でleg合計と表示時間が一致）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G128" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5363,17 +5363,17 @@
       </c>
       <c r="E132" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F132" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性を確認、問題なし（猿橋駅→徒歩30分の登山口アクセスも実際の距離と整合）。</t>
+          <t>経路・時間・運賃とも整合性を確認、問題なし（猿橋駅→徒歩30分の登山口アクセスも実際の距離と整合）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G132" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5398,17 +5398,17 @@
       </c>
       <c r="E133" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F133" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性確認済み、問題なし。</t>
+          <t>経路・時間・運賃とも整合性確認済み、問題なし。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G133" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5503,17 +5503,17 @@
       </c>
       <c r="E136" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F136" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性確認済み、問題なし。</t>
+          <t>経路・時間・運賃とも整合性確認済み、問題なし。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G136" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5538,17 +5538,17 @@
       </c>
       <c r="E137" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F137" s="55" t="inlineStr">
         <is>
-          <t>「笹子駅→登山口」の徒歩時間が全経路で「約5分」と表示されていたが、実際の公式情報（大月市等）では「約30分」だった（バス/徒歩区間の時間過小表示バグ）。全経路で30分に修正、FAQの記載も連動修正。新宿:1時間40分/2,090円、大宮:2時間10分/2,618円、横浜:2時間14分/2,706円（運賃据え置き、時間のみ修正）。</t>
+          <t>「笹子駅→登山口」の徒歩時間が全経路で「約5分」と表示されていたが、実際の公式情報（大月市等）では「約30分」だった（バス/徒歩区間の時間過小表示バグ）。全経路で30分に修正、FAQの記載も連動修正。新宿:1時間40分/2,090円、大宮:2時間10分/2,618円、横浜:2時間14分/2,706円（運賃据え置き、時間のみ修正）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G137" s="37" t="inlineStr">
         <is>
-          <t>高（現地時刻表・公式サイト等で検算・修正済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5573,17 +5573,17 @@
       </c>
       <c r="E138" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F138" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性確認済み、問題なし。</t>
+          <t>経路・時間・運賃とも整合性確認済み、問題なし。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G138" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>中（バス運賃または一部所要時間が算出値）</t>
         </is>
       </c>
     </row>
@@ -5608,17 +5608,17 @@
       </c>
       <c r="E139" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F139" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性確認済み、問題なし。</t>
+          <t>経路・時間・運賃とも整合性確認済み、問題なし。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G139" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5643,17 +5643,17 @@
       </c>
       <c r="E140" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F140" s="55" t="inlineStr">
         <is>
-          <t>新宿発の「新宿→武蔵五日市」区間が68分表示だったが、オミヤ・横浜発の同一区間は60分表示で、8分の食い違いがあった（kisokoma/utsugiと同種の横断整合性バグ）。60分に統一。</t>
+          <t>新宿発の「新宿→武蔵五日市」区間が68分表示だったが、オミヤ・横浜発の同一区間は60分表示で、8分の食い違いがあった（kisokoma/utsugiと同種の横断整合性バグ）。60分に統一。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G140" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで現地時刻表・公式サイト等と照合済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5748,17 +5748,17 @@
       </c>
       <c r="E143" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F143" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性確認済み、問題なし。</t>
+          <t>経路・時間・運賃とも整合性確認済み、問題なし。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G143" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5923,17 +5923,17 @@
       </c>
       <c r="E148" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F148" s="55" t="inlineStr">
         <is>
-          <t>全156山を対象にした「同一駅が連続して2回出現する重複レグ」の一斉点検で発見（bukosanと同型のデータ破損バグ、新宿→池袋間が実在しない埼京線＋山手線の二重レグに分裂し所要時間を水増ししていた）。重複レグを除去し所要時間を再計算：新宿183→174分、大宮213→204分、横浜217→208分。</t>
+          <t>全156山を対象にした「同一駅が連続して2回出現する重複レグ」の一斉点検で発見（bukosanと同型のデータ破損バグ、新宿→池袋間が実在しない埼京線＋山手線の二重レグに分裂し所要時間を水増ししていた）。重複レグを除去し所要時間を再計算：新宿183→174分、大宮213→204分、横浜217→208分。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G148" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで現地時刻表・公式サイト等と照合済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5958,17 +5958,17 @@
       </c>
       <c r="E149" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F149" s="55" t="inlineStr">
         <is>
-          <t>同一駅連続重複レグバグ（池袋・西武線コリドー沿いの同型バグ、5件目の発見）を一斉点検で発見・修正。所要時間：新宿183→174分、大宮213→204分、横浜217→208分。 ｜【2026-09-25追加修正】合計時間を174/204/208分に同期</t>
+          <t>同一駅連続重複レグバグ（池袋・西武線コリドー沿いの同型バグ、5件目の発見）を一斉点検で発見・修正。所要時間：新宿183→174分、大宮213→204分、横浜217→208分。 ｜【2026-09-25追加修正】合計時間を174/204/208分に同期 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G149" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで現地時刻表・公式サイト等と照合済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -5993,17 +5993,17 @@
       </c>
       <c r="E150" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F150" s="55" t="inlineStr">
         <is>
-          <t>ルート・運賃とも正常。新宿発バッファのみ他区間との整合性のため99分→94分に調整。</t>
+          <t>ルート・運賃とも正常。新宿発バッファのみ他区間との整合性のため99分→94分に調整。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G150" s="37" t="inlineStr">
         <is>
-          <t>高（本セッションで現地時刻表・公式サイト等と照合済み）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -6168,17 +6168,17 @@
       </c>
       <c r="E155" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F155" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性を確認、問題なし（池袋駅経由・東武東上線・イーグルバスの経路も実在確認、leg合計と表示時間が一致）。</t>
+          <t>経路・時間・運賃とも整合性を確認、問題なし（池袋駅経由・東武東上線・イーグルバスの経路も実在確認、leg合計と表示時間が一致）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
         </is>
       </c>
       <c r="G155" s="37" t="inlineStr">
         <is>
-          <t>高（整合性確認済み、修正不要）</t>
+          <t>高（2026-09-27 Yahoo!路線情報で出発地別に確認）</t>
         </is>
       </c>
     </row>
@@ -6252,6 +6252,8 @@
         </is>
       </c>
     </row>
+    <row r="158"/>
+    <row r="159"/>
     <row r="160" ht="15" customHeight="1" s="30">
       <c r="A160" s="39" t="inlineStr">
         <is>
@@ -9037,25 +9039,25 @@
       </c>
       <c r="I47" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 山梨市駅 --[山梨交通「西沢渓谷線」]--&gt; 乾徳山登山口（季節）</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 山梨市駅 --[山梨交通「西沢渓谷線」]--&gt; 乾徳山登山口（季節）</t>
         </is>
       </c>
       <c r="J47" s="41" t="n">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="K47" s="41" t="n">
-        <v>4928</v>
+        <v>2820</v>
       </c>
       <c r="L47" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 山梨市駅 --[山梨交通「西沢渓谷線」]--&gt; 乾徳山登山口（季節）</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 山梨市駅 --[山梨交通「西沢渓谷線」]--&gt; 乾徳山登山口（季節）</t>
         </is>
       </c>
       <c r="M47" s="41" t="n">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="N47" s="41" t="n">
-        <v>5016</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="48" ht="26.25" customHeight="1" s="30">
@@ -9095,25 +9097,25 @@
       </c>
       <c r="I48" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 小淵沢駅 --[タクシー]--&gt; 尾白川渓谷駐車場</t>
+          <t>大宮駅 --[JR埼京線・特急あずさ（新宿乗換）]--&gt; 小淵沢駅 --[タクシー]--&gt; 尾白川渓谷駐車場</t>
         </is>
       </c>
       <c r="J48" s="41" t="n">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="K48" s="41" t="n">
-        <v>8458</v>
+        <v>7930</v>
       </c>
       <c r="L48" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 小淵沢駅 --[タクシー]--&gt; 尾白川渓谷駐車場</t>
+          <t>横浜駅 --[JR横浜線・特急あずさ（八王子乗換）]--&gt; 小淵沢駅 --[タクシー]--&gt; 尾白川渓谷駐車場</t>
         </is>
       </c>
       <c r="M48" s="41" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="N48" s="41" t="n">
-        <v>8546</v>
+        <v>7270</v>
       </c>
     </row>
     <row r="49" ht="26.25" customHeight="1" s="30">
@@ -9385,25 +9387,25 @@
       </c>
       <c r="I53" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[特急あずさ・大糸線]--&gt; 信濃大町駅 --[アルピコ交通「扇沢線」]--&gt; 扇沢（季節）</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・特急あずさ・大糸線（西国分寺・立川・松本乗換）]--&gt; 信濃大町駅 --[アルピコ交通「扇沢線」]--&gt; 扇沢（季節）</t>
         </is>
       </c>
       <c r="J53" s="41" t="n">
-        <v>255</v>
+        <v>313</v>
       </c>
       <c r="K53" s="41" t="n">
-        <v>9528</v>
+        <v>8690</v>
       </c>
       <c r="L53" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[特急あずさ・大糸線]--&gt; 信濃大町駅 --[アルピコ交通「扇沢線」]--&gt; 扇沢（季節）</t>
+          <t>横浜駅 --[JR横浜線・特急あずさ・大糸線（八王子・松本乗換）]--&gt; 信濃大町駅 --[アルピコ交通「扇沢線」]--&gt; 扇沢（季節）</t>
         </is>
       </c>
       <c r="M53" s="41" t="n">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="N53" s="41" t="n">
-        <v>9616</v>
+        <v>8690</v>
       </c>
     </row>
     <row r="54" ht="39" customHeight="1" s="30">
@@ -9558,36 +9560,36 @@
       </c>
       <c r="F57" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央本線(特急あずさ・かいじ)]--&gt; 小淵沢駅 --[JR小海線]--&gt; 小海駅 --[北相木村営バス]--&gt; 白岩</t>
+          <t>新宿駅 --[JR特急あずさ(小淵沢乗換 JR小海線)]--&gt; 小海駅 --[北相木村営バス]--&gt; 白岩</t>
         </is>
       </c>
       <c r="G57" s="41" t="n">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="H57" s="41" t="n">
-        <v>6400</v>
+        <v>6520</v>
       </c>
       <c r="I57" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線(特急あずさ・かいじ)]--&gt; 小淵沢駅 --[JR小海線]--&gt; 小海駅 --[北相木村営バス]--&gt; 白岩</t>
+          <t>大宮駅 --[北陸新幹線(佐久平乗換 JR小海線)]--&gt; 小海駅 --[北相木村営バス]--&gt; 白岩</t>
         </is>
       </c>
       <c r="J57" s="41" t="n">
-        <v>233</v>
+        <v>141</v>
       </c>
       <c r="K57" s="41" t="n">
-        <v>6980</v>
+        <v>5490</v>
       </c>
       <c r="L57" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線(特急あずさ・かいじ)]--&gt; 小淵沢駅 --[JR小海線]--&gt; 小海駅 --[北相木村営バス]--&gt; 白岩</t>
+          <t>横浜駅 --[JR横須賀線・北陸新幹線(東京・佐久平乗換 JR小海線)]--&gt; 小海駅 --[北相木村営バス]--&gt; 白岩</t>
         </is>
       </c>
       <c r="M57" s="41" t="n">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="N57" s="41" t="n">
-        <v>6970</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="58" ht="39" customHeight="1" s="30">
@@ -9790,36 +9792,36 @@
       </c>
       <c r="F61" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR湘南新宿ライン・東海道線・身延線]--&gt; 富士宮駅 --[富士急静岡バス]--&gt; 朝霧高原（毛無山登山口）</t>
+          <t>新宿駅 --[JR東海道線・身延線（品川・熱海・富士乗換）]--&gt; 富士宮駅 --[富士急静岡バス]--&gt; 朝霧高原（毛無山登山口）</t>
         </is>
       </c>
       <c r="G61" s="41" t="n">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="H61" s="41" t="n">
         <v>4400</v>
       </c>
       <c r="I61" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR湘南新宿ライン・東海道線・身延線]--&gt; 富士宮駅 --[富士急静岡バス]--&gt; 朝霧高原（毛無山登山口）</t>
+          <t>大宮駅 --[JR上野東京ライン・東海道線・身延線（熱海・富士乗換）]--&gt; 富士宮駅 --[富士急静岡バス]--&gt; 朝霧高原（毛無山登山口）</t>
         </is>
       </c>
       <c r="J61" s="41" t="n">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="K61" s="41" t="n">
-        <v>4928</v>
+        <v>5170</v>
       </c>
       <c r="L61" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR湘南新宿ライン・東海道線・身延線]--&gt; 富士宮駅 --[富士急静岡バス]--&gt; 朝霧高原（毛無山登山口）</t>
+          <t>横浜駅 --[JR東海道線・身延線（熱海・富士乗換）]--&gt; 富士宮駅 --[富士急静岡バス]--&gt; 朝霧高原（毛無山登山口）</t>
         </is>
       </c>
       <c r="M61" s="41" t="n">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="N61" s="41" t="n">
-        <v>5016</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="30">
@@ -9852,10 +9854,10 @@
         </is>
       </c>
       <c r="G62" s="41" t="n">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="H62" s="41" t="n">
-        <v>5000</v>
+        <v>4970</v>
       </c>
       <c r="I62" s="44" t="inlineStr">
         <is>
@@ -9863,10 +9865,10 @@
         </is>
       </c>
       <c r="J62" s="41" t="n">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="K62" s="41" t="n">
-        <v>5580</v>
+        <v>5550</v>
       </c>
       <c r="L62" s="44" t="inlineStr">
         <is>
@@ -9874,10 +9876,10 @@
         </is>
       </c>
       <c r="M62" s="41" t="n">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="N62" s="41" t="n">
-        <v>5580</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="63" ht="39" customHeight="1" s="30">
@@ -10230,36 +10232,36 @@
       </c>
       <c r="F69" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央本線(特急あずさ)]--&gt; 岡谷駅 --[JR飯田線]--&gt; 伊那市駅 --[伊那バス(西箕輪線)]--&gt; 羽広 --[徒歩]--&gt; 仲仙寺</t>
+          <t>新宿駅 --[JR特急あずさ(上諏訪乗換 JR飯田線)]--&gt; 伊那市駅 --[伊那バス(西箕輪線)]--&gt; 羽広 --[徒歩]--&gt; 仲仙寺</t>
         </is>
       </c>
       <c r="G69" s="41" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H69" s="41" t="n">
-        <v>7040</v>
+        <v>6730</v>
       </c>
       <c r="I69" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線(特急あずさ)]--&gt; 岡谷駅 --[JR飯田線]--&gt; 伊那市駅 --[伊那バス(西箕輪線)]--&gt; 羽広 --[徒歩]--&gt; 仲仙寺</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線(立川乗換)]--&gt; 立川駅 --[JR特急あずさ(岡谷乗換 JR飯田線)]--&gt; 伊那市駅 --[伊那バス(西箕輪線)]--&gt; 羽広 --[徒歩]--&gt; 仲仙寺</t>
         </is>
       </c>
       <c r="J69" s="41" t="n">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="K69" s="41" t="n">
-        <v>7620</v>
+        <v>6730</v>
       </c>
       <c r="L69" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線(特急あずさ)]--&gt; 岡谷駅 --[JR飯田線]--&gt; 伊那市駅 --[伊那バス(西箕輪線)]--&gt; 羽広 --[徒歩]--&gt; 仲仙寺</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ(岡谷乗換 JR飯田線)]--&gt; 伊那市駅 --[伊那バス(西箕輪線)]--&gt; 羽広 --[徒歩]--&gt; 仲仙寺</t>
         </is>
       </c>
       <c r="M69" s="41" t="n">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="N69" s="41" t="n">
-        <v>7620</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="70" ht="39" customHeight="1" s="30">
@@ -10565,25 +10567,25 @@
       </c>
       <c r="I75" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線 特急あずさ(松本・信濃大町方面)]--&gt; 南小谷駅 --[小谷村営バス 栂池高原・雨飾高原線]--&gt; 雨飾高原(雨飾荘)</t>
+          <t>大宮駅 --[JR湘南新宿ライン・特急あずさ・大糸線（新宿・白馬乗換）]--&gt; 南小谷駅 --[小谷村営バス 栂池高原・雨飾高原線]--&gt; 雨飾高原(雨飾荘)</t>
         </is>
       </c>
       <c r="J75" s="41" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="K75" s="41" t="n">
-        <v>9400</v>
+        <v>9090</v>
       </c>
       <c r="L75" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線 特急あずさ(松本・信濃大町方面)]--&gt; 南小谷駅 --[小谷村営バス 栂池高原・雨飾高原線]--&gt; 雨飾高原(雨飾荘)</t>
+          <t>横浜駅 --[JR横浜線・特急あずさ・大糸線（八王子・白馬乗換）]--&gt; 南小谷駅 --[小谷村営バス 栂池高原・雨飾高原線]--&gt; 雨飾高原(雨飾荘)</t>
         </is>
       </c>
       <c r="M75" s="41" t="n">
-        <v>364</v>
+        <v>331</v>
       </c>
       <c r="N75" s="41" t="n">
-        <v>9450</v>
+        <v>8870</v>
       </c>
     </row>
     <row r="76" ht="39" customHeight="1" s="30">
@@ -10739,7 +10741,7 @@
       </c>
       <c r="I78" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[濃飛バス・京王バス 新宿～新穂高温泉・平湯温泉線]--&gt; 新穂高温泉</t>
+          <t>大宮駅 --[JR埼京線]--&gt; バスタ新宿 --[濃飛バス・京王バス 新宿～新穂高温泉・平湯温泉線]--&gt; 新穂高温泉</t>
         </is>
       </c>
       <c r="J78" s="41" t="n">
@@ -10757,7 +10759,7 @@
         <v>379</v>
       </c>
       <c r="N78" s="41" t="n">
-        <v>8580</v>
+        <v>8620</v>
       </c>
     </row>
     <row r="79" ht="39" customHeight="1" s="30">
@@ -10786,36 +10788,36 @@
       </c>
       <c r="F79" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ+特急しなの（松本乗換）]--&gt; 木曽福島駅 --[おんたけ交通バス]--&gt; 田の原（王滝口・季節運行）</t>
+          <t>新宿駅 --[JR特急あずさ・特急しなの（塩尻乗換）]--&gt; 木曽福島駅 --[おんたけ交通バス]--&gt; 田の原（王滝口・季節運行）</t>
         </is>
       </c>
       <c r="G79" s="41" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="H79" s="41" t="n">
         <v>10880</v>
       </c>
       <c r="I79" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ+特急しなの（松本乗換）]--&gt; 木曽福島駅 --[おんたけ交通バス]--&gt; 田の原（王滝口・季節運行）</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・特急あずさ・特急しなの（西国分寺・立川・塩尻乗換）]--&gt; 木曽福島駅 --[おんたけ交通バス]--&gt; 田の原（王滝口・季節運行）</t>
         </is>
       </c>
       <c r="J79" s="41" t="n">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="K79" s="41" t="n">
-        <v>11408</v>
+        <v>10570</v>
       </c>
       <c r="L79" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ+特急しなの（松本乗換）]--&gt; 木曽福島駅 --[おんたけ交通バス]--&gt; 田の原（王滝口・季節運行）</t>
+          <t>横浜駅 --[JR横浜線・特急あずさ・特急しなの（八王子・塩尻乗換）]--&gt; 木曽福島駅 --[おんたけ交通バス]--&gt; 田の原（王滝口・季節運行）</t>
         </is>
       </c>
       <c r="M79" s="41" t="n">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="N79" s="41" t="n">
-        <v>11496</v>
+        <v>10570</v>
       </c>
     </row>
     <row r="80" ht="39" customHeight="1" s="30">
@@ -10844,36 +10846,36 @@
       </c>
       <c r="F80" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[特急あずさ・大糸線]--&gt; 神城駅 --[徒歩]--&gt; エスカルプラザ（テレキャビン乗り場）</t>
+          <t>新宿駅 --[JR特急あずさ・大糸線（松本乗換）]--&gt; 神城駅 --[徒歩]--&gt; エスカルプラザ（テレキャビン乗り場）</t>
         </is>
       </c>
       <c r="G80" s="41" t="n">
         <v>220</v>
       </c>
       <c r="H80" s="41" t="n">
-        <v>8400</v>
+        <v>7940</v>
       </c>
       <c r="I80" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[特急あずさ・大糸線]--&gt; 神城駅 --[徒歩]--&gt; エスカルプラザ（テレキャビン乗り場）</t>
+          <t>大宮駅 --[JR埼京線・特急あずさ・大糸線（新宿・松本乗換）]--&gt; 神城駅 --[徒歩]--&gt; エスカルプラザ（テレキャビン乗り場）</t>
         </is>
       </c>
       <c r="J80" s="41" t="n">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="K80" s="41" t="n">
-        <v>8928</v>
+        <v>7940</v>
       </c>
       <c r="L80" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[特急あずさ・大糸線]--&gt; 神城駅 --[徒歩]--&gt; エスカルプラザ（テレキャビン乗り場）</t>
+          <t>横浜駅 --[JR横浜線・特急あずさ・大糸線（八王子・松本乗換）]--&gt; 神城駅 --[徒歩]--&gt; エスカルプラザ（テレキャビン乗り場）</t>
         </is>
       </c>
       <c r="M80" s="41" t="n">
-        <v>254</v>
+        <v>330</v>
       </c>
       <c r="N80" s="41" t="n">
-        <v>9016</v>
+        <v>7630</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="30">
@@ -10936,7 +10938,7 @@
       </c>
       <c r="F82" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[高速バス]--&gt; 駒ヶ根駅 --[バス]--&gt; 菅の台バスセンター --[中央アルプス観光バス]--&gt; しらび平 --[ロープウェイ]--&gt; 千畳敷</t>
+          <t>バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[バス]--&gt; 菅の台バスセンター --[中央アルプス観光バス]--&gt; しらび平 --[ロープウェイ]--&gt; 千畳敷</t>
         </is>
       </c>
       <c r="G82" s="41" t="n">
@@ -10947,25 +10949,25 @@
       </c>
       <c r="I82" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR飯田線]--&gt; 駒ヶ根駅 --[バス]--&gt; 菅の台バスセンター --[中央アルプス観光バス]--&gt; しらび平 --[ロープウェイ]--&gt; 千畳敷</t>
+          <t>大宮駅 --[JR埼京線]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[バス]--&gt; 菅の台バスセンター --[中央アルプス観光バス]--&gt; しらび平 --[ロープウェイ]--&gt; 千畳敷</t>
         </is>
       </c>
       <c r="J82" s="41" t="n">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="K82" s="41" t="n">
-        <v>8928</v>
+        <v>8930</v>
       </c>
       <c r="L82" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR飯田線]--&gt; 駒ヶ根駅 --[バス]--&gt; 菅の台バスセンター --[中央アルプス観光バス]--&gt; しらび平 --[ロープウェイ]--&gt; 千畳敷</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[バス]--&gt; 菅の台バスセンター --[中央アルプス観光バス]--&gt; しらび平 --[ロープウェイ]--&gt; 千畳敷</t>
         </is>
       </c>
       <c r="M82" s="41" t="n">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="N82" s="41" t="n">
-        <v>9016</v>
+        <v>9020</v>
       </c>
     </row>
     <row r="83" ht="26.25" customHeight="1" s="30">
@@ -11005,25 +11007,25 @@
       </c>
       <c r="I83" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 松本駅 --[アルピコ交通バス]--&gt; 美ヶ原高原（夏季）</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・特急あずさ（西国分寺・立川乗換）]--&gt; 松本駅 --[アルピコ交通バス]--&gt; 美ヶ原高原（夏季）</t>
         </is>
       </c>
       <c r="J83" s="41" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="K83" s="41" t="n">
-        <v>8528</v>
+        <v>7690</v>
       </c>
       <c r="L83" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 松本駅 --[アルピコ交通バス]--&gt; 美ヶ原高原（夏季）</t>
+          <t>横浜駅 --[JR横浜線・特急あずさ（八王子乗換）]--&gt; 松本駅 --[アルピコ交通バス]--&gt; 美ヶ原高原（夏季）</t>
         </is>
       </c>
       <c r="M83" s="41" t="n">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="N83" s="41" t="n">
-        <v>8616</v>
+        <v>7690</v>
       </c>
     </row>
     <row r="84" ht="26.25" customHeight="1" s="30">
@@ -11110,7 +11112,7 @@
       </c>
       <c r="F85" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
         </is>
       </c>
       <c r="G85" s="41" t="n">
@@ -11121,25 +11123,25 @@
       </c>
       <c r="I85" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR飯田線]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>大宮駅 --[JR埼京線]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
         </is>
       </c>
       <c r="J85" s="41" t="n">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="K85" s="41" t="n">
-        <v>4728</v>
+        <v>4730</v>
       </c>
       <c r="L85" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR飯田線]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
         </is>
       </c>
       <c r="M85" s="41" t="n">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="N85" s="41" t="n">
-        <v>4816</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="30">
@@ -11202,36 +11204,36 @@
       </c>
       <c r="F87" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央本線 特急あずさ(岡谷乗換 JR飯田線)]--&gt; 伊那大島駅 --[伊那バス 南アルプス登山バス 鳥倉線]--&gt; 鳥倉登山口</t>
+          <t>新宿駅 --[JR特急あずさ(上諏訪乗換 JR飯田線)]--&gt; 伊那大島駅 --[伊那バス 南アルプス登山バス 鳥倉線]--&gt; 鳥倉登山口</t>
         </is>
       </c>
       <c r="G87" s="41" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H87" s="41" t="n">
-        <v>8680</v>
+        <v>8870</v>
       </c>
       <c r="I87" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線 特急あずさ(岡谷乗換 JR飯田線)]--&gt; 伊那大島駅 --[伊那バス 南アルプス登山バス 鳥倉線]--&gt; 鳥倉登山口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線(立川乗換)]--&gt; 立川駅 --[JR特急あずさ(上諏訪乗換 JR飯田線)]--&gt; 伊那大島駅 --[伊那バス 南アルプス登山バス 鳥倉線]--&gt; 鳥倉登山口</t>
         </is>
       </c>
       <c r="J87" s="41" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K87" s="41" t="n">
-        <v>9210</v>
+        <v>8870</v>
       </c>
       <c r="L87" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線 特急あずさ(岡谷乗換 JR飯田線)]--&gt; 伊那大島駅 --[伊那バス 南アルプス登山バス 鳥倉線]--&gt; 鳥倉登山口</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ(上諏訪乗換 JR飯田線)]--&gt; 伊那大島駅 --[伊那バス 南アルプス登山バス 鳥倉線]--&gt; 鳥倉登山口</t>
         </is>
       </c>
       <c r="M87" s="41" t="n">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="N87" s="41" t="n">
-        <v>9260</v>
+        <v>8870</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="30">
@@ -11851,25 +11853,25 @@
       </c>
       <c r="I98" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 塩山駅 --[山梨交通「西沢渓谷線」]--&gt; 道の駅みとみ（西沢渓谷入口）</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 塩山駅 --[山梨交通「西沢渓谷線」]--&gt; 道の駅みとみ（西沢渓谷入口）</t>
         </is>
       </c>
       <c r="J98" s="41" t="n">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="K98" s="41" t="n">
-        <v>5418</v>
+        <v>3310</v>
       </c>
       <c r="L98" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 塩山駅 --[山梨交通「西沢渓谷線」]--&gt; 道の駅みとみ（西沢渓谷入口）</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 塩山駅 --[山梨交通「西沢渓谷線」]--&gt; 道の駅みとみ（西沢渓谷入口）</t>
         </is>
       </c>
       <c r="M98" s="41" t="n">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="N98" s="41" t="n">
-        <v>5506</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="99" ht="51.75" customHeight="1" s="30">
@@ -11956,7 +11958,7 @@
       </c>
       <c r="F100" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
         </is>
       </c>
       <c r="G100" s="41" t="n">
@@ -11967,25 +11969,25 @@
       </c>
       <c r="I100" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[高速バス（新宿〜駒ヶ根線）]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>大宮駅 --[JR埼京線]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
         </is>
       </c>
       <c r="J100" s="41" t="n">
         <v>275</v>
       </c>
       <c r="K100" s="41" t="n">
-        <v>6308</v>
+        <v>6310</v>
       </c>
       <c r="L100" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[高速バス（新宿〜駒ヶ根線）]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
         </is>
       </c>
       <c r="M100" s="41" t="n">
         <v>279</v>
       </c>
       <c r="N100" s="41" t="n">
-        <v>6396</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="101" ht="39" customHeight="1" s="30">
@@ -12420,36 +12422,36 @@
       </c>
       <c r="F108" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR青梅線]--&gt; 軍畑駅 --[徒歩]--&gt; 登山口</t>
+          <t>新宿駅 --[JR中央線・青梅線（立川・青梅乗換）]--&gt; 軍畑駅 --[徒歩]--&gt; 登山口</t>
         </is>
       </c>
       <c r="G108" s="41" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H108" s="41" t="n">
-        <v>883</v>
+        <v>1040</v>
       </c>
       <c r="I108" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR青梅線]--&gt; 軍畑駅 --[徒歩]--&gt; 登山口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・青梅線（西国分寺・立川・青梅乗換）]--&gt; 軍畑駅 --[徒歩]--&gt; 登山口</t>
         </is>
       </c>
       <c r="J108" s="41" t="n">
         <v>150</v>
       </c>
       <c r="K108" s="41" t="n">
-        <v>1411</v>
+        <v>1230</v>
       </c>
       <c r="L108" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR青梅線]--&gt; 軍畑駅 --[徒歩]--&gt; 登山口</t>
+          <t>横浜駅 --[JR横浜線・八高線・青梅線（八王子・立川・青梅乗換）]--&gt; 軍畑駅 --[徒歩]--&gt; 登山口</t>
         </is>
       </c>
       <c r="M108" s="41" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="N108" s="41" t="n">
-        <v>1499</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="109" ht="26.25" customHeight="1" s="30">
@@ -12536,36 +12538,36 @@
       </c>
       <c r="F110" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線]--&gt; 高麗駅 --[徒歩]--&gt; 日和田山登山口</t>
+          <t>新宿駅 --[JR山手線]--&gt; 池袋駅 --[西武池袋線]--&gt; 高麗駅 --[徒歩]--&gt; 日和田山登山口</t>
         </is>
       </c>
       <c r="G110" s="41" t="n">
         <v>74</v>
       </c>
       <c r="H110" s="41" t="n">
-        <v>690</v>
+        <v>830</v>
       </c>
       <c r="I110" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 池袋駅 --[西武池袋線]--&gt; 高麗駅 --[徒歩]--&gt; 日和田山登山口</t>
+          <t>大宮駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線]--&gt; 高麗駅 --[徒歩]--&gt; 日和田山登山口</t>
         </is>
       </c>
       <c r="J110" s="41" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K110" s="41" t="n">
-        <v>1218</v>
+        <v>1070</v>
       </c>
       <c r="L110" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 池袋駅 --[西武池袋線]--&gt; 高麗駅 --[徒歩]--&gt; 日和田山登山口</t>
+          <t>横浜駅 --[JR京浜東北線・山手線（品川乗換）]--&gt; 池袋駅 --[西武池袋線]--&gt; 高麗駅 --[徒歩]--&gt; 日和田山登山口</t>
         </is>
       </c>
       <c r="M110" s="41" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="N110" s="41" t="n">
-        <v>1306</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="111" ht="26.25" customHeight="1" s="30">
@@ -12594,36 +12596,36 @@
       </c>
       <c r="F111" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武秩父線]--&gt; 正丸駅 --[徒歩]--&gt; 伊豆ヶ岳登山口</t>
+          <t>新宿駅 --[JR山手線]--&gt; 池袋駅 --[西武池袋線・西武秩父線]--&gt; 正丸駅 --[徒歩]--&gt; 伊豆ヶ岳登山口</t>
         </is>
       </c>
       <c r="G111" s="41" t="n">
         <v>89</v>
       </c>
       <c r="H111" s="41" t="n">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="I111" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 池袋駅 --[西武秩父線]--&gt; 正丸駅 --[徒歩]--&gt; 伊豆ヶ岳登山口</t>
+          <t>大宮駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線・西武秩父線]--&gt; 正丸駅 --[徒歩]--&gt; 伊豆ヶ岳登山口</t>
         </is>
       </c>
       <c r="J111" s="41" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K111" s="41" t="n">
-        <v>1462</v>
+        <v>1180</v>
       </c>
       <c r="L111" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 池袋駅 --[西武秩父線]--&gt; 正丸駅 --[徒歩]--&gt; 伊豆ヶ岳登山口</t>
+          <t>横浜駅 --[JR京浜東北線・山手線（品川乗換）]--&gt; 池袋駅 --[西武池袋線・西武秩父線]--&gt; 正丸駅 --[徒歩]--&gt; 伊豆ヶ岳登山口</t>
         </is>
       </c>
       <c r="M111" s="41" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="N111" s="41" t="n">
-        <v>1550</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="112" ht="39" customHeight="1" s="30">
@@ -12942,36 +12944,36 @@
       </c>
       <c r="F117" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線]--&gt; 初狩駅 --[徒歩]--&gt; 高川山登山口</t>
+          <t>新宿駅 --[JR中央線（高尾乗換）]--&gt; 初狩駅 --[徒歩]--&gt; 高川山登山口</t>
         </is>
       </c>
       <c r="G117" s="41" t="n">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="H117" s="41" t="n">
         <v>1600</v>
       </c>
       <c r="I117" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線]--&gt; 初狩駅 --[徒歩]--&gt; 高川山登山口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 初狩駅 --[徒歩]--&gt; 高川山登山口</t>
         </is>
       </c>
       <c r="J117" s="41" t="n">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="K117" s="41" t="n">
-        <v>2128</v>
+        <v>1790</v>
       </c>
       <c r="L117" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線]--&gt; 初狩駅 --[徒歩]--&gt; 高川山登山口</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 初狩駅 --[徒歩]--&gt; 高川山登山口</t>
         </is>
       </c>
       <c r="M117" s="41" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="N117" s="41" t="n">
-        <v>2216</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="118" ht="26.25" customHeight="1" s="30">
@@ -13290,33 +13292,33 @@
       </c>
       <c r="F123" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線・総武線快速]--&gt; 千葉駅 --[JR内房線]--&gt; 岩井駅 --[市営バス]--&gt; 天神郷バス停</t>
+          <t>新宿駅 --[JR中央線・総武線快速]--&gt; 千葉駅 --[JR内房線]--&gt; 岩井駅 --[市営バス]--&gt; 天神郷バス停 --[徒歩]--&gt; 平群天神社</t>
         </is>
       </c>
       <c r="G123" s="41" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H123" s="41" t="n">
         <v>2180</v>
       </c>
       <c r="I123" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR内房線]--&gt; 岩井駅 --[市営バス]--&gt; 天神郷バス停</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR内房線]--&gt; 岩井駅 --[市営バス]--&gt; 天神郷バス停 --[徒歩]--&gt; 平群天神社</t>
         </is>
       </c>
       <c r="J123" s="41" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K123" s="41" t="n">
         <v>2708</v>
       </c>
       <c r="L123" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線・総武線・内房線(君津・木更津経由)]--&gt; 岩井駅 --[市営バス]--&gt; 天神郷バス停</t>
+          <t>横浜駅 --[JR東海道線・総武線・内房線(君津・木更津経由)]--&gt; 岩井駅 --[市営バス]--&gt; 天神郷バス停 --[徒歩]--&gt; 平群天神社</t>
         </is>
       </c>
       <c r="M123" s="41" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="N123" s="41" t="n">
         <v>2620</v>
@@ -13580,36 +13582,36 @@
       </c>
       <c r="F128" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央本線]--&gt; 相模湖駅 --[神奈川中央交通バス]--&gt; 石老山入口バス停</t>
+          <t>新宿駅 --[JR中央線（高尾乗換）]--&gt; 相模湖駅 --[神奈川中央交通バス]--&gt; 石老山入口バス停</t>
         </is>
       </c>
       <c r="G128" s="41" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H128" s="41" t="n">
-        <v>1230</v>
+        <v>1300</v>
       </c>
       <c r="I128" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 相模湖駅 --[神奈川中央交通バス]--&gt; 石老山入口バス停</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 相模湖駅 --[神奈川中央交通バス]--&gt; 石老山入口バス停</t>
         </is>
       </c>
       <c r="J128" s="41" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K128" s="41" t="n">
-        <v>1758</v>
+        <v>1490</v>
       </c>
       <c r="L128" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 相模湖駅 --[神奈川中央交通バス]--&gt; 石老山入口バス停</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 相模湖駅 --[神奈川中央交通バス]--&gt; 石老山入口バス停</t>
         </is>
       </c>
       <c r="M128" s="41" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="N128" s="41" t="n">
-        <v>1846</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="129" ht="26.25" customHeight="1" s="30">
@@ -13638,36 +13640,36 @@
       </c>
       <c r="F129" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央本線]--&gt; 大月駅 岩殿山登山口</t>
+          <t>新宿駅 --[JR中央線（高尾乗換）]--&gt; 大月駅 --[徒歩]--&gt; 畑倉登山口</t>
         </is>
       </c>
       <c r="G129" s="41" t="n">
         <v>98</v>
       </c>
       <c r="H129" s="41" t="n">
-        <v>1400</v>
+        <v>1410</v>
       </c>
       <c r="I129" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 大月駅 岩殿山登山口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 大月駅 --[徒歩]--&gt; 畑倉登山口</t>
         </is>
       </c>
       <c r="J129" s="41" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K129" s="41" t="n">
-        <v>1928</v>
+        <v>1600</v>
       </c>
       <c r="L129" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 大月駅 岩殿山登山口</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 大月駅 --[徒歩]--&gt; 畑倉登山口</t>
         </is>
       </c>
       <c r="M129" s="41" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="N129" s="41" t="n">
-        <v>2016</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="130" ht="39" customHeight="1" s="30">
@@ -13754,33 +13756,33 @@
       </c>
       <c r="F131" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[徒歩]--&gt; 松田駅 --[JR御殿場線]--&gt; 山北駅</t>
+          <t>新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[徒歩]--&gt; 松田駅 --[JR御殿場線]--&gt; 山北駅 --[徒歩]--&gt; 大野山入口</t>
         </is>
       </c>
       <c r="G131" s="41" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H131" s="41" t="n">
         <v>986</v>
       </c>
       <c r="I131" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[徒歩]--&gt; 松田駅 --[JR御殿場線]--&gt; 山北駅</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[徒歩]--&gt; 松田駅 --[JR御殿場線]--&gt; 山北駅 --[徒歩]--&gt; 大野山入口</t>
         </is>
       </c>
       <c r="J131" s="41" t="n">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="K131" s="41" t="n">
         <v>1514</v>
       </c>
       <c r="L131" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 国府津駅 --[JR御殿場線]--&gt; 山北駅</t>
+          <t>横浜駅 --[JR東海道線]--&gt; 国府津駅 --[JR御殿場線]--&gt; 山北駅 --[徒歩]--&gt; 大野山入口</t>
         </is>
       </c>
       <c r="M131" s="41" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="N131" s="41" t="n">
         <v>1446</v>
@@ -13812,36 +13814,36 @@
       </c>
       <c r="F132" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央本線]--&gt; 猿橋駅 --[徒歩]--&gt; 大月市営総合グラウンド（百蔵山登山口）</t>
+          <t>新宿駅 --[JR中央線（高尾乗換）]--&gt; 猿橋駅 --[徒歩]--&gt; 大月市営総合グラウンド（百蔵山登山口）</t>
         </is>
       </c>
       <c r="G132" s="41" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H132" s="41" t="n">
         <v>1410</v>
       </c>
       <c r="I132" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 猿橋駅 --[徒歩]--&gt; 大月市営総合グラウンド（百蔵山登山口）</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 猿橋駅 --[徒歩]--&gt; 大月市営総合グラウンド（百蔵山登山口）</t>
         </is>
       </c>
       <c r="J132" s="41" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K132" s="41" t="n">
-        <v>1938</v>
+        <v>1600</v>
       </c>
       <c r="L132" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 猿橋駅 --[徒歩]--&gt; 大月市営総合グラウンド（百蔵山登山口）</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 猿橋駅 --[徒歩]--&gt; 大月市営総合グラウンド（百蔵山登山口）</t>
         </is>
       </c>
       <c r="M132" s="41" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="N132" s="41" t="n">
-        <v>2026</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="133" ht="26.25" customHeight="1" s="30">
@@ -13870,36 +13872,36 @@
       </c>
       <c r="F133" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線]--&gt; 鳥沢駅 --[徒歩]--&gt; 梨ノ木平登山口</t>
+          <t>新宿駅 --[JR中央線（高尾乗換）]--&gt; 鳥沢駅 --[徒歩]--&gt; 梨ノ木平登山口</t>
         </is>
       </c>
       <c r="G133" s="41" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="H133" s="41" t="n">
         <v>1410</v>
       </c>
       <c r="I133" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 鳥沢駅 --[徒歩]--&gt; 梨ノ木平登山口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 鳥沢駅 --[徒歩]--&gt; 梨ノ木平登山口</t>
         </is>
       </c>
       <c r="J133" s="41" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K133" s="41" t="n">
-        <v>1938</v>
+        <v>1600</v>
       </c>
       <c r="L133" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 鳥沢駅 --[徒歩]--&gt; 梨ノ木平登山口</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 鳥沢駅 --[徒歩]--&gt; 梨ノ木平登山口</t>
         </is>
       </c>
       <c r="M133" s="41" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="N133" s="41" t="n">
-        <v>2026</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="134" ht="26.25" customHeight="1" s="30">
@@ -14044,36 +14046,36 @@
       </c>
       <c r="F136" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線]--&gt; 鳥沢駅 --[徒歩]--&gt; 穴路峠登山口</t>
+          <t>新宿駅 --[JR中央線（高尾乗換）]--&gt; 鳥沢駅 --[徒歩]--&gt; 穴路峠登山口</t>
         </is>
       </c>
       <c r="G136" s="41" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="H136" s="41" t="n">
         <v>1410</v>
       </c>
       <c r="I136" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 鳥沢駅 --[徒歩]--&gt; 穴路峠登山口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 鳥沢駅 --[徒歩]--&gt; 穴路峠登山口</t>
         </is>
       </c>
       <c r="J136" s="41" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K136" s="41" t="n">
-        <v>1938</v>
+        <v>1600</v>
       </c>
       <c r="L136" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 鳥沢駅 --[徒歩]--&gt; 穴路峠登山口</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 鳥沢駅 --[徒歩]--&gt; 穴路峠登山口</t>
         </is>
       </c>
       <c r="M136" s="41" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="N136" s="41" t="n">
-        <v>2026</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="137" ht="26.25" customHeight="1" s="30">
@@ -14102,36 +14104,36 @@
       </c>
       <c r="F137" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央本線]--&gt; 笹子駅 --[徒歩]--&gt; 笹子雁ヶ腹摺山登山口</t>
+          <t>新宿駅 --[JR中央線（高尾乗換）]--&gt; 笹子駅 --[徒歩]--&gt; 笹子雁ヶ腹摺山登山口</t>
         </is>
       </c>
       <c r="G137" s="41" t="n">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="H137" s="41" t="n">
         <v>2090</v>
       </c>
       <c r="I137" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 笹子駅 --[徒歩]--&gt; 笹子雁ヶ腹摺山登山口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 笹子駅 --[徒歩]--&gt; 笹子雁ヶ腹摺山登山口</t>
         </is>
       </c>
       <c r="J137" s="41" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="K137" s="41" t="n">
-        <v>2618</v>
+        <v>2090</v>
       </c>
       <c r="L137" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 笹子駅 --[徒歩]--&gt; 笹子雁ヶ腹摺山登山口</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 笹子駅 --[徒歩]--&gt; 笹子雁ヶ腹摺山登山口</t>
         </is>
       </c>
       <c r="M137" s="41" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="N137" s="41" t="n">
-        <v>2706</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="138" ht="26.25" customHeight="1" s="30">
@@ -14160,36 +14162,36 @@
       </c>
       <c r="F138" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央本線]--&gt; 上野原駅 --[富士急バス]--&gt; 井戸バス停</t>
+          <t>新宿駅 --[JR中央線（高尾乗換）]--&gt; 上野原駅 --[富士急バス]--&gt; 井戸バス停</t>
         </is>
       </c>
       <c r="G138" s="41" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="H138" s="41" t="n">
         <v>1504</v>
       </c>
       <c r="I138" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 上野原駅 --[富士急バス]--&gt; 井戸バス停</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 上野原駅 --[富士急バス]--&gt; 井戸バス停</t>
         </is>
       </c>
       <c r="J138" s="41" t="n">
         <v>125</v>
       </c>
       <c r="K138" s="41" t="n">
-        <v>2032</v>
+        <v>1874</v>
       </c>
       <c r="L138" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央本線]--&gt; 上野原駅 --[富士急バス]--&gt; 井戸バス停</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 上野原駅 --[富士急バス]--&gt; 井戸バス停</t>
         </is>
       </c>
       <c r="M138" s="41" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="N138" s="41" t="n">
-        <v>2120</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="139" ht="26.25" customHeight="1" s="30">
@@ -14218,36 +14220,36 @@
       </c>
       <c r="F139" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線]--&gt; 大月駅 --[富士急行線]--&gt; 禾生駅 --[徒歩]--&gt; 九鬼山登山口</t>
+          <t>新宿駅 --[JR中央線（高尾乗換）]--&gt; 大月駅 --[富士急行線]--&gt; 禾生駅 --[徒歩]--&gt; 九鬼山登山口</t>
         </is>
       </c>
       <c r="G139" s="41" t="n">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="H139" s="41" t="n">
-        <v>2740</v>
+        <v>1720</v>
       </c>
       <c r="I139" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線]--&gt; 大月駅 --[富士急行線]--&gt; 禾生駅 --[徒歩]--&gt; 九鬼山登山口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 大月駅 --[富士急行線]--&gt; 禾生駅 --[徒歩]--&gt; 九鬼山登山口</t>
         </is>
       </c>
       <c r="J139" s="41" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="K139" s="41" t="n">
-        <v>3268</v>
+        <v>1910</v>
       </c>
       <c r="L139" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線]--&gt; 大月駅 --[富士急行線]--&gt; 禾生駅 --[徒歩]--&gt; 九鬼山登山口</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 大月駅 --[富士急行線]--&gt; 禾生駅 --[徒歩]--&gt; 九鬼山登山口</t>
         </is>
       </c>
       <c r="M139" s="41" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="N139" s="41" t="n">
-        <v>3356</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="140" ht="39" customHeight="1" s="30">
@@ -14276,36 +14278,36 @@
       </c>
       <c r="F140" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線・五日市線]--&gt; 武蔵五日市駅 --[西東京バス「数馬行」]--&gt; 数馬 --[都民の森連絡バス]--&gt; 都民の森</t>
+          <t>新宿駅 --[JR中央線・五日市線（立川乗換）]--&gt; 武蔵五日市駅 --[西東京バス「数馬行」]--&gt; 数馬 --[都民の森連絡バス]--&gt; 都民の森</t>
         </is>
       </c>
       <c r="G140" s="41" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="H140" s="41" t="n">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="I140" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR五日市線]--&gt; 武蔵五日市駅 --[西東京バス「数馬行」]--&gt; 数馬 --[都民の森連絡バス]--&gt; 都民の森</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・五日市線（西国分寺・立川乗換）]--&gt; 武蔵五日市駅 --[西東京バス「数馬行」]--&gt; 数馬 --[都民の森連絡バス]--&gt; 都民の森</t>
         </is>
       </c>
       <c r="J140" s="41" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="K140" s="41" t="n">
-        <v>2550</v>
+        <v>2160</v>
       </c>
       <c r="L140" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR五日市線]--&gt; 武蔵五日市駅 --[西東京バス「数馬行」]--&gt; 数馬 --[都民の森連絡バス]--&gt; 都民の森</t>
+          <t>横浜駅 --[JR京浜東北線・南武線・五日市線（川崎・立川乗換）]--&gt; 武蔵五日市駅 --[西東京バス「数馬行」]--&gt; 数馬 --[都民の森連絡バス]--&gt; 都民の森</t>
         </is>
       </c>
       <c r="M140" s="41" t="n">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="N140" s="41" t="n">
-        <v>2638</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="141" ht="39" customHeight="1" s="30">
@@ -14450,36 +14452,36 @@
       </c>
       <c r="F143" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線・五日市線]--&gt; 武蔵五日市駅 --[西東京バス]--&gt; 払沢の滝入口</t>
+          <t>新宿駅 --[JR中央線・五日市線（立川乗換）]--&gt; 武蔵五日市駅 --[西東京バス]--&gt; 払沢の滝入口</t>
         </is>
       </c>
       <c r="G143" s="41" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="H143" s="41" t="n">
-        <v>1432</v>
+        <v>1440</v>
       </c>
       <c r="I143" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR五日市線]--&gt; 武蔵五日市駅 --[西東京バス]--&gt; 払沢の滝入口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・五日市線（西国分寺・立川乗換）]--&gt; 武蔵五日市駅 --[西東京バス]--&gt; 払沢の滝入口</t>
         </is>
       </c>
       <c r="J143" s="41" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="K143" s="41" t="n">
-        <v>1960</v>
+        <v>1570</v>
       </c>
       <c r="L143" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR五日市線]--&gt; 武蔵五日市駅 --[西東京バス]--&gt; 払沢の滝入口</t>
+          <t>横浜駅 --[JR京浜東北線・南武線・五日市線（川崎・立川乗換）]--&gt; 武蔵五日市駅 --[西東京バス]--&gt; 払沢の滝入口</t>
         </is>
       </c>
       <c r="M143" s="41" t="n">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="N143" s="41" t="n">
-        <v>2048</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="144" ht="39" customHeight="1" s="30">
@@ -14570,29 +14572,29 @@
         </is>
       </c>
       <c r="G145" s="41" t="n">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H145" s="41" t="n">
         <v>3090</v>
       </c>
       <c r="I145" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線（高尾乗換）]--&gt; 大月駅 --[富士急行線]--&gt; 河口湖駅 --[富士急バス「西湖周遊バス」]--&gt; 毛無山登山口バス停 --[徒歩]--&gt; 文化洞トンネル</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 大月駅 --[富士急行線]--&gt; 河口湖駅 --[富士急バス「西湖周遊バス」]--&gt; 毛無山登山口バス停 --[徒歩]--&gt; 文化洞トンネル</t>
         </is>
       </c>
       <c r="J145" s="41" t="n">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="K145" s="41" t="n">
         <v>3280</v>
       </c>
       <c r="L145" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR横浜線・中央線（八王子・高尾乗換）]--&gt; 大月駅 --[富士急行線]--&gt; 河口湖駅 --[富士急バス「西湖周遊バス」]--&gt; 毛無山登山口バス停 --[徒歩]--&gt; 文化洞トンネル</t>
+          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 大月駅 --[富士急行線]--&gt; 河口湖駅 --[富士急バス「西湖周遊バス」]--&gt; 毛無山登山口バス停 --[徒歩]--&gt; 文化洞トンネル</t>
         </is>
       </c>
       <c r="M145" s="41" t="n">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="N145" s="41" t="n">
         <v>3280</v>
@@ -14740,36 +14742,36 @@
       </c>
       <c r="F148" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線]--&gt; 飯能駅 --[西武秩父線]--&gt; 西武秩父駅 --[秩父鉄道]--&gt; 長瀞駅 --[徒歩またはロープウェイ]--&gt; 宝登山</t>
+          <t>新宿駅 --[JR山手線]--&gt; 池袋駅 --[東武東上線（小川町乗換）]--&gt; 寄居駅 --[秩父鉄道]--&gt; 長瀞駅 --[徒歩またはロープウェイ]--&gt; 宝登山</t>
         </is>
       </c>
       <c r="G148" s="41" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="H148" s="41" t="n">
-        <v>2200</v>
+        <v>1670</v>
       </c>
       <c r="I148" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線]--&gt; 飯能駅 --[西武秩父線]--&gt; 西武秩父駅 --[秩父鉄道]--&gt; 長瀞駅 --[徒歩またはロープウェイ]--&gt; 宝登山</t>
+          <t>大宮駅 --[JR高崎線]--&gt; 熊谷駅 --[秩父鉄道]--&gt; 長瀞駅 --[徒歩またはロープウェイ]--&gt; 宝登山</t>
         </is>
       </c>
       <c r="J148" s="41" t="n">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K148" s="41" t="n">
-        <v>2728</v>
+        <v>1470</v>
       </c>
       <c r="L148" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線]--&gt; 飯能駅 --[西武秩父線]--&gt; 西武秩父駅 --[秩父鉄道]--&gt; 長瀞駅 --[徒歩またはロープウェイ]--&gt; 宝登山</t>
+          <t>横浜駅 --[JR上野東京ライン・高崎線]--&gt; 熊谷駅 --[秩父鉄道]--&gt; 長瀞駅 --[徒歩またはロープウェイ]--&gt; 宝登山</t>
         </is>
       </c>
       <c r="M148" s="41" t="n">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="N148" s="41" t="n">
-        <v>2816</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="149" ht="51.75" customHeight="1" s="30">
@@ -14798,36 +14800,36 @@
       </c>
       <c r="F149" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線]--&gt; 飯能駅 --[西武秩父線]--&gt; 西武秩父駅 --[秩父鉄道]--&gt; 皆野駅 --[徒歩]--&gt; 風戸登山口</t>
+          <t>新宿駅 --[JR山手線]--&gt; 池袋駅 --[東武東上線（小川町乗換）]--&gt; 寄居駅 --[秩父鉄道]--&gt; 皆野駅 --[徒歩]--&gt; 風戸登山口</t>
         </is>
       </c>
       <c r="G149" s="41" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="H149" s="41" t="n">
-        <v>2200</v>
+        <v>1770</v>
       </c>
       <c r="I149" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線]--&gt; 飯能駅 --[西武秩父線]--&gt; 西武秩父駅 --[秩父鉄道]--&gt; 皆野駅 --[徒歩]--&gt; 風戸登山口</t>
+          <t>大宮駅 --[JR高崎線]--&gt; 熊谷駅 --[秩父鉄道]--&gt; 皆野駅 --[徒歩]--&gt; 風戸登山口</t>
         </is>
       </c>
       <c r="J149" s="41" t="n">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="K149" s="41" t="n">
-        <v>2728</v>
+        <v>1520</v>
       </c>
       <c r="L149" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線]--&gt; 飯能駅 --[西武秩父線]--&gt; 西武秩父駅 --[秩父鉄道]--&gt; 皆野駅 --[徒歩]--&gt; 風戸登山口</t>
+          <t>横浜駅 --[JR上野東京ライン・高崎線]--&gt; 熊谷駅 --[秩父鉄道]--&gt; 皆野駅 --[徒歩]--&gt; 風戸登山口</t>
         </is>
       </c>
       <c r="M149" s="41" t="n">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="N149" s="41" t="n">
-        <v>2816</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="150" ht="26.25" customHeight="1" s="30">
@@ -14856,36 +14858,36 @@
       </c>
       <c r="F150" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線]--&gt; 池袋駅 --[東武東上線]--&gt; 武蔵嵐山駅 --[徒歩]--&gt; 嵐山渓谷入口</t>
+          <t>新宿駅 --[JR山手線]--&gt; 池袋駅 --[東武東上線]--&gt; 武蔵嵐山駅 --[徒歩]--&gt; 嵐山渓谷入口</t>
         </is>
       </c>
       <c r="G150" s="41" t="n">
         <v>94</v>
       </c>
       <c r="H150" s="41" t="n">
-        <v>910</v>
+        <v>950</v>
       </c>
       <c r="I150" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 池袋駅 --[東武東上線]--&gt; 武蔵嵐山駅 --[徒歩]--&gt; 嵐山渓谷入口</t>
+          <t>大宮駅 --[JR川越線]--&gt; 川越駅 --[東武東上線]--&gt; 武蔵嵐山駅 --[徒歩]--&gt; 嵐山渓谷入口</t>
         </is>
       </c>
       <c r="J150" s="41" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="K150" s="41" t="n">
-        <v>1438</v>
+        <v>780</v>
       </c>
       <c r="L150" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 池袋駅 --[東武東上線]--&gt; 武蔵嵐山駅 --[徒歩]--&gt; 嵐山渓谷入口</t>
+          <t>横浜駅 --[JR京浜東北線・山手線（品川乗換）]--&gt; 池袋駅 --[東武東上線]--&gt; 武蔵嵐山駅 --[徒歩]--&gt; 嵐山渓谷入口</t>
         </is>
       </c>
       <c r="M150" s="41" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="N150" s="41" t="n">
-        <v>1526</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="151" ht="26.25" customHeight="1" s="30">
@@ -15146,36 +15148,36 @@
       </c>
       <c r="F155" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線]--&gt; 池袋駅 --[東武東上線]--&gt; 小川町駅 --[イーグルバス]--&gt; パトリアおがわ --[徒歩]--&gt; 官ノ倉山登山口</t>
+          <t>新宿駅 --[JR山手線]--&gt; 池袋駅 --[東武東上線]--&gt; 小川町駅 --[イーグルバス]--&gt; パトリアおがわ --[徒歩]--&gt; 官ノ倉山登山口</t>
         </is>
       </c>
       <c r="G155" s="41" t="n">
         <v>116</v>
       </c>
       <c r="H155" s="41" t="n">
-        <v>1225</v>
+        <v>1260</v>
       </c>
       <c r="I155" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 池袋駅 --[東武東上線]--&gt; 小川町駅 --[イーグルバス]--&gt; パトリアおがわ --[徒歩]--&gt; 官ノ倉山登山口</t>
+          <t>大宮駅 --[JR川越線]--&gt; 川越駅 --[東武東上線]--&gt; 小川町駅 --[イーグルバス]--&gt; パトリアおがわ --[徒歩]--&gt; 官ノ倉山登山口</t>
         </is>
       </c>
       <c r="J155" s="41" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="K155" s="41" t="n">
-        <v>1753</v>
+        <v>1070</v>
       </c>
       <c r="L155" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 池袋駅 --[東武東上線]--&gt; 小川町駅 --[イーグルバス]--&gt; パトリアおがわ --[徒歩]--&gt; 官ノ倉山登山口</t>
+          <t>横浜駅 --[JR京浜東北線・山手線（品川乗換）]--&gt; 池袋駅 --[東武東上線]--&gt; 小川町駅 --[イーグルバス]--&gt; パトリアおがわ --[徒歩]--&gt; 官ノ倉山登山口</t>
         </is>
       </c>
       <c r="M155" s="41" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="N155" s="41" t="n">
-        <v>1841</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" s="30">
@@ -24235,7 +24237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K255"/>
+  <dimension ref="A1:K299"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -38276,8 +38278,2428 @@
         </is>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" s="53" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C256" s="53" t="inlineStr">
+        <is>
+          <t>takeson他6山</t>
+        </is>
+      </c>
+      <c r="D256" s="54" t="inlineStr">
+        <is>
+          <t>武尊山・荒船山・浅間隠山・餓鬼岳・平ヶ岳・皇海山・恵那山</t>
+        </is>
+      </c>
+      <c r="E256" s="54" t="inlineStr">
+        <is>
+          <t>アクセス手段の一次情報検証</t>
+        </is>
+      </c>
+      <c r="F256" s="54" t="inlineStr">
+        <is>
+          <t>FAQ（アクセス方法）</t>
+        </is>
+      </c>
+      <c r="G256" s="55" t="inlineStr">
+        <is>
+          <t>「公共交通なし・マイカー基本」のみ（恵那山は神坂峠への公共交通、荒船山・餓鬼岳・皇海山のタクシー、武尊山の冬季シャトルの情報が不足）</t>
+        </is>
+      </c>
+      <c r="H256" s="55" t="inlineStr">
+        <is>
+          <t>各山の公共交通・タクシーの実情をWebで確認して追記。恵那山は園原バス停からヘブンスそのはらのロープウェイ等を乗り継ぐ神坂峠ルートを追加。荒船山（下仁田/佐久平駅からタクシー約40分・約8千円）、餓鬼岳（信濃大町駅から約30分・約4千円）、皇海山（通洞駅から銀山平まで約15分・約3千円）。浅間隠山は公共交通を確認できず</t>
+        </is>
+      </c>
+      <c r="I256" s="56" t="inlineStr">
+        <is>
+          <t>登山口ねっと・Culmina・山と溪谷・各観光協会</t>
+        </is>
+      </c>
+      <c r="J256" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件（FAQに運賃額を書くと不一致になるため「約○千円」表記）</t>
+        </is>
+      </c>
+      <c r="K256" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="53" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C257" s="53" t="inlineStr">
+        <is>
+          <t>shirasunayama</t>
+        </is>
+      </c>
+      <c r="D257" s="54" t="inlineStr">
+        <is>
+          <t>白砂山</t>
+        </is>
+      </c>
+      <c r="E257" s="54" t="inlineStr">
+        <is>
+          <t>運賃・時間（公表値で確定）</t>
+        </is>
+      </c>
+      <c r="F257" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G257" s="55" t="inlineStr">
+        <is>
+          <t>バス（長野原草津口〜野反湖）約80分・運賃は概算。5,000/5,580/5,580円</t>
+        </is>
+      </c>
+      <c r="H257" s="55" t="inlineStr">
+        <is>
+          <t>約75分・1,570円（中之条町営バス）、上州ゆめぐり号3,400円の公表値で確定。4,970/5,550/5,550円。所要は−5分</t>
+        </is>
+      </c>
+      <c r="I257" s="56" t="inlineStr">
+        <is>
+          <t>中之条町公式（時刻表・運賃表）・NAVITIME・ジョルダン</t>
+        </is>
+      </c>
+      <c r="J257" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K257" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="53" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C258" s="53" t="inlineStr">
+        <is>
+          <t>shiomidake</t>
+        </is>
+      </c>
+      <c r="D258" s="54" t="inlineStr">
+        <is>
+          <t>塩見岳</t>
+        </is>
+      </c>
+      <c r="E258" s="54" t="inlineStr">
+        <is>
+          <t>時間（公表値）</t>
+        </is>
+      </c>
+      <c r="F258" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G258" s="55" t="inlineStr">
+        <is>
+          <t>鳥倉線バス約105分</t>
+        </is>
+      </c>
+      <c r="H258" s="55" t="inlineStr">
+        <is>
+          <t>約110分（伊那バス公表・伊那大島駅〜鳥倉登山口）。運賃は新宿〜伊那大島間の再確認ができず概算のまま（9,180円前後の可能性あり、要フォロー）</t>
+        </is>
+      </c>
+      <c r="I258" s="56" t="inlineStr">
+        <is>
+          <t>伊那バス・駅探・Yahoo!路線情報</t>
+        </is>
+      </c>
+      <c r="J258" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K258" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="53" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C259" s="53" t="inlineStr">
+        <is>
+          <t>fuji他3山</t>
+        </is>
+      </c>
+      <c r="D259" s="54" t="inlineStr">
+        <is>
+          <t>富士山・御前山・大天井岳・常念岳</t>
+        </is>
+      </c>
+      <c r="E259" s="54" t="inlineStr">
+        <is>
+          <t>規制・注意情報の再確認</t>
+        </is>
+      </c>
+      <c r="F259" s="54" t="inlineStr">
+        <is>
+          <t>status / warnBanner</t>
+        </is>
+      </c>
+      <c r="G259" s="55" t="inlineStr">
+        <is>
+          <t>富士山は閉山済みの表示なし、御前山（奥多摩湖側通行止め）・大天井岳（中房線の時間帯規制）・常念岳（一ノ沢林道崩落）の注意表示なし</t>
+        </is>
+      </c>
+      <c r="H259" s="55" t="inlineStr">
+        <is>
+          <t>2026年9月時点の公式情報でstatus（caution）と注意バナーを追加</t>
+        </is>
+      </c>
+      <c r="I259" s="56" t="inlineStr">
+        <is>
+          <t>山梨県・奥多摩ビジターセンター・安曇野市</t>
+        </is>
+      </c>
+      <c r="J259" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K259" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="53" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C260" s="53" t="inlineStr">
+        <is>
+          <t>shiomidake</t>
+        </is>
+      </c>
+      <c r="D260" s="54" t="inlineStr">
+        <is>
+          <t>塩見岳</t>
+        </is>
+      </c>
+      <c r="E260" s="54" t="inlineStr">
+        <is>
+          <t>経路・運賃（最適ルート）</t>
+        </is>
+      </c>
+      <c r="F260" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G260" s="55" t="inlineStr">
+        <is>
+          <t>あずさ岡谷乗換、全員新宿経由。8,680/9,210/9,260円（鉄道運賃は概算）</t>
+        </is>
+      </c>
+      <c r="H260" s="55" t="inlineStr">
+        <is>
+          <t>あずさ上諏訪乗換（新宿）、立川乗換（大宮）、八王子乗換（横浜）。鉄道7,190円（乗車券4,950＋特急券2,240）＋バス1,680円＝8,870円（3出発地とも）。所要340/368/353分</t>
+        </is>
+      </c>
+      <c r="I260" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（新宿・大宮・横浜→伊那大島）、伊那バス公式</t>
+        </is>
+      </c>
+      <c r="J260" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件。大宮・横浜の立川/八王子以降の乗車時間は新宿発の同じ列車から差し引いて算出</t>
+        </is>
+      </c>
+      <c r="K260" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="53" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C261" s="53" t="inlineStr">
+        <is>
+          <t>kazahariyama</t>
+        </is>
+      </c>
+      <c r="D261" s="54" t="inlineStr">
+        <is>
+          <t>御座山</t>
+        </is>
+      </c>
+      <c r="E261" s="54" t="inlineStr">
+        <is>
+          <t>経路・運賃（最適ルート）</t>
+        </is>
+      </c>
+      <c r="F261" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G261" s="55" t="inlineStr">
+        <is>
+          <t>全員新宿経由・あずさ小淵沢。6,400/6,980/6,970円（目安）</t>
+        </is>
+      </c>
+      <c r="H261" s="55" t="inlineStr">
+        <is>
+          <t>新宿：あずさ小淵沢乗換6,420円＋村営バス100円＝6,520円。大宮：北陸新幹線 佐久平乗換5,390円＋100円＝5,490円。横浜：東京で北陸新幹線 6,700円＋100円＝6,800円。所要220/141/215分</t>
+        </is>
+      </c>
+      <c r="I261" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（新宿・大宮・横浜→小海）、北相木村（運賃100円）</t>
+        </is>
+      </c>
+      <c r="J261" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K261" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="53" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C262" s="53" t="inlineStr">
+        <is>
+          <t>keizandake</t>
+        </is>
+      </c>
+      <c r="D262" s="54" t="inlineStr">
+        <is>
+          <t>経ヶ岳</t>
+        </is>
+      </c>
+      <c r="E262" s="54" t="inlineStr">
+        <is>
+          <t>経路・運賃（最適ルート）</t>
+        </is>
+      </c>
+      <c r="F262" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G262" s="55" t="inlineStr">
+        <is>
+          <t>あずさ岡谷乗換、全員新宿経由。7,040/7,620/7,620円</t>
+        </is>
+      </c>
+      <c r="H262" s="55" t="inlineStr">
+        <is>
+          <t>新宿：あずさ上諏訪乗換6,420円、大宮：立川乗換6,420円、横浜：八王子乗換6,420円＋伊那バス310円＝6,730円（3出発地とも）。所要251/297/303分</t>
+        </is>
+      </c>
+      <c r="I262" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（新宿・大宮・横浜→伊那市）、伊那市公式時刻表（310円・27分）</t>
+        </is>
+      </c>
+      <c r="J262" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K262" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="53" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C263" s="53" t="inlineStr">
+        <is>
+          <t>shirouma他2山</t>
+        </is>
+      </c>
+      <c r="D263" s="54" t="inlineStr">
+        <is>
+          <t>白馬岳・白山・雲取山</t>
+        </is>
+      </c>
+      <c r="E263" s="54" t="inlineStr">
+        <is>
+          <t>規制・注意情報の再確認</t>
+        </is>
+      </c>
+      <c r="F263" s="54" t="inlineStr">
+        <is>
+          <t>status / warnBanner</t>
+        </is>
+      </c>
+      <c r="G263" s="55" t="inlineStr">
+        <is>
+          <t>表示なし</t>
+        </is>
+      </c>
+      <c r="H263" s="55" t="inlineStr">
+        <is>
+          <t>白馬大雪渓ルート通行止め（8/31〜当面）、白山 観光新道の一部通行止め（9/24〜11月）の注意バナーを追加。雲取山は後山林道（三条の湯方面）通行止めをstatusに記録（掲載ルートへの影響なし）</t>
+        </is>
+      </c>
+      <c r="I263" s="56" t="inlineStr">
+        <is>
+          <t>白馬館・環境省・奥多摩ビジターセンター</t>
+        </is>
+      </c>
+      <c r="J263" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K263" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="53" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C264" s="53" t="inlineStr">
+        <is>
+          <t>ohnoyama</t>
+        </is>
+      </c>
+      <c r="D264" s="54" t="inlineStr">
+        <is>
+          <t>大野山</t>
+        </is>
+      </c>
+      <c r="E264" s="54" t="inlineStr">
+        <is>
+          <t>徒歩区間・登山口</t>
+        </is>
+      </c>
+      <c r="F264" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G264" s="55" t="inlineStr">
+        <is>
+          <t>経路は山北駅止まり。登山口欄は「共和バス停（山北駅バス約10分）から徒歩30分」でルート（山北駅から歩く）と矛盾</t>
+        </is>
+      </c>
+      <c r="H264" s="55" t="inlineStr">
+        <is>
+          <t>山北駅→徒歩約20分→大野山入口を経路に追加（106/136/90分）。登山口欄・FAQ・注記を統一</t>
+        </is>
+      </c>
+      <c r="I264" s="56" t="inlineStr">
+        <is>
+          <t>山北町公式ハイキングコース・ヤマレコ</t>
+        </is>
+      </c>
+      <c r="J264" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K264" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="53" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C265" s="53" t="inlineStr">
+        <is>
+          <t>iyogatake</t>
+        </is>
+      </c>
+      <c r="D265" s="54" t="inlineStr">
+        <is>
+          <t>伊予ヶ岳</t>
+        </is>
+      </c>
+      <c r="E265" s="54" t="inlineStr">
+        <is>
+          <t>徒歩区間</t>
+        </is>
+      </c>
+      <c r="F265" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G265" s="55" t="inlineStr">
+        <is>
+          <t>天神郷バス停止まり</t>
+        </is>
+      </c>
+      <c r="H265" s="55" t="inlineStr">
+        <is>
+          <t>天神郷→徒歩約5分→平群天神社を追加（194/224/140分）。新宿・横浜発の文章に所要時間を補完</t>
+        </is>
+      </c>
+      <c r="I265" s="56" t="inlineStr">
+        <is>
+          <t>既存注記（徒歩5分）</t>
+        </is>
+      </c>
+      <c r="J265" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K265" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="53" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C266" s="53" t="inlineStr">
+        <is>
+          <t>iwadonoyama</t>
+        </is>
+      </c>
+      <c r="D266" s="54" t="inlineStr">
+        <is>
+          <t>岩殿山</t>
+        </is>
+      </c>
+      <c r="E266" s="54" t="inlineStr">
+        <is>
+          <t>徒歩区間・運賃（加算方式の誤り）</t>
+        </is>
+      </c>
+      <c r="F266" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G266" s="55" t="inlineStr">
+        <is>
+          <t>徒歩の所要時間なし。運賃1,400/1,928/2,016円（大宮・横浜は新宿までの運賃を足し算した誤り）</t>
+        </is>
+      </c>
+      <c r="H266" s="55" t="inlineStr">
+        <is>
+          <t>大月駅→徒歩約15分を追加。大宮は武蔵野線経由、横浜は横浜線・八王子経由の通し運賃に修正：1,410/1,600/1,600円、98/135/127分</t>
+        </is>
+      </c>
+      <c r="I266" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（新宿・大宮・横浜→大月）</t>
+        </is>
+      </c>
+      <c r="J266" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K266" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="53" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C267" s="53" t="inlineStr">
+        <is>
+          <t>juunigadake</t>
+        </is>
+      </c>
+      <c r="D267" s="54" t="inlineStr">
+        <is>
+          <t>十二ヶ岳</t>
+        </is>
+      </c>
+      <c r="E267" s="54" t="inlineStr">
+        <is>
+          <t>経路の再確認・時間</t>
+        </is>
+      </c>
+      <c r="F267" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G267" s="55" t="inlineStr">
+        <is>
+          <t>新宿→大月116分など時間が長すぎ（209/239/222分）。大宮・横浜は新宿経由</t>
+        </is>
+      </c>
+      <c r="H267" s="55" t="inlineStr">
+        <is>
+          <t>運賃3,090/3,280/3,280円は正しいことを確認。大宮は武蔵野線経由、横浜は八王子経由に変更し、所要190/206/198分に修正。富士回遊の選択肢を注記に追加</t>
+        </is>
+      </c>
+      <c r="I267" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（新宿・大宮・横浜→河口湖／大月）</t>
+        </is>
+      </c>
+      <c r="J267" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K267" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="53" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C268" s="53" t="inlineStr">
+        <is>
+          <t>keirisan・kogashiyama</t>
+        </is>
+      </c>
+      <c r="D268" s="54" t="inlineStr">
+        <is>
+          <t>蓼科山・古賀志山</t>
+        </is>
+      </c>
+      <c r="E268" s="54" t="inlineStr">
+        <is>
+          <t>登山口・座標の確認</t>
+        </is>
+      </c>
+      <c r="F268" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図</t>
+        </is>
+      </c>
+      <c r="G268" s="55" t="inlineStr">
+        <is>
+          <t>竜源橋・駐車場座標が未確認</t>
+        </is>
+      </c>
+      <c r="H268" s="55" t="inlineStr">
+        <is>
+          <t>竜源橋は山と溪谷の登山口情報で実在を確認。七合目（女神茶屋）への土休日直通バス（朝1便・1,400円）を注記に追加。古賀志山の駐車場座標をNAVITIME等の値（36.6199,139.7925）に修正（旧値と約90m差）</t>
+        </is>
+      </c>
+      <c r="I268" s="56" t="inlineStr">
+        <is>
+          <t>山と溪谷・登山口ねっと・TRAIN&amp;TRAIL・NAVITIME</t>
+        </is>
+      </c>
+      <c r="J268" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K268" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="53" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C269" s="53" t="inlineStr">
+        <is>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="D269" s="54" t="inlineStr">
+        <is>
+          <t>ofuna-daytrip・shinjuku-daytrip・tobu-hiking</t>
+        </is>
+      </c>
+      <c r="E269" s="54" t="inlineStr">
+        <is>
+          <t>件数の不一致</t>
+        </is>
+      </c>
+      <c r="F269" s="54" t="inlineStr">
+        <is>
+          <t>N選・掲載数</t>
+        </is>
+      </c>
+      <c r="G269" s="55" t="inlineStr">
+        <is>
+          <t>57選/58選/5選に対しカード56/57/4枚。ItemListのnumberOfItemsも52/53</t>
+        </is>
+      </c>
+      <c r="H269" s="55" t="inlineStr">
+        <is>
+          <t>56選/57選/4選に修正、本文の座数・numberOfItemsも統一。tobu-hikingの既存のdiv開閉ずれ（閉じ過多2）を修正</t>
+        </is>
+      </c>
+      <c r="I269" s="56" t="inlineStr">
+        <is>
+          <t>ページ内カード数の機械カウント</t>
+        </is>
+      </c>
+      <c r="J269" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件・div開閉一致</t>
+        </is>
+      </c>
+      <c r="K269" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="53" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C270" s="53" t="inlineStr">
+        <is>
+          <t>takamizusanzan</t>
+        </is>
+      </c>
+      <c r="D270" s="54" t="inlineStr">
+        <is>
+          <t>高水三山</t>
+        </is>
+      </c>
+      <c r="E270" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F270" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G270" s="55" t="inlineStr">
+        <is>
+          <t>883/1,411/1,499円・120/150/154分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H270" s="55" t="inlineStr">
+        <is>
+          <t>1,040/1,230/1,230円・113/150/157分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃。新宿発の旧運賃883円はIC運賃相当のため、きっぷ運賃1,040円に統一</t>
+        </is>
+      </c>
+      <c r="I270" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J270" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K270" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="53" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C271" s="53" t="inlineStr">
+        <is>
+          <t>takagawayama</t>
+        </is>
+      </c>
+      <c r="D271" s="54" t="inlineStr">
+        <is>
+          <t>高川山</t>
+        </is>
+      </c>
+      <c r="E271" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F271" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G271" s="55" t="inlineStr">
+        <is>
+          <t>1,600/2,128/2,216円・110/140/144分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H271" s="55" t="inlineStr">
+        <is>
+          <t>1,600/1,790/1,790円・134/158/164分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I271" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J271" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K271" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="53" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C272" s="53" t="inlineStr">
+        <is>
+          <t>momakurasan</t>
+        </is>
+      </c>
+      <c r="D272" s="54" t="inlineStr">
+        <is>
+          <t>百蔵山</t>
+        </is>
+      </c>
+      <c r="E272" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F272" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G272" s="55" t="inlineStr">
+        <is>
+          <t>1,410/1,938/2,026円・110/140/144分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H272" s="55" t="inlineStr">
+        <is>
+          <t>1,410/1,600/1,600円・130/146/138分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I272" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J272" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K272" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="53" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C273" s="53" t="inlineStr">
+        <is>
+          <t>ogiyama</t>
+        </is>
+      </c>
+      <c r="D273" s="54" t="inlineStr">
+        <is>
+          <t>扇山</t>
+        </is>
+      </c>
+      <c r="E273" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F273" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G273" s="55" t="inlineStr">
+        <is>
+          <t>1,410/1,938/2,026円・140/170/174分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H273" s="55" t="inlineStr">
+        <is>
+          <t>1,410/1,600/1,410円・157/173/164分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I273" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J273" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K273" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="53" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C274" s="53" t="inlineStr">
+        <is>
+          <t>kuratakeyama</t>
+        </is>
+      </c>
+      <c r="D274" s="54" t="inlineStr">
+        <is>
+          <t>倉岳山</t>
+        </is>
+      </c>
+      <c r="E274" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F274" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G274" s="55" t="inlineStr">
+        <is>
+          <t>1,410/1,938/2,026円・110/140/144分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H274" s="55" t="inlineStr">
+        <is>
+          <t>1,410/1,600/1,410円・127/143/134分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I274" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J274" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K274" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="53" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C275" s="53" t="inlineStr">
+        <is>
+          <t>sasakogarigaburiyama</t>
+        </is>
+      </c>
+      <c r="D275" s="54" t="inlineStr">
+        <is>
+          <t>笹子雁ヶ腹摺山</t>
+        </is>
+      </c>
+      <c r="E275" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F275" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G275" s="55" t="inlineStr">
+        <is>
+          <t>2,090/2,618/2,706円・100/130/134分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H275" s="55" t="inlineStr">
+        <is>
+          <t>2,090/2,090/1,790円・141/165/171分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I275" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J275" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K275" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="53" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C276" s="53" t="inlineStr">
+        <is>
+          <t>ishirousan</t>
+        </is>
+      </c>
+      <c r="D276" s="54" t="inlineStr">
+        <is>
+          <t>石老山</t>
+        </is>
+      </c>
+      <c r="E276" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F276" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G276" s="55" t="inlineStr">
+        <is>
+          <t>1,230/1,758/1,846円・72/102/106分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H276" s="55" t="inlineStr">
+        <is>
+          <t>1,300/1,490/1,300円・84/99/91分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I276" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J276" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K276" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="53" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C277" s="53" t="inlineStr">
+        <is>
+          <t>shodosan_namatate</t>
+        </is>
+      </c>
+      <c r="D277" s="54" t="inlineStr">
+        <is>
+          <t>生藤山</t>
+        </is>
+      </c>
+      <c r="E277" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F277" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G277" s="55" t="inlineStr">
+        <is>
+          <t>1,504/2,032/2,120円・95/125/129分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H277" s="55" t="inlineStr">
+        <is>
+          <t>1,504/1,874/1,694円・110/125/117分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃。上野原〜井戸のバス運賃は公式で確認できず、旧データの差額（464円）を使用</t>
+        </is>
+      </c>
+      <c r="I277" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J277" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K277" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="53" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C278" s="53" t="inlineStr">
+        <is>
+          <t>sengenrei</t>
+        </is>
+      </c>
+      <c r="D278" s="54" t="inlineStr">
+        <is>
+          <t>浅間嶺</t>
+        </is>
+      </c>
+      <c r="E278" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F278" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G278" s="55" t="inlineStr">
+        <is>
+          <t>1,432/1,960/2,048円・93/110/114分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H278" s="55" t="inlineStr">
+        <is>
+          <t>1,440/1,570/1,760円・105/131/147分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I278" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J278" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K278" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="53" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C279" s="53" t="inlineStr">
+        <is>
+          <t>mitosaan</t>
+        </is>
+      </c>
+      <c r="D279" s="54" t="inlineStr">
+        <is>
+          <t>三頭山</t>
+        </is>
+      </c>
+      <c r="E279" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F279" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G279" s="55" t="inlineStr">
+        <is>
+          <t>2,022/2,550/2,638円・130/160/164分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H279" s="55" t="inlineStr">
+        <is>
+          <t>2,030/2,160/2,350円・150/176/192分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I279" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J279" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K279" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="53" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C280" s="53" t="inlineStr">
+        <is>
+          <t>kukiyama</t>
+        </is>
+      </c>
+      <c r="D280" s="54" t="inlineStr">
+        <is>
+          <t>九鬼山</t>
+        </is>
+      </c>
+      <c r="E280" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F280" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G280" s="55" t="inlineStr">
+        <is>
+          <t>2,740/3,268/3,356円・115/145/149分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H280" s="55" t="inlineStr">
+        <is>
+          <t>1,720/1,910/1,910円・149/165/157分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃。新宿発の旧運賃2,740円は富士急行線の運賃誤り（正：310円）</t>
+        </is>
+      </c>
+      <c r="I280" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J280" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K280" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="53" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C281" s="53" t="inlineStr">
+        <is>
+          <t>hiwadayama</t>
+        </is>
+      </c>
+      <c r="D281" s="54" t="inlineStr">
+        <is>
+          <t>日和田山</t>
+        </is>
+      </c>
+      <c r="E281" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F281" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G281" s="55" t="inlineStr">
+        <is>
+          <t>690/1,218/1,306円・74/91/113分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H281" s="55" t="inlineStr">
+        <is>
+          <t>830/1,070/1,350円・74/99/121分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I281" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J281" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K281" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="53" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C282" s="53" t="inlineStr">
+        <is>
+          <t>izugatake</t>
+        </is>
+      </c>
+      <c r="D282" s="54" t="inlineStr">
+        <is>
+          <t>伊豆ヶ岳</t>
+        </is>
+      </c>
+      <c r="E282" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F282" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G282" s="55" t="inlineStr">
+        <is>
+          <t>934/1,462/1,550円・89/106/128分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H282" s="55" t="inlineStr">
+        <is>
+          <t>940/1,180/1,460円・89/114/136分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I282" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J282" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K282" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="53" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C283" s="53" t="inlineStr">
+        <is>
+          <t>ranzan_saitama</t>
+        </is>
+      </c>
+      <c r="D283" s="54" t="inlineStr">
+        <is>
+          <t>嵐山</t>
+        </is>
+      </c>
+      <c r="E283" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F283" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G283" s="55" t="inlineStr">
+        <is>
+          <t>910/1,438/1,526円・94/111/133分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H283" s="55" t="inlineStr">
+        <is>
+          <t>950/780/1,470円・94/84/141分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I283" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J283" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K283" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="53" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C284" s="53" t="inlineStr">
+        <is>
+          <t>kannokura</t>
+        </is>
+      </c>
+      <c r="D284" s="54" t="inlineStr">
+        <is>
+          <t>官ノ倉山</t>
+        </is>
+      </c>
+      <c r="E284" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F284" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G284" s="55" t="inlineStr">
+        <is>
+          <t>1,225/1,753/1,841円・116/133/155分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H284" s="55" t="inlineStr">
+        <is>
+          <t>1,260/1,070/1,780円・116/99/163分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I284" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J284" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K284" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="53" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C285" s="53" t="inlineStr">
+        <is>
+          <t>hodosan</t>
+        </is>
+      </c>
+      <c r="D285" s="54" t="inlineStr">
+        <is>
+          <t>宝登山</t>
+        </is>
+      </c>
+      <c r="E285" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F285" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G285" s="55" t="inlineStr">
+        <is>
+          <t>2,200/2,728/2,816円・174/204/208分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H285" s="55" t="inlineStr">
+        <is>
+          <t>1,670/1,470/2,640円・187/130/191分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃。ロープウェイ代は含まない</t>
+        </is>
+      </c>
+      <c r="I285" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J285" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K285" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="53" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C286" s="53" t="inlineStr">
+        <is>
+          <t>hafuzan_chichibu</t>
+        </is>
+      </c>
+      <c r="D286" s="54" t="inlineStr">
+        <is>
+          <t>破風山</t>
+        </is>
+      </c>
+      <c r="E286" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F286" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G286" s="55" t="inlineStr">
+        <is>
+          <t>2,200/2,728/2,816円・174/204/208分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H286" s="55" t="inlineStr">
+        <is>
+          <t>1,770/1,520/2,690円・191/133/194分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I286" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J286" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K286" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="53" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C287" s="53" t="inlineStr">
+        <is>
+          <t>kasagatake</t>
+        </is>
+      </c>
+      <c r="D287" s="54" t="inlineStr">
+        <is>
+          <t>笠ヶ岳</t>
+        </is>
+      </c>
+      <c r="E287" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F287" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G287" s="55" t="inlineStr">
+        <is>
+          <t>8,000/8,530/8,580円・345/375/379分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H287" s="55" t="inlineStr">
+        <is>
+          <t>8,000/8,530/8,620円・345/375/379分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I287" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J287" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K287" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="53" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C288" s="53" t="inlineStr">
+        <is>
+          <t>minamikomagatake</t>
+        </is>
+      </c>
+      <c r="D288" s="54" t="inlineStr">
+        <is>
+          <t>南駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E288" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F288" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G288" s="55" t="inlineStr">
+        <is>
+          <t>5,780/6,308/6,396円・245/275/279分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H288" s="55" t="inlineStr">
+        <is>
+          <t>5,780/6,310/6,400円・245/275/279分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I288" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J288" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K288" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="53" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C289" s="53" t="inlineStr">
+        <is>
+          <t>kisokoma</t>
+        </is>
+      </c>
+      <c r="D289" s="54" t="inlineStr">
+        <is>
+          <t>木曽駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E289" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F289" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G289" s="55" t="inlineStr">
+        <is>
+          <t>8,400/8,928/9,016円・283/326/330分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H289" s="55" t="inlineStr">
+        <is>
+          <t>8,400/8,930/9,020円・283/313/317分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I289" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J289" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K289" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="53" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C290" s="53" t="inlineStr">
+        <is>
+          <t>utsugi</t>
+        </is>
+      </c>
+      <c r="D290" s="54" t="inlineStr">
+        <is>
+          <t>空木岳</t>
+        </is>
+      </c>
+      <c r="E290" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F290" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G290" s="55" t="inlineStr">
+        <is>
+          <t>4,200/4,728/4,816円・245/288/292分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H290" s="55" t="inlineStr">
+        <is>
+          <t>4,200/4,730/4,820円・245/275/279分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I290" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J290" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K290" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="53" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C291" s="53" t="inlineStr">
+        <is>
+          <t>kashimayari</t>
+        </is>
+      </c>
+      <c r="D291" s="54" t="inlineStr">
+        <is>
+          <t>鹿島槍ヶ岳</t>
+        </is>
+      </c>
+      <c r="E291" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F291" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G291" s="55" t="inlineStr">
+        <is>
+          <t>9,000/9,528/9,616円・225/255/259分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H291" s="55" t="inlineStr">
+        <is>
+          <t>9,000/8,690/8,690円・225/313/319分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃。新宿発の鉄道所要時間は旧データのまま</t>
+        </is>
+      </c>
+      <c r="I291" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J291" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K291" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="53" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C292" s="53" t="inlineStr">
+        <is>
+          <t>goryudake</t>
+        </is>
+      </c>
+      <c r="D292" s="54" t="inlineStr">
+        <is>
+          <t>五竜岳</t>
+        </is>
+      </c>
+      <c r="E292" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F292" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G292" s="55" t="inlineStr">
+        <is>
+          <t>8,400/8,928/9,016円・220/250/254分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H292" s="55" t="inlineStr">
+        <is>
+          <t>7,940/7,940/7,630円・220/329/330分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃。新宿発は旧データに内訳不明の460円が含まれていたため鉄道運賃7,940円に修正</t>
+        </is>
+      </c>
+      <c r="I292" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J292" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K292" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="53" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C293" s="53" t="inlineStr">
+        <is>
+          <t>amakazari</t>
+        </is>
+      </c>
+      <c r="D293" s="54" t="inlineStr">
+        <is>
+          <t>雨飾山</t>
+        </is>
+      </c>
+      <c r="E293" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F293" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G293" s="55" t="inlineStr">
+        <is>
+          <t>8,870/9,400/9,450円・330/360/364分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H293" s="55" t="inlineStr">
+        <is>
+          <t>8,870/9,090/8,870円・330/330/331分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃。村営バス約600円は概算のまま。大宮は立川経由の経路をYahooで確認できず新宿経由</t>
+        </is>
+      </c>
+      <c r="I293" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J293" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K293" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="53" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C294" s="53" t="inlineStr">
+        <is>
+          <t>utsukushigahara</t>
+        </is>
+      </c>
+      <c r="D294" s="54" t="inlineStr">
+        <is>
+          <t>美ヶ原</t>
+        </is>
+      </c>
+      <c r="E294" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F294" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G294" s="55" t="inlineStr">
+        <is>
+          <t>8,000/8,528/8,616円・250/280/284分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H294" s="55" t="inlineStr">
+        <is>
+          <t>8,000/7,690/7,690円・250/295/301分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I294" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J294" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K294" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="53" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C295" s="53" t="inlineStr">
+        <is>
+          <t>ontakesan</t>
+        </is>
+      </c>
+      <c r="D295" s="54" t="inlineStr">
+        <is>
+          <t>御嶽山</t>
+        </is>
+      </c>
+      <c r="E295" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F295" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G295" s="55" t="inlineStr">
+        <is>
+          <t>10,880/11,408/11,496円・330/360/364分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H295" s="55" t="inlineStr">
+        <is>
+          <t>10,880/10,570/10,570円・310/347/353分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I295" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J295" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K295" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="53" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C296" s="53" t="inlineStr">
+        <is>
+          <t>hinata</t>
+        </is>
+      </c>
+      <c r="D296" s="54" t="inlineStr">
+        <is>
+          <t>日向山</t>
+        </is>
+      </c>
+      <c r="E296" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F296" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G296" s="55" t="inlineStr">
+        <is>
+          <t>7,930/8,458/8,546円・135/165/169分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H296" s="55" t="inlineStr">
+        <is>
+          <t>7,930/7,930/7,270円・135/179/176分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I296" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J296" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K296" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="53" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C297" s="53" t="inlineStr">
+        <is>
+          <t>karisaka</t>
+        </is>
+      </c>
+      <c r="D297" s="54" t="inlineStr">
+        <is>
+          <t>雁坂嶺</t>
+        </is>
+      </c>
+      <c r="E297" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F297" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G297" s="55" t="inlineStr">
+        <is>
+          <t>4,890/5,418/5,506円・145/175/179分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H297" s="55" t="inlineStr">
+        <is>
+          <t>4,890/3,310/3,310円・145/211/217分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃</t>
+        </is>
+      </c>
+      <c r="I297" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J297" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K297" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="53" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C298" s="53" t="inlineStr">
+        <is>
+          <t>kentoku</t>
+        </is>
+      </c>
+      <c r="D298" s="54" t="inlineStr">
+        <is>
+          <t>乾徳山</t>
+        </is>
+      </c>
+      <c r="E298" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F298" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G298" s="55" t="inlineStr">
+        <is>
+          <t>4,400/4,928/5,016円・117/150/154分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H298" s="55" t="inlineStr">
+        <is>
+          <t>4,400/2,820/2,490円・117/187/193分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃。山梨市駅〜登山口のバス運賃は旧データの差額（400円）を使用</t>
+        </is>
+      </c>
+      <c r="I298" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J298" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K298" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="53" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="53" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C299" s="53" t="inlineStr">
+        <is>
+          <t>kenashiyama</t>
+        </is>
+      </c>
+      <c r="D299" s="54" t="inlineStr">
+        <is>
+          <t>毛無山</t>
+        </is>
+      </c>
+      <c r="E299" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路（加算方式の誤りを修正）</t>
+        </is>
+      </c>
+      <c r="F299" s="54" t="inlineStr">
+        <is>
+          <t>新宿・大宮・横浜</t>
+        </is>
+      </c>
+      <c r="G299" s="55" t="inlineStr">
+        <is>
+          <t>4,400/4,928/5,016円・187/217/221分（大宮・横浜は新宿発に一律528円/616円を加算）</t>
+        </is>
+      </c>
+      <c r="H299" s="55" t="inlineStr">
+        <is>
+          <t>4,400/5,170/4,030円・234/249/189分。大宮・横浜は新宿を経由しない最適経路（武蔵野線・横浜線・川越線・高崎線など）の通し運賃。大宮発の所要時間は横浜発＋大宮〜横浜で算出</t>
+        </is>
+      </c>
+      <c r="I299" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（出発地別の検索結果）</t>
+        </is>
+      </c>
+      <c r="J299" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K299" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K255"/>
+  <autoFilter ref="A1:K299"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証チェックリスト'!$A$1:$G$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経路・運賃・時間データ一覧'!$A$1:$N$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'バス情報整合性チェック'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$299</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$318</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -6252,8 +6252,6 @@
         </is>
       </c>
     </row>
-    <row r="158"/>
-    <row r="159"/>
     <row r="160" ht="15" customHeight="1" s="30">
       <c r="A160" s="39" t="inlineStr">
         <is>
@@ -6732,7 +6730,7 @@
       </c>
       <c r="F7" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急かいじ]--&gt; 大月駅 --[JR中央本線（普通）]--&gt; 甲斐大和駅 --[栄和交通「大菩薩上日川峠線」]--&gt; 上日川峠（土日祝中心）</t>
+          <t>新宿駅 --[JR特急かいじ]--&gt; 大月駅 --[JR中央本線（普通）]--&gt; 甲斐大和駅 --[栄和交通「大菩薩上日川峠線」]--&gt; 上日川峠</t>
         </is>
       </c>
       <c r="G7" s="41" t="n">
@@ -6743,7 +6741,7 @@
       </c>
       <c r="I7" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 大月駅 --[JR中央本線（普通）]--&gt; 甲斐大和駅 --[栄和交通「大菩薩上日川峠線」]--&gt; 上日川峠（土日祝中心）</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 大月駅 --[JR中央本線（普通）]--&gt; 甲斐大和駅 --[栄和交通「大菩薩上日川峠線」]--&gt; 上日川峠</t>
         </is>
       </c>
       <c r="J7" s="41" t="n">
@@ -6754,7 +6752,7 @@
       </c>
       <c r="L7" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 大月駅 --[JR中央本線（普通）]--&gt; 甲斐大和駅 --[栄和交通「大菩薩上日川峠線」]--&gt; 上日川峠（土日祝中心）</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 大月駅 --[JR中央本線（普通）]--&gt; 甲斐大和駅 --[栄和交通「大菩薩上日川峠線」]--&gt; 上日川峠</t>
         </is>
       </c>
       <c r="M7" s="41" t="n">
@@ -7254,7 +7252,7 @@
       </c>
       <c r="F16" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[アルピコ交通バス]--&gt; 美濃戸口（夏季）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[アルピコ交通バス]--&gt; 美濃戸口</t>
         </is>
       </c>
       <c r="G16" s="41" t="n">
@@ -7265,7 +7263,7 @@
       </c>
       <c r="I16" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[アルピコ交通バス]--&gt; 美濃戸口（夏季）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[アルピコ交通バス]--&gt; 美濃戸口</t>
         </is>
       </c>
       <c r="J16" s="41" t="n">
@@ -7276,7 +7274,7 @@
       </c>
       <c r="L16" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[アルピコ交通バス]--&gt; 美濃戸口（夏季）</t>
+          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[アルピコ交通バス]--&gt; 美濃戸口</t>
         </is>
       </c>
       <c r="M16" s="41" t="n">
@@ -7486,36 +7484,36 @@
       </c>
       <c r="F20" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[上越新幹線とき]--&gt; 高崎駅 --[JR上越線 普通]--&gt; 水上駅 --[JR上越線 普通]--&gt; 土合駅 --[徒歩（462段の階段）]--&gt; 谷川岳ロープウェイ乗り場 --[ロープウェイ]--&gt; 天神平駅</t>
+          <t>新宿駅 --[JR湘南新宿ライン・上越新幹線とき（大宮乗換）]--&gt; 上毛高原駅 --[関越交通バス「水上線」]--&gt; 谷川岳ヨッホ（ロープウェイ乗り場） --[ロープウェイ]--&gt; 天神平駅</t>
         </is>
       </c>
       <c r="G20" s="41" t="n">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="H20" s="41" t="n">
-        <v>6860</v>
+        <v>6990</v>
       </c>
       <c r="I20" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[上越新幹線とき]--&gt; 高崎駅 --[JR上越線 普通]--&gt; 水上駅 --[JR上越線 普通]--&gt; 土合駅 --[徒歩（462段の階段）]--&gt; 谷川岳ロープウェイ乗り場 --[ロープウェイ]--&gt; 天神平駅</t>
+          <t>大宮駅 --[上越新幹線とき]--&gt; 上毛高原駅 --[関越交通バス「水上線」]--&gt; 谷川岳ヨッホ（ロープウェイ乗り場） --[ロープウェイ]--&gt; 天神平駅</t>
         </is>
       </c>
       <c r="J20" s="41" t="n">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="K20" s="41" t="n">
-        <v>6420</v>
+        <v>6660</v>
       </c>
       <c r="L20" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[上越新幹線とき]--&gt; 高崎駅 --[JR上越線 普通]--&gt; 水上駅 --[JR上越線 普通]--&gt; 土合駅 --[徒歩（462段の階段）]--&gt; 谷川岳ロープウェイ乗り場 --[ロープウェイ]--&gt; 天神平駅</t>
+          <t>横浜駅 --[JR上野東京ライン・上越新幹線とき（東京乗換）]--&gt; 上毛高原駅 --[関越交通バス「水上線」]--&gt; 谷川岳ヨッホ（ロープウェイ乗り場） --[ロープウェイ]--&gt; 天神平駅</t>
         </is>
       </c>
       <c r="M20" s="41" t="n">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="N20" s="41" t="n">
-        <v>8160</v>
+        <v>7970</v>
       </c>
     </row>
     <row r="21" ht="26.25" customHeight="1" s="30">
@@ -7694,7 +7692,7 @@
       </c>
       <c r="F24" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠</t>
         </is>
       </c>
       <c r="G24" s="41" t="n">
@@ -7705,7 +7703,7 @@
       </c>
       <c r="I24" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠</t>
         </is>
       </c>
       <c r="J24" s="41" t="n">
@@ -7716,7 +7714,7 @@
       </c>
       <c r="L24" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
+          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠</t>
         </is>
       </c>
       <c r="M24" s="41" t="n">
@@ -7752,7 +7750,7 @@
       </c>
       <c r="F25" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠</t>
         </is>
       </c>
       <c r="G25" s="41" t="n">
@@ -7763,7 +7761,7 @@
       </c>
       <c r="I25" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠</t>
         </is>
       </c>
       <c r="J25" s="41" t="n">
@@ -7774,7 +7772,7 @@
       </c>
       <c r="L25" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠（季節運行・金土日祝中心）</t>
+          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[JRバス関東「南アルプスジオライナー」]--&gt; 戸台パーク --[南アルプス林道バス「クイーンライン」]--&gt; 北沢峠</t>
         </is>
       </c>
       <c r="M25" s="41" t="n">
@@ -7868,7 +7866,7 @@
       </c>
       <c r="F27" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス「乗鞍高原線」]--&gt; 乗鞍高原観光センター --[畳平シャトルバス（要予約）]--&gt; 畳平（マイカー規制・7/1〜10/31運行）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス「乗鞍高原線」]--&gt; 乗鞍高原観光センター --[畳平シャトルバス（予約優先制）]--&gt; 畳平</t>
         </is>
       </c>
       <c r="G27" s="41" t="n">
@@ -7879,7 +7877,7 @@
       </c>
       <c r="I27" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス「乗鞍高原線」]--&gt; 乗鞍高原観光センター --[畳平シャトルバス（要予約）]--&gt; 畳平（マイカー規制・7/1〜10/31運行）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス「乗鞍高原線」]--&gt; 乗鞍高原観光センター --[畳平シャトルバス（予約優先制）]--&gt; 畳平</t>
         </is>
       </c>
       <c r="J27" s="41" t="n">
@@ -7890,7 +7888,7 @@
       </c>
       <c r="L27" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス「乗鞍高原線」]--&gt; 乗鞍高原観光センター --[畳平シャトルバス（要予約）]--&gt; 畳平（マイカー規制・7/1〜10/31運行）</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス「乗鞍高原線」]--&gt; 乗鞍高原観光センター --[畳平シャトルバス（予約優先制）]--&gt; 畳平</t>
         </is>
       </c>
       <c r="M27" s="41" t="n">
@@ -8042,36 +8040,36 @@
       </c>
       <c r="F30" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス（予約優先制）]--&gt; 上高地バスターミナル</t>
         </is>
       </c>
       <c r="G30" s="41" t="n">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H30" s="41" t="n">
-        <v>9190</v>
+        <v>10540</v>
       </c>
       <c r="I30" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス（予約優先制）]--&gt; 上高地バスターミナル</t>
         </is>
       </c>
       <c r="J30" s="41" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K30" s="41" t="n">
-        <v>8880</v>
+        <v>10230</v>
       </c>
       <c r="L30" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス（予約優先制）]--&gt; 上高地バスターミナル</t>
         </is>
       </c>
       <c r="M30" s="41" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="N30" s="41" t="n">
-        <v>9190</v>
+        <v>10230</v>
       </c>
     </row>
     <row r="31" ht="39" customHeight="1" s="30">
@@ -8100,36 +8098,36 @@
       </c>
       <c r="F31" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス（予約優先制）]--&gt; 上高地バスターミナル</t>
         </is>
       </c>
       <c r="G31" s="41" t="n">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H31" s="41" t="n">
-        <v>8890</v>
+        <v>10540</v>
       </c>
       <c r="I31" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス（予約優先制）]--&gt; 上高地バスターミナル</t>
         </is>
       </c>
       <c r="J31" s="41" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K31" s="41" t="n">
-        <v>8580</v>
+        <v>10230</v>
       </c>
       <c r="L31" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス（予約優先制）]--&gt; 上高地バスターミナル</t>
         </is>
       </c>
       <c r="M31" s="41" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="N31" s="41" t="n">
-        <v>8890</v>
+        <v>10230</v>
       </c>
     </row>
     <row r="32" ht="39" customHeight="1" s="30">
@@ -8564,7 +8562,7 @@
       </c>
       <c r="F39" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR・東武特急（北千住乗換）]--&gt; 会津田島駅 --[会津バス「檜枝岐線」]--&gt; 御池（2024年10月より会津高原尾瀬口駅発着は廃線、会津田島駅発着に変更。到着が従来より約40分遅くなっている点に注意）</t>
+          <t>新宿駅 --[JR・東武特急（北千住乗換）]--&gt; 会津田島駅 --[会津バス「檜枝岐線」]--&gt; 御池</t>
         </is>
       </c>
       <c r="G39" s="41" t="n">
@@ -8586,7 +8584,7 @@
       </c>
       <c r="L39" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 北千住駅 --[東武特急リバティ会津]--&gt; 会津田島駅 --[会津バス「檜枝岐線」]--&gt; 御池（2024年10月より会津高原尾瀬口駅発着は廃線、会津田島駅発着に変更。到着が従来より約40分遅くなっている点に注意）</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 北千住駅 --[東武特急リバティ会津]--&gt; 会津田島駅 --[会津バス「檜枝岐線」]--&gt; 御池</t>
         </is>
       </c>
       <c r="M39" s="41" t="n">
@@ -10614,7 +10612,7 @@
       </c>
       <c r="F76" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR湘南新宿ライン（大宮乗換込み）]--&gt; 大宮駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 妙高高原駅 --[頸南バス「笹ヶ峰直行バス」]--&gt; 笹ヶ峰（季節運行）</t>
+          <t>新宿駅 --[JR湘南新宿ライン（大宮乗換込み）]--&gt; 大宮駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 妙高高原駅 --[頸南バス「笹ヶ峰直行バス」]--&gt; 笹ヶ峰</t>
         </is>
       </c>
       <c r="G76" s="41" t="n">
@@ -10625,7 +10623,7 @@
       </c>
       <c r="I76" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 妙高高原駅 --[頸南バス「笹ヶ峰直行バス」]--&gt; 笹ヶ峰（季節運行）</t>
+          <t>大宮駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 妙高高原駅 --[頸南バス「笹ヶ峰直行バス」]--&gt; 笹ヶ峰</t>
         </is>
       </c>
       <c r="J76" s="41" t="n">
@@ -10636,7 +10634,7 @@
       </c>
       <c r="L76" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR上野東京ライン（上野乗換込み）]--&gt; 上野駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 妙高高原駅 --[頸南バス「笹ヶ峰直行バス」]--&gt; 笹ヶ峰（季節運行）</t>
+          <t>横浜駅 --[JR上野東京ライン（上野乗換込み）]--&gt; 上野駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 妙高高原駅 --[頸南バス「笹ヶ峰直行バス」]--&gt; 笹ヶ峰</t>
         </is>
       </c>
       <c r="M76" s="41" t="n">
@@ -24237,7 +24235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K299"/>
+  <dimension ref="A1:K318"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -40698,8 +40696,1053 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" s="53" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C300" s="53" t="inlineStr">
+        <is>
+          <t>fuji</t>
+        </is>
+      </c>
+      <c r="D300" s="54" t="inlineStr">
+        <is>
+          <t>富士山</t>
+        </is>
+      </c>
+      <c r="E300" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（ルート→登山口→アクセス）</t>
+        </is>
+      </c>
+      <c r="F300" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G300" s="55" t="inlineStr">
+        <is>
+          <t>登山口「富士宮口五合目」・定数31〜58・6200/6390/6390円</t>
+        </is>
+      </c>
+      <c r="H300" s="55" t="inlineStr">
+        <is>
+          <t>登山口「富士宮口五合目」・定数34〜38（ルートの値から自動生成）・6200/6390/6390円。代表ルート富士宮口にマイカー規制（7/10〜9/10・水ヶ塚）を主表示。電車ルートは吉田口行きと明示。閉山期間を閉鎖表示</t>
+        </is>
+      </c>
+      <c r="I300" s="56" t="inlineStr">
+        <is>
+          <t>各山の一次情報（修正後欄に記載）・国土地理院 地名検索（座標）</t>
+        </is>
+      </c>
+      <c r="J300" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K300" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="53" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C301" s="53" t="inlineStr">
+        <is>
+          <t>yatsugatake</t>
+        </is>
+      </c>
+      <c r="D301" s="54" t="inlineStr">
+        <is>
+          <t>八ヶ岳（赤岳）</t>
+        </is>
+      </c>
+      <c r="E301" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（ルート→登山口→アクセス）</t>
+        </is>
+      </c>
+      <c r="F301" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G301" s="55" t="inlineStr">
+        <is>
+          <t>登山口「美濃戸口」・定数40〜42・7660/7660/7000円</t>
+        </is>
+      </c>
+      <c r="H301" s="55" t="inlineStr">
+        <is>
+          <t>登山口「美濃戸口」・定数35〜38（ルートの値から自動生成）・7660/7660/7000円。美濃戸口線を「季節運行（2026年は5/2〜10/25）」に修正（アルピコ交通）</t>
+        </is>
+      </c>
+      <c r="I301" s="56" t="inlineStr">
+        <is>
+          <t>各山の一次情報（修正後欄に記載）・国土地理院 地名検索（座標）</t>
+        </is>
+      </c>
+      <c r="J301" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K301" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="53" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C302" s="53" t="inlineStr">
+        <is>
+          <t>komagatake</t>
+        </is>
+      </c>
+      <c r="D302" s="54" t="inlineStr">
+        <is>
+          <t>甲斐駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E302" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（ルート→登山口→アクセス）</t>
+        </is>
+      </c>
+      <c r="F302" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G302" s="55" t="inlineStr">
+        <is>
+          <t>登山口「広河原（バス）」・定数38〜62・8710/8710/8050円</t>
+        </is>
+      </c>
+      <c r="H302" s="55" t="inlineStr">
+        <is>
+          <t>登山口「北沢峠」・定数27〜56（ルートの値から自動生成）・8710/8710/8050円。登山口を北沢峠、駐車場・拠点を戸台パークに統一。広河原・芦安を代表アクセスから削除（伊那市）</t>
+        </is>
+      </c>
+      <c r="I302" s="56" t="inlineStr">
+        <is>
+          <t>各山の一次情報（修正後欄に記載）・国土地理院 地名検索（座標）</t>
+        </is>
+      </c>
+      <c r="J302" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K302" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="53" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C303" s="53" t="inlineStr">
+        <is>
+          <t>senjogatake</t>
+        </is>
+      </c>
+      <c r="D303" s="54" t="inlineStr">
+        <is>
+          <t>仙丈ヶ岳</t>
+        </is>
+      </c>
+      <c r="E303" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（ルート→登山口→アクセス）</t>
+        </is>
+      </c>
+      <c r="F303" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G303" s="55" t="inlineStr">
+        <is>
+          <t>登山口「北沢峠」・定数32〜45・8710/8710/8050円</t>
+        </is>
+      </c>
+      <c r="H303" s="55" t="inlineStr">
+        <is>
+          <t>登山口「北沢峠」・定数30〜34（ルートの値から自動生成）・8710/8710/8050円。甲斐駒ヶ岳と同じ北沢峠アクセスを共有。「仙流荘」を「戸台パーク」に更新</t>
+        </is>
+      </c>
+      <c r="I303" s="56" t="inlineStr">
+        <is>
+          <t>各山の一次情報（修正後欄に記載）・国土地理院 地名検索（座標）</t>
+        </is>
+      </c>
+      <c r="J303" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K303" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="53" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C304" s="53" t="inlineStr">
+        <is>
+          <t>shirouma</t>
+        </is>
+      </c>
+      <c r="D304" s="54" t="inlineStr">
+        <is>
+          <t>白馬岳</t>
+        </is>
+      </c>
+      <c r="E304" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（ルート→登山口→アクセス）</t>
+        </is>
+      </c>
+      <c r="F304" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G304" s="55" t="inlineStr">
+        <is>
+          <t>登山口「猿倉」・定数35〜55・10870/11420/11420円</t>
+        </is>
+      </c>
+      <c r="H304" s="55" t="inlineStr">
+        <is>
+          <t>登山口「栂池自然園」・定数31〜41（ルートの値から自動生成）・10870/11420/11420円。白馬大雪渓ルートを通行止め表示（8/31〜当面・白馬館）。代表ルートを栂池に変更。栂池の電車・バス経路は未作成</t>
+        </is>
+      </c>
+      <c r="I304" s="56" t="inlineStr">
+        <is>
+          <t>各山の一次情報（修正後欄に記載）・国土地理院 地名検索（座標）</t>
+        </is>
+      </c>
+      <c r="J304" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K304" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="53" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C305" s="53" t="inlineStr">
+        <is>
+          <t>shibutsu</t>
+        </is>
+      </c>
+      <c r="D305" s="54" t="inlineStr">
+        <is>
+          <t>至仏山</t>
+        </is>
+      </c>
+      <c r="E305" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（ルート→登山口→アクセス）</t>
+        </is>
+      </c>
+      <c r="F305" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G305" s="55" t="inlineStr">
+        <is>
+          <t>登山口「尾瀬ヶ原（鳩待峠）」・定数27〜34・10430/8890/10460円</t>
+        </is>
+      </c>
+      <c r="H305" s="55" t="inlineStr">
+        <is>
+          <t>登山口「鳩待峠」・定数23〜27（ルートの値から自動生成）・10430/8890/10460円。登山口を鳩待峠に統一。5/7〜6/19の登山道全面閉鎖を装備情報ではなく閉鎖として表示（尾瀬保護財団）</t>
+        </is>
+      </c>
+      <c r="I305" s="56" t="inlineStr">
+        <is>
+          <t>各山の一次情報（修正後欄に記載）・国土地理院 地名検索（座標）</t>
+        </is>
+      </c>
+      <c r="J305" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K305" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="53" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C306" s="53" t="inlineStr">
+        <is>
+          <t>hiuchigatake</t>
+        </is>
+      </c>
+      <c r="D306" s="54" t="inlineStr">
+        <is>
+          <t>燧ヶ岳</t>
+        </is>
+      </c>
+      <c r="E306" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（ルート→登山口→アクセス）</t>
+        </is>
+      </c>
+      <c r="F306" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G306" s="55" t="inlineStr">
+        <is>
+          <t>登山口「御池」・定数27〜38・7870/8480/9000円</t>
+        </is>
+      </c>
+      <c r="H306" s="55" t="inlineStr">
+        <is>
+          <t>登山口「御池」・定数23〜31（ルートの値から自動生成）・7870/8480/9000円。御池と沼山峠を別アクセスに分離。標高差表記（++900mm）を修正。沼山峠シャトル5/23〜10/25</t>
+        </is>
+      </c>
+      <c r="I306" s="56" t="inlineStr">
+        <is>
+          <t>各山の一次情報（修正後欄に記載）・国土地理院 地名検索（座標）</t>
+        </is>
+      </c>
+      <c r="J306" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K306" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="53" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C307" s="53" t="inlineStr">
+        <is>
+          <t>jonengatake</t>
+        </is>
+      </c>
+      <c r="D307" s="54" t="inlineStr">
+        <is>
+          <t>常念岳</t>
+        </is>
+      </c>
+      <c r="E307" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（ルート→登山口→アクセス）</t>
+        </is>
+      </c>
+      <c r="F307" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G307" s="55" t="inlineStr">
+        <is>
+          <t>登山口「一ノ沢」・定数32〜45・12200/11890/12200円</t>
+        </is>
+      </c>
+      <c r="H307" s="55" t="inlineStr">
+        <is>
+          <t>登山口「一ノ沢登山口」・定数36〜44（ルートの値から自動生成）・12200/11890/12200円。一ノ沢駐車場の通常表示を停止。復旧予定を2027年1月末、徒歩約1.5kmに修正（安曇野市）</t>
+        </is>
+      </c>
+      <c r="I307" s="56" t="inlineStr">
+        <is>
+          <t>各山の一次情報（修正後欄に記載）・国土地理院 地名検索（座標）</t>
+        </is>
+      </c>
+      <c r="J307" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K307" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="53" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C308" s="53" t="inlineStr">
+        <is>
+          <t>tanigawa</t>
+        </is>
+      </c>
+      <c r="D308" s="54" t="inlineStr">
+        <is>
+          <t>谷川岳</t>
+        </is>
+      </c>
+      <c r="E308" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F308" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G308" s="55" t="inlineStr">
+        <is>
+          <t>登山口「谷川岳ロープウェイ土合口駅」・定数18〜42・6860/6420/8160円</t>
+        </is>
+      </c>
+      <c r="H308" s="55" t="inlineStr">
+        <is>
+          <t>登山口「天神平（ロープウェイ山頂駅）」・定数18〜29・6990/6660/7970円。代表アクセスを上毛高原駅→関越交通バス（45分・1,600円）に変更。土合駅ルートは別アクセスとして保持。名称を「谷川岳ヨッホ」に更新。ロープウェイ4/18〜11/15</t>
+        </is>
+      </c>
+      <c r="I308" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J308" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K308" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="53" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C309" s="53" t="inlineStr">
+        <is>
+          <t>kisokoma</t>
+        </is>
+      </c>
+      <c r="D309" s="54" t="inlineStr">
+        <is>
+          <t>木曽駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E309" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F309" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G309" s="55" t="inlineStr">
+        <is>
+          <t>登山口「菅の台バスセンター（マイカー規制）」・定数11〜15・8400/8930/9020円</t>
+        </is>
+      </c>
+      <c r="H309" s="55" t="inlineStr">
+        <is>
+          <t>登山口「千畳敷（ロープウェイ山頂駅）」・定数12〜15・8400/8930/9020円。登山口＝千畳敷、拠点＝菅の台バスセンターに分離。バッジを通年運行に修正</t>
+        </is>
+      </c>
+      <c r="I309" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J309" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K309" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="53" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C310" s="53" t="inlineStr">
+        <is>
+          <t>karamatsu</t>
+        </is>
+      </c>
+      <c r="D310" s="54" t="inlineStr">
+        <is>
+          <t>唐松岳</t>
+        </is>
+      </c>
+      <c r="E310" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F310" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G310" s="55" t="inlineStr">
+        <is>
+          <t>登山口「八方尾根（ゴンドラ・リフト利用）」・定数22〜36・8870/9420/9420円</t>
+        </is>
+      </c>
+      <c r="H310" s="55" t="inlineStr">
+        <is>
+          <t>登山口「八方池山荘（リフト終点）」・定数19〜33・8870/9420/9420円。登山口＝八方池山荘、拠点＝八方駅に分離。八方アルペンライン6/6〜11/3</t>
+        </is>
+      </c>
+      <c r="I310" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J310" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K310" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="53" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C311" s="53" t="inlineStr">
+        <is>
+          <t>goryudake</t>
+        </is>
+      </c>
+      <c r="D311" s="54" t="inlineStr">
+        <is>
+          <t>五竜岳</t>
+        </is>
+      </c>
+      <c r="E311" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F311" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G311" s="55" t="inlineStr">
+        <is>
+          <t>登山口「白馬五竜テレキャビン」・定数45〜65・7940/7940/7630円</t>
+        </is>
+      </c>
+      <c r="H311" s="55" t="inlineStr">
+        <is>
+          <t>登山口「アルプス平（テレキャビン山頂駅）」・定数38・7940/7940/7630円。登山口＝アルプス平、拠点＝エスカルプラザに分離。テレキャビン6/20〜10/18</t>
+        </is>
+      </c>
+      <c r="I311" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J311" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K311" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="53" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C312" s="53" t="inlineStr">
+        <is>
+          <t>hiuchi</t>
+        </is>
+      </c>
+      <c r="D312" s="54" t="inlineStr">
+        <is>
+          <t>火打山</t>
+        </is>
+      </c>
+      <c r="E312" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F312" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G312" s="55" t="inlineStr">
+        <is>
+          <t>登山口「笹ヶ峰」・定数45〜45・9200/8540/9680円</t>
+        </is>
+      </c>
+      <c r="H312" s="55" t="inlineStr">
+        <is>
+          <t>登山口「笹ヶ峰登山口」・定数36・9200/8540/9680円。笹ヶ峰直行バス7/11〜10/25（観光サイト値・公式未確認）。運行終了後も登山道は利用可と明記</t>
+        </is>
+      </c>
+      <c r="I312" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J312" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K312" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="53" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C313" s="53" t="inlineStr">
+        <is>
+          <t>nikko_shirane</t>
+        </is>
+      </c>
+      <c r="D313" s="54" t="inlineStr">
+        <is>
+          <t>日光白根山</t>
+        </is>
+      </c>
+      <c r="E313" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F313" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G313" s="55" t="inlineStr">
+        <is>
+          <t>登山口「丸沼高原ロープウェイ」・定数21〜31・7380/7050/7400円</t>
+        </is>
+      </c>
+      <c r="H313" s="55" t="inlineStr">
+        <is>
+          <t>登山口「丸沼高原ロープウェイ山頂駅」・定数20〜28・7380/7050/7400円。ロープウェイ6/4〜11/8を登山適期と別管理。菅沼ルートを別登山口に分離</t>
+        </is>
+      </c>
+      <c r="I313" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J313" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K313" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="53" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C314" s="53" t="inlineStr">
+        <is>
+          <t>kinpusan</t>
+        </is>
+      </c>
+      <c r="D314" s="54" t="inlineStr">
+        <is>
+          <t>金峰山</t>
+        </is>
+      </c>
+      <c r="E314" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F314" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G314" s="55" t="inlineStr">
+        <is>
+          <t>登山口「大弛峠」・定数21〜45・6670/7000/7330円</t>
+        </is>
+      </c>
+      <c r="H314" s="55" t="inlineStr">
+        <is>
+          <t>登山口「大弛峠」・定数15〜35・6670/7000/7330円。大弛峠線：5/30〜11/8の土日祝・WEB予約・片道3,000円。廻り目平を別登山口に分離</t>
+        </is>
+      </c>
+      <c r="I314" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J314" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K314" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="53" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C315" s="53" t="inlineStr">
+        <is>
+          <t>okutama</t>
+        </is>
+      </c>
+      <c r="D315" s="54" t="inlineStr">
+        <is>
+          <t>大菩薩嶺</t>
+        </is>
+      </c>
+      <c r="E315" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F315" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G315" s="55" t="inlineStr">
+        <is>
+          <t>登山口「上日川峠」・定数22〜34・4130/4130/4130円</t>
+        </is>
+      </c>
+      <c r="H315" s="55" t="inlineStr">
+        <is>
+          <t>登山口「上日川峠」・定数16〜26・4130/4130/4130円。旧い塩山駅の記述（trainInfo）を廃止。上日川峠線4/18〜12/13。裂石ルートを別登山口に分離</t>
+        </is>
+      </c>
+      <c r="I315" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J315" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K315" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="53" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C316" s="53" t="inlineStr">
+        <is>
+          <t>norikura</t>
+        </is>
+      </c>
+      <c r="D316" s="54" t="inlineStr">
+        <is>
+          <t>乗鞍岳</t>
+        </is>
+      </c>
+      <c r="E316" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F316" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G316" s="55" t="inlineStr">
+        <is>
+          <t>登山口「畳平」・定数8〜18・10540/10230/10540円</t>
+        </is>
+      </c>
+      <c r="H316" s="55" t="inlineStr">
+        <is>
+          <t>登山口「畳平」・定数5〜9・10540/10230/10540円。「全便事前予約制」→「予約優先制」。7/1〜10/31。運賃は公式表で未確認</t>
+        </is>
+      </c>
+      <c r="I316" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J316" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K316" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="53" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C317" s="53" t="inlineStr">
+        <is>
+          <t>yari</t>
+        </is>
+      </c>
+      <c r="D317" s="54" t="inlineStr">
+        <is>
+          <t>槍ヶ岳</t>
+        </is>
+      </c>
+      <c r="E317" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F317" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G317" s="55" t="inlineStr">
+        <is>
+          <t>登山口「上高地」・定数55〜85・9190/8880/9190円</t>
+        </is>
+      </c>
+      <c r="H317" s="55" t="inlineStr">
+        <is>
+          <t>登山口「上高地バスターミナル」・定数51〜53・10540/10230/10230円。上高地アクセスを奥穂高岳と共有。「往路予約不要」→往復とも予約優先制。運賃を10,540/10,230/10,230円に修正（新島々〜上高地3,100円へ改定）</t>
+        </is>
+      </c>
+      <c r="I317" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J317" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K317" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="53" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C318" s="53" t="inlineStr">
+        <is>
+          <t>hotaka</t>
+        </is>
+      </c>
+      <c r="D318" s="54" t="inlineStr">
+        <is>
+          <t>奥穂高岳</t>
+        </is>
+      </c>
+      <c r="E318" s="54" t="inlineStr">
+        <is>
+          <t>新構造への移行（Phase C）</t>
+        </is>
+      </c>
+      <c r="F318" s="54" t="inlineStr">
+        <is>
+          <t>登山口・地図・コース定数・季節・アクセス</t>
+        </is>
+      </c>
+      <c r="G318" s="55" t="inlineStr">
+        <is>
+          <t>登山口「上高地」・定数50〜80・8890/8580/8890円</t>
+        </is>
+      </c>
+      <c r="H318" s="55" t="inlineStr">
+        <is>
+          <t>登山口「上高地バスターミナル」・定数48〜55・10540/10230/10230円。槍ヶ岳と同じ上高地アクセスを共有（旧運賃8,890円は槍ヶ岳と食い違っていた）</t>
+        </is>
+      </c>
+      <c r="I318" s="56" t="inlineStr">
+        <is>
+          <t>各事業者の公式情報・Yahoo!路線情報・国土地理院 地名検索</t>
+        </is>
+      </c>
+      <c r="J318" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 15項目 0件</t>
+        </is>
+      </c>
+      <c r="K318" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K299"/>
+  <autoFilter ref="A1:K318"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証チェックリスト'!$A$1:$G$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経路・運賃・時間データ一覧'!$A$1:$N$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'バス情報整合性チェック'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$318</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'修正履歴データ管理表'!$A$1:$K$322</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -813,12 +813,12 @@
       </c>
       <c r="E2" s="53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F2" s="55" t="inlineStr">
         <is>
-          <t>横浜発が「小田急・相鉄直通」(1964年廃止の存在しないルート)だったため全面書き換え。運賃も新価格に更新 ｜【2026-09-25追加修正】渋沢→大倉バスを15分に統一（合計-5分） ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照）</t>
+          <t>横浜発が「小田急・相鉄直通」(1964年廃止の存在しないルート)だったため全面書き換え。運賃も新価格に更新 ｜【2026-09-25追加修正】渋沢→大倉バスを15分に統一（合計-5分） ｜【2026-09-25追加修正】同一ゲートウェイの運賃差額を統一（修正履歴参照） ／ 2026-10-06: 大倉ルートを追加</t>
         </is>
       </c>
       <c r="G2" s="37" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="E45" s="53" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F45" s="55" t="inlineStr">
         <is>
-          <t>横浜発のバッファ（legsum120分+0分）が新宿発（130+30分）・大宮発（160+30分）の+30分基準と不揃いだったため150分（120+30）に統一。FAQ本文の最寄りバス停表記が「仙石原バス停」という誤記だったため正しい「金時神社入口バス停」に修正。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照） ｜【2026-09-26】経路・時間・運賃を駅探・公式情報で再検証して更新（修正履歴参照）</t>
+          <t>横浜発のバッファ（legsum120分+0分）が新宿発（130+30分）・大宮発（160+30分）の+30分基準と不揃いだったため150分（120+30）に統一。FAQ本文の最寄りバス停表記が「仙石原バス停」という誤記だったため正しい「金時神社入口バス停」に修正。 ｜【2026-09-25追加修正】ルートデータの誤コピー/異常値を修正（修正履歴参照） ｜【2026-09-26】経路・時間・運賃を駅探・公式情報で再検証して更新（修正履歴参照） ／ 2026-10-06: 住所・登山口を訂正</t>
         </is>
       </c>
       <c r="G45" s="37" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="E48" s="53" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F48" s="55" t="inlineStr">
         <is>
-          <t>経路・時間・運賃とも整合性確認済み、問題なし。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
+          <t>経路・時間・運賃とも整合性確認済み、問題なし。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正 ／ 2026-10-06: 徒歩50分を追加、錦滝方面の通行禁止を表示</t>
         </is>
       </c>
       <c r="G48" s="37" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="E60" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F60" s="55" t="inlineStr">
         <is>
-          <t>経路・運賃は概ね妥当。大宮発のバッファ（+0分）・横浜発（+7分）が新宿発（+10分）と不揃いだったため+10分に統一（大宮130→140分、横浜172→182分）。運賃は変更なし。</t>
+          <t>経路・運賃は概ね妥当。大宮発のバッファ（+0分）・横浜発（+7分）が新宿発（+10分）と不揃いだったため+10分に統一（大宮130→140分、横浜172→182分）。運賃は変更なし。 ／ 2026-10-06: シャトルバスの記載を削除しタクシーに。運賃を引き直し</t>
         </is>
       </c>
       <c r="G60" s="37" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E71" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F71" s="55" t="inlineStr">
         <is>
-          <t>大宮発legの「大宮→米沢」区間が150分と表示されていたが、実際のつばさ大宮-米沢所要時間（89〜110分）を大幅に超過（新宿経由より大宮発の方が遅いのは物理的に矛盾）。104分に修正しtrainTimeOmiya 196→150分に。</t>
+          <t>大宮発legの「大宮→米沢」区間が150分と表示されていたが、実際のつばさ大宮-米沢所要時間（89〜110分）を大幅に超過（新宿経由より大宮発の方が遅いのは物理的に矛盾）。104分に修正しtrainTimeOmiya 196→150分に。 ／ 2026-10-06: 登山口を天元台に訂正、運賃・時間を引き直し</t>
         </is>
       </c>
       <c r="G71" s="37" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="E90" s="53" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F90" s="55" t="inlineStr">
         <is>
-          <t>荒川岳・赤石岳と同一の畑薙第一ダム経由（降車地=聖沢登山口）。trainAccess=trueに変更、trainRoutes新規構築。 ｜【2026-09-26追加修正】同一ゲートウェイの経路・時間・運賃差額を駅探で再検証し統一（修正履歴参照） ｜【2026-09-26】2026年の運行期間・運賃で注記を更新、新宿発運賃の内訳（5,940＋5,000円）を確認</t>
+          <t>荒川岳・赤石岳と同一の畑薙第一ダム経由（降車地=聖沢登山口）。trainAccess=trueに変更、trainRoutes新規構築。 ｜【2026-09-26追加修正】同一ゲートウェイの経路・時間・運賃差額を駅探で再検証し統一（修正履歴参照） ｜【2026-09-26】2026年の運行期間・運賃で注記を更新、新宿発運賃の内訳（5,940＋5,000円）を確認 ／ 2026-10-06: 住所・駐車場を訂正。通行状況は未確認</t>
         </is>
       </c>
       <c r="G90" s="37" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="E91" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F91" s="55" t="inlineStr">
         <is>
-          <t>trainAccess=falseだったが、道の駅遠山郷から予約制タクシーで到達可能と判明。trueに変更、trainRoutes新規構築（要事前予約・前泊推奨）。</t>
+          <t>trainAccess=falseだったが、道の駅遠山郷から予約制タクシーで到達可能と判明。trueに変更、trainRoutes新規構築（要事前予約・前泊推奨）。 ／ 2026-10-06: 終点を芝沢ゲートに</t>
         </is>
       </c>
       <c r="G91" s="37" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="E95" s="53" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F95" s="55" t="inlineStr">
         <is>
-          <t>重大な経路誤り。nokogiriyamaと同一の「甲府→広河原」データが誤って流用されていたが、正しい登山口は「奈良田」（新宿→身延→はやかわ乗合バス経由）。全面再構築。 ｜【2026-09-26追加修正】同一ゲートウェイの経路・時間・運賃差額を駅探で再検証し統一（修正履歴参照）</t>
+          <t>重大な経路誤り。nokogiriyamaと同一の「甲府→広河原」データが誤って流用されていたが、正しい登山口は「奈良田」（新宿→身延→はやかわ乗合バス経由）。全面再構築。 ｜【2026-09-26追加修正】同一ゲートウェイの経路・時間・運賃差額を駅探で再検証し統一（修正履歴参照） ／ 2026-10-06: 電車を広河原行きに変更</t>
         </is>
       </c>
       <c r="G95" s="37" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="E99" s="53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F99" s="55" t="inlineStr">
         <is>
-          <t>重大な経路誤り。noutoriと同一の「甲府→広河原」データが誤って流用されていたが、正しい登山口は「戸台パーク」（新宿→茅野→南アルプスジオライナー経由）。全面再構築。 ｜【2026-09-25追加修正】茅野ゲートウェイ方式に統一（大宮=立川、横浜=八王子乗換のあずさ）</t>
+          <t>重大な経路誤り。noutoriと同一の「甲府→広河原」データが誤って流用されていたが、正しい登山口は「戸台パーク」（新宿→茅野→南アルプスジオライナー経由）。全面再構築。 ｜【2026-09-25追加修正】茅野ゲートウェイ方式に統一（大宮=立川、横浜=八王子乗換のあずさ） ／ 2026-10-06: 登山口を戸台パークに</t>
         </is>
       </c>
       <c r="G99" s="37" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="E100" s="53" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F100" s="56" t="inlineStr">
         <is>
-          <t>**経路実在性バグ**: 大宮・横浜発が「新宿駅からJR飯田線」208分と案内していたが、JR飯田線は新宿駅を通らないため物理的に不可能（豊橋〜辰野間の路線）。新宿発と同じ高速バス（新宿〜駒ヶ根線、220分）に統一。大宮:2時間35分/6,308円、横浜:2時間39分/6,396円（所要時間のみ修正、運賃は元々妥当だったため据え置き）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正</t>
+          <t>**経路実在性バグ**: 大宮・横浜発が「新宿駅からJR飯田線」208分と案内していたが、JR飯田線は新宿駅を通らないため物理的に不可能（豊橋〜辰野間の路線）。新宿発と同じ高速バス（新宿〜駒ヶ根線、220分）に統一。大宮:2時間35分/6,308円、横浜:2時間39分/6,396円（所要時間のみ修正、運賃は元々妥当だったため据え置き）。 ｜【2026-09-27】大宮・横浜発の運賃が「新宿発＋528/616円」の足し算だった誤りを、Yahoo!路線情報の出発地別の通し運賃・最適経路で修正 ／ 2026-10-06: 登山口を伊奈川ダムに訂正、経路を須原駅経由に作り直し</t>
         </is>
       </c>
       <c r="G100" s="37" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="E125" s="53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F125" s="55" t="inlineStr">
         <is>
-          <t>複数の問題を発見。①新宿・オミヤ発は「地蔵堂バス停」で終端していたが、横浜発だけ「地蔵堂バス停→徒歩20分→登山口」という追加区間があり構造が不一致だったため統一。②乗換案内リンクが横浜発のみが通る「大雄山駅」を指しており、新宿・オミヤ発（新松田駅経由）の実態と食い違っていたため「新松田駅」に修正。③バス時刻表リンクが全く別会社（伊豆箱根バス）のページを指しており、実際に使う「箱根登山バス」の公式ページに修正。横浜発のバス区間のオペレーター名表記（「バス」の未記載）も「箱根登山バス」に補完。</t>
+          <t>複数の問題を発見。①新宿・オミヤ発は「地蔵堂バス停」で終端していたが、横浜発だけ「地蔵堂バス停→徒歩20分→登山口」という追加区間があり構造が不一致だったため統一。②乗換案内リンクが横浜発のみが通る「大雄山駅」を指しており、新宿・オミヤ発（新松田駅経由）の実態と食い違っていたため「新松田駅」に修正。③バス時刻表リンクが全く別会社（伊豆箱根バス）のページを指しており、実際に使う「箱根登山バス」の公式ページに修正。横浜発のバス区間のオペレーター名表記（「バス」の未記載）も「箱根登山バス」に補完。 ／ 2026-10-06: 根拠のない徒歩20分を削除</t>
         </is>
       </c>
       <c r="G125" s="37" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="F2" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[小田急小田原線]--&gt; 渋沢駅 --[神奈川中央交通バス]--&gt; 大倉バス停 塔ノ岳・丹沢山方面</t>
+          <t>新宿駅 --[小田急小田原線]--&gt; 渋沢駅 --[神奈川中央交通バス]--&gt; 大倉バス停</t>
         </is>
       </c>
       <c r="G2" s="41" t="n">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="I2" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急小田原線]--&gt; 渋沢駅 --[神奈川中央交通バス]--&gt; 大倉バス停 塔ノ岳・丹沢山方面</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急小田原線]--&gt; 渋沢駅 --[神奈川中央交通バス]--&gt; 大倉バス停</t>
         </is>
       </c>
       <c r="J2" s="41" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="L2" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[相鉄本線特急]--&gt; 海老名駅 --[小田急小田原線急行]--&gt; 渋沢駅 --[神奈川中央交通バス]--&gt; 大倉バス停 塔ノ岳・丹沢山方面</t>
+          <t>横浜駅 --[相鉄本線特急]--&gt; 海老名駅 --[小田急小田原線急行]--&gt; 渋沢駅 --[神奈川中央交通バス]--&gt; 大倉バス停</t>
         </is>
       </c>
       <c r="M2" s="41" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="F40" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[京王線]--&gt; 高尾山口駅 --[徒歩]--&gt; 登山口</t>
+          <t>新宿駅 --[京王線]--&gt; 高尾山口駅 --[徒歩]--&gt; 清滝駅前（1号路・6号路・稲荷山コース入口）</t>
         </is>
       </c>
       <c r="G40" s="41" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="I40" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[京王線]--&gt; 高尾山口駅 --[徒歩]--&gt; 登山口</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[京王線]--&gt; 高尾山口駅 --[徒歩]--&gt; 清滝駅前（1号路・6号路・稲荷山コース入口）</t>
         </is>
       </c>
       <c r="J40" s="41" t="n">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="L40" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR中央線・京王線]--&gt; 高尾山口駅 --[徒歩]--&gt; 登山口</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR中央線・京王線]--&gt; 高尾山口駅 --[徒歩]--&gt; 清滝駅前（1号路・6号路・稲荷山コース入口）</t>
         </is>
       </c>
       <c r="M40" s="41" t="n">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F45" s="44" t="inlineStr">
         <is>
-          <t>新宿駅（バスタ新宿） --[小田急ハイウェイバス「新宿〜御殿場・箱根線」]--&gt; 金時登山口（金時神社入口・乙女口にも停車）</t>
+          <t>新宿駅（バスタ新宿） --[小田急ハイウェイバス「新宿〜御殿場・箱根線」]--&gt; 金時神社入口（金時登山口・乙女口にも停車）</t>
         </is>
       </c>
       <c r="G45" s="41" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="I45" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅（バスタ新宿） --[小田急ハイウェイバス「新宿〜御殿場・箱根線」]--&gt; 金時登山口（金時神社入口・乙女口にも停車）</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅（バスタ新宿） --[小田急ハイウェイバス「新宿〜御殿場・箱根線」]--&gt; 金時神社入口（金時登山口・乙女口にも停車）</t>
         </is>
       </c>
       <c r="J45" s="41" t="n">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="L45" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅（バスタ新宿） --[小田急ハイウェイバス「新宿〜御殿場・箱根線」]--&gt; 金時登山口（金時神社入口・乙女口にも停車）</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅（バスタ新宿） --[小田急ハイウェイバス「新宿〜御殿場・箱根線」]--&gt; 金時神社入口（金時登山口・乙女口にも停車）</t>
         </is>
       </c>
       <c r="M45" s="41" t="n">
@@ -9084,36 +9084,36 @@
       </c>
       <c r="F48" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 小淵沢駅 --[タクシー]--&gt; 尾白川渓谷駐車場</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 小淵沢駅 --[タクシー]--&gt; 尾白川渓谷駐車場 --[徒歩]--&gt; 矢立石登山口</t>
         </is>
       </c>
       <c r="G48" s="41" t="n">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="H48" s="41" t="n">
-        <v>7930</v>
+        <v>5430</v>
       </c>
       <c r="I48" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線・特急あずさ（新宿乗換）]--&gt; 小淵沢駅 --[タクシー]--&gt; 尾白川渓谷駐車場</t>
+          <t>大宮駅 --[JR埼京線・特急あずさ（新宿乗換）]--&gt; 小淵沢駅 --[タクシー]--&gt; 尾白川渓谷駐車場 --[徒歩]--&gt; 矢立石登山口</t>
         </is>
       </c>
       <c r="J48" s="41" t="n">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="K48" s="41" t="n">
-        <v>7930</v>
+        <v>5430</v>
       </c>
       <c r="L48" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR横浜線・特急あずさ（八王子乗換）]--&gt; 小淵沢駅 --[タクシー]--&gt; 尾白川渓谷駐車場</t>
+          <t>横浜駅 --[JR横浜線・特急あずさ（八王子乗換）]--&gt; 小淵沢駅 --[タクシー]--&gt; 尾白川渓谷駐車場 --[徒歩]--&gt; 矢立石登山口</t>
         </is>
       </c>
       <c r="M48" s="41" t="n">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="N48" s="41" t="n">
-        <v>7270</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="49" ht="26.25" customHeight="1" s="30">
@@ -9732,36 +9732,36 @@
       </c>
       <c r="F60" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線あさま（東京駅乗換）]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 黒姫駅 --[黒姫高原シャトルバス]--&gt; 古池登山口（季節）</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 黒姫駅 --[タクシー]--&gt; 大橋登山口</t>
         </is>
       </c>
       <c r="G60" s="41" t="n">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="H60" s="41" t="n">
-        <v>9000</v>
+        <v>7999</v>
       </c>
       <c r="I60" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線あさま]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 黒姫駅 --[黒姫高原シャトルバス]--&gt; 古池登山口（季節運行）</t>
+          <t>大宮駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 黒姫駅 --[タクシー]--&gt; 大橋登山口</t>
         </is>
       </c>
       <c r="J60" s="41" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="K60" s="41" t="n">
-        <v>8472</v>
+        <v>7339</v>
       </c>
       <c r="L60" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線あさま]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 黒姫駅 --[黒姫高原シャトルバス]--&gt; 古池登山口（季節）</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 長野駅 --[しなの鉄道北しなの線]--&gt; 黒姫駅 --[タクシー]--&gt; 大橋登山口</t>
         </is>
       </c>
       <c r="M60" s="41" t="n">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="N60" s="41" t="n">
-        <v>8972</v>
+        <v>9539</v>
       </c>
     </row>
     <row r="61" ht="39" customHeight="1" s="30">
@@ -10346,36 +10346,36 @@
       </c>
       <c r="F71" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR奥羽本線]--&gt; 米沢駅 --[山交バス]--&gt; 白布温泉 --[天元台ロープウェイ]--&gt; 天元台高原</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[山形新幹線つばさ]--&gt; 米沢駅 --[山交バス 米沢〜白布温泉線]--&gt; 白布湯元 --[天元台ロープウェイ]--&gt; 天元台高原駅</t>
         </is>
       </c>
       <c r="G71" s="41" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H71" s="41" t="n">
-        <v>11720</v>
+        <v>11510</v>
       </c>
       <c r="I71" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[山形新幹線つばさ]--&gt; 米沢駅 --[山交バス]--&gt; 白布温泉 --[天元台ロープウェイ]--&gt; 天元台高原</t>
+          <t>大宮駅 --[山形新幹線つばさ]--&gt; 米沢駅 --[山交バス 米沢〜白布温泉線]--&gt; 白布湯元 --[天元台ロープウェイ]--&gt; 天元台高原駅</t>
         </is>
       </c>
       <c r="J71" s="41" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="K71" s="41" t="n">
-        <v>11192</v>
+        <v>11180</v>
       </c>
       <c r="L71" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[山形新幹線つばさ]--&gt; 米沢駅 --[山交バス]--&gt; 白布温泉 --[天元台ロープウェイ]--&gt; 天元台高原</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[山形新幹線つばさ]--&gt; 米沢駅 --[山交バス 米沢〜白布温泉線]--&gt; 白布湯元 --[天元台ロープウェイ]--&gt; 天元台高原駅</t>
         </is>
       </c>
       <c r="M71" s="41" t="n">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="N71" s="41" t="n">
-        <v>11692</v>
+        <v>12270</v>
       </c>
     </row>
     <row r="72" ht="51.75" customHeight="1" s="30">
@@ -11434,33 +11434,33 @@
       </c>
       <c r="F91" s="44" t="inlineStr">
         <is>
-          <t>バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[南信州バス(遠山郷方面路線バス)]--&gt; 道の駅遠山郷 --[予約制タクシー(天竜観光タクシー等・要事前電話予約)]--&gt; 易老渡</t>
+          <t>バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー(天竜観光タクシー等・要事前電話予約)]--&gt; 芝沢ゲート --[徒歩（林道 約5km）]--&gt; 易老渡</t>
         </is>
       </c>
       <c r="G91" s="41" t="n">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="H91" s="41" t="n">
         <v>24800</v>
       </c>
       <c r="I91" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[南信州バス(遠山郷方面路線バス)]--&gt; 道の駅遠山郷 --[予約制タクシー(天竜観光タクシー等・要事前電話予約)]--&gt; 易老渡</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー(天竜観光タクシー等・要事前電話予約)]--&gt; 芝沢ゲート --[徒歩（林道 約5km）]--&gt; 易老渡</t>
         </is>
       </c>
       <c r="J91" s="41" t="n">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="K91" s="41" t="n">
         <v>25380</v>
       </c>
       <c r="L91" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[南信州バス(遠山郷方面路線バス)]--&gt; 道の駅遠山郷 --[予約制タクシー(天竜観光タクシー等・要事前電話予約)]--&gt; 易老渡</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー(天竜観光タクシー等・要事前電話予約)]--&gt; 芝沢ゲート --[徒歩（林道 約5km）]--&gt; 易老渡</t>
         </is>
       </c>
       <c r="M91" s="41" t="n">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="N91" s="41" t="n">
         <v>25380</v>
@@ -11666,36 +11666,36 @@
       </c>
       <c r="F95" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 奈良田温泉 --[徒歩]--&gt; 農鳥岳登山口（大門沢登山口）</t>
+          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「南アルプス登山バス」]--&gt; 広河原（マイカー規制）</t>
         </is>
       </c>
       <c r="G95" s="41" t="n">
-        <v>318</v>
+        <v>230</v>
       </c>
       <c r="H95" s="41" t="n">
-        <v>6770</v>
+        <v>6290</v>
       </c>
       <c r="I95" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 奈良田温泉 --[徒歩]--&gt; 農鳥岳登山口（大門沢登山口）</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「南アルプス登山バス」]--&gt; 広河原（マイカー規制）</t>
         </is>
       </c>
       <c r="J95" s="41" t="n">
-        <v>348</v>
+        <v>265</v>
       </c>
       <c r="K95" s="41" t="n">
-        <v>6210</v>
+        <v>7060</v>
       </c>
       <c r="L95" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 奈良田温泉 --[徒歩]--&gt; 農鳥岳登山口（大門沢登山口）</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「南アルプス登山バス」]--&gt; 広河原（マイカー規制）</t>
         </is>
       </c>
       <c r="M95" s="41" t="n">
-        <v>352</v>
+        <v>269</v>
       </c>
       <c r="N95" s="41" t="n">
-        <v>6770</v>
+        <v>7060</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="30">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="F99" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[南アルプスジオライナー]--&gt; 戸台パーク（南アルプスマイカー規制のため利用、乗車協力金別途）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 茅野駅 --[南アルプスジオライナー]--&gt; 戸台パーク</t>
         </is>
       </c>
       <c r="G99" s="41" t="n">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="I99" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[南アルプスジオライナー]--&gt; 戸台パーク（南アルプスマイカー規制のため利用、乗車協力金別途）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 茅野駅 --[南アルプスジオライナー]--&gt; 戸台パーク</t>
         </is>
       </c>
       <c r="J99" s="41" t="n">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="L99" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[南アルプスジオライナー]--&gt; 戸台パーク（南アルプスマイカー規制のため利用、乗車協力金別途）</t>
+          <t>横浜駅 --[JR京浜東北線・横浜線（八王子乗換）]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 茅野駅 --[南アルプスジオライナー]--&gt; 戸台パーク</t>
         </is>
       </c>
       <c r="M99" s="41" t="n">
@@ -11956,36 +11956,36 @@
       </c>
       <c r="F100" s="44" t="inlineStr">
         <is>
-          <t>バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 塩尻駅 --[JR中央本線（中津川行）]--&gt; 須原駅 --[タクシー]--&gt; 伊奈川ダム</t>
         </is>
       </c>
       <c r="G100" s="41" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H100" s="41" t="n">
-        <v>5780</v>
+        <v>7830</v>
       </c>
       <c r="I100" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 塩尻駅 --[JR中央本線（中津川行）]--&gt; 須原駅 --[タクシー]--&gt; 伊奈川ダム</t>
         </is>
       </c>
       <c r="J100" s="41" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K100" s="41" t="n">
-        <v>6310</v>
+        <v>7830</v>
       </c>
       <c r="L100" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 塩尻駅 --[JR中央本線（中津川行）]--&gt; 須原駅 --[タクシー]--&gt; 伊奈川ダム</t>
         </is>
       </c>
       <c r="M100" s="41" t="n">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="N100" s="41" t="n">
-        <v>6400</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="101" ht="39" customHeight="1" s="30">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="F108" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線・青梅線（立川・青梅乗換）]--&gt; 軍畑駅 --[徒歩]--&gt; 登山口</t>
+          <t>新宿駅 --[JR中央線・青梅線（立川・青梅乗換）]--&gt; 軍畑駅 --[徒歩]--&gt; 高水山登山口（高源寺）</t>
         </is>
       </c>
       <c r="G108" s="41" t="n">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="I108" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・青梅線（西国分寺・立川・青梅乗換）]--&gt; 軍畑駅 --[徒歩]--&gt; 登山口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・青梅線（西国分寺・立川・青梅乗換）]--&gt; 軍畑駅 --[徒歩]--&gt; 高水山登山口（高源寺）</t>
         </is>
       </c>
       <c r="J108" s="41" t="n">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="L108" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR横浜線・八高線・青梅線（八王子・立川・青梅乗換）]--&gt; 軍畑駅 --[徒歩]--&gt; 登山口</t>
+          <t>横浜駅 --[JR横浜線・八高線・青梅線（八王子・立川・青梅乗換）]--&gt; 軍畑駅 --[徒歩]--&gt; 高水山登山口（高源寺）</t>
         </is>
       </c>
       <c r="M108" s="41" t="n">
@@ -13406,33 +13406,33 @@
       </c>
       <c r="F125" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[箱根登山バス]--&gt; 地蔵堂バス停 --[徒歩]--&gt; 登山口</t>
+          <t>新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[箱根登山バス]--&gt; 地蔵堂バス停（登山口）</t>
         </is>
       </c>
       <c r="G125" s="41" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H125" s="41" t="n">
         <v>1536</v>
       </c>
       <c r="I125" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[箱根登山バス]--&gt; 地蔵堂バス停 --[徒歩]--&gt; 登山口</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[箱根登山バス]--&gt; 地蔵堂バス停（登山口）</t>
         </is>
       </c>
       <c r="J125" s="41" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="K125" s="41" t="n">
         <v>2064</v>
       </c>
       <c r="L125" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 小田原駅 --[伊豆箱根鉄道大雄山線]--&gt; 大雄山駅 --[箱根登山バス]--&gt; 地蔵堂バス停 --[徒歩]--&gt; 登山口</t>
+          <t>横浜駅 --[JR東海道線]--&gt; 小田原駅 --[伊豆箱根鉄道大雄山線]--&gt; 大雄山駅 --[箱根登山バス]--&gt; 地蔵堂バス停（登山口）</t>
         </is>
       </c>
       <c r="M125" s="41" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="N125" s="41" t="n">
         <v>2010</v>
@@ -24235,7 +24235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K318"/>
+  <dimension ref="A1:K345"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -41741,8 +41741,1493 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="53" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C319" s="53" t="inlineStr">
+        <is>
+          <t>norikura</t>
+        </is>
+      </c>
+      <c r="D319" s="54" t="inlineStr">
+        <is>
+          <t>乗鞍岳</t>
+        </is>
+      </c>
+      <c r="E319" s="54" t="inlineStr">
+        <is>
+          <t>コース定数（ルートの元データ誤り）</t>
+        </is>
+      </c>
+      <c r="F319" s="54" t="inlineStr">
+        <is>
+          <t>routes（時間・距離・標高差）</t>
+        </is>
+      </c>
+      <c r="G319" s="55" t="inlineStr">
+        <is>
+          <t>畳平〜剣ヶ峰往復 2時間30分/5.0km/+250m（定数9）。標高差が畳平2,702m→剣ヶ峰3,026mの単純差324mより小さく誤り。途中区間「肩の小屋〜剣ヶ峰往復」（定数5）が別ルート扱いで、上部表示が5〜9に</t>
+        </is>
+      </c>
+      <c r="H319" s="55" t="inlineStr">
+        <is>
+          <t>2時間55分/5.3km/+391m（定数11）に修正。途中区間のルートは代表ルートに統合（removedRoutesに記録）。上部表示は定数11</t>
+        </is>
+      </c>
+      <c r="I319" s="56" t="inlineStr">
+        <is>
+          <t>山と高原地図Web（往復5.3km・±391m・2時間55分、コース定数〜11）</t>
+        </is>
+      </c>
+      <c r="J319" s="55" t="inlineStr">
+        <is>
+          <t>一般式で再計算＝11（出典の値と一致）。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K319" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="53" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C320" s="53" t="inlineStr">
+        <is>
+          <t>全山</t>
+        </is>
+      </c>
+      <c r="D320" s="54" t="inlineStr">
+        <is>
+          <t>山の位置座標（lat/lng）</t>
+        </is>
+      </c>
+      <c r="E320" s="54" t="inlineStr">
+        <is>
+          <t>座標の誤り（天気・地図表示に影響）</t>
+        </is>
+      </c>
+      <c r="F320" s="54" t="inlineStr">
+        <is>
+          <t>lat / lng</t>
+        </is>
+      </c>
+      <c r="G320" s="55" t="inlineStr">
+        <is>
+          <t>81山で山の位置が実際の山頂から3km以上ずれていた（最大：小金沢山 約26km、農鳥岳 約21km、間ノ岳 約20km）。この座標は山ページの天気予報とトップの地図表示に使われる</t>
+        </is>
+      </c>
+      <c r="H320" s="55" t="inlineStr">
+        <is>
+          <t>国土地理院の地名検索で同名の山頂を特定できた145山の座標を更新（旧値は summitCoordLegacy に保存）。未解決：和名倉山・丸山（奥武蔵）・草戸山・笹子雁ヶ腹摺山・高水三山・鎌倉アルプス・吾妻山（二宮）・嵐山</t>
+        </is>
+      </c>
+      <c r="I320" s="56" t="inlineStr">
+        <is>
+          <t>国土地理院 地名検索（msearch.gsi.go.jp）</t>
+        </is>
+      </c>
+      <c r="J320" s="55" t="inlineStr">
+        <is>
+          <t>同名が複数ある山は最寄り候補との距離差で判定。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K320" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="53" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C321" s="53" t="inlineStr">
+        <is>
+          <t>134山</t>
+        </is>
+      </c>
+      <c r="D321" s="54" t="inlineStr">
+        <is>
+          <t>地図リンク</t>
+        </is>
+      </c>
+      <c r="E321" s="54" t="inlineStr">
+        <is>
+          <t>座標の二重管理</t>
+        </is>
+      </c>
+      <c r="F321" s="54" t="inlineStr">
+        <is>
+          <t>gmapUrl / amapUrl / mapBtnsHtml</t>
+        </is>
+      </c>
+      <c r="G321" s="55" t="inlineStr">
+        <is>
+          <t>山ページの地図ボタンは表示上は登山口の座標（mapBtnsHtml）だが、読み込み後にJSが gmapUrl（山頂付近を中心にした名称検索）で上書きしていた</t>
+        </is>
+      </c>
+      <c r="H321" s="55" t="inlineStr">
+        <is>
+          <t>未移行の134山で gmapUrl / amapUrl を地図ボタンと同じリンクに統一（旧値は gmapUrlLegacy / amapUrlLegacy に保存）。ボタンの座標は山の位置から20km以内であることを確認</t>
+        </is>
+      </c>
+      <c r="I321" s="56" t="inlineStr">
+        <is>
+          <t>既存の地図ボタン（Googleプレイス）</t>
+        </is>
+      </c>
+      <c r="J321" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K321" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="53" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C322" s="53" t="inlineStr">
+        <is>
+          <t>18山</t>
+        </is>
+      </c>
+      <c r="D322" s="54" t="inlineStr">
+        <is>
+          <t>移行済みの山</t>
+        </is>
+      </c>
+      <c r="E322" s="54" t="inlineStr">
+        <is>
+          <t>コース定数（表示を元に戻す）</t>
+        </is>
+      </c>
+      <c r="F322" s="54" t="inlineStr">
+        <is>
+          <t>coeffMin / coeffMax ほか</t>
+        </is>
+      </c>
+      <c r="G322" s="55" t="inlineStr">
+        <is>
+          <t>新構造への移行時に上部表示をルートの値へ切替えたが、ルートの時間・距離・標高差が未照合で低く出る山があった</t>
+        </is>
+      </c>
+      <c r="H322" s="55" t="inlineStr">
+        <is>
+          <t>照合が済むまで従来の表示値に戻した（乗鞍岳のみ出典と照合済みで11）。ルートの値を上部表示に使うのは coeffFromRoutes: true の山だけにする仕組みへ変更</t>
+        </is>
+      </c>
+      <c r="I322" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J322" s="55" t="inlineStr">
+        <is>
+          <t>検索ページのカードも元の値に戻した。check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K322" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="53" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C323" s="53" t="inlineStr">
+        <is>
+          <t>tanzawa</t>
+        </is>
+      </c>
+      <c r="D323" s="54" t="inlineStr">
+        <is>
+          <t>丹沢山</t>
+        </is>
+      </c>
+      <c r="E323" s="54" t="inlineStr">
+        <is>
+          <t>登山口とルートの不一致</t>
+        </is>
+      </c>
+      <c r="F323" s="54" t="inlineStr">
+        <is>
+          <t>ルート・電車の終点</t>
+        </is>
+      </c>
+      <c r="G323" s="55" t="inlineStr">
+        <is>
+          <t>ルートが塩水橋（車向け）2本だけ。電車の終点が「塔ノ岳・丹沢山方面」</t>
+        </is>
+      </c>
+      <c r="H323" s="55" t="inlineStr">
+        <is>
+          <t>大倉〜塔ノ岳〜丹沢山（往復 10時間49分・18.0km・+1,751m）を追加。電車の終点を大倉バス停に</t>
+        </is>
+      </c>
+      <c r="I323" s="56" t="inlineStr">
+        <is>
+          <t>YAMAPモデルコース94542</t>
+        </is>
+      </c>
+      <c r="J323" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K323" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="53" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C324" s="53" t="inlineStr">
+        <is>
+          <t>hirugata</t>
+        </is>
+      </c>
+      <c r="D324" s="54" t="inlineStr">
+        <is>
+          <t>蛭ヶ岳</t>
+        </is>
+      </c>
+      <c r="E324" s="54" t="inlineStr">
+        <is>
+          <t>登山口の表記</t>
+        </is>
+      </c>
+      <c r="F324" s="54" t="inlineStr">
+        <is>
+          <t>登山口・駐車場</t>
+        </is>
+      </c>
+      <c r="G324" s="55" t="inlineStr">
+        <is>
+          <t>「大倉 or 姫次」／大倉駐車場 約80台・500円</t>
+        </is>
+      </c>
+      <c r="H324" s="55" t="inlineStr">
+        <is>
+          <t>大倉／丹沢山と同じ駐車場表記（約150台・時間制）</t>
+        </is>
+      </c>
+      <c r="I324" s="56" t="inlineStr">
+        <is>
+          <t>秦野戸川公園の駐車場情報</t>
+        </is>
+      </c>
+      <c r="J324" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K324" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="53" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C325" s="53" t="inlineStr">
+        <is>
+          <t>kurobegorodam</t>
+        </is>
+      </c>
+      <c r="D325" s="54" t="inlineStr">
+        <is>
+          <t>黒部五郎岳</t>
+        </is>
+      </c>
+      <c r="E325" s="54" t="inlineStr">
+        <is>
+          <t>登山口の表記</t>
+        </is>
+      </c>
+      <c r="F325" s="54" t="inlineStr">
+        <is>
+          <t>登山口</t>
+        </is>
+      </c>
+      <c r="G325" s="55" t="inlineStr">
+        <is>
+          <t>「折立または新穂高」</t>
+        </is>
+      </c>
+      <c r="H325" s="55" t="inlineStr">
+        <is>
+          <t>折立</t>
+        </is>
+      </c>
+      <c r="I325" s="56" t="inlineStr">
+        <is>
+          <t>既存の経路データ（折立行き）と一致</t>
+        </is>
+      </c>
+      <c r="J325" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K325" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="53" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C326" s="53" t="inlineStr">
+        <is>
+          <t>takao・takamizusanzan・yaguradake</t>
+        </is>
+      </c>
+      <c r="D326" s="54" t="inlineStr">
+        <is>
+          <t>高尾山・高水三山・矢倉岳</t>
+        </is>
+      </c>
+      <c r="E326" s="54" t="inlineStr">
+        <is>
+          <t>終点の表記</t>
+        </is>
+      </c>
+      <c r="F326" s="54" t="inlineStr">
+        <is>
+          <t>電車の終点</t>
+        </is>
+      </c>
+      <c r="G326" s="55" t="inlineStr">
+        <is>
+          <t>終点が「登山口」。矢倉岳は地蔵堂バス停から「徒歩20分→登山口」</t>
+        </is>
+      </c>
+      <c r="H326" s="55" t="inlineStr">
+        <is>
+          <t>清滝駅前／高水山登山口（高源寺）／地蔵堂バス停（登山口）。矢倉岳の徒歩20分は根拠がないため削除（所要時間−20分）</t>
+        </is>
+      </c>
+      <c r="I326" s="56" t="inlineStr">
+        <is>
+          <t>既存データの登山口名</t>
+        </is>
+      </c>
+      <c r="J326" s="55" t="inlineStr">
+        <is>
+          <t>legs合計と所要時間の一致</t>
+        </is>
+      </c>
+      <c r="K326" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="53" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C327" s="53" t="inlineStr">
+        <is>
+          <t>azuma</t>
+        </is>
+      </c>
+      <c r="D327" s="54" t="inlineStr">
+        <is>
+          <t>西吾妻山</t>
+        </is>
+      </c>
+      <c r="E327" s="54" t="inlineStr">
+        <is>
+          <t>登山口の誤り・運賃・時間</t>
+        </is>
+      </c>
+      <c r="F327" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G327" s="55" t="inlineStr">
+        <is>
+          <t>登山口「浄土平」（別の山域）。新宿→米沢「JR奥羽本線140分」。バス40分。11,720／11,192／11,692円</t>
+        </is>
+      </c>
+      <c r="H327" s="55" t="inlineStr">
+        <is>
+          <t>天元台ロープウェイ湯元駅。新宿は大宮乗換（32分＋つばさ99分）、バス50分。11,510／11,180／12,270円</t>
+        </is>
+      </c>
+      <c r="I327" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（2026-10-17）、Googleマップ経路（山交バス50分・970円）</t>
+        </is>
+      </c>
+      <c r="J327" s="55" t="inlineStr">
+        <is>
+          <t>JR＋バス970円で検算</t>
+        </is>
+      </c>
+      <c r="K327" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="53" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C328" s="53" t="inlineStr">
+        <is>
+          <t>zaosan・nakawarayama・kazahariyama</t>
+        </is>
+      </c>
+      <c r="D328" s="54" t="inlineStr">
+        <is>
+          <t>蔵王山・和名倉山・御座山</t>
+        </is>
+      </c>
+      <c r="E328" s="54" t="inlineStr">
+        <is>
+          <t>電車の行き先の明示</t>
+        </is>
+      </c>
+      <c r="F328" s="54" t="inlineStr">
+        <is>
+          <t>電車アクセス</t>
+        </is>
+      </c>
+      <c r="G328" s="55" t="inlineStr">
+        <is>
+          <t>電車の行き先が登山口欄と別ルートなのに説明なし。御座山の住所が北相木村</t>
+        </is>
+      </c>
+      <c r="H328" s="55" t="inlineStr">
+        <is>
+          <t>「行き先：○○」を表示し、各ルートに登山口名を付けた。御座山の住所を南相木村に訂正</t>
+        </is>
+      </c>
+      <c r="I328" s="56" t="inlineStr">
+        <is>
+          <t>長野県の案内（栗生は南相木村）</t>
+        </is>
+      </c>
+      <c r="J328" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K328" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="53" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C329" s="53" t="inlineStr">
+        <is>
+          <t>minamikomagatake</t>
+        </is>
+      </c>
+      <c r="D329" s="54" t="inlineStr">
+        <is>
+          <t>南駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E329" s="54" t="inlineStr">
+        <is>
+          <t>登山口・経路の誤り</t>
+        </is>
+      </c>
+      <c r="F329" s="54" t="inlineStr">
+        <is>
+          <t>全出発地・車</t>
+        </is>
+      </c>
+      <c r="G329" s="55" t="inlineStr">
+        <is>
+          <t>ルートは木曽側（越百山）なのに登山口・電車が伊那側の菅の台バスセンター。5,780／6,310／6,400円</t>
+        </is>
+      </c>
+      <c r="H329" s="55" t="inlineStr">
+        <is>
+          <t>伊奈川ダム上登山口。須原駅からタクシー約15分。7,830／7,830／7,190円。車の所要時間も引き直し（新宿235分ほか）</t>
+        </is>
+      </c>
+      <c r="I329" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（2026-10-17）、Googleマップ経路</t>
+        </is>
+      </c>
+      <c r="J329" s="55" t="inlineStr">
+        <is>
+          <t>運賃5,280＋特急2,550（横浜は4,950＋2,240）</t>
+        </is>
+      </c>
+      <c r="K329" s="57" t="inlineStr">
+        <is>
+          <t>高（タクシー会社は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="53" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C330" s="53" t="inlineStr">
+        <is>
+          <t>hijiridade</t>
+        </is>
+      </c>
+      <c r="D330" s="54" t="inlineStr">
+        <is>
+          <t>聖岳</t>
+        </is>
+      </c>
+      <c r="E330" s="54" t="inlineStr">
+        <is>
+          <t>登山口・住所の誤り</t>
+        </is>
+      </c>
+      <c r="F330" s="54" t="inlineStr">
+        <is>
+          <t>登山口・駐車場・注意表示</t>
+        </is>
+      </c>
+      <c r="G330" s="55" t="inlineStr">
+        <is>
+          <t>住所が静岡県浜松市。便ヶ島駐車場（約30台）と案内</t>
+        </is>
+      </c>
+      <c r="H330" s="55" t="inlineStr">
+        <is>
+          <t>長野県飯田市南信濃木沢。車は芝沢ゲートまで。電車は静岡側の聖沢登山口行きと明示</t>
+        </is>
+      </c>
+      <c r="I330" s="56" t="inlineStr">
+        <is>
+          <t>環境省 南アルプス国立公園アクセス情報</t>
+        </is>
+      </c>
+      <c r="J330" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K330" s="57" t="inlineStr">
+        <is>
+          <t>中（2026年の通行状況は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="53" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C331" s="53" t="inlineStr">
+        <is>
+          <t>terkari</t>
+        </is>
+      </c>
+      <c r="D331" s="54" t="inlineStr">
+        <is>
+          <t>光岳</t>
+        </is>
+      </c>
+      <c r="E331" s="54" t="inlineStr">
+        <is>
+          <t>終点・所要時間</t>
+        </is>
+      </c>
+      <c r="F331" s="54" t="inlineStr">
+        <is>
+          <t>タクシー区間</t>
+        </is>
+      </c>
+      <c r="G331" s="55" t="inlineStr">
+        <is>
+          <t>道の駅遠山郷→タクシー75分→易老渡</t>
+        </is>
+      </c>
+      <c r="H331" s="55" t="inlineStr">
+        <is>
+          <t>タクシー45分→芝沢ゲート→徒歩約5km→易老渡（所要時間−30分）</t>
+        </is>
+      </c>
+      <c r="I331" s="56" t="inlineStr">
+        <is>
+          <t>環境省アクセス情報、Googleマップ経路（45分・27km）</t>
+        </is>
+      </c>
+      <c r="J331" s="55" t="inlineStr">
+        <is>
+          <t>legs合計と一致</t>
+        </is>
+      </c>
+      <c r="K331" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="53" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C332" s="53" t="inlineStr">
+        <is>
+          <t>noutori</t>
+        </is>
+      </c>
+      <c r="D332" s="54" t="inlineStr">
+        <is>
+          <t>農鳥岳</t>
+        </is>
+      </c>
+      <c r="E332" s="54" t="inlineStr">
+        <is>
+          <t>ルートと電車の不一致</t>
+        </is>
+      </c>
+      <c r="F332" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G332" s="55" t="inlineStr">
+        <is>
+          <t>ルートは広河原発なのに電車が奈良田（下山口）行き。6,770／6,210／6,770円</t>
+        </is>
+      </c>
+      <c r="H332" s="55" t="inlineStr">
+        <is>
+          <t>北岳と同じ広河原行きに変更。6,290／7,060／7,060円。奈良田からの帰りは注記に</t>
+        </is>
+      </c>
+      <c r="I332" s="56" t="inlineStr">
+        <is>
+          <t>北岳の検証済みデータ</t>
+        </is>
+      </c>
+      <c r="J332" s="55" t="inlineStr">
+        <is>
+          <t>北岳と同値</t>
+        </is>
+      </c>
+      <c r="K332" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="53" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C333" s="53" t="inlineStr">
+        <is>
+          <t>hinata</t>
+        </is>
+      </c>
+      <c r="D333" s="54" t="inlineStr">
+        <is>
+          <t>日向山</t>
+        </is>
+      </c>
+      <c r="E333" s="54" t="inlineStr">
+        <is>
+          <t>終点・駐車場・通行禁止</t>
+        </is>
+      </c>
+      <c r="F333" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G333" s="55" t="inlineStr">
+        <is>
+          <t>タクシーで尾白川渓谷駐車場まで（そこから先の記載なし）。矢立石駐車場 約30台</t>
+        </is>
+      </c>
+      <c r="H333" s="55" t="inlineStr">
+        <is>
+          <t>尾白川渓谷駐車場から徒歩約50分を追加（所要時間＋50分）。矢立石は約10台。錦滝方面は通行禁止と表示</t>
+        </is>
+      </c>
+      <c r="I333" s="56" t="inlineStr">
+        <is>
+          <t>やまなし観光推進機構、Googleマップ経路（18分）</t>
+        </is>
+      </c>
+      <c r="J333" s="55" t="inlineStr">
+        <is>
+          <t>legs合計と一致</t>
+        </is>
+      </c>
+      <c r="K333" s="57" t="inlineStr">
+        <is>
+          <t>高（運賃はタクシー込みの旧値のまま）</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="53" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C334" s="53" t="inlineStr">
+        <is>
+          <t>kurohimesan</t>
+        </is>
+      </c>
+      <c r="D334" s="54" t="inlineStr">
+        <is>
+          <t>黒姫山</t>
+        </is>
+      </c>
+      <c r="E334" s="54" t="inlineStr">
+        <is>
+          <t>実在が確認できない経路</t>
+        </is>
+      </c>
+      <c r="F334" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G334" s="55" t="inlineStr">
+        <is>
+          <t>黒姫駅→黒姫高原シャトルバス20分→古池登山口（季節）。9,000／8,472／8,972円</t>
+        </is>
+      </c>
+      <c r="H334" s="55" t="inlineStr">
+        <is>
+          <t>黒姫駅→タクシー約18分→大橋登山口。7,999／7,339／9,539円（黒姫駅まで）</t>
+        </is>
+      </c>
+      <c r="I334" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（2026-10-17）、Googleマップ経路（18分・11.6km）</t>
+        </is>
+      </c>
+      <c r="J334" s="55" t="inlineStr">
+        <is>
+          <t>運賃4,829＋特急3,170ほか</t>
+        </is>
+      </c>
+      <c r="K334" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="53" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C335" s="53" t="inlineStr">
+        <is>
+          <t>kintoki</t>
+        </is>
+      </c>
+      <c r="D335" s="54" t="inlineStr">
+        <is>
+          <t>金時山</t>
+        </is>
+      </c>
+      <c r="E335" s="54" t="inlineStr">
+        <is>
+          <t>住所・登山口・駐車場</t>
+        </is>
+      </c>
+      <c r="F335" s="54" t="inlineStr">
+        <is>
+          <t>登山口</t>
+        </is>
+      </c>
+      <c r="G335" s="55" t="inlineStr">
+        <is>
+          <t>住所が静岡県小山町、駐車場が乙女峠駐車場</t>
+        </is>
+      </c>
+      <c r="H335" s="55" t="inlineStr">
+        <is>
+          <t>箱根町仙石原の金時神社入口・乙女口。公時神社ルート（2時間30分・4.6km）を追加</t>
+        </is>
+      </c>
+      <c r="I335" s="56" t="inlineStr">
+        <is>
+          <t>環境省 富士箱根伊豆国立公園 コース06</t>
+        </is>
+      </c>
+      <c r="J335" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K335" s="57" t="inlineStr">
+        <is>
+          <t>中（駐車場の台数は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="53" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C336" s="53" t="inlineStr">
+        <is>
+          <t>nokogiriyama</t>
+        </is>
+      </c>
+      <c r="D336" s="54" t="inlineStr">
+        <is>
+          <t>鋸岳</t>
+        </is>
+      </c>
+      <c r="E336" s="54" t="inlineStr">
+        <is>
+          <t>登山口・駐車場</t>
+        </is>
+      </c>
+      <c r="F336" s="54" t="inlineStr">
+        <is>
+          <t>登山口</t>
+        </is>
+      </c>
+      <c r="G336" s="55" t="inlineStr">
+        <is>
+          <t>戸台口（仙流荘）・仙流荘前駐車場（無料）</t>
+        </is>
+      </c>
+      <c r="H336" s="55" t="inlineStr">
+        <is>
+          <t>戸台パーク。戸台河原駐車場は利用不可との注意を表示</t>
+        </is>
+      </c>
+      <c r="I336" s="56" t="inlineStr">
+        <is>
+          <t>長野県の山岳情報（検索結果の記載）、環境省アクセス情報</t>
+        </is>
+      </c>
+      <c r="J336" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K336" s="57" t="inlineStr">
+        <is>
+          <t>中（駐車料金・通行止めの現況は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="53" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C337" s="53" t="inlineStr">
+        <is>
+          <t>65山</t>
+        </is>
+      </c>
+      <c r="D337" s="54" t="inlineStr">
+        <is>
+          <t>複数ルートの山</t>
+        </is>
+      </c>
+      <c r="E337" s="54" t="inlineStr">
+        <is>
+          <t>ルートと登山口の対応</t>
+        </is>
+      </c>
+      <c r="F337" s="54" t="inlineStr">
+        <is>
+          <t>routes[].trailheadName</t>
+        </is>
+      </c>
+      <c r="G337" s="55" t="inlineStr">
+        <is>
+          <t>2本目以降のルートがどの登山口から歩くのか表示がなかった</t>
+        </is>
+      </c>
+      <c r="H337" s="55" t="inlineStr">
+        <is>
+          <t>ルート名から起点が読み取れるものに登山口名を付けた（読み取れない7ルートは空欄のまま）</t>
+        </is>
+      </c>
+      <c r="I337" s="56" t="inlineStr">
+        <is>
+          <t>既存のルート名</t>
+        </is>
+      </c>
+      <c r="J337" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K337" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="53" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C338" s="53" t="inlineStr">
+        <is>
+          <t>myojingatake</t>
+        </is>
+      </c>
+      <c r="D338" s="54" t="inlineStr">
+        <is>
+          <t>明神ヶ岳</t>
+        </is>
+      </c>
+      <c r="E338" s="54" t="inlineStr">
+        <is>
+          <t>登山口の誤り（他山の内容）</t>
+        </is>
+      </c>
+      <c r="F338" s="54" t="inlineStr">
+        <is>
+          <t>登山口・住所・駐車場・地図</t>
+        </is>
+      </c>
+      <c r="G338" s="55" t="inlineStr">
+        <is>
+          <t>南足柄市矢倉沢（矢倉岳と同じ内容）。電車は宮城野行き</t>
+        </is>
+      </c>
+      <c r="H338" s="55" t="inlineStr">
+        <is>
+          <t>箱根町宮城野に統一。ルート「矢倉沢登山口 往復」は要確認として残した</t>
+        </is>
+      </c>
+      <c r="I338" s="56" t="inlineStr">
+        <is>
+          <t>既存の経路データ（宮城野支所前）</t>
+        </is>
+      </c>
+      <c r="J338" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K338" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="53" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C339" s="53" t="inlineStr">
+        <is>
+          <t>koganzan・naeba・koubousan・kusatoriyama</t>
+        </is>
+      </c>
+      <c r="D339" s="54" t="inlineStr">
+        <is>
+          <t>小金沢山・苗場山・弘法山・草戸山</t>
+        </is>
+      </c>
+      <c r="E339" s="54" t="inlineStr">
+        <is>
+          <t>登山口の表記・徒歩時間</t>
+        </is>
+      </c>
+      <c r="F339" s="54" t="inlineStr">
+        <is>
+          <t>登山口</t>
+        </is>
+      </c>
+      <c r="G339" s="55" t="inlineStr">
+        <is>
+          <t>小金沢山「大菩薩峠〜牛奥ノ雁ヶ腹摺山」／苗場山「和田小屋」と終点「祓川登山口」／弘法山「秦野駅または鶴巻温泉駅」／草戸山FAQ「徒歩約15分」</t>
+        </is>
+      </c>
+      <c r="H339" s="55" t="inlineStr">
+        <is>
+          <t>上日川峠／祓川登山口（和田小屋）／秦野駅（横浜発のみ鶴巻温泉のまま・要確認）／徒歩約5分</t>
+        </is>
+      </c>
+      <c r="I339" s="56" t="inlineStr">
+        <is>
+          <t>Googleマップ徒歩経路（高尾山口駅→草戸山登山口 4分・240m）</t>
+        </is>
+      </c>
+      <c r="J339" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K339" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="53" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C340" s="53" t="inlineStr">
+        <is>
+          <t>23山</t>
+        </is>
+      </c>
+      <c r="D340" s="54" t="inlineStr">
+        <is>
+          <t>2本目ルートの登山口</t>
+        </is>
+      </c>
+      <c r="E340" s="54" t="inlineStr">
+        <is>
+          <t>ルート別のアクセス</t>
+        </is>
+      </c>
+      <c r="F340" s="54" t="inlineStr">
+        <is>
+          <t>routes[].accessNote</t>
+        </is>
+      </c>
+      <c r="G340" s="55" t="inlineStr">
+        <is>
+          <t>別の登山口から出るルートに、そこへの行き方の記載がなかった</t>
+        </is>
+      </c>
+      <c r="H340" s="55" t="inlineStr">
+        <is>
+          <t>24ルートに行き方を追記。サイト内の検証済みデータ・駅起点の10件は確定、観光サイトや登山記録が出典の14件は「未確認の情報を含みます」と表示</t>
+        </is>
+      </c>
+      <c r="I340" s="56" t="inlineStr">
+        <is>
+          <t>サイト内の他山データ／観光情報サイト／登山記録</t>
+        </is>
+      </c>
+      <c r="J340" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K340" s="57" t="inlineStr">
+        <is>
+          <t>確定10件：高／残り14件：低</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="53" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C341" s="53" t="inlineStr">
+        <is>
+          <t>chogatake・kumotori・houou</t>
+        </is>
+      </c>
+      <c r="D341" s="54" t="inlineStr">
+        <is>
+          <t>蝶ヶ岳・雲取山・鳳凰山</t>
+        </is>
+      </c>
+      <c r="E341" s="54" t="inlineStr">
+        <is>
+          <t>ルート別のアクセス（裏取り）</t>
+        </is>
+      </c>
+      <c r="F341" s="54" t="inlineStr">
+        <is>
+          <t>三股／三峯神社／青木鉱泉</t>
+        </is>
+      </c>
+      <c r="G341" s="55" t="inlineStr">
+        <is>
+          <t>観光サイト・登山記録が出典の未確認情報</t>
+        </is>
+      </c>
+      <c r="H341" s="55" t="inlineStr">
+        <is>
+          <t>三股線：2026年7/17〜10/13のうち63日・2,000円・WEB予約必須／三峯神社線：約1時間20分・1,100円・平日6便 土日祝9便／鳳凰三山登山バス：6/20〜10/12の土日と三連休・2往復・完全予約制</t>
+        </is>
+      </c>
+      <c r="I341" s="56" t="inlineStr">
+        <is>
+          <t>安曇野市公式（2026-08-14更新）、西武バス三峯神社線、鳳凰小屋アクセス案内</t>
+        </is>
+      </c>
+      <c r="J341" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K341" s="57" t="inlineStr">
+        <is>
+          <t>高（鳳凰山の運賃のみ未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="53" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C342" s="53" t="inlineStr">
+        <is>
+          <t>naeba・keirisan・utsukushigahara・bandai</t>
+        </is>
+      </c>
+      <c r="D342" s="54" t="inlineStr">
+        <is>
+          <t>苗場山・蓼科山・美ヶ原・磐梯山</t>
+        </is>
+      </c>
+      <c r="E342" s="54" t="inlineStr">
+        <is>
+          <t>ルート別のアクセス（一部裏取り）</t>
+        </is>
+      </c>
+      <c r="F342" s="54" t="inlineStr">
+        <is>
+          <t>小赤沢／七合目／三城／猪苗代スキー場</t>
+        </is>
+      </c>
+      <c r="G342" s="55" t="inlineStr">
+        <is>
+          <t>観光サイト・登山記録が出典の記載</t>
+        </is>
+      </c>
+      <c r="H342" s="55" t="inlineStr">
+        <is>
+          <t>苗場山：駐車場約100台、バス停から徒歩約90分／蓼科山：バスの乗り継ぎ経路、ゴンドラに休業期間／美ヶ原：直行バスの2026年運行日（三城停車は未確認）／磐梯山：夏の路線バスは確認できず、タクシーに訂正</t>
+        </is>
+      </c>
+      <c r="I342" s="56" t="inlineStr">
+        <is>
+          <t>雪国観光圏、信州たてしな観光協会、松本市公式観光サイト</t>
+        </is>
+      </c>
+      <c r="J342" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K342" s="57" t="inlineStr">
+        <is>
+          <t>中（4本とも未確認表示のまま）</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="53" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C343" s="53" t="inlineStr">
+        <is>
+          <t>hinata</t>
+        </is>
+      </c>
+      <c r="D343" s="54" t="inlineStr">
+        <is>
+          <t>日向山</t>
+        </is>
+      </c>
+      <c r="E343" s="54" t="inlineStr">
+        <is>
+          <t>運賃（概算の除去）</t>
+        </is>
+      </c>
+      <c r="F343" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G343" s="55" t="inlineStr">
+        <is>
+          <t>7,930／7,930／7,270円（タクシー代の概算込み）</t>
+        </is>
+      </c>
+      <c r="H343" s="55" t="inlineStr">
+        <is>
+          <t>5,430／5,430／4,770円（小淵沢駅まで。タクシー代は別）</t>
+        </is>
+      </c>
+      <c r="I343" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（2026-10-17）</t>
+        </is>
+      </c>
+      <c r="J343" s="55" t="inlineStr">
+        <is>
+          <t>運賃3,190＋特急2,240（横浜は八王子から1,580）</t>
+        </is>
+      </c>
+      <c r="K343" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="53" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C344" s="53" t="inlineStr">
+        <is>
+          <t>terkari</t>
+        </is>
+      </c>
+      <c r="D344" s="54" t="inlineStr">
+        <is>
+          <t>光岳</t>
+        </is>
+      </c>
+      <c r="E344" s="54" t="inlineStr">
+        <is>
+          <t>バス事業者名・所要時間</t>
+        </is>
+      </c>
+      <c r="F344" s="54" t="inlineStr">
+        <is>
+          <t>飯田駅〜遠山郷</t>
+        </is>
+      </c>
+      <c r="G344" s="55" t="inlineStr">
+        <is>
+          <t>南信州バス 70分→道の駅遠山郷</t>
+        </is>
+      </c>
+      <c r="H344" s="55" t="inlineStr">
+        <is>
+          <t>信南交通「遠山郷線」83分→かぐらの湯（道の駅遠山郷）。所要時間＋13分。運賃24,800円ほかは概算のまま（要確認）</t>
+        </is>
+      </c>
+      <c r="I344" s="56" t="inlineStr">
+        <is>
+          <t>NAVITIME 遠山郷線[信南交通]（飯田駅前09:30→かぐらの湯10:53）</t>
+        </is>
+      </c>
+      <c r="J344" s="55" t="inlineStr">
+        <is>
+          <t>legs合計と一致</t>
+        </is>
+      </c>
+      <c r="K344" s="57" t="inlineStr">
+        <is>
+          <t>中（運賃は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="53" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C345" s="53" t="inlineStr">
+        <is>
+          <t>tsurugi・iide・arafune ほか4山</t>
+        </is>
+      </c>
+      <c r="D345" s="54" t="inlineStr">
+        <is>
+          <t>剱岳・飯豊山・荒船山・男体山・武尊山・平ヶ岳・恵那山</t>
+        </is>
+      </c>
+      <c r="E345" s="54" t="inlineStr">
+        <is>
+          <t>ルート別のアクセス（裏取り）</t>
+        </is>
+      </c>
+      <c r="F345" s="54" t="inlineStr">
+        <is>
+          <t>馬場島／弥平四郎／相沢／志津乗越／オグナほたか／中ノ岐／広河原</t>
+        </is>
+      </c>
+      <c r="G345" s="55" t="inlineStr">
+        <is>
+          <t>未確認の記載。荒船山は「南牧村方面のバス＋徒歩約90分・駐車2台」と誤り</t>
+        </is>
+      </c>
+      <c r="H345" s="55" t="inlineStr">
+        <is>
+          <t>剱岳：上市駅からタクシー約37分・駐車約150台／飯豊山：祓川駐車場約30台、デマンドバスは集落まで、新長坂ルート通行止め／荒船山：下仁田町営バス三ツ瀬・駐車4台ほどに訂正／ほか4山は登山情報サイトの内容に更新（未確認表示のまま）</t>
+        </is>
+      </c>
+      <c r="I345" s="56" t="inlineStr">
+        <is>
+          <t>上市町公式、西会津町公式、下仁田町公式、山と溪谷オンライン</t>
+        </is>
+      </c>
+      <c r="J345" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K345" s="57" t="inlineStr">
+        <is>
+          <t>公式3件：高／4件：中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K318"/>
+  <autoFilter ref="A1:K322"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -11434,33 +11434,33 @@
       </c>
       <c r="F91" s="44" t="inlineStr">
         <is>
-          <t>バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー(天竜観光タクシー等・要事前電話予約)]--&gt; 芝沢ゲート --[徒歩（林道 約5km）]--&gt; 易老渡</t>
+          <t>バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー（易老渡まで入れる特定車両）]--&gt; 易老渡</t>
         </is>
       </c>
       <c r="G91" s="41" t="n">
-        <v>378</v>
+        <v>413</v>
       </c>
       <c r="H91" s="41" t="n">
         <v>24800</v>
       </c>
       <c r="I91" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー(天竜観光タクシー等・要事前電話予約)]--&gt; 芝沢ゲート --[徒歩（林道 約5km）]--&gt; 易老渡</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー（易老渡まで入れる特定車両）]--&gt; 易老渡</t>
         </is>
       </c>
       <c r="J91" s="41" t="n">
-        <v>408</v>
+        <v>443</v>
       </c>
       <c r="K91" s="41" t="n">
         <v>25380</v>
       </c>
       <c r="L91" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー(天竜観光タクシー等・要事前電話予約)]--&gt; 芝沢ゲート --[徒歩（林道 約5km）]--&gt; 易老渡</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー（易老渡まで入れる特定車両）]--&gt; 易老渡</t>
         </is>
       </c>
       <c r="M91" s="41" t="n">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="N91" s="41" t="n">
         <v>25380</v>
@@ -24235,7 +24235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K345"/>
+  <dimension ref="A1:K352"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -43223,6 +43223,391 @@
       <c r="K345" s="57" t="inlineStr">
         <is>
           <t>公式3件：高／4件：中</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="53" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C346" s="53" t="inlineStr">
+        <is>
+          <t>terkari</t>
+        </is>
+      </c>
+      <c r="D346" s="54" t="inlineStr">
+        <is>
+          <t>光岳</t>
+        </is>
+      </c>
+      <c r="E346" s="54" t="inlineStr">
+        <is>
+          <t>前回修正の誤りを訂正</t>
+        </is>
+      </c>
+      <c r="F346" s="54" t="inlineStr">
+        <is>
+          <t>タクシー区間</t>
+        </is>
+      </c>
+      <c r="G346" s="55" t="inlineStr">
+        <is>
+          <t>No.330で「タクシーは芝沢ゲートまで45分、その先は徒歩約5km」に変更</t>
+        </is>
+      </c>
+      <c r="H346" s="55" t="inlineStr">
+        <is>
+          <t>予約制タクシーは易老渡駐車場まで入れる（約1時間20分・1台15,000〜20,000円・2026年7/1〜11/8・4:30発）。一般車だけが芝沢ゲートまで（駐車約50台・協力金約1,000円、易老渡へ徒歩約1時間30分）</t>
+        </is>
+      </c>
+      <c r="I346" s="56" t="inlineStr">
+        <is>
+          <t>遠山郷観光協会（2026-07-09更新）</t>
+        </is>
+      </c>
+      <c r="J346" s="55" t="inlineStr">
+        <is>
+          <t>legs合計と一致</t>
+        </is>
+      </c>
+      <c r="K346" s="57" t="inlineStr">
+        <is>
+          <t>高（運賃は概算のまま）</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="53" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C347" s="53" t="inlineStr">
+        <is>
+          <t>hijiridade</t>
+        </is>
+      </c>
+      <c r="D347" s="54" t="inlineStr">
+        <is>
+          <t>聖岳</t>
+        </is>
+      </c>
+      <c r="E347" s="54" t="inlineStr">
+        <is>
+          <t>通行止めの確認</t>
+        </is>
+      </c>
+      <c r="F347" s="54" t="inlineStr">
+        <is>
+          <t>便ヶ島ルート</t>
+        </is>
+      </c>
+      <c r="G347" s="55" t="inlineStr">
+        <is>
+          <t>「通行止めとの情報あり・2026年は未確認」</t>
+        </is>
+      </c>
+      <c r="H347" s="55" t="inlineStr">
+        <is>
+          <t>便ヶ島〜西沢渡は災害復旧工事で当分の間通行不可と確認。ルートに通行止め表示、注意バナーを書き換え。駐車場は約50台・協力金約1,000円</t>
+        </is>
+      </c>
+      <c r="I347" s="56" t="inlineStr">
+        <is>
+          <t>遠山郷観光協会（2026-07-09更新）</t>
+        </is>
+      </c>
+      <c r="J347" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K347" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="53" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C348" s="53" t="inlineStr">
+        <is>
+          <t>nokogiriyama</t>
+        </is>
+      </c>
+      <c r="D348" s="54" t="inlineStr">
+        <is>
+          <t>鋸岳</t>
+        </is>
+      </c>
+      <c r="E348" s="54" t="inlineStr">
+        <is>
+          <t>駐車場の確認</t>
+        </is>
+      </c>
+      <c r="F348" s="54" t="inlineStr">
+        <is>
+          <t>戸台河原</t>
+        </is>
+      </c>
+      <c r="G348" s="55" t="inlineStr">
+        <is>
+          <t>「利用不可との情報」</t>
+        </is>
+      </c>
+      <c r="H348" s="55" t="inlineStr">
+        <is>
+          <t>戸台河原駐車場は大雨で流出し利用不可（復旧未定）、代替は南アルプス林道バス駐車場と確認</t>
+        </is>
+      </c>
+      <c r="I348" s="56" t="inlineStr">
+        <is>
+          <t>伊那市公式（2025-04-21更新）</t>
+        </is>
+      </c>
+      <c r="J348" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K348" s="57" t="inlineStr">
+        <is>
+          <t>高（戸台パークの料金は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="53" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C349" s="53" t="inlineStr">
+        <is>
+          <t>myojingatake</t>
+        </is>
+      </c>
+      <c r="D349" s="54" t="inlineStr">
+        <is>
+          <t>明神ヶ岳</t>
+        </is>
+      </c>
+      <c r="E349" s="54" t="inlineStr">
+        <is>
+          <t>ルートの作り直し</t>
+        </is>
+      </c>
+      <c r="F349" s="54" t="inlineStr">
+        <is>
+          <t>代表ルート</t>
+        </is>
+      </c>
+      <c r="G349" s="55" t="inlineStr">
+        <is>
+          <t>矢倉沢登山口 往復 4時間30分・9.0km・+850m（出典不明）</t>
+        </is>
+      </c>
+      <c r="H349" s="55" t="inlineStr">
+        <is>
+          <t>宮城野〜明神ヶ岳（往復）4時間・7.2km・+724m・定数17。旧ルートは removedRoutes に退避</t>
+        </is>
+      </c>
+      <c r="I349" s="56" t="inlineStr">
+        <is>
+          <t>YAMAPモデルコース15215</t>
+        </is>
+      </c>
+      <c r="J349" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K349" s="57" t="inlineStr">
+        <is>
+          <t>中（上部のコース定数表示は保留）</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="53" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C350" s="53" t="inlineStr">
+        <is>
+          <t>29山</t>
+        </is>
+      </c>
+      <c r="D350" s="54" t="inlineStr">
+        <is>
+          <t>駐車場が空欄の山</t>
+        </is>
+      </c>
+      <c r="E350" s="54" t="inlineStr">
+        <is>
+          <t>駐車場</t>
+        </is>
+      </c>
+      <c r="F350" s="54" t="inlineStr">
+        <is>
+          <t>parking</t>
+        </is>
+      </c>
+      <c r="G350" s="55" t="inlineStr">
+        <is>
+          <t>空欄</t>
+        </is>
+      </c>
+      <c r="H350" s="55" t="inlineStr">
+        <is>
+          <t>3山を記入（太平山 26台・無料／三頭山 都民の森100台・無料／三ツ峠山 約10台）。駅・バス停から歩く19山は「登山者用の駐車場は確認できていません」と表示。7山は空欄のまま要確認に記録</t>
+        </is>
+      </c>
+      <c r="I350" s="56" t="inlineStr">
+        <is>
+          <t>栃木市資料、東京都観光公式サイト、富士河口湖町観光課の掲載情報</t>
+        </is>
+      </c>
+      <c r="J350" s="55" t="inlineStr">
+        <is>
+          <t>check_pages.py 0件</t>
+        </is>
+      </c>
+      <c r="K350" s="57" t="inlineStr">
+        <is>
+          <t>3山：中／他：未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="53" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C351" s="53" t="inlineStr">
+        <is>
+          <t>hijiridade</t>
+        </is>
+      </c>
+      <c r="D351" s="54" t="inlineStr">
+        <is>
+          <t>聖岳</t>
+        </is>
+      </c>
+      <c r="E351" s="54" t="inlineStr">
+        <is>
+          <t>ルートの追加（枠のみ）</t>
+        </is>
+      </c>
+      <c r="F351" s="54" t="inlineStr">
+        <is>
+          <t>聖沢登山口ルート</t>
+        </is>
+      </c>
+      <c r="G351" s="55" t="inlineStr">
+        <is>
+          <t>代表ルート（便ヶ島）が通行止めで、歩けるルートの記載なし</t>
+        </is>
+      </c>
+      <c r="H351" s="55" t="inlineStr">
+        <is>
+          <t>聖沢登山口〜聖平小屋〜聖岳を追加（時間・距離は資料により幅があり未登録）</t>
+        </is>
+      </c>
+      <c r="I351" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J351" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K351" s="57" t="inlineStr">
+        <is>
+          <t>低（数値なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="53" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C352" s="53" t="inlineStr">
+        <is>
+          <t>全山</t>
+        </is>
+      </c>
+      <c r="D352" s="54" t="inlineStr">
+        <is>
+          <t>年次データの見張り</t>
+        </is>
+      </c>
+      <c r="E352" s="54" t="inlineStr">
+        <is>
+          <t>仕組みの追加</t>
+        </is>
+      </c>
+      <c r="F352" s="54" t="inlineStr">
+        <is>
+          <t>季節運行・規制・閉鎖期間</t>
+        </is>
+      </c>
+      <c r="G352" s="55" t="inlineStr">
+        <is>
+          <t>期限切れの情報がそのまま表示され続ける。来季の発表に気づく手段がない</t>
+        </is>
+      </c>
+      <c r="H352" s="55" t="inlineStr">
+        <is>
+          <t>期限を過ぎると山ページが自動で「終了」と注記／check_annual_updates.py と月1回のGitHub Actionsで期限切れ・出典の変更を一覧化（データは自動で書き換えない）／旧構造11山に annualItems を登録</t>
+        </is>
+      </c>
+      <c r="I352" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J352" s="55" t="inlineStr">
+        <is>
+          <t>ローカルで実行：44項目、期限切れ5、30日以内13、未登録47山</t>
+        </is>
+      </c>
+      <c r="K352" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -6911,7 +6911,7 @@
         <v>176</v>
       </c>
       <c r="H10" s="41" t="n">
-        <v>6100</v>
+        <v>6430</v>
       </c>
       <c r="I10" s="44" t="inlineStr">
         <is>
@@ -6922,18 +6922,18 @@
         <v>206</v>
       </c>
       <c r="K10" s="41" t="n">
-        <v>6870</v>
+        <v>6430</v>
       </c>
       <c r="L10" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 韮崎駅 --[山梨峡北交通「韮崎瑞牆線」]--&gt; みずがき山荘（4〜11月季節運行）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 甲府駅 --[JR中央本線（普通）]--&gt; 韮崎駅 --[山梨峡北交通「韮崎瑞牆線」]--&gt; みずがき山荘（4〜11月季節運行）</t>
         </is>
       </c>
       <c r="M10" s="41" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N10" s="41" t="n">
-        <v>6870</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="11" ht="51.75" customHeight="1" s="30">
@@ -7198,7 +7198,7 @@
         </is>
       </c>
       <c r="G15" s="41" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="H15" s="41" t="n">
         <v>6290</v>
@@ -7209,21 +7209,21 @@
         </is>
       </c>
       <c r="J15" s="41" t="n">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="K15" s="41" t="n">
-        <v>7060</v>
+        <v>6290</v>
       </c>
       <c r="L15" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「南アルプス登山バス」]--&gt; 広河原（マイカー規制）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 甲府駅 --[山梨交通「南アルプス登山バス」]--&gt; 広河原（マイカー規制）</t>
         </is>
       </c>
       <c r="M15" s="41" t="n">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="N15" s="41" t="n">
-        <v>7060</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="16" ht="26.25" customHeight="1" s="30">
@@ -8272,36 +8272,36 @@
       </c>
       <c r="F34" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[東北新幹線（東京駅乗換）]--&gt; 郡山駅 --[JR磐越西線]--&gt; 山都駅 --[会津バス「飯豊登山アクセスバス」（夏季限定・7月上旬〜8月下旬・1日2便のみ）]--&gt; 川入バス停 --[徒歩]--&gt; 御沢野営場（登山口）</t>
+          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[東北新幹線やまびこ]--&gt; 郡山駅 --[JR磐越西線快速]--&gt; 会津若松駅 --[JR磐越西線]--&gt; 山都駅 --[飯豊山登山アクセスバス（喜多方市・夏の金〜月曜のみ）]--&gt; 川入バス停 --[徒歩]--&gt; 御沢野営場（登山口）</t>
         </is>
       </c>
       <c r="G34" s="41" t="n">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="H34" s="41" t="n">
-        <v>9430</v>
+        <v>9460</v>
       </c>
       <c r="I34" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[東北新幹線やまびこ]--&gt; 郡山駅 --[JR磐越西線快速]--&gt; 会津若松駅 --[JR磐越西線]--&gt; 山都駅 --[会津バス「飯豊登山アクセスバス」]--&gt; 川入バス停 --[徒歩]--&gt; 御沢野営場（登山口）</t>
+          <t>大宮駅 --[東北新幹線やまびこ]--&gt; 郡山駅 --[JR磐越西線快速]--&gt; 会津若松駅 --[JR磐越西線]--&gt; 山都駅 --[飯豊山登山アクセスバス（喜多方市・夏の金〜月曜のみ）]--&gt; 川入バス停 --[徒歩]--&gt; 御沢野営場（登山口）</t>
         </is>
       </c>
       <c r="J34" s="41" t="n">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="K34" s="41" t="n">
-        <v>8560</v>
+        <v>8030</v>
       </c>
       <c r="L34" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[東北新幹線やまびこ]--&gt; 郡山駅 --[JR磐越西線]--&gt; 山都駅 --[会津バス「飯豊登山アクセスバス」（夏季限定・1日2便のみ）]--&gt; 川入バス停 --[徒歩]--&gt; 御沢野営場（登山口）</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[東北新幹線やまびこ]--&gt; 郡山駅 --[JR磐越西線快速]--&gt; 会津若松駅 --[JR磐越西線]--&gt; 山都駅 --[飯豊山登山アクセスバス（喜多方市・夏の金〜月曜のみ）]--&gt; 川入バス停 --[徒歩]--&gt; 御沢野営場（登山口）</t>
         </is>
       </c>
       <c r="M34" s="41" t="n">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="N34" s="41" t="n">
-        <v>10710</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="35" ht="39" customHeight="1" s="30">
@@ -8446,36 +8446,36 @@
       </c>
       <c r="F37" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[上越・北陸新幹線]--&gt; 高崎駅 --[JR吾妻線]--&gt; 長野原草津口駅 --[JRバス関東]--&gt; 草津温泉（噴火警戒レベル1）</t>
+          <t>新宿駅 --[JR埼京線・湘南新宿ライン]--&gt; 大宮駅 --[上越・北陸新幹線]--&gt; 高崎駅 --[JR吾妻線]--&gt; 長野原草津口駅 --[JRバス関東]--&gt; 草津温泉バスターミナル</t>
         </is>
       </c>
       <c r="G37" s="41" t="n">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="H37" s="41" t="n">
-        <v>6410</v>
+        <v>5840</v>
       </c>
       <c r="I37" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR特急「草津・四万」]--&gt; 長野原草津口駅 --[JRバス関東]--&gt; 草津温泉（噴火警戒レベル1・2026年5月15日時点。湯釜火口から概ね500m範囲は火山灰等に注意）</t>
+          <t>大宮駅 --[上越・北陸新幹線]--&gt; 高崎駅 --[JR吾妻線]--&gt; 長野原草津口駅 --[JRバス関東]--&gt; 草津温泉バスターミナル</t>
         </is>
       </c>
       <c r="J37" s="41" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K37" s="41" t="n">
-        <v>4860</v>
+        <v>5400</v>
       </c>
       <c r="L37" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[上越・北陸新幹線]--&gt; 高崎駅 --[JR吾妻線]--&gt; 長野原草津口駅 --[JRバス関東]--&gt; 草津温泉（噴火警戒レベル1・2026年5月15日時点。湯釜火口から概ね500m範囲は火山灰等に注意）</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[上越・北陸新幹線]--&gt; 高崎駅 --[JR吾妻線]--&gt; 長野原草津口駅 --[JRバス関東]--&gt; 草津温泉バスターミナル</t>
         </is>
       </c>
       <c r="M37" s="41" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="N37" s="41" t="n">
-        <v>6710</v>
+        <v>7140</v>
       </c>
     </row>
     <row r="38" ht="39" customHeight="1" s="30">
@@ -8504,14 +8504,14 @@
       </c>
       <c r="F38" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[東北新幹線やまびこ（東京駅乗換）]--&gt; 郡山駅 --[JR磐越西線]--&gt; 猪苗代駅 --[タクシー]--&gt; 八方台登山口（バス路線なし、タクシー利用）</t>
+          <t>新宿駅 --[JR埼京線・湘南新宿ライン]--&gt; 大宮駅 --[東北新幹線やまびこ]--&gt; 郡山駅 --[JR磐越西線]--&gt; 猪苗代駅 --[タクシー]--&gt; 八方台登山口（バス路線なし、タクシー利用）</t>
         </is>
       </c>
       <c r="G38" s="41" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="H38" s="41" t="n">
-        <v>7900</v>
+        <v>7700</v>
       </c>
       <c r="I38" s="44" t="inlineStr">
         <is>
@@ -8519,21 +8519,21 @@
         </is>
       </c>
       <c r="J38" s="41" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="K38" s="41" t="n">
-        <v>6160</v>
+        <v>6820</v>
       </c>
       <c r="L38" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[東北新幹線やまびこ]--&gt; 郡山駅 --[JR磐越西線]--&gt; 猪苗代駅 --[タクシー]--&gt; 八方台登山口（バス路線なし、タクシー利用）</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[東北新幹線やまびこ]--&gt; 郡山駅 --[JR磐越西線]--&gt; 猪苗代駅 --[タクシー]--&gt; 八方台登山口（バス路線なし、タクシー利用）</t>
         </is>
       </c>
       <c r="M38" s="41" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="N38" s="41" t="n">
-        <v>8400</v>
+        <v>9130</v>
       </c>
     </row>
     <row r="39" ht="64.5" customHeight="1" s="30">
@@ -8986,18 +8986,18 @@
         <v>160</v>
       </c>
       <c r="K46" s="41" t="n">
-        <v>5800</v>
+        <v>5030</v>
       </c>
       <c r="L46" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 韮崎駅 --[山梨峡北交通バス「韮崎深田公園線」]--&gt; 深田記念公園</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 甲府駅 --[JR中央本線（普通）]--&gt; 韮崎駅 --[山梨峡北交通バス「韮崎深田公園線」]--&gt; 深田記念公園</t>
         </is>
       </c>
       <c r="M46" s="41" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="N46" s="41" t="n">
-        <v>5800</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="47" ht="39" customHeight="1" s="30">
@@ -9378,32 +9378,32 @@
         </is>
       </c>
       <c r="G53" s="41" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H53" s="41" t="n">
-        <v>9000</v>
+        <v>9610</v>
       </c>
       <c r="I53" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・特急あずさ・大糸線（西国分寺・立川・松本乗換）]--&gt; 信濃大町駅 --[アルピコ交通「扇沢線」]--&gt; 扇沢（季節）</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[アルピコ交通「扇沢線」]--&gt; 扇沢（季節）</t>
         </is>
       </c>
       <c r="J53" s="41" t="n">
-        <v>313</v>
+        <v>265</v>
       </c>
       <c r="K53" s="41" t="n">
-        <v>8690</v>
+        <v>9610</v>
       </c>
       <c r="L53" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR横浜線・特急あずさ・大糸線（八王子・松本乗換）]--&gt; 信濃大町駅 --[アルピコ交通「扇沢線」]--&gt; 扇沢（季節）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[アルピコ交通「扇沢線」]--&gt; 扇沢（季節）</t>
         </is>
       </c>
       <c r="M53" s="41" t="n">
-        <v>319</v>
+        <v>261</v>
       </c>
       <c r="N53" s="41" t="n">
-        <v>8690</v>
+        <v>9610</v>
       </c>
     </row>
     <row r="54" ht="39" customHeight="1" s="30">
@@ -9674,33 +9674,33 @@
       </c>
       <c r="F59" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 一ノ鳥居苑地</t>
+          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 飯綱登山口バス停（一ノ鳥居苑地）</t>
         </is>
       </c>
       <c r="G59" s="41" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="H59" s="41" t="n">
         <v>8760</v>
       </c>
       <c r="I59" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 一ノ鳥居苑地</t>
+          <t>大宮駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 飯綱登山口バス停（一ノ鳥居苑地）</t>
         </is>
       </c>
       <c r="J59" s="41" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="K59" s="41" t="n">
         <v>6860</v>
       </c>
       <c r="L59" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 一ノ鳥居苑地</t>
+          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 飯綱登山口バス停（一ノ鳥居苑地）</t>
         </is>
       </c>
       <c r="M59" s="41" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="N59" s="41" t="n">
         <v>9200</v>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="F63" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 羽衣登山口（季節）</t>
+          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 七面山登山口・赤沢入口バス停 --[タクシー（所要時間は未確認）]--&gt; 羽衣登山口</t>
         </is>
       </c>
       <c r="G63" s="41" t="n">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="I63" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 羽衣登山口（季節）</t>
+          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 七面山登山口・赤沢入口バス停 --[タクシー（所要時間は未確認）]--&gt; 羽衣登山口</t>
         </is>
       </c>
       <c r="J63" s="41" t="n">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="L63" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 羽衣登山口（季節）</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 七面山登山口・赤沢入口バス停 --[タクシー（所要時間は未確認）]--&gt; 羽衣登山口</t>
         </is>
       </c>
       <c r="M63" s="41" t="n">
@@ -10172,36 +10172,36 @@
       </c>
       <c r="F68" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（夏季）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（夏季）</t>
         </is>
       </c>
       <c r="G68" s="41" t="n">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="H68" s="41" t="n">
-        <v>8400</v>
+        <v>8670</v>
       </c>
       <c r="I68" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（夏季）</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（夏季）</t>
         </is>
       </c>
       <c r="J68" s="41" t="n">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="K68" s="41" t="n">
-        <v>8090</v>
+        <v>8670</v>
       </c>
       <c r="L68" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（夏季）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（夏季）</t>
         </is>
       </c>
       <c r="M68" s="41" t="n">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="N68" s="41" t="n">
-        <v>8400</v>
+        <v>8670</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="30">
@@ -10790,10 +10790,10 @@
         </is>
       </c>
       <c r="G79" s="41" t="n">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="H79" s="41" t="n">
-        <v>10880</v>
+        <v>9660</v>
       </c>
       <c r="I79" s="44" t="inlineStr">
         <is>
@@ -10801,10 +10801,10 @@
         </is>
       </c>
       <c r="J79" s="41" t="n">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="K79" s="41" t="n">
-        <v>10570</v>
+        <v>9350</v>
       </c>
       <c r="L79" s="44" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="M79" s="41" t="n">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="N79" s="41" t="n">
-        <v>10570</v>
+        <v>9350</v>
       </c>
     </row>
     <row r="80" ht="39" customHeight="1" s="30">
@@ -11608,36 +11608,36 @@
       </c>
       <c r="F94" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「広河原線」]--&gt; 広河原（マイカー規制）</t>
+          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「南アルプス登山バス」]--&gt; 広河原（マイカー規制）</t>
         </is>
       </c>
       <c r="G94" s="41" t="n">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="H94" s="41" t="n">
-        <v>6700</v>
+        <v>6290</v>
       </c>
       <c r="I94" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「広河原線」]--&gt; 広河原（マイカー規制）</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「南アルプス登山バス」]--&gt; 広河原（マイカー規制）</t>
         </is>
       </c>
       <c r="J94" s="41" t="n">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="K94" s="41" t="n">
-        <v>7470</v>
+        <v>6290</v>
       </c>
       <c r="L94" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「広河原線」]--&gt; 広河原（マイカー規制）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 甲府駅 --[山梨交通「南アルプス登山バス」]--&gt; 広河原（マイカー規制）</t>
         </is>
       </c>
       <c r="M94" s="41" t="n">
-        <v>294</v>
+        <v>225</v>
       </c>
       <c r="N94" s="41" t="n">
-        <v>7470</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="95" ht="51.75" customHeight="1" s="30">
@@ -11670,7 +11670,7 @@
         </is>
       </c>
       <c r="G95" s="41" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="H95" s="41" t="n">
         <v>6290</v>
@@ -11681,21 +11681,21 @@
         </is>
       </c>
       <c r="J95" s="41" t="n">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="K95" s="41" t="n">
-        <v>7060</v>
+        <v>6290</v>
       </c>
       <c r="L95" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「南アルプス登山バス」]--&gt; 広河原（マイカー規制）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 甲府駅 --[山梨交通「南アルプス登山バス」]--&gt; 広河原（マイカー規制）</t>
         </is>
       </c>
       <c r="M95" s="41" t="n">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="N95" s="41" t="n">
-        <v>7060</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="30">
@@ -12072,36 +12072,36 @@
       </c>
       <c r="F102" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（燕岳経由で大天井岳へ縦走・夏季運行）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（燕岳経由で大天井岳へ縦走・夏季運行）</t>
         </is>
       </c>
       <c r="G102" s="41" t="n">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="H102" s="41" t="n">
-        <v>9900</v>
+        <v>8670</v>
       </c>
       <c r="I102" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR中央線・大糸線（松本乗換）]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（燕岳経由で大天井岳へ縦走・夏季運行）</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（燕岳経由で大天井岳へ縦走・夏季運行）</t>
         </is>
       </c>
       <c r="J102" s="41" t="n">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="K102" s="41" t="n">
-        <v>9590</v>
+        <v>8670</v>
       </c>
       <c r="L102" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線・大糸線（松本乗換）]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（燕岳経由で大天井岳へ縦走・夏季運行）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 穂高駅 --[南安タクシー「中房温泉行き定期バス」]--&gt; 中房温泉（燕岳経由で大天井岳へ縦走・夏季運行）</t>
         </is>
       </c>
       <c r="M102" s="41" t="n">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="N102" s="41" t="n">
-        <v>9900</v>
+        <v>8670</v>
       </c>
     </row>
     <row r="103" ht="39" customHeight="1" s="30">
@@ -12130,36 +12130,36 @@
       </c>
       <c r="F103" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 信濃大町駅 --[アルピコ交通バス「扇沢線」]--&gt; 扇沢（季節運行）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[アルピコ交通バス「扇沢線」]--&gt; 扇沢（季節運行）</t>
         </is>
       </c>
       <c r="G103" s="41" t="n">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="H103" s="41" t="n">
-        <v>9000</v>
+        <v>9610</v>
       </c>
       <c r="I103" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 信濃大町駅 --[アルピコ交通バス「扇沢線」]--&gt; 扇沢（季節運行）</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[アルピコ交通バス「扇沢線」]--&gt; 扇沢（季節運行）</t>
         </is>
       </c>
       <c r="J103" s="41" t="n">
-        <v>310</v>
+        <v>265</v>
       </c>
       <c r="K103" s="41" t="n">
-        <v>8690</v>
+        <v>9610</v>
       </c>
       <c r="L103" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[JR大糸線]--&gt; 信濃大町駅 --[アルピコ交通バス「扇沢線」]--&gt; 扇沢（季節運行）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[アルピコ交通バス「扇沢線」]--&gt; 扇沢（季節運行）</t>
         </is>
       </c>
       <c r="M103" s="41" t="n">
-        <v>314</v>
+        <v>261</v>
       </c>
       <c r="N103" s="41" t="n">
-        <v>9000</v>
+        <v>9610</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="30">
@@ -12188,36 +12188,36 @@
       </c>
       <c r="F104" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
         </is>
       </c>
       <c r="G104" s="41" t="n">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="H104" s="41" t="n">
-        <v>9200</v>
+        <v>9110</v>
       </c>
       <c r="I104" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR中央線特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
         </is>
       </c>
       <c r="J104" s="41" t="n">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="K104" s="41" t="n">
-        <v>8890</v>
+        <v>9110</v>
       </c>
       <c r="L104" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
         </is>
       </c>
       <c r="M104" s="41" t="n">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="N104" s="41" t="n">
-        <v>9200</v>
+        <v>9110</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="30">
@@ -12246,36 +12246,36 @@
       </c>
       <c r="F105" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
         </is>
       </c>
       <c r="G105" s="41" t="n">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="H105" s="41" t="n">
-        <v>9200</v>
+        <v>9110</v>
       </c>
       <c r="I105" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR中央線特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
+          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
         </is>
       </c>
       <c r="J105" s="41" t="n">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="K105" s="41" t="n">
-        <v>8890</v>
+        <v>9110</v>
       </c>
       <c r="L105" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 信濃大町駅 --[裏銀座登山バス(季節運行・予約不要)]--&gt; 七倉 --[特定区間タクシー(許可車両のみ・七倉山荘等手配)]--&gt; 高瀬ダム</t>
         </is>
       </c>
       <c r="M105" s="41" t="n">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="N105" s="41" t="n">
-        <v>9200</v>
+        <v>9110</v>
       </c>
     </row>
     <row r="106" ht="26.25" customHeight="1" s="30">
@@ -13174,36 +13174,36 @@
       </c>
       <c r="F121" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[上越新幹線とき]--&gt; 越後湯沢駅 --[南越後観光バス]--&gt; 平標登山口バス停</t>
+          <t>新宿駅 --[JR埼京線・湘南新宿ライン]--&gt; 大宮駅 --[上越新幹線とき]--&gt; 越後湯沢駅 --[南越後交通バス]--&gt; 平標登山口バス停</t>
         </is>
       </c>
       <c r="G121" s="41" t="n">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="H121" s="41" t="n">
-        <v>6700</v>
+        <v>6820</v>
       </c>
       <c r="I121" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[上越新幹線とき直通]--&gt; 越後湯沢駅 --[南越後観光バス]--&gt; 平標登山口バス停</t>
+          <t>大宮駅 --[上越新幹線とき]--&gt; 越後湯沢駅 --[南越後交通バス]--&gt; 平標登山口バス停</t>
         </is>
       </c>
       <c r="J121" s="41" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K121" s="41" t="n">
-        <v>5920</v>
+        <v>6490</v>
       </c>
       <c r="L121" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[上越新幹線とき直通]--&gt; 越後湯沢駅 --[南越後観光バス]--&gt; 平標登山口バス停</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[上越新幹線]--&gt; 越後湯沢駅 --[南越後交通バス]--&gt; 平標登山口バス停</t>
         </is>
       </c>
       <c r="M121" s="41" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="N121" s="41" t="n">
-        <v>6420</v>
+        <v>7690</v>
       </c>
     </row>
     <row r="122" ht="26.25" customHeight="1" s="30">
@@ -15204,36 +15204,36 @@
       </c>
       <c r="F156" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線・湘南新宿ライン]--&gt; 大宮駅 --[北陸新幹線(あさま)]--&gt; 上田駅 --[上田バス(菅平線)]--&gt; 菅平高原(ダボス)</t>
+          <t>新宿駅 --[JR埼京線・湘南新宿ライン]--&gt; 大宮駅 --[北陸新幹線]--&gt; 上田駅 --[上田バス(菅平線)]--&gt; 菅平高原(ダボス)</t>
         </is>
       </c>
       <c r="G156" s="41" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="H156" s="41" t="n">
-        <v>6660</v>
+        <v>6760</v>
       </c>
       <c r="I156" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線(あさま)]--&gt; 上田駅 --[上田バス(菅平線)]--&gt; 菅平高原(ダボス)</t>
+          <t>大宮駅 --[北陸新幹線]--&gt; 上田駅 --[上田バス(菅平線)]--&gt; 菅平高原(ダボス)</t>
         </is>
       </c>
       <c r="J156" s="41" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="K156" s="41" t="n">
-        <v>4700</v>
+        <v>5990</v>
       </c>
       <c r="L156" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR埼京線・湘南新宿ライン]--&gt; 大宮駅 --[北陸新幹線(あさま)]--&gt; 上田駅 --[上田バス(菅平線)]--&gt; 菅平高原(ダボス)</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[北陸新幹線]--&gt; 上田駅 --[上田バス(菅平線)]--&gt; 菅平高原(ダボス)</t>
         </is>
       </c>
       <c r="M156" s="41" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N156" s="41" t="n">
-        <v>7240</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="157" ht="39" customHeight="1" s="30">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="E25" s="44" t="inlineStr">
         <is>
-          <t>会津バス「飯豊登山アクセスバス」（夏季限定・7月上旬〜8月下旬・1日2便のみ）／会津バス「飯豊登山アクセスバス」／会津バス「飯豊登山アクセスバス」（夏季限定・1日2便のみ）</t>
+          <t>飯豊山登山アクセスバス（喜多方市・山都タクシー運行）</t>
         </is>
       </c>
       <c r="F25" s="49" t="inlineStr">
@@ -16760,12 +16760,12 @@
       </c>
       <c r="K25" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L25" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>会津バス表記は誤り。2026年の運行日は未確認</t>
         </is>
       </c>
     </row>
@@ -18110,7 +18110,7 @@
       </c>
       <c r="E48" s="44" t="inlineStr">
         <is>
-          <t>南越後観光バス</t>
+          <t>南越後交通バス</t>
         </is>
       </c>
       <c r="F48" s="49" t="inlineStr">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="K48" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L48" s="44" t="inlineStr">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="E67" s="44" t="inlineStr">
         <is>
-          <t>上越新幹線・南越後観光バス</t>
+          <t>上越新幹線・南越後交通バス</t>
         </is>
       </c>
       <c r="F67" s="47" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="K67" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L67" s="44" t="inlineStr">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="E96" s="44" t="inlineStr">
         <is>
-          <t>JR中央線・山梨市民バス「西沢渓谷線」</t>
+          <t>山梨市民バス「西沢渓谷線」（毎日運行）</t>
         </is>
       </c>
       <c r="F96" s="49" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="K96" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L96" s="44" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="E134" s="44" t="inlineStr">
         <is>
-          <t>南越後観光バス急行(浦佐駅－奥只見ダム線)</t>
+          <t>南越後交通バス急行(浦佐駅－奥只見ダム線)</t>
         </is>
       </c>
       <c r="F134" s="49" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="K134" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="L134" s="44" t="inlineStr">
@@ -24235,7 +24235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K352"/>
+  <dimension ref="A1:K381"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -43608,6 +43608,1601 @@
       <c r="K352" s="57" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="53" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C353" s="53" t="inlineStr">
+        <is>
+          <t>22山</t>
+        </is>
+      </c>
+      <c r="D353" s="54" t="inlineStr">
+        <is>
+          <t>季節運行の山</t>
+        </is>
+      </c>
+      <c r="E353" s="54" t="inlineStr">
+        <is>
+          <t>2026年の運行期間を登録</t>
+        </is>
+      </c>
+      <c r="F353" s="54" t="inlineStr">
+        <is>
+          <t>annualItems</t>
+        </is>
+      </c>
+      <c r="G353" s="55" t="inlineStr">
+        <is>
+          <t>「例年◯月〜」の文章のみ</t>
+        </is>
+      </c>
+      <c r="H353" s="55" t="inlineStr">
+        <is>
+          <t>広河原 6/26〜11/3／中房温泉 4/24〜11/3／扇沢・アルペンルート 4/15〜11/30／裏銀座登山バス 7/17〜10/25／韮崎瑞牆線 4/4〜11/23／那須 4/1〜11/30／奥只見 6/1〜11/3／雨飾高原 4/1〜11/30／上日川峠 4/18〜12/13 ほか</t>
+        </is>
+      </c>
+      <c r="I353" s="56" t="inlineStr">
+        <is>
+          <t>各事業者・自治体・観光協会のページ（annualItems.sourceUrl）</t>
+        </is>
+      </c>
+      <c r="J353" s="55" t="inlineStr">
+        <is>
+          <t>check_annual_updates.py で出典を取得できることを確認</t>
+        </is>
+      </c>
+      <c r="K353" s="57" t="inlineStr">
+        <is>
+          <t>中〜高</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="53" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C354" s="53" t="inlineStr">
+        <is>
+          <t>19山</t>
+        </is>
+      </c>
+      <c r="D354" s="54" t="inlineStr">
+        <is>
+          <t>季節運行の山</t>
+        </is>
+      </c>
+      <c r="E354" s="54" t="inlineStr">
+        <is>
+          <t>出典のみ登録</t>
+        </is>
+      </c>
+      <c r="F354" s="54" t="inlineStr">
+        <is>
+          <t>annualItems</t>
+        </is>
+      </c>
+      <c r="G354" s="55" t="inlineStr">
+        <is>
+          <t>登録なし</t>
+        </is>
+      </c>
+      <c r="H354" s="55" t="inlineStr">
+        <is>
+          <t>今年の期間は未確認。出典ページの変更検知の対象にした</t>
+        </is>
+      </c>
+      <c r="I354" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J354" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K354" s="57" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="53" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C355" s="53" t="inlineStr">
+        <is>
+          <t>iide・aizu_koma・tairappyo・makihata・naeba</t>
+        </is>
+      </c>
+      <c r="D355" s="54" t="inlineStr">
+        <is>
+          <t>飯豊山・会津駒ヶ岳・平標山・巻機山・苗場山</t>
+        </is>
+      </c>
+      <c r="E355" s="54" t="inlineStr">
+        <is>
+          <t>リンク切れ</t>
+        </is>
+      </c>
+      <c r="F355" s="54" t="inlineStr">
+        <is>
+          <t>バス時刻表リンク</t>
+        </is>
+      </c>
+      <c r="G355" s="55" t="inlineStr">
+        <is>
+          <t>aizubus.com/rosen/jikokuhyou、minamiechigo.co.jp/rosen/（どちらも404）</t>
+        </is>
+      </c>
+      <c r="H355" s="55" t="inlineStr">
+        <is>
+          <t>aizubus.com/rosen、minamiechigo.co.jp/ に差し替え</t>
+        </is>
+      </c>
+      <c r="I355" s="56" t="inlineStr">
+        <is>
+          <t>HTTPステータスを確認</t>
+        </is>
+      </c>
+      <c r="J355" s="55" t="inlineStr">
+        <is>
+          <t>check_annual_updates.py で取得できることを確認</t>
+        </is>
+      </c>
+      <c r="K355" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="53" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C356" s="53" t="inlineStr">
+        <is>
+          <t>nokogiriyama・kirigamine・shiomidake</t>
+        </is>
+      </c>
+      <c r="D356" s="54" t="inlineStr">
+        <is>
+          <t>鋸岳・霧ヶ峰・塩見岳</t>
+        </is>
+      </c>
+      <c r="E356" s="54" t="inlineStr">
+        <is>
+          <t>2026年の運行期間を登録</t>
+        </is>
+      </c>
+      <c r="F356" s="54" t="inlineStr">
+        <is>
+          <t>annualItems・注記</t>
+        </is>
+      </c>
+      <c r="G356" s="55" t="inlineStr">
+        <is>
+          <t>「例年◯月〜」</t>
+        </is>
+      </c>
+      <c r="H356" s="55" t="inlineStr">
+        <is>
+          <t>ジオライナー 7/17〜10/12／霧ヶ峰線 5/2〜10/25／鳥倉線 7/18〜8/30</t>
+        </is>
+      </c>
+      <c r="I356" s="56" t="inlineStr">
+        <is>
+          <t>JRバス関東、霧ヶ峰自然保護センター、伊那バスの告知</t>
+        </is>
+      </c>
+      <c r="J356" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K356" s="57" t="inlineStr">
+        <is>
+          <t>中〜高</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="53" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C357" s="53" t="inlineStr">
+        <is>
+          <t>arasawadake・echigokoma・tairappyo・hiragadake</t>
+        </is>
+      </c>
+      <c r="D357" s="54" t="inlineStr">
+        <is>
+          <t>荒沢岳・越後駒ヶ岳・平標山・平ヶ岳</t>
+        </is>
+      </c>
+      <c r="E357" s="54" t="inlineStr">
+        <is>
+          <t>事業者名の変更</t>
+        </is>
+      </c>
+      <c r="F357" s="54" t="inlineStr">
+        <is>
+          <t>バス会社名</t>
+        </is>
+      </c>
+      <c r="G357" s="55" t="inlineStr">
+        <is>
+          <t>南越後観光バス</t>
+        </is>
+      </c>
+      <c r="H357" s="55" t="inlineStr">
+        <is>
+          <t>南越後交通バス（2026年4月1日に社名変更）。検索ページ2本も修正</t>
+        </is>
+      </c>
+      <c r="I357" s="56" t="inlineStr">
+        <is>
+          <t>十日町市の資料、事業者サイト</t>
+        </is>
+      </c>
+      <c r="J357" s="55" t="inlineStr">
+        <is>
+          <t>残存0件をgrepで確認</t>
+        </is>
+      </c>
+      <c r="K357" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="53" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C358" s="53" t="inlineStr">
+        <is>
+          <t>iide</t>
+        </is>
+      </c>
+      <c r="D358" s="54" t="inlineStr">
+        <is>
+          <t>飯豊山</t>
+        </is>
+      </c>
+      <c r="E358" s="54" t="inlineStr">
+        <is>
+          <t>バス事業者名の誤り</t>
+        </is>
+      </c>
+      <c r="F358" s="54" t="inlineStr">
+        <is>
+          <t>山都駅〜川入</t>
+        </is>
+      </c>
+      <c r="G358" s="55" t="inlineStr">
+        <is>
+          <t>会津バス「飯豊登山アクセスバス」（7月上旬〜8月下旬）</t>
+        </is>
+      </c>
+      <c r="H358" s="55" t="inlineStr">
+        <is>
+          <t>喜多方市の「飯豊山登山アクセスバス」（山都タクシー運行・過去実績は7月中旬〜9月中旬の金〜月曜・1日2便・1,000円）。2026年の運行日は未確認と明記</t>
+        </is>
+      </c>
+      <c r="I358" s="56" t="inlineStr">
+        <is>
+          <t>飯豊町「飯豊山登山情報（市町村別一覧）」</t>
+        </is>
+      </c>
+      <c r="J358" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K358" s="57" t="inlineStr">
+        <is>
+          <t>中（2026年は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="53" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C359" s="53" t="inlineStr">
+        <is>
+          <t>kentoku・karisaka</t>
+        </is>
+      </c>
+      <c r="D359" s="54" t="inlineStr">
+        <is>
+          <t>乾徳山・雁坂嶺</t>
+        </is>
+      </c>
+      <c r="E359" s="54" t="inlineStr">
+        <is>
+          <t>運行形態の誤り</t>
+        </is>
+      </c>
+      <c r="F359" s="54" t="inlineStr">
+        <is>
+          <t>山梨市駅〜乾徳山登山口</t>
+        </is>
+      </c>
+      <c r="G359" s="55" t="inlineStr">
+        <is>
+          <t>乾徳山：山梨交通「西沢渓谷線」・季節運行</t>
+        </is>
+      </c>
+      <c r="H359" s="55" t="inlineStr">
+        <is>
+          <t>山梨市民バス「西沢渓谷線」・毎日運行（1/1・1/2運休）。雁坂嶺の注記にも市民バスを追記。検索ページ4本の「（季節）」を削除</t>
+        </is>
+      </c>
+      <c r="I359" s="56" t="inlineStr">
+        <is>
+          <t>山梨市公式（2025-08-01更新）</t>
+        </is>
+      </c>
+      <c r="J359" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K359" s="57" t="inlineStr">
+        <is>
+          <t>高（冬の途中止まりは未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="53" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C360" s="53" t="inlineStr">
+        <is>
+          <t>ontakesan</t>
+        </is>
+      </c>
+      <c r="D360" s="54" t="inlineStr">
+        <is>
+          <t>御嶽山</t>
+        </is>
+      </c>
+      <c r="E360" s="54" t="inlineStr">
+        <is>
+          <t>バスの所要時間・運行日</t>
+        </is>
+      </c>
+      <c r="F360" s="54" t="inlineStr">
+        <is>
+          <t>木曽福島駅〜田の原</t>
+        </is>
+      </c>
+      <c r="G360" s="55" t="inlineStr">
+        <is>
+          <t>バス約100分、例年7月〜10月</t>
+        </is>
+      </c>
+      <c r="H360" s="55" t="inlineStr">
+        <is>
+          <t>約75分（8:40発→9:55着）。2026年は7/4〜10/18の土日祝と8/3〜7・8/10、1日2便。全出発地で所要時間−25分</t>
+        </is>
+      </c>
+      <c r="I360" s="56" t="inlineStr">
+        <is>
+          <t>王滝村公式「田の原線バス」（令和8年）</t>
+        </is>
+      </c>
+      <c r="J360" s="55" t="inlineStr">
+        <is>
+          <t>legs合計と一致</t>
+        </is>
+      </c>
+      <c r="K360" s="57" t="inlineStr">
+        <is>
+          <t>高（運賃合計の内訳は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="53" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C361" s="53" t="inlineStr">
+        <is>
+          <t>keirisan・shirane_gunma</t>
+        </is>
+      </c>
+      <c r="D361" s="54" t="inlineStr">
+        <is>
+          <t>蓼科山・草津白根山</t>
+        </is>
+      </c>
+      <c r="E361" s="54" t="inlineStr">
+        <is>
+          <t>2026年の運行状況を登録</t>
+        </is>
+      </c>
+      <c r="F361" s="54" t="inlineStr">
+        <is>
+          <t>annualItems・注記</t>
+        </is>
+      </c>
+      <c r="G361" s="55" t="inlineStr">
+        <is>
+          <t>「例年◯月〜」／記載なし</t>
+        </is>
+      </c>
+      <c r="H361" s="55" t="inlineStr">
+        <is>
+          <t>蓼科高原ラウンドバス 5/2〜10/25（登山口経由は土日祝と夏の毎日・1往復）／草津温泉〜白根火山は当面全便運休</t>
+        </is>
+      </c>
+      <c r="I361" s="56" t="inlineStr">
+        <is>
+          <t>茅野市・アルピコ交通、JRバス関東の運行情報</t>
+        </is>
+      </c>
+      <c r="J361" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K361" s="57" t="inlineStr">
+        <is>
+          <t>中〜高</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="53" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C362" s="53" t="inlineStr">
+        <is>
+          <t>makihata</t>
+        </is>
+      </c>
+      <c r="D362" s="54" t="inlineStr">
+        <is>
+          <t>巻機山</t>
+        </is>
+      </c>
+      <c r="E362" s="54" t="inlineStr">
+        <is>
+          <t>運行形態の表記</t>
+        </is>
+      </c>
+      <c r="F362" s="54" t="inlineStr">
+        <is>
+          <t>六日町駅〜清水</t>
+        </is>
+      </c>
+      <c r="G362" s="55" t="inlineStr">
+        <is>
+          <t>バッジ「季節運行」</t>
+        </is>
+      </c>
+      <c r="H362" s="55" t="inlineStr">
+        <is>
+          <t>「平日のみ・要予約」。路線バス（六日町〜清水線）は2026/3/31廃止、4/1からMOSSのみと注記</t>
+        </is>
+      </c>
+      <c r="I362" s="56" t="inlineStr">
+        <is>
+          <t>南魚沼市観光協会（2026-06-15）、南魚沼市公式（2026-10-01更新）</t>
+        </is>
+      </c>
+      <c r="J362" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K362" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="53" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C363" s="53" t="inlineStr">
+        <is>
+          <t>iizunasan</t>
+        </is>
+      </c>
+      <c r="D363" s="54" t="inlineStr">
+        <is>
+          <t>飯縄山</t>
+        </is>
+      </c>
+      <c r="E363" s="54" t="inlineStr">
+        <is>
+          <t>運行形態・終点の表記</t>
+        </is>
+      </c>
+      <c r="F363" s="54" t="inlineStr">
+        <is>
+          <t>長野駅〜飯綱登山口</t>
+        </is>
+      </c>
+      <c r="G363" s="55" t="inlineStr">
+        <is>
+          <t>バッジ「季節運行」、終点「一ノ鳥居苑地」</t>
+        </is>
+      </c>
+      <c r="H363" s="55" t="inlineStr">
+        <is>
+          <t>「年中運行」（冬ダイヤあり）、終点「飯綱登山口バス停（一ノ鳥居苑地）」。検索ページ5か所も修正</t>
+        </is>
+      </c>
+      <c r="I363" s="56" t="inlineStr">
+        <is>
+          <t>アルピコ交通 戸隠線（冬ダイヤの時刻表に飯綱登山口の記載）</t>
+        </is>
+      </c>
+      <c r="J363" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K363" s="57" t="inlineStr">
+        <is>
+          <t>中〜高</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="53" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C364" s="53" t="inlineStr">
+        <is>
+          <t>nanaitsurasan</t>
+        </is>
+      </c>
+      <c r="D364" s="54" t="inlineStr">
+        <is>
+          <t>七面山</t>
+        </is>
+      </c>
+      <c r="E364" s="54" t="inlineStr">
+        <is>
+          <t>終点の誤り・運行形態</t>
+        </is>
+      </c>
+      <c r="F364" s="54" t="inlineStr">
+        <is>
+          <t>身延駅〜羽衣</t>
+        </is>
+      </c>
+      <c r="G364" s="55" t="inlineStr">
+        <is>
+          <t>バッジ「季節運行」。バス20分で「羽衣登山口（季節）」に着く表記</t>
+        </is>
+      </c>
+      <c r="H364" s="55" t="inlineStr">
+        <is>
+          <t>バスは毎日運行・1日4本で、着くのは「七面山登山口・赤沢入口」。羽衣まではタクシー（時間未確認）。検索ページ3か所も修正</t>
+        </is>
+      </c>
+      <c r="I364" s="56" t="inlineStr">
+        <is>
+          <t>早川町観光協会のアクセス案内</t>
+        </is>
+      </c>
+      <c r="J364" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K364" s="57" t="inlineStr">
+        <is>
+          <t>中（予約要否・タクシー区間は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="53" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C365" s="53" t="inlineStr">
+        <is>
+          <t>tairappyo</t>
+        </is>
+      </c>
+      <c r="D365" s="54" t="inlineStr">
+        <is>
+          <t>平標山</t>
+        </is>
+      </c>
+      <c r="E365" s="54" t="inlineStr">
+        <is>
+          <t>運行形態・バス運賃</t>
+        </is>
+      </c>
+      <c r="F365" s="54" t="inlineStr">
+        <is>
+          <t>越後湯沢駅〜平標登山口</t>
+        </is>
+      </c>
+      <c r="G365" s="55" t="inlineStr">
+        <is>
+          <t>バッジ「バス季節運行」、約640円</t>
+        </is>
+      </c>
+      <c r="H365" s="55" t="inlineStr">
+        <is>
+          <t>「年中運行」・1日8便、660円（2026年4月改正）。運賃合計は未修正（要確認）</t>
+        </is>
+      </c>
+      <c r="I365" s="56" t="inlineStr">
+        <is>
+          <t>南越後交通バス 2026-04-01改正時刻表</t>
+        </is>
+      </c>
+      <c r="J365" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K365" s="57" t="inlineStr">
+        <is>
+          <t>高（合計運賃は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="53" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C366" s="53" t="inlineStr">
+        <is>
+          <t>mitosaan</t>
+        </is>
+      </c>
+      <c r="D366" s="54" t="inlineStr">
+        <is>
+          <t>三頭山</t>
+        </is>
+      </c>
+      <c r="E366" s="54" t="inlineStr">
+        <is>
+          <t>運行期間の表記</t>
+        </is>
+      </c>
+      <c r="F366" s="54" t="inlineStr">
+        <is>
+          <t>数馬〜都民の森</t>
+        </is>
+      </c>
+      <c r="G366" s="55" t="inlineStr">
+        <is>
+          <t>急行バス「3月中旬〜11月の土日祝」</t>
+        </is>
+      </c>
+      <c r="H366" s="55" t="inlineStr">
+        <is>
+          <t>連絡バス・急行バスとも4〜11月の開園日は毎日、3月は土日祝。12〜2月は運行なし。休園日は運休</t>
+        </is>
+      </c>
+      <c r="I366" s="56" t="inlineStr">
+        <is>
+          <t>檜原都民の森の公式案内</t>
+        </is>
+      </c>
+      <c r="J366" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K366" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="53" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C367" s="53" t="inlineStr">
+        <is>
+          <t>kayagatake</t>
+        </is>
+      </c>
+      <c r="D367" s="54" t="inlineStr">
+        <is>
+          <t>茅ヶ岳</t>
+        </is>
+      </c>
+      <c r="E367" s="54" t="inlineStr">
+        <is>
+          <t>2026年の運行期間を登録</t>
+        </is>
+      </c>
+      <c r="F367" s="54" t="inlineStr">
+        <is>
+          <t>韮崎駅〜深田記念公園</t>
+        </is>
+      </c>
+      <c r="G367" s="55" t="inlineStr">
+        <is>
+          <t>例年4月〜11月の土日祝</t>
+        </is>
+      </c>
+      <c r="H367" s="55" t="inlineStr">
+        <is>
+          <t>2026年は4/4〜11/23の土日祝（4/29〜5/5は毎日）、1日2往復・700円</t>
+        </is>
+      </c>
+      <c r="I367" s="56" t="inlineStr">
+        <is>
+          <t>山梨峡北交通の告知</t>
+        </is>
+      </c>
+      <c r="J367" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K367" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="53" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C368" s="53" t="inlineStr">
+        <is>
+          <t>shirasunayama</t>
+        </is>
+      </c>
+      <c r="D368" s="54" t="inlineStr">
+        <is>
+          <t>白砂山</t>
+        </is>
+      </c>
+      <c r="E368" s="54" t="inlineStr">
+        <is>
+          <t>運行期間の表記</t>
+        </is>
+      </c>
+      <c r="F368" s="54" t="inlineStr">
+        <is>
+          <t>花敷温泉〜野反湖</t>
+        </is>
+      </c>
+      <c r="G368" s="55" t="inlineStr">
+        <is>
+          <t>夏山シーズン（6月頃〜10月）限定</t>
+        </is>
+      </c>
+      <c r="H368" s="55" t="inlineStr">
+        <is>
+          <t>5月1日〜10月20日・1日3便。期間外は花敷温泉止まり。annualItemsに登録</t>
+        </is>
+      </c>
+      <c r="I368" s="56" t="inlineStr">
+        <is>
+          <t>中之条町 六合地区路線バス時刻表PDF（令和7年3月15日現在）を直接確認</t>
+        </is>
+      </c>
+      <c r="J368" s="55" t="inlineStr">
+        <is>
+          <t>所要時間76分（10:57発→12:13着）が既存の75分と整合</t>
+        </is>
+      </c>
+      <c r="K368" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="53" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C369" s="53" t="inlineStr">
+        <is>
+          <t>tairappyo</t>
+        </is>
+      </c>
+      <c r="D369" s="54" t="inlineStr">
+        <is>
+          <t>平標山</t>
+        </is>
+      </c>
+      <c r="E369" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路の検算</t>
+        </is>
+      </c>
+      <c r="F369" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G369" s="55" t="inlineStr">
+        <is>
+          <t>6,700／5,920／6,420円。新宿は東京駅経由</t>
+        </is>
+      </c>
+      <c r="H369" s="55" t="inlineStr">
+        <is>
+          <t>6,820／6,490／7,690円。新宿は大宮で新幹線に乗換（速くて安い）。所要時間 124／92／134分</t>
+        </is>
+      </c>
+      <c r="I369" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（2026-10-17）＋バス660円</t>
+        </is>
+      </c>
+      <c r="J369" s="55" t="inlineStr">
+        <is>
+          <t>JR 6,160／5,830／7,030＋660</t>
+        </is>
+      </c>
+      <c r="K369" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="53" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C370" s="53" t="inlineStr">
+        <is>
+          <t>ontakesan</t>
+        </is>
+      </c>
+      <c r="D370" s="54" t="inlineStr">
+        <is>
+          <t>御嶽山</t>
+        </is>
+      </c>
+      <c r="E370" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F370" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G370" s="55" t="inlineStr">
+        <is>
+          <t>10,880／10,570／10,570円</t>
+        </is>
+      </c>
+      <c r="H370" s="55" t="inlineStr">
+        <is>
+          <t>9,660／9,350／9,350円</t>
+        </is>
+      </c>
+      <c r="I370" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（2026-10-17）＋バス1,500円（王滝村公式）</t>
+        </is>
+      </c>
+      <c r="J370" s="55" t="inlineStr">
+        <is>
+          <t>JR 8,160／7,850／7,850＋1,500</t>
+        </is>
+      </c>
+      <c r="K370" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="53" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C371" s="53" t="inlineStr">
+        <is>
+          <t>iide</t>
+        </is>
+      </c>
+      <c r="D371" s="54" t="inlineStr">
+        <is>
+          <t>飯豊山</t>
+        </is>
+      </c>
+      <c r="E371" s="54" t="inlineStr">
+        <is>
+          <t>運賃・所要時間の検算</t>
+        </is>
+      </c>
+      <c r="F371" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G371" s="55" t="inlineStr">
+        <is>
+          <t>9,430／8,560／10,710円。東京→郡山65分、郡山→山都100分 ほか</t>
+        </is>
+      </c>
+      <c r="H371" s="55" t="inlineStr">
+        <is>
+          <t>山都駅まで 9,460／8,030／10,010円（バス代は別）。東京→郡山100分、郡山→会津若松72分、会津若松→山都34分。所要時間 296／256／307分</t>
+        </is>
+      </c>
+      <c r="I371" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（2026-10-17、やまびこ203号）</t>
+        </is>
+      </c>
+      <c r="J371" s="55" t="inlineStr">
+        <is>
+          <t>legs合計と一致</t>
+        </is>
+      </c>
+      <c r="K371" s="57" t="inlineStr">
+        <is>
+          <t>高（バスは未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="53" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C372" s="53" t="inlineStr">
+        <is>
+          <t>kitadake・noutori・ainodake</t>
+        </is>
+      </c>
+      <c r="D372" s="54" t="inlineStr">
+        <is>
+          <t>北岳・農鳥岳・間ノ岳</t>
+        </is>
+      </c>
+      <c r="E372" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（大宮・横浜が新宿＋770円）</t>
+        </is>
+      </c>
+      <c r="F372" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G372" s="55" t="inlineStr">
+        <is>
+          <t>北岳・農鳥岳 6,290／7,060／7,060円、間ノ岳 6,700／7,470／7,470円</t>
+        </is>
+      </c>
+      <c r="H372" s="55" t="inlineStr">
+        <is>
+          <t>3山とも 6,290／6,290／5,730円（JR＋バス1,990＋協力金300）。横浜は横浜線で八王子に出て特急。間ノ岳の経路を北岳と同じ登山バスに統一</t>
+        </is>
+      </c>
+      <c r="I372" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（2026-10-17）：→甲府 4,000／4,000／3,440</t>
+        </is>
+      </c>
+      <c r="J372" s="55" t="inlineStr">
+        <is>
+          <t>JR＋1,990＋300</t>
+        </is>
+      </c>
+      <c r="K372" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="53" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C373" s="53" t="inlineStr">
+        <is>
+          <t>kayagatake</t>
+        </is>
+      </c>
+      <c r="D373" s="54" t="inlineStr">
+        <is>
+          <t>茅ヶ岳</t>
+        </is>
+      </c>
+      <c r="E373" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F373" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G373" s="55" t="inlineStr">
+        <is>
+          <t>5,030／5,800／5,800円</t>
+        </is>
+      </c>
+      <c r="H373" s="55" t="inlineStr">
+        <is>
+          <t>5,030／5,030／4,470円（JR＋バス700）</t>
+        </is>
+      </c>
+      <c r="I373" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→韮崎 4,330／4,330／3,770</t>
+        </is>
+      </c>
+      <c r="J373" s="55" t="inlineStr">
+        <is>
+          <t>JR＋700</t>
+        </is>
+      </c>
+      <c r="K373" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="53" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C374" s="53" t="inlineStr">
+        <is>
+          <t>mizugaki</t>
+        </is>
+      </c>
+      <c r="D374" s="54" t="inlineStr">
+        <is>
+          <t>瑞牆山</t>
+        </is>
+      </c>
+      <c r="E374" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F374" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G374" s="55" t="inlineStr">
+        <is>
+          <t>6,100／6,870／6,870円（新宿発が甲府までの運賃で計算されていた）</t>
+        </is>
+      </c>
+      <c r="H374" s="55" t="inlineStr">
+        <is>
+          <t>6,430／6,430／5,870円（JR＋バス2,100）</t>
+        </is>
+      </c>
+      <c r="I374" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→韮崎 4,330／4,330／3,770</t>
+        </is>
+      </c>
+      <c r="J374" s="55" t="inlineStr">
+        <is>
+          <t>JR＋2,100</t>
+        </is>
+      </c>
+      <c r="K374" s="57" t="inlineStr">
+        <is>
+          <t>高（バス2,100円は既存の注記の値）</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="53" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C375" s="53" t="inlineStr">
+        <is>
+          <t>harinokidake・kashimayari</t>
+        </is>
+      </c>
+      <c r="D375" s="54" t="inlineStr">
+        <is>
+          <t>針ノ木岳・鹿島槍ヶ岳</t>
+        </is>
+      </c>
+      <c r="E375" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F375" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G375" s="55" t="inlineStr">
+        <is>
+          <t>針ノ木 9,000／8,690／9,000円、鹿島槍 9,000／8,690／8,690円（同じ扇沢行きで不一致）</t>
+        </is>
+      </c>
+      <c r="H375" s="55" t="inlineStr">
+        <is>
+          <t>2山とも 9,610円（3出発地同額）。バスは2,000円・約40分</t>
+        </is>
+      </c>
+      <c r="I375" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→信濃大町 7,610円（3出発地同額）、アルピコ交通 扇沢線運賃表（2026-04-15改正）</t>
+        </is>
+      </c>
+      <c r="J375" s="55" t="inlineStr">
+        <is>
+          <t>7,610＋2,000</t>
+        </is>
+      </c>
+      <c r="K375" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="53" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C376" s="53" t="inlineStr">
+        <is>
+          <t>eboshidake_kita・noguchigoro</t>
+        </is>
+      </c>
+      <c r="D376" s="54" t="inlineStr">
+        <is>
+          <t>烏帽子岳・野口五郎岳</t>
+        </is>
+      </c>
+      <c r="E376" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F376" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G376" s="55" t="inlineStr">
+        <is>
+          <t>9,200／8,890／9,200円</t>
+        </is>
+      </c>
+      <c r="H376" s="55" t="inlineStr">
+        <is>
+          <t>9,110円（3出発地同額。七倉まで、タクシー代は別）</t>
+        </is>
+      </c>
+      <c r="I376" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報、裏銀座登山バス 1,500円</t>
+        </is>
+      </c>
+      <c r="J376" s="55" t="inlineStr">
+        <is>
+          <t>7,610＋1,500</t>
+        </is>
+      </c>
+      <c r="K376" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="53" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C377" s="53" t="inlineStr">
+        <is>
+          <t>arikayama・otenshoudake</t>
+        </is>
+      </c>
+      <c r="D377" s="54" t="inlineStr">
+        <is>
+          <t>有明山・大天井岳</t>
+        </is>
+      </c>
+      <c r="E377" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F377" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G377" s="55" t="inlineStr">
+        <is>
+          <t>有明山 8,400／8,090／8,400円、大天井岳 9,900／9,590／9,900円（同じ中房温泉行きで1,500円差）</t>
+        </is>
+      </c>
+      <c r="H377" s="55" t="inlineStr">
+        <is>
+          <t>2山とも 8,670円（3出発地同額）</t>
+        </is>
+      </c>
+      <c r="I377" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→穂高 7,170円（3出発地同額）、中房温泉行き定期バス 1,500円</t>
+        </is>
+      </c>
+      <c r="J377" s="55" t="inlineStr">
+        <is>
+          <t>7,170＋1,500</t>
+        </is>
+      </c>
+      <c r="K377" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="53" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C378" s="53" t="inlineStr">
+        <is>
+          <t>azumayasan</t>
+        </is>
+      </c>
+      <c r="D378" s="54" t="inlineStr">
+        <is>
+          <t>四阿山</t>
+        </is>
+      </c>
+      <c r="E378" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F378" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G378" s="55" t="inlineStr">
+        <is>
+          <t>6,660／4,700／7,240円</t>
+        </is>
+      </c>
+      <c r="H378" s="55" t="inlineStr">
+        <is>
+          <t>6,760／5,990／7,300円（JR自由席＋バス600）。バス58分</t>
+        </is>
+      </c>
+      <c r="I378" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→上田 6,160／5,390／6,700、NAVITIME（バス600円・58分）</t>
+        </is>
+      </c>
+      <c r="J378" s="55" t="inlineStr">
+        <is>
+          <t>JR＋600</t>
+        </is>
+      </c>
+      <c r="K378" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="53" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C379" s="53" t="inlineStr">
+        <is>
+          <t>shirane_gunma</t>
+        </is>
+      </c>
+      <c r="D379" s="54" t="inlineStr">
+        <is>
+          <t>草津白根山</t>
+        </is>
+      </c>
+      <c r="E379" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路の検算</t>
+        </is>
+      </c>
+      <c r="F379" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G379" s="55" t="inlineStr">
+        <is>
+          <t>6,410／4,860／6,710円。新宿・横浜は東京駅経由</t>
+        </is>
+      </c>
+      <c r="H379" s="55" t="inlineStr">
+        <is>
+          <t>5,840／5,400／7,140円（JR自由席＋バス780）。新宿は大宮で新幹線に乗換</t>
+        </is>
+      </c>
+      <c r="I379" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→長野原草津口 5,060／4,620／6,360、NAVITIME（バス780円・25分）</t>
+        </is>
+      </c>
+      <c r="J379" s="55" t="inlineStr">
+        <is>
+          <t>JR＋780</t>
+        </is>
+      </c>
+      <c r="K379" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="53" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C380" s="53" t="inlineStr">
+        <is>
+          <t>bandai</t>
+        </is>
+      </c>
+      <c r="D380" s="54" t="inlineStr">
+        <is>
+          <t>磐梯山</t>
+        </is>
+      </c>
+      <c r="E380" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路の検算</t>
+        </is>
+      </c>
+      <c r="F380" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G380" s="55" t="inlineStr">
+        <is>
+          <t>7,900／6,160／8,400円。新宿は東京駅経由</t>
+        </is>
+      </c>
+      <c r="H380" s="55" t="inlineStr">
+        <is>
+          <t>7,700／6,820／9,130円（猪苗代駅まで。タクシー代は別）。新宿は大宮で新幹線に乗換</t>
+        </is>
+      </c>
+      <c r="I380" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→猪苗代 7,700／6,820／9,130</t>
+        </is>
+      </c>
+      <c r="J380" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K380" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="53" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C381" s="53" t="inlineStr">
+        <is>
+          <t>iizunasan</t>
+        </is>
+      </c>
+      <c r="D381" s="54" t="inlineStr">
+        <is>
+          <t>飯縄山</t>
+        </is>
+      </c>
+      <c r="E381" s="54" t="inlineStr">
+        <is>
+          <t>バスの所要時間</t>
+        </is>
+      </c>
+      <c r="F381" s="54" t="inlineStr">
+        <is>
+          <t>長野駅〜飯綱登山口</t>
+        </is>
+      </c>
+      <c r="G381" s="55" t="inlineStr">
+        <is>
+          <t>バス30分</t>
+        </is>
+      </c>
+      <c r="H381" s="55" t="inlineStr">
+        <is>
+          <t>約47分（全出発地で＋17分）。運賃合計は未検算のまま（バス運賃が未確認）</t>
+        </is>
+      </c>
+      <c r="I381" s="56" t="inlineStr">
+        <is>
+          <t>NAVITIME 70：戸隠線（07:00発→07:47着）</t>
+        </is>
+      </c>
+      <c r="J381" s="55" t="inlineStr">
+        <is>
+          <t>legs合計と一致</t>
+        </is>
+      </c>
+      <c r="K381" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -6621,7 +6621,7 @@
         <v>146</v>
       </c>
       <c r="H5" s="41" t="n">
-        <v>1670</v>
+        <v>1990</v>
       </c>
       <c r="I5" s="44" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>183</v>
       </c>
       <c r="K5" s="41" t="n">
-        <v>1850</v>
+        <v>2170</v>
       </c>
       <c r="L5" s="44" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>152</v>
       </c>
       <c r="N5" s="41" t="n">
-        <v>2040</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="6" ht="26.25" customHeight="1" s="30">
@@ -6788,36 +6788,36 @@
       </c>
       <c r="F8" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線特急ちちぶ]--&gt; 西武秩父駅 --[小鹿野町営バス（薬師の湯乗継）]--&gt; 日向大谷口（通年）</t>
+          <t>新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線特急ちちぶ]--&gt; 西武秩父駅 --[小鹿野町営バス（薬師の湯乗継）]--&gt; 日向大谷口</t>
         </is>
       </c>
       <c r="G8" s="41" t="n">
         <v>149</v>
       </c>
       <c r="H8" s="41" t="n">
-        <v>2300</v>
+        <v>1899</v>
       </c>
       <c r="I8" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR川越線・八高線・西武池袋線各停]--&gt; 西武秩父駅 --[小鹿野町営バス（薬師の湯乗継）]--&gt; 日向大谷口（バスは1日7本程度、本数少なめ）</t>
+          <t>大宮駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線特急ちちぶ]--&gt; 西武秩父駅 --[小鹿野町営バス（薬師の湯乗継）]--&gt; 日向大谷口</t>
         </is>
       </c>
       <c r="J8" s="41" t="n">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="K8" s="41" t="n">
-        <v>1610</v>
+        <v>2140</v>
       </c>
       <c r="L8" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線特急ちちぶ]--&gt; 西武秩父駅 --[小鹿野町営バス（薬師の湯乗継）]--&gt; 日向大谷口（通年）</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線特急ちちぶ]--&gt; 西武秩父駅 --[小鹿野町営バス（薬師の湯乗継）]--&gt; 日向大谷口</t>
         </is>
       </c>
       <c r="M8" s="41" t="n">
         <v>197</v>
       </c>
       <c r="N8" s="41" t="n">
-        <v>2916</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="9" ht="39" customHeight="1" s="30">
@@ -6850,32 +6850,32 @@
         </is>
       </c>
       <c r="G9" s="41" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="H9" s="41" t="n">
-        <v>5650</v>
+        <v>6640</v>
       </c>
       <c r="I9" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 小淵沢駅 --[JR小海線]--&gt; 信濃川上駅 --[川上村営バス「川端下行」]--&gt; 梓山 --[徒歩]--&gt; 毛木平（登山口）</t>
+          <t>大宮駅 --[北陸新幹線あさま]--&gt; 佐久平駅 --[JR小海線]--&gt; 信濃川上駅 --[川上村営バス「川端下行」]--&gt; 梓山 --[徒歩]--&gt; 毛木平（登山口）</t>
         </is>
       </c>
       <c r="J9" s="41" t="n">
-        <v>280</v>
+        <v>225</v>
       </c>
       <c r="K9" s="41" t="n">
-        <v>6310</v>
+        <v>6380</v>
       </c>
       <c r="L9" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 小淵沢駅 --[JR小海線]--&gt; 信濃川上駅 --[川上村営バス「川端下行」]--&gt; 梓山 --[徒歩]--&gt; 毛木平（登山口）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 小淵沢駅 --[JR小海線]--&gt; 信濃川上駅 --[川上村営バス「川端下行」]--&gt; 梓山 --[徒歩]--&gt; 毛木平（登山口）</t>
         </is>
       </c>
       <c r="M9" s="41" t="n">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="N9" s="41" t="n">
-        <v>6310</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="10" ht="39" customHeight="1" s="30">
@@ -7096,18 +7096,18 @@
         <v>205</v>
       </c>
       <c r="K13" s="41" t="n">
-        <v>6160</v>
+        <v>5760</v>
       </c>
       <c r="L13" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急かいじ]--&gt; 甲府駅 --[山梨交通「広河原線」]--&gt; 夜叉神峠登山口</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[山梨交通「広河原線」]--&gt; 夜叉神峠登山口</t>
         </is>
       </c>
       <c r="M13" s="41" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="N13" s="41" t="n">
-        <v>6260</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="14" ht="39" customHeight="1" s="30">
@@ -7143,7 +7143,7 @@
         <v>170</v>
       </c>
       <c r="H14" s="41" t="n">
-        <v>5290</v>
+        <v>5540</v>
       </c>
       <c r="I14" s="44" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>140</v>
       </c>
       <c r="K14" s="41" t="n">
-        <v>4780</v>
+        <v>5030</v>
       </c>
       <c r="L14" s="44" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>204</v>
       </c>
       <c r="N14" s="41" t="n">
-        <v>5870</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="15" ht="39" customHeight="1" s="30">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="F21" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[東北新幹線なすの]--&gt; 那須塩原駅 --[関東自動車バス]--&gt; 那須ロープウェイ --[徒歩]--&gt; 峠の茶屋（季節運行）</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[東北新幹線なすの]--&gt; 那須塩原駅 --[関東自動車バス]--&gt; 那須ロープウェイ --[徒歩]--&gt; 峠の茶屋登山口</t>
         </is>
       </c>
       <c r="G21" s="41" t="n">
@@ -7560,11 +7560,11 @@
         <v>137</v>
       </c>
       <c r="K21" s="41" t="n">
-        <v>6590</v>
+        <v>6700</v>
       </c>
       <c r="L21" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[東北新幹線なすの]--&gt; 那須塩原駅 --[関東自動車バス]--&gt; 那須ロープウェイ --[徒歩]--&gt; 峠の茶屋入口</t>
+          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[東北新幹線なすの]--&gt; 那須塩原駅 --[関東自動車バス]--&gt; 那須ロープウェイ --[徒歩]--&gt; 峠の茶屋登山口</t>
         </is>
       </c>
       <c r="M21" s="41" t="n">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="F28" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線（東京駅乗換）]--&gt; 富山駅 --[富山地方鉄道]--&gt; 立山駅 --[ケーブルカー・高原バス]--&gt; 室堂（季節運行）</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地方鉄道]--&gt; 立山駅 --[ケーブルカー・高原バス]--&gt; 室堂（季節運行）</t>
         </is>
       </c>
       <c r="G28" s="41" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H28" s="41" t="n">
-        <v>18470</v>
+        <v>18920</v>
       </c>
       <c r="I28" s="44" t="inlineStr">
         <is>
@@ -7939,21 +7939,21 @@
         </is>
       </c>
       <c r="J28" s="41" t="n">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="K28" s="41" t="n">
-        <v>18260</v>
+        <v>18590</v>
       </c>
       <c r="L28" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地方鉄道]--&gt; 立山駅 --[ケーブルカー・高原バス]--&gt; 室堂（季節運行）</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地方鉄道]--&gt; 立山駅 --[ケーブルカー・高原バス]--&gt; 室堂（季節運行）</t>
         </is>
       </c>
       <c r="M28" s="41" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N28" s="41" t="n">
-        <v>18700</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="29" ht="39" customHeight="1" s="30">
@@ -7982,14 +7982,14 @@
       </c>
       <c r="F29" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線（東京駅乗換）]--&gt; 富山駅 --[富山地方鉄道]--&gt; 立山駅 --[ケーブルカー・高原バス]--&gt; 室堂（季節運行）</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地方鉄道]--&gt; 立山駅 --[ケーブルカー・高原バス]--&gt; 室堂（季節運行）</t>
         </is>
       </c>
       <c r="G29" s="41" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="H29" s="41" t="n">
-        <v>18000</v>
+        <v>18920</v>
       </c>
       <c r="I29" s="44" t="inlineStr">
         <is>
@@ -7997,21 +7997,21 @@
         </is>
       </c>
       <c r="J29" s="41" t="n">
-        <v>269</v>
+        <v>235</v>
       </c>
       <c r="K29" s="41" t="n">
-        <v>17950</v>
+        <v>18590</v>
       </c>
       <c r="L29" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地方鉄道]--&gt; 立山駅 --[ケーブルカー・高原バス]--&gt; 室堂（季節運行）</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地方鉄道]--&gt; 立山駅 --[ケーブルカー・高原バス]--&gt; 室堂（季節運行）</t>
         </is>
       </c>
       <c r="M29" s="41" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N29" s="41" t="n">
-        <v>18940</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="30" ht="39" customHeight="1" s="30">
@@ -8156,36 +8156,36 @@
       </c>
       <c r="F32" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線はくたか（東京駅乗換）]--&gt; 上越妙高駅 --[えちごトキめき鉄道]--&gt; 妙高高原駅 --[頸南バス]--&gt; 燕温泉</t>
+          <t>新宿駅 --[JR埼京線・湘南新宿ライン]--&gt; 大宮駅 --[北陸新幹線はくたか]--&gt; 上越妙高駅 --[えちごトキめき鉄道 妙高はねうまライン]--&gt; 関山駅 --[妙高市営バス「関・燕温泉線」]--&gt; 燕温泉</t>
         </is>
       </c>
       <c r="G32" s="41" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H32" s="41" t="n">
-        <v>9100</v>
+        <v>9570</v>
       </c>
       <c r="I32" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線はくたか]--&gt; 上越妙高駅 --[えちごトキめき鉄道]--&gt; 妙高高原駅 --[頸南バス]--&gt; 燕温泉</t>
+          <t>大宮駅 --[北陸新幹線はくたか]--&gt; 上越妙高駅 --[えちごトキめき鉄道 妙高はねうまライン]--&gt; 関山駅 --[妙高市営バス「関・燕温泉線」]--&gt; 燕温泉</t>
         </is>
       </c>
       <c r="J32" s="41" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="K32" s="41" t="n">
-        <v>8830</v>
+        <v>8800</v>
       </c>
       <c r="L32" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線はくたか]--&gt; 上越妙高駅 --[えちごトキめき鉄道]--&gt; 妙高高原駅 --[頸南バス]--&gt; 燕温泉</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[北陸新幹線はくたか]--&gt; 上越妙高駅 --[えちごトキめき鉄道 妙高はねうまライン]--&gt; 関山駅 --[妙高市営バス「関・燕温泉線」]--&gt; 燕温泉</t>
         </is>
       </c>
       <c r="M32" s="41" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="N32" s="41" t="n">
-        <v>9330</v>
+        <v>10110</v>
       </c>
     </row>
     <row r="33" ht="39" customHeight="1" s="30">
@@ -8700,14 +8700,14 @@
       </c>
       <c r="L41" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 伊勢原駅 --[バス]--&gt; 大山ケーブル駅</t>
+          <t>横浜駅 --[相鉄本線特急]--&gt; 海老名駅 --[小田急小田原線]--&gt; 伊勢原駅 --[バス]--&gt; 大山ケーブル駅</t>
         </is>
       </c>
       <c r="M41" s="41" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="N41" s="41" t="n">
-        <v>1023</v>
+        <v>924</v>
       </c>
     </row>
     <row r="42" ht="26.25" customHeight="1" s="30">
@@ -9146,21 +9146,21 @@
         </is>
       </c>
       <c r="G49" s="41" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H49" s="41" t="n">
-        <v>1143</v>
+        <v>1446</v>
       </c>
       <c r="I49" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線特急ちちぶ]--&gt; 飯能駅 --[バス]--&gt; 河又名栗湖入口</t>
+          <t>大宮駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線]--&gt; 飯能駅 --[国際興業バス]--&gt; 河又名栗湖入口</t>
         </is>
       </c>
       <c r="J49" s="41" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="K49" s="41" t="n">
-        <v>2050</v>
+        <v>1687</v>
       </c>
       <c r="L49" s="44" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         </is>
       </c>
       <c r="M49" s="41" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N49" s="41" t="n">
-        <v>1759</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="50" ht="26.25" customHeight="1" s="30">
@@ -9964,36 +9964,36 @@
       </c>
       <c r="F64" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線・湘南新宿ライン]--&gt; 大宮駅 --[JR上越新幹線(とき)]--&gt; 浦佐駅 --[南越後観光バス急行(浦佐駅－奥只見ダム線)]--&gt; 銀山平(舟付場)</t>
+          <t>新宿駅 --[JR埼京線・湘南新宿ライン]--&gt; 大宮駅 --[JR上越新幹線(とき)]--&gt; 浦佐駅 --[南越後交通バス急行(浦佐駅－奥只見ダム線)]--&gt; 銀山平(舟付場)</t>
         </is>
       </c>
       <c r="G64" s="41" t="n">
         <v>140</v>
       </c>
       <c r="H64" s="41" t="n">
-        <v>8320</v>
+        <v>8020</v>
       </c>
       <c r="I64" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR上越新幹線(とき)]--&gt; 浦佐駅 --[南越後観光バス急行(浦佐駅－奥只見ダム線)]--&gt; 銀山平(舟付場)</t>
+          <t>大宮駅 --[JR上越新幹線(とき)]--&gt; 浦佐駅 --[南越後交通バス急行(浦佐駅－奥只見ダム線)]--&gt; 銀山平(舟付場)</t>
         </is>
       </c>
       <c r="J64" s="41" t="n">
         <v>110</v>
       </c>
       <c r="K64" s="41" t="n">
-        <v>7660</v>
+        <v>7360</v>
       </c>
       <c r="L64" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[JR上越新幹線(とき)]--&gt; 浦佐駅 --[南越後観光バス急行(浦佐駅－奥只見ダム線)]--&gt; 銀山平(舟付場)</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[JR上越新幹線(とき)]--&gt; 浦佐駅 --[南越後交通バス急行(浦佐駅－奥只見ダム線)]--&gt; 銀山平(舟付場)</t>
         </is>
       </c>
       <c r="M64" s="41" t="n">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="N64" s="41" t="n">
-        <v>9300</v>
+        <v>9560</v>
       </c>
     </row>
     <row r="65" ht="26.25" customHeight="1" s="30">
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="G70" s="41" t="n">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="H70" s="41" t="n">
         <v>8060</v>
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="J70" s="41" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K70" s="41" t="n">
         <v>7290</v>
@@ -10314,7 +10314,7 @@
         </is>
       </c>
       <c r="M70" s="41" t="n">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="N70" s="41" t="n">
         <v>9600</v>
@@ -11492,14 +11492,14 @@
       </c>
       <c r="F92" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地鉄バス 夏山バス(有峰線)直通便]--&gt; 折立</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地鉄バス 夏山バス(有峰線)直通便]--&gt; 折立</t>
         </is>
       </c>
       <c r="G92" s="41" t="n">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="H92" s="41" t="n">
-        <v>17880</v>
+        <v>18970</v>
       </c>
       <c r="I92" s="44" t="inlineStr">
         <is>
@@ -11507,21 +11507,21 @@
         </is>
       </c>
       <c r="J92" s="41" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="K92" s="41" t="n">
-        <v>17140</v>
+        <v>18640</v>
       </c>
       <c r="L92" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地鉄バス 夏山バス(有峰線)直通便]--&gt; 折立</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地鉄バス 夏山バス(有峰線)直通便]--&gt; 折立</t>
         </is>
       </c>
       <c r="M92" s="41" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="N92" s="41" t="n">
-        <v>18160</v>
+        <v>19730</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="30">
@@ -11550,14 +11550,14 @@
       </c>
       <c r="F93" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地鉄バス 夏山バス(有峰線)直通便]--&gt; 折立</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地鉄バス 夏山バス(有峰線)直通便]--&gt; 折立</t>
         </is>
       </c>
       <c r="G93" s="41" t="n">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="H93" s="41" t="n">
-        <v>17880</v>
+        <v>18970</v>
       </c>
       <c r="I93" s="44" t="inlineStr">
         <is>
@@ -11565,21 +11565,21 @@
         </is>
       </c>
       <c r="J93" s="41" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="K93" s="41" t="n">
-        <v>17140</v>
+        <v>18640</v>
       </c>
       <c r="L93" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地鉄バス 夏山バス(有峰線)直通便]--&gt; 折立</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 富山駅 --[富山地鉄バス 夏山バス(有峰線)直通便]--&gt; 折立</t>
         </is>
       </c>
       <c r="M93" s="41" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="N93" s="41" t="n">
-        <v>18160</v>
+        <v>19730</v>
       </c>
     </row>
     <row r="94" ht="39" customHeight="1" s="30">
@@ -11724,36 +11724,36 @@
       </c>
       <c r="F96" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 金沢駅 --[JR北陸本線]--&gt; 松任駅 --[白山登山バス(松任便)]--&gt; 市ノ瀬 --[白山市営 定期シャトルバス]--&gt; 別当出合</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[北陸新幹線かがやき]--&gt; 金沢駅 --[北陸鉄道 白山登山バス]--&gt; 市ノ瀬 --[市ノ瀬〜別当出合シャトルバス]--&gt; 別当出合</t>
         </is>
       </c>
       <c r="G96" s="41" t="n">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="H96" s="41" t="n">
-        <v>18720</v>
+        <v>17250</v>
       </c>
       <c r="I96" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線かがやき]--&gt; 金沢駅 --[JR北陸本線]--&gt; 松任駅 --[白山登山バス(松任便)]--&gt; 市ノ瀬 --[白山市営 定期シャトルバス]--&gt; 別当出合</t>
+          <t>大宮駅 --[北陸新幹線かがやき]--&gt; 金沢駅 --[北陸鉄道 白山登山バス]--&gt; 市ノ瀬 --[市ノ瀬〜別当出合シャトルバス]--&gt; 別当出合</t>
         </is>
       </c>
       <c r="J96" s="41" t="n">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="K96" s="41" t="n">
-        <v>17980</v>
+        <v>16810</v>
       </c>
       <c r="L96" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 金沢駅 --[JR北陸本線]--&gt; 松任駅 --[白山登山バス(松任便)]--&gt; 市ノ瀬 --[白山市営 定期シャトルバス]--&gt; 別当出合</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[北陸新幹線かがやき]--&gt; 金沢駅 --[北陸鉄道 白山登山バス]--&gt; 市ノ瀬 --[市ノ瀬〜別当出合シャトルバス]--&gt; 別当出合</t>
         </is>
       </c>
       <c r="M96" s="41" t="n">
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="N96" s="41" t="n">
-        <v>19000</v>
+        <v>17680</v>
       </c>
     </row>
     <row r="97" ht="39" customHeight="1" s="30">
@@ -11782,36 +11782,36 @@
       </c>
       <c r="F97" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[JR山形新幹線つばさ（東京駅乗換）]--&gt; 山形駅 --[山交バス蔵王温泉行き]--&gt; 蔵王温泉バスターミナル</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[山形新幹線つばさ]--&gt; 山形駅 --[山交バス蔵王温泉行き]--&gt; 蔵王温泉バスターミナル</t>
         </is>
       </c>
       <c r="G97" s="41" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H97" s="41" t="n">
-        <v>13070</v>
+        <v>12660</v>
       </c>
       <c r="I97" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[山形新幹線つばさ]--&gt; 山形駅 --[山交バス]--&gt; 蔵王温泉</t>
+          <t>大宮駅 --[山形新幹線つばさ]--&gt; 山形駅 --[山交バス蔵王温泉行き]--&gt; 蔵王温泉バスターミナル</t>
         </is>
       </c>
       <c r="J97" s="41" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="K97" s="41" t="n">
-        <v>12530</v>
+        <v>12330</v>
       </c>
       <c r="L97" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[JR山形新幹線つばさ]--&gt; 山形駅 --[山交バス]--&gt; 蔵王温泉バスターミナル</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[山形新幹線つばさ]--&gt; 山形駅 --[山交バス蔵王温泉行き]--&gt; 蔵王温泉バスターミナル</t>
         </is>
       </c>
       <c r="M97" s="41" t="n">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="N97" s="41" t="n">
-        <v>13320</v>
+        <v>13530</v>
       </c>
     </row>
     <row r="98" ht="39" customHeight="1" s="30">
@@ -12014,36 +12014,36 @@
       </c>
       <c r="F101" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス（予約優先制）]--&gt; 上高地バスターミナル</t>
         </is>
       </c>
       <c r="G101" s="41" t="n">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H101" s="41" t="n">
-        <v>9190</v>
+        <v>10540</v>
       </c>
       <c r="I101" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス（予約優先制）]--&gt; 上高地バスターミナル</t>
         </is>
       </c>
       <c r="J101" s="41" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K101" s="41" t="n">
-        <v>8880</v>
+        <v>10230</v>
       </c>
       <c r="L101" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 上高地バスターミナル（季節）</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコ交通バス（予約優先制）]--&gt; 上高地バスターミナル</t>
         </is>
       </c>
       <c r="M101" s="41" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="N101" s="41" t="n">
-        <v>9190</v>
+        <v>10230</v>
       </c>
     </row>
     <row r="102" ht="51.75" customHeight="1" s="30">
@@ -12482,21 +12482,21 @@
         </is>
       </c>
       <c r="G109" s="41" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H109" s="41" t="n">
-        <v>690</v>
+        <v>756</v>
       </c>
       <c r="I109" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線特急ちちぶ]--&gt; 飯能駅 --[徒歩]--&gt; 天覧山登山口</t>
+          <t>大宮駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線]--&gt; 飯能駅 --[徒歩]--&gt; 天覧山登山口</t>
         </is>
       </c>
       <c r="J109" s="41" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K109" s="41" t="n">
-        <v>1597</v>
+        <v>997</v>
       </c>
       <c r="L109" s="44" t="inlineStr">
         <is>
@@ -12504,10 +12504,10 @@
         </is>
       </c>
       <c r="M109" s="41" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="N109" s="41" t="n">
-        <v>1306</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="110" ht="26.25" customHeight="1" s="30">
@@ -12652,36 +12652,36 @@
       </c>
       <c r="F112" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武秩父線特急ちちぶ]--&gt; 西武秩父駅 --[タクシー（バス路線なし）]--&gt; 一ノ鳥居登山口</t>
+          <t>新宿駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線特急ちちぶ]--&gt; 西武秩父駅 --[タクシー（バス路線なし）]--&gt; 一ノ鳥居登山口</t>
         </is>
       </c>
       <c r="G112" s="41" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="H112" s="41" t="n">
-        <v>3499</v>
+        <v>1899</v>
       </c>
       <c r="I112" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR川越線・八高線・西武池袋線各停、新宿・池袋いずれも経由しない短絡ルート)]--&gt; 西武秩父駅 --[タクシー（バス路線なし）]--&gt; 一ノ鳥居登山口</t>
+          <t>大宮駅 --[JR埼京線]--&gt; 池袋駅 --[西武池袋線特急ちちぶ]--&gt; 西武秩父駅 --[タクシー（バス路線なし）]--&gt; 一ノ鳥居登山口</t>
         </is>
       </c>
       <c r="J112" s="41" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="K112" s="41" t="n">
-        <v>3999</v>
+        <v>2140</v>
       </c>
       <c r="L112" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 池袋駅 --[西武秩父線特急ちちぶ]--&gt; 西武秩父駅 --[タクシー（バス路線なし）]--&gt; 一ノ鳥居登山口</t>
+          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 池袋駅 --[西武池袋線特急ちちぶ]--&gt; 西武秩父駅 --[タクシー（バス路線なし）]--&gt; 一ノ鳥居登山口</t>
         </is>
       </c>
       <c r="M112" s="41" t="n">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="N112" s="41" t="n">
-        <v>4115</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="113" ht="26.25" customHeight="1" s="30">
@@ -12902,7 +12902,7 @@
         <v>110</v>
       </c>
       <c r="K116" s="41" t="n">
-        <v>1523</v>
+        <v>1314</v>
       </c>
       <c r="L116" s="44" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>89</v>
       </c>
       <c r="N116" s="41" t="n">
-        <v>1188</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="117" ht="26.25" customHeight="1" s="30">
@@ -13018,7 +13018,7 @@
         <v>111</v>
       </c>
       <c r="K118" s="41" t="n">
-        <v>1523</v>
+        <v>1314</v>
       </c>
       <c r="L118" s="44" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>89</v>
       </c>
       <c r="N118" s="41" t="n">
-        <v>1188</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="119" ht="26.25" customHeight="1" s="30">
@@ -13297,29 +13297,29 @@
         <v>194</v>
       </c>
       <c r="H123" s="41" t="n">
-        <v>2180</v>
+        <v>2290</v>
       </c>
       <c r="I123" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR内房線]--&gt; 岩井駅 --[市営バス]--&gt; 天神郷バス停 --[徒歩]--&gt; 平群天神社</t>
+          <t>大宮駅 --[JR上野東京ライン・総武線快速・内房線（東京・木更津乗換）]--&gt; 岩井駅 --[市営バス]--&gt; 天神郷バス停 --[徒歩]--&gt; 平群天神社</t>
         </is>
       </c>
       <c r="J123" s="41" t="n">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="K123" s="41" t="n">
-        <v>2708</v>
+        <v>2950</v>
       </c>
       <c r="L123" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線・総武線・内房線(君津・木更津経由)]--&gt; 岩井駅 --[市営バス]--&gt; 天神郷バス停 --[徒歩]--&gt; 平群天神社</t>
+          <t>横浜駅 --[JR横須賀線・総武線快速直通・内房線（木更津乗換）]--&gt; 岩井駅 --[市営バス]--&gt; 天神郷バス停 --[徒歩]--&gt; 平群天神社</t>
         </is>
       </c>
       <c r="M123" s="41" t="n">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="N123" s="41" t="n">
-        <v>2620</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="124" ht="26.25" customHeight="1" s="30">
@@ -13714,7 +13714,7 @@
         <v>136</v>
       </c>
       <c r="K130" s="41" t="n">
-        <v>1362</v>
+        <v>1198</v>
       </c>
       <c r="L130" s="44" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>158</v>
       </c>
       <c r="N130" s="41" t="n">
-        <v>1573</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="131" ht="26.25" customHeight="1" s="30">
@@ -13928,25 +13928,25 @@
       </c>
       <c r="F134" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR東海道本線]--&gt; 湯河原駅 --[箱根登山バス]--&gt; 幕山公園</t>
+          <t>新宿駅 --[JR湘南新宿ライン・東海道本線]--&gt; 湯河原駅 --[箱根登山バス]--&gt; 幕山公園</t>
         </is>
       </c>
       <c r="G134" s="41" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H134" s="41" t="n">
-        <v>2420</v>
+        <v>2380</v>
       </c>
       <c r="I134" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR東海道本線]--&gt; 湯河原駅 --[箱根登山バス]--&gt; 幕山公園</t>
+          <t>大宮駅 --[JR上野東京ライン（直通）]--&gt; 湯河原駅 --[箱根登山バス]--&gt; 幕山公園</t>
         </is>
       </c>
       <c r="J134" s="41" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K134" s="41" t="n">
-        <v>2948</v>
+        <v>2710</v>
       </c>
       <c r="L134" s="44" t="inlineStr">
         <is>
@@ -13954,10 +13954,10 @@
         </is>
       </c>
       <c r="M134" s="41" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N134" s="41" t="n">
-        <v>1880</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="135" ht="26.25" customHeight="1" s="30">
@@ -14526,7 +14526,7 @@
         <v>121</v>
       </c>
       <c r="K144" s="41" t="n">
-        <v>1362</v>
+        <v>1198</v>
       </c>
       <c r="L144" s="44" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>143</v>
       </c>
       <c r="N144" s="41" t="n">
-        <v>1573</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="145" ht="39" customHeight="1" s="30">
@@ -14682,25 +14682,25 @@
       </c>
       <c r="F147" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR東海道本線]--&gt; 二宮駅 --[徒歩]--&gt; 吾妻山公園入口</t>
+          <t>新宿駅 --[JR湘南新宿ライン（東海道線直通）]--&gt; 二宮駅 --[徒歩]--&gt; 吾妻山公園入口</t>
         </is>
       </c>
       <c r="G147" s="41" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="H147" s="41" t="n">
-        <v>1030</v>
+        <v>1408</v>
       </c>
       <c r="I147" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR東海道本線]--&gt; 二宮駅 --[徒歩]--&gt; 吾妻山公園入口</t>
+          <t>大宮駅 --[JR上野東京ライン（東海道線直通）]--&gt; 二宮駅 --[徒歩]--&gt; 吾妻山公園入口</t>
         </is>
       </c>
       <c r="J147" s="41" t="n">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="K147" s="41" t="n">
-        <v>1558</v>
+        <v>2090</v>
       </c>
       <c r="L147" s="44" t="inlineStr">
         <is>
@@ -14708,10 +14708,10 @@
         </is>
       </c>
       <c r="M147" s="41" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N147" s="41" t="n">
-        <v>810</v>
+        <v>803</v>
       </c>
     </row>
     <row r="148" ht="51.75" customHeight="1" s="30">
@@ -15030,25 +15030,25 @@
       </c>
       <c r="F153" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR横須賀線]--&gt; 北鎌倉駅 --[徒歩]--&gt; 天園ハイキングコース入口</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 北鎌倉駅 --[徒歩]--&gt; 天園ハイキングコース入口</t>
         </is>
       </c>
       <c r="G153" s="41" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H153" s="41" t="n">
-        <v>945</v>
+        <v>1034</v>
       </c>
       <c r="I153" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR横須賀線]--&gt; 北鎌倉駅 --[徒歩]--&gt; 天園ハイキングコース入口</t>
+          <t>大宮駅 --[JR湘南新宿ライン（直通）]--&gt; 北鎌倉駅 --[徒歩]--&gt; 天園ハイキングコース入口</t>
         </is>
       </c>
       <c r="J153" s="41" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K153" s="41" t="n">
-        <v>1473</v>
+        <v>1408</v>
       </c>
       <c r="L153" s="44" t="inlineStr">
         <is>
@@ -15056,10 +15056,10 @@
         </is>
       </c>
       <c r="M153" s="41" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N153" s="41" t="n">
-        <v>350</v>
+        <v>341</v>
       </c>
     </row>
     <row r="154" ht="39" customHeight="1" s="30">
@@ -15088,25 +15088,25 @@
       </c>
       <c r="F154" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR横須賀線]--&gt; 逗子駅 --[京浜急行バス]--&gt; 前田橋バス停 --[徒歩]--&gt; 大楠山登山口</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 逗子駅 --[京浜急行バス]--&gt; 前田橋バス停 --[徒歩]--&gt; 大楠山登山口</t>
         </is>
       </c>
       <c r="G154" s="41" t="n">
         <v>118</v>
       </c>
       <c r="H154" s="41" t="n">
-        <v>1395</v>
+        <v>1411</v>
       </c>
       <c r="I154" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR横須賀線]--&gt; 逗子駅 --[京浜急行バス]--&gt; 前田橋バス停 --[徒歩]--&gt; 大楠山登山口</t>
+          <t>大宮駅 --[JR湘南新宿ライン（直通）]--&gt; 逗子駅 --[京浜急行バス]--&gt; 前田橋バス停 --[徒歩]--&gt; 大楠山登山口</t>
         </is>
       </c>
       <c r="J154" s="41" t="n">
         <v>148</v>
       </c>
       <c r="K154" s="41" t="n">
-        <v>1923</v>
+        <v>1972</v>
       </c>
       <c r="L154" s="44" t="inlineStr">
         <is>
@@ -15114,10 +15114,10 @@
         </is>
       </c>
       <c r="M154" s="41" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N154" s="41" t="n">
-        <v>890</v>
+        <v>817</v>
       </c>
     </row>
     <row r="155" ht="39" customHeight="1" s="30">
@@ -16670,12 +16670,12 @@
       </c>
       <c r="E24" s="44" t="inlineStr">
         <is>
-          <t>えちごトキめき鉄道・妙高市営バス「関・燕温泉線」</t>
+          <t>妙高市営バス「関・燕温泉線」（関山駅〜燕温泉。運行は妙高ハブネットに委託）</t>
         </is>
       </c>
       <c r="F24" s="47" t="inlineStr">
         <is>
-          <t>http://www.keinanbus.com/</t>
+          <t>https://www.city.myoko.niigata.jp/docs/892.html</t>
         </is>
       </c>
       <c r="G24" s="47" t="inlineStr">
@@ -16700,12 +16700,12 @@
       </c>
       <c r="K24" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L24" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>起点駅を妙高高原駅→関山駅、事業者を頸南バス→妙高市営バスに訂正</t>
         </is>
       </c>
     </row>
@@ -23811,13 +23811,12 @@
       </c>
       <c r="E143" s="44" t="inlineStr">
         <is>
-          <t>白山市営 定期シャトルバス
-白山登山バス(松任便)</t>
+          <t>北陸鉄道 白山登山バス（金沢駅西口〜市ノ瀬）＋市ノ瀬〜別当出合シャトルバス</t>
         </is>
       </c>
       <c r="F143" s="49" t="inlineStr">
         <is>
-          <t>https://map.ishikawa.jp/hakusan-bus-2025/</t>
+          <t>https://www.hokutetsu.co.jp/news/news-11388/</t>
         </is>
       </c>
       <c r="G143" s="47" t="inlineStr">
@@ -23842,12 +23841,12 @@
       </c>
       <c r="K143" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L143" s="44" t="inlineStr">
         <is>
-          <t>グループ9でtrainAccess=falseから新規構築。会社名・リンク確認済み（季節運行バス多数、要現地最新確認）</t>
+          <t>松任便の表記を金沢駅西口発に変更。シャトルバスの運賃は未確認</t>
         </is>
       </c>
     </row>
@@ -24235,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K381"/>
+  <dimension ref="A1:K416"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -45203,6 +45202,1931 @@
       <c r="K381" s="57" t="inlineStr">
         <is>
           <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="53" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C382" s="53" t="inlineStr">
+        <is>
+          <t>chogatake</t>
+        </is>
+      </c>
+      <c r="D382" s="54" t="inlineStr">
+        <is>
+          <t>蝶ヶ岳</t>
+        </is>
+      </c>
+      <c r="E382" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F382" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G382" s="55" t="inlineStr">
+        <is>
+          <t>9,190／8,880／9,190円（同じ上高地行きの槍ヶ岳は10,540／10,230／10,230円）</t>
+        </is>
+      </c>
+      <c r="H382" s="55" t="inlineStr">
+        <is>
+          <t>10,540／10,230／10,230円。経路・注記も検証済みの上高地アクセスに統一</t>
+        </is>
+      </c>
+      <c r="I382" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→新島々 7,440／7,130／7,130、アルピコ交通 新島々〜上高地 3,100円</t>
+        </is>
+      </c>
+      <c r="J382" s="55" t="inlineStr">
+        <is>
+          <t>JR・上高地線＋3,100</t>
+        </is>
+      </c>
+      <c r="K382" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="53" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C383" s="53" t="inlineStr">
+        <is>
+          <t>keirisan・kirigamine・nokogiriyama・akagi・juunigadake</t>
+        </is>
+      </c>
+      <c r="D383" s="54" t="inlineStr">
+        <is>
+          <t>蓼科山・霧ヶ峰・鋸岳・赤城山・十二ヶ岳</t>
+        </is>
+      </c>
+      <c r="E383" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F383" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G383" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H383" s="55" t="inlineStr">
+        <is>
+          <t>検算の結果、現行の額で整合（茅野まで5,760／5,760／5,100円、前橋まで3,960／1,600〜3,470／2,750〜5,260円、河口湖まで2,569／2,756／2,756円）</t>
+        </is>
+      </c>
+      <c r="I383" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（2026-10-17）</t>
+        </is>
+      </c>
+      <c r="J383" s="55" t="inlineStr">
+        <is>
+          <t>JR＋注記のバス運賃</t>
+        </is>
+      </c>
+      <c r="K383" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="53" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C384" s="53" t="inlineStr">
+        <is>
+          <t>yakushidake・kurobegorodam</t>
+        </is>
+      </c>
+      <c r="D384" s="54" t="inlineStr">
+        <is>
+          <t>薬師岳・黒部五郎岳</t>
+        </is>
+      </c>
+      <c r="E384" s="54" t="inlineStr">
+        <is>
+          <t>運賃・バスの検算</t>
+        </is>
+      </c>
+      <c r="F384" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G384" s="55" t="inlineStr">
+        <is>
+          <t>17,880／17,140／18,160円。バス120分、運行期間 7/15〜8/27毎日・9/2〜9/24土日祝</t>
+        </is>
+      </c>
+      <c r="H384" s="55" t="inlineStr">
+        <is>
+          <t>18,970／18,640／19,730円（JR＋バス6,000）。バス100分。運行期間は 7/11〜8/23毎日・8/29〜9/27土日祝。朝便は6:10発のため前泊が必要と注記</t>
+        </is>
+      </c>
+      <c r="I384" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→富山 12,970／12,640／13,730、高速バスドットコム（夏山バス有峰線）</t>
+        </is>
+      </c>
+      <c r="J384" s="55" t="inlineStr">
+        <is>
+          <t>JR＋6,000</t>
+        </is>
+      </c>
+      <c r="K384" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="53" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C385" s="53" t="inlineStr">
+        <is>
+          <t>tateyama・tsurugi</t>
+        </is>
+      </c>
+      <c r="D385" s="54" t="inlineStr">
+        <is>
+          <t>立山・剱岳</t>
+        </is>
+      </c>
+      <c r="E385" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F385" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G385" s="55" t="inlineStr">
+        <is>
+          <t>立山 18,470／18,260／18,700円、剱岳 18,000／17,950／18,940円（同じ室堂行きで不一致）</t>
+        </is>
+      </c>
+      <c r="H385" s="55" t="inlineStr">
+        <is>
+          <t>2山とも 18,920／18,590／19,680円（JR＋地鉄1,280＋立山駅〜室堂4,670）</t>
+        </is>
+      </c>
+      <c r="I385" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報、アルペンルートの運賃</t>
+        </is>
+      </c>
+      <c r="J385" s="55" t="inlineStr">
+        <is>
+          <t>JR＋1,280＋4,670</t>
+        </is>
+      </c>
+      <c r="K385" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="53" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C386" s="53" t="inlineStr">
+        <is>
+          <t>zaosan</t>
+        </is>
+      </c>
+      <c r="D386" s="54" t="inlineStr">
+        <is>
+          <t>蔵王山</t>
+        </is>
+      </c>
+      <c r="E386" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路の検算</t>
+        </is>
+      </c>
+      <c r="F386" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G386" s="55" t="inlineStr">
+        <is>
+          <t>13,070／12,530／13,320円</t>
+        </is>
+      </c>
+      <c r="H386" s="55" t="inlineStr">
+        <is>
+          <t>12,660／12,330／13,530円（JR＋バス1,200）。新宿は大宮で新幹線に乗換</t>
+        </is>
+      </c>
+      <c r="I386" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→山形 11,460／11,130／12,330、NAVITIME（バス1,200円・37分）</t>
+        </is>
+      </c>
+      <c r="J386" s="55" t="inlineStr">
+        <is>
+          <t>JR＋1,200</t>
+        </is>
+      </c>
+      <c r="K386" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="53" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C387" s="53" t="inlineStr">
+        <is>
+          <t>nasu</t>
+        </is>
+      </c>
+      <c r="D387" s="54" t="inlineStr">
+        <is>
+          <t>那須岳</t>
+        </is>
+      </c>
+      <c r="E387" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F387" s="54" t="inlineStr">
+        <is>
+          <t>大宮発</t>
+        </is>
+      </c>
+      <c r="G387" s="55" t="inlineStr">
+        <is>
+          <t>大宮 6,590円</t>
+        </is>
+      </c>
+      <c r="H387" s="55" t="inlineStr">
+        <is>
+          <t>大宮 6,700円（新宿7,030円・横浜8,010円は変更なし）。終点の表記を「峠の茶屋登山口」に統一</t>
+        </is>
+      </c>
+      <c r="I387" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→那須塩原 5,390／5,060／6,370＋バス1,640</t>
+        </is>
+      </c>
+      <c r="J387" s="55" t="inlineStr">
+        <is>
+          <t>JR＋1,640</t>
+        </is>
+      </c>
+      <c r="K387" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="53" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C388" s="53" t="inlineStr">
+        <is>
+          <t>hakusan</t>
+        </is>
+      </c>
+      <c r="D388" s="54" t="inlineStr">
+        <is>
+          <t>白山</t>
+        </is>
+      </c>
+      <c r="E388" s="54" t="inlineStr">
+        <is>
+          <t>経路・運賃の検算</t>
+        </is>
+      </c>
+      <c r="F388" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G388" s="55" t="inlineStr">
+        <is>
+          <t>18,720／17,980／19,000円。松任駅から白山登山バス(松任便)75分</t>
+        </is>
+      </c>
+      <c r="H388" s="55" t="inlineStr">
+        <is>
+          <t>17,250／16,810／17,680円（JR＋白山登山バス2,860。市ノ瀬まで、シャトル代は別）。金沢駅西口発・約2時間15分に変更。朝6時台発のため前泊が必要と注記</t>
+        </is>
+      </c>
+      <c r="I388" s="56" t="inlineStr">
+        <is>
+          <t>北陸鉄道（2026年 白山登山バス 7/4〜10/13）、Yahoo!路線情報：→金沢 14,390／13,950／14,820</t>
+        </is>
+      </c>
+      <c r="J388" s="55" t="inlineStr">
+        <is>
+          <t>JR＋2,860</t>
+        </is>
+      </c>
+      <c r="K388" s="57" t="inlineStr">
+        <is>
+          <t>高（シャトルバス代は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="53" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C389" s="53" t="inlineStr">
+        <is>
+          <t>hijiridade・arakawadake・akaisidake</t>
+        </is>
+      </c>
+      <c r="D389" s="54" t="inlineStr">
+        <is>
+          <t>聖岳・荒川岳・赤石岳</t>
+        </is>
+      </c>
+      <c r="E389" s="54" t="inlineStr">
+        <is>
+          <t>送迎バスの期間を再確認</t>
+        </is>
+      </c>
+      <c r="F389" s="54" t="inlineStr">
+        <is>
+          <t>畑薙〜椹島</t>
+        </is>
+      </c>
+      <c r="G389" s="55" t="inlineStr">
+        <is>
+          <t>2026年は7/11〜10/12（文中の日付から登録）</t>
+        </is>
+      </c>
+      <c r="H389" s="55" t="inlineStr">
+        <is>
+          <t>出典で再確認（7/11〜10/12、約1時間10分）。聖岳登山口の乗降は7・8月だけと注記。静鉄バスの期間と運賃合計は未確認として記録</t>
+        </is>
+      </c>
+      <c r="I389" s="56" t="inlineStr">
+        <is>
+          <t>特種東海フォレスト（2026-04-30更新）</t>
+        </is>
+      </c>
+      <c r="J389" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K389" s="57" t="inlineStr">
+        <is>
+          <t>高（静鉄バスは未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="53" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C390" s="53" t="inlineStr">
+        <is>
+          <t>aizu_koma</t>
+        </is>
+      </c>
+      <c r="D390" s="54" t="inlineStr">
+        <is>
+          <t>会津駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E390" s="54" t="inlineStr">
+        <is>
+          <t>運行期間を再確認・運賃は未検算</t>
+        </is>
+      </c>
+      <c r="F390" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G390" s="55" t="inlineStr">
+        <is>
+          <t>8,750／9,360／9,950円</t>
+        </is>
+      </c>
+      <c r="H390" s="55" t="inlineStr">
+        <is>
+          <t>運行期間 5/1〜10/31 は2026年の時刻表で確認。運賃は鉄道分（5,320／4,770／5,690円）まで確認、バス運賃が未確定のため合計は据え置き</t>
+        </is>
+      </c>
+      <c r="I390" s="56" t="inlineStr">
+        <is>
+          <t>2026年 会津鉄道・会津バス時刻表、Yahoo!路線情報</t>
+        </is>
+      </c>
+      <c r="J390" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K390" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="53" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C391" s="53" t="inlineStr">
+        <is>
+          <t>arasawadake</t>
+        </is>
+      </c>
+      <c r="D391" s="54" t="inlineStr">
+        <is>
+          <t>荒沢岳</t>
+        </is>
+      </c>
+      <c r="E391" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路の検算</t>
+        </is>
+      </c>
+      <c r="F391" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G391" s="55" t="inlineStr">
+        <is>
+          <t>8,320／7,660／9,300円（バスを奥只見ダムまでの1,500円で計算）</t>
+        </is>
+      </c>
+      <c r="H391" s="55" t="inlineStr">
+        <is>
+          <t>8,020／7,360／9,560円（JR自由席＋バス1,200）。横浜は東京で新幹線に乗換</t>
+        </is>
+      </c>
+      <c r="I391" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→浦佐 6,820／6,160／8,360、南越後交通バス運賃表（浦佐駅東口〜銀山平舟付場 1,200円）</t>
+        </is>
+      </c>
+      <c r="J391" s="55" t="inlineStr">
+        <is>
+          <t>JR＋1,200</t>
+        </is>
+      </c>
+      <c r="K391" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="53" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C392" s="53" t="inlineStr">
+        <is>
+          <t>adatara</t>
+        </is>
+      </c>
+      <c r="D392" s="54" t="inlineStr">
+        <is>
+          <t>安達太良山</t>
+        </is>
+      </c>
+      <c r="E392" s="54" t="inlineStr">
+        <is>
+          <t>バスの所要時間（運賃は変更なし）</t>
+        </is>
+      </c>
+      <c r="F392" s="54" t="inlineStr">
+        <is>
+          <t>二本松駅〜奥岳</t>
+        </is>
+      </c>
+      <c r="G392" s="55" t="inlineStr">
+        <is>
+          <t>バス30分</t>
+        </is>
+      </c>
+      <c r="H392" s="55" t="inlineStr">
+        <is>
+          <t>45分（08:13発→08:58着）。運賃 8,060／7,290／9,600円は検算で整合（JR＋バス800）。検索ページ3本の「バス30分→岳温泉（季節）」も修正</t>
+        </is>
+      </c>
+      <c r="I392" s="56" t="inlineStr">
+        <is>
+          <t>福島交通の発着時刻・運賃検索、Yahoo!路線情報：→二本松 7,260／6,490／8,800</t>
+        </is>
+      </c>
+      <c r="J392" s="55" t="inlineStr">
+        <is>
+          <t>JR＋800</t>
+        </is>
+      </c>
+      <c r="K392" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="53" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C393" s="53" t="inlineStr">
+        <is>
+          <t>amakazari</t>
+        </is>
+      </c>
+      <c r="D393" s="54" t="inlineStr">
+        <is>
+          <t>雨飾山</t>
+        </is>
+      </c>
+      <c r="E393" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F393" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G393" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H393" s="55" t="inlineStr">
+        <is>
+          <t>JR分は現行と一致（南小谷まで大宮8,490円・横浜8,270円）。バス約600円は未確認</t>
+        </is>
+      </c>
+      <c r="I393" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報</t>
+        </is>
+      </c>
+      <c r="J393" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K393" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="53" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C394" s="53" t="inlineStr">
+        <is>
+          <t>houou</t>
+        </is>
+      </c>
+      <c r="D394" s="54" t="inlineStr">
+        <is>
+          <t>鳳凰山</t>
+        </is>
+      </c>
+      <c r="E394" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F394" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G394" s="55" t="inlineStr">
+        <is>
+          <t>5,760／6,160／6,260円</t>
+        </is>
+      </c>
+      <c r="H394" s="55" t="inlineStr">
+        <is>
+          <t>5,760／5,760／5,200円（JR＋バス1,760）。横浜は横浜線で八王子に出て特急</t>
+        </is>
+      </c>
+      <c r="I394" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→甲府 4,000／4,000／3,440、山梨交通（甲府駅〜夜叉神峠登山口 1,760円）</t>
+        </is>
+      </c>
+      <c r="J394" s="55" t="inlineStr">
+        <is>
+          <t>JR＋1,760</t>
+        </is>
+      </c>
+      <c r="K394" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="53" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C395" s="53" t="inlineStr">
+        <is>
+          <t>nantaisan</t>
+        </is>
+      </c>
+      <c r="D395" s="54" t="inlineStr">
+        <is>
+          <t>男体山</t>
+        </is>
+      </c>
+      <c r="E395" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（バスの旧運賃）</t>
+        </is>
+      </c>
+      <c r="F395" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G395" s="55" t="inlineStr">
+        <is>
+          <t>5,290／4,780／5,870円（バス1,150円で計算。注記は1,400円）</t>
+        </is>
+      </c>
+      <c r="H395" s="55" t="inlineStr">
+        <is>
+          <t>5,540／5,030／6,120円（特急日光＋バス1,400）</t>
+        </is>
+      </c>
+      <c r="I395" s="56" t="inlineStr">
+        <is>
+          <t>NAVITIME（東武日光駅〜二荒山神社中宮祠 1,400円・53分）</t>
+        </is>
+      </c>
+      <c r="J395" s="55" t="inlineStr">
+        <is>
+          <t>鳴虫山の運賃（鉄道のみ）＋1,400</t>
+        </is>
+      </c>
+      <c r="K395" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="53" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C396" s="53" t="inlineStr">
+        <is>
+          <t>nakimushiyama・amagi</t>
+        </is>
+      </c>
+      <c r="D396" s="54" t="inlineStr">
+        <is>
+          <t>鳴虫山・天城山</t>
+        </is>
+      </c>
+      <c r="E396" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F396" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G396" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H396" s="55" t="inlineStr">
+        <is>
+          <t>現行の額で整合（鳴虫山は特急日光利用の鉄道運賃、天城山は鉄道＋バス1,340）</t>
+        </is>
+      </c>
+      <c r="I396" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報</t>
+        </is>
+      </c>
+      <c r="J396" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K396" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="53" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C397" s="53" t="inlineStr">
+        <is>
+          <t>myoko</t>
+        </is>
+      </c>
+      <c r="D397" s="54" t="inlineStr">
+        <is>
+          <t>妙高山</t>
+        </is>
+      </c>
+      <c r="E397" s="54" t="inlineStr">
+        <is>
+          <t>経路の誤り（バスの起点駅・事業者）・運賃</t>
+        </is>
+      </c>
+      <c r="F397" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G397" s="55" t="inlineStr">
+        <is>
+          <t>上越妙高→妙高高原駅→頸南バス30分→燕温泉。9,100／8,830／9,330円</t>
+        </is>
+      </c>
+      <c r="H397" s="55" t="inlineStr">
+        <is>
+          <t>上越妙高→関山駅→妙高市営バス「関・燕温泉線」20〜34分→燕温泉。9,570／8,800／10,110円（関山駅まで。バス代は別）。検索ページ3本も修正</t>
+        </is>
+      </c>
+      <c r="I397" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→関山 9,570／8,800／10,110、NAVITIME（関山駅10:49→燕温泉11:23）、妙高市公式（通年運行）</t>
+        </is>
+      </c>
+      <c r="J397" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K397" s="57" t="inlineStr">
+        <is>
+          <t>高（バス運賃は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="53" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C398" s="53" t="inlineStr">
+        <is>
+          <t>kobushigatake</t>
+        </is>
+      </c>
+      <c r="D398" s="54" t="inlineStr">
+        <is>
+          <t>甲武信ヶ岳</t>
+        </is>
+      </c>
+      <c r="E398" s="54" t="inlineStr">
+        <is>
+          <t>運賃・経路の検算</t>
+        </is>
+      </c>
+      <c r="F398" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G398" s="55" t="inlineStr">
+        <is>
+          <t>5,650／6,310／6,310円。大宮・横浜は新宿経由</t>
+        </is>
+      </c>
+      <c r="H398" s="55" t="inlineStr">
+        <is>
+          <t>6,640／6,380／5,980円（JR＋村営バス550）。大宮は佐久平経由、横浜は八王子乗車</t>
+        </is>
+      </c>
+      <c r="I398" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→信濃川上 6,090／5,830／5,430、川上村営バス 550円</t>
+        </is>
+      </c>
+      <c r="J398" s="55" t="inlineStr">
+        <is>
+          <t>JR＋550</t>
+        </is>
+      </c>
+      <c r="K398" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="53" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C399" s="53" t="inlineStr">
+        <is>
+          <t>kamakura_alps</t>
+        </is>
+      </c>
+      <c r="D399" s="54" t="inlineStr">
+        <is>
+          <t>鎌倉アルプス</t>
+        </is>
+      </c>
+      <c r="E399" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（大宮＝新宿＋528円の足し算）</t>
+        </is>
+      </c>
+      <c r="F399" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G399" s="55" t="inlineStr">
+        <is>
+          <t>945／1,473／350円</t>
+        </is>
+      </c>
+      <c r="H399" s="55" t="inlineStr">
+        <is>
+          <t>1,034／1,408／341円（JR直通の通し運賃）</t>
+        </is>
+      </c>
+      <c r="I399" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（JRのみの経路）：→北鎌倉</t>
+        </is>
+      </c>
+      <c r="J399" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K399" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="53" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C400" s="53" t="inlineStr">
+        <is>
+          <t>okusuyama</t>
+        </is>
+      </c>
+      <c r="D400" s="54" t="inlineStr">
+        <is>
+          <t>大楠山</t>
+        </is>
+      </c>
+      <c r="E400" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F400" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G400" s="55" t="inlineStr">
+        <is>
+          <t>1,395／1,923／890円</t>
+        </is>
+      </c>
+      <c r="H400" s="55" t="inlineStr">
+        <is>
+          <t>1,411／1,972／817円（JR＋京急バス377）。バス23分</t>
+        </is>
+      </c>
+      <c r="I400" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→逗子 1,034／1,595／440、京急バス（逗子駅〜前田橋）</t>
+        </is>
+      </c>
+      <c r="J400" s="55" t="inlineStr">
+        <is>
+          <t>JR＋377</t>
+        </is>
+      </c>
+      <c r="K400" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="53" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C401" s="53" t="inlineStr">
+        <is>
+          <t>makuyama</t>
+        </is>
+      </c>
+      <c r="D401" s="54" t="inlineStr">
+        <is>
+          <t>幕山</t>
+        </is>
+      </c>
+      <c r="E401" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F401" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G401" s="55" t="inlineStr">
+        <is>
+          <t>2,420／2,948／1,880円。バス10分</t>
+        </is>
+      </c>
+      <c r="H401" s="55" t="inlineStr">
+        <is>
+          <t>2,380／2,710／1,698円（JR＋バス290）。バス18分</t>
+        </is>
+      </c>
+      <c r="I401" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→湯河原 2,090／2,420／1,408、箱根登山バス（湯河原駅〜幕山公園）</t>
+        </is>
+      </c>
+      <c r="J401" s="55" t="inlineStr">
+        <is>
+          <t>JR＋290</t>
+        </is>
+      </c>
+      <c r="K401" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="53" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C402" s="53" t="inlineStr">
+        <is>
+          <t>iyogatake</t>
+        </is>
+      </c>
+      <c r="D402" s="54" t="inlineStr">
+        <is>
+          <t>伊予ヶ岳</t>
+        </is>
+      </c>
+      <c r="E402" s="54" t="inlineStr">
+        <is>
+          <t>運賃・所要時間の検算</t>
+        </is>
+      </c>
+      <c r="F402" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G402" s="55" t="inlineStr">
+        <is>
+          <t>2,180／2,708／2,620円。横浜→岩井115分</t>
+        </is>
+      </c>
+      <c r="H402" s="55" t="inlineStr">
+        <is>
+          <t>2,290／2,950／2,950円（JR＋市営バス200）。大宮190分、横浜169分</t>
+        </is>
+      </c>
+      <c r="I402" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→岩井 2,090／2,750／2,750、南房総市営バス富山線 200円</t>
+        </is>
+      </c>
+      <c r="J402" s="55" t="inlineStr">
+        <is>
+          <t>JR＋200</t>
+        </is>
+      </c>
+      <c r="K402" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="53" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C403" s="53" t="inlineStr">
+        <is>
+          <t>tomisan</t>
+        </is>
+      </c>
+      <c r="D403" s="54" t="inlineStr">
+        <is>
+          <t>富山</t>
+        </is>
+      </c>
+      <c r="E403" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F403" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G403" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H403" s="55" t="inlineStr">
+        <is>
+          <t>2,090／2,750／2,750円で整合</t>
+        </is>
+      </c>
+      <c r="I403" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→岩井</t>
+        </is>
+      </c>
+      <c r="J403" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K403" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="53" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C404" s="53" t="inlineStr">
+        <is>
+          <t>kagenobusan・kobotokeshiroyama</t>
+        </is>
+      </c>
+      <c r="D404" s="54" t="inlineStr">
+        <is>
+          <t>景信山・小仏城山</t>
+        </is>
+      </c>
+      <c r="E404" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（大宮＝新宿＋528円の足し算）</t>
+        </is>
+      </c>
+      <c r="F404" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G404" s="55" t="inlineStr">
+        <is>
+          <t>995／1,523／1,188円</t>
+        </is>
+      </c>
+      <c r="H404" s="55" t="inlineStr">
+        <is>
+          <t>995／1,314／1,314円（JR＋京王バス280）。景信山の注記の「約250円」も280円に統一</t>
+        </is>
+      </c>
+      <c r="I404" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（JRのみ）：→高尾 715／1,034／1,034</t>
+        </is>
+      </c>
+      <c r="J404" s="55" t="inlineStr">
+        <is>
+          <t>JR＋280</t>
+        </is>
+      </c>
+      <c r="K404" s="57" t="inlineStr">
+        <is>
+          <t>高（バス280円は注記の値）</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="53" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C405" s="53" t="inlineStr">
+        <is>
+          <t>中央線の8山</t>
+        </is>
+      </c>
+      <c r="D405" s="54" t="inlineStr">
+        <is>
+          <t>扇山・倉岳山・岩殿山・笹子雁ヶ腹摺山・百蔵山・高川山・石老山・陣馬山</t>
+        </is>
+      </c>
+      <c r="E405" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F405" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G405" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H405" s="55" t="inlineStr">
+        <is>
+          <t>現行の額で整合（鳥沢 1,408／1,595／1,408、大月 1,408／1,595／1,595、笹子 2,090／2,090／1,782、藤野 1,034／1,221／1,221、相模湖 1,034／—／1,034）。百蔵山（猿橋）・高川山（初狩）は隣の駅との整合で判断</t>
+        </is>
+      </c>
+      <c r="I405" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（JRのみ・IC運賃）</t>
+        </is>
+      </c>
+      <c r="J405" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K405" s="57" t="inlineStr">
+        <is>
+          <t>高（猿橋・初狩は中）</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="53" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C406" s="53" t="inlineStr">
+        <is>
+          <t>kumotori</t>
+        </is>
+      </c>
+      <c r="D406" s="54" t="inlineStr">
+        <is>
+          <t>雲取山</t>
+        </is>
+      </c>
+      <c r="E406" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（バスの旧運賃）</t>
+        </is>
+      </c>
+      <c r="F406" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G406" s="55" t="inlineStr">
+        <is>
+          <t>1,670／1,850／2,040円（バス440円で計算）</t>
+        </is>
+      </c>
+      <c r="H406" s="55" t="inlineStr">
+        <is>
+          <t>1,990／2,170／2,360円（JR＋西東京バス760。奥多摩駅〜鴨沢は2025年4月の改定で760円）</t>
+        </is>
+      </c>
+      <c r="I406" s="56" t="inlineStr">
+        <is>
+          <t>西東京バスの運賃改定資料（2025-04-01から）、Yahoo!路線情報：→奥多摩 1,221／1,408／1,595（IC）</t>
+        </is>
+      </c>
+      <c r="J406" s="55" t="inlineStr">
+        <is>
+          <t>JR（きっぷ）1,230／1,410／1,600＋760</t>
+        </is>
+      </c>
+      <c r="K406" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="53" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C407" s="53" t="inlineStr">
+        <is>
+          <t>青梅線・五日市線の9山</t>
+        </is>
+      </c>
+      <c r="D407" s="54" t="inlineStr">
+        <is>
+          <t>川苔山・鷹ノ巣山・本仁田山・御前山・大岳山・御岳山・日の出山・高水三山・三頭山</t>
+        </is>
+      </c>
+      <c r="E407" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F407" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G407" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H407" s="55" t="inlineStr">
+        <is>
+          <t>現行の額で整合。バス：川乗橋310円、東日原530円、奥多摩湖430円、御嶽駅〜ケーブル下340円、ケーブルカー600円、都民の森1,120円</t>
+        </is>
+      </c>
+      <c r="I407" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（JRのみ）：→御嶽 1,034／1,221／1,408、→武蔵五日市 902／1,034／1,221、西東京バスの運賃改定資料</t>
+        </is>
+      </c>
+      <c r="J407" s="55" t="inlineStr">
+        <is>
+          <t>JR＋バス</t>
+        </is>
+      </c>
+      <c r="K407" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="53" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C408" s="53" t="inlineStr">
+        <is>
+          <t>oyama</t>
+        </is>
+      </c>
+      <c r="D408" s="54" t="inlineStr">
+        <is>
+          <t>大山（丹沢）</t>
+        </is>
+      </c>
+      <c r="E408" s="54" t="inlineStr">
+        <is>
+          <t>経路の誤り・運賃</t>
+        </is>
+      </c>
+      <c r="F408" s="54" t="inlineStr">
+        <is>
+          <t>横浜発</t>
+        </is>
+      </c>
+      <c r="G408" s="55" t="inlineStr">
+        <is>
+          <t>横浜→JR東海道線35分→伊勢原駅（伊勢原は東海道線の駅ではない）。1,023円</t>
+        </is>
+      </c>
+      <c r="H408" s="55" t="inlineStr">
+        <is>
+          <t>横浜→相鉄本線→海老名→小田急線→伊勢原。924円（電車554＋バス370）。新宿980円・大宮1,508円は検算で整合</t>
+        </is>
+      </c>
+      <c r="I408" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→伊勢原 607／—／554、神奈川中央交通（伊勢原駅北口〜大山ケーブル 370円）</t>
+        </is>
+      </c>
+      <c r="J408" s="55" t="inlineStr">
+        <is>
+          <t>電車＋370</t>
+        </is>
+      </c>
+      <c r="K408" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="53" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C409" s="53" t="inlineStr">
+        <is>
+          <t>azumayama_ninomiya</t>
+        </is>
+      </c>
+      <c r="D409" s="54" t="inlineStr">
+        <is>
+          <t>吾妻山</t>
+        </is>
+      </c>
+      <c r="E409" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（経路表と額の不一致）</t>
+        </is>
+      </c>
+      <c r="F409" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G409" s="55" t="inlineStr">
+        <is>
+          <t>1,030／1,558／810円（小田急経由の額。経路表はJR東海道線）</t>
+        </is>
+      </c>
+      <c r="H409" s="55" t="inlineStr">
+        <is>
+          <t>1,408／2,090／803円（JR直通の通し運賃）。所要時間 80／105／48分。小田急経由が安い旨を注記</t>
+        </is>
+      </c>
+      <c r="I409" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（JRのみ）：→二宮</t>
+        </is>
+      </c>
+      <c r="J409" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K409" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="53" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C410" s="53" t="inlineStr">
+        <is>
+          <t>丹沢の5山</t>
+        </is>
+      </c>
+      <c r="D410" s="54" t="inlineStr">
+        <is>
+          <t>丹沢山・塔ノ岳・蛭ヶ岳・鍋割山・三ノ塔</t>
+        </is>
+      </c>
+      <c r="E410" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F410" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G410" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H410" s="55" t="inlineStr">
+        <is>
+          <t>970／1,500／930円で整合（渋沢まで新宿692円・横浜648円＋バス270円。きっぷ運賃との差は10円程度）</t>
+        </is>
+      </c>
+      <c r="I410" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報、神奈川中央交通（渋沢駅北口〜大倉 270円）</t>
+        </is>
+      </c>
+      <c r="J410" s="55" t="inlineStr">
+        <is>
+          <t>電車＋270</t>
+        </is>
+      </c>
+      <c r="K410" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="53" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C411" s="53" t="inlineStr">
+        <is>
+          <t>tenzandake</t>
+        </is>
+      </c>
+      <c r="D411" s="54" t="inlineStr">
+        <is>
+          <t>天覧山・多峯主山</t>
+        </is>
+      </c>
+      <c r="E411" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F411" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G411" s="55" t="inlineStr">
+        <is>
+          <t>690／1,597／1,306円（大宮発だけ特急の経路）</t>
+        </is>
+      </c>
+      <c r="H411" s="55" t="inlineStr">
+        <is>
+          <t>756／997／1,272円（JR＋西武557）</t>
+        </is>
+      </c>
+      <c r="I411" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：池袋まで 199／440／715、池袋〜飯能 557</t>
+        </is>
+      </c>
+      <c r="J411" s="55" t="inlineStr">
+        <is>
+          <t>JR＋557</t>
+        </is>
+      </c>
+      <c r="K411" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="53" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C412" s="53" t="inlineStr">
+        <is>
+          <t>bonori</t>
+        </is>
+      </c>
+      <c r="D412" s="54" t="inlineStr">
+        <is>
+          <t>棒ノ折山</t>
+        </is>
+      </c>
+      <c r="E412" s="54" t="inlineStr">
+        <is>
+          <t>運賃・バスの検算</t>
+        </is>
+      </c>
+      <c r="F412" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G412" s="55" t="inlineStr">
+        <is>
+          <t>1,143／2,050／1,759円。バス25分</t>
+        </is>
+      </c>
+      <c r="H412" s="55" t="inlineStr">
+        <is>
+          <t>1,446／1,687／1,962円（JR＋西武557＋バス690）。バス約40分。検索ページ4本の「バス25分」も修正</t>
+        </is>
+      </c>
+      <c r="I412" s="56" t="inlineStr">
+        <is>
+          <t>同上、国際興業バス（飯能駅〜河又名栗湖入口 690円・約40分）</t>
+        </is>
+      </c>
+      <c r="J412" s="55" t="inlineStr">
+        <is>
+          <t>JR＋557＋690</t>
+        </is>
+      </c>
+      <c r="K412" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="53" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C413" s="53" t="inlineStr">
+        <is>
+          <t>maruyama_okubusuma・futagoyama_okumusa</t>
+        </is>
+      </c>
+      <c r="D413" s="54" t="inlineStr">
+        <is>
+          <t>丸山・二子山（奥武蔵）</t>
+        </is>
+      </c>
+      <c r="E413" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F413" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G413" s="55" t="inlineStr">
+        <is>
+          <t>957／1,362／1,573円</t>
+        </is>
+      </c>
+      <c r="H413" s="55" t="inlineStr">
+        <is>
+          <t>957／1,198／1,473円（JR＋西武758）</t>
+        </is>
+      </c>
+      <c r="I413" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：池袋〜芦ヶ久保 758</t>
+        </is>
+      </c>
+      <c r="J413" s="55" t="inlineStr">
+        <is>
+          <t>JR＋758</t>
+        </is>
+      </c>
+      <c r="K413" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="53" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C414" s="53" t="inlineStr">
+        <is>
+          <t>bukosan</t>
+        </is>
+      </c>
+      <c r="D414" s="54" t="inlineStr">
+        <is>
+          <t>武甲山</t>
+        </is>
+      </c>
+      <c r="E414" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（タクシー代の概算を除去）</t>
+        </is>
+      </c>
+      <c r="F414" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G414" s="55" t="inlineStr">
+        <is>
+          <t>3,499／3,999／4,115円（タクシー代の目安を含む）。大宮発は川越線・八高線経由</t>
+        </is>
+      </c>
+      <c r="H414" s="55" t="inlineStr">
+        <is>
+          <t>1,899／2,140／2,415円（西武秩父駅まで。特急料金込み、タクシー代は別）。大宮発を池袋経由に統一</t>
+        </is>
+      </c>
+      <c r="I414" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：池袋〜西武秩父 800＋特急900</t>
+        </is>
+      </c>
+      <c r="J414" s="55" t="inlineStr">
+        <is>
+          <t>JR＋1,700</t>
+        </is>
+      </c>
+      <c r="K414" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="53" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C415" s="53" t="inlineStr">
+        <is>
+          <t>ryokami</t>
+        </is>
+      </c>
+      <c r="D415" s="54" t="inlineStr">
+        <is>
+          <t>両神山</t>
+        </is>
+      </c>
+      <c r="E415" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F415" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G415" s="55" t="inlineStr">
+        <is>
+          <t>2,300／1,610／2,916円</t>
+        </is>
+      </c>
+      <c r="H415" s="55" t="inlineStr">
+        <is>
+          <t>1,899／2,140／2,415円（西武秩父駅まで。町営バス代は別・未確認）。大宮発を池袋経由に統一</t>
+        </is>
+      </c>
+      <c r="I415" s="56" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="J415" s="55" t="inlineStr">
+        <is>
+          <t>JR＋1,700</t>
+        </is>
+      </c>
+      <c r="K415" s="57" t="inlineStr">
+        <is>
+          <t>中（バス運賃は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="53" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C416" s="53" t="inlineStr">
+        <is>
+          <t>hiwadayama・izugatake</t>
+        </is>
+      </c>
+      <c r="D416" s="54" t="inlineStr">
+        <is>
+          <t>日和田山・伊豆ヶ岳</t>
+        </is>
+      </c>
+      <c r="E416" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F416" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G416" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H416" s="55" t="inlineStr">
+        <is>
+          <t>現行の額で整合（池袋〜高麗 627、正丸 735）</t>
+        </is>
+      </c>
+      <c r="I416" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報</t>
+        </is>
+      </c>
+      <c r="J416" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K416" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -6585,7 +6585,7 @@
         <v>143</v>
       </c>
       <c r="N4" s="41" t="n">
-        <v>2608</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="5" ht="39" customHeight="1" s="30">
@@ -7437,25 +7437,25 @@
       </c>
       <c r="I19" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線あさま]--&gt; 佐久平駅 --[しなの鉄道]--&gt; 小諸駅 --[JRバス関東「高峰高原線」]--&gt; 車坂峠（高峰高原ホテル前）</t>
+          <t>大宮駅 --[北陸新幹線]--&gt; 佐久平駅 --[JRバス関東「高峰高原線」]--&gt; 車坂峠（高峰高原ホテル前）</t>
         </is>
       </c>
       <c r="J19" s="41" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K19" s="41" t="n">
-        <v>6325</v>
+        <v>6510</v>
       </c>
       <c r="L19" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線あさま]--&gt; 佐久平駅 --[しなの鉄道]--&gt; 小諸駅 --[JRバス関東「高峰高原線」]--&gt; 車坂峠（高峰高原ホテル前）</t>
+          <t>横浜駅 --[JR上野東京ライン]--&gt; 東京駅 --[北陸新幹線]--&gt; 佐久平駅 --[JRバス関東「高峰高原線」]--&gt; 車坂峠（高峰高原ホテル前）</t>
         </is>
       </c>
       <c r="M19" s="41" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N19" s="41" t="n">
-        <v>7635</v>
+        <v>7820</v>
       </c>
     </row>
     <row r="20" ht="51.75" customHeight="1" s="30">
@@ -8214,36 +8214,36 @@
       </c>
       <c r="F33" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR埼京線]--&gt; 大宮駅 --[上越新幹線とき]--&gt; 浦佐駅 --[JR上越線]--&gt; 六日町駅 --[オンデマンド交通「MOSS」（平日のみ運行）]--&gt; 清水（桜坂駐車場）</t>
+          <t>新宿駅→JR埼京線約26分→大宮駅→上越新幹線とき約55分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」（平日のみ運行）約30分→清水（桜坂駐車場）</t>
         </is>
       </c>
       <c r="G33" s="41" t="n">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="H33" s="41" t="n">
-        <v>7380</v>
+        <v>7080</v>
       </c>
       <c r="I33" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[上越新幹線とき、越後湯沢の先まで延長)]--&gt; 浦佐駅 --[JR上越線]--&gt; 六日町駅 --[オンデマンド交通「MOSS」]--&gt; 清水（桜坂駐車場）</t>
+          <t>大宮駅→上越新幹線とき、越後湯沢の先まで延長)約55分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」約40分→清水（桜坂駐車場）</t>
         </is>
       </c>
       <c r="J33" s="41" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K33" s="41" t="n">
-        <v>6720</v>
+        <v>6420</v>
       </c>
       <c r="L33" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[上越新幹線とき（越後湯沢の先まで延長）]--&gt; 浦佐駅 --[JR上越線]--&gt; 六日町駅 --[オンデマンド交通「MOSS」]--&gt; 清水（桜坂駐車場）</t>
+          <t>横浜駅→JR東海道線約18分→東京駅→上越新幹線とき（越後湯沢の先まで延長）約1時間19分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」約40分→清水（桜坂駐車場）</t>
         </is>
       </c>
       <c r="M33" s="41" t="n">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="N33" s="41" t="n">
-        <v>8920</v>
+        <v>8620</v>
       </c>
     </row>
     <row r="34" ht="51.75" customHeight="1" s="30">
@@ -8388,36 +8388,36 @@
       </c>
       <c r="F36" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR山手線]--&gt; 西日暮里駅 --[東京メトロ千代田線]--&gt; 北千住駅 --[東武特急リバティ会津]--&gt; 会津田島駅 --[会津バス「檜枝岐線」]--&gt; 駒ヶ岳登山口 --[徒歩]--&gt; 滝沢登山口（バスは5/1〜10/31運行）</t>
+          <t>新宿駅→JR山手線約19分→西日暮里駅→東京メトロ千代田線約6分→北千住駅→東武特急リバティ会津約2時間57分→会津田島駅→会津バス「檜枝岐線」約1時間28分→駒ヶ岳登山口→徒歩約30分→滝沢登山口（バスは5/1〜10/31運行）</t>
         </is>
       </c>
       <c r="G36" s="41" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H36" s="41" t="n">
-        <v>8750</v>
+        <v>8573</v>
       </c>
       <c r="I36" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[東武アーバンパークライン]--&gt; 春日部駅 --[東武特急リバティ会津]--&gt; 会津田島駅 --[会津バス「檜枝岐線」]--&gt; 駒ヶ岳登山口 --[徒歩]--&gt; 滝沢登山口（バスは5/1〜10/31運行）</t>
+          <t>大宮駅→東武アーバンパークライン約30分→春日部駅→東武特急リバティ会津約2時間37分→会津田島駅→会津バス「檜枝岐線」約1時間28分→駒ヶ岳登山口→徒歩約30分→滝沢登山口（バスは5/1〜10/31運行）</t>
         </is>
       </c>
       <c r="J36" s="41" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K36" s="41" t="n">
-        <v>9360</v>
+        <v>7940</v>
       </c>
       <c r="L36" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR上野東京ライン・地下鉄千代田線経由]--&gt; 北千住駅 --[東武特急リバティ会津]--&gt; 会津田島駅 --[会津バス「檜枝岐線」]--&gt; 駒ヶ岳登山口 --[徒歩]--&gt; 滝沢登山口（バスは5/1〜10/31運行）</t>
+          <t>横浜駅→JR上野東京ライン・常磐線（上野乗換）約1時間15分→北千住駅→東武特急リバティ会津約2時間57分→会津田島駅→会津バス「檜枝岐線」約1時間28分→駒ヶ岳登山口→徒歩約30分→滝沢登山口（バスは5/1〜10/31運行）</t>
         </is>
       </c>
       <c r="M36" s="41" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N36" s="41" t="n">
-        <v>9950</v>
+        <v>8860</v>
       </c>
     </row>
     <row r="37" ht="51.75" customHeight="1" s="30">
@@ -9316,36 +9316,36 @@
       </c>
       <c r="F52" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 中の湯バス停（季節）</t>
+          <t>新宿駅→JR特急あずさ約2時間30分→松本駅→松本電鉄上高地線約30分→新島々駅→アルピコ交通バス（予約優先制）約55分→中の湯バス停</t>
         </is>
       </c>
       <c r="G52" s="41" t="n">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H52" s="41" t="n">
-        <v>8900</v>
+        <v>9840</v>
       </c>
       <c r="I52" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 中の湯バス停（季節）</t>
+          <t>大宮駅→JR埼京線・武蔵野線・中央線（立川乗換）約55分→立川駅→JR特急あずさ約2時間20分→松本駅→松本電鉄上高地線約30分→新島々駅→アルピコ交通バス（予約優先制）約55分→中の湯バス停</t>
         </is>
       </c>
       <c r="J52" s="41" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K52" s="41" t="n">
-        <v>8590</v>
+        <v>9530</v>
       </c>
       <c r="L52" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[松本電鉄上高地線]--&gt; 新島々駅 --[アルピコバス]--&gt; 中の湯バス停（季節）</t>
+          <t>横浜駅→JR横浜線約50分→八王子駅→JR特急あずさ約2時間31分→松本駅→松本電鉄上高地線約30分→新島々駅→アルピコ交通バス（予約優先制）約55分→中の湯バス停</t>
         </is>
       </c>
       <c r="M52" s="41" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="N52" s="41" t="n">
-        <v>8900</v>
+        <v>9530</v>
       </c>
     </row>
     <row r="53" ht="39" customHeight="1" s="30">
@@ -9674,36 +9674,36 @@
       </c>
       <c r="F59" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 飯綱登山口バス停（一ノ鳥居苑地）</t>
+          <t>新宿駅→JR中央線快速約15分→東京駅→北陸新幹線あさま約1時間40分→長野駅→アルピコ交通バス「戸隠線」約47分→飯綱登山口バス停（一ノ鳥居苑地）</t>
         </is>
       </c>
       <c r="G59" s="41" t="n">
         <v>162</v>
       </c>
       <c r="H59" s="41" t="n">
-        <v>8760</v>
+        <v>7770</v>
       </c>
       <c r="I59" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 飯綱登山口バス停（一ノ鳥居苑地）</t>
+          <t>大宮駅→北陸新幹線あさま約1時間22分→長野駅→アルピコ交通バス「戸隠線」約47分→飯綱登山口バス停（一ノ鳥居苑地）</t>
         </is>
       </c>
       <c r="J59" s="41" t="n">
         <v>129</v>
       </c>
       <c r="K59" s="41" t="n">
-        <v>6860</v>
+        <v>7110</v>
       </c>
       <c r="L59" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 飯綱登山口バス停（一ノ鳥居苑地）</t>
+          <t>横浜駅→JR東海道線約18分→東京駅→北陸新幹線あさま約1時間46分→長野駅→アルピコ交通バス「戸隠線」約47分→飯綱登山口バス停（一ノ鳥居苑地）</t>
         </is>
       </c>
       <c r="M59" s="41" t="n">
         <v>171</v>
       </c>
       <c r="N59" s="41" t="n">
-        <v>9200</v>
+        <v>9310</v>
       </c>
     </row>
     <row r="60" ht="39" customHeight="1" s="30">
@@ -9790,36 +9790,36 @@
       </c>
       <c r="F61" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR東海道線・身延線（品川・熱海・富士乗換）]--&gt; 富士宮駅 --[富士急静岡バス]--&gt; 朝霧高原（毛無山登山口）</t>
+          <t>新宿駅→JR東海道線・身延線（品川・熱海・富士乗換）約3時間22分→富士宮駅→富士急バス（新富士線・富士山駅行き）約32分→朝霧高原（毛無山登山口）</t>
         </is>
       </c>
       <c r="G61" s="41" t="n">
         <v>234</v>
       </c>
       <c r="H61" s="41" t="n">
-        <v>4400</v>
+        <v>3830</v>
       </c>
       <c r="I61" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR上野東京ライン・東海道線・身延線（熱海・富士乗換）]--&gt; 富士宮駅 --[富士急静岡バス]--&gt; 朝霧高原（毛無山登山口）</t>
+          <t>大宮駅→JR上野東京ライン・東海道線・身延線（熱海・富士乗換）約3時間37分→富士宮駅→富士急バス（新富士線・富士山駅行き）約32分→朝霧高原（毛無山登山口）</t>
         </is>
       </c>
       <c r="J61" s="41" t="n">
         <v>249</v>
       </c>
       <c r="K61" s="41" t="n">
-        <v>5170</v>
+        <v>4600</v>
       </c>
       <c r="L61" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線・身延線（熱海・富士乗換）]--&gt; 富士宮駅 --[富士急静岡バス]--&gt; 朝霧高原（毛無山登山口）</t>
+          <t>横浜駅→JR東海道線・身延線（熱海・富士乗換）約2時間37分→富士宮駅→富士急バス（新富士線・富士山駅行き）約32分→朝霧高原（毛無山登山口）</t>
         </is>
       </c>
       <c r="M61" s="41" t="n">
         <v>189</v>
       </c>
       <c r="N61" s="41" t="n">
-        <v>4030</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="30">
@@ -9866,7 +9866,7 @@
         <v>305</v>
       </c>
       <c r="K62" s="41" t="n">
-        <v>5550</v>
+        <v>5500</v>
       </c>
       <c r="L62" s="44" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>309</v>
       </c>
       <c r="N62" s="41" t="n">
-        <v>5550</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="63" ht="39" customHeight="1" s="30">
@@ -10022,36 +10022,36 @@
       </c>
       <c r="F65" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR・西武池袋線・秩父鉄道（池袋・飯能・西武秩父乗換込み）]--&gt; 三峰口駅 --[西武観光バス「三峯神社線」]--&gt; 秩父湖バス停</t>
+          <t>新宿駅→JR・西武池袋線・秩父鉄道（池袋・飯能・西武秩父乗換込み）約2時間44分→三峰口駅→西武観光バス「三峯神社線」約40分→秩父湖バス停</t>
         </is>
       </c>
       <c r="G65" s="41" t="n">
         <v>204</v>
       </c>
       <c r="H65" s="41" t="n">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="I65" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR高崎線・秩父鉄道（熊谷乗換込み）]--&gt; 三峰口駅 --[西武観光バス「三峯神社線」]--&gt; 秩父湖バス停</t>
+          <t>大宮駅→JR高崎線・秩父鉄道（熊谷乗換込み）約2時間17分→三峰口駅→西武観光バス「三峯神社線」約40分→秩父湖バス停</t>
         </is>
       </c>
       <c r="J65" s="41" t="n">
         <v>177</v>
       </c>
       <c r="K65" s="41" t="n">
-        <v>2250</v>
+        <v>2246</v>
       </c>
       <c r="L65" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR・西武池袋線・秩父鉄道（池袋・飯能・西武秩父乗換込み）]--&gt; 三峰口駅 --[西武観光バス「三峯神社線」]--&gt; 秩父湖バス停</t>
+          <t>横浜駅→JR・西武池袋線・秩父鉄道（池袋・飯能・西武秩父乗換込み）約3時間22分→三峰口駅→西武観光バス「三峯神社線」約40分→秩父湖バス停</t>
         </is>
       </c>
       <c r="M65" s="41" t="n">
         <v>242</v>
       </c>
       <c r="N65" s="41" t="n">
-        <v>2600</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="66" ht="39" customHeight="1" s="30">
@@ -10237,7 +10237,7 @@
         <v>251</v>
       </c>
       <c r="H69" s="41" t="n">
-        <v>6730</v>
+        <v>7040</v>
       </c>
       <c r="I69" s="44" t="inlineStr">
         <is>
@@ -10496,36 +10496,36 @@
       </c>
       <c r="F74" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[上越新幹線とき]--&gt; 越後湯沢駅 --[タクシー（路線バスなし）]--&gt; 祓川登山口駐車場 --[徒歩（林道）]--&gt; 祓川登山口</t>
+          <t>新宿駅→JR中央線快速約15分→東京駅→上越新幹線とき約1時間13分→越後湯沢駅→タクシー（路線バスなし）約25分→祓川登山口駐車場→徒歩（林道）約30分→祓川登山口</t>
         </is>
       </c>
       <c r="G74" s="41" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="H74" s="41" t="n">
-        <v>9800</v>
+        <v>6160</v>
       </c>
       <c r="I74" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[上越新幹線とき]--&gt; 越後湯沢駅 --[タクシー（路線バスなし）]--&gt; 祓川登山口駐車場 --[徒歩（林道）]--&gt; 祓川登山口</t>
+          <t>大宮駅→上越新幹線とき約49分→越後湯沢駅→タクシー（路線バスなし）約25分→祓川登山口駐車場→徒歩（林道）約30分→祓川登山口</t>
         </is>
       </c>
       <c r="J74" s="41" t="n">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="K74" s="41" t="n">
-        <v>9020</v>
+        <v>5830</v>
       </c>
       <c r="L74" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[上越新幹線とき]--&gt; 越後湯沢駅 --[タクシー（路線バスなし）]--&gt; 祓川登山口駐車場 --[徒歩（林道）]--&gt; 祓川登山口</t>
+          <t>横浜駅→JR東海道線約18分→東京駅→上越新幹線とき約1時間13分→越後湯沢駅→タクシー（路線バスなし）約25分→祓川登山口駐車場→徒歩（林道）約30分→祓川登山口</t>
         </is>
       </c>
       <c r="M74" s="41" t="n">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="N74" s="41" t="n">
-        <v>9520</v>
+        <v>7030</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="30">
@@ -10670,36 +10670,36 @@
       </c>
       <c r="F77" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線あさま（東京駅乗換）]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 戸隠キャンプ場（高妻山登山口）</t>
+          <t>新宿駅→JR中央線快速約15分→東京駅→北陸新幹線あさま（東京駅乗換）約1時間40分→長野駅→アルピコ交通「観光特急戸隠線」（予約制）約1時間5分→戸隠キャンプ場（高妻山登山口）</t>
         </is>
       </c>
       <c r="G77" s="41" t="n">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="H77" s="41" t="n">
-        <v>8060</v>
+        <v>9320</v>
       </c>
       <c r="I77" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 戸隠キャンプ場（高妻山登山口）</t>
+          <t>大宮駅→北陸新幹線あさま約1時間16分→長野駅→アルピコ交通「観光特急戸隠線」（予約制）約1時間5分→戸隠キャンプ場（高妻山登山口）</t>
         </is>
       </c>
       <c r="J77" s="41" t="n">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="K77" s="41" t="n">
-        <v>6160</v>
+        <v>8660</v>
       </c>
       <c r="L77" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線あさま]--&gt; 長野駅 --[アルピコ交通バス「戸隠線」]--&gt; 戸隠キャンプ場（高妻山登山口）</t>
+          <t>横浜駅→JR東海道線約18分→東京駅→北陸新幹線あさま約1時間46分→長野駅→アルピコ交通「観光特急戸隠線」（予約制）約1時間5分→戸隠キャンプ場（高妻山登山口）</t>
         </is>
       </c>
       <c r="M77" s="41" t="n">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="N77" s="41" t="n">
-        <v>8500</v>
+        <v>10860</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="30">
@@ -10994,36 +10994,36 @@
       </c>
       <c r="F83" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ]--&gt; 松本駅 --[アルピコ交通バス]--&gt; 美ヶ原高原（夏季）</t>
+          <t>新宿駅→JR特急あずさ約2時間30分→松本駅→信州美ヶ原高原直行バス（完全予約制）約1時間20分→美ヶ原自然保護センター</t>
         </is>
       </c>
       <c r="G83" s="41" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="H83" s="41" t="n">
-        <v>8000</v>
+        <v>8230</v>
       </c>
       <c r="I83" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・特急あずさ（西国分寺・立川乗換）]--&gt; 松本駅 --[アルピコ交通バス]--&gt; 美ヶ原高原（夏季）</t>
+          <t>大宮駅→JR埼京線・武蔵野線・中央線・特急あずさ（西国分寺・立川乗換）約3時間15分→松本駅→信州美ヶ原高原直行バス（完全予約制）約1時間20分→美ヶ原自然保護センター</t>
         </is>
       </c>
       <c r="J83" s="41" t="n">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="K83" s="41" t="n">
-        <v>7690</v>
+        <v>7920</v>
       </c>
       <c r="L83" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR横浜線・特急あずさ（八王子乗換）]--&gt; 松本駅 --[アルピコ交通バス]--&gt; 美ヶ原高原（夏季）</t>
+          <t>横浜駅→JR横浜線・特急あずさ（八王子乗換）約3時間21分→松本駅→信州美ヶ原高原直行バス（完全予約制）約1時間20分→美ヶ原自然保護センター</t>
         </is>
       </c>
       <c r="M83" s="41" t="n">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="N83" s="41" t="n">
-        <v>7690</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="84" ht="26.25" customHeight="1" s="30">
@@ -11840,33 +11840,33 @@
       </c>
       <c r="F98" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急かいじ]--&gt; 塩山駅 --[山梨交通「西沢渓谷線」]--&gt; 道の駅みとみ（西沢渓谷入口）</t>
+          <t>新宿駅→JR特急かいじ約1時間25分→塩山駅→山梨交通「西沢渓谷線」約1時間3分→道の駅みとみ（西沢渓谷入口）</t>
         </is>
       </c>
       <c r="G98" s="41" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H98" s="41" t="n">
         <v>4890</v>
       </c>
       <c r="I98" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 塩山駅 --[山梨交通「西沢渓谷線」]--&gt; 道の駅みとみ（西沢渓谷入口）</t>
+          <t>大宮駅→JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）約2時間31分→塩山駅→山梨交通「西沢渓谷線」約1時間3分→道の駅みとみ（西沢渓谷入口）</t>
         </is>
       </c>
       <c r="J98" s="41" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K98" s="41" t="n">
         <v>3310</v>
       </c>
       <c r="L98" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 塩山駅 --[山梨交通「西沢渓谷線」]--&gt; 道の駅みとみ（西沢渓谷入口）</t>
+          <t>横浜駅→JR横浜線・中央線（八王子乗換）約2時間37分→塩山駅→山梨交通「西沢渓谷線」約1時間3分→道の駅みとみ（西沢渓谷入口）</t>
         </is>
       </c>
       <c r="M98" s="41" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="N98" s="41" t="n">
         <v>3310</v>
@@ -12311,29 +12311,29 @@
         <v>150</v>
       </c>
       <c r="H106" s="41" t="n">
-        <v>1980</v>
+        <v>2090</v>
       </c>
       <c r="I106" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR内房線]--&gt; 浜金谷駅 --[徒歩]--&gt; 鋸山登山口</t>
+          <t>大宮駅 --[JR上野東京ライン・総武線快速・内房線（東京・木更津乗換）]--&gt; 浜金谷駅 --[徒歩]--&gt; 鋸山登山口</t>
         </is>
       </c>
       <c r="J106" s="41" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="K106" s="41" t="n">
         <v>2420</v>
       </c>
       <c r="L106" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線・総武線・内房線(君津・木更津経由)]--&gt; 浜金谷駅 --[徒歩]--&gt; 鋸山登山口</t>
+          <t>横浜駅 --[JR横須賀線・総武線快速直通・内房線（木更津乗換）]--&gt; 浜金谷駅 --[徒歩]--&gt; 鋸山登山口</t>
         </is>
       </c>
       <c r="M106" s="41" t="n">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="N106" s="41" t="n">
-        <v>2310</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="107" ht="26.25" customHeight="1" s="30">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="F115" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[小田急線]--&gt; 鶴巻温泉駅または秦野駅 --[徒歩]--&gt; 弘法山登山口</t>
+          <t>新宿駅→小田急線約1時間10分→秦野駅→徒歩約25分→弘法山登山口</t>
         </is>
       </c>
       <c r="G115" s="41" t="n">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="I115" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急線]--&gt; 鶴巻温泉駅または秦野駅 --[徒歩]--&gt; 弘法山登山口</t>
+          <t>大宮駅→JR湘南新宿ライン約30分→新宿駅→小田急線約1時間10分→秦野駅→徒歩約25分→弘法山登山口</t>
         </is>
       </c>
       <c r="J115" s="41" t="n">
@@ -12848,14 +12848,14 @@
       </c>
       <c r="L115" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[相鉄本線]--&gt; 海老名駅 --[小田急線]--&gt; 鶴巻温泉駅 --[徒歩]--&gt; 弘法山登山口</t>
+          <t>横浜駅→相鉄本線約26分→海老名駅→小田急線（乗換待ち含む）約33分→秦野駅→徒歩約25分→弘法山登山口</t>
         </is>
       </c>
       <c r="M115" s="41" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="N115" s="41" t="n">
-        <v>600</v>
+        <v>617</v>
       </c>
     </row>
     <row r="116" ht="26.25" customHeight="1" s="30">
@@ -13406,36 +13406,36 @@
       </c>
       <c r="F125" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[箱根登山バス]--&gt; 地蔵堂バス停（登山口）</t>
+          <t>新宿駅→小田急線快速急行約1時間20分→新松田駅→箱根登山バス（関本で乗り換え）約47分→地蔵堂バス停（登山口）</t>
         </is>
       </c>
       <c r="G125" s="41" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H125" s="41" t="n">
-        <v>1536</v>
+        <v>1806</v>
       </c>
       <c r="I125" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[箱根登山バス]--&gt; 地蔵堂バス停（登山口）</t>
+          <t>大宮駅→JR湘南新宿ライン約30分→新宿駅→小田急線快速急行約1時間20分→新松田駅→箱根登山バス（関本で乗り換え）約47分→地蔵堂バス停（登山口）</t>
         </is>
       </c>
       <c r="J125" s="41" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="K125" s="41" t="n">
-        <v>2064</v>
+        <v>2334</v>
       </c>
       <c r="L125" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 小田原駅 --[伊豆箱根鉄道大雄山線]--&gt; 大雄山駅 --[箱根登山バス]--&gt; 地蔵堂バス停（登山口）</t>
+          <t>横浜駅→JR東海道線約55分→小田原駅→伊豆箱根鉄道大雄山線約49分→大雄山駅→箱根登山バス約28分→地蔵堂バス停（登山口）</t>
         </is>
       </c>
       <c r="M125" s="41" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="N125" s="41" t="n">
-        <v>2010</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="126" ht="39" customHeight="1" s="30">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="F131" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[徒歩]--&gt; 松田駅 --[JR御殿場線]--&gt; 山北駅 --[徒歩]--&gt; 大野山入口</t>
+          <t>新宿駅→小田急線快速急行約1時間16分→新松田駅→徒歩約3分→松田駅→JR御殿場線約7分→山北駅→徒歩約20分→大野山入口</t>
         </is>
       </c>
       <c r="G131" s="41" t="n">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="I131" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[小田急線快速急行]--&gt; 新松田駅 --[徒歩]--&gt; 松田駅 --[JR御殿場線]--&gt; 山北駅 --[徒歩]--&gt; 大野山入口</t>
+          <t>大宮駅→JR湘南新宿ライン約30分→新宿駅→小田急線快速急行約1時間16分→新松田駅→徒歩約3分→松田駅→JR御殿場線約7分→山北駅→徒歩約20分→大野山入口</t>
         </is>
       </c>
       <c r="J131" s="41" t="n">
@@ -13776,14 +13776,14 @@
       </c>
       <c r="L131" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 国府津駅 --[JR御殿場線]--&gt; 山北駅 --[徒歩]--&gt; 大野山入口</t>
+          <t>横浜駅→JR東海道線約48分→国府津駅→JR御殿場線約22分→山北駅→徒歩約20分→大野山入口</t>
         </is>
       </c>
       <c r="M131" s="41" t="n">
         <v>90</v>
       </c>
       <c r="N131" s="41" t="n">
-        <v>1446</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="132" ht="26.25" customHeight="1" s="30">
@@ -13990,10 +13990,10 @@
         </is>
       </c>
       <c r="G135" s="41" t="n">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="H135" s="41" t="n">
-        <v>3100</v>
+        <v>1595</v>
       </c>
       <c r="I135" s="44" t="inlineStr">
         <is>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="J135" s="41" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K135" s="41" t="n">
-        <v>2730</v>
+        <v>1221</v>
       </c>
       <c r="L135" s="44" t="inlineStr">
         <is>
@@ -14012,10 +14012,10 @@
         </is>
       </c>
       <c r="M135" s="41" t="n">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="N135" s="41" t="n">
-        <v>3716</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="136" ht="26.25" customHeight="1" s="30">
@@ -14450,36 +14450,36 @@
       </c>
       <c r="F143" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線・五日市線（立川乗換）]--&gt; 武蔵五日市駅 --[西東京バス]--&gt; 払沢の滝入口</t>
+          <t>新宿駅→JR中央線・五日市線（立川乗換）約1時間20分→武蔵五日市駅→西東京バス約23分→払沢の滝入口</t>
         </is>
       </c>
       <c r="G143" s="41" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H143" s="41" t="n">
-        <v>1440</v>
+        <v>1432</v>
       </c>
       <c r="I143" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線・武蔵野線・中央線・五日市線（西国分寺・立川乗換）]--&gt; 武蔵五日市駅 --[西東京バス]--&gt; 払沢の滝入口</t>
+          <t>大宮駅→JR埼京線・武蔵野線・中央線・五日市線（西国分寺・立川乗換）約1時間46分→武蔵五日市駅→西東京バス約23分→払沢の滝入口</t>
         </is>
       </c>
       <c r="J143" s="41" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K143" s="41" t="n">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="L143" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR京浜東北線・南武線・五日市線（川崎・立川乗換）]--&gt; 武蔵五日市駅 --[西東京バス]--&gt; 払沢の滝入口</t>
+          <t>横浜駅→JR京浜東北線・南武線・五日市線（川崎・立川乗換）約2時間2分→武蔵五日市駅→西東京バス約23分→払沢の滝入口</t>
         </is>
       </c>
       <c r="M143" s="41" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N143" s="41" t="n">
-        <v>1760</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="144" ht="39" customHeight="1" s="30">
@@ -14624,36 +14624,36 @@
       </c>
       <c r="F146" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線]--&gt; 大月駅 --[富士急行線]--&gt; 河口湖駅 --[富士急バス]--&gt; 山中湖平野バス停</t>
+          <t>新宿駅→JR中央線（高尾乗換）約1時間44分→大月駅→富士急行線約59分→河口湖駅→富士急バス「ふじっ湖号」約55分→山中湖平野バス停</t>
         </is>
       </c>
       <c r="G146" s="41" t="n">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="H146" s="41" t="n">
-        <v>4339</v>
+        <v>3619</v>
       </c>
       <c r="I146" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線]--&gt; 大月駅 --[富士急行線]--&gt; 河口湖駅 --[富士急バス]--&gt; 山中湖平野バス停</t>
+          <t>大宮駅→JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）約2時間→大月駅→富士急行線約59分→河口湖駅→富士急バス「ふじっ湖号」約55分→山中湖平野バス停</t>
         </is>
       </c>
       <c r="J146" s="41" t="n">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="K146" s="41" t="n">
-        <v>4529</v>
+        <v>3806</v>
       </c>
       <c r="L146" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線]--&gt; 大月駅 --[富士急行線]--&gt; 河口湖駅 --[富士急バス]--&gt; 山中湖平野バス停</t>
+          <t>横浜駅→JR横浜線・中央線（八王子乗換）約1時間52分→大月駅→富士急行線約59分→河口湖駅→富士急バス「ふじっ湖号」約55分→山中湖平野バス停</t>
         </is>
       </c>
       <c r="M146" s="41" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="N146" s="41" t="n">
-        <v>4529</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="147" ht="26.25" customHeight="1" s="30">
@@ -14972,36 +14972,36 @@
       </c>
       <c r="F152" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線・富士急行線直通特急「富士回遊」]--&gt; 河口湖駅 --[富士急バス「天下茶屋線」]--&gt; 三つ峠登山口バス停</t>
+          <t>新宿駅→JR中央線・富士急行線直通特急「富士回遊」約1時間55分→河口湖駅→富士急バス「天下茶屋線」約25分→三つ峠登山口バス停</t>
         </is>
       </c>
       <c r="G152" s="41" t="n">
         <v>140</v>
       </c>
       <c r="H152" s="41" t="n">
-        <v>5040</v>
+        <v>5029</v>
       </c>
       <c r="I152" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線・富士急行線直通特急「富士回遊」]--&gt; 河口湖駅 --[富士急バス「天下茶屋線」]--&gt; 三つ峠登山口バス停</t>
+          <t>大宮駅→JR湘南新宿ライン約30分→新宿駅→JR中央線・富士急行線直通特急「富士回遊」約1時間55分→河口湖駅→富士急バス「天下茶屋線」約25分→三つ峠登山口バス停</t>
         </is>
       </c>
       <c r="J152" s="41" t="n">
         <v>170</v>
       </c>
       <c r="K152" s="41" t="n">
-        <v>5230</v>
+        <v>5216</v>
       </c>
       <c r="L152" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR中央線・富士急行線直通特急「富士回遊」]--&gt; 河口湖駅 --[富士急バス「天下茶屋線」]--&gt; 三つ峠登山口バス停</t>
+          <t>横浜駅→JR湘南新宿ライン約34分→新宿駅→JR中央線・富士急行線直通特急「富士回遊」約1時間55分→河口湖駅→富士急バス「天下茶屋線」約25分→三つ峠登山口バス停</t>
         </is>
       </c>
       <c r="M152" s="41" t="n">
         <v>174</v>
       </c>
       <c r="N152" s="41" t="n">
-        <v>5230</v>
+        <v>5216</v>
       </c>
     </row>
     <row r="153" ht="26.25" customHeight="1" s="30">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="E38" s="44" t="inlineStr">
         <is>
-          <t>高速バス「さわやか信州号」</t>
+          <t>JR特急あずさ・松本電鉄上高地線・アルピコ交通バス</t>
         </is>
       </c>
       <c r="F38" s="49" t="inlineStr">
@@ -17540,12 +17540,12 @@
       </c>
       <c r="K38" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L38" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>2026-10-07 新島々〜中の湯2,400円（2026年4月17日改定の運賃表）</t>
         </is>
       </c>
     </row>
@@ -17600,12 +17600,12 @@
       </c>
       <c r="K39" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L39" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>2026-10-07 70系統 長野駅〜飯綱登山口 47分・950円。2026年ダイヤは戸隠中社止まり</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17690,7 @@
       </c>
       <c r="E41" s="44" t="inlineStr">
         <is>
-          <t>JR湘南新宿ライン・東海道線・身延線・富士急静岡バス「新富士線」</t>
+          <t>富士急バス（新富士線・富士山駅行き）</t>
         </is>
       </c>
       <c r="F41" s="49" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="K41" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L41" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>2026-10-07 事業者表記を富士急静岡バス→富士急バス（新富士線）に修正。1,080円・32分・1日3便</t>
         </is>
       </c>
     </row>
@@ -18200,12 +18200,12 @@
       </c>
       <c r="K49" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L49" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>2026-10-07 運賃は電車代のみに変更（タクシーは注記）</t>
         </is>
       </c>
     </row>
@@ -18230,12 +18230,12 @@
       </c>
       <c r="E50" s="44" t="inlineStr">
         <is>
-          <t>アルピコ交通バス「戸隠線」</t>
+          <t>JR北陸新幹線・アルピコ交通「観光特急戸隠線」</t>
         </is>
       </c>
       <c r="F50" s="49" t="inlineStr">
         <is>
-          <t>https://www.alpico.co.jp/traffic/local/nagano/togakushi/</t>
+          <t>https://www.alpico.co.jp/traffic/express/express_togakushi/</t>
         </is>
       </c>
       <c r="G50" s="47" t="inlineStr">
@@ -18260,12 +18260,12 @@
       </c>
       <c r="K50" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L50" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>2026-10-07 70系統は戸隠中社止まりのため観光特急戸隠線（予約制・2,500円・65分、4/1〜12/4予定）に修正</t>
         </is>
       </c>
     </row>
@@ -18440,12 +18440,12 @@
       </c>
       <c r="K53" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L53" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>2026-10-07 行き先を美ヶ原自然保護センターに修正。1,500円・80分・1日2便</t>
         </is>
       </c>
     </row>
@@ -19460,12 +19460,12 @@
       </c>
       <c r="K70" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L70" s="44" t="inlineStr">
         <is>
-          <t>本セッションで会社名/リンクの不一致を発見・修正済み</t>
+          <t>本セッションで会社名/リンクの不一致を発見・修正済み ｜2026-10-07 新松田からは関本乗り継ぎ（直通なし）。地蔵堂行きは本数僅少（10/1改正）</t>
         </is>
       </c>
     </row>
@@ -19940,12 +19940,12 @@
       </c>
       <c r="K78" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L78" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>2026-10-07 バス530円・23分</t>
         </is>
       </c>
     </row>
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E80" s="44" t="inlineStr">
         <is>
-          <t>富士急行線</t>
+          <t>JR中央線・富士急行線・富士急バス「ふじっ湖号」</t>
         </is>
       </c>
       <c r="F80" s="49" t="inlineStr">
         <is>
-          <t>https://www.fujikyubus.co.jp/regular/</t>
+          <t>https://www.fujikyubus.co.jp/fujikko</t>
         </is>
       </c>
       <c r="G80" s="47" t="inlineStr">
@@ -20060,12 +20060,12 @@
       </c>
       <c r="K80" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L80" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>2026-10-07 ふじっ湖号 河口湖駅〜山中湖平野 1,050円・55分</t>
         </is>
       </c>
     </row>
@@ -20180,12 +20180,12 @@
       </c>
       <c r="K82" s="47" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="L82" s="44" t="inlineStr">
         <is>
-          <t>グループ8検証で経路再構築・会社名/リンク確認済み ｜2026-09-25 バス25分・840円に修正（大宮・横浜発も河口湖駅経由に統一）</t>
+          <t>グループ8検証で経路再構築・会社名/リンク確認済み ｜2026-09-25 バス25分・840円に修正（大宮・横浜発も河口湖駅経由に統一） ｜2026-10-07 運賃840円を再確認。10月1日改正後の時刻は未確認</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K416"/>
+  <dimension ref="A1:K441"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -47125,6 +47125,1381 @@
         </is>
       </c>
       <c r="K416" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="53" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C417" s="53" t="inlineStr">
+        <is>
+          <t>taiheizan</t>
+        </is>
+      </c>
+      <c r="D417" s="54" t="inlineStr">
+        <is>
+          <t>太平山</t>
+        </is>
+      </c>
+      <c r="E417" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F417" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G417" s="55" t="inlineStr">
+        <is>
+          <t>3,100／2,730／3,716円</t>
+        </is>
+      </c>
+      <c r="H417" s="55" t="inlineStr">
+        <is>
+          <t>1,595／1,221／2,420円（JR。小山で両毛線に乗換）</t>
+        </is>
+      </c>
+      <c r="I417" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（JRのみ・小山経由）：→栃木</t>
+        </is>
+      </c>
+      <c r="J417" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K417" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="53" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C418" s="53" t="inlineStr">
+        <is>
+          <t>nokogiriyama_chiba</t>
+        </is>
+      </c>
+      <c r="D418" s="54" t="inlineStr">
+        <is>
+          <t>鋸山</t>
+        </is>
+      </c>
+      <c r="E418" s="54" t="inlineStr">
+        <is>
+          <t>運賃・所要時間の検算</t>
+        </is>
+      </c>
+      <c r="F418" s="54" t="inlineStr">
+        <is>
+          <t>新宿・横浜発</t>
+        </is>
+      </c>
+      <c r="G418" s="55" t="inlineStr">
+        <is>
+          <t>1,980／2,420／2,310円。横浜→浜金谷110分</t>
+        </is>
+      </c>
+      <c r="H418" s="55" t="inlineStr">
+        <is>
+          <t>2,090／2,420／2,420円。大宮178分、横浜157分</t>
+        </is>
+      </c>
+      <c r="I418" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（JRのみ）：→浜金谷</t>
+        </is>
+      </c>
+      <c r="J418" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K418" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="53" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C419" s="53" t="inlineStr">
+        <is>
+          <t>嵐山・官ノ倉山・宝登山・破風山・古賀志山</t>
+        </is>
+      </c>
+      <c r="D419" s="54" t="inlineStr">
+        <is>
+          <t>東武東上線・秩父鉄道・宇都宮の5山</t>
+        </is>
+      </c>
+      <c r="E419" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F419" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G419" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H419" s="55" t="inlineStr">
+        <is>
+          <t>現行の額で整合（古賀志山は宇都宮まで 2,090／1,408／2,420＋バス640。宝登山・破風山の新宿発だけ未照合）</t>
+        </is>
+      </c>
+      <c r="I419" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報</t>
+        </is>
+      </c>
+      <c r="J419" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K419" s="57" t="inlineStr">
+        <is>
+          <t>高〜中</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="53" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C420" s="53" t="inlineStr">
+        <is>
+          <t>asama</t>
+        </is>
+      </c>
+      <c r="D420" s="54" t="inlineStr">
+        <is>
+          <t>浅間山</t>
+        </is>
+      </c>
+      <c r="E420" s="54" t="inlineStr">
+        <is>
+          <t>経路の誤り・運賃</t>
+        </is>
+      </c>
+      <c r="F420" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G420" s="55" t="inlineStr">
+        <is>
+          <t>佐久平駅→しなの鉄道22分→小諸駅→バス34分（佐久平はしなの鉄道の駅ではない）。6,325／7,635円</t>
+        </is>
+      </c>
+      <c r="H420" s="55" t="inlineStr">
+        <is>
+          <t>佐久平駅→JRバス関東 高峰高原線 54分→車坂峠。6,510／7,820円（新幹線自由席＋バス1,450）</t>
+        </is>
+      </c>
+      <c r="I420" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→佐久平 5,060／6,370、NAVITIME（佐久平駅→高峰高原ホテル前 1,450円・54分）</t>
+        </is>
+      </c>
+      <c r="J420" s="55" t="inlineStr">
+        <is>
+          <t>新幹線＋1,450</t>
+        </is>
+      </c>
+      <c r="K420" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="53" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C421" s="53" t="inlineStr">
+        <is>
+          <t>shirasunayama</t>
+        </is>
+      </c>
+      <c r="D421" s="54" t="inlineStr">
+        <is>
+          <t>白砂山</t>
+        </is>
+      </c>
+      <c r="E421" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F421" s="54" t="inlineStr">
+        <is>
+          <t>大宮・横浜発</t>
+        </is>
+      </c>
+      <c r="G421" s="55" t="inlineStr">
+        <is>
+          <t>大宮5,550円・横浜5,550円（同額）</t>
+        </is>
+      </c>
+      <c r="H421" s="55" t="inlineStr">
+        <is>
+          <t>大宮5,500円・横浜5,590円（新宿発4,970円＋新宿までのJR 530円・620円）</t>
+        </is>
+      </c>
+      <c r="I421" s="56" t="inlineStr">
+        <is>
+          <t>既存の高速バス・町営バス運賃＋JR</t>
+        </is>
+      </c>
+      <c r="J421" s="55" t="inlineStr">
+        <is>
+          <t>4,970＋530／＋620</t>
+        </is>
+      </c>
+      <c r="K421" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="53" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C422" s="53" t="inlineStr">
+        <is>
+          <t>tsukuba</t>
+        </is>
+      </c>
+      <c r="D422" s="54" t="inlineStr">
+        <is>
+          <t>筑波山</t>
+        </is>
+      </c>
+      <c r="E422" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F422" s="54" t="inlineStr">
+        <is>
+          <t>横浜発</t>
+        </is>
+      </c>
+      <c r="G422" s="55" t="inlineStr">
+        <is>
+          <t>横浜 2,608円</t>
+        </is>
+      </c>
+      <c r="H422" s="55" t="inlineStr">
+        <is>
+          <t>横浜 2,666円（JR秋葉原まで616＋TX1,280＋バス770）。新宿2,259円・大宮2,299円は一致</t>
+        </is>
+      </c>
+      <c r="I422" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報、関東鉄道（筑波山シャトル770円）</t>
+        </is>
+      </c>
+      <c r="J422" s="55" t="inlineStr">
+        <is>
+          <t>電車＋770</t>
+        </is>
+      </c>
+      <c r="K422" s="57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="53" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C423" s="53" t="inlineStr">
+        <is>
+          <t>kintoki・kasagatake</t>
+        </is>
+      </c>
+      <c r="D423" s="54" t="inlineStr">
+        <is>
+          <t>金時山・笠ヶ岳</t>
+        </is>
+      </c>
+      <c r="E423" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F423" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G423" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H423" s="55" t="inlineStr">
+        <is>
+          <t>大宮・横浜発は新宿までのJRを足す計算で整合。高速バスの運賃そのものは注記の値で未再確認</t>
+        </is>
+      </c>
+      <c r="I423" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J423" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K423" s="57" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="53" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C424" s="53" t="inlineStr">
+        <is>
+          <t>keizandake</t>
+        </is>
+      </c>
+      <c r="D424" s="54" t="inlineStr">
+        <is>
+          <t>経ヶ岳</t>
+        </is>
+      </c>
+      <c r="E424" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F424" s="54" t="inlineStr">
+        <is>
+          <t>新宿発</t>
+        </is>
+      </c>
+      <c r="G424" s="55" t="inlineStr">
+        <is>
+          <t>6,730／6,730／6,730円（3出発地同額。新宿発はバス代が入っていなかった）</t>
+        </is>
+      </c>
+      <c r="H424" s="55" t="inlineStr">
+        <is>
+          <t>7,040／6,730／6,730円（JR＋伊那バス310）。大宮は立川、横浜は八王子乗車で特急料金が2,240円になるため新宿発より安い</t>
+        </is>
+      </c>
+      <c r="I424" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報：→伊那市 新宿6,730（4,180＋2,550）、横浜6,420（4,180＋2,240）、大宮は立川経由で乗車券4,180</t>
+        </is>
+      </c>
+      <c r="J424" s="55" t="inlineStr">
+        <is>
+          <t>JR＋310</t>
+        </is>
+      </c>
+      <c r="K424" s="57" t="inlineStr">
+        <is>
+          <t>高（大宮の特急料金は区間距離からの判断）</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="53" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" s="53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C425" s="53" t="inlineStr">
+        <is>
+          <t>御座山・明神ヶ岳・生藤山 ほか5山</t>
+        </is>
+      </c>
+      <c r="D425" s="54" t="inlineStr">
+        <is>
+          <t>御座山・明神ヶ岳・生藤山・九鬼山・高尾山・草戸山・小金沢山・塩見岳</t>
+        </is>
+      </c>
+      <c r="E425" s="54" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F425" s="54" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G425" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H425" s="55" t="inlineStr">
+        <is>
+          <t>現行の額で整合（小海まで 新宿6,420・大宮5,390・横浜6,700＋村営バス100／小田原まで 小田急901・JR横浜1,034＋バス790／上野原まで 1,034・1,408・1,221）。九鬼山ほか5山は以前の引き直しで確認済み</t>
+        </is>
+      </c>
+      <c r="I425" s="56" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報</t>
+        </is>
+      </c>
+      <c r="J425" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K425" s="57" t="inlineStr">
+        <is>
+          <t>高（生藤山のバス運賃は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="29" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C426" s="29" t="inlineStr">
+        <is>
+          <t>yakedake</t>
+        </is>
+      </c>
+      <c r="D426" s="29" t="inlineStr">
+        <is>
+          <t>焼岳</t>
+        </is>
+      </c>
+      <c r="E426" s="29" t="inlineStr">
+        <is>
+          <t>バス運賃の確定・経路を上高地アクセスに統一</t>
+        </is>
+      </c>
+      <c r="F426" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G426" s="29" t="inlineStr">
+        <is>
+          <t>8,900／8,590／8,900円</t>
+        </is>
+      </c>
+      <c r="H426" s="29" t="inlineStr">
+        <is>
+          <t>9,840／9,530／9,530円（235／280／286分）</t>
+        </is>
+      </c>
+      <c r="I426" s="29" t="inlineStr">
+        <is>
+          <t>アルピコ交通 上高地線運賃表（2026年4月17日改定）新島々〜中の湯2,400円／Yahoo!路線情報</t>
+        </is>
+      </c>
+      <c r="J426" s="29" t="inlineStr">
+        <is>
+          <t>新島々まで7,440・7,130・7,130＋2,400</t>
+        </is>
+      </c>
+      <c r="K426" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="29" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C427" s="29" t="inlineStr">
+        <is>
+          <t>iizunasan</t>
+        </is>
+      </c>
+      <c r="D427" s="29" t="inlineStr">
+        <is>
+          <t>飯縄山</t>
+        </is>
+      </c>
+      <c r="E427" s="29" t="inlineStr">
+        <is>
+          <t>バス運賃の確定</t>
+        </is>
+      </c>
+      <c r="F427" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G427" s="29" t="inlineStr">
+        <is>
+          <t>8,760／6,860／9,200円</t>
+        </is>
+      </c>
+      <c r="H427" s="29" t="inlineStr">
+        <is>
+          <t>7,770／7,110／9,310円（162／129／171分）</t>
+        </is>
+      </c>
+      <c r="I427" s="29" t="inlineStr">
+        <is>
+          <t>NAVITIME（70系統 長野駅〜飯綱登山口 47分・950円）／アルピコ交通 2026年ダイヤ・運賃表（2023年4月1日改定）</t>
+        </is>
+      </c>
+      <c r="J427" s="29" t="inlineStr">
+        <is>
+          <t>長野まで6,820・6,160・8,360＋950</t>
+        </is>
+      </c>
+      <c r="K427" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="29" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C428" s="29" t="inlineStr">
+        <is>
+          <t>takatsuma</t>
+        </is>
+      </c>
+      <c r="D428" s="29" t="inlineStr">
+        <is>
+          <t>高妻山</t>
+        </is>
+      </c>
+      <c r="E428" s="29" t="inlineStr">
+        <is>
+          <t>経路の修正（70系統は戸隠中社止まり→観光特急）・運賃</t>
+        </is>
+      </c>
+      <c r="F428" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G428" s="29" t="inlineStr">
+        <is>
+          <t>8,060／6,160／8,500円</t>
+        </is>
+      </c>
+      <c r="H428" s="29" t="inlineStr">
+        <is>
+          <t>9,320／8,660／10,860円（180／141／189分）</t>
+        </is>
+      </c>
+      <c r="I428" s="29" t="inlineStr">
+        <is>
+          <t>アルピコ交通 観光特急戸隠線 2026年4月1日〜12月4日（予定）時刻表・NAVITIME（特急2,500円・65分）</t>
+        </is>
+      </c>
+      <c r="J428" s="29" t="inlineStr">
+        <is>
+          <t>長野まで6,820・6,160・8,360＋2,500</t>
+        </is>
+      </c>
+      <c r="K428" s="29" t="inlineStr">
+        <is>
+          <t>高（運賃表は画像のため金額はNAVITIMEと検索結果の2系統で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="29" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C429" s="29" t="inlineStr">
+        <is>
+          <t>utsukushigahara</t>
+        </is>
+      </c>
+      <c r="D429" s="29" t="inlineStr">
+        <is>
+          <t>美ヶ原</t>
+        </is>
+      </c>
+      <c r="E429" s="29" t="inlineStr">
+        <is>
+          <t>JR運賃の引き直し・バスの行き先と時間</t>
+        </is>
+      </c>
+      <c r="F429" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G429" s="29" t="inlineStr">
+        <is>
+          <t>8,000／7,690／7,690円</t>
+        </is>
+      </c>
+      <c r="H429" s="29" t="inlineStr">
+        <is>
+          <t>8,230／7,920／7,920円（230／275／281分）</t>
+        </is>
+      </c>
+      <c r="I429" s="29" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報 新宿→松本6,730／松本市観光サイト・直行バス公式（1,500円、8:15→9:35）</t>
+        </is>
+      </c>
+      <c r="J429" s="29" t="inlineStr">
+        <is>
+          <t>松本まで6,730・6,420・6,420＋1,500</t>
+        </is>
+      </c>
+      <c r="K429" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="29" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C430" s="29" t="inlineStr">
+        <is>
+          <t>ishiwariyama</t>
+        </is>
+      </c>
+      <c r="D430" s="29" t="inlineStr">
+        <is>
+          <t>石割山</t>
+        </is>
+      </c>
+      <c r="E430" s="29" t="inlineStr">
+        <is>
+          <t>経路の修正（特急なしの検証済み経路）・バス運賃の確定</t>
+        </is>
+      </c>
+      <c r="F430" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G430" s="29" t="inlineStr">
+        <is>
+          <t>4,339／4,529／4,529円</t>
+        </is>
+      </c>
+      <c r="H430" s="29" t="inlineStr">
+        <is>
+          <t>3,619／3,806／3,806円（218／234／226分）</t>
+        </is>
+      </c>
+      <c r="I430" s="29" t="inlineStr">
+        <is>
+          <t>富士急バス ふじっ湖号運賃表（2026年）河口湖駅〜山中湖平野1,050円／NAVITIME 55分</t>
+        </is>
+      </c>
+      <c r="J430" s="29" t="inlineStr">
+        <is>
+          <t>河口湖まで2,569・2,756・2,756＋1,050</t>
+        </is>
+      </c>
+      <c r="K430" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="29" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C431" s="29" t="inlineStr">
+        <is>
+          <t>mitsutoge</t>
+        </is>
+      </c>
+      <c r="D431" s="29" t="inlineStr">
+        <is>
+          <t>三ツ峠山</t>
+        </is>
+      </c>
+      <c r="E431" s="29" t="inlineStr">
+        <is>
+          <t>バス運賃の確定</t>
+        </is>
+      </c>
+      <c r="F431" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G431" s="29" t="inlineStr">
+        <is>
+          <t>5,040／5,230／5,230円</t>
+        </is>
+      </c>
+      <c r="H431" s="29" t="inlineStr">
+        <is>
+          <t>5,029／5,216／5,216円（140／170／174分）</t>
+        </is>
+      </c>
+      <c r="I431" s="29" t="inlineStr">
+        <is>
+          <t>NAVITIME（天下茶屋線 河口湖駅〜三ッ峠登山口 25分・840円）</t>
+        </is>
+      </c>
+      <c r="J431" s="29" t="inlineStr">
+        <is>
+          <t>富士回遊4,189（大宮・横浜は4,376）＋840</t>
+        </is>
+      </c>
+      <c r="K431" s="29" t="inlineStr">
+        <is>
+          <t>中（富士急の古いモデルコースのページは730円表記。10月1日改正後の時刻は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="29" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C432" s="29" t="inlineStr">
+        <is>
+          <t>naeba</t>
+        </is>
+      </c>
+      <c r="D432" s="29" t="inlineStr">
+        <is>
+          <t>苗場山</t>
+        </is>
+      </c>
+      <c r="E432" s="29" t="inlineStr">
+        <is>
+          <t>運賃からタクシー概算を除外</t>
+        </is>
+      </c>
+      <c r="F432" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G432" s="29" t="inlineStr">
+        <is>
+          <t>9,800／9,020／9,520円</t>
+        </is>
+      </c>
+      <c r="H432" s="29" t="inlineStr">
+        <is>
+          <t>6,160／5,830／7,030円（143／104／146分）</t>
+        </is>
+      </c>
+      <c r="I432" s="29" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（越後湯沢まで）</t>
+        </is>
+      </c>
+      <c r="J432" s="29" t="inlineStr">
+        <is>
+          <t>電車代のみ。タクシー約4,000円/台は注記に分離</t>
+        </is>
+      </c>
+      <c r="K432" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="29" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C433" s="29" t="inlineStr">
+        <is>
+          <t>koubousan</t>
+        </is>
+      </c>
+      <c r="D433" s="29" t="inlineStr">
+        <is>
+          <t>弘法山</t>
+        </is>
+      </c>
+      <c r="E433" s="29" t="inlineStr">
+        <is>
+          <t>横浜発の降車駅を秦野駅に統一・運賃</t>
+        </is>
+      </c>
+      <c r="F433" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G433" s="29" t="inlineStr">
+        <is>
+          <t>692／1,220／600円</t>
+        </is>
+      </c>
+      <c r="H433" s="29" t="inlineStr">
+        <is>
+          <t>692／1,220／617円（95／125／84分）</t>
+        </is>
+      </c>
+      <c r="I433" s="29" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報 横浜→秦野 617円・59分</t>
+        </is>
+      </c>
+      <c r="J433" s="29" t="inlineStr">
+        <is>
+          <t>相鉄＋小田急の通し</t>
+        </is>
+      </c>
+      <c r="K433" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="29" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C434" s="29" t="inlineStr">
+        <is>
+          <t>yaguradake</t>
+        </is>
+      </c>
+      <c r="D434" s="29" t="inlineStr">
+        <is>
+          <t>矢倉岳</t>
+        </is>
+      </c>
+      <c r="E434" s="29" t="inlineStr">
+        <is>
+          <t>バス運賃の確定・乗り継ぎの明記</t>
+        </is>
+      </c>
+      <c r="F434" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G434" s="29" t="inlineStr">
+        <is>
+          <t>1,536／2,064／2,010円</t>
+        </is>
+      </c>
+      <c r="H434" s="29" t="inlineStr">
+        <is>
+          <t>1,806／2,334／1,924円（127／157／132分）</t>
+        </is>
+      </c>
+      <c r="I434" s="29" t="inlineStr">
+        <is>
+          <t>NAVITIME 新松田→関本→地蔵堂1,010円・47分／大雄山駅→地蔵堂580円・28分、Yahoo!路線情報 横浜→小田原1,034＋大雄山線310、箱根登山バス時刻表（2026年10月1日改正）</t>
+        </is>
+      </c>
+      <c r="J434" s="29" t="inlineStr">
+        <is>
+          <t>796＋1,010／＋528／1,034＋310＋580</t>
+        </is>
+      </c>
+      <c r="K434" s="29" t="inlineStr">
+        <is>
+          <t>高（直通と書いていた注記は誤りだった）</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="29" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C435" s="29" t="inlineStr">
+        <is>
+          <t>ohnoyama</t>
+        </is>
+      </c>
+      <c r="D435" s="29" t="inlineStr">
+        <is>
+          <t>大野山</t>
+        </is>
+      </c>
+      <c r="E435" s="29" t="inlineStr">
+        <is>
+          <t>横浜発の運賃</t>
+        </is>
+      </c>
+      <c r="F435" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G435" s="29" t="inlineStr">
+        <is>
+          <t>986／1,514／1,446円</t>
+        </is>
+      </c>
+      <c r="H435" s="29" t="inlineStr">
+        <is>
+          <t>986／1,514／1,220円（106／136／90分）</t>
+        </is>
+      </c>
+      <c r="I435" s="29" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報 新宿→山北986（796＋190）、横浜→山北 国府津経由1,220</t>
+        </is>
+      </c>
+      <c r="J435" s="29" t="inlineStr">
+        <is>
+          <t>JR通し</t>
+        </is>
+      </c>
+      <c r="K435" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="29" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C436" s="29" t="inlineStr">
+        <is>
+          <t>sengenrei</t>
+        </is>
+      </c>
+      <c r="D436" s="29" t="inlineStr">
+        <is>
+          <t>浅間嶺</t>
+        </is>
+      </c>
+      <c r="E436" s="29" t="inlineStr">
+        <is>
+          <t>バス運賃の確定・JR運賃の引き直し</t>
+        </is>
+      </c>
+      <c r="F436" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G436" s="29" t="inlineStr">
+        <is>
+          <t>1,440／1,570／1,760円</t>
+        </is>
+      </c>
+      <c r="H436" s="29" t="inlineStr">
+        <is>
+          <t>1,432／1,564／1,751円（103／129／145分）</t>
+        </is>
+      </c>
+      <c r="I436" s="29" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報 →武蔵五日市 902／1,034／1,221、NAVITIME 武蔵五日市駅→払沢の滝入口530円・23分</t>
+        </is>
+      </c>
+      <c r="J436" s="29" t="inlineStr">
+        <is>
+          <t>JR＋530</t>
+        </is>
+      </c>
+      <c r="K436" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="29" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C437" s="29" t="inlineStr">
+        <is>
+          <t>aizu_koma</t>
+        </is>
+      </c>
+      <c r="D437" s="29" t="inlineStr">
+        <is>
+          <t>会津駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E437" s="29" t="inlineStr">
+        <is>
+          <t>運賃の検算（リバティ会津直通の額）・バス運賃の確定</t>
+        </is>
+      </c>
+      <c r="F437" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G437" s="29" t="inlineStr">
+        <is>
+          <t>8,750／9,360／9,950円</t>
+        </is>
+      </c>
+      <c r="H437" s="29" t="inlineStr">
+        <is>
+          <t>8,573／7,940／8,860円（320／305／370分）</t>
+        </is>
+      </c>
+      <c r="I437" s="29" t="inlineStr">
+        <is>
+          <t>会津バス公式検索 会津田島駅→駒ヶ岳登山口2,330円・88分／Yahoo!路線情報 リバティ会津113号 新宿6,243・大宮5,610・横浜6,530</t>
+        </is>
+      </c>
+      <c r="J437" s="29" t="inlineStr">
+        <is>
+          <t>鉄道＋2,330</t>
+        </is>
+      </c>
+      <c r="K437" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="29" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C438" s="29" t="inlineStr">
+        <is>
+          <t>kenashiyama</t>
+        </is>
+      </c>
+      <c r="D438" s="29" t="inlineStr">
+        <is>
+          <t>毛無山</t>
+        </is>
+      </c>
+      <c r="E438" s="29" t="inlineStr">
+        <is>
+          <t>運賃の検算</t>
+        </is>
+      </c>
+      <c r="F438" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G438" s="29" t="inlineStr">
+        <is>
+          <t>4,400／5,170／4,030円</t>
+        </is>
+      </c>
+      <c r="H438" s="29" t="inlineStr">
+        <is>
+          <t>3,830／4,600／3,460円（234／249／189分）</t>
+        </is>
+      </c>
+      <c r="I438" s="29" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報 →富士宮 2,750／3,520／2,380、NAVITIME 富士宮駅→朝霧高原1,080円・32分</t>
+        </is>
+      </c>
+      <c r="J438" s="29" t="inlineStr">
+        <is>
+          <t>JR＋1,080</t>
+        </is>
+      </c>
+      <c r="K438" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>makihata</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>巻機山</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>運賃からMOSS（距離別・未確定）を除外</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>7,380／6,720／8,920円</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>7,080／6,420／8,620円（121／105／147分）</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>南魚沼市 MOSS（距離別300〜1,000円、月〜金8:30〜17:30）／Yahoo!路線情報 浦佐経由 7,080・6,420・8,620</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>六日町駅までの電車代のみ</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>高（MOSSの清水乗降と距離区分は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>nakawarayama</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>和名倉山</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>運賃の検算（端数の修正）</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>2,080／2,250／2,600円</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>2,079／2,246／2,595円（204／177／242分）</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報 →三峰口 1,499／1,666／2,015＋西武観光バス580</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>鉄道＋580</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>karisaka</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>雁坂嶺</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）・バス所要時間60→63分</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>4,890／3,310／3,310円</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>4,890／3,310／3,310円（148／214／220分）</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報 →塩山 3,670／2,090／2,090、NAVITIME 塩山駅南口→西沢渓谷入口1,220円・63分</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>JR＋1,220</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
         <is>
           <t>高</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -8236,11 +8236,11 @@
       </c>
       <c r="L33" s="44" t="inlineStr">
         <is>
-          <t>横浜駅→JR東海道線約18分→東京駅→上越新幹線とき（越後湯沢の先まで延長）約1時間19分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」約40分→清水（桜坂駐車場）</t>
+          <t>横浜駅→JR東海道線約26分→東京駅→上越新幹線とき（越後湯沢の先まで延長）約1時間19分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」約40分→清水（桜坂駐車場）</t>
         </is>
       </c>
       <c r="M33" s="41" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="N33" s="41" t="n">
         <v>8620</v>
@@ -9026,33 +9026,33 @@
       </c>
       <c r="F47" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急かいじ]--&gt; 山梨市駅 --[山梨交通「西沢渓谷線」]--&gt; 乾徳山登山口（季節）</t>
+          <t>新宿駅→JR特急かいじ約1時間27分→山梨市駅→山梨市民バス「西沢渓谷線」約32分→乾徳山登山口</t>
         </is>
       </c>
       <c r="G47" s="41" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H47" s="41" t="n">
         <v>4400</v>
       </c>
       <c r="I47" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）]--&gt; 山梨市駅 --[山梨交通「西沢渓谷線」]--&gt; 乾徳山登山口（季節）</t>
+          <t>大宮駅→JR埼京線・武蔵野線・中央線（西国分寺・高尾乗換）約2時間37分→山梨市駅→山梨市民バス「西沢渓谷線」約32分→乾徳山登山口</t>
         </is>
       </c>
       <c r="J47" s="41" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K47" s="41" t="n">
         <v>2820</v>
       </c>
       <c r="L47" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR横浜線・中央線（八王子乗換）]--&gt; 山梨市駅 --[山梨交通「西沢渓谷線」]--&gt; 乾徳山登山口（季節）</t>
+          <t>横浜駅→JR横浜線・中央線（八王子乗換）約2時間43分→山梨市駅→山梨市民バス「西沢渓谷線」約32分→乾徳山登山口</t>
         </is>
       </c>
       <c r="M47" s="41" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N47" s="41" t="n">
         <v>2490</v>
@@ -9616,36 +9616,36 @@
       </c>
       <c r="F58" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[北陸新幹線あさま（東京駅乗換）]--&gt; 長野駅 --[長野電鉄]--&gt; 湯田中駅 --[長電バス]--&gt; 聖平入口（季節）</t>
+          <t>新宿駅→JR中央線快速約15分→東京駅→北陸新幹線あさま（東京駅乗換）約1時間40分→長野駅→長野電鉄 特急（特急料金100円）約45分→湯田中駅→長電バス「奥志賀高原線」約46分→一ノ瀬スキー場バス停</t>
         </is>
       </c>
       <c r="G58" s="41" t="n">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="H58" s="41" t="n">
-        <v>8800</v>
+        <v>10030</v>
       </c>
       <c r="I58" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[北陸新幹線あさま]--&gt; 長野駅 --[長野電鉄]--&gt; 湯田中駅 --[長電バス]--&gt; 聖平入口（季節運行）</t>
+          <t>大宮駅→北陸新幹線あさま約1時間22分→長野駅→長野電鉄 特急（特急料金100円）約45分→湯田中駅→長電バス「奥志賀高原線」約46分→一ノ瀬スキー場バス停</t>
         </is>
       </c>
       <c r="J58" s="41" t="n">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="K58" s="41" t="n">
-        <v>8272</v>
+        <v>9370</v>
       </c>
       <c r="L58" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR東海道線]--&gt; 東京駅 --[北陸新幹線あさま]--&gt; 長野駅 --[長野電鉄]--&gt; 湯田中駅 --[長電バス]--&gt; 聖平入口（季節）</t>
+          <t>横浜駅→JR東海道線約26分→東京駅→北陸新幹線あさま約1時間46分→長野駅→長野電鉄 特急（特急料金100円）約45分→湯田中駅→長電バス「奥志賀高原線」約46分→一ノ瀬スキー場バス停</t>
         </is>
       </c>
       <c r="M58" s="41" t="n">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="N58" s="41" t="n">
-        <v>8772</v>
+        <v>11570</v>
       </c>
     </row>
     <row r="59" ht="26.25" customHeight="1" s="30">
@@ -9696,11 +9696,11 @@
       </c>
       <c r="L59" s="44" t="inlineStr">
         <is>
-          <t>横浜駅→JR東海道線約18分→東京駅→北陸新幹線あさま約1時間46分→長野駅→アルピコ交通バス「戸隠線」約47分→飯綱登山口バス停（一ノ鳥居苑地）</t>
+          <t>横浜駅→JR東海道線約26分→東京駅→北陸新幹線あさま約1時間46分→長野駅→アルピコ交通バス「戸隠線」約47分→飯綱登山口バス停（一ノ鳥居苑地）</t>
         </is>
       </c>
       <c r="M59" s="41" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N59" s="41" t="n">
         <v>9310</v>
@@ -9906,36 +9906,36 @@
       </c>
       <c r="F63" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 七面山登山口・赤沢入口バス停 --[タクシー（所要時間は未確認）]--&gt; 羽衣登山口</t>
+          <t>新宿駅→JR特急あずさ・かいじ約1時間31分→甲府駅→JR身延線（乗換待ち含む）約1時間47分→身延駅→はやかわ乗合バス約20分→七面山登山口・赤沢入口バス停→タクシー（所要時間は未確認）→羽衣登山口</t>
         </is>
       </c>
       <c r="G63" s="41" t="n">
         <v>218</v>
       </c>
       <c r="H63" s="41" t="n">
-        <v>5520</v>
+        <v>5700</v>
       </c>
       <c r="I63" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 七面山登山口・赤沢入口バス停 --[タクシー（所要時間は未確認）]--&gt; 羽衣登山口</t>
+          <t>大宮駅→JR武蔵野線・中央線（立川乗換）約55分→立川駅→JR特急かいじ約1時間6分→甲府駅→JR身延線（乗換待ち含む）約1時間47分→身延駅→はやかわ乗合バス約20分→七面山登山口・赤沢入口バス停→タクシー（所要時間は未確認）→羽衣登山口</t>
         </is>
       </c>
       <c r="J63" s="41" t="n">
         <v>248</v>
       </c>
       <c r="K63" s="41" t="n">
-        <v>4960</v>
+        <v>5140</v>
       </c>
       <c r="L63" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[はやかわ乗合バス]--&gt; 七面山登山口・赤沢入口バス停 --[タクシー（所要時間は未確認）]--&gt; 羽衣登山口</t>
+          <t>横浜駅→JR湘南新宿ライン約34分→新宿駅→JR特急あずさ・かいじ約1時間31分→甲府駅→JR身延線（乗換待ち含む）約1時間47分→身延駅→はやかわ乗合バス約20分→七面山登山口・赤沢入口バス停→タクシー（所要時間は未確認）→羽衣登山口</t>
         </is>
       </c>
       <c r="M63" s="41" t="n">
         <v>252</v>
       </c>
       <c r="N63" s="41" t="n">
-        <v>5520</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="30">
@@ -10080,36 +10080,36 @@
       </c>
       <c r="F66" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 大島バス停 --[予約制乗合タクシー]--&gt; 老平登山口</t>
+          <t>新宿駅→JR特急あずさ・かいじ約1時間31分→甲府駅→JR身延線（乗換待ち含む）約1時間47分→身延駅→早川町乗合バス約40分→大島バス停→予約制乗合タクシー約20分→老平登山口</t>
         </is>
       </c>
       <c r="G66" s="41" t="n">
         <v>258</v>
       </c>
       <c r="H66" s="41" t="n">
-        <v>7520</v>
+        <v>5700</v>
       </c>
       <c r="I66" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR武蔵野線・中央線（立川乗換）]--&gt; 立川駅 --[JR特急かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 大島バス停 --[予約制乗合タクシー]--&gt; 老平登山口</t>
+          <t>大宮駅→JR武蔵野線・中央線（立川乗換）約55分→立川駅→JR特急かいじ約1時間6分→甲府駅→JR身延線（乗換待ち含む）約1時間47分→身延駅→早川町乗合バス約40分→大島バス停→予約制乗合タクシー約20分→老平登山口</t>
         </is>
       </c>
       <c r="J66" s="41" t="n">
         <v>288</v>
       </c>
       <c r="K66" s="41" t="n">
-        <v>6960</v>
+        <v>5140</v>
       </c>
       <c r="L66" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; 新宿駅 --[JR特急あずさ・かいじ]--&gt; 甲府駅 --[JR身延線（乗換待ち含む）]--&gt; 身延駅 --[早川町乗合バス]--&gt; 大島バス停 --[予約制乗合タクシー]--&gt; 老平登山口</t>
+          <t>横浜駅→JR湘南新宿ライン約34分→新宿駅→JR特急あずさ・かいじ約1時間31分→甲府駅→JR身延線（乗換待ち含む）約1時間47分→身延駅→早川町乗合バス約40分→大島バス停→予約制乗合タクシー約20分→老平登山口</t>
         </is>
       </c>
       <c r="M66" s="41" t="n">
         <v>292</v>
       </c>
       <c r="N66" s="41" t="n">
-        <v>7520</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="30">
@@ -10404,36 +10404,36 @@
       </c>
       <c r="F72" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線快速]--&gt; 東京駅 --[上越新幹線（東京駅乗換）]--&gt; 越後湯沢駅 --[JR上越線]--&gt; 小出駅 --[南越後観光バス]--&gt; 枝折峠登山口（バスは夏季6月下旬〜10月頃の1日1便のみ）</t>
+          <t>新宿駅→JR埼京線約26分→大宮駅→上越新幹線とき約55分→浦佐駅→JR上越線約10分→小出駅→南越後交通バス（2026年の運行は未確認）約1時間5分→枝折峠登山口</t>
         </is>
       </c>
       <c r="G72" s="41" t="n">
-        <v>215</v>
+        <v>156</v>
       </c>
       <c r="H72" s="41" t="n">
-        <v>7700</v>
+        <v>6820</v>
       </c>
       <c r="I72" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[上越新幹線とき（浦佐経由）]--&gt; 浦佐駅 --[JR上越線]--&gt; 小出駅 --[南越後観光バス]--&gt; 枝折峠登山口（夏季6月下旬〜10月頃の1日1便のみ）</t>
+          <t>大宮駅→上越新幹線とき約55分→浦佐駅→JR上越線約10分→小出駅→南越後交通バス（2026年の運行は未確認）約1時間5分→枝折峠登山口</t>
         </is>
       </c>
       <c r="J72" s="41" t="n">
         <v>130</v>
       </c>
       <c r="K72" s="41" t="n">
-        <v>7172</v>
+        <v>6490</v>
       </c>
       <c r="L72" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン直通]--&gt; 大宮駅 --[上越新幹線とき（浦佐経由）]--&gt; 浦佐駅 --[JR上越線]--&gt; 小出駅 --[南越後観光バス]--&gt; 枝折峠登山口（夏季1日1便）</t>
+          <t>横浜駅→JR東海道線約26分→東京駅→上越新幹線とき約1時間19分→浦佐駅→JR上越線約10分→小出駅→南越後交通バス（2026年の運行は未確認）約1時間5分→枝折峠登山口</t>
         </is>
       </c>
       <c r="M72" s="41" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="N72" s="41" t="n">
-        <v>8200</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="30">
@@ -10518,11 +10518,11 @@
       </c>
       <c r="L74" s="44" t="inlineStr">
         <is>
-          <t>横浜駅→JR東海道線約18分→東京駅→上越新幹線とき約1時間13分→越後湯沢駅→タクシー（路線バスなし）約25分→祓川登山口駐車場→徒歩（林道）約30分→祓川登山口</t>
+          <t>横浜駅→JR東海道線約26分→東京駅→上越新幹線とき約1時間13分→越後湯沢駅→タクシー（路線バスなし）約25分→祓川登山口駐車場→徒歩（林道）約30分→祓川登山口</t>
         </is>
       </c>
       <c r="M74" s="41" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N74" s="41" t="n">
         <v>7030</v>
@@ -10692,11 +10692,11 @@
       </c>
       <c r="L77" s="44" t="inlineStr">
         <is>
-          <t>横浜駅→JR東海道線約18分→東京駅→北陸新幹線あさま約1時間46分→長野駅→アルピコ交通「観光特急戸隠線」（予約制）約1時間5分→戸隠キャンプ場（高妻山登山口）</t>
+          <t>横浜駅→JR東海道線約26分→東京駅→北陸新幹線あさま約1時間46分→長野駅→アルピコ交通「観光特急戸隠線」（予約制）約1時間5分→戸隠キャンプ場（高妻山登山口）</t>
         </is>
       </c>
       <c r="M77" s="41" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="N77" s="41" t="n">
         <v>10860</v>
@@ -11110,36 +11110,36 @@
       </c>
       <c r="F85" s="44" t="inlineStr">
         <is>
-          <t>バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>バスタ新宿→高速バス約3時間40分→駒ヶ根駅→伊那バス・中央アルプス観光約25分→菅の台バスセンター</t>
         </is>
       </c>
       <c r="G85" s="41" t="n">
         <v>245</v>
       </c>
       <c r="H85" s="41" t="n">
-        <v>4200</v>
+        <v>4980</v>
       </c>
       <c r="I85" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>大宮駅→JR埼京線約30分→バスタ新宿→高速バス約3時間40分→駒ヶ根駅→伊那バス・中央アルプス観光約25分→菅の台バスセンター</t>
         </is>
       </c>
       <c r="J85" s="41" t="n">
         <v>275</v>
       </c>
       <c r="K85" s="41" t="n">
-        <v>4730</v>
+        <v>5508</v>
       </c>
       <c r="L85" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[伊那バス・中央アルプス観光]--&gt; 菅の台バスセンター</t>
+          <t>横浜駅→JR湘南新宿ライン約34分→バスタ新宿→高速バス約3時間40分→駒ヶ根駅→伊那バス・中央アルプス観光約25分→菅の台バスセンター</t>
         </is>
       </c>
       <c r="M85" s="41" t="n">
         <v>279</v>
       </c>
       <c r="N85" s="41" t="n">
-        <v>4820</v>
+        <v>5596</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="30">
@@ -11434,36 +11434,36 @@
       </c>
       <c r="F91" s="44" t="inlineStr">
         <is>
-          <t>バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー（易老渡まで入れる特定車両）]--&gt; 易老渡</t>
+          <t>バスタ新宿→高速バス(伊那バス/信南交通 新宿線)約4時間10分→飯田駅→信南交通「遠山郷線」約1時間23分→かぐらの湯（道の駅遠山郷）→予約制タクシー（易老渡まで入れる特定車両）約1時間20分→易老渡</t>
         </is>
       </c>
       <c r="G91" s="41" t="n">
         <v>413</v>
       </c>
       <c r="H91" s="41" t="n">
-        <v>24800</v>
+        <v>5700</v>
       </c>
       <c r="I91" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー（易老渡まで入れる特定車両）]--&gt; 易老渡</t>
+          <t>大宮駅→JR湘南新宿ライン約30分→バスタ新宿→高速バス(伊那バス/信南交通 新宿線)約4時間10分→飯田駅→信南交通「遠山郷線」約1時間23分→かぐらの湯（道の駅遠山郷）→予約制タクシー（易老渡まで入れる特定車両）約1時間20分→易老渡</t>
         </is>
       </c>
       <c r="J91" s="41" t="n">
         <v>443</v>
       </c>
       <c r="K91" s="41" t="n">
-        <v>25380</v>
+        <v>6228</v>
       </c>
       <c r="L91" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス(伊那バス/信南交通 新宿線)]--&gt; 飯田駅 --[信南交通「遠山郷線」]--&gt; かぐらの湯（道の駅遠山郷） --[予約制タクシー（易老渡まで入れる特定車両）]--&gt; 易老渡</t>
+          <t>横浜駅→JR湘南新宿ライン約34分→バスタ新宿→高速バス(伊那バス/信南交通 新宿線)約4時間10分→飯田駅→信南交通「遠山郷線」約1時間23分→かぐらの湯（道の駅遠山郷）→予約制タクシー（易老渡まで入れる特定車両）約1時間20分→易老渡</t>
         </is>
       </c>
       <c r="M91" s="41" t="n">
         <v>447</v>
       </c>
       <c r="N91" s="41" t="n">
-        <v>25380</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="30">
@@ -18125,27 +18125,27 @@
       </c>
       <c r="H48" s="47" t="inlineStr">
         <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I48" s="47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J48" s="47" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I48" s="47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J48" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="K48" s="47" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L48" s="44" t="inlineStr">
         <is>
-          <t>グループ8検証で経路再構築・会社名/リンク確認済み</t>
+          <t>2026-10-08 小出駅〜枝折峠のバスは事業者サイトの路線一覧に無い。公表は浦佐駅東口〜銀山平〜奥只見ダム（6/1〜11/3土日祝）。営業所への確認が必要</t>
         </is>
       </c>
     </row>
@@ -21020,12 +21020,12 @@
       </c>
       <c r="K96" s="47" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L96" s="44" t="inlineStr">
         <is>
-          <t>バス区間なし</t>
+          <t>2026-10-08 時刻表リンクを山梨市の市民バスのページに統一（旧：山梨交通の検索ページ）。山梨市駅〜乾徳山登山口400円・32分</t>
         </is>
       </c>
     </row>
@@ -21245,27 +21245,27 @@
       </c>
       <c r="H100" s="47" t="inlineStr">
         <is>
+          <t>N→修正済</t>
+        </is>
+      </c>
+      <c r="I100" s="47" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I100" s="47" t="inlineStr">
+      <c r="J100" s="47" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J100" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="K100" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L100" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>2026-10-08 降車バス停を一ノ瀬スキー場に修正（聖平入口は存在しない）。46分・1,450円</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24061,7 @@
       </c>
       <c r="F147" s="49" t="inlineStr">
         <is>
-          <t>https://tohyamago.com/archives/19377</t>
+          <t>https://www.shinnan.co.jp/sb/time_E1_02.html#link</t>
         </is>
       </c>
       <c r="G147" s="47" t="inlineStr">
@@ -24086,12 +24086,12 @@
       </c>
       <c r="K147" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L147" s="44" t="inlineStr">
         <is>
-          <t>グループ9でtrainAccess=falseから新規構築。会社名・リンク確認済み（季節運行バス多数、要現地最新確認）</t>
+          <t>2026-10-08 時刻表リンクを信南交通 遠山郷線（和田）に設定。飯田駅前〜かぐらの湯700円。平日朝は和田止まり（かぐらの湯まで徒歩12分）</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K441"/>
+  <dimension ref="A1:K452"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -48341,165 +48341,770 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="n">
+      <c r="A439" s="29" t="n">
         <v>438</v>
       </c>
-      <c r="B439" t="inlineStr">
+      <c r="B439" s="29" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr">
+      <c r="C439" s="29" t="inlineStr">
         <is>
           <t>makihata</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr">
+      <c r="D439" s="29" t="inlineStr">
         <is>
           <t>巻機山</t>
         </is>
       </c>
-      <c r="E439" t="inlineStr">
+      <c r="E439" s="29" t="inlineStr">
         <is>
           <t>運賃からMOSS（距離別・未確定）を除外</t>
         </is>
       </c>
-      <c r="F439" t="inlineStr">
+      <c r="F439" s="29" t="inlineStr">
         <is>
           <t>全出発地</t>
         </is>
       </c>
-      <c r="G439" t="inlineStr">
+      <c r="G439" s="29" t="inlineStr">
         <is>
           <t>7,380／6,720／8,920円</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr">
+      <c r="H439" s="29" t="inlineStr">
         <is>
           <t>7,080／6,420／8,620円（121／105／147分）</t>
         </is>
       </c>
-      <c r="I439" t="inlineStr">
+      <c r="I439" s="29" t="inlineStr">
         <is>
           <t>南魚沼市 MOSS（距離別300〜1,000円、月〜金8:30〜17:30）／Yahoo!路線情報 浦佐経由 7,080・6,420・8,620</t>
         </is>
       </c>
-      <c r="J439" t="inlineStr">
+      <c r="J439" s="29" t="inlineStr">
         <is>
           <t>六日町駅までの電車代のみ</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr">
+      <c r="K439" s="29" t="inlineStr">
         <is>
           <t>高（MOSSの清水乗降と距離区分は未確認）</t>
         </is>
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="n">
+      <c r="A440" s="29" t="n">
         <v>439</v>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B440" s="29" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
+      <c r="C440" s="29" t="inlineStr">
         <is>
           <t>nakawarayama</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr">
+      <c r="D440" s="29" t="inlineStr">
         <is>
           <t>和名倉山</t>
         </is>
       </c>
-      <c r="E440" t="inlineStr">
+      <c r="E440" s="29" t="inlineStr">
         <is>
           <t>運賃の検算（端数の修正）</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr">
+      <c r="F440" s="29" t="inlineStr">
         <is>
           <t>全出発地</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr">
+      <c r="G440" s="29" t="inlineStr">
         <is>
           <t>2,080／2,250／2,600円</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr">
+      <c r="H440" s="29" t="inlineStr">
         <is>
           <t>2,079／2,246／2,595円（204／177／242分）</t>
         </is>
       </c>
-      <c r="I440" t="inlineStr">
+      <c r="I440" s="29" t="inlineStr">
         <is>
           <t>Yahoo!路線情報 →三峰口 1,499／1,666／2,015＋西武観光バス580</t>
         </is>
       </c>
-      <c r="J440" t="inlineStr">
+      <c r="J440" s="29" t="inlineStr">
         <is>
           <t>鉄道＋580</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr">
+      <c r="K440" s="29" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="n">
+      <c r="A441" s="29" t="n">
         <v>440</v>
       </c>
-      <c r="B441" t="inlineStr">
+      <c r="B441" s="29" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr">
+      <c r="C441" s="29" t="inlineStr">
         <is>
           <t>karisaka</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr">
+      <c r="D441" s="29" t="inlineStr">
         <is>
           <t>雁坂嶺</t>
         </is>
       </c>
-      <c r="E441" t="inlineStr">
+      <c r="E441" s="29" t="inlineStr">
         <is>
           <t>運賃の検算（変更なし）・バス所要時間60→63分</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr">
+      <c r="F441" s="29" t="inlineStr">
         <is>
           <t>全出発地</t>
         </is>
       </c>
-      <c r="G441" t="inlineStr">
+      <c r="G441" s="29" t="inlineStr">
         <is>
           <t>4,890／3,310／3,310円</t>
         </is>
       </c>
-      <c r="H441" t="inlineStr">
+      <c r="H441" s="29" t="inlineStr">
         <is>
           <t>4,890／3,310／3,310円（148／214／220分）</t>
         </is>
       </c>
-      <c r="I441" t="inlineStr">
+      <c r="I441" s="29" t="inlineStr">
         <is>
           <t>Yahoo!路線情報 →塩山 3,670／2,090／2,090、NAVITIME 塩山駅南口→西沢渓谷入口1,220円・63分</t>
         </is>
       </c>
-      <c r="J441" t="inlineStr">
+      <c r="J441" s="29" t="inlineStr">
         <is>
           <t>JR＋1,220</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr">
+      <c r="K441" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="29" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C442" s="29" t="inlineStr">
+        <is>
+          <t>iwasugesan</t>
+        </is>
+      </c>
+      <c r="D442" s="29" t="inlineStr">
+        <is>
+          <t>岩菅山</t>
+        </is>
+      </c>
+      <c r="E442" s="29" t="inlineStr">
+        <is>
+          <t>経路の修正（聖平入口というバス停は無い→一ノ瀬スキー場）・運賃</t>
+        </is>
+      </c>
+      <c r="F442" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G442" s="29" t="inlineStr">
+        <is>
+          <t>8,800／8,272／8,772円</t>
+        </is>
+      </c>
+      <c r="H442" s="29" t="inlineStr">
+        <is>
+          <t>10,030／9,370／11,570円（206／173／223分）</t>
+        </is>
+      </c>
+      <c r="I442" s="29" t="inlineStr">
+        <is>
+          <t>長電バス 奥志賀高原線の停留所一覧（2026年4月7日改正）、NAVITIME 湯田中駅→一ノ瀬スキー場46分・1,450円、Yahoo!路線情報 長野→湯田中 特急1,760円</t>
+        </is>
+      </c>
+      <c r="J442" s="29" t="inlineStr">
+        <is>
+          <t>長野まで6,820・6,160・8,360＋1,760＋1,450</t>
+        </is>
+      </c>
+      <c r="K442" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="29" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C443" s="29" t="inlineStr">
+        <is>
+          <t>echigokoma</t>
+        </is>
+      </c>
+      <c r="D443" s="29" t="inlineStr">
+        <is>
+          <t>越後駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E443" s="29" t="inlineStr">
+        <is>
+          <t>バスの運行未確認を明記・運賃を電車代のみに・経路を浦佐乗換に統一</t>
+        </is>
+      </c>
+      <c r="F443" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G443" s="29" t="inlineStr">
+        <is>
+          <t>7,700／7,172／8,200円</t>
+        </is>
+      </c>
+      <c r="H443" s="29" t="inlineStr">
+        <is>
+          <t>6,820／6,490／8,800円（156／130／180分）</t>
+        </is>
+      </c>
+      <c r="I443" s="29" t="inlineStr">
+        <is>
+          <t>南越後交通バス 路線一覧と奥只見線時刻表（2026年6月1日改正）、Yahoo!路線情報 →小出 6,820・6,490・8,800</t>
+        </is>
+      </c>
+      <c r="J443" s="29" t="inlineStr">
+        <is>
+          <t>小出駅までの電車代のみ</t>
+        </is>
+      </c>
+      <c r="K443" s="29" t="inlineStr">
+        <is>
+          <t>中（枝折峠のバスの有無は営業所への確認が必要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="29" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C444" s="29" t="inlineStr">
+        <is>
+          <t>makihata・iizunasan・naeba・takatsuma・iwasugesan</t>
+        </is>
+      </c>
+      <c r="D444" s="29" t="inlineStr">
+        <is>
+          <t>巻機山・飯縄山・苗場山・高妻山・岩菅山</t>
+        </is>
+      </c>
+      <c r="E444" s="29" t="inlineStr">
+        <is>
+          <t>所要時間の修正</t>
+        </is>
+      </c>
+      <c r="F444" s="29" t="inlineStr">
+        <is>
+          <t>横浜発</t>
+        </is>
+      </c>
+      <c r="G444" s="29" t="inlineStr">
+        <is>
+          <t>横浜→東京 東海道線18分</t>
+        </is>
+      </c>
+      <c r="H444" s="29" t="inlineStr">
+        <is>
+          <t>26分（横浜発の合計が各8分増）</t>
+        </is>
+      </c>
+      <c r="I444" s="29" t="inlineStr">
+        <is>
+          <t>他の18山は24〜29分</t>
+        </is>
+      </c>
+      <c r="J444" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K444" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="29" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C445" s="29" t="inlineStr">
+        <is>
+          <t>iwasugesan</t>
+        </is>
+      </c>
+      <c r="D445" s="29" t="inlineStr">
+        <is>
+          <t>岩菅山</t>
+        </is>
+      </c>
+      <c r="E445" s="29" t="inlineStr">
+        <is>
+          <t>検索ページの表記修正</t>
+        </is>
+      </c>
+      <c r="F445" s="29" t="inlineStr">
+        <is>
+          <t>search 5ページ</t>
+        </is>
+      </c>
+      <c r="G445" s="29" t="inlineStr">
+        <is>
+          <t>湯田中駅→バス25分→聖平入口</t>
+        </is>
+      </c>
+      <c r="H445" s="29" t="inlineStr">
+        <is>
+          <t>湯田中駅→バス46分→一ノ瀬スキー場</t>
+        </is>
+      </c>
+      <c r="I445" s="29" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="J445" s="29" t="inlineStr">
+        <is>
+          <t>re.subn 5件</t>
+        </is>
+      </c>
+      <c r="K445" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="29" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C446" s="29" t="inlineStr">
+        <is>
+          <t>nanaitsurasan</t>
+        </is>
+      </c>
+      <c r="D446" s="29" t="inlineStr">
+        <is>
+          <t>七面山</t>
+        </is>
+      </c>
+      <c r="E446" s="29" t="inlineStr">
+        <is>
+          <t>運賃の検算・バス運賃の確定</t>
+        </is>
+      </c>
+      <c r="F446" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G446" s="29" t="inlineStr">
+        <is>
+          <t>5,520／4,960／5,520円</t>
+        </is>
+      </c>
+      <c r="H446" s="29" t="inlineStr">
+        <is>
+          <t>5,700／5,140／6,030円（218／248／252分）</t>
+        </is>
+      </c>
+      <c r="I446" s="29" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報 →身延 5,100／4,540（武蔵野線経由・立川乗車 3,520＋1,020）／5,430、早川町乗合バス運賃表 身延駅〜七面山登山口・赤沢入口600円</t>
+        </is>
+      </c>
+      <c r="J446" s="29" t="inlineStr">
+        <is>
+          <t>身延まで＋600（タクシー別）</t>
+        </is>
+      </c>
+      <c r="K446" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="29" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C447" s="29" t="inlineStr">
+        <is>
+          <t>yarigatake2</t>
+        </is>
+      </c>
+      <c r="D447" s="29" t="inlineStr">
+        <is>
+          <t>笊ヶ岳</t>
+        </is>
+      </c>
+      <c r="E447" s="29" t="inlineStr">
+        <is>
+          <t>運賃の検算（乗合タクシーの目安額を除外）</t>
+        </is>
+      </c>
+      <c r="F447" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G447" s="29" t="inlineStr">
+        <is>
+          <t>7,520／6,960／7,520円</t>
+        </is>
+      </c>
+      <c r="H447" s="29" t="inlineStr">
+        <is>
+          <t>5,700／5,140／6,030円（258／288／292分）</t>
+        </is>
+      </c>
+      <c r="I447" s="29" t="inlineStr">
+        <is>
+          <t>同上。身延駅〜大島600円</t>
+        </is>
+      </c>
+      <c r="J447" s="29" t="inlineStr">
+        <is>
+          <t>大島バス停まで。乗合タクシーは別（未確認）</t>
+        </is>
+      </c>
+      <c r="K447" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="29" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C448" s="29" t="inlineStr">
+        <is>
+          <t>utsugi</t>
+        </is>
+      </c>
+      <c r="D448" s="29" t="inlineStr">
+        <is>
+          <t>空木岳</t>
+        </is>
+      </c>
+      <c r="E448" s="29" t="inlineStr">
+        <is>
+          <t>路線バス運賃の確定・高速バスは最安額で表示</t>
+        </is>
+      </c>
+      <c r="F448" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G448" s="29" t="inlineStr">
+        <is>
+          <t>4,200／4,730／4,820円</t>
+        </is>
+      </c>
+      <c r="H448" s="29" t="inlineStr">
+        <is>
+          <t>4,580／5,108／5,196円（245／275／279分）</t>
+        </is>
+      </c>
+      <c r="I448" s="29" t="inlineStr">
+        <is>
+          <t>中央アルプス観光 路線バス運賃表 駒ヶ根駅前〜菅の台380円／高速バスは変動制（最安4,200円は比較サイト）</t>
+        </is>
+      </c>
+      <c r="J448" s="29" t="inlineStr">
+        <is>
+          <t>4,200＋380、大宮＋528、横浜＋616</t>
+        </is>
+      </c>
+      <c r="K448" s="29" t="inlineStr">
+        <is>
+          <t>中（高速バスは変動制）</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="29" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C449" s="29" t="inlineStr">
+        <is>
+          <t>arakawadake・akaisidake・hijiridade</t>
+        </is>
+      </c>
+      <c r="D449" s="29" t="inlineStr">
+        <is>
+          <t>荒川岳・赤石岳・聖岳</t>
+        </is>
+      </c>
+      <c r="E449" s="29" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）</t>
+        </is>
+      </c>
+      <c r="F449" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G449" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H449" s="29" t="inlineStr">
+        <is>
+          <t>10,940／11,300／10,180円で整合（静岡まで 新宿5,940・大宮6,300・横浜5,180＋静鉄バス5,000）</t>
+        </is>
+      </c>
+      <c r="I449" s="29" t="inlineStr">
+        <is>
+          <t>Yahoo!路線情報（ひかり自由席。大宮は上野東京ライン、横浜は横浜線で新横浜）</t>
+        </is>
+      </c>
+      <c r="J449" s="29" t="inlineStr">
+        <is>
+          <t>JR＋5,000</t>
+        </is>
+      </c>
+      <c r="K449" s="29" t="inlineStr">
+        <is>
+          <t>高（静鉄バス5,000円は既存の注記の額。2026年の告知ページは開けず再確認できていない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="29" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C450" s="29" t="inlineStr">
+        <is>
+          <t>kentoku</t>
+        </is>
+      </c>
+      <c r="D450" s="29" t="inlineStr">
+        <is>
+          <t>乾徳山</t>
+        </is>
+      </c>
+      <c r="E450" s="29" t="inlineStr">
+        <is>
+          <t>運賃の検算（変更なし）・バス所要時間30→32分・時刻表リンクの統一</t>
+        </is>
+      </c>
+      <c r="F450" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G450" s="29" t="inlineStr">
+        <is>
+          <t>4,400／2,820／2,490円（117／187／193分）</t>
+        </is>
+      </c>
+      <c r="H450" s="29" t="inlineStr">
+        <is>
+          <t>4,400／2,820／2,490円（119／189／195分）</t>
+        </is>
+      </c>
+      <c r="I450" s="29" t="inlineStr">
+        <is>
+          <t>山梨市 市民バス西沢渓谷線の料金表（平成30年7月1日改定、以後変更なし）山梨市駅〜乾徳山登山口400円／Yahoo!路線情報 →山梨市 4,000・2,420・2,090</t>
+        </is>
+      </c>
+      <c r="J450" s="29" t="inlineStr">
+        <is>
+          <t>JR＋400</t>
+        </is>
+      </c>
+      <c r="K450" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>terkari</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>光岳</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>運賃からタクシー概算を除外・時刻表リンク・注記</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>24,800／25,380／25,380円</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>5,700／6,228／6,316円（かぐらの湯まで。タクシー1台15,000〜20,000円は別）</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>遠山郷線700円（運営者確認）／京王バス 新宿〜伊那飯田線 運賃表（2025年9月1日現在）飯田駅前 月〜木5,000円</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>5,000＋700、大宮＋528、横浜＋616</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>451</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>utsugi</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>空木岳</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>高速バスを窓口運賃に修正</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>4,580／5,108／5,196円（最安4,200円で計算）</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>4,980／5,508／5,596円</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>京王バス 新宿〜伊那飯田線 運賃表 駒ヶ根 月〜木4,600円＋路線バス380円</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>4,600＋380、大宮＋528、横浜＋616</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
         <is>
           <t>高</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -8214,36 +8214,36 @@
       </c>
       <c r="F33" s="44" t="inlineStr">
         <is>
-          <t>新宿駅→JR埼京線約26分→大宮駅→上越新幹線とき約55分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」（平日のみ運行）約30分→清水（桜坂駐車場）</t>
+          <t>新宿駅→JR埼京線約26分→大宮駅→上越新幹線とき約55分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」（平日のみ・要予約）約30分→清水（桜坂駐車場）</t>
         </is>
       </c>
       <c r="G33" s="41" t="n">
         <v>121</v>
       </c>
       <c r="H33" s="41" t="n">
-        <v>7080</v>
+        <v>7580</v>
       </c>
       <c r="I33" s="44" t="inlineStr">
         <is>
-          <t>大宮駅→上越新幹線とき、越後湯沢の先まで延長)約55分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」約40分→清水（桜坂駐車場）</t>
+          <t>大宮駅→上越新幹線とき、越後湯沢の先まで延長)約55分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」（平日のみ・要予約）約30分→清水（桜坂駐車場）</t>
         </is>
       </c>
       <c r="J33" s="41" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="K33" s="41" t="n">
-        <v>6420</v>
+        <v>6920</v>
       </c>
       <c r="L33" s="44" t="inlineStr">
         <is>
-          <t>横浜駅→JR東海道線約26分→東京駅→上越新幹線とき（越後湯沢の先まで延長）約1時間19分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」約40分→清水（桜坂駐車場）</t>
+          <t>横浜駅→JR東海道線約26分→東京駅→上越新幹線とき（越後湯沢の先まで延長）約1時間19分→浦佐駅→JR上越線約10分→六日町駅→オンデマンド交通「MOSS」（平日のみ・要予約）約30分→清水（桜坂駐車場）</t>
         </is>
       </c>
       <c r="M33" s="41" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="N33" s="41" t="n">
-        <v>8620</v>
+        <v>9120</v>
       </c>
     </row>
     <row r="34" ht="51.75" customHeight="1" s="30">
@@ -10087,7 +10087,7 @@
         <v>258</v>
       </c>
       <c r="H66" s="41" t="n">
-        <v>5700</v>
+        <v>5900</v>
       </c>
       <c r="I66" s="44" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>288</v>
       </c>
       <c r="K66" s="41" t="n">
-        <v>5140</v>
+        <v>5340</v>
       </c>
       <c r="L66" s="44" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>292</v>
       </c>
       <c r="N66" s="41" t="n">
-        <v>6030</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="30">
@@ -10404,36 +10404,36 @@
       </c>
       <c r="F72" s="44" t="inlineStr">
         <is>
-          <t>新宿駅→JR埼京線約26分→大宮駅→上越新幹線とき約55分→浦佐駅→JR上越線約10分→小出駅→南越後交通バス（2026年の運行は未確認）約1時間5分→枝折峠登山口</t>
+          <t>新宿駅→JR埼京線約26分→大宮駅→上越新幹線とき約55分→浦佐駅→JR上越線約10分→小出駅→南越後交通バス「栃尾又線」（通年運行）約25分→大湯公園（前泊）→うおぬま滝雲シャトルバス（土日祝・早朝）約40分→枝折峠登山口</t>
         </is>
       </c>
       <c r="G72" s="41" t="n">
         <v>156</v>
       </c>
       <c r="H72" s="41" t="n">
-        <v>6820</v>
+        <v>8220</v>
       </c>
       <c r="I72" s="44" t="inlineStr">
         <is>
-          <t>大宮駅→上越新幹線とき約55分→浦佐駅→JR上越線約10分→小出駅→南越後交通バス（2026年の運行は未確認）約1時間5分→枝折峠登山口</t>
+          <t>大宮駅→上越新幹線とき約55分→浦佐駅→JR上越線約10分→小出駅→南越後交通バス「栃尾又線」（通年運行）約25分→大湯公園（前泊）→うおぬま滝雲シャトルバス（土日祝・早朝）約40分→枝折峠登山口</t>
         </is>
       </c>
       <c r="J72" s="41" t="n">
         <v>130</v>
       </c>
       <c r="K72" s="41" t="n">
-        <v>6490</v>
+        <v>7890</v>
       </c>
       <c r="L72" s="44" t="inlineStr">
         <is>
-          <t>横浜駅→JR東海道線約26分→東京駅→上越新幹線とき約1時間19分→浦佐駅→JR上越線約10分→小出駅→南越後交通バス（2026年の運行は未確認）約1時間5分→枝折峠登山口</t>
+          <t>横浜駅→JR東海道線約26分→東京駅→上越新幹線とき約1時間19分→浦佐駅→JR上越線約10分→小出駅→南越後交通バス「栃尾又線」（通年運行）約25分→大湯公園（前泊）→うおぬま滝雲シャトルバス（土日祝・早朝）約40分→枝折峠登山口</t>
         </is>
       </c>
       <c r="M72" s="41" t="n">
         <v>180</v>
       </c>
       <c r="N72" s="41" t="n">
-        <v>8800</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="30">
@@ -10936,36 +10936,36 @@
       </c>
       <c r="F82" s="44" t="inlineStr">
         <is>
-          <t>バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[バス]--&gt; 菅の台バスセンター --[中央アルプス観光バス]--&gt; しらび平 --[ロープウェイ]--&gt; 千畳敷</t>
+          <t>バスタ新宿→高速バス約3時間40分→駒ヶ根駅→バス約25分→菅の台バスセンター→中央アルプス観光バス約30分→しらび平→ロープウェイ約8分→千畳敷</t>
         </is>
       </c>
       <c r="G82" s="41" t="n">
         <v>283</v>
       </c>
       <c r="H82" s="41" t="n">
-        <v>8400</v>
+        <v>7020</v>
       </c>
       <c r="I82" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[バス]--&gt; 菅の台バスセンター --[中央アルプス観光バス]--&gt; しらび平 --[ロープウェイ]--&gt; 千畳敷</t>
+          <t>大宮駅→JR埼京線約30分→バスタ新宿→高速バス約3時間40分→駒ヶ根駅→バス約25分→菅の台バスセンター→中央アルプス観光バス約30分→しらび平→ロープウェイ約8分→千畳敷</t>
         </is>
       </c>
       <c r="J82" s="41" t="n">
         <v>313</v>
       </c>
       <c r="K82" s="41" t="n">
-        <v>8930</v>
+        <v>7548</v>
       </c>
       <c r="L82" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン]--&gt; バスタ新宿 --[高速バス]--&gt; 駒ヶ根駅 --[バス]--&gt; 菅の台バスセンター --[中央アルプス観光バス]--&gt; しらび平 --[ロープウェイ]--&gt; 千畳敷</t>
+          <t>横浜駅→JR湘南新宿ライン約34分→バスタ新宿→高速バス約3時間40分→駒ヶ根駅→バス約25分→菅の台バスセンター→中央アルプス観光バス約30分→しらび平→ロープウェイ約8分→千畳敷</t>
         </is>
       </c>
       <c r="M82" s="41" t="n">
         <v>317</v>
       </c>
       <c r="N82" s="41" t="n">
-        <v>9020</v>
+        <v>7636</v>
       </c>
     </row>
     <row r="83" ht="26.25" customHeight="1" s="30">
@@ -18110,12 +18110,12 @@
       </c>
       <c r="E48" s="44" t="inlineStr">
         <is>
-          <t>南越後交通バス</t>
+          <t>上越新幹線・JR上越線・南越後交通バス・うおぬま滝雲シャトルバス</t>
         </is>
       </c>
       <c r="F48" s="49" t="inlineStr">
         <is>
-          <t>（未登録）</t>
+          <t>https://www.iine-uonuma.jp/31055/</t>
         </is>
       </c>
       <c r="G48" s="47" t="inlineStr">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="H48" s="47" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I48" s="47" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="L48" s="44" t="inlineStr">
         <is>
-          <t>2026-10-08 小出駅〜枝折峠のバスは事業者サイトの路線一覧に無い。公表は浦佐駅東口〜銀山平〜奥只見ダム（6/1〜11/3土日祝）。営業所への確認が必要</t>
+          <t>2026-10-08 小出駅〜枝折峠の路線バスは無い（運営者確認）。大湯公園発「うおぬま滝雲シャトルバス」（9/19〜11/3土日祝、片道1,000円）＋小出駅前〜大湯公園400円・25分に修正</t>
         </is>
       </c>
     </row>
@@ -21740,12 +21740,12 @@
       </c>
       <c r="K108" s="47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="L108" s="44" t="inlineStr">
         <is>
-          <t>問題なし</t>
+          <t>2026-10-08 時刻表リンクを南魚沼市のMOSSのページに修正（旧：南越後交通バス。路線バスは2026年3月31日廃止）。六日町駅〜清水500円。MOSSの乗降場所に六日町駅・清水があることを運営者が確認</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K452"/>
+  <dimension ref="A1:K464"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -49001,112 +49001,772 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="n">
+      <c r="A451" s="29" t="n">
         <v>450</v>
       </c>
-      <c r="B451" t="inlineStr">
+      <c r="B451" s="29" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr">
+      <c r="C451" s="29" t="inlineStr">
         <is>
           <t>terkari</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr">
+      <c r="D451" s="29" t="inlineStr">
         <is>
           <t>光岳</t>
         </is>
       </c>
-      <c r="E451" t="inlineStr">
+      <c r="E451" s="29" t="inlineStr">
         <is>
           <t>運賃からタクシー概算を除外・時刻表リンク・注記</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr">
+      <c r="F451" s="29" t="inlineStr">
         <is>
           <t>全出発地</t>
         </is>
       </c>
-      <c r="G451" t="inlineStr">
+      <c r="G451" s="29" t="inlineStr">
         <is>
           <t>24,800／25,380／25,380円</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr">
+      <c r="H451" s="29" t="inlineStr">
         <is>
           <t>5,700／6,228／6,316円（かぐらの湯まで。タクシー1台15,000〜20,000円は別）</t>
         </is>
       </c>
-      <c r="I451" t="inlineStr">
+      <c r="I451" s="29" t="inlineStr">
         <is>
           <t>遠山郷線700円（運営者確認）／京王バス 新宿〜伊那飯田線 運賃表（2025年9月1日現在）飯田駅前 月〜木5,000円</t>
         </is>
       </c>
-      <c r="J451" t="inlineStr">
+      <c r="J451" s="29" t="inlineStr">
         <is>
           <t>5,000＋700、大宮＋528、横浜＋616</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr">
+      <c r="K451" s="29" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="n">
+      <c r="A452" s="29" t="n">
         <v>451</v>
       </c>
-      <c r="B452" t="inlineStr">
+      <c r="B452" s="29" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr">
+      <c r="C452" s="29" t="inlineStr">
         <is>
           <t>utsugi</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr">
+      <c r="D452" s="29" t="inlineStr">
         <is>
           <t>空木岳</t>
         </is>
       </c>
-      <c r="E452" t="inlineStr">
+      <c r="E452" s="29" t="inlineStr">
         <is>
           <t>高速バスを窓口運賃に修正</t>
         </is>
       </c>
-      <c r="F452" t="inlineStr">
+      <c r="F452" s="29" t="inlineStr">
         <is>
           <t>全出発地</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr">
+      <c r="G452" s="29" t="inlineStr">
         <is>
           <t>4,580／5,108／5,196円（最安4,200円で計算）</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr">
+      <c r="H452" s="29" t="inlineStr">
         <is>
           <t>4,980／5,508／5,596円</t>
         </is>
       </c>
-      <c r="I452" t="inlineStr">
+      <c r="I452" s="29" t="inlineStr">
         <is>
           <t>京王バス 新宿〜伊那飯田線 運賃表 駒ヶ根 月〜木4,600円＋路線バス380円</t>
         </is>
       </c>
-      <c r="J452" t="inlineStr">
+      <c r="J452" s="29" t="inlineStr">
         <is>
           <t>4,600＋380、大宮＋528、横浜＋616</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr">
+      <c r="K452" s="29" t="inlineStr">
         <is>
           <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="29" t="n">
+        <v>452</v>
+      </c>
+      <c r="B453" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C453" s="29" t="inlineStr">
+        <is>
+          <t>echigokoma</t>
+        </is>
+      </c>
+      <c r="D453" s="29" t="inlineStr">
+        <is>
+          <t>越後駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E453" s="29" t="inlineStr">
+        <is>
+          <t>経路の修正（路線バスなし→滝雲シャトルバス）・運賃</t>
+        </is>
+      </c>
+      <c r="F453" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G453" s="29" t="inlineStr">
+        <is>
+          <t>6,820／6,490／8,800円（小出駅まで）</t>
+        </is>
+      </c>
+      <c r="H453" s="29" t="inlineStr">
+        <is>
+          <t>8,220／7,890／10,200円（小出駅まで＋バス400＋シャトル1,000）</t>
+        </is>
+      </c>
+      <c r="I453" s="29" t="inlineStr">
+        <is>
+          <t>魚沼市観光協会 2026年度うおぬま滝雲シャトルバス（2026.10.3更新）／南越後交通バス 栃尾又線 運賃表・休日時刻表</t>
+        </is>
+      </c>
+      <c r="J453" s="29" t="inlineStr">
+        <is>
+          <t>JR＋400＋1,000</t>
+        </is>
+      </c>
+      <c r="K453" s="29" t="inlineStr">
+        <is>
+          <t>高（所要40分は2026-10-08に運営者確認で確定。「大湯公園発の最終日は未確認」は読み違いで、大湯公園発も11月3日まで運行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="29" t="n">
+        <v>453</v>
+      </c>
+      <c r="B454" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C454" s="29" t="inlineStr">
+        <is>
+          <t>echigokoma</t>
+        </is>
+      </c>
+      <c r="D454" s="29" t="inlineStr">
+        <is>
+          <t>越後駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E454" s="29" t="inlineStr">
+        <is>
+          <t>検索ページの表記修正</t>
+        </is>
+      </c>
+      <c r="F454" s="29" t="inlineStr">
+        <is>
+          <t>search 2ページ・3か所</t>
+        </is>
+      </c>
+      <c r="G454" s="29" t="inlineStr">
+        <is>
+          <t>小出駅→枝折峠行きバス（季節運行）</t>
+        </is>
+      </c>
+      <c r="H454" s="29" t="inlineStr">
+        <is>
+          <t>大湯公園→滝雲シャトルバス（秋の土日祝のみ・前泊）</t>
+        </is>
+      </c>
+      <c r="I454" s="29" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="J454" s="29" t="inlineStr">
+        <is>
+          <t>re.subn 3件</t>
+        </is>
+      </c>
+      <c r="K454" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="29" t="n">
+        <v>454</v>
+      </c>
+      <c r="B455" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C455" s="29" t="inlineStr">
+        <is>
+          <t>makihata</t>
+        </is>
+      </c>
+      <c r="D455" s="29" t="inlineStr">
+        <is>
+          <t>巻機山</t>
+        </is>
+      </c>
+      <c r="E455" s="29" t="inlineStr">
+        <is>
+          <t>MOSS運賃の確定・リンク修正・所要時間の統一</t>
+        </is>
+      </c>
+      <c r="F455" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G455" s="29" t="inlineStr">
+        <is>
+          <t>7,080／6,420／8,620円（六日町駅まで）</t>
+        </is>
+      </c>
+      <c r="H455" s="29" t="inlineStr">
+        <is>
+          <t>7,580／6,920／9,120円（＋MOSS 500円）。MOSSの所要時間を30分に統一（大宮・横浜は40分だった）</t>
+        </is>
+      </c>
+      <c r="I455" s="29" t="inlineStr">
+        <is>
+          <t>南魚沼市 MOSS（13〜17km未満500円）、六日町駅〜清水は約15km（運営者確認）</t>
+        </is>
+      </c>
+      <c r="J455" s="29" t="inlineStr">
+        <is>
+          <t>電車代＋500</t>
+        </is>
+      </c>
+      <c r="K455" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="29" t="n">
+        <v>455</v>
+      </c>
+      <c r="B456" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C456" s="29" t="inlineStr">
+        <is>
+          <t>kisokoma</t>
+        </is>
+      </c>
+      <c r="D456" s="29" t="inlineStr">
+        <is>
+          <t>木曽駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E456" s="29" t="inlineStr">
+        <is>
+          <t>運賃の引き直し（片道合計になっていなかった）</t>
+        </is>
+      </c>
+      <c r="F456" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G456" s="29" t="inlineStr">
+        <is>
+          <t>8,400／8,930／9,020円（高速バス最安4,200＋バス・ロープウェイ往復4,200）</t>
+        </is>
+      </c>
+      <c r="H456" s="29" t="inlineStr">
+        <is>
+          <t>7,020／7,548／7,636円（片道：高速バス月〜木4,600＋路線バス1,050＋ロープウェイC運賃1,370）</t>
+        </is>
+      </c>
+      <c r="I456" s="29" t="inlineStr">
+        <is>
+          <t>中央アルプス駒ヶ岳ロープウェイ 2026年度運賃カレンダー／京王バス 新宿〜伊那飯田線 運賃表</t>
+        </is>
+      </c>
+      <c r="J456" s="29" t="inlineStr">
+        <is>
+          <t>4,600＋1,050＋1,370、大宮＋528、横浜＋616</t>
+        </is>
+      </c>
+      <c r="K456" s="29" t="inlineStr">
+        <is>
+          <t>高（日によりA〜E運賃・高速バス3区分で変動。表示は月〜木・C運賃）</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="29" t="n">
+        <v>456</v>
+      </c>
+      <c r="B457" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C457" s="29" t="inlineStr">
+        <is>
+          <t>yarigatake2</t>
+        </is>
+      </c>
+      <c r="D457" s="29" t="inlineStr">
+        <is>
+          <t>笊ヶ岳</t>
+        </is>
+      </c>
+      <c r="E457" s="29" t="inlineStr">
+        <is>
+          <t>乗合タクシー運賃の確定</t>
+        </is>
+      </c>
+      <c r="F457" s="29" t="inlineStr">
+        <is>
+          <t>全出発地</t>
+        </is>
+      </c>
+      <c r="G457" s="29" t="inlineStr">
+        <is>
+          <t>5,700／5,140／6,030円（大島バス停まで）</t>
+        </is>
+      </c>
+      <c r="H457" s="29" t="inlineStr">
+        <is>
+          <t>5,900／5,340／6,230円（＋乗合タクシー200円）</t>
+        </is>
+      </c>
+      <c r="I457" s="29" t="inlineStr">
+        <is>
+          <t>乗合タクシー200円（運営者確認）</t>
+        </is>
+      </c>
+      <c r="J457" s="29" t="inlineStr">
+        <is>
+          <t>身延まで＋バス600＋タクシー200</t>
+        </is>
+      </c>
+      <c r="K457" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="29" t="n">
+        <v>457</v>
+      </c>
+      <c r="B458" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C458" s="29" t="inlineStr">
+        <is>
+          <t>echigokoma</t>
+        </is>
+      </c>
+      <c r="D458" s="29" t="inlineStr">
+        <is>
+          <t>越後駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E458" s="29" t="inlineStr">
+        <is>
+          <t>シャトルバスの注記を最新情報に修正</t>
+        </is>
+      </c>
+      <c r="F458" s="29" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="G458" s="29" t="inlineStr">
+        <is>
+          <t>大湯公園発は1日2便・10月中旬まで（＝読み違いによる誤記。10月中旬までなのは災害復旧による1日2便の減便ダイヤ）／帰りの臨時便の所要時間なし</t>
+        </is>
+      </c>
+      <c r="H458" s="29" t="inlineStr">
+        <is>
+          <t>10月9日の国道352号規制解除で随時運行に戻る（3:30〜7:00）／帰りの臨時便は白銀の湯経由で約70分／路線バスは通年運行と明記</t>
+        </is>
+      </c>
+      <c r="I458" s="29" t="inlineStr">
+        <is>
+          <t>魚沼市観光協会（2026.10.8更新・10.5予告）、70分は運営者確認</t>
+        </is>
+      </c>
+      <c r="J458" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K458" s="29" t="inlineStr">
+        <is>
+          <t>高（行きの所要時間は未確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="29" t="n">
+        <v>458</v>
+      </c>
+      <c r="B459" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C459" s="29" t="inlineStr">
+        <is>
+          <t>echigokoma</t>
+        </is>
+      </c>
+      <c r="D459" s="29" t="inlineStr">
+        <is>
+          <t>越後駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E459" s="29" t="inlineStr">
+        <is>
+          <t>シャトルバス行きの所要時間の確定</t>
+        </is>
+      </c>
+      <c r="F459" s="29" t="inlineStr">
+        <is>
+          <t>大湯公園→枝折峠</t>
+        </is>
+      </c>
+      <c r="G459" s="29" t="inlineStr">
+        <is>
+          <t>約40分（未確認）</t>
+        </is>
+      </c>
+      <c r="H459" s="29" t="inlineStr">
+        <is>
+          <t>約40分（確定）。要確認フラグを解除</t>
+        </is>
+      </c>
+      <c r="I459" s="29" t="inlineStr">
+        <is>
+          <t>運営者確認</t>
+        </is>
+      </c>
+      <c r="J459" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K459" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="29" t="n">
+        <v>459</v>
+      </c>
+      <c r="B460" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C460" s="29" t="inlineStr">
+        <is>
+          <t>echigokoma</t>
+        </is>
+      </c>
+      <c r="D460" s="29" t="inlineStr">
+        <is>
+          <t>越後駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E460" s="29" t="inlineStr">
+        <is>
+          <t>記載の訂正（読み違い）</t>
+        </is>
+      </c>
+      <c r="F460" s="29" t="inlineStr">
+        <is>
+          <t>シャトルバス 大湯公園発</t>
+        </is>
+      </c>
+      <c r="G460" s="29" t="inlineStr">
+        <is>
+          <t>「大湯公園発は10月中旬まで」「大湯公園発の最終運行日は未確認」</t>
+        </is>
+      </c>
+      <c r="H460" s="29" t="inlineStr">
+        <is>
+          <t>大湯公園発も白銀の湯発と同じく11月3日まで運行。10月中旬までだったのは災害復旧による「1日2便」の減便で、国道352号の規制解除（10月9日15時）で随時運行に戻る。ページ・データは修正済みで誤記の残存なし</t>
+        </is>
+      </c>
+      <c r="I460" s="29" t="inlineStr">
+        <is>
+          <t>魚沼市観光協会（2026.10.8更新）の原文「運行ルート2は災害復旧のため10月中旬まで随時運行ではなく1日2便運行」</t>
+        </is>
+      </c>
+      <c r="J460" s="29" t="inlineStr">
+        <is>
+          <t>grepで残存0件を確認</t>
+        </is>
+      </c>
+      <c r="K460" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>460</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>azuma</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>西吾妻山</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>運行期間の登録</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>ロープウェイ・夏山リフト</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>期間未登録</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>2026年 ロープウェイ6/13〜11/3、夏山リフト6/13〜10/25（運休日あり）</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>天元台高原 公式（ロープウェイ・リフト）</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>461</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>iwasugesan</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>岩菅山</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>バッジの修正（季節運行→通年運行）</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>湯田中駅〜一ノ瀬スキー場</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>季節運行</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>通年運行（季節でダイヤが変わる）。年次の見張りは対象外に</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>長電バス 奥志賀高原線 時刻表（2026年4月7日改正）</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>462</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>hinata</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>日向山</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>林道冬期閉鎖の出典を登録</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>矢立石への林道</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>出典未登録</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>山梨県 県営林道通行規制情報を登録（前季2025/12/10〜2026/4/24、今季未発表）</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>山梨県 県営林道通行規制情報</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>中（今季の日付は未発表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>463</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>karisaka</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>雁坂嶺</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>運行パターンの明記</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>塩山駅〜西沢渓谷入口</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>「季節運行で運休期間や土日祝限定の期間あり」</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>西沢渓谷入口まで行くのは例年4月下旬〜9月下旬の土日祝と、4月下旬〜5月上旬・7月中旬〜8月中旬・10月上旬〜11月下旬。他は窪平止まり</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>甲州市の案内（窪平・西沢渓谷線、年の記載なし）</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>中（2026年の正確な日付は未確認）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K464"/>
+  <dimension ref="A1:K485"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -49551,222 +49551,1377 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="n">
+      <c r="A461" s="29" t="n">
         <v>460</v>
       </c>
-      <c r="B461" t="inlineStr">
+      <c r="B461" s="29" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr">
+      <c r="C461" s="29" t="inlineStr">
         <is>
           <t>azuma</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr">
+      <c r="D461" s="29" t="inlineStr">
         <is>
           <t>西吾妻山</t>
         </is>
       </c>
-      <c r="E461" t="inlineStr">
+      <c r="E461" s="29" t="inlineStr">
         <is>
           <t>運行期間の登録</t>
         </is>
       </c>
-      <c r="F461" t="inlineStr">
+      <c r="F461" s="29" t="inlineStr">
         <is>
           <t>ロープウェイ・夏山リフト</t>
         </is>
       </c>
-      <c r="G461" t="inlineStr">
+      <c r="G461" s="29" t="inlineStr">
         <is>
           <t>期間未登録</t>
         </is>
       </c>
-      <c r="H461" t="inlineStr">
+      <c r="H461" s="29" t="inlineStr">
         <is>
           <t>2026年 ロープウェイ6/13〜11/3、夏山リフト6/13〜10/25（運休日あり）</t>
         </is>
       </c>
-      <c r="I461" t="inlineStr">
+      <c r="I461" s="29" t="inlineStr">
         <is>
           <t>天元台高原 公式（ロープウェイ・リフト）</t>
         </is>
       </c>
-      <c r="J461" t="inlineStr">
+      <c r="J461" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr">
+      <c r="K461" s="29" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="n">
+      <c r="A462" s="29" t="n">
         <v>461</v>
       </c>
-      <c r="B462" t="inlineStr">
+      <c r="B462" s="29" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr">
+      <c r="C462" s="29" t="inlineStr">
         <is>
           <t>iwasugesan</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr">
+      <c r="D462" s="29" t="inlineStr">
         <is>
           <t>岩菅山</t>
         </is>
       </c>
-      <c r="E462" t="inlineStr">
+      <c r="E462" s="29" t="inlineStr">
         <is>
           <t>バッジの修正（季節運行→通年運行）</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr">
+      <c r="F462" s="29" t="inlineStr">
         <is>
           <t>湯田中駅〜一ノ瀬スキー場</t>
         </is>
       </c>
-      <c r="G462" t="inlineStr">
+      <c r="G462" s="29" t="inlineStr">
         <is>
           <t>季節運行</t>
         </is>
       </c>
-      <c r="H462" t="inlineStr">
+      <c r="H462" s="29" t="inlineStr">
         <is>
           <t>通年運行（季節でダイヤが変わる）。年次の見張りは対象外に</t>
         </is>
       </c>
-      <c r="I462" t="inlineStr">
+      <c r="I462" s="29" t="inlineStr">
         <is>
           <t>長電バス 奥志賀高原線 時刻表（2026年4月7日改正）</t>
         </is>
       </c>
-      <c r="J462" t="inlineStr">
+      <c r="J462" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr">
+      <c r="K462" s="29" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="n">
+      <c r="A463" s="29" t="n">
         <v>462</v>
       </c>
-      <c r="B463" t="inlineStr">
+      <c r="B463" s="29" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr">
+      <c r="C463" s="29" t="inlineStr">
         <is>
           <t>hinata</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr">
+      <c r="D463" s="29" t="inlineStr">
         <is>
           <t>日向山</t>
         </is>
       </c>
-      <c r="E463" t="inlineStr">
+      <c r="E463" s="29" t="inlineStr">
         <is>
           <t>林道冬期閉鎖の出典を登録</t>
         </is>
       </c>
-      <c r="F463" t="inlineStr">
+      <c r="F463" s="29" t="inlineStr">
         <is>
           <t>矢立石への林道</t>
         </is>
       </c>
-      <c r="G463" t="inlineStr">
+      <c r="G463" s="29" t="inlineStr">
         <is>
           <t>出典未登録</t>
         </is>
       </c>
-      <c r="H463" t="inlineStr">
+      <c r="H463" s="29" t="inlineStr">
         <is>
           <t>山梨県 県営林道通行規制情報を登録（前季2025/12/10〜2026/4/24、今季未発表）</t>
         </is>
       </c>
-      <c r="I463" t="inlineStr">
+      <c r="I463" s="29" t="inlineStr">
         <is>
           <t>山梨県 県営林道通行規制情報</t>
         </is>
       </c>
-      <c r="J463" t="inlineStr">
+      <c r="J463" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr">
+      <c r="K463" s="29" t="inlineStr">
         <is>
           <t>中（今季の日付は未発表）</t>
         </is>
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="n">
+      <c r="A464" s="29" t="n">
         <v>463</v>
       </c>
-      <c r="B464" t="inlineStr">
+      <c r="B464" s="29" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr">
+      <c r="C464" s="29" t="inlineStr">
         <is>
           <t>karisaka</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr">
+      <c r="D464" s="29" t="inlineStr">
         <is>
           <t>雁坂嶺</t>
         </is>
       </c>
-      <c r="E464" t="inlineStr">
+      <c r="E464" s="29" t="inlineStr">
         <is>
           <t>運行パターンの明記</t>
         </is>
       </c>
-      <c r="F464" t="inlineStr">
+      <c r="F464" s="29" t="inlineStr">
         <is>
           <t>塩山駅〜西沢渓谷入口</t>
         </is>
       </c>
-      <c r="G464" t="inlineStr">
+      <c r="G464" s="29" t="inlineStr">
         <is>
           <t>「季節運行で運休期間や土日祝限定の期間あり」</t>
         </is>
       </c>
-      <c r="H464" t="inlineStr">
+      <c r="H464" s="29" t="inlineStr">
         <is>
           <t>西沢渓谷入口まで行くのは例年4月下旬〜9月下旬の土日祝と、4月下旬〜5月上旬・7月中旬〜8月中旬・10月上旬〜11月下旬。他は窪平止まり</t>
         </is>
       </c>
-      <c r="I464" t="inlineStr">
+      <c r="I464" s="29" t="inlineStr">
         <is>
           <t>甲州市の案内（窪平・西沢渓谷線、年の記載なし）</t>
         </is>
       </c>
-      <c r="J464" t="inlineStr">
+      <c r="J464" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr">
+      <c r="K464" s="29" t="inlineStr">
         <is>
           <t>中（2026年の正確な日付は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="29" t="n">
+        <v>464</v>
+      </c>
+      <c r="B465" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C465" s="29" t="inlineStr">
+        <is>
+          <t>全156山</t>
+        </is>
+      </c>
+      <c r="D465" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E465" s="29" t="inlineStr">
+        <is>
+          <t>装備カレンダーの改修</t>
+        </is>
+      </c>
+      <c r="F465" s="29" t="inlineStr">
+        <is>
+          <t>シーズンカレンダー</t>
+        </is>
+      </c>
+      <c r="G465" s="29" t="inlineStr">
+        <is>
+          <t>3区分（アイゼン不要／6本アイゼンで可／12本アイゼン必要）</t>
+        </is>
+      </c>
+      <c r="H465" s="29" t="inlineStr">
+        <is>
+          <t>4区分（アイゼン不要／軽アイゼン等／冬山装備／入山不可）＋月途中の切替（斜め2色・タップで切替日）。新フィールド gearCalendar、check_pages セクション16を追加</t>
+        </is>
+      </c>
+      <c r="I465" s="29" t="inlineStr">
+        <is>
+          <t>改修方針（運営者）</t>
+        </is>
+      </c>
+      <c r="J465" s="29" t="inlineStr">
+        <is>
+          <t>全156山を再生成・16セクション0件</t>
+        </is>
+      </c>
+      <c r="K465" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="29" t="n">
+        <v>465</v>
+      </c>
+      <c r="B466" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C466" s="29" t="inlineStr">
+        <is>
+          <t>全156山</t>
+        </is>
+      </c>
+      <c r="D466" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E466" s="29" t="inlineStr">
+        <is>
+          <t>装備カード・トップ・診断の文言と連動</t>
+        </is>
+      </c>
+      <c r="F466" s="29" t="inlineStr">
+        <is>
+          <t>装備カードの説明文ほか</t>
+        </is>
+      </c>
+      <c r="G466" s="29" t="inlineStr">
+        <is>
+          <t>「12本アイゼンが必要です」「軽アイゼン（6本爪）」「6本可」「12本必要」</t>
+        </is>
+      </c>
+      <c r="H466" s="29" t="inlineStr">
+        <is>
+          <t>「12本爪アイゼン・ピッケル等の冬山装備」「チェーンスパイクや6本爪アイゼンなどの軽アイゼン等」「軽アイゼン等」「冬山装備」。入山不可の月は装備カードを出さず、診断では末尾に回す</t>
+        </is>
+      </c>
+      <c r="I466" s="29" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="J466" s="29" t="inlineStr">
+        <is>
+          <t>gear-data.json 1,072か所、記事・検索208か所、残存0件</t>
+        </is>
+      </c>
+      <c r="K466" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="29" t="n">
+        <v>466</v>
+      </c>
+      <c r="B467" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C467" s="29" t="inlineStr">
+        <is>
+          <t>ontakesan</t>
+        </is>
+      </c>
+      <c r="D467" s="29" t="inlineStr">
+        <is>
+          <t>御嶽山</t>
+        </is>
+      </c>
+      <c r="E467" s="29" t="inlineStr">
+        <is>
+          <t>入山不可の登録</t>
+        </is>
+      </c>
+      <c r="F467" s="29" t="inlineStr">
+        <is>
+          <t>1〜6月・10/15〜・11〜12月</t>
+        </is>
+      </c>
+      <c r="G467" s="29" t="inlineStr">
+        <is>
+          <t>冬山装備／軽アイゼン等</t>
+        </is>
+      </c>
+      <c r="H467" s="29" t="inlineStr">
+        <is>
+          <t>入山不可（剣ヶ峰への登山道は規制緩和期間 2026年7月1日〜10月14日正午だけ通行可）。10月は斜め2色</t>
+        </is>
+      </c>
+      <c r="I467" s="29" t="inlineStr">
+        <is>
+          <t>木曽町「御嶽山立ち入り規制の情報について」</t>
+        </is>
+      </c>
+      <c r="J467" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K467" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="29" t="n">
+        <v>467</v>
+      </c>
+      <c r="B468" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C468" s="29" t="inlineStr">
+        <is>
+          <t>oyama・otake・amagi・ogiyama・myojingatake・sasakogarigaburiyama</t>
+        </is>
+      </c>
+      <c r="D468" s="29" t="inlineStr">
+        <is>
+          <t>大山（丹沢）・大岳山・天城山・扇山・明神ヶ岳・笹子雁ヶ腹摺山</t>
+        </is>
+      </c>
+      <c r="E468" s="29" t="inlineStr">
+        <is>
+          <t>冬の区分の修正</t>
+        </is>
+      </c>
+      <c r="F468" s="29" t="inlineStr">
+        <is>
+          <t>冬の月</t>
+        </is>
+      </c>
+      <c r="G468" s="29" t="inlineStr">
+        <is>
+          <t>通年アイゼン不要</t>
+        </is>
+      </c>
+      <c r="H468" s="29" t="inlineStr">
+        <is>
+          <t>冬は軽アイゼン等（大山12〜3月、大岳山・扇山・笹子雁ヶ腹摺山12〜2月、天城山1〜3月、明神ヶ岳1〜2月）。FAQ・装備カード・旧フィールドも同期</t>
+        </is>
+      </c>
+      <c r="I468" s="29" t="inlineStr">
+        <is>
+          <t>神奈川県の積雪情報、登山記録、同じ山域・標高帯の山との比較</t>
+        </is>
+      </c>
+      <c r="J468" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K468" s="29" t="inlineStr">
+        <is>
+          <t>中（月の範囲は近隣の山に合わせた）</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="29" t="n">
+        <v>468</v>
+      </c>
+      <c r="B469" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C469" s="29" t="inlineStr">
+        <is>
+          <t>nantaisan</t>
+        </is>
+      </c>
+      <c r="D469" s="29" t="inlineStr">
+        <is>
+          <t>男体山</t>
+        </is>
+      </c>
+      <c r="E469" s="29" t="inlineStr">
+        <is>
+          <t>入山不可の登録</t>
+        </is>
+      </c>
+      <c r="F469" s="29" t="inlineStr">
+        <is>
+          <t>1〜3月・12月、4/1〜4/24、11/12〜</t>
+        </is>
+      </c>
+      <c r="G469" s="29" t="inlineStr">
+        <is>
+          <t>冬山装備／軽アイゼン等</t>
+        </is>
+      </c>
+      <c r="H469" s="29" t="inlineStr">
+        <is>
+          <t>入山不可（開山期間は4月25日〜11月11日。期間外は閉山）。4月・11月は斜め2色</t>
+        </is>
+      </c>
+      <c r="I469" s="29" t="inlineStr">
+        <is>
+          <t>日光市観光協会「男体山」</t>
+        </is>
+      </c>
+      <c r="J469" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K469" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="29" t="n">
+        <v>469</v>
+      </c>
+      <c r="B470" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C470" s="29" t="inlineStr">
+        <is>
+          <t>harinokidake</t>
+        </is>
+      </c>
+      <c r="D470" s="29" t="inlineStr">
+        <is>
+          <t>針ノ木岳</t>
+        </is>
+      </c>
+      <c r="E470" s="29" t="inlineStr">
+        <is>
+          <t>区分の修正</t>
+        </is>
+      </c>
+      <c r="F470" s="29" t="inlineStr">
+        <is>
+          <t>6月・7月</t>
+        </is>
+      </c>
+      <c r="G470" s="29" t="inlineStr">
+        <is>
+          <t>6月 軽アイゼン等／7月 アイゼン不要</t>
+        </is>
+      </c>
+      <c r="H470" s="29" t="inlineStr">
+        <is>
+          <t>6月 冬山装備／7月 軽アイゼン等（代表ルートが針ノ木雪渓を登る）</t>
+        </is>
+      </c>
+      <c r="I470" s="29" t="inlineStr">
+        <is>
+          <t>慎太郎祭の装備案内（6月はアイゼン・ピッケル、軽アイゼン不可）、7月の登山記録</t>
+        </is>
+      </c>
+      <c r="J470" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K470" s="29" t="inlineStr">
+        <is>
+          <t>中（8月は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="29" t="n">
+        <v>470</v>
+      </c>
+      <c r="B471" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C471" s="29" t="inlineStr">
+        <is>
+          <t>tsurugi</t>
+        </is>
+      </c>
+      <c r="D471" s="29" t="inlineStr">
+        <is>
+          <t>剱岳</t>
+        </is>
+      </c>
+      <c r="E471" s="29" t="inlineStr">
+        <is>
+          <t>区分の修正</t>
+        </is>
+      </c>
+      <c r="F471" s="29" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="G471" s="29" t="inlineStr">
+        <is>
+          <t>アイゼン不要</t>
+        </is>
+      </c>
+      <c r="H471" s="29" t="inlineStr">
+        <is>
+          <t>軽アイゼン等（雪の多い年は7月下旬〜8月上旬まで別山尾根に残雪）</t>
+        </is>
+      </c>
+      <c r="I471" s="29" t="inlineStr">
+        <is>
+          <t>富山県警察 山岳情報</t>
+        </is>
+      </c>
+      <c r="J471" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K471" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="29" t="n">
+        <v>471</v>
+      </c>
+      <c r="B472" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C472" s="29" t="inlineStr">
+        <is>
+          <t>nasu</t>
+        </is>
+      </c>
+      <c r="D472" s="29" t="inlineStr">
+        <is>
+          <t>那須岳</t>
+        </is>
+      </c>
+      <c r="E472" s="29" t="inlineStr">
+        <is>
+          <t>区分の修正</t>
+        </is>
+      </c>
+      <c r="F472" s="29" t="inlineStr">
+        <is>
+          <t>12〜3月</t>
+        </is>
+      </c>
+      <c r="G472" s="29" t="inlineStr">
+        <is>
+          <t>軽アイゼン等</t>
+        </is>
+      </c>
+      <c r="H472" s="29" t="inlineStr">
+        <is>
+          <t>冬山装備（峰の茶屋から上は12本爪アイゼン・ピッケル）</t>
+        </is>
+      </c>
+      <c r="I472" s="29" t="inlineStr">
+        <is>
+          <t>登山記録、同じ標高帯の安達太良山・磐梯山との比較</t>
+        </is>
+      </c>
+      <c r="J472" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K472" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="29" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C473" s="29" t="inlineStr">
+        <is>
+          <t>全156山</t>
+        </is>
+      </c>
+      <c r="D473" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E473" s="29" t="inlineStr">
+        <is>
+          <t>トップの絞り込みを装備カレンダー基準に変更</t>
+        </is>
+      </c>
+      <c r="F473" s="29" t="inlineStr">
+        <is>
+          <t>アイゼン不要／軽アイゼン等まで</t>
+        </is>
+      </c>
+      <c r="G473" s="29" t="inlineStr">
+        <is>
+          <t>月の文字（seasonNoGear など）で判定。51山でカレンダーと食い違っていた</t>
+        </is>
+      </c>
+      <c r="H473" s="29" t="inlineStr">
+        <is>
+          <t>装備カレンダー（gearCalendar）で判定。月の表示もカレンダーから作る</t>
+        </is>
+      </c>
+      <c r="I473" s="29" t="inlineStr">
+        <is>
+          <t>check 16セクション0件・トップの表示確認</t>
+        </is>
+      </c>
+      <c r="J473" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K473" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="29" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C474" s="29" t="inlineStr">
+        <is>
+          <t>kitadake・yari・hotaka・harinokidake・momakurasan</t>
+        </is>
+      </c>
+      <c r="D474" s="29" t="inlineStr">
+        <is>
+          <t>北岳・槍ヶ岳・奥穂高岳・針ノ木岳・百蔵山</t>
+        </is>
+      </c>
+      <c r="E474" s="29" t="inlineStr">
+        <is>
+          <t>区分の修正（切替日不明は安全側）</t>
+        </is>
+      </c>
+      <c r="F474" s="29" t="inlineStr">
+        <is>
+          <t>7月ほか</t>
+        </is>
+      </c>
+      <c r="G474" s="29" t="inlineStr">
+        <is>
+          <t>7月 アイゼン不要（北岳・槍・奥穂）／6月 軽アイゼン等（槍・奥穂）／8月 アイゼン不要（針ノ木）／通年アイゼン不要（百蔵山）</t>
+        </is>
+      </c>
+      <c r="H474" s="29" t="inlineStr">
+        <is>
+          <t>7月 軽アイゼン等／6月 冬山装備／8月 軽アイゼン等／12〜2月 軽アイゼン等</t>
+        </is>
+      </c>
+      <c r="I474" s="29" t="inlineStr">
+        <is>
+          <t>運営者の方針（安全側）、山梨県の北岳登山案内、涸沢・槍沢の残雪情報</t>
+        </is>
+      </c>
+      <c r="J474" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K474" s="29" t="inlineStr">
+        <is>
+          <t>中（切替日は未確定のため月全体を厳しいほうに）</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="29" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C475" s="29" t="inlineStr">
+        <is>
+          <t>kitadake ほか20山</t>
+        </is>
+      </c>
+      <c r="D475" s="29" t="inlineStr">
+        <is>
+          <t>北岳・甲斐駒ヶ岳・仙丈ヶ岳・白馬岳・乗鞍岳・立山・剱岳・常念岳・鹿島槍ヶ岳・笠ヶ岳・五竜岳・塩見岳・荒川岳・赤石岳・聖岳・薬師岳・黒部五郎岳・間ノ岳・農鳥岳・大天井岳・野口五郎岳</t>
+        </is>
+      </c>
+      <c r="E475" s="29" t="inlineStr">
+        <is>
+          <t>区分の修正（安全側）</t>
+        </is>
+      </c>
+      <c r="F475" s="29" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="G475" s="29" t="inlineStr">
+        <is>
+          <t>軽アイゼン等</t>
+        </is>
+      </c>
+      <c r="H475" s="29" t="inlineStr">
+        <is>
+          <t>冬山装備（北ア・南アの標高2,800m以上。装備カードも冬山装備に）</t>
+        </is>
+      </c>
+      <c r="I475" s="29" t="inlineStr">
+        <is>
+          <t>運営者の方針（安全側）。山ごとの切替時期は未確認</t>
+        </is>
+      </c>
+      <c r="J475" s="29" t="inlineStr">
+        <is>
+          <t>21山を再生成・16セクション0件</t>
+        </is>
+      </c>
+      <c r="K475" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="29" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C476" s="29" t="inlineStr">
+        <is>
+          <t>tateyama・norikura・yakushidake・otenshoudake</t>
+        </is>
+      </c>
+      <c r="D476" s="29" t="inlineStr">
+        <is>
+          <t>立山・乗鞍岳・薬師岳・大天井岳</t>
+        </is>
+      </c>
+      <c r="E476" s="29" t="inlineStr">
+        <is>
+          <t>6月の区分を個別調査で見直し</t>
+        </is>
+      </c>
+      <c r="F476" s="29" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="G476" s="29" t="inlineStr">
+        <is>
+          <t>冬山装備（一括変更）</t>
+        </is>
+      </c>
+      <c r="H476" s="29" t="inlineStr">
+        <is>
+          <t>軽アイゼン等に戻す（登山記録でチェーンスパイク・軽アイゼン程度、燕山荘は「6本歯以上」と案内）</t>
+        </is>
+      </c>
+      <c r="I476" s="29" t="inlineStr">
+        <is>
+          <t>YAMAPの6月の登山記録、燕山荘の案内</t>
+        </is>
+      </c>
+      <c r="J476" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K476" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="29" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C477" s="29" t="inlineStr">
+        <is>
+          <t>kisokoma・iide</t>
+        </is>
+      </c>
+      <c r="D477" s="29" t="inlineStr">
+        <is>
+          <t>木曽駒ヶ岳・飯豊山</t>
+        </is>
+      </c>
+      <c r="E477" s="29" t="inlineStr">
+        <is>
+          <t>6月の区分を個別調査で見直し</t>
+        </is>
+      </c>
+      <c r="F477" s="29" t="inlineStr">
+        <is>
+          <t>6月（飯豊山は7月も）</t>
+        </is>
+      </c>
+      <c r="G477" s="29" t="inlineStr">
+        <is>
+          <t>軽アイゼン等</t>
+        </is>
+      </c>
+      <c r="H477" s="29" t="inlineStr">
+        <is>
+          <t>冬山装備（木曽駒：11〜6月は雪山装備が必要／飯豊：7月上旬までアイゼン・ピッケルが必要な場合あり）。飯豊山の7月は軽アイゼン等</t>
+        </is>
+      </c>
+      <c r="I477" s="29" t="inlineStr">
+        <is>
+          <t>山岳ガイド記事・登山記録</t>
+        </is>
+      </c>
+      <c r="J477" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K477" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="29" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C478" s="29" t="inlineStr">
+        <is>
+          <t>shirouma ほか16山</t>
+        </is>
+      </c>
+      <c r="D478" s="29" t="inlineStr">
+        <is>
+          <t>白馬岳・剱岳・常念岳・笠ヶ岳・鹿島槍ヶ岳・北岳・五竜岳／黒部五郎岳・野口五郎岳・仙丈ヶ岳・甲斐駒ヶ岳・間ノ岳・農鳥岳・塩見岳・赤石岳・荒川岳・聖岳</t>
+        </is>
+      </c>
+      <c r="E478" s="29" t="inlineStr">
+        <is>
+          <t>6月の区分を個別調査で確認</t>
+        </is>
+      </c>
+      <c r="F478" s="29" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="G478" s="29" t="inlineStr">
+        <is>
+          <t>冬山装備</t>
+        </is>
+      </c>
+      <c r="H478" s="29" t="inlineStr">
+        <is>
+          <t>変更なし。前の7山は根拠あり（長野県警の山岳通信：6月下旬の白馬大雪渓・針ノ木雪渓はアイゼン＋ピッケル推奨 ほか）。後の10山は6月の情報が取れず安全側のまま</t>
+        </is>
+      </c>
+      <c r="I478" s="29" t="inlineStr">
+        <is>
+          <t>長野県山岳遭難防止対策協会「山岳通信」第451号・第190号、登山記録</t>
+        </is>
+      </c>
+      <c r="J478" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K478" s="29" t="inlineStr">
+        <is>
+          <t>前7山：高〜中／後10山：低（要確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="29" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C479" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D479" s="29" t="inlineStr">
+        <is>
+          <t>記事「アイゼン不要で冬に登れる山5選」</t>
+        </is>
+      </c>
+      <c r="E479" s="29" t="inlineStr">
+        <is>
+          <t>大山を弘法山に差し替え</t>
+        </is>
+      </c>
+      <c r="F479" s="29" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="G479" s="29" t="inlineStr">
+        <is>
+          <t>大山（丹沢）</t>
+        </is>
+      </c>
+      <c r="H479" s="29" t="inlineStr">
+        <is>
+          <t>弘法山（標高235m）。title・description・FAQの山名も変更。写真は未設定</t>
+        </is>
+      </c>
+      <c r="I479" s="29" t="inlineStr">
+        <is>
+          <t>運営者の指示</t>
+        </is>
+      </c>
+      <c r="J479" s="29" t="inlineStr">
+        <is>
+          <t>div数一致・残存0件</t>
+        </is>
+      </c>
+      <c r="K479" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="29" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C480" s="29" t="inlineStr">
+        <is>
+          <t>echigokoma・arasawadake・hiuchigatake・myoko・takatsuma・kurohimesan・tanigawa・hakusan・kisokoma・shirouma</t>
+        </is>
+      </c>
+      <c r="D480" s="29" t="inlineStr">
+        <is>
+          <t>越後駒ヶ岳・荒沢岳・燧ヶ岳・妙高山・高妻山・黒姫山・谷川岳・白山・木曽駒ヶ岳・白馬岳</t>
+        </is>
+      </c>
+      <c r="E480" s="29" t="inlineStr">
+        <is>
+          <t>残雪期の区分の修正（個別調査）</t>
+        </is>
+      </c>
+      <c r="F480" s="29" t="inlineStr">
+        <is>
+          <t>4〜7月</t>
+        </is>
+      </c>
+      <c r="G480" s="29" t="inlineStr">
+        <is>
+          <t>6月がアイゼン不要（越後駒・荒沢・燧・妙高・高妻・黒姫・谷川）／7月がアイゼン不要（白山・木曽駒・白馬）ほか</t>
+        </is>
+      </c>
+      <c r="H480" s="29" t="inlineStr">
+        <is>
+          <t>6月または7月を軽アイゼン等に。越後駒・荒沢の4月と燧ヶ岳の5月は冬山装備に。FAQ・装備カードも同期</t>
+        </is>
+      </c>
+      <c r="I480" s="29" t="inlineStr">
+        <is>
+          <t>新潟県観光協会、群馬県の登山道情報、登山記録（YAMAP）</t>
+        </is>
+      </c>
+      <c r="J480" s="29" t="inlineStr">
+        <is>
+          <t>10山を再生成・16セクション0件</t>
+        </is>
+      </c>
+      <c r="K480" s="29" t="inlineStr">
+        <is>
+          <t>中（荒沢岳・黒姫山は近隣の山からの類推、白山・木曽駒の7月は安全側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="29" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C481" s="29" t="inlineStr">
+        <is>
+          <t>標高2,800m以上の29山</t>
+        </is>
+      </c>
+      <c r="D481" s="29" t="inlineStr">
+        <is>
+          <t>北岳・槍ヶ岳・奥穂高岳・白馬岳・立山・剱岳・木曽駒ヶ岳・八ヶ岳（赤岳）ほか</t>
+        </is>
+      </c>
+      <c r="E481" s="29" t="inlineStr">
+        <is>
+          <t>10月の区分の修正（月途中の切替）</t>
+        </is>
+      </c>
+      <c r="F481" s="29" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="G481" s="29" t="inlineStr">
+        <is>
+          <t>軽アイゼン等（月全体）</t>
+        </is>
+      </c>
+      <c r="H481" s="29" t="inlineStr">
+        <is>
+          <t>10/10まで軽アイゼン等／10/11〜冬山装備（斜め2色）</t>
+        </is>
+      </c>
+      <c r="I481" s="29" t="inlineStr">
+        <is>
+          <t>長野県山岳遭難防止対策協会「山岳通信」第319号・第320号（2023年10月）、第205号（2020年10月）</t>
+        </is>
+      </c>
+      <c r="J481" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K481" s="29" t="inlineStr">
+        <is>
+          <t>中（切替日は「中旬以降」の初日で安全側。年により前後する）</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="29" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C482" s="29" t="inlineStr">
+        <is>
+          <t>senjogatake・komagatake・shiomidake</t>
+        </is>
+      </c>
+      <c r="D482" s="29" t="inlineStr">
+        <is>
+          <t>仙丈ヶ岳・甲斐駒ヶ岳・塩見岳</t>
+        </is>
+      </c>
+      <c r="E482" s="29" t="inlineStr">
+        <is>
+          <t>6月の区分を個別調査で見直し</t>
+        </is>
+      </c>
+      <c r="F482" s="29" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="G482" s="29" t="inlineStr">
+        <is>
+          <t>冬山装備（一括変更）</t>
+        </is>
+      </c>
+      <c r="H482" s="29" t="inlineStr">
+        <is>
+          <t>軽アイゼン等に戻す</t>
+        </is>
+      </c>
+      <c r="I482" s="29" t="inlineStr">
+        <is>
+          <t>伊那市「【残雪注意】6月に南アルプスを登山される皆様へ」（2026年5月1日更新）</t>
+        </is>
+      </c>
+      <c r="J482" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K482" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="29" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C483" s="29" t="inlineStr">
+        <is>
+          <t>takamizusanzan・kintoki</t>
+        </is>
+      </c>
+      <c r="D483" s="29" t="inlineStr">
+        <is>
+          <t>高水三山・金時山</t>
+        </is>
+      </c>
+      <c r="E483" s="29" t="inlineStr">
+        <is>
+          <t>厳しすぎた区分の修正</t>
+        </is>
+      </c>
+      <c r="F483" s="29" t="inlineStr">
+        <is>
+          <t>3〜4月</t>
+        </is>
+      </c>
+      <c r="G483" s="29" t="inlineStr">
+        <is>
+          <t>高水三山 12〜4月／金時山 12〜4月が軽アイゼン等</t>
+        </is>
+      </c>
+      <c r="H483" s="29" t="inlineStr">
+        <is>
+          <t>高水三山 12〜2月／金時山 12〜3月</t>
+        </is>
+      </c>
+      <c r="I483" s="29" t="inlineStr">
+        <is>
+          <t>登山記録、神奈川県の積雪情報、同じ山域の山との比較</t>
+        </is>
+      </c>
+      <c r="J483" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K483" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="29" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C484" s="29" t="inlineStr">
+        <is>
+          <t>bonori・hinodesaan・mitakesan</t>
+        </is>
+      </c>
+      <c r="D484" s="29" t="inlineStr">
+        <is>
+          <t>棒ノ折山・日の出山・御岳山</t>
+        </is>
+      </c>
+      <c r="E484" s="29" t="inlineStr">
+        <is>
+          <t>冬の区分の修正（個別調査）</t>
+        </is>
+      </c>
+      <c r="F484" s="29" t="inlineStr">
+        <is>
+          <t>1〜2月</t>
+        </is>
+      </c>
+      <c r="G484" s="29" t="inlineStr">
+        <is>
+          <t>通年アイゼン不要</t>
+        </is>
+      </c>
+      <c r="H484" s="29" t="inlineStr">
+        <is>
+          <t>1〜2月を軽アイゼン等に（降雪・凍結のあとに必要）。FAQ・装備カードも同期</t>
+        </is>
+      </c>
+      <c r="I484" s="29" t="inlineStr">
+        <is>
+          <t>登山記録（ヤマレコ・YAMAP・好日山荘）、御岳ビジターセンターの案内、平年の最深積雪</t>
+        </is>
+      </c>
+      <c r="J484" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K484" s="29" t="inlineStr">
+        <is>
+          <t>棒ノ折山：高／御岳山・日の出山：中</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>mitakesan・hinodesaan・bonori・takamizusanzan・momakurasan・ogiyama・myojingatake</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>御岳山・日の出山・棒ノ折山・高水三山・百蔵山・扇山・明神ヶ岳</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>冬の区分を通年アイゼン不要に戻す</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>冬の月</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>1〜2月または12〜2月が軽アイゼン等</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>通年アイゼン不要。降雪後の数日だけ滑り止めが要るのは例外として扱う（運営者の方針）。関東の低山は標高1,200mを目安に線引き</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>運営者の方針</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>7山を再生成・16セクション0件</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K485"/>
+  <dimension ref="A1:K486"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -50871,55 +50871,110 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="n">
+      <c r="A485" s="29" t="n">
         <v>484</v>
       </c>
-      <c r="B485" t="inlineStr">
+      <c r="B485" s="29" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr">
+      <c r="C485" s="29" t="inlineStr">
         <is>
           <t>mitakesan・hinodesaan・bonori・takamizusanzan・momakurasan・ogiyama・myojingatake</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr">
+      <c r="D485" s="29" t="inlineStr">
         <is>
           <t>御岳山・日の出山・棒ノ折山・高水三山・百蔵山・扇山・明神ヶ岳</t>
         </is>
       </c>
-      <c r="E485" t="inlineStr">
+      <c r="E485" s="29" t="inlineStr">
         <is>
           <t>冬の区分を通年アイゼン不要に戻す</t>
         </is>
       </c>
-      <c r="F485" t="inlineStr">
+      <c r="F485" s="29" t="inlineStr">
         <is>
           <t>冬の月</t>
         </is>
       </c>
-      <c r="G485" t="inlineStr">
+      <c r="G485" s="29" t="inlineStr">
         <is>
           <t>1〜2月または12〜2月が軽アイゼン等</t>
         </is>
       </c>
-      <c r="H485" t="inlineStr">
+      <c r="H485" s="29" t="inlineStr">
         <is>
           <t>通年アイゼン不要。降雪後の数日だけ滑り止めが要るのは例外として扱う（運営者の方針）。関東の低山は標高1,200mを目安に線引き</t>
         </is>
       </c>
-      <c r="I485" t="inlineStr">
+      <c r="I485" s="29" t="inlineStr">
         <is>
           <t>運営者の方針</t>
         </is>
       </c>
-      <c r="J485" t="inlineStr">
+      <c r="J485" s="29" t="inlineStr">
         <is>
           <t>7山を再生成・16セクション0件</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr">
+      <c r="K485" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>全山（電車・バス欄のある136山）</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>電車・バス欄の注記の整理</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>運賃欄の下の注記（※）と補足（💡）の2か所に分かれて表示</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>1つの箇条書きに統合。重複は自動で1つに。アクセスと関係のない項目42件と、言い換えの重複など17件を個別に指定して削除</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>運営者の指示</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>全156山を再生成・16セクション0件。削除項目は scripts/migrations/access_notes_cleanup*_2026_10.py に一覧</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K486"/>
+  <dimension ref="A1:K501"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -50926,57 +50926,882 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="n">
+      <c r="A486" s="29" t="n">
         <v>485</v>
       </c>
-      <c r="B486" t="inlineStr">
+      <c r="B486" s="29" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr">
+      <c r="C486" s="29" t="inlineStr">
         <is>
           <t>全山（電車・バス欄のある136山）</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr">
+      <c r="D486" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E486" t="inlineStr">
+      <c r="E486" s="29" t="inlineStr">
         <is>
           <t>電車・バス欄の注記の整理</t>
         </is>
       </c>
-      <c r="F486" t="inlineStr">
+      <c r="F486" s="29" t="inlineStr">
         <is>
           <t>注記</t>
         </is>
       </c>
-      <c r="G486" t="inlineStr">
+      <c r="G486" s="29" t="inlineStr">
         <is>
           <t>運賃欄の下の注記（※）と補足（💡）の2か所に分かれて表示</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr">
+      <c r="H486" s="29" t="inlineStr">
         <is>
           <t>1つの箇条書きに統合。重複は自動で1つに。アクセスと関係のない項目42件と、言い換えの重複など17件を個別に指定して削除</t>
         </is>
       </c>
-      <c r="I486" t="inlineStr">
+      <c r="I486" s="29" t="inlineStr">
         <is>
           <t>運営者の指示</t>
         </is>
       </c>
-      <c r="J486" t="inlineStr">
+      <c r="J486" s="29" t="inlineStr">
         <is>
           <t>全156山を再生成・16セクション0件。削除項目は scripts/migrations/access_notes_cleanup*_2026_10.py に一覧</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr">
+      <c r="K486" s="29" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="29" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C487" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D487" s="29" t="inlineStr">
+        <is>
+          <t>診断（/recommend/）</t>
+        </is>
+      </c>
+      <c r="E487" s="29" t="inlineStr">
+        <is>
+          <t>おすすめの理由の作り方を変更</t>
+        </is>
+      </c>
+      <c r="F487" s="29" t="inlineStr">
+        <is>
+          <t>結果カードの理由3つ</t>
+        </is>
+      </c>
+      <c r="G487" s="29" t="inlineStr">
+        <is>
+          <t>①山の一言紹介 ②出発地からの所要時間 ③タイプの相性＋コース定数</t>
+        </is>
+      </c>
+      <c r="H487" s="29" t="inlineStr">
+        <is>
+          <t>3つとも山の特徴（一言紹介／「こんな気分の人に」／紹介文）から選ぶ。タイプで加点された特徴に触れた文を優先。コース定数は理由の下に1行で添える。所要時間はアクセス欄にあるので理由から外した</t>
+        </is>
+      </c>
+      <c r="I487" s="29" t="inlineStr">
+        <is>
+          <t>運営者の指示</t>
+        </is>
+      </c>
+      <c r="J487" s="29" t="inlineStr">
+        <is>
+          <t>全156山で試算：155山が3つ、1山が2つ</t>
+        </is>
+      </c>
+      <c r="K487" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="29" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C488" s="29" t="inlineStr">
+        <is>
+          <t>fuji ほか31山</t>
+        </is>
+      </c>
+      <c r="D488" s="29" t="inlineStr">
+        <is>
+          <t>富士山・槍ヶ岳・奥穂高岳・北岳・剱岳・立山・白馬岳 ほか</t>
+        </is>
+      </c>
+      <c r="E488" s="29" t="inlineStr">
+        <is>
+          <t>「こんな気分の人に」の書き直し</t>
+        </is>
+      </c>
+      <c r="F488" s="29" t="inlineStr">
+        <is>
+          <t>Vibes 3項目</t>
+        </is>
+      </c>
+      <c r="G488" s="29" t="inlineStr">
+        <is>
+          <t>テンプレ文（コース定数◯◯のレベル／新宿から車◯時間／公共交通機関でアクセス可能）</t>
+        </is>
+      </c>
+      <c r="H488" s="29" t="inlineStr">
+        <is>
+          <t>山ごとの特徴3項目（例：槍ヶ岳「最後は鎖とハシゴで岩の穂先を登る」）</t>
+        </is>
+      </c>
+      <c r="I488" s="29" t="inlineStr">
+        <is>
+          <t>各山の地形・名所として広く知られている事実</t>
+        </is>
+      </c>
+      <c r="J488" s="29" t="inlineStr">
+        <is>
+          <t>32山を再生成・16セクション0件</t>
+        </is>
+      </c>
+      <c r="K488" s="29" t="inlineStr">
+        <is>
+          <t>中（内容は要目視確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="29" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C489" s="29" t="inlineStr">
+        <is>
+          <t>takao・tsukuba・tanzawa・tonosaki・oyama・mitakesan・kumotori・kintoki</t>
+        </is>
+      </c>
+      <c r="D489" s="29" t="inlineStr">
+        <is>
+          <t>高尾山・筑波山・丹沢山・塔ノ岳・大山・御岳山・雲取山・金時山</t>
+        </is>
+      </c>
+      <c r="E489" s="29" t="inlineStr">
+        <is>
+          <t>診断の理由用に山の特徴を個別調査（第1回・8山）</t>
+        </is>
+      </c>
+      <c r="F489" s="29" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G489" s="29" t="inlineStr">
+        <is>
+          <t>一言紹介と「こんな気分の人に」から自動で選択</t>
+        </is>
+      </c>
+      <c r="H489" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに調べた特徴3〜5項目（種類・見出し・本文）を登録。診断はタイプに合う種類を優先して3つ表示</t>
+        </is>
+      </c>
+      <c r="I489" s="29" t="inlineStr">
+        <is>
+          <t>観光協会・自治体・山岳メディアの記事（各山の featureSources に記録）</t>
+        </is>
+      </c>
+      <c r="J489" s="29" t="inlineStr">
+        <is>
+          <t>2タイプで表示を確認</t>
+        </is>
+      </c>
+      <c r="K489" s="29" t="inlineStr">
+        <is>
+          <t>中（検索結果の要約で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="29" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C490" s="29" t="inlineStr">
+        <is>
+          <t>okutama ほか13山＋takao</t>
+        </is>
+      </c>
+      <c r="D490" s="29" t="inlineStr">
+        <is>
+          <t>大菩薩嶺・瑞牆山・金峰山・谷川岳・赤城山・那須岳・日光白根山・八ヶ岳（赤岳）・至仏山・燧ヶ岳・木曽駒ヶ岳・乗鞍岳・立山・白馬岳（＋高尾山の補強）</t>
+        </is>
+      </c>
+      <c r="E490" s="29" t="inlineStr">
+        <is>
+          <t>診断の理由用に山の特徴を個別調査（第2回）</t>
+        </is>
+      </c>
+      <c r="F490" s="29" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G490" s="29" t="inlineStr">
+        <is>
+          <t>一言紹介と「こんな気分の人に」から自動で選択</t>
+        </is>
+      </c>
+      <c r="H490" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに調べた特徴4〜6項目を登録（累計22山）</t>
+        </is>
+      </c>
+      <c r="I490" s="29" t="inlineStr">
+        <is>
+          <t>観光協会・自治体・環境省・山岳メディアの記事（各山の featureSources に記録）</t>
+        </is>
+      </c>
+      <c r="J490" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K490" s="29" t="inlineStr">
+        <is>
+          <t>中（検索結果の要約で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="29" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C491" s="29" t="inlineStr">
+        <is>
+          <t>fuji ほか15山</t>
+        </is>
+      </c>
+      <c r="D491" s="29" t="inlineStr">
+        <is>
+          <t>富士山・槍ヶ岳・奥穂高岳・剱岳・北岳・甲斐駒ヶ岳・仙丈ヶ岳・鳳凰山・御嶽山・白山・妙高山・火打山・浅間山・両神山・甲武信ヶ岳・蓼科山</t>
+        </is>
+      </c>
+      <c r="E491" s="29" t="inlineStr">
+        <is>
+          <t>診断の理由用に山の特徴を個別調査（第3回）</t>
+        </is>
+      </c>
+      <c r="F491" s="29" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G491" s="29" t="inlineStr">
+        <is>
+          <t>一言紹介と「こんな気分の人に」から自動で選択</t>
+        </is>
+      </c>
+      <c r="H491" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに調べた特徴4〜6項目を登録（累計38山）</t>
+        </is>
+      </c>
+      <c r="I491" s="29" t="inlineStr">
+        <is>
+          <t>観光協会・自治体・環境省・国土交通省の解説・山岳メディアの記事（各山の featureSources に記録）</t>
+        </is>
+      </c>
+      <c r="J491" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K491" s="29" t="inlineStr">
+        <is>
+          <t>中（検索結果の要約で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="29" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C492" s="29" t="inlineStr">
+        <is>
+          <t>jonengatake ほか15山</t>
+        </is>
+      </c>
+      <c r="D492" s="29" t="inlineStr">
+        <is>
+          <t>常念岳・鹿島槍ヶ岳・五竜岳・唐松岳・薬師岳・笠ヶ岳・蝶ヶ岳・大天井岳・塩見岳・赤石岳・聖岳・光岳・空木岳・恵那山・美ヶ原・霧ヶ峰</t>
+        </is>
+      </c>
+      <c r="E492" s="29" t="inlineStr">
+        <is>
+          <t>診断の理由用に山の特徴を個別調査（第4回）</t>
+        </is>
+      </c>
+      <c r="F492" s="29" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G492" s="29" t="inlineStr">
+        <is>
+          <t>一言紹介と「こんな気分の人に」から自動で選択</t>
+        </is>
+      </c>
+      <c r="H492" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに調べた特徴4〜5項目を登録（累計54山）</t>
+        </is>
+      </c>
+      <c r="I492" s="29" t="inlineStr">
+        <is>
+          <t>観光協会・自治体（静岡市ほか）・林野庁・国土交通省の解説・山岳メディアの記事（各山の featureSources に記録）</t>
+        </is>
+      </c>
+      <c r="J492" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K492" s="29" t="inlineStr">
+        <is>
+          <t>中（検索結果の要約で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="29" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C493" s="29" t="inlineStr">
+        <is>
+          <t>bandai ほか14山</t>
+        </is>
+      </c>
+      <c r="D493" s="29" t="inlineStr">
+        <is>
+          <t>磐梯山・安達太良山・蔵王山・西吾妻山・飯豊山・会津駒ヶ岳・平ヶ岳・越後駒ヶ岳・巻機山・苗場山・雨飾山・高妻山・四阿山・武尊山・男体山</t>
+        </is>
+      </c>
+      <c r="E493" s="29" t="inlineStr">
+        <is>
+          <t>診断の理由用に山の特徴を個別調査（第5回）</t>
+        </is>
+      </c>
+      <c r="F493" s="29" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G493" s="29" t="inlineStr">
+        <is>
+          <t>一言紹介と「こんな気分の人に」から自動で選択</t>
+        </is>
+      </c>
+      <c r="H493" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに調べた特徴4〜6項目を登録（累計69山）。草津白根山は規制中のため見送り</t>
+        </is>
+      </c>
+      <c r="I493" s="29" t="inlineStr">
+        <is>
+          <t>観光協会・自治体・林野庁・環境省・山岳メディアの記事（各山の featureSources に記録）</t>
+        </is>
+      </c>
+      <c r="J493" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K493" s="29" t="inlineStr">
+        <is>
+          <t>中（検索結果の要約で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="29" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C494" s="29" t="inlineStr">
+        <is>
+          <t>jinba ほか15山</t>
+        </is>
+      </c>
+      <c r="D494" s="29" t="inlineStr">
+        <is>
+          <t>陣馬山・景信山・小仏城山・大岳山・御前山・川苔山・三頭山・棒ノ折山・鷹ノ巣山・日の出山・高水三山・本仁田山・浅間嶺・蛭ヶ岳・鍋割山・三ノ塔</t>
+        </is>
+      </c>
+      <c r="E494" s="29" t="inlineStr">
+        <is>
+          <t>診断の理由用に山の特徴を個別調査（第6回）</t>
+        </is>
+      </c>
+      <c r="F494" s="29" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G494" s="29" t="inlineStr">
+        <is>
+          <t>一言紹介と「こんな気分の人に」から自動で選択</t>
+        </is>
+      </c>
+      <c r="H494" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに調べた特徴3〜5項目を登録（累計85山）</t>
+        </is>
+      </c>
+      <c r="I494" s="29" t="inlineStr">
+        <is>
+          <t>観光協会・自治体・山岳メディアの記事（各山の featureSources に記録）</t>
+        </is>
+      </c>
+      <c r="J494" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K494" s="29" t="inlineStr">
+        <is>
+          <t>中（検索結果の要約で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="29" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C495" s="29" t="inlineStr">
+        <is>
+          <t>mitsutoge ほか16山</t>
+        </is>
+      </c>
+      <c r="D495" s="29" t="inlineStr">
+        <is>
+          <t>三ツ峠山・石割山・茅ヶ岳・乾徳山・扇山・百蔵山・高川山・岩殿山・伊豆ヶ岳・武甲山・宝登山・日和田山・天覧山・多峯主山・丸山・二子山・官ノ倉山・破風山</t>
+        </is>
+      </c>
+      <c r="E495" s="29" t="inlineStr">
+        <is>
+          <t>診断の理由用に山の特徴を個別調査（第7回）</t>
+        </is>
+      </c>
+      <c r="F495" s="29" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G495" s="29" t="inlineStr">
+        <is>
+          <t>一言紹介と「こんな気分の人に」から自動で選択</t>
+        </is>
+      </c>
+      <c r="H495" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに調べた特徴3〜5項目を登録（累計102山）。九鬼山は情報が取れず見送り</t>
+        </is>
+      </c>
+      <c r="I495" s="29" t="inlineStr">
+        <is>
+          <t>観光協会・自治体・国土交通省の解説・山岳メディアの記事（各山の featureSources に記録）</t>
+        </is>
+      </c>
+      <c r="J495" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K495" s="29" t="inlineStr">
+        <is>
+          <t>中（検索結果の要約で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="29" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C496" s="29" t="inlineStr">
+        <is>
+          <t>nantaisan ほか6山</t>
+        </is>
+      </c>
+      <c r="D496" s="29" t="inlineStr">
+        <is>
+          <t>男体山・大岳山・浅間嶺・破風山・官ノ倉山・茅ヶ岳・武甲山</t>
+        </is>
+      </c>
+      <c r="E496" s="29" t="inlineStr">
+        <is>
+          <t>featureSources の点検（ページを取得して確認）</t>
+        </is>
+      </c>
+      <c r="F496" s="29" t="inlineStr">
+        <is>
+          <t>featureSources</t>
+        </is>
+      </c>
+      <c r="G496" s="29" t="inlineStr">
+        <is>
+          <t>別の山・無関係の記事を指すURLが7件</t>
+        </is>
+      </c>
+      <c r="H496" s="29" t="inlineStr">
+        <is>
+          <t>該当URLを削除（本文は該当の山の内容で変更なし）</t>
+        </is>
+      </c>
+      <c r="I496" s="29" t="inlineStr">
+        <is>
+          <t>各URLのページタイトル・本文を取得して確認</t>
+        </is>
+      </c>
+      <c r="J496" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K496" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="29" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C497" s="29" t="inlineStr">
+        <is>
+          <t>amagi ほか23山</t>
+        </is>
+      </c>
+      <c r="D497" s="29" t="inlineStr">
+        <is>
+          <t>天城山・鋸山・弘法山・草戸山・鳴虫山・富山・伊予ヶ岳・明神ヶ岳・矢倉岳・石老山・大野山・幕山・太平山・古賀志山・鎌倉アルプス・大楠山・吾妻山・倉岳山・生藤山・九鬼山・十二ヶ岳・嵐山・笹子雁ヶ腹摺山・小金沢山</t>
+        </is>
+      </c>
+      <c r="E497" s="29" t="inlineStr">
+        <is>
+          <t>診断の理由用に山の特徴を個別調査（第8回）</t>
+        </is>
+      </c>
+      <c r="F497" s="29" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G497" s="29" t="inlineStr">
+        <is>
+          <t>一言紹介と「こんな気分の人に」から自動で選択</t>
+        </is>
+      </c>
+      <c r="H497" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに調べた特徴3〜5項目を登録（累計126山）</t>
+        </is>
+      </c>
+      <c r="I497" s="29" t="inlineStr">
+        <is>
+          <t>観光協会・自治体・国土交通省の解説・山岳メディアの記事・登山記録（各山の featureSources に記録）</t>
+        </is>
+      </c>
+      <c r="J497" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K497" s="29" t="inlineStr">
+        <is>
+          <t>中（検索結果の要約で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="29" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C498" s="29" t="inlineStr">
+        <is>
+          <t>hinata ほか28山</t>
+        </is>
+      </c>
+      <c r="D498" s="29" t="inlineStr">
+        <is>
+          <t>日向山・焼岳・荒船山・浅間隠山・御座山・岩菅山・飯縄山・黒姫山・毛無山・白砂山・七面山・荒沢岳・和名倉山・平標山・笊ヶ岳・餓鬼岳・有明山・経ヶ岳・皇海山・荒川岳・黒部五郎岳・間ノ岳・農鳥岳・雁坂嶺・鋸岳・南駒ヶ岳・針ノ木岳・烏帽子岳・野口五郎岳</t>
+        </is>
+      </c>
+      <c r="E498" s="29" t="inlineStr">
+        <is>
+          <t>診断の理由用に山の特徴を個別調査（第9回）</t>
+        </is>
+      </c>
+      <c r="F498" s="29" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G498" s="29" t="inlineStr">
+        <is>
+          <t>一言紹介と「こんな気分の人に」から自動で選択</t>
+        </is>
+      </c>
+      <c r="H498" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに調べた特徴3〜5項目を登録（累計155山。草津白根山は規制中のため未登録）</t>
+        </is>
+      </c>
+      <c r="I498" s="29" t="inlineStr">
+        <is>
+          <t>観光協会・自治体・国の機関の解説・山岳メディアの記事・登山記録（各山の featureSources に記録）</t>
+        </is>
+      </c>
+      <c r="J498" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K498" s="29" t="inlineStr">
+        <is>
+          <t>中（検索結果の要約で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="29" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C499" s="29" t="inlineStr">
+        <is>
+          <t>sukai</t>
+        </is>
+      </c>
+      <c r="D499" s="29" t="inlineStr">
+        <is>
+          <t>皇海山</t>
+        </is>
+      </c>
+      <c r="E499" s="29" t="inlineStr">
+        <is>
+          <t>通れない群馬側（皇海橋）のルートが代表コースのままだった</t>
+        </is>
+      </c>
+      <c r="F499" s="29" t="inlineStr">
+        <is>
+          <t>routes / coeffMin・Max / difficulty / daytrip / types / 紹介文 / Vibes / FAQ / meta / annualItems / 検索ページ6枚</t>
+        </is>
+      </c>
+      <c r="G499" s="29" t="inlineStr">
+        <is>
+          <t>皇海橋〜皇海山（往復）5時間・11.0km・+800m／定数28／中〜上級／日帰り可</t>
+        </is>
+      </c>
+      <c r="H499" s="29" t="inlineStr">
+        <is>
+          <t>銀山平〜庚申山〜鋸山〜皇海山〜六林班峠（周回）14時間17分・24.4km・+2216m／定数57／上級／日帰り可を外す。日帰り一覧2ページから削除。通洞駅タクシーの料金・時間は未確認のためFAQから削除</t>
+        </is>
+      </c>
+      <c r="I499" s="29" t="inlineStr">
+        <is>
+          <t>沼田市 交通規制のお知らせ【市道皇海線】（令和8年9月1日）https://www.city.numata.gunma.jp/life/kotsu/douro/1018292.html ／日光市観光協会 https://www.nikko-kankou.org/spot/1108 ／距離・標高・時間は YAMAP モデルコース https://yamap.com/mountains/169</t>
+        </is>
+      </c>
+      <c r="J499" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K499" s="29" t="inlineStr">
+        <is>
+          <t>高（通行止め・所要時間）／中（距離・累積標高はYAMAP）</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="29" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C500" s="29" t="inlineStr">
+        <is>
+          <t>kusatoriyama・ranzan_saitama</t>
+        </is>
+      </c>
+      <c r="D500" s="29" t="inlineStr">
+        <is>
+          <t>草戸山・嵐山</t>
+        </is>
+      </c>
+      <c r="E500" s="29" t="inlineStr">
+        <is>
+          <t>紹介文の誤り</t>
+        </is>
+      </c>
+      <c r="F500" s="29" t="inlineStr">
+        <is>
+          <t>description / introHtml</t>
+        </is>
+      </c>
+      <c r="G500" s="29" t="inlineStr">
+        <is>
+          <t>草戸山「相模湖を望む」／嵐山「都名勝の嵐山渓谷」</t>
+        </is>
+      </c>
+      <c r="H500" s="29" t="inlineStr">
+        <is>
+          <t>草戸山「山頂の松見平から城山湖を見下ろせる」／嵐山「都名勝の」を削除</t>
+        </is>
+      </c>
+      <c r="I500" s="29" t="inlineStr">
+        <is>
+          <t>BE-PAL https://www.bepal.net/archives/258060 ほか</t>
+        </is>
+      </c>
+      <c r="J500" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K500" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>sukai</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>皇海山</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>地域表示の修正／車の所要時間の確認</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>栃木県・群馬県（登山口は栃木県日光市足尾）。車の時間は変更なし：Googleマップで新宿駅→銀山平登山者駐車場 186km・3時間19分（混雑時）、データは185km・220分</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Googleマップ（2026-10-10 取得）</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K501"/>
+  <dimension ref="A1:K510"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -51751,57 +51751,552 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="n">
+      <c r="A501" s="29" t="n">
         <v>500</v>
       </c>
-      <c r="B501" t="inlineStr">
+      <c r="B501" s="29" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr">
+      <c r="C501" s="29" t="inlineStr">
         <is>
           <t>sukai</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr">
+      <c r="D501" s="29" t="inlineStr">
         <is>
           <t>皇海山</t>
         </is>
       </c>
-      <c r="E501" t="inlineStr">
+      <c r="E501" s="29" t="inlineStr">
         <is>
           <t>地域表示の修正／車の所要時間の確認</t>
         </is>
       </c>
-      <c r="F501" t="inlineStr">
+      <c r="F501" s="29" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="G501" t="inlineStr">
+      <c r="G501" s="29" t="inlineStr">
         <is>
           <t>群馬県</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr">
+      <c r="H501" s="29" t="inlineStr">
         <is>
           <t>栃木県・群馬県（登山口は栃木県日光市足尾）。車の時間は変更なし：Googleマップで新宿駅→銀山平登山者駐車場 186km・3時間19分（混雑時）、データは185km・220分</t>
         </is>
       </c>
-      <c r="I501" t="inlineStr">
+      <c r="I501" s="29" t="inlineStr">
         <is>
           <t>Googleマップ（2026-10-10 取得）</t>
         </is>
       </c>
-      <c r="J501" t="inlineStr">
+      <c r="J501" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr">
+      <c r="K501" s="29" t="inlineStr">
         <is>
           <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="29" t="n">
+        <v>501</v>
+      </c>
+      <c r="B502" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C502" s="29" t="inlineStr">
+        <is>
+          <t>search/shinjuku・omiya・yokohama・ofuna</t>
+        </is>
+      </c>
+      <c r="D502" s="29" t="inlineStr">
+        <is>
+          <t>出発地別の全件一覧4ページ</t>
+        </is>
+      </c>
+      <c r="E502" s="29" t="inlineStr">
+        <is>
+          <t>車の所要時間・並び順・件数表記がデータとずれていた</t>
+        </is>
+      </c>
+      <c r="F502" s="29" t="inlineStr">
+        <is>
+          <t>ページの所要時間／難易度・日帰り表示／並び順／件数</t>
+        </is>
+      </c>
+      <c r="G502" s="29" t="inlineStr">
+        <is>
+          <t>データと不一致：新宿63・大宮56・横浜59・大船28件（うち30分以上 11・26・13・1件）。件数表記は実数より1多かった</t>
+        </is>
+      </c>
+      <c r="H502" s="29" t="inlineStr">
+        <is>
+          <t>mountains.json の車の所要時間に合わせ、時間の短い順に並べ直し。scripts/sync_search_hubs.py を新設し、check_pages.py セクション17で検出</t>
+        </is>
+      </c>
+      <c r="I502" s="29" t="inlineStr">
+        <is>
+          <t>data/mountains.json（driveTime* / driveOfuna）。データ側の時間そのものの正しさは未検証</t>
+        </is>
+      </c>
+      <c r="J502" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K502" s="29" t="inlineStr">
+        <is>
+          <t>中（ページとデータの一致は高。データの値は未検証）</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="29" t="n">
+        <v>502</v>
+      </c>
+      <c r="B503" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C503" s="29" t="inlineStr">
+        <is>
+          <t>全山（140山を更新・16山は対象外）</t>
+        </is>
+      </c>
+      <c r="D503" s="29" t="inlineStr">
+        <is>
+          <t>全山</t>
+        </is>
+      </c>
+      <c r="E503" s="29" t="inlineStr">
+        <is>
+          <t>車の所要時間を全山で測り直し</t>
+        </is>
+      </c>
+      <c r="F503" s="29" t="inlineStr">
+        <is>
+          <t>driveTime* / drive* / driveDistance／meta・og・FAQの「新宿から車で約◯」／検索ページのカード／記事 kanto-day-trip-100</t>
+        </is>
+      </c>
+      <c r="G503" s="29" t="inlineStr">
+        <is>
+          <t>出所不明の値。同じ登山口で値が違う組が12組、機械計算より大幅に短い値が44件</t>
+        </is>
+      </c>
+      <c r="H503" s="29" t="inlineStr">
+        <is>
+          <t>Googleマップの経路検索（車）の渋滞を含まない標準の所要時間を5分単位に丸めた値に統一（1,310個の値が変更）。マイカー規制等で行き先に車が入れない16山は未変更で driveNeedsVerification を付与</t>
+        </is>
+      </c>
+      <c r="I503" s="29" t="inlineStr">
+        <is>
+          <t>Googleマップ（2026-10-10 取得。記録：scripts/migrations/drive_times_gmaps_2026_10.json）</t>
+        </is>
+      </c>
+      <c r="J503" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K503" s="29" t="inlineStr">
+        <is>
+          <t>中（機械取得。渋滞は含まない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="29" t="n">
+        <v>503</v>
+      </c>
+      <c r="B504" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C504" s="29" t="inlineStr">
+        <is>
+          <t>kitadake ほか15山</t>
+        </is>
+      </c>
+      <c r="D504" s="29" t="inlineStr">
+        <is>
+          <t>北岳・間ノ岳・農鳥岳・甲斐駒ヶ岳・仙丈ヶ岳・立山・剱岳・槍ヶ岳・奥穂高岳・蝶ヶ岳・乗鞍岳・至仏山・荒川岳・赤石岳・烏帽子岳・野口五郎岳</t>
+        </is>
+      </c>
+      <c r="E504" s="29" t="inlineStr">
+        <is>
+          <t>車の所要時間（一般車が登山口まで入れない山）</t>
+        </is>
+      </c>
+      <c r="F504" s="29" t="inlineStr">
+        <is>
+          <t>driveTime* / drive* / driveDistance / driveTarget</t>
+        </is>
+      </c>
+      <c r="G504" s="29" t="inlineStr">
+        <is>
+          <t>出所不明の値（未測定）</t>
+        </is>
+      </c>
+      <c r="H504" s="29" t="inlineStr">
+        <is>
+          <t>車を置く手前の駐車場・乗り換え地点までの時間に統一：芦安／戸台パーク／立山駅／沢渡／乗鞍高原観光センター／尾瀬戸倉／畑薙第一ダム／七倉</t>
+        </is>
+      </c>
+      <c r="I504" s="29" t="inlineStr">
+        <is>
+          <t>Googleマップの経路検索（2026-10-10 取得・渋滞を含まない標準の所要時間）。解決された場所の名前・住所は scripts/migrations/drive_times_hubs_2026_10.py に記録</t>
+        </is>
+      </c>
+      <c r="J504" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K504" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="29" t="n">
+        <v>504</v>
+      </c>
+      <c r="B505" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C505" s="29" t="inlineStr">
+        <is>
+          <t>全山</t>
+        </is>
+      </c>
+      <c r="D505" s="29" t="inlineStr">
+        <is>
+          <t>全山</t>
+        </is>
+      </c>
+      <c r="E505" s="29" t="inlineStr">
+        <is>
+          <t>山ページ「車でのアクセス時間」に注記を追加</t>
+        </is>
+      </c>
+      <c r="F505" s="29" t="inlineStr">
+        <is>
+          <t>gen_mountain_pages.py（car_note）／_base_mountain_style.css</t>
+        </is>
+      </c>
+      <c r="G505" s="29" t="inlineStr">
+        <is>
+          <t>注記なし</t>
+        </is>
+      </c>
+      <c r="H505" s="29" t="inlineStr">
+        <is>
+          <t>「渋滞を含まない目安」を全山に表示。登山口まで一般車が入れない16山は「◯◯までの時間。そこから乗り換え」と表示</t>
+        </is>
+      </c>
+      <c r="I505" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J505" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K505" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="29" t="n">
+        <v>505</v>
+      </c>
+      <c r="B506" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C506" s="29" t="inlineStr">
+        <is>
+          <t>komagatake・senjogatake・yari・hotaka・norikura・shibutsu</t>
+        </is>
+      </c>
+      <c r="D506" s="29" t="inlineStr">
+        <is>
+          <t>甲斐駒ヶ岳・仙丈ヶ岳・槍ヶ岳・奥穂高岳・乗鞍岳・至仏山</t>
+        </is>
+      </c>
+      <c r="E506" s="29" t="inlineStr">
+        <is>
+          <t>乗り換え地点の座標を入力（地図ボタンの行き先）</t>
+        </is>
+      </c>
+      <c r="F506" s="29" t="inlineStr">
+        <is>
+          <t>data/trailheads.json（todai-park / sawando / norikura-kogen / oze-tokura）</t>
+        </is>
+      </c>
+      <c r="G506" s="29" t="inlineStr">
+        <is>
+          <t>座標なし（名称検索で地図を開く）</t>
+        </is>
+      </c>
+      <c r="H506" s="29" t="inlineStr">
+        <is>
+          <t>戸台パーク 35.76879,138.09448／さわんどバスターミナル 36.16460,137.65594／松本市乗鞍観光センター 36.12199,137.62495／尾瀬第1駐車場 36.83814,139.25048</t>
+        </is>
+      </c>
+      <c r="I506" s="29" t="inlineStr">
+        <is>
+          <t>Googleマップの場所検索で解決された座標・住所（2026-10-10）</t>
+        </is>
+      </c>
+      <c r="J506" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K506" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="29" t="n">
+        <v>506</v>
+      </c>
+      <c r="B507" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C507" s="29" t="inlineStr">
+        <is>
+          <t>fuji／トップ・検索ページ</t>
+        </is>
+      </c>
+      <c r="D507" s="29" t="inlineStr">
+        <is>
+          <t>富士山／全体</t>
+        </is>
+      </c>
+      <c r="E507" s="29" t="inlineStr">
+        <is>
+          <t>水ヶ塚駐車場の座標を入力／車の時間の注記をトップと検索ページに追加</t>
+        </is>
+      </c>
+      <c r="F507" s="29" t="inlineStr">
+        <is>
+          <t>data/trailheads.json（mizugatsuka）／index.html／search 9ページ</t>
+        </is>
+      </c>
+      <c r="G507" s="29" t="inlineStr">
+        <is>
+          <t>座標なし／注記なし</t>
+        </is>
+      </c>
+      <c r="H507" s="29" t="inlineStr">
+        <is>
+          <t>水ヶ塚駐車場 35.30545,138.77066（裾野市須山2308）／「車の所要時間は、駐車場までの渋滞を含まない目安です」を表示</t>
+        </is>
+      </c>
+      <c r="I507" s="29" t="inlineStr">
+        <is>
+          <t>Googleマップの場所検索（2026-10-10）</t>
+        </is>
+      </c>
+      <c r="J507" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K507" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="29" t="n">
+        <v>507</v>
+      </c>
+      <c r="B508" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C508" s="29" t="inlineStr">
+        <is>
+          <t>find/index.html</t>
+        </is>
+      </c>
+      <c r="D508" s="29" t="inlineStr">
+        <is>
+          <t>山選び診断（/find/）</t>
+        </is>
+      </c>
+      <c r="E508" s="29" t="inlineStr">
+        <is>
+          <t>おすすめの理由が、行き方・難易度・コース定数ばかりだった（前回は登山タイプ診断 /recommend/ だけを直していた）</t>
+        </is>
+      </c>
+      <c r="F508" s="29" t="inlineStr">
+        <is>
+          <t>buildReason / buildFitNote</t>
+        </is>
+      </c>
+      <c r="G508" s="29" t="inlineStr">
+        <is>
+          <t>電車で行ける／難易度／コース定数／雰囲気の定型文</t>
+        </is>
+      </c>
+      <c r="H508" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに調べた特徴（featurePoints）から、選んだ気分に合うものを先に3つ表示。行き方・難易度・コース定数は下の1行に分離</t>
+        </is>
+      </c>
+      <c r="I508" s="29" t="inlineStr">
+        <is>
+          <t>data/mountains.json の featurePoints</t>
+        </is>
+      </c>
+      <c r="J508" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K508" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="29" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C509" s="29" t="inlineStr">
+        <is>
+          <t>find/index.html</t>
+        </is>
+      </c>
+      <c r="D509" s="29" t="inlineStr">
+        <is>
+          <t>山選び診断（/find/）</t>
+        </is>
+      </c>
+      <c r="E509" s="29" t="inlineStr">
+        <is>
+          <t>山の選び方（点数付け）の見直し</t>
+        </is>
+      </c>
+      <c r="F509" s="29" t="inlineStr">
+        <is>
+          <t>scoreMount / vibeHits / gearThisMonth / getTrainTime / pickTop3</t>
+        </is>
+      </c>
+      <c r="G509" s="29" t="inlineStr">
+        <is>
+          <t>気分と合わない山・今月入山できない山が上位に出ることがあった。電車は車の時間×1.4で代用</t>
+        </is>
+      </c>
+      <c r="H509" s="29" t="inlineStr">
+        <is>
+          <t>気分の判定に調べた特徴のタグを追加し、合う山が3つ以上あれば合わない山を外す。今月が入山不可・冬山装備の山と規制中の山は出さない（軽アイゼン等は体力「低」で出さない）。電車は実際の所要時間で判定。回答の全216通りで3山以上出ることを確認</t>
+        </is>
+      </c>
+      <c r="I509" s="29" t="inlineStr">
+        <is>
+          <t>data/mountains.json（gearCalendar / featurePoints / trainTime*）</t>
+        </is>
+      </c>
+      <c r="J509" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K509" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>509</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>find/index.html ほか</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>山選び診断（/find/）</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>質問を2問追加（5問→7問）</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>QUESTIONS（when / who）／scoreMount／buildReason／buildFitNote／見出し。index.html・recommend/index.html・guide/gear-checklist の「5問」表記</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>5問（交通手段・運動量・気分・移動時間・出発地）</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>「いつごろ行く予定か（今月・来月・2か月先）」「誰と行くか（ひとり・友人やパートナー・子どもや家族）」を追加。行く月の装備区分と見ごろ、同行者に合わせて山を選び、見ごろの特徴を理由の先頭に表示。回答の全1,944通りで3山以上出ることを確認</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>data/mountains.json（gearCalendar / featurePoints）</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K510"/>
+  <dimension ref="A1:K512"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -52246,55 +52246,165 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="n">
+      <c r="A510" s="29" t="n">
         <v>509</v>
       </c>
-      <c r="B510" t="inlineStr">
+      <c r="B510" s="29" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr">
+      <c r="C510" s="29" t="inlineStr">
         <is>
           <t>find/index.html ほか</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr">
+      <c r="D510" s="29" t="inlineStr">
         <is>
           <t>山選び診断（/find/）</t>
         </is>
       </c>
-      <c r="E510" t="inlineStr">
+      <c r="E510" s="29" t="inlineStr">
         <is>
           <t>質問を2問追加（5問→7問）</t>
         </is>
       </c>
-      <c r="F510" t="inlineStr">
+      <c r="F510" s="29" t="inlineStr">
         <is>
           <t>QUESTIONS（when / who）／scoreMount／buildReason／buildFitNote／見出し。index.html・recommend/index.html・guide/gear-checklist の「5問」表記</t>
         </is>
       </c>
-      <c r="G510" t="inlineStr">
+      <c r="G510" s="29" t="inlineStr">
         <is>
           <t>5問（交通手段・運動量・気分・移動時間・出発地）</t>
         </is>
       </c>
-      <c r="H510" t="inlineStr">
+      <c r="H510" s="29" t="inlineStr">
         <is>
           <t>「いつごろ行く予定か（今月・来月・2か月先）」「誰と行くか（ひとり・友人やパートナー・子どもや家族）」を追加。行く月の装備区分と見ごろ、同行者に合わせて山を選び、見ごろの特徴を理由の先頭に表示。回答の全1,944通りで3山以上出ることを確認</t>
         </is>
       </c>
-      <c r="I510" t="inlineStr">
+      <c r="I510" s="29" t="inlineStr">
         <is>
           <t>data/mountains.json（gearCalendar / featurePoints）</t>
         </is>
       </c>
-      <c r="J510" t="inlineStr">
+      <c r="J510" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr">
+      <c r="K510" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="29" t="n">
+        <v>510</v>
+      </c>
+      <c r="B511" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C511" s="29" t="inlineStr">
+        <is>
+          <t>hakusan ほか34山</t>
+        </is>
+      </c>
+      <c r="D511" s="29" t="inlineStr">
+        <is>
+          <t>白山・飯豊山・聖岳・黒部五郎岳・奥穂高岳・会津駒ヶ岳・燧ヶ岳・常念岳・焼岳・鹿島槍ヶ岳・笠ヶ岳・唐松岳・塩見岳・荒川岳・赤石岳・光岳・薬師岳・蔵王山・明神ヶ岳・矢倉岳・川苔山・鷹ノ巣山・岩殿山・丸山・大野山・百蔵山・扇山・幕山・太平山・九鬼山・破風山・嵐山・鎌倉アルプス・大楠山・官ノ倉山</t>
+        </is>
+      </c>
+      <c r="E511" s="29" t="inlineStr">
+        <is>
+          <t>YAMAPへのリンクの誤り（ユーザー指摘4山＋全山確認で発見）</t>
+        </is>
+      </c>
+      <c r="F511" s="29" t="inlineStr">
+        <is>
+          <t>yamapUrl／area（笠ヶ岳・倉岳山）</t>
+        </is>
+      </c>
+      <c r="G511" s="29" t="inlineStr">
+        <is>
+          <t>404のリンク16件／別の山を指すリンク15件／活動日記の検索を開くリンク5件。笠ヶ岳の地域「長野県北部」、倉岳山の地域「神奈川県」</t>
+        </is>
+      </c>
+      <c r="H511" s="29" t="inlineStr">
+        <is>
+          <t>YAMAPの山検索で名前・標高・都道府県が一致するページに修正（修正後、全156山のリンクを再取得して確認）。笠ヶ岳→岐阜県、倉岳山→山梨県</t>
+        </is>
+      </c>
+      <c r="I511" s="29" t="inlineStr">
+        <is>
+          <t>YAMAP（各山のページ・山検索。2026-10-10）</t>
+        </is>
+      </c>
+      <c r="J511" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K511" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>511</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>全山</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>全山</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>YAMAPリンクの見張りを月1回の確認に追加</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>scripts/check_annual_updates.py（check_yamap）／mountains.json に yamapName を追加</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>YAMAPリンクの誤りを検出する仕組みがなかった</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>毎月の年次データ確認でYAMAPリンクを開き、ページが無い・別の山を指す・山ページ以外のリンクを一覧に出す（誤りがあれば Issue が作られる）。全156山に yamapName（YAMAPのページに出る山名）を登録</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>YAMAP（2026-10-10 取得）</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K512"/>
+  <dimension ref="A1:K514"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -52356,55 +52356,165 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="n">
+      <c r="A512" s="29" t="n">
         <v>511</v>
       </c>
-      <c r="B512" t="inlineStr">
+      <c r="B512" s="29" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr">
+      <c r="C512" s="29" t="inlineStr">
         <is>
           <t>全山</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr">
+      <c r="D512" s="29" t="inlineStr">
         <is>
           <t>全山</t>
         </is>
       </c>
-      <c r="E512" t="inlineStr">
+      <c r="E512" s="29" t="inlineStr">
         <is>
           <t>YAMAPリンクの見張りを月1回の確認に追加</t>
         </is>
       </c>
-      <c r="F512" t="inlineStr">
+      <c r="F512" s="29" t="inlineStr">
         <is>
           <t>scripts/check_annual_updates.py（check_yamap）／mountains.json に yamapName を追加</t>
         </is>
       </c>
-      <c r="G512" t="inlineStr">
+      <c r="G512" s="29" t="inlineStr">
         <is>
           <t>YAMAPリンクの誤りを検出する仕組みがなかった</t>
         </is>
       </c>
-      <c r="H512" t="inlineStr">
+      <c r="H512" s="29" t="inlineStr">
         <is>
           <t>毎月の年次データ確認でYAMAPリンクを開き、ページが無い・別の山を指す・山ページ以外のリンクを一覧に出す（誤りがあれば Issue が作られる）。全156山に yamapName（YAMAPのページに出る山名）を登録</t>
         </is>
       </c>
-      <c r="I512" t="inlineStr">
+      <c r="I512" s="29" t="inlineStr">
         <is>
           <t>YAMAP（2026-10-10 取得）</t>
         </is>
       </c>
-      <c r="J512" t="inlineStr">
+      <c r="J512" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr">
+      <c r="K512" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="29" t="n">
+        <v>512</v>
+      </c>
+      <c r="B513" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C513" s="29" t="inlineStr">
+        <is>
+          <t>火山の18山</t>
+        </is>
+      </c>
+      <c r="D513" s="29" t="inlineStr">
+        <is>
+          <t>蔵王山・西吾妻山・安達太良山・磐梯山・燧ヶ岳・那須岳・日光白根山・赤城山・草津白根山・浅間山・妙高山・立山・焼岳・乗鞍岳・御嶽山・白山・富士山・男体山</t>
+        </is>
+      </c>
+      <c r="E513" s="29" t="inlineStr">
+        <is>
+          <t>噴火警戒レベルの自動表示を追加</t>
+        </is>
+      </c>
+      <c r="F513" s="29" t="inlineStr">
+        <is>
+          <t>assets/js/volcano-status.js（新規）／mountains.json に volcanoCodes・volcanoScope／gen_mountain_pages.py／index.html／find・recommend／check_annual_updates.py</t>
+        </is>
+      </c>
+      <c r="G513" s="29" t="inlineStr">
+        <is>
+          <t>噴火警戒レベルは手書きの注意文だけで、自動では追っていなかった</t>
+        </is>
+      </c>
+      <c r="H513" s="29" t="inlineStr">
+        <is>
+          <t>ページを開くたびに気象庁の噴火警報・予報を読み、山ページに現在の状態を表示。火口周辺規制以上の山は一覧の末尾に回し、診断から外す。月次の確認にも追加</t>
+        </is>
+      </c>
+      <c r="I513" s="29" t="inlineStr">
+        <is>
+          <t>気象庁 噴火警報・予報 https://www.jma.go.jp/bosai/volcano/data/warning.json （火山コードは同 volcano_list.json）</t>
+        </is>
+      </c>
+      <c r="J513" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K513" s="29" t="inlineStr">
+        <is>
+          <t>中（火山コードの対応は手で付けた）</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>513</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>更新の運用を決定（自動で切り替わるもの＋月1回の通知を受けて「月次更新して」で反映）</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>.github/workflows/annual-data-check.yml（通知文）／site-check.yml（新規）／CLAUDE.md「月次更新の手順」</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>月1回の Issue（一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Issue に運営者あての通知と次にやることを記載。プッシュのたびと毎週月曜にサイトのチェックを実行。GitHub上でAIが自動で書き換える仕組みは作らない</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K514"/>
+  <dimension ref="A1:K522"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -52466,55 +52466,495 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="n">
+      <c r="A514" s="29" t="n">
         <v>513</v>
       </c>
-      <c r="B514" t="inlineStr">
+      <c r="B514" s="29" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr">
+      <c r="C514" s="29" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr">
+      <c r="D514" s="29" t="inlineStr">
         <is>
           <t>全体</t>
         </is>
       </c>
-      <c r="E514" t="inlineStr">
+      <c r="E514" s="29" t="inlineStr">
         <is>
           <t>更新の運用を決定（自動で切り替わるもの＋月1回の通知を受けて「月次更新して」で反映）</t>
         </is>
       </c>
-      <c r="F514" t="inlineStr">
+      <c r="F514" s="29" t="inlineStr">
         <is>
           <t>.github/workflows/annual-data-check.yml（通知文）／site-check.yml（新規）／CLAUDE.md「月次更新の手順」</t>
         </is>
       </c>
-      <c r="G514" t="inlineStr">
+      <c r="G514" s="29" t="inlineStr">
         <is>
           <t>月1回の Issue（一覧のみ）</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr">
+      <c r="H514" s="29" t="inlineStr">
         <is>
           <t>Issue に運営者あての通知と次にやることを記載。プッシュのたびと毎週月曜にサイトのチェックを実行。GitHub上でAIが自動で書き換える仕組みは作らない</t>
         </is>
       </c>
-      <c r="I514" t="inlineStr">
+      <c r="I514" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J514" t="inlineStr">
+      <c r="J514" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr">
+      <c r="K514" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="29" t="n">
+        <v>514</v>
+      </c>
+      <c r="B515" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C515" s="29" t="inlineStr">
+        <is>
+          <t>新機能</t>
+        </is>
+      </c>
+      <c r="D515" s="29" t="inlineStr">
+        <is>
+          <t>全山</t>
+        </is>
+      </c>
+      <c r="E515" s="29" t="inlineStr">
+        <is>
+          <t>お気に入り数・登頂数の集計と表示（準備）</t>
+        </is>
+      </c>
+      <c r="F515" s="29" t="inlineStr">
+        <is>
+          <t>assets/js/ym-counts.js・counts-config.js（新規）／gen_mountain_pages.py／index.html／mypage／privacy</t>
+        </is>
+      </c>
+      <c r="G515" s="29" t="inlineStr">
+        <is>
+          <t>集計なし</t>
+        </is>
+      </c>
+      <c r="H515" s="29" t="inlineStr">
+        <is>
+          <t>山ページのヒーロー左上に★と旗で表示する仕組みを追加。集計先（Firebase）のアドレスが未設定のため、まだ動かない</t>
+        </is>
+      </c>
+      <c r="I515" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J515" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K515" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="29" t="n">
+        <v>515</v>
+      </c>
+      <c r="B516" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C516" s="29" t="inlineStr">
+        <is>
+          <t>新機能</t>
+        </is>
+      </c>
+      <c r="D516" s="29" t="inlineStr">
+        <is>
+          <t>山小屋80軒</t>
+        </is>
+      </c>
+      <c r="E516" s="29" t="inlineStr">
+        <is>
+          <t>山小屋まとめページ（β）を追加</t>
+        </is>
+      </c>
+      <c r="F516" s="29" t="inlineStr">
+        <is>
+          <t>data/huts.json／scripts/build_huts_from_nagano.py・gen_huts_page.py／huts/index.html／index.html（メニュー）／sitemap.xml</t>
+        </is>
+      </c>
+      <c r="G516" s="29" t="inlineStr">
+        <is>
+          <t>ページなし</t>
+        </is>
+      </c>
+      <c r="H516" s="29" t="inlineStr">
+        <is>
+          <t>長野県の公式ポータルに載っている山小屋のうち、サイトの山に関係する80軒を掲載。予約の開始・方法は出典の文を手で書き写し。規模（収容人数）は未確認</t>
+        </is>
+      </c>
+      <c r="I516" s="29" t="inlineStr">
+        <is>
+          <t>長野県 山小屋情報ポータルサイト（2026年5〜6月更新） https://www.pref.nagano.lg.jp/kankoki/sangyo/kanko/sotaikyo/yamagoya/yamagoya.html</t>
+        </is>
+      </c>
+      <c r="J516" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K516" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="29" t="n">
+        <v>516</v>
+      </c>
+      <c r="B517" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C517" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D517" s="29" t="inlineStr">
+        <is>
+          <t>山小屋80軒</t>
+        </is>
+      </c>
+      <c r="E517" s="29" t="inlineStr">
+        <is>
+          <t>対応する山の割り当てを見直し</t>
+        </is>
+      </c>
+      <c r="F517" s="29" t="inlineStr">
+        <is>
+          <t>data/huts.json（mountainIds / otherMountains）</t>
+        </is>
+      </c>
+      <c r="G517" s="29" t="inlineStr">
+        <is>
+          <t>78軒を手で割り当て（未見直し）</t>
+        </is>
+      </c>
+      <c r="H517" s="29" t="inlineStr">
+        <is>
+          <t>サイトのルートと突き合わせ、ルート上にある67軒を「対応する山」、別ルート・縦走で使う14軒を「別ルート・縦走」に分離。山本小屋ふる里館・村営天狗山荘を追加</t>
+        </is>
+      </c>
+      <c r="I517" s="29" t="inlineStr">
+        <is>
+          <t>data/mountains.json の routes と、出典の「位置」欄</t>
+        </is>
+      </c>
+      <c r="J517" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K517" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="29" t="n">
+        <v>517</v>
+      </c>
+      <c r="B518" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C518" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D518" s="29" t="inlineStr">
+        <is>
+          <t>山小屋まとめ（β）</t>
+        </is>
+      </c>
+      <c r="E518" s="29" t="inlineStr">
+        <is>
+          <t>長野県外の山小屋を追加（80軒→139軒）</t>
+        </is>
+      </c>
+      <c r="F518" s="29" t="inlineStr">
+        <is>
+          <t>scripts/huts_extra.py（新規・手入力）／data/huts.json／huts/index.html</t>
+        </is>
+      </c>
+      <c r="G518" s="29" t="inlineStr">
+        <is>
+          <t>長野県のポータルに載っている80軒のみ</t>
+        </is>
+      </c>
+      <c r="H518" s="29" t="inlineStr">
+        <is>
+          <t>南アルプス（山梨・静岡側）、北アルプス（富山・岐阜側）、雲取山、山梨の山（大菩薩・金峰・瑞牆・三ツ峠・雁坂・和名倉）、丹沢の59軒を追加。予約の開始・方法・規模は確認できたものだけ記載</t>
+        </is>
+      </c>
+      <c r="I518" s="29" t="inlineStr">
+        <is>
+          <t>営業期間：山と溪谷オンライン 山小屋リスト2026（北ア id=2535／中央・南ア id=2556）ほか。予約：各小屋の公式サイト・予約サイト（huts_extra.py の bsrc に記録）</t>
+        </is>
+      </c>
+      <c r="J518" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K518" s="29" t="inlineStr">
+        <is>
+          <t>中（予約情報の多くは検索結果の要約で確認。公式ページを直接読んだのは一部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="29" t="n">
+        <v>518</v>
+      </c>
+      <c r="B519" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C519" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D519" s="29" t="inlineStr">
+        <is>
+          <t>山小屋139軒</t>
+        </is>
+      </c>
+      <c r="E519" s="29" t="inlineStr">
+        <is>
+          <t>公式サイトと照合（予約の開始・方法・規模・営業期間）</t>
+        </is>
+      </c>
+      <c r="F519" s="29" t="inlineStr">
+        <is>
+          <t>scripts/build_huts_from_nagano.py（HUT_BOOKING・HUT_CAPACITY・HUT_OFFICIAL_NOTE）／scripts/huts_extra.py</t>
+        </is>
+      </c>
+      <c r="G519" s="29" t="inlineStr">
+        <is>
+          <t>規模あり7軒／予約の開始あり42軒</t>
+        </is>
+      </c>
+      <c r="H519" s="29" t="inlineStr">
+        <is>
+          <t>各小屋の公式ページ130件を取得して照合。規模20軒、予約の開始49軒、予約方法62軒に。宿泊時期で開始日が分かれる小屋（白馬山荘・五竜山荘・涸沢小屋・七丈小屋など）は分かれ方を記載。公式と出典で営業期間が違う4軒は公式の記載を併記</t>
+        </is>
+      </c>
+      <c r="I519" s="29" t="inlineStr">
+        <is>
+          <t>各山小屋の公式サイト（2026-10-10 取得）</t>
+        </is>
+      </c>
+      <c r="J519" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K519" s="29" t="inlineStr">
+        <is>
+          <t>中（公式ページから該当行を機械的に抜き出して目で確認。記載のない小屋は未確認のまま）</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="29" t="n">
+        <v>519</v>
+      </c>
+      <c r="B520" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C520" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D520" s="29" t="inlineStr">
+        <is>
+          <t>山小屋139軒</t>
+        </is>
+      </c>
+      <c r="E520" s="29" t="inlineStr">
+        <is>
+          <t>定期更新の仕組みを追加</t>
+        </is>
+      </c>
+      <c r="F520" s="29" t="inlineStr">
+        <is>
+          <t>scripts/update_huts.py・huts_fetch.py（新規）／data/huts_verified.json／.github/workflows/huts-update.yml／gen_huts_page.py</t>
+        </is>
+      </c>
+      <c r="G520" s="29" t="inlineStr">
+        <is>
+          <t>手動のみ</t>
+        </is>
+      </c>
+      <c r="H520" s="29" t="inlineStr">
+        <is>
+          <t>毎週、出典を取り直して営業期間を自動更新。予約の開始・方法は自動では書き換えず、出典や公式ページの記載が変わった小屋をページ上で「確認中」に切り替える</t>
+        </is>
+      </c>
+      <c r="I520" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J520" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K520" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="29" t="n">
+        <v>520</v>
+      </c>
+      <c r="B521" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C521" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D521" s="29" t="inlineStr">
+        <is>
+          <t>山小屋139軒</t>
+        </is>
+      </c>
+      <c r="E521" s="29" t="inlineStr">
+        <is>
+          <t>予約の開始・方法・規模の追加確認</t>
+        </is>
+      </c>
+      <c r="F521" s="29" t="inlineStr">
+        <is>
+          <t>scripts/build_huts_from_nagano.py／scripts/huts_extra.py／data/huts_yamakei.json（新規）／gen_huts_page.py</t>
+        </is>
+      </c>
+      <c r="G521" s="29" t="inlineStr">
+        <is>
+          <t>規模20軒・予約の開始49軒・予約方法62軒</t>
+        </is>
+      </c>
+      <c r="H521" s="29" t="inlineStr">
+        <is>
+          <t>予約サイト「やまたん」の各小屋ページ（定員・営業期間・予約方法が登録されている）24軒分と、公式サイトを1階層たどった記載を反映。規模は公式・予約サイトの定員36軒＋山と溪谷オンラインの山小屋情報の収容人数（参考）97軒。予約の開始70軒、予約方法74軒</t>
+        </is>
+      </c>
+      <c r="I521" s="29" t="inlineStr">
+        <is>
+          <t>やまたん https://www.yamatan.net/ ／各小屋の公式サイト／山と溪谷オンライン 山小屋・宿泊施設（各ページ）</t>
+        </is>
+      </c>
+      <c r="J521" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K521" s="29" t="inlineStr">
+        <is>
+          <t>中（参考の収容人数は現在の定員と違う小屋がある）</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>521</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>山小屋139軒</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>公式サイト・予約サイトからの自動取得と、見に行く頻度の切り替えを追加</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>scripts/huts_auto.py（新規）／data/huts_sources.json・huts_recipes.json・huts_history.json（新規）／update_huts.py／huts-update.yml</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>営業期間（一覧の出典）だけ自動</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>予約サイト「やまたん」24軒は定員・営業期間を自動取得。公式ページの言い回しを読むレシピ21件で予約の開始・営業期間を自動取得（年・日付・前年とのずれを確認してから採用）。発表が出そうな期間だけ3日に1回、それ以外は月1回</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K522"/>
+  <dimension ref="A1:K523"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -52906,57 +52906,112 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="n">
+      <c r="A522" s="29" t="n">
         <v>521</v>
       </c>
-      <c r="B522" t="inlineStr">
+      <c r="B522" s="29" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr">
+      <c r="C522" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr">
+      <c r="D522" s="29" t="inlineStr">
         <is>
           <t>山小屋139軒</t>
         </is>
       </c>
-      <c r="E522" t="inlineStr">
+      <c r="E522" s="29" t="inlineStr">
         <is>
           <t>公式サイト・予約サイトからの自動取得と、見に行く頻度の切り替えを追加</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr">
+      <c r="F522" s="29" t="inlineStr">
         <is>
           <t>scripts/huts_auto.py（新規）／data/huts_sources.json・huts_recipes.json・huts_history.json（新規）／update_huts.py／huts-update.yml</t>
         </is>
       </c>
-      <c r="G522" t="inlineStr">
+      <c r="G522" s="29" t="inlineStr">
         <is>
           <t>営業期間（一覧の出典）だけ自動</t>
         </is>
       </c>
-      <c r="H522" t="inlineStr">
+      <c r="H522" s="29" t="inlineStr">
         <is>
           <t>予約サイト「やまたん」24軒は定員・営業期間を自動取得。公式ページの言い回しを読むレシピ21件で予約の開始・営業期間を自動取得（年・日付・前年とのずれを確認してから採用）。発表が出そうな期間だけ3日に1回、それ以外は月1回</t>
         </is>
       </c>
-      <c r="I522" t="inlineStr">
+      <c r="I522" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J522" t="inlineStr">
+      <c r="J522" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr">
+      <c r="K522" s="29" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>522</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>山小屋まとめ（β）</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>富士山・白山・上信越・尾瀬・東北の山小屋を追加（139軒→185軒）</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>scripts/huts_extra.py／data/huts_yamakei.json／data/huts_sources.json／build_huts_from_nagano.py（萬岳荘を恵那山に）</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>139軒・54山</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>富士山25軒（富士宮口8・吉田口17）、白山2軒、妙高・火打2軒、飯豊3軒、尾瀬6軒、会津駒・越後駒・平ヶ岳・谷川岳・平標山・皇海山・雨飾山・恵那山の小屋を追加。小屋のある山は69山に。営業期間は「例年」の値で、予約サイトに登録のある14軒は今年の営業期間・定員を自動取得</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>山と溪谷オンライン 山小屋・宿泊施設（各ページ）／予約サイト「やまたん」</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>中（例年の値。今年の日程は予約サイト登録分のみ）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K523"/>
+  <dimension ref="A1:K525"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -52961,57 +52961,167 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="n">
+      <c r="A523" s="29" t="n">
         <v>522</v>
       </c>
-      <c r="B523" t="inlineStr">
+      <c r="B523" s="29" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr">
+      <c r="C523" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr">
+      <c r="D523" s="29" t="inlineStr">
         <is>
           <t>山小屋まとめ（β）</t>
         </is>
       </c>
-      <c r="E523" t="inlineStr">
+      <c r="E523" s="29" t="inlineStr">
         <is>
           <t>富士山・白山・上信越・尾瀬・東北の山小屋を追加（139軒→185軒）</t>
         </is>
       </c>
-      <c r="F523" t="inlineStr">
+      <c r="F523" s="29" t="inlineStr">
         <is>
           <t>scripts/huts_extra.py／data/huts_yamakei.json／data/huts_sources.json／build_huts_from_nagano.py（萬岳荘を恵那山に）</t>
         </is>
       </c>
-      <c r="G523" t="inlineStr">
+      <c r="G523" s="29" t="inlineStr">
         <is>
           <t>139軒・54山</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr">
+      <c r="H523" s="29" t="inlineStr">
         <is>
           <t>富士山25軒（富士宮口8・吉田口17）、白山2軒、妙高・火打2軒、飯豊3軒、尾瀬6軒、会津駒・越後駒・平ヶ岳・谷川岳・平標山・皇海山・雨飾山・恵那山の小屋を追加。小屋のある山は69山に。営業期間は「例年」の値で、予約サイトに登録のある14軒は今年の営業期間・定員を自動取得</t>
         </is>
       </c>
-      <c r="I523" t="inlineStr">
+      <c r="I523" s="29" t="inlineStr">
         <is>
           <t>山と溪谷オンライン 山小屋・宿泊施設（各ページ）／予約サイト「やまたん」</t>
         </is>
       </c>
-      <c r="J523" t="inlineStr">
+      <c r="J523" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr">
+      <c r="K523" s="29" t="inlineStr">
         <is>
           <t>中（例年の値。今年の日程は予約サイト登録分のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>523</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>山小屋185軒</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>予約の開始・予約方法を公式サイトで追加確認</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>scripts/huts_booking_extra.py（新規）／data/huts_official_urls.json（新規）</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>予約の開始71軒・予約方法76軒（139軒中）</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>公式サイトの未登録35軒のURLを特定し、全185軒の公式サイトを1階層たどって確認。予約の開始81軒、予約方法121軒、予約必須79軒（185軒中）</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>各山小屋の公式サイト・予約サイト「やまたん」（2026-10-10 取得）</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>524</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>山小屋まとめ（β）</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>表示の見直しと「山から探す」の追加</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>scripts/gen_huts_page.py（全面書き換え）／huts/index.html</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>項目を縦に並べた一覧のみ</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>予約の開始・予約方法・規模を大きな3つの枠で表示し、補足は小さい字に。出典の原文や電話は「くわしく」に収納。「山から探す」（69山）を追加し、/huts/?m=山ID で山ごとの一覧を直接開ける</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K525"/>
+  <dimension ref="A1:K526"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -53016,112 +53016,167 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" t="n">
+      <c r="A524" s="29" t="n">
         <v>523</v>
       </c>
-      <c r="B524" t="inlineStr">
+      <c r="B524" s="29" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
+      <c r="C524" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr">
+      <c r="D524" s="29" t="inlineStr">
         <is>
           <t>山小屋185軒</t>
         </is>
       </c>
-      <c r="E524" t="inlineStr">
+      <c r="E524" s="29" t="inlineStr">
         <is>
           <t>予約の開始・予約方法を公式サイトで追加確認</t>
         </is>
       </c>
-      <c r="F524" t="inlineStr">
+      <c r="F524" s="29" t="inlineStr">
         <is>
           <t>scripts/huts_booking_extra.py（新規）／data/huts_official_urls.json（新規）</t>
         </is>
       </c>
-      <c r="G524" t="inlineStr">
+      <c r="G524" s="29" t="inlineStr">
         <is>
           <t>予約の開始71軒・予約方法76軒（139軒中）</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr">
+      <c r="H524" s="29" t="inlineStr">
         <is>
           <t>公式サイトの未登録35軒のURLを特定し、全185軒の公式サイトを1階層たどって確認。予約の開始81軒、予約方法121軒、予約必須79軒（185軒中）</t>
         </is>
       </c>
-      <c r="I524" t="inlineStr">
+      <c r="I524" s="29" t="inlineStr">
         <is>
           <t>各山小屋の公式サイト・予約サイト「やまたん」（2026-10-10 取得）</t>
         </is>
       </c>
-      <c r="J524" t="inlineStr">
+      <c r="J524" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr">
+      <c r="K524" s="29" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="n">
+      <c r="A525" s="29" t="n">
         <v>524</v>
       </c>
-      <c r="B525" t="inlineStr">
+      <c r="B525" s="29" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
+      <c r="C525" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr">
+      <c r="D525" s="29" t="inlineStr">
         <is>
           <t>山小屋まとめ（β）</t>
         </is>
       </c>
-      <c r="E525" t="inlineStr">
+      <c r="E525" s="29" t="inlineStr">
         <is>
           <t>表示の見直しと「山から探す」の追加</t>
         </is>
       </c>
-      <c r="F525" t="inlineStr">
+      <c r="F525" s="29" t="inlineStr">
         <is>
           <t>scripts/gen_huts_page.py（全面書き換え）／huts/index.html</t>
         </is>
       </c>
-      <c r="G525" t="inlineStr">
+      <c r="G525" s="29" t="inlineStr">
         <is>
           <t>項目を縦に並べた一覧のみ</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr">
+      <c r="H525" s="29" t="inlineStr">
         <is>
           <t>予約の開始・予約方法・規模を大きな3つの枠で表示し、補足は小さい字に。出典の原文や電話は「くわしく」に収納。「山から探す」（69山）を追加し、/huts/?m=山ID で山ごとの一覧を直接開ける</t>
         </is>
       </c>
-      <c r="I525" t="inlineStr">
+      <c r="I525" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J525" t="inlineStr">
+      <c r="J525" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr">
+      <c r="K525" s="29" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>525</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>山小屋185軒</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>予約の開始・予約方法の追加確認（2回目）</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>scripts/huts_booking_extra.py／build_huts_from_nagano.py</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>予約の開始81軒・予約方法121軒</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>公式サイトのお知らせ・予約案内、自治体・観光協会のページを小屋ごとに検索して確認。予約の開始101軒、予約方法159軒（185軒中）。尾瀬・平標山・高谷池・飯豊切合小屋は今年の営業期間も反映</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>各山小屋の公式サイト・観光協会ほか（2026-10-10 検索）。富士山吉田口の一部は山小屋まとめサイトの記載</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>中（多くは検索結果の要約で確認）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K526"/>
+  <dimension ref="A1:K527"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -53126,57 +53126,112 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="n">
+      <c r="A526" s="29" t="n">
         <v>525</v>
       </c>
-      <c r="B526" t="inlineStr">
+      <c r="B526" s="29" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
+      <c r="C526" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr">
+      <c r="D526" s="29" t="inlineStr">
         <is>
           <t>山小屋185軒</t>
         </is>
       </c>
-      <c r="E526" t="inlineStr">
+      <c r="E526" s="29" t="inlineStr">
         <is>
           <t>予約の開始・予約方法の追加確認（2回目）</t>
         </is>
       </c>
-      <c r="F526" t="inlineStr">
+      <c r="F526" s="29" t="inlineStr">
         <is>
           <t>scripts/huts_booking_extra.py／build_huts_from_nagano.py</t>
         </is>
       </c>
-      <c r="G526" t="inlineStr">
+      <c r="G526" s="29" t="inlineStr">
         <is>
           <t>予約の開始81軒・予約方法121軒</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr">
+      <c r="H526" s="29" t="inlineStr">
         <is>
           <t>公式サイトのお知らせ・予約案内、自治体・観光協会のページを小屋ごとに検索して確認。予約の開始101軒、予約方法159軒（185軒中）。尾瀬・平標山・高谷池・飯豊切合小屋は今年の営業期間も反映</t>
         </is>
       </c>
-      <c r="I526" t="inlineStr">
+      <c r="I526" s="29" t="inlineStr">
         <is>
           <t>各山小屋の公式サイト・観光協会ほか（2026-10-10 検索）。富士山吉田口の一部は山小屋まとめサイトの記載</t>
         </is>
       </c>
-      <c r="J526" t="inlineStr">
+      <c r="J526" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr">
+      <c r="K526" s="29" t="inlineStr">
         <is>
           <t>中（多くは検索結果の要約で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="29" t="n">
+        <v>526</v>
+      </c>
+      <c r="B527" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C527" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D527" s="29" t="inlineStr">
+        <is>
+          <t>山小屋185軒</t>
+        </is>
+      </c>
+      <c r="E527" s="29" t="inlineStr">
+        <is>
+          <t>通年営業の小屋の予約できる範囲／避難小屋の「予約不要」表示</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>scripts/huts_booking_extra.py／huts_auto.py／build_huts_from_nagano.py／gen_huts_page.py</t>
+        </is>
+      </c>
+      <c r="G527" s="29" t="inlineStr">
+        <is>
+          <t>予約の開始101軒（通年営業の多くが空欄、避難小屋も空欄）</t>
+        </is>
+      </c>
+      <c r="H527" s="29" t="inlineStr">
+        <is>
+          <t>山小屋まとめ：通年営業の小屋の「何か月先まで予約できるか」を公式ページで確認して追加（みやま山荘 2か月前／七ツ石小屋 13週間前／山本小屋ふる里館 約半年前／赤岳鉱泉・行者小屋 冬季分11/9〜／横尾山荘 Webは2か月前／三ツ峠山荘 365日前）。予約の受付がない避難小屋6軒を「予約不要」と表示（越後駒 駒の小屋・庚申山荘・三国小屋・本山小屋・中岳・赤石岳）。介山荘・ロッヂ長兵衛は公式に記載なしと表示。予約サイト「やまたん」の「◯日前／◯か月前から」を自動取得に追加（huts_auto.py）</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>各小屋の公式ページ・魚沼市・日光市（2026-10-10 本文を取得して確認）。三国小屋・本山小屋の「予約不要」は山小屋情報サイト（yamagoya.info）の記載</t>
+        </is>
+      </c>
+      <c r="J527" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K527" s="29" t="inlineStr">
+        <is>
+          <t>高（公式ページの本文）。三国小屋・本山小屋は中</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K527"/>
+  <dimension ref="A1:K528"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -53204,7 +53204,7 @@
           <t>通年営業の小屋の予約できる範囲／避難小屋の「予約不要」表示</t>
         </is>
       </c>
-      <c r="F527" t="inlineStr">
+      <c r="F527" s="29" t="inlineStr">
         <is>
           <t>scripts/huts_booking_extra.py／huts_auto.py／build_huts_from_nagano.py／gen_huts_page.py</t>
         </is>
@@ -53219,7 +53219,7 @@
           <t>山小屋まとめ：通年営業の小屋の「何か月先まで予約できるか」を公式ページで確認して追加（みやま山荘 2か月前／七ツ石小屋 13週間前／山本小屋ふる里館 約半年前／赤岳鉱泉・行者小屋 冬季分11/9〜／横尾山荘 Webは2か月前／三ツ峠山荘 365日前）。予約の受付がない避難小屋6軒を「予約不要」と表示（越後駒 駒の小屋・庚申山荘・三国小屋・本山小屋・中岳・赤石岳）。介山荘・ロッヂ長兵衛は公式に記載なしと表示。予約サイト「やまたん」の「◯日前／◯か月前から」を自動取得に追加（huts_auto.py）</t>
         </is>
       </c>
-      <c r="I527" t="inlineStr">
+      <c r="I527" s="29" t="inlineStr">
         <is>
           <t>各小屋の公式ページ・魚沼市・日光市（2026-10-10 本文を取得して確認）。三国小屋・本山小屋の「予約不要」は山小屋情報サイト（yamagoya.info）の記載</t>
         </is>
@@ -53232,6 +53232,61 @@
       <c r="K527" s="29" t="inlineStr">
         <is>
           <t>高（公式ページの本文）。三国小屋・本山小屋は中</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>527</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>山小屋185軒</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>SNS・小屋のお知らせから予約の開始を追加確認／予約サイトの「予約開始のお知らせ」を自動取得に追加</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>scripts/huts_booking_extra.py／huts_auto.py／gen_huts_page.py／data/huts_sources.json</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>予約の開始103軒</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>予約の開始119軒。追加：甲武信小屋・冷池山荘・種池山荘・みくりが池温泉・会津駒 駒の小屋・栂池ヒュッテ・山の鼻小屋（元ページで原文確認）、やまたんのお知らせから立山室堂山荘・富士宮口5軒・日の出館・白雲荘ほか。七丈小屋（夏山4/1）・塩見小屋（GW4/1・夏6/1）を訂正</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>やまたん「2026年度シーズン予約開始のお知らせ」、山と溪谷オンライン現地最新情報、各小屋の公式お知らせ（2026-10-10 本文取得）。X・Instagramは直接読めず検索経由</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>高（原文確認）。山の鼻小屋は中</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K528"/>
+  <dimension ref="A1:K529"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -53236,57 +53236,112 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="n">
+      <c r="A528" s="29" t="n">
         <v>527</v>
       </c>
-      <c r="B528" t="inlineStr">
+      <c r="B528" s="29" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr">
+      <c r="C528" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr">
+      <c r="D528" s="29" t="inlineStr">
         <is>
           <t>山小屋185軒</t>
         </is>
       </c>
-      <c r="E528" t="inlineStr">
+      <c r="E528" s="29" t="inlineStr">
         <is>
           <t>SNS・小屋のお知らせから予約の開始を追加確認／予約サイトの「予約開始のお知らせ」を自動取得に追加</t>
         </is>
       </c>
-      <c r="F528" t="inlineStr">
+      <c r="F528" s="29" t="inlineStr">
         <is>
           <t>scripts/huts_booking_extra.py／huts_auto.py／gen_huts_page.py／data/huts_sources.json</t>
         </is>
       </c>
-      <c r="G528" t="inlineStr">
+      <c r="G528" s="29" t="inlineStr">
         <is>
           <t>予約の開始103軒</t>
         </is>
       </c>
-      <c r="H528" t="inlineStr">
+      <c r="H528" s="29" t="inlineStr">
         <is>
           <t>予約の開始119軒。追加：甲武信小屋・冷池山荘・種池山荘・みくりが池温泉・会津駒 駒の小屋・栂池ヒュッテ・山の鼻小屋（元ページで原文確認）、やまたんのお知らせから立山室堂山荘・富士宮口5軒・日の出館・白雲荘ほか。七丈小屋（夏山4/1）・塩見小屋（GW4/1・夏6/1）を訂正</t>
         </is>
       </c>
-      <c r="I528" t="inlineStr">
+      <c r="I528" s="29" t="inlineStr">
         <is>
           <t>やまたん「2026年度シーズン予約開始のお知らせ」、山と溪谷オンライン現地最新情報、各小屋の公式お知らせ（2026-10-10 本文取得）。X・Instagramは直接読めず検索経由</t>
         </is>
       </c>
-      <c r="J528" t="inlineStr">
+      <c r="J528" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr">
+      <c r="K528" s="29" t="inlineStr">
         <is>
           <t>高（原文確認）。山の鼻小屋は中</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>528</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>山小屋ページ</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>SEO対策（山ごと・山小屋ごとのページ新設、タイトル・説明文・構造化データ）</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>scripts/gen_huts_page.py／sitemap.xml／.github/workflows/huts-update.yml</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>/huts/ の1ページのみ（解析タグ・構造化データなし）</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>山ごと69ページ・山小屋ごと185ページ（うち15は noindex）を生成。タイトルに予約開始の答えを入れる。パンくず・FAQ・比較表・内部リンク・構造化データ・GAタグ・サイトマップ240件を追加</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>data/huts.json（表示内容は既存データのみ）</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K529"/>
+  <dimension ref="A1:K530"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -53291,57 +53291,112 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="n">
+      <c r="A529" s="29" t="n">
         <v>528</v>
       </c>
-      <c r="B529" t="inlineStr">
+      <c r="B529" s="29" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr">
+      <c r="C529" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr">
+      <c r="D529" s="29" t="inlineStr">
         <is>
           <t>山小屋ページ</t>
         </is>
       </c>
-      <c r="E529" t="inlineStr">
+      <c r="E529" s="29" t="inlineStr">
         <is>
           <t>SEO対策（山ごと・山小屋ごとのページ新設、タイトル・説明文・構造化データ）</t>
         </is>
       </c>
-      <c r="F529" t="inlineStr">
+      <c r="F529" s="29" t="inlineStr">
         <is>
           <t>scripts/gen_huts_page.py／sitemap.xml／.github/workflows/huts-update.yml</t>
         </is>
       </c>
-      <c r="G529" t="inlineStr">
+      <c r="G529" s="29" t="inlineStr">
         <is>
           <t>/huts/ の1ページのみ（解析タグ・構造化データなし）</t>
         </is>
       </c>
-      <c r="H529" t="inlineStr">
+      <c r="H529" s="29" t="inlineStr">
         <is>
           <t>山ごと69ページ・山小屋ごと185ページ（うち15は noindex）を生成。タイトルに予約開始の答えを入れる。パンくず・FAQ・比較表・内部リンク・構造化データ・GAタグ・サイトマップ240件を追加</t>
         </is>
       </c>
-      <c r="I529" t="inlineStr">
+      <c r="I529" s="29" t="inlineStr">
         <is>
           <t>data/huts.json（表示内容は既存データのみ）</t>
         </is>
       </c>
-      <c r="J529" t="inlineStr">
+      <c r="J529" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr">
+      <c r="K529" s="29" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>529</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>山小屋ページ</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>地図表示を追加（一覧・山ごと・山小屋ごと）</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>scripts/build_huts_coords.py／gen_huts_page.py／assets/js/huts-map.js／data/huts_coords.json</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>地図なし</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>185軒中167軒の位置を OpenStreetMap から取得（名前一致149軒＋同じ小屋と確かめた別表記18軒）。18軒は位置を確認できず地図に出していない</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>OpenStreetMap（Overpass API、2026-10-12 取得）。地図は地理院タイル</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>高（名前一致＋登山口から20km以内）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -6962,36 +6962,36 @@
       </c>
       <c r="F11" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[上越新幹線とき]--&gt; 高崎駅 --[JR両毛線]--&gt; 前橋駅 --[関越交通バス「あかぎ広場前行」]--&gt; あかぎ広場前（赤城山ビジターセンター建替え工事のため終点）</t>
+          <t>新宿駅 --[JR湘南新宿ライン]--&gt; 大宮駅 --[上越新幹線とき]--&gt; 高崎駅 --[JR両毛線]--&gt; 前橋駅 --[関越交通バス（スノーピークランドステーション赤城行き）]--&gt; あかぎ広場前</t>
         </is>
       </c>
       <c r="G11" s="41" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H11" s="41" t="n">
-        <v>5460</v>
+        <v>5810</v>
       </c>
       <c r="I11" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR高崎線]--&gt; 高崎駅 --[JR両毛線]--&gt; 前橋駅 --[関越交通バス「あかぎ広場前行」]--&gt; あかぎ広場前（赤城山ビジターセンター建替え工事のため終点）</t>
+          <t>大宮駅 --[JR高崎線]--&gt; 高崎駅 --[JR両毛線]--&gt; 前橋駅 --[関越交通バス（スノーピークランドステーション赤城行き）]--&gt; あかぎ広場前</t>
         </is>
       </c>
       <c r="J11" s="41" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="K11" s="41" t="n">
-        <v>3100</v>
+        <v>3450</v>
       </c>
       <c r="L11" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR湘南新宿ライン直通]--&gt; 大宮駅 --[JR高崎線]--&gt; 高崎駅 --[JR両毛線]--&gt; 前橋駅 --[関越交通バス「あかぎ広場前行」]--&gt; あかぎ広場前（赤城山ビジターセンター建替え工事のため終点）</t>
+          <t>横浜駅 --[JR湘南新宿ライン直通]--&gt; 大宮駅 --[JR高崎線]--&gt; 高崎駅 --[JR両毛線]--&gt; 前橋駅 --[関越交通バス（スノーピークランドステーション赤城行き）]--&gt; あかぎ広場前</t>
         </is>
       </c>
       <c r="M11" s="41" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="N11" s="41" t="n">
-        <v>4250</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="12" ht="26.25" customHeight="1" s="30">
@@ -9200,36 +9200,36 @@
       </c>
       <c r="F50" s="44" t="inlineStr">
         <is>
-          <t>新宿駅 --[JR中央線・青梅線]--&gt; 御嶽駅 --[西東京バス]--&gt; 御岳登山口</t>
+          <t>新宿駅 --[JR中央線・青梅線]--&gt; 御嶽駅 --[西東京バス]--&gt; ケーブル下 --[ケーブルカー]--&gt; 御岳山</t>
         </is>
       </c>
       <c r="G50" s="41" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H50" s="41" t="n">
-        <v>1374</v>
+        <v>1974</v>
       </c>
       <c r="I50" s="44" t="inlineStr">
         <is>
-          <t>大宮駅 --[JR埼京線・武蔵野線・中央線経由]--&gt; 御嶽駅 --[バス・ケーブルカー]--&gt; 御岳登山口</t>
+          <t>大宮駅 --[JR埼京線・武蔵野線・中央線経由]--&gt; 御嶽駅 --[バス・ケーブルカー]--&gt; 御岳山</t>
         </is>
       </c>
       <c r="J50" s="41" t="n">
         <v>119</v>
       </c>
       <c r="K50" s="41" t="n">
-        <v>1564</v>
+        <v>2164</v>
       </c>
       <c r="L50" s="44" t="inlineStr">
         <is>
-          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR青梅線]--&gt; 御嶽駅 --[西東京バス]--&gt; 御岳登山口</t>
+          <t>横浜駅 --[JR横浜線]--&gt; 八王子駅 --[JR青梅線]--&gt; 御嶽駅 --[西東京バス]--&gt; ケーブル下 --[ケーブルカー]--&gt; 御岳山</t>
         </is>
       </c>
       <c r="M50" s="41" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="N50" s="41" t="n">
-        <v>1744</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="30">
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K530"/>
+  <dimension ref="A1:K534"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -53346,57 +53346,277 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="n">
+      <c r="A530" s="29" t="n">
         <v>529</v>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B530" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
+      <c r="C530" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr">
+      <c r="D530" s="29" t="inlineStr">
         <is>
           <t>山小屋ページ</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr">
+      <c r="E530" s="29" t="inlineStr">
         <is>
           <t>地図表示を追加（一覧・山ごと・山小屋ごと）</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr">
+      <c r="F530" s="29" t="inlineStr">
         <is>
           <t>scripts/build_huts_coords.py／gen_huts_page.py／assets/js/huts-map.js／data/huts_coords.json</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr">
+      <c r="G530" s="29" t="inlineStr">
         <is>
           <t>地図なし</t>
         </is>
       </c>
-      <c r="H530" t="inlineStr">
+      <c r="H530" s="29" t="inlineStr">
         <is>
           <t>185軒中167軒の位置を OpenStreetMap から取得（名前一致149軒＋同じ小屋と確かめた別表記18軒）。18軒は位置を確認できず地図に出していない</t>
         </is>
       </c>
-      <c r="I530" t="inlineStr">
+      <c r="I530" s="29" t="inlineStr">
         <is>
           <t>OpenStreetMap（Overpass API、2026-10-12 取得）。地図は地理院タイル</t>
         </is>
       </c>
-      <c r="J530" t="inlineStr">
+      <c r="J530" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr">
+      <c r="K530" s="29" t="inlineStr">
         <is>
           <t>高（名前一致＋登山口から20km以内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="29" t="n">
+        <v>530</v>
+      </c>
+      <c r="B531" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C531" s="29" t="inlineStr">
+        <is>
+          <t>akagi</t>
+        </is>
+      </c>
+      <c r="D531" s="29" t="inlineStr">
+        <is>
+          <t>赤城山</t>
+        </is>
+      </c>
+      <c r="E531" s="29" t="inlineStr">
+        <is>
+          <t>バスの終点・所要時間・運賃（2026年9月19日改正）</t>
+        </is>
+      </c>
+      <c r="F531" s="29" t="inlineStr">
+        <is>
+          <t>trainRoutes／fare*／trainTime*／FAQ／annualItems</t>
+        </is>
+      </c>
+      <c r="G531" s="29" t="inlineStr">
+        <is>
+          <t>バス75分・1,500円、終点「あかぎ広場前（建替え工事のため終点）」。合計5,460／3,100／4,250円、145／170／220分</t>
+        </is>
+      </c>
+      <c r="H531" s="29" t="inlineStr">
+        <is>
+          <t>直通バス65分・1,850円（前橋駅〜あかぎ広場前）、終点はスノーピークランドステーション赤城。合計5,810／3,450／4,600円、135／160／220分。夏ダイヤの期限（11/30）を登録</t>
+        </is>
+      </c>
+      <c r="I531" s="29" t="inlineStr">
+        <is>
+          <t>関越交通 公式（赤城山直通バス）時刻表・運賃表PDF 2026年9月19日改正・改定</t>
+        </is>
+      </c>
+      <c r="J531" s="29" t="inlineStr">
+        <is>
+          <t>PDFを直接読んで確認</t>
+        </is>
+      </c>
+      <c r="K531" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="29" t="n">
+        <v>531</v>
+      </c>
+      <c r="B532" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C532" s="29" t="inlineStr">
+        <is>
+          <t>otake</t>
+        </is>
+      </c>
+      <c r="D532" s="29" t="inlineStr">
+        <is>
+          <t>大岳山</t>
+        </is>
+      </c>
+      <c r="E532" s="29" t="inlineStr">
+        <is>
+          <t>経路の終点とコースの出発点の食い違い</t>
+        </is>
+      </c>
+      <c r="F532" s="29" t="inlineStr">
+        <is>
+          <t>trainRoutes／fare*／trainTime*／FAQ</t>
+        </is>
+      </c>
+      <c r="G532" s="29" t="inlineStr">
+        <is>
+          <t>ケーブル下（御岳登山口）止まり・バス20分・ケーブルカーなし。1,374／1,564／1,744円・100分。注記にバスの間隔が2通り</t>
+        </is>
+      </c>
+      <c r="H532" s="29" t="inlineStr">
+        <is>
+          <t>御岳山駅まで（バス10分＋ケーブルカー6分）。御岳山と同じ1,974／2,164／2,344円・96分。未確認のバス本数・概算運賃を注記から削除</t>
+        </is>
+      </c>
+      <c r="I532" s="29" t="inlineStr">
+        <is>
+          <t>サイト内：御岳山（mitakesan）の検算済み経路（2026-10-07）</t>
+        </is>
+      </c>
+      <c r="J532" s="29" t="inlineStr">
+        <is>
+          <t>同じ区間の検算済みデータにそろえた</t>
+        </is>
+      </c>
+      <c r="K532" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="29" t="n">
+        <v>532</v>
+      </c>
+      <c r="B533" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C533" s="29" t="inlineStr">
+        <is>
+          <t>utsukushigahara・hijiridade</t>
+        </is>
+      </c>
+      <c r="D533" s="29" t="inlineStr">
+        <is>
+          <t>美ヶ原・聖岳</t>
+        </is>
+      </c>
+      <c r="E533" s="29" t="inlineStr">
+        <is>
+          <t>バスの終点から歩くコースの追加／コースタイムの補完</t>
+        </is>
+      </c>
+      <c r="F533" s="29" t="inlineStr">
+        <is>
+          <t>routes[]</t>
+        </is>
+      </c>
+      <c r="G533" s="29" t="inlineStr">
+        <is>
+          <t>美ヶ原：自然保護センター発のコースなし。聖岳：聖沢登山口コースの時間・距離なし</t>
+        </is>
+      </c>
+      <c r="H533" s="29" t="inlineStr">
+        <is>
+          <t>美ヶ原：自然保護センター〜王ヶ頭（往復1時間）を追加（距離・標高差は未確認のまま）。聖岳：15時間45分・23.4km（1泊2日）</t>
+        </is>
+      </c>
+      <c r="I533" s="29" t="inlineStr">
+        <is>
+          <t>tabi-mag「美ヶ原」／YAMA HACK「聖岳」（2026/03/10更新）</t>
+        </is>
+      </c>
+      <c r="J533" s="29" t="inlineStr">
+        <is>
+          <t>ページ本文を取得して確認。累積標高は未採用</t>
+        </is>
+      </c>
+      <c r="K533" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>533</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>山小屋ページ</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>営業中マーク／場所の説明／地図に山を表示／一覧を地域別に</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>scripts/huts_season.py・build_summit_coords.py・gen_huts_page.py／assets/js/huts-status.js・huts-map.js／data/summit_coords.json</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>営業中かどうかは営業期間の文を読むしかない。場所は出典の記載（81軒）だけ。地図は小屋のピンのみ</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>182軒に営業中マーク（緑・黄・灰）。167軒に山頂からの直線距離と場所の区分。地図に対応する山の山頂（69山）を表示。一覧を11地域の見出しで区切り</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>山頂の位置：OpenStreetMap（2026-10-12 取得、標高で照合）</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>営業期間は既存データの文を期間に変換（新しい事実は足していない）</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>高（距離は直線）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K534"/>
+  <dimension ref="A1:K540"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -53566,57 +53566,387 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" t="n">
+      <c r="A534" s="29" t="n">
         <v>533</v>
       </c>
-      <c r="B534" t="inlineStr">
+      <c r="B534" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr">
+      <c r="C534" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr">
+      <c r="D534" s="29" t="inlineStr">
         <is>
           <t>山小屋ページ</t>
         </is>
       </c>
-      <c r="E534" t="inlineStr">
+      <c r="E534" s="29" t="inlineStr">
         <is>
           <t>営業中マーク／場所の説明／地図に山を表示／一覧を地域別に</t>
         </is>
       </c>
-      <c r="F534" t="inlineStr">
+      <c r="F534" s="29" t="inlineStr">
         <is>
           <t>scripts/huts_season.py・build_summit_coords.py・gen_huts_page.py／assets/js/huts-status.js・huts-map.js／data/summit_coords.json</t>
         </is>
       </c>
-      <c r="G534" t="inlineStr">
+      <c r="G534" s="29" t="inlineStr">
         <is>
           <t>営業中かどうかは営業期間の文を読むしかない。場所は出典の記載（81軒）だけ。地図は小屋のピンのみ</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr">
+      <c r="H534" s="29" t="inlineStr">
         <is>
           <t>182軒に営業中マーク（緑・黄・灰）。167軒に山頂からの直線距離と場所の区分。地図に対応する山の山頂（69山）を表示。一覧を11地域の見出しで区切り</t>
         </is>
       </c>
-      <c r="I534" t="inlineStr">
+      <c r="I534" s="29" t="inlineStr">
         <is>
           <t>山頂の位置：OpenStreetMap（2026-10-12 取得、標高で照合）</t>
         </is>
       </c>
-      <c r="J534" t="inlineStr">
+      <c r="J534" s="29" t="inlineStr">
         <is>
           <t>営業期間は既存データの文を期間に変換（新しい事実は足していない）</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr">
+      <c r="K534" s="29" t="inlineStr">
         <is>
           <t>高（距離は直線）</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="29" t="n">
+        <v>534</v>
+      </c>
+      <c r="B535" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C535" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D535" s="29" t="inlineStr">
+        <is>
+          <t>山小屋ページ</t>
+        </is>
+      </c>
+      <c r="E535" s="29" t="inlineStr">
+        <is>
+          <t>山小屋の特徴（名物の食事・風呂・設備・眺め・歴史）を追加</t>
+        </is>
+      </c>
+      <c r="F535" s="29" t="inlineStr">
+        <is>
+          <t>scripts/huts_features.py（新規）／gen_huts_page.py</t>
+        </is>
+      </c>
+      <c r="G535" s="29" t="inlineStr">
+        <is>
+          <t>特徴の記載なし</t>
+        </is>
+      </c>
+      <c r="H535" s="29" t="inlineStr">
+        <is>
+          <t>75軒に特徴を登録（カードに「特徴」の行、山小屋ごとのページのFAQ・説明文にも反映）。110軒は未登録</t>
+        </is>
+      </c>
+      <c r="I535" s="29" t="inlineStr">
+        <is>
+          <t>各山小屋の公式サイト（2026-10-12 本文を取得）</t>
+        </is>
+      </c>
+      <c r="J535" s="29" t="inlineStr">
+        <is>
+          <t>公式サイトの文から手で書き写し</t>
+        </is>
+      </c>
+      <c r="K535" s="29" t="inlineStr">
+        <is>
+          <t>高（公式の記載。メニューは年で変わる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="29" t="n">
+        <v>535</v>
+      </c>
+      <c r="B536" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C536" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D536" s="29" t="inlineStr">
+        <is>
+          <t>山小屋ページ</t>
+        </is>
+      </c>
+      <c r="E536" s="29" t="inlineStr">
+        <is>
+          <t>特徴の追加（公式サイトの食事・施設ページ、山岳雑誌の紹介記事）</t>
+        </is>
+      </c>
+      <c r="F536" s="29" t="inlineStr">
+        <is>
+          <t>scripts/huts_features.py</t>
+        </is>
+      </c>
+      <c r="G536" s="29" t="inlineStr">
+        <is>
+          <t>75軒</t>
+        </is>
+      </c>
+      <c r="H536" s="29" t="inlineStr">
+        <is>
+          <t>95軒（20軒追加）。雑誌記事が根拠の5軒は出典リンクと「取材時の内容」を表示</t>
+        </is>
+      </c>
+      <c r="I536" s="29" t="inlineStr">
+        <is>
+          <t>各山小屋の公式サイト／PEAKS「北アルプス山小屋大全」「日本山小屋完全ガイド」／ランドネ／.HYAKKEI（2026-10-12 本文取得）</t>
+        </is>
+      </c>
+      <c r="J536" s="29" t="inlineStr">
+        <is>
+          <t>山と溪谷オンラインの山小屋ページは基本データのみで特徴の記載なし。SNSは直接読めず検索経由</t>
+        </is>
+      </c>
+      <c r="K536" s="29" t="inlineStr">
+        <is>
+          <t>高（公式）／中（雑誌は取材時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="29" t="n">
+        <v>536</v>
+      </c>
+      <c r="B537" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C537" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D537" s="29" t="inlineStr">
+        <is>
+          <t>公式サイトのリンク</t>
+        </is>
+      </c>
+      <c r="E537" s="29" t="inlineStr">
+        <is>
+          <t>リンク切れ・別サイト化の修正</t>
+        </is>
+      </c>
+      <c r="F537" s="29" t="inlineStr">
+        <is>
+          <t>data/huts_official_urls.json（override）／build_huts_from_nagano.py</t>
+        </is>
+      </c>
+      <c r="G537" s="29" t="inlineStr">
+        <is>
+          <t>至仏山荘のリンク先が無関係なブログに変わっていた。ほかにリンク切れ7軒・旧URL3軒</t>
+        </is>
+      </c>
+      <c r="H537" s="29" t="inlineStr">
+        <is>
+          <t>至仏山荘・トモエ館2軒・太子館・山の鼻小屋・赤岳鉱泉・行者小屋・赤岳頂上山荘を確かめ直したURLに変更。御来光山荘・花小屋・日の出館・谷川岳肩の小屋はリンクを外した</t>
+        </is>
+      </c>
+      <c r="I537" s="29" t="inlineStr">
+        <is>
+          <t>全167軒の公式リンクを開いてタイトルと応答を確認（2026-10-12）</t>
+        </is>
+      </c>
+      <c r="J537" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K537" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="29" t="n">
+        <v>537</v>
+      </c>
+      <c r="B538" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C538" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D538" s="29" t="inlineStr">
+        <is>
+          <t>山小屋ページ・マイページ・ホーム</t>
+        </is>
+      </c>
+      <c r="E538" s="29" t="inlineStr">
+        <is>
+          <t>見た目の刷新（地形図ヘッダー・12か月の帯・ガイドブック風の組版）／お気に入り／予約開始のお知らせ</t>
+        </is>
+      </c>
+      <c r="F538" s="29" t="inlineStr">
+        <is>
+          <t>scripts/gen_huts_page.py・huts_rules.py（新規）／assets/js/huts-alert.js（新規）・huts-status.js／mypage/index.html／index.html／data/huts_rules.json</t>
+        </is>
+      </c>
+      <c r="G538" s="29" t="inlineStr">
+        <is>
+          <t>文字だけのページ。お気に入り・通知なし</t>
+        </is>
+      </c>
+      <c r="H538" s="29" t="inlineStr">
+        <is>
+          <t>全255ページに地形図ヘッダー、182軒に12か月の帯。お気に入りは全員、予約開始のお知らせはホーム画面に追加した人向け（110軒が対応：何日前型33・一斉型64・期間区切り型11・月ごと型2）。お知らせがあるあいだ、下のバーの「マイページ」に鈴マーク（4秒ごとに小刻みに揺れる）</t>
+        </is>
+      </c>
+      <c r="I538" s="29" t="inlineStr">
+        <is>
+          <t>予約の型は既存の「予約の開始」の文を型に直したもの（新しい事実は足していない）</t>
+        </is>
+      </c>
+      <c r="J538" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K538" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="29" t="n">
+        <v>538</v>
+      </c>
+      <c r="B539" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C539" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D539" s="29" t="inlineStr">
+        <is>
+          <t>予約開始日の自動取得・通知</t>
+        </is>
+      </c>
+      <c r="E539" s="29" t="inlineStr">
+        <is>
+          <t>自動取得の対象を拡大／通知の見本機能／ホームの通知を簡素化</t>
+        </is>
+      </c>
+      <c r="F539" s="29" t="inlineStr">
+        <is>
+          <t>scripts/huts_make_recipes.py（新規）・huts_auto.py・huts_rules.py／data/huts_recipes.json／assets/js/huts-alert.js／.github/workflows/huts-update.yml</t>
+        </is>
+      </c>
+      <c r="G539" s="29" t="inlineStr">
+        <is>
+          <t>予約開始日のレシピ13軒。手で書いた型が自動取得より優先。通知用データが定期更新の公開対象外</t>
+        </is>
+      </c>
+      <c r="H539" s="29" t="inlineStr">
+        <is>
+          <t>レシピ24軒（11軒追加）。自動の日付が新しい年なら型より優先。レシピの無い30軒は来季の候補文を報告に出す。通知の見本、ホームは鈴と2秒のお知らせのみ</t>
+        </is>
+      </c>
+      <c r="I539" s="29" t="inlineStr">
+        <is>
+          <t>各山小屋の公式ページの現在の文（2026-10-12）</t>
+        </is>
+      </c>
+      <c r="J539" s="29" t="inlineStr">
+        <is>
+          <t>作った正規表現を当て直し、同じ日付が読めることを確認</t>
+        </is>
+      </c>
+      <c r="K539" s="29" t="inlineStr">
+        <is>
+          <t>高（読み取りは翌年の文が同じ言い回しの場合に限る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>539</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>山小屋まとめ（/huts/）</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>予約開始のお知らせの案内バナーと説明ポップアップ</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>scripts/gen_huts_page.py／assets/js/huts-alert.js</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>案内なし（各山小屋ページの設定欄のみ）</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>上部にバナーを追加。押すと説明・対応軒数（110軒／185軒、型ごとの内訳）・見本・ホーム画面への追加案内のポップアップが開く</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K540"/>
+  <dimension ref="A1:K543"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -53896,55 +53896,220 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="n">
+      <c r="A540" s="29" t="n">
         <v>539</v>
       </c>
-      <c r="B540" t="inlineStr">
+      <c r="B540" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr">
+      <c r="C540" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr">
+      <c r="D540" s="29" t="inlineStr">
         <is>
           <t>山小屋まとめ（/huts/）</t>
         </is>
       </c>
-      <c r="E540" t="inlineStr">
+      <c r="E540" s="29" t="inlineStr">
         <is>
           <t>予約開始のお知らせの案内バナーと説明ポップアップ</t>
         </is>
       </c>
-      <c r="F540" t="inlineStr">
+      <c r="F540" s="29" t="inlineStr">
         <is>
           <t>scripts/gen_huts_page.py／assets/js/huts-alert.js</t>
         </is>
       </c>
-      <c r="G540" t="inlineStr">
+      <c r="G540" s="29" t="inlineStr">
         <is>
           <t>案内なし（各山小屋ページの設定欄のみ）</t>
         </is>
       </c>
-      <c r="H540" t="inlineStr">
+      <c r="H540" s="29" t="inlineStr">
         <is>
           <t>上部にバナーを追加。押すと説明・対応軒数（110軒／185軒、型ごとの内訳）・見本・ホーム画面への追加案内のポップアップが開く</t>
         </is>
       </c>
-      <c r="I540" t="inlineStr">
+      <c r="I540" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J540" t="inlineStr">
+      <c r="J540" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr">
+      <c r="K540" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="29" t="n">
+        <v>540</v>
+      </c>
+      <c r="B541" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C541" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D541" s="29" t="inlineStr">
+        <is>
+          <t>予約開始日の自動取得</t>
+        </is>
+      </c>
+      <c r="E541" s="29" t="inlineStr">
+        <is>
+          <t>予約開始の書き方を型で読む仕組み（全小屋に適用）</t>
+        </is>
+      </c>
+      <c r="F541" s="29" t="inlineStr">
+        <is>
+          <t>scripts/huts_patterns.py（新規）・huts_auto.py・huts_rules.py・huts_booking_extra.py</t>
+        </is>
+      </c>
+      <c r="G541" s="29" t="inlineStr">
+        <is>
+          <t>小屋ごとの読み取り設定（24軒）と予約サイトのお知らせだけ</t>
+        </is>
+      </c>
+      <c r="H541" s="29" t="inlineStr">
+        <is>
+          <t>型で全小屋を走査。一斉解放型で自動で来季に切り替わる小屋は29→39軒。未登録・食い違い・複数候補は報告に出す。山口山荘の予約開始（3月2日・2026年）を新規登録</t>
+        </is>
+      </c>
+      <c r="I541" s="29" t="inlineStr">
+        <is>
+          <t>分かっている小屋の公式ページ・一覧の出典の文を調べて型を決定（2026-10-12）</t>
+        </is>
+      </c>
+      <c r="J541" s="29" t="inlineStr">
+        <is>
+          <t>分かっている小屋で照合：一斉型23軒中22軒・何日前型19軒中19軒で最上位の候補が正しい</t>
+        </is>
+      </c>
+      <c r="K541" s="29" t="inlineStr">
+        <is>
+          <t>高（自動採用は前年との照合つき）</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="29" t="n">
+        <v>541</v>
+      </c>
+      <c r="B542" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C542" s="29" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D542" s="29" t="inlineStr">
+        <is>
+          <t>予約開始のお知らせ</t>
+        </is>
+      </c>
+      <c r="E542" s="29" t="inlineStr">
+        <is>
+          <t>見本を、ホームとマイページの画面の見本に変更</t>
+        </is>
+      </c>
+      <c r="F542" s="29" t="inlineStr">
+        <is>
+          <t>assets/js/huts-alert.js</t>
+        </is>
+      </c>
+      <c r="G542" s="29" t="inlineStr">
+        <is>
+          <t>見本は、いま開いているページの上にお知らせを順に出すだけ</t>
+        </is>
+      </c>
+      <c r="H542" s="29" t="inlineStr">
+        <is>
+          <t>ホームとマイページの小さな画面を並べ、上のお知らせ（ホームは2秒で消える／マイページは残る）・一覧の「あと◯日」・下のバーの鈴を、1週間前・前日・当日の順に見せる</t>
+        </is>
+      </c>
+      <c r="I542" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J542" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K542" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>542</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>山小屋</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>予約開始のお知らせ</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>実際の画面でのお試し通知</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>assets/js/huts-alert.js／scripts/gen_huts_page.py</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>見本は山小屋ページ内の小さな画面だけ</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>お試しをセットすると、ホームとマイページで本物と同じ表示（上のお知らせ・一覧・鈴）が出る。マイページで見るとお試しが終わり表示が消える（見なくても1日で消える）</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K543"/>
+  <dimension ref="A1:K562"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -54061,57 +54061,1102 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="n">
+      <c r="A543" s="29" t="n">
         <v>542</v>
       </c>
-      <c r="B543" t="inlineStr">
+      <c r="B543" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr">
+      <c r="C543" s="29" t="inlineStr">
         <is>
           <t>山小屋</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr">
+      <c r="D543" s="29" t="inlineStr">
         <is>
           <t>予約開始のお知らせ</t>
         </is>
       </c>
-      <c r="E543" t="inlineStr">
+      <c r="E543" s="29" t="inlineStr">
         <is>
           <t>実際の画面でのお試し通知</t>
         </is>
       </c>
-      <c r="F543" t="inlineStr">
+      <c r="F543" s="29" t="inlineStr">
         <is>
           <t>assets/js/huts-alert.js／scripts/gen_huts_page.py</t>
         </is>
       </c>
-      <c r="G543" t="inlineStr">
+      <c r="G543" s="29" t="inlineStr">
         <is>
           <t>見本は山小屋ページ内の小さな画面だけ</t>
         </is>
       </c>
-      <c r="H543" t="inlineStr">
+      <c r="H543" s="29" t="inlineStr">
         <is>
           <t>お試しをセットすると、ホームとマイページで本物と同じ表示（上のお知らせ・一覧・鈴）が出る。マイページで見るとお試しが終わり表示が消える（見なくても1日で消える）</t>
         </is>
       </c>
-      <c r="I543" t="inlineStr">
+      <c r="I543" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J543" t="inlineStr">
+      <c r="J543" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr">
+      <c r="K543" s="29" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="29" t="n">
+        <v>543</v>
+      </c>
+      <c r="B544" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C544" s="29" t="inlineStr">
+        <is>
+          <t>全156山</t>
+        </is>
+      </c>
+      <c r="D544" s="29" t="inlineStr">
+        <is>
+          <t>山ページ</t>
+        </is>
+      </c>
+      <c r="E544" s="29" t="inlineStr">
+        <is>
+          <t>検索結果の見出し・説明文の作り直し（クリック率の改善）</t>
+        </is>
+      </c>
+      <c r="F544" s="29" t="inlineStr">
+        <is>
+          <t>scripts/build_meta.py（新規）・gen_mountain_pages.py／mountains.json の metaTitle・metaDescription／sitemap.xml</t>
+        </is>
+      </c>
+      <c r="G544" s="29" t="inlineStr">
+        <is>
+          <t>見出し「◯◯ 登山｜初中級・定数14〜20| Yamatch」（全山同じ形。「定数」が中心）。説明文は116山が同じひな形。更新日は固定値</t>
+        </is>
+      </c>
+      <c r="H544" s="29" t="inlineStr">
+        <is>
+          <t>見出しに所要時間・難易度・最寄り駅からの行き方を入れた形に（全156山）。説明文は116山を作り直し、40山は手書きのまま。更新日・記事の構造化データ・山ごとの画像を追加</t>
+        </is>
+      </c>
+      <c r="I544" s="29" t="inlineStr">
+        <is>
+          <t>mountains.json の既存の値のみ</t>
+        </is>
+      </c>
+      <c r="J544" s="29" t="inlineStr">
+        <is>
+          <t>新しい事実は足していない</t>
+        </is>
+      </c>
+      <c r="K544" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="29" t="n">
+        <v>544</v>
+      </c>
+      <c r="B545" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C545" s="29" t="inlineStr">
+        <is>
+          <t>全156山</t>
+        </is>
+      </c>
+      <c r="D545" s="29" t="inlineStr">
+        <is>
+          <t>山ページ</t>
+        </is>
+      </c>
+      <c r="E545" s="29" t="inlineStr">
+        <is>
+          <t>Search Console の検索語に合わせた見出し・説明文（山ごと）</t>
+        </is>
+      </c>
+      <c r="F545" s="29" t="inlineStr">
+        <is>
+          <t>scripts/gsc_import.py（新規）・build_meta.py／data/seo_intents.json／mountains.json</t>
+        </is>
+      </c>
+      <c r="G545" s="29" t="inlineStr">
+        <is>
+          <t>見出しは全山同じ形（所要時間・行き方中心）。「難易度」の語なし</t>
+        </is>
+      </c>
+      <c r="H545" s="29" t="inlineStr">
+        <is>
+          <t>山ごとに、いちばん多い検索意図に答える見出し・説明文に変更（難易度133山・初心者9・アクセス9・日帰り3・時間2）。手書きだった40山の説明文は metaDescriptionManual に退避</t>
+        </is>
+      </c>
+      <c r="I545" s="29" t="inlineStr">
+        <is>
+          <t>Search Console 検索パフォーマンス（2026-09-12〜10-09・過去28日）</t>
+        </is>
+      </c>
+      <c r="J545" s="29" t="inlineStr">
+        <is>
+          <t>山ページ：表示98,499回・クリック1,921回・CTR 1.95%。山名を含む検索語の表示の約4割が「難易度・レベル」</t>
+        </is>
+      </c>
+      <c r="K545" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="29" t="n">
+        <v>545</v>
+      </c>
+      <c r="B546" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C546" s="29" t="inlineStr">
+        <is>
+          <t>全156山</t>
+        </is>
+      </c>
+      <c r="D546" s="29" t="inlineStr">
+        <is>
+          <t>山ページ</t>
+        </is>
+      </c>
+      <c r="E546" s="29" t="inlineStr">
+        <is>
+          <t>見出しの追加改善（「登山」の語・長い日帰りの言い方・大見出しの副題）</t>
+        </is>
+      </c>
+      <c r="F546" s="29" t="inlineStr">
+        <is>
+          <t>scripts/build_meta.py・gen_mountain_pages.py・_base_mountain_style.css</t>
+        </is>
+      </c>
+      <c r="G546" s="29" t="inlineStr">
+        <is>
+          <t>「登山」を含む見出しは20山。日帰り8時間以上も「日帰り◯時間」。大見出しは山名だけ</t>
+        </is>
+      </c>
+      <c r="H546" s="29" t="inlineStr">
+        <is>
+          <t>全156山の見出しに「登山」。日帰り8時間以上の9山は「健脚向け日帰り◯時間」。大見出しに副題「登山ガイド｜難易度・コースタイム・アクセス」</t>
+        </is>
+      </c>
+      <c r="I546" s="29" t="inlineStr">
+        <is>
+          <t>Search Console の検索語（「登山」を含む検索が上位語の約2割）</t>
+        </is>
+      </c>
+      <c r="J546" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K546" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="29" t="n">
+        <v>546</v>
+      </c>
+      <c r="B547" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C547" s="29" t="inlineStr">
+        <is>
+          <t>yari ほか12山</t>
+        </is>
+      </c>
+      <c r="D547" s="29" t="inlineStr">
+        <is>
+          <t>槍ヶ岳・北岳・至仏山・唐松岳・御嶽山・木曽駒ヶ岳・塔ノ岳・乾徳山・金峰山・赤城山・巻機山・高尾山・蝶ヶ岳</t>
+        </is>
+      </c>
+      <c r="E547" s="29" t="inlineStr">
+        <is>
+          <t>難易度の理由を個別に調査して書き直し（第1回）</t>
+        </is>
+      </c>
+      <c r="F547" s="29" t="inlineStr">
+        <is>
+          <t>dlReasonsHtml／dlReasonsSources（scripts/migrations/difficulty_reasons_2026_10.py）</t>
+        </is>
+      </c>
+      <c r="G547" s="29" t="inlineStr">
+        <is>
+          <t>ひな形の文（「◯◯は上級レベル（コース定数…）。初心者には不向き…」）</t>
+        </is>
+      </c>
+      <c r="H547" s="29" t="inlineStr">
+        <is>
+          <t>山ごとの具体的な理由（岩場・鎖・急登・行程・雪渓・規制など）を3〜5項目</t>
+        </is>
+      </c>
+      <c r="I547" s="29" t="inlineStr">
+        <is>
+          <t>尾瀬保護財団・新潟県・秦野市観光協会・王滝村・蝶ヶ岳ヒュッテ・信州 山のグレーディング、登山ガイドサイト（各山の dlReasonsSources）</t>
+        </is>
+      </c>
+      <c r="J547" s="29" t="inlineStr">
+        <is>
+          <t>公式ページは本文を取得して確認。ガイドサイト分は検索結果の要約で確認</t>
+        </is>
+      </c>
+      <c r="K547" s="29" t="inlineStr">
+        <is>
+          <t>高（公式）／中（ガイドサイト）</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="29" t="n">
+        <v>547</v>
+      </c>
+      <c r="B548" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C548" s="29" t="inlineStr">
+        <is>
+          <t>yakedake ほか11山</t>
+        </is>
+      </c>
+      <c r="D548" s="29" t="inlineStr">
+        <is>
+          <t>焼岳・笠ヶ岳・磐梯山・金時山・富士山・安達太良山・日光白根山・白山・那須岳・苗場山・大菩薩嶺・常念岳</t>
+        </is>
+      </c>
+      <c r="E548" s="29" t="inlineStr">
+        <is>
+          <t>難易度の理由を個別に調査して書き直し（第2回）</t>
+        </is>
+      </c>
+      <c r="F548" s="29" t="inlineStr">
+        <is>
+          <t>dlReasonsHtml／dlReasonsSources（scripts/migrations/difficulty_reasons2_2026_10.py）</t>
+        </is>
+      </c>
+      <c r="G548" s="29" t="inlineStr">
+        <is>
+          <t>ひな形の文</t>
+        </is>
+      </c>
+      <c r="H548" s="29" t="inlineStr">
+        <is>
+          <t>山ごとの具体的な理由を4〜6項目。個別の理由つきは計40山</t>
+        </is>
+      </c>
+      <c r="I548" s="29" t="inlineStr">
+        <is>
+          <t>磐梯山ビジターセンター・石川県・富士登山オフィシャルサイト・内閣府（安達太良山の火山ガス事故）、登山ガイドサイト</t>
+        </is>
+      </c>
+      <c r="J548" s="29" t="inlineStr">
+        <is>
+          <t>公式ページは本文を取得して確認。ガイドサイト分は検索結果の要約で確認</t>
+        </is>
+      </c>
+      <c r="K548" s="29" t="inlineStr">
+        <is>
+          <t>高（公式）／中（ガイドサイト）</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="29" t="n">
+        <v>548</v>
+      </c>
+      <c r="B549" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C549" s="29" t="inlineStr">
+        <is>
+          <t>hakusan</t>
+        </is>
+      </c>
+      <c r="D549" s="29" t="inlineStr">
+        <is>
+          <t>白山</t>
+        </is>
+      </c>
+      <c r="E549" s="29" t="inlineStr">
+        <is>
+          <t>通行止めの注意表示を訂正</t>
+        </is>
+      </c>
+      <c r="F549" s="29" t="inlineStr">
+        <is>
+          <t>status／warnBanner／annualItems</t>
+        </is>
+      </c>
+      <c r="G549" s="29" t="inlineStr">
+        <is>
+          <t>「観光新道の一部が通行止め。砂防新道は通行可。往復とも砂防新道を利用」</t>
+        </is>
+      </c>
+      <c r="H549" s="29" t="inlineStr">
+        <is>
+          <t>砂防新道の南竜分岐〜黒ボコ岩間も9月14日〜10月下旬に通行止め（工事）。中飯場の水場・トイレ使用不可。観光新道の通行止めも併記</t>
+        </is>
+      </c>
+      <c r="I549" s="29" t="inlineStr">
+        <is>
+          <t>石川県「白山の施設・登山道の状況について」（2026-10-02時点の記載を2026-10-12に確認）</t>
+        </is>
+      </c>
+      <c r="J549" s="29" t="inlineStr">
+        <is>
+          <t>本文を取得して確認</t>
+        </is>
+      </c>
+      <c r="K549" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="29" t="n">
+        <v>549</v>
+      </c>
+      <c r="B550" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C550" s="29" t="inlineStr">
+        <is>
+          <t>ontakesan</t>
+        </is>
+      </c>
+      <c r="D550" s="29" t="inlineStr">
+        <is>
+          <t>御嶽山</t>
+        </is>
+      </c>
+      <c r="E550" s="29" t="inlineStr">
+        <is>
+          <t>コースの標高差を訂正</t>
+        </is>
+      </c>
+      <c r="F550" s="29" t="inlineStr">
+        <is>
+          <t>routes[0].elevation</t>
+        </is>
+      </c>
+      <c r="G550" s="29" t="inlineStr">
+        <is>
+          <t>+600m</t>
+        </is>
+      </c>
+      <c r="H550" s="29" t="inlineStr">
+        <is>
+          <t>+890m</t>
+        </is>
+      </c>
+      <c r="I550" s="29" t="inlineStr">
+        <is>
+          <t>田の原（約2,180m）〜剣ヶ峰（3,067m）。運営者の指示</t>
+        </is>
+      </c>
+      <c r="J550" s="29" t="inlineStr">
+        <is>
+          <t>標高の差し引き</t>
+        </is>
+      </c>
+      <c r="K550" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="29" t="n">
+        <v>550</v>
+      </c>
+      <c r="B551" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C551" s="29" t="inlineStr">
+        <is>
+          <t>tonosaki</t>
+        </is>
+      </c>
+      <c r="D551" s="29" t="inlineStr">
+        <is>
+          <t>塔ノ岳</t>
+        </is>
+      </c>
+      <c r="E551" s="29" t="inlineStr">
+        <is>
+          <t>コースの所要時間を訂正</t>
+        </is>
+      </c>
+      <c r="F551" s="29" t="inlineStr">
+        <is>
+          <t>大倉尾根ルート</t>
+        </is>
+      </c>
+      <c r="G551" s="29" t="inlineStr">
+        <is>
+          <t>5時間</t>
+        </is>
+      </c>
+      <c r="H551" s="29" t="inlineStr">
+        <is>
+          <t>6時間</t>
+        </is>
+      </c>
+      <c r="I551" s="29" t="inlineStr">
+        <is>
+          <t>秦野市観光協会（歩行約6時間）。運営者の指示</t>
+        </is>
+      </c>
+      <c r="J551" s="29" t="inlineStr">
+        <is>
+          <t>出典ページ</t>
+        </is>
+      </c>
+      <c r="K551" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="29" t="n">
+        <v>551</v>
+      </c>
+      <c r="B552" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C552" s="29" t="inlineStr">
+        <is>
+          <t>makihata</t>
+        </is>
+      </c>
+      <c r="D552" s="29" t="inlineStr">
+        <is>
+          <t>巻機山</t>
+        </is>
+      </c>
+      <c r="E552" s="29" t="inlineStr">
+        <is>
+          <t>コース名・内容を訂正</t>
+        </is>
+      </c>
+      <c r="F552" s="29" t="inlineStr">
+        <is>
+          <t>routes[1]</t>
+        </is>
+      </c>
+      <c r="G552" s="29" t="inlineStr">
+        <is>
+          <t>割引岳経由周回</t>
+        </is>
+      </c>
+      <c r="H552" s="29" t="inlineStr">
+        <is>
+          <t>ヌクビ沢〜割引岳〜巻機山（上級者向け・登り専用・下山禁止）。時間・距離は未記載</t>
+        </is>
+      </c>
+      <c r="I552" s="29" t="inlineStr">
+        <is>
+          <t>新潟県／南魚沼市観光協会 https://m-uonuma.jp/trekking/makihata/</t>
+        </is>
+      </c>
+      <c r="J552" s="29" t="inlineStr">
+        <is>
+          <t>出典ページ。時間・距離は未確認のため空欄</t>
+        </is>
+      </c>
+      <c r="K552" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="29" t="n">
+        <v>552</v>
+      </c>
+      <c r="B553" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C553" s="29" t="inlineStr">
+        <is>
+          <t>ontakesan</t>
+        </is>
+      </c>
+      <c r="D553" s="29" t="inlineStr">
+        <is>
+          <t>御嶽山</t>
+        </is>
+      </c>
+      <c r="E553" s="29" t="inlineStr">
+        <is>
+          <t>登れる期間と日帰り表記の矛盾を解消</t>
+        </is>
+      </c>
+      <c r="F553" s="29" t="inlineStr">
+        <is>
+          <t>metaTitle／metaDescription／faq／warnBanner</t>
+        </is>
+      </c>
+      <c r="G553" s="29" t="inlineStr">
+        <is>
+          <t>「日帰りで登れます」</t>
+        </is>
+      </c>
+      <c r="H553" s="29" t="inlineStr">
+        <is>
+          <t>「登れる期間中なら日帰り」＋【登れるのは7/1〜10/14】（10/14正午まで）</t>
+        </is>
+      </c>
+      <c r="I553" s="29" t="inlineStr">
+        <is>
+          <t>annualItems（規制緩和 7/1〜10/14正午）</t>
+        </is>
+      </c>
+      <c r="J553" s="29" t="inlineStr">
+        <is>
+          <t>ページ再生成後に grep</t>
+        </is>
+      </c>
+      <c r="K553" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="29" t="n">
+        <v>553</v>
+      </c>
+      <c r="B554" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C554" s="29" t="inlineStr">
+        <is>
+          <t>24山</t>
+        </is>
+      </c>
+      <c r="D554" s="29" t="inlineStr">
+        <is>
+          <t>日帰り検索の多い24山</t>
+        </is>
+      </c>
+      <c r="E554" s="29" t="inlineStr">
+        <is>
+          <t>FAQ「日帰りできますか」を山ごとの内容に</t>
+        </is>
+      </c>
+      <c r="F554" s="29" t="inlineStr">
+        <is>
+          <t>faq</t>
+        </is>
+      </c>
+      <c r="G554" s="29" t="inlineStr">
+        <is>
+          <t>所要時間は？日帰りできますか？（ひな形）</t>
+        </is>
+      </c>
+      <c r="H554" s="29" t="inlineStr">
+        <is>
+          <t>◯◯は日帰りできますか？所要時間の目安（山ごとのコース時間で回答）</t>
+        </is>
+      </c>
+      <c r="I554" s="29" t="inlineStr">
+        <is>
+          <t>data/seo_intents.json（日帰りの検索がある山）</t>
+        </is>
+      </c>
+      <c r="J554" s="29" t="inlineStr">
+        <is>
+          <t>routes の時間から作成。日帰り不可の7山は出典を読んで手書き</t>
+        </is>
+      </c>
+      <c r="K554" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="29" t="n">
+        <v>554</v>
+      </c>
+      <c r="B555" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C555" s="29" t="inlineStr">
+        <is>
+          <t>houou</t>
+        </is>
+      </c>
+      <c r="D555" s="29" t="inlineStr">
+        <is>
+          <t>鳳凰山</t>
+        </is>
+      </c>
+      <c r="E555" s="29" t="inlineStr">
+        <is>
+          <t>コースの時間・距離を訂正</t>
+        </is>
+      </c>
+      <c r="F555" s="29" t="inlineStr">
+        <is>
+          <t>routes</t>
+        </is>
+      </c>
+      <c r="G555" s="29" t="inlineStr">
+        <is>
+          <t>夜叉神峠9時間・18km／青木鉱泉10時間・20km</t>
+        </is>
+      </c>
+      <c r="H555" s="29" t="inlineStr">
+        <is>
+          <t>夜叉神峠15時間30分・24.3km（要確認）／青木鉱泉12時間・14.6km</t>
+        </is>
+      </c>
+      <c r="I555" s="29" t="inlineStr">
+        <is>
+          <t>https://www.yamakei-online.com/cl_record/detail.php?id=129058 ／ https://yamasugu.com/houousanzan-route/</t>
+        </is>
+      </c>
+      <c r="J555" s="29" t="inlineStr">
+        <is>
+          <t>出典ページ。夜叉神峠は出典1つで要確認</t>
+        </is>
+      </c>
+      <c r="K555" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="29" t="n">
+        <v>555</v>
+      </c>
+      <c r="B556" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C556" s="29" t="inlineStr">
+        <is>
+          <t>hirugata</t>
+        </is>
+      </c>
+      <c r="D556" s="29" t="inlineStr">
+        <is>
+          <t>蛭ヶ岳</t>
+        </is>
+      </c>
+      <c r="E556" s="29" t="inlineStr">
+        <is>
+          <t>コースの時間を訂正・日帰りコースを追加</t>
+        </is>
+      </c>
+      <c r="F556" s="29" t="inlineStr">
+        <is>
+          <t>routes</t>
+        </is>
+      </c>
+      <c r="G556" s="29" t="inlineStr">
+        <is>
+          <t>大倉往復9時間・22km</t>
+        </is>
+      </c>
+      <c r="H556" s="29" t="inlineStr">
+        <is>
+          <t>大倉往復12時間30分・26.0km。青根〜姫次往復（9時間45分・20.9km・日帰りの最短）を追加</t>
+        </is>
+      </c>
+      <c r="I556" s="29" t="inlineStr">
+        <is>
+          <t>https://yamahack.com/3215</t>
+        </is>
+      </c>
+      <c r="J556" s="29" t="inlineStr">
+        <is>
+          <t>出典ページ</t>
+        </is>
+      </c>
+      <c r="K556" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="29" t="n">
+        <v>556</v>
+      </c>
+      <c r="B557" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C557" s="29" t="inlineStr">
+        <is>
+          <t>hotaka</t>
+        </is>
+      </c>
+      <c r="D557" s="29" t="inlineStr">
+        <is>
+          <t>奥穂高岳</t>
+        </is>
+      </c>
+      <c r="E557" s="29" t="inlineStr">
+        <is>
+          <t>コースの時間・距離を訂正</t>
+        </is>
+      </c>
+      <c r="F557" s="29" t="inlineStr">
+        <is>
+          <t>routes（白出沢）</t>
+        </is>
+      </c>
+      <c r="G557" s="29" t="inlineStr">
+        <is>
+          <t>12時間・22km・+1900m</t>
+        </is>
+      </c>
+      <c r="H557" s="29" t="inlineStr">
+        <is>
+          <t>15時間・18.4km・+2400m（日帰りは健脚者のみ）</t>
+        </is>
+      </c>
+      <c r="I557" s="29" t="inlineStr">
+        <is>
+          <t>https://www.yamakei-online.com/cl_record/detail.php?id=142918</t>
+        </is>
+      </c>
+      <c r="J557" s="29" t="inlineStr">
+        <is>
+          <t>出典ページ（標準15時間）</t>
+        </is>
+      </c>
+      <c r="K557" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="29" t="n">
+        <v>557</v>
+      </c>
+      <c r="B558" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C558" s="29" t="inlineStr">
+        <is>
+          <t>kasagatake</t>
+        </is>
+      </c>
+      <c r="D558" s="29" t="inlineStr">
+        <is>
+          <t>笠ヶ岳</t>
+        </is>
+      </c>
+      <c r="E558" s="29" t="inlineStr">
+        <is>
+          <t>コースの時間・距離を訂正</t>
+        </is>
+      </c>
+      <c r="F558" s="29" t="inlineStr">
+        <is>
+          <t>routes（笠新道）</t>
+        </is>
+      </c>
+      <c r="G558" s="29" t="inlineStr">
+        <is>
+          <t>13時間・22km</t>
+        </is>
+      </c>
+      <c r="H558" s="29" t="inlineStr">
+        <is>
+          <t>15時間15分・23.8km（日帰りは健脚者のみ）</t>
+        </is>
+      </c>
+      <c r="I558" s="29" t="inlineStr">
+        <is>
+          <t>https://yamahack.com/4748</t>
+        </is>
+      </c>
+      <c r="J558" s="29" t="inlineStr">
+        <is>
+          <t>出典ページ</t>
+        </is>
+      </c>
+      <c r="K558" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="29" t="n">
+        <v>558</v>
+      </c>
+      <c r="B559" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C559" s="29" t="inlineStr">
+        <is>
+          <t>myoko／shiomidake／terkari</t>
+        </is>
+      </c>
+      <c r="D559" s="29" t="inlineStr">
+        <is>
+          <t>妙高山・塩見岳・光岳</t>
+        </is>
+      </c>
+      <c r="E559" s="29" t="inlineStr">
+        <is>
+          <t>日帰りの注記を追加</t>
+        </is>
+      </c>
+      <c r="F559" s="29" t="inlineStr">
+        <is>
+          <t>routes[].note</t>
+        </is>
+      </c>
+      <c r="G559" s="29" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="H559" s="29" t="inlineStr">
+        <is>
+          <t>日帰りの可否と標準コースタイムの注記を追加</t>
+        </is>
+      </c>
+      <c r="I559" s="29" t="inlineStr">
+        <is>
+          <t>https://www.japanesealps.net/100moutains/myokosan/ ／ https://yamap.com/model-courses/213 ／ 216</t>
+        </is>
+      </c>
+      <c r="J559" s="29" t="inlineStr">
+        <is>
+          <t>出典ページ</t>
+        </is>
+      </c>
+      <c r="K559" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="29" t="n">
+        <v>559</v>
+      </c>
+      <c r="B560" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C560" s="29" t="inlineStr">
+        <is>
+          <t>hakusan</t>
+        </is>
+      </c>
+      <c r="D560" s="29" t="inlineStr">
+        <is>
+          <t>白山</t>
+        </is>
+      </c>
+      <c r="E560" s="29" t="inlineStr">
+        <is>
+          <t>FAQに通行止めの注意を追記</t>
+        </is>
+      </c>
+      <c r="F560" s="29" t="inlineStr">
+        <is>
+          <t>faq</t>
+        </is>
+      </c>
+      <c r="G560" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H560" s="29" t="inlineStr">
+        <is>
+          <t>砂防新道の一部通行止め（10月下旬まで）を追記</t>
+        </is>
+      </c>
+      <c r="I560" s="29" t="inlineStr">
+        <is>
+          <t>https://www.pref.ishikawa.lg.jp/hakusan/tozaninf/attention.html</t>
+        </is>
+      </c>
+      <c r="J560" s="29" t="inlineStr">
+        <is>
+          <t>status と同じ内容</t>
+        </is>
+      </c>
+      <c r="K560" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>560</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>myoko</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>妙高山</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>日帰りの区分・コースの時間を訂正</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>routes（燕温泉）／daytrip</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>9時間・日帰り不可</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>7時間50分・日帰り可（定義：8時間程度以下のコースがある山）</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>https://www.japanesealps.net/100moutains/myokosan/（燕登山道 登り4:30・下り3:20）</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>出典ページ</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>561</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>noguchigoro</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>野口五郎岳</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>日帰りの区分を訂正</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>daytrip／faq／vibes／紹介文</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>日帰り可（コースは1泊2日だけ）</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>日帰り不可。本文の「日帰り可能」を「1泊2日が基本」に</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>運営者の定義（8時間程度以下のコースがある山）</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>全156山を定義で機械照合（ずれはこの2山）</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K562"/>
+  <dimension ref="A1:K567"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -55051,110 +55051,385 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" t="n">
+      <c r="A561" s="29" t="n">
         <v>560</v>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B561" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C561" s="29" t="inlineStr">
         <is>
           <t>myoko</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr">
+      <c r="D561" s="29" t="inlineStr">
         <is>
           <t>妙高山</t>
         </is>
       </c>
-      <c r="E561" t="inlineStr">
+      <c r="E561" s="29" t="inlineStr">
         <is>
           <t>日帰りの区分・コースの時間を訂正</t>
         </is>
       </c>
-      <c r="F561" t="inlineStr">
+      <c r="F561" s="29" t="inlineStr">
         <is>
           <t>routes（燕温泉）／daytrip</t>
         </is>
       </c>
-      <c r="G561" t="inlineStr">
+      <c r="G561" s="29" t="inlineStr">
         <is>
           <t>9時間・日帰り不可</t>
         </is>
       </c>
-      <c r="H561" t="inlineStr">
+      <c r="H561" s="29" t="inlineStr">
         <is>
           <t>7時間50分・日帰り可（定義：8時間程度以下のコースがある山）</t>
         </is>
       </c>
-      <c r="I561" t="inlineStr">
+      <c r="I561" s="29" t="inlineStr">
         <is>
           <t>https://www.japanesealps.net/100moutains/myokosan/（燕登山道 登り4:30・下り3:20）</t>
         </is>
       </c>
-      <c r="J561" t="inlineStr">
+      <c r="J561" s="29" t="inlineStr">
         <is>
           <t>出典ページ</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr">
+      <c r="K561" s="29" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="n">
+      <c r="A562" s="29" t="n">
         <v>561</v>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B562" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C562" s="29" t="inlineStr">
         <is>
           <t>noguchigoro</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr">
+      <c r="D562" s="29" t="inlineStr">
         <is>
           <t>野口五郎岳</t>
         </is>
       </c>
-      <c r="E562" t="inlineStr">
+      <c r="E562" s="29" t="inlineStr">
         <is>
           <t>日帰りの区分を訂正</t>
         </is>
       </c>
-      <c r="F562" t="inlineStr">
+      <c r="F562" s="29" t="inlineStr">
         <is>
           <t>daytrip／faq／vibes／紹介文</t>
         </is>
       </c>
-      <c r="G562" t="inlineStr">
+      <c r="G562" s="29" t="inlineStr">
         <is>
           <t>日帰り可（コースは1泊2日だけ）</t>
         </is>
       </c>
-      <c r="H562" t="inlineStr">
+      <c r="H562" s="29" t="inlineStr">
         <is>
           <t>日帰り不可。本文の「日帰り可能」を「1泊2日が基本」に</t>
         </is>
       </c>
-      <c r="I562" t="inlineStr">
+      <c r="I562" s="29" t="inlineStr">
         <is>
           <t>運営者の定義（8時間程度以下のコースがある山）</t>
         </is>
       </c>
-      <c r="J562" t="inlineStr">
+      <c r="J562" s="29" t="inlineStr">
         <is>
           <t>全156山を定義で機械照合（ずれはこの2山）</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr">
+      <c r="K562" s="29" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="29" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C563" s="29" t="inlineStr">
+        <is>
+          <t>12山</t>
+        </is>
+      </c>
+      <c r="D563" s="29" t="inlineStr">
+        <is>
+          <t>雨飾山・針ノ木岳・塩見岳・飯豊山・高川山・会津駒ヶ岳・御岳山・鍋割山・鋸山・火打山・黒姫山・武尊山</t>
+        </is>
+      </c>
+      <c r="E563" s="29" t="inlineStr">
+        <is>
+          <t>難易度の理由を個別の内容に（第3回）</t>
+        </is>
+      </c>
+      <c r="F563" s="29" t="inlineStr">
+        <is>
+          <t>dlReasonsHtml</t>
+        </is>
+      </c>
+      <c r="G563" s="29" t="inlineStr">
+        <is>
+          <t>ひな形の文（コース定数…）</t>
+        </is>
+      </c>
+      <c r="H563" s="29" t="inlineStr">
+        <is>
+          <t>山ごとの具体的な理由（岩場・急登・行程・雪渓・設備）</t>
+        </is>
+      </c>
+      <c r="I563" s="29" t="inlineStr">
+        <is>
+          <t>各山の dlReasonsSources（自治体・観光協会・登山ガイド）</t>
+        </is>
+      </c>
+      <c r="J563" s="29" t="inlineStr">
+        <is>
+          <t>出典ページを開いて確認</t>
+        </is>
+      </c>
+      <c r="K563" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>563</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>nabewari</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>鍋割山</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>コースの時間・距離を訂正</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>大倉〜後沢乗越〜鍋割山（往復）</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>4時間〜4時間30分・9.4km</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>6時間15分・16.2km</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>秦野市観光協会（片道8.1km・登り3時間50分）／YAMA HACK（往復6時間15分・16.63km）</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>出典ページ。標高差は未確認のため据え置き</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>564</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>kurohimesan</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>黒姫山</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>コースの時間・距離を訂正</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>大橋林道〜黒姫山往復</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>5時間30分・10.0km</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>6時間15分・13.5km</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>山と溪谷オンラインの記録（標準6時間15分・約13.5km）／YAMA HACK（6時間45分・13.41km）</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>出典ページ</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>565</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>takeson</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>武尊山</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>コースに注記を追加</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>川場スキー場リフト利用ルート</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>注記なし</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>「積雪期のルート」の印と注記（スキー場営業期間中の雪山登山・登山届とココヘリ必須。無雪期のリフト運行は未確認）</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>川場スキー場 FAQ</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>出典ページ。要確認つき</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>566</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>nokogiriyama_chiba</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>鋸山</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>通行止めを出典の見張りに登録</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>annualItems</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>関東ふれあいの道（林道金谷元名線）土砂崩落・保田方面へ通り抜け不可</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>富津市 https://www.city.futtsu.lg.jp/0000000317.html（更新日2025-06-04）</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>出典ページ。代表の車力道コースは通行可</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
         <is>
           <t>高</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K567"/>
+  <dimension ref="A1:K568"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -55216,222 +55216,277 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="n">
+      <c r="A564" s="29" t="n">
         <v>563</v>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B564" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
+      <c r="C564" s="29" t="inlineStr">
         <is>
           <t>nabewari</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr">
+      <c r="D564" s="29" t="inlineStr">
         <is>
           <t>鍋割山</t>
         </is>
       </c>
-      <c r="E564" t="inlineStr">
+      <c r="E564" s="29" t="inlineStr">
         <is>
           <t>コースの時間・距離を訂正</t>
         </is>
       </c>
-      <c r="F564" t="inlineStr">
+      <c r="F564" s="29" t="inlineStr">
         <is>
           <t>大倉〜後沢乗越〜鍋割山（往復）</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr">
+      <c r="G564" s="29" t="inlineStr">
         <is>
           <t>4時間〜4時間30分・9.4km</t>
         </is>
       </c>
-      <c r="H564" t="inlineStr">
+      <c r="H564" s="29" t="inlineStr">
         <is>
           <t>6時間15分・16.2km</t>
         </is>
       </c>
-      <c r="I564" t="inlineStr">
+      <c r="I564" s="29" t="inlineStr">
         <is>
           <t>秦野市観光協会（片道8.1km・登り3時間50分）／YAMA HACK（往復6時間15分・16.63km）</t>
         </is>
       </c>
-      <c r="J564" t="inlineStr">
+      <c r="J564" s="29" t="inlineStr">
         <is>
           <t>出典ページ。標高差は未確認のため据え置き</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr">
+      <c r="K564" s="29" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="n">
+      <c r="A565" s="29" t="n">
         <v>564</v>
       </c>
-      <c r="B565" t="inlineStr">
+      <c r="B565" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
+      <c r="C565" s="29" t="inlineStr">
         <is>
           <t>kurohimesan</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr">
+      <c r="D565" s="29" t="inlineStr">
         <is>
           <t>黒姫山</t>
         </is>
       </c>
-      <c r="E565" t="inlineStr">
+      <c r="E565" s="29" t="inlineStr">
         <is>
           <t>コースの時間・距離を訂正</t>
         </is>
       </c>
-      <c r="F565" t="inlineStr">
+      <c r="F565" s="29" t="inlineStr">
         <is>
           <t>大橋林道〜黒姫山往復</t>
         </is>
       </c>
-      <c r="G565" t="inlineStr">
+      <c r="G565" s="29" t="inlineStr">
         <is>
           <t>5時間30分・10.0km</t>
         </is>
       </c>
-      <c r="H565" t="inlineStr">
+      <c r="H565" s="29" t="inlineStr">
         <is>
           <t>6時間15分・13.5km</t>
         </is>
       </c>
-      <c r="I565" t="inlineStr">
+      <c r="I565" s="29" t="inlineStr">
         <is>
           <t>山と溪谷オンラインの記録（標準6時間15分・約13.5km）／YAMA HACK（6時間45分・13.41km）</t>
         </is>
       </c>
-      <c r="J565" t="inlineStr">
+      <c r="J565" s="29" t="inlineStr">
         <is>
           <t>出典ページ</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr">
+      <c r="K565" s="29" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="n">
+      <c r="A566" s="29" t="n">
         <v>565</v>
       </c>
-      <c r="B566" t="inlineStr">
+      <c r="B566" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
+      <c r="C566" s="29" t="inlineStr">
         <is>
           <t>takeson</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr">
+      <c r="D566" s="29" t="inlineStr">
         <is>
           <t>武尊山</t>
         </is>
       </c>
-      <c r="E566" t="inlineStr">
+      <c r="E566" s="29" t="inlineStr">
         <is>
           <t>コースに注記を追加</t>
         </is>
       </c>
-      <c r="F566" t="inlineStr">
+      <c r="F566" s="29" t="inlineStr">
         <is>
           <t>川場スキー場リフト利用ルート</t>
         </is>
       </c>
-      <c r="G566" t="inlineStr">
+      <c r="G566" s="29" t="inlineStr">
         <is>
           <t>注記なし</t>
         </is>
       </c>
-      <c r="H566" t="inlineStr">
+      <c r="H566" s="29" t="inlineStr">
         <is>
           <t>「積雪期のルート」の印と注記（スキー場営業期間中の雪山登山・登山届とココヘリ必須。無雪期のリフト運行は未確認）</t>
         </is>
       </c>
-      <c r="I566" t="inlineStr">
+      <c r="I566" s="29" t="inlineStr">
         <is>
           <t>川場スキー場 FAQ</t>
         </is>
       </c>
-      <c r="J566" t="inlineStr">
+      <c r="J566" s="29" t="inlineStr">
         <is>
           <t>出典ページ。要確認つき</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr">
+      <c r="K566" s="29" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="n">
+      <c r="A567" s="29" t="n">
         <v>566</v>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B567" s="29" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr">
+      <c r="C567" s="29" t="inlineStr">
         <is>
           <t>nokogiriyama_chiba</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr">
+      <c r="D567" s="29" t="inlineStr">
         <is>
           <t>鋸山</t>
         </is>
       </c>
-      <c r="E567" t="inlineStr">
+      <c r="E567" s="29" t="inlineStr">
         <is>
           <t>通行止めを出典の見張りに登録</t>
         </is>
       </c>
-      <c r="F567" t="inlineStr">
+      <c r="F567" s="29" t="inlineStr">
         <is>
           <t>annualItems</t>
         </is>
       </c>
-      <c r="G567" t="inlineStr">
+      <c r="G567" s="29" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="H567" t="inlineStr">
+      <c r="H567" s="29" t="inlineStr">
         <is>
           <t>関東ふれあいの道（林道金谷元名線）土砂崩落・保田方面へ通り抜け不可</t>
         </is>
       </c>
-      <c r="I567" t="inlineStr">
+      <c r="I567" s="29" t="inlineStr">
         <is>
           <t>富津市 https://www.city.futtsu.lg.jp/0000000317.html（更新日2025-06-04）</t>
         </is>
       </c>
-      <c r="J567" t="inlineStr">
+      <c r="J567" s="29" t="inlineStr">
         <is>
           <t>出典ページ。代表の車力道コースは通行可</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr">
+      <c r="K567" s="29" t="inlineStr">
         <is>
           <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>567</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>16山</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>北岳・間ノ岳・農鳥岳・甲斐駒ヶ岳・仙丈ヶ岳・乗鞍岳・立山・剱岳・槍ヶ岳・奥穂高岳・蝶ヶ岳・至仏山・荒川岳・赤石岳・白山・富士山</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>マイカー規制のバス案内を追加</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>carShuttle（規制バナー内）</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>区間・運賃・運行期間・案内ページ（芦安→広河原 1,450円/乗合タクシー1,400円＋協力金300円、戸台パーク→北沢峠 1,150円＋手回り品220円、乗鞍高原→畳平 2,450円、立山駅→室堂 片道4,090円・往復7,380円、沢渡→上高地 片道1,600円・往復3,000円、戸倉→鳩待峠 1,300円、畑薙→椹島 宿泊者のみ往復無料、市ノ瀬→別当出合 片道1,000円・往復2,000円、水ヶ塚→富士宮口 片道1,320円・往復2,400円）</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>山梨県・伊那市・アルピコ交通・立山黒部アルペンルート・群馬県・特種東海フォレスト・石川県／株式会社マップ・静岡県の公式資料</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>各公式ページ・PDFを開いて確認</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>高（白山は運行会社のページ名が2025年版）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K568"/>
+  <dimension ref="A1:K570"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -55436,57 +55436,167 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="n">
+      <c r="A568" s="29" t="n">
         <v>567</v>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B568" s="29" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C568" s="29" t="inlineStr">
         <is>
           <t>16山</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr">
+      <c r="D568" s="29" t="inlineStr">
         <is>
           <t>北岳・間ノ岳・農鳥岳・甲斐駒ヶ岳・仙丈ヶ岳・乗鞍岳・立山・剱岳・槍ヶ岳・奥穂高岳・蝶ヶ岳・至仏山・荒川岳・赤石岳・白山・富士山</t>
         </is>
       </c>
-      <c r="E568" t="inlineStr">
+      <c r="E568" s="29" t="inlineStr">
         <is>
           <t>マイカー規制のバス案内を追加</t>
         </is>
       </c>
-      <c r="F568" t="inlineStr">
+      <c r="F568" s="29" t="inlineStr">
         <is>
           <t>carShuttle（規制バナー内）</t>
         </is>
       </c>
-      <c r="G568" t="inlineStr">
+      <c r="G568" s="29" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="H568" t="inlineStr">
+      <c r="H568" s="29" t="inlineStr">
         <is>
           <t>区間・運賃・運行期間・案内ページ（芦安→広河原 1,450円/乗合タクシー1,400円＋協力金300円、戸台パーク→北沢峠 1,150円＋手回り品220円、乗鞍高原→畳平 2,450円、立山駅→室堂 片道4,090円・往復7,380円、沢渡→上高地 片道1,600円・往復3,000円、戸倉→鳩待峠 1,300円、畑薙→椹島 宿泊者のみ往復無料、市ノ瀬→別当出合 片道1,000円・往復2,000円、水ヶ塚→富士宮口 片道1,320円・往復2,400円）</t>
         </is>
       </c>
-      <c r="I568" t="inlineStr">
+      <c r="I568" s="29" t="inlineStr">
         <is>
           <t>山梨県・伊那市・アルピコ交通・立山黒部アルペンルート・群馬県・特種東海フォレスト・石川県／株式会社マップ・静岡県の公式資料</t>
         </is>
       </c>
-      <c r="J568" t="inlineStr">
+      <c r="J568" s="29" t="inlineStr">
         <is>
           <t>各公式ページ・PDFを開いて確認</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr">
+      <c r="K568" s="29" t="inlineStr">
         <is>
           <t>高（白山は運行会社のページ名が2025年版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>568</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>13山</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>金峰山・塔ノ岳・那須岳・高水三山・火打山・焼岳・三ノ塔・大天井岳・唐松岳・剱岳・燧ヶ岳・間ノ岳・北岳</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>消えていた写真を復元</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>photos／image-credits.json</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>写真なし（2026-08〜09 に画像ツールで設定した写真が、作業フォルダからのコピーで上書きされて消えていた）</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>画像ツールで最後に設定した写真の一覧とクレジット（7山はクレジットも履歴から復元）</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>GitHub の [images] コミットの履歴</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>ファイルの存在とクレジットの対応を機械的に確認</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>569</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>全山（写真あり55山）</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>写真クレジットの表示を復元</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>photo-credits.js の読み込み</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>表示なし（2026-08-11 以降、ページの作り直しで消えていた）</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>写真のある山すべてで表示</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>ブラウザで表示を確認</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K570"/>
+  <dimension ref="A1:K574"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -55491,112 +55491,332 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" t="n">
+      <c r="A569" s="29" t="n">
         <v>568</v>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B569" s="29" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr">
+      <c r="C569" s="29" t="inlineStr">
         <is>
           <t>13山</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr">
+      <c r="D569" s="29" t="inlineStr">
         <is>
           <t>金峰山・塔ノ岳・那須岳・高水三山・火打山・焼岳・三ノ塔・大天井岳・唐松岳・剱岳・燧ヶ岳・間ノ岳・北岳</t>
         </is>
       </c>
-      <c r="E569" t="inlineStr">
+      <c r="E569" s="29" t="inlineStr">
         <is>
           <t>消えていた写真を復元</t>
         </is>
       </c>
-      <c r="F569" t="inlineStr">
+      <c r="F569" s="29" t="inlineStr">
         <is>
           <t>photos／image-credits.json</t>
         </is>
       </c>
-      <c r="G569" t="inlineStr">
+      <c r="G569" s="29" t="inlineStr">
         <is>
           <t>写真なし（2026-08〜09 に画像ツールで設定した写真が、作業フォルダからのコピーで上書きされて消えていた）</t>
         </is>
       </c>
-      <c r="H569" t="inlineStr">
+      <c r="H569" s="29" t="inlineStr">
         <is>
           <t>画像ツールで最後に設定した写真の一覧とクレジット（7山はクレジットも履歴から復元）</t>
         </is>
       </c>
-      <c r="I569" t="inlineStr">
+      <c r="I569" s="29" t="inlineStr">
         <is>
           <t>GitHub の [images] コミットの履歴</t>
         </is>
       </c>
-      <c r="J569" t="inlineStr">
+      <c r="J569" s="29" t="inlineStr">
         <is>
           <t>ファイルの存在とクレジットの対応を機械的に確認</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr">
+      <c r="K569" s="29" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="570">
-      <c r="A570" t="n">
+      <c r="A570" s="29" t="n">
         <v>569</v>
       </c>
-      <c r="B570" t="inlineStr">
+      <c r="B570" s="29" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr">
+      <c r="C570" s="29" t="inlineStr">
         <is>
           <t>全山（写真あり55山）</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr">
+      <c r="D570" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E570" t="inlineStr">
+      <c r="E570" s="29" t="inlineStr">
         <is>
           <t>写真クレジットの表示を復元</t>
         </is>
       </c>
-      <c r="F570" t="inlineStr">
+      <c r="F570" s="29" t="inlineStr">
         <is>
           <t>photo-credits.js の読み込み</t>
         </is>
       </c>
-      <c r="G570" t="inlineStr">
+      <c r="G570" s="29" t="inlineStr">
         <is>
           <t>表示なし（2026-08-11 以降、ページの作り直しで消えていた）</t>
         </is>
       </c>
-      <c r="H570" t="inlineStr">
+      <c r="H570" s="29" t="inlineStr">
         <is>
           <t>写真のある山すべてで表示</t>
         </is>
       </c>
-      <c r="I570" t="inlineStr">
+      <c r="I570" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J570" t="inlineStr">
+      <c r="J570" s="29" t="inlineStr">
         <is>
           <t>ブラウザで表示を確認</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr">
+      <c r="K570" s="29" t="inlineStr">
         <is>
           <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>570</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>kagenobusan／kobotokeshiroyama</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>景信山・小仏城山</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>茶屋の記述を訂正</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>faq／description／introHtml</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>景信山「茶屋2軒（景信茶屋 青木・かげ信小屋）」、小仏城山「城山茶屋・春美茶屋」</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>景信山は三角点かげ信小屋の1軒。小仏城山は城山茶屋と山の茶屋 青天狗（景信茶屋 青木が2024年3月に旧春美茶屋の場所へ移転）</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>高尾山マガジン（2024-01-25）・食べログ・山と溪谷オンライン山行記録（2024-03-30）</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>出典ページを開いて確認</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>571</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>adatara</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>安達太良山</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>山小屋の記述を訂正</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>くろがね小屋「通年営業の山小屋」</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>建て替え工事のため閉鎖中（宿泊・トイレ不可）</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>二本松市（更新日2024-10-10）・二本松市観光連盟（2026年山開き）</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>出典ページを開いて確認</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>572</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>tonosaki</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>塔ノ岳</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>茶屋の軒数を削除</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>featurePoints</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>大倉尾根に5軒の茶屋・山小屋</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>途中に茶屋・山小屋（軒数は書かない）</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>営業状況を確かめられないため（堀山の家の火災は登山者の記録のみ）</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>573</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>20山</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>電車で行ける日帰り登山まとめ</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>ページを作り直し</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>search/train-daytrip（gen_train_daytrip.py）</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>42選・車の時間・{n}座・FAQの数字の誤り・日帰り不可6山</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>20選（電車の時間・運賃・乗り継ぎ・帰りの最終バス）＋ほか16山の一覧</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>mountains.json・西東京バス公式時刻表（2026-04-01改正）</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>生成スクリプトとcheck_pages</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>高（最終バスは13山が確認中）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K574"/>
+  <dimension ref="A1:K576"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -55601,222 +55601,332 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" t="n">
+      <c r="A571" s="29" t="n">
         <v>570</v>
       </c>
-      <c r="B571" t="inlineStr">
+      <c r="B571" s="29" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="C571" t="inlineStr">
+      <c r="C571" s="29" t="inlineStr">
         <is>
           <t>kagenobusan／kobotokeshiroyama</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr">
+      <c r="D571" s="29" t="inlineStr">
         <is>
           <t>景信山・小仏城山</t>
         </is>
       </c>
-      <c r="E571" t="inlineStr">
+      <c r="E571" s="29" t="inlineStr">
         <is>
           <t>茶屋の記述を訂正</t>
         </is>
       </c>
-      <c r="F571" t="inlineStr">
+      <c r="F571" s="29" t="inlineStr">
         <is>
           <t>faq／description／introHtml</t>
         </is>
       </c>
-      <c r="G571" t="inlineStr">
+      <c r="G571" s="29" t="inlineStr">
         <is>
           <t>景信山「茶屋2軒（景信茶屋 青木・かげ信小屋）」、小仏城山「城山茶屋・春美茶屋」</t>
         </is>
       </c>
-      <c r="H571" t="inlineStr">
+      <c r="H571" s="29" t="inlineStr">
         <is>
           <t>景信山は三角点かげ信小屋の1軒。小仏城山は城山茶屋と山の茶屋 青天狗（景信茶屋 青木が2024年3月に旧春美茶屋の場所へ移転）</t>
         </is>
       </c>
-      <c r="I571" t="inlineStr">
+      <c r="I571" s="29" t="inlineStr">
         <is>
           <t>高尾山マガジン（2024-01-25）・食べログ・山と溪谷オンライン山行記録（2024-03-30）</t>
         </is>
       </c>
-      <c r="J571" t="inlineStr">
+      <c r="J571" s="29" t="inlineStr">
         <is>
           <t>出典ページを開いて確認</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr">
+      <c r="K571" s="29" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="n">
+      <c r="A572" s="29" t="n">
         <v>571</v>
       </c>
-      <c r="B572" t="inlineStr">
+      <c r="B572" s="29" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="C572" t="inlineStr">
+      <c r="C572" s="29" t="inlineStr">
         <is>
           <t>adatara</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr">
+      <c r="D572" s="29" t="inlineStr">
         <is>
           <t>安達太良山</t>
         </is>
       </c>
-      <c r="E572" t="inlineStr">
+      <c r="E572" s="29" t="inlineStr">
         <is>
           <t>山小屋の記述を訂正</t>
         </is>
       </c>
-      <c r="F572" t="inlineStr">
+      <c r="F572" s="29" t="inlineStr">
         <is>
           <t>featurePoints</t>
         </is>
       </c>
-      <c r="G572" t="inlineStr">
+      <c r="G572" s="29" t="inlineStr">
         <is>
           <t>くろがね小屋「通年営業の山小屋」</t>
         </is>
       </c>
-      <c r="H572" t="inlineStr">
+      <c r="H572" s="29" t="inlineStr">
         <is>
           <t>建て替え工事のため閉鎖中（宿泊・トイレ不可）</t>
         </is>
       </c>
-      <c r="I572" t="inlineStr">
+      <c r="I572" s="29" t="inlineStr">
         <is>
           <t>二本松市（更新日2024-10-10）・二本松市観光連盟（2026年山開き）</t>
         </is>
       </c>
-      <c r="J572" t="inlineStr">
+      <c r="J572" s="29" t="inlineStr">
         <is>
           <t>出典ページを開いて確認</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr">
+      <c r="K572" s="29" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="n">
+      <c r="A573" s="29" t="n">
         <v>572</v>
       </c>
-      <c r="B573" t="inlineStr">
+      <c r="B573" s="29" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr">
+      <c r="C573" s="29" t="inlineStr">
         <is>
           <t>tonosaki</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr">
+      <c r="D573" s="29" t="inlineStr">
         <is>
           <t>塔ノ岳</t>
         </is>
       </c>
-      <c r="E573" t="inlineStr">
+      <c r="E573" s="29" t="inlineStr">
         <is>
           <t>茶屋の軒数を削除</t>
         </is>
       </c>
-      <c r="F573" t="inlineStr">
+      <c r="F573" s="29" t="inlineStr">
         <is>
           <t>featurePoints</t>
         </is>
       </c>
-      <c r="G573" t="inlineStr">
+      <c r="G573" s="29" t="inlineStr">
         <is>
           <t>大倉尾根に5軒の茶屋・山小屋</t>
         </is>
       </c>
-      <c r="H573" t="inlineStr">
+      <c r="H573" s="29" t="inlineStr">
         <is>
           <t>途中に茶屋・山小屋（軒数は書かない）</t>
         </is>
       </c>
-      <c r="I573" t="inlineStr">
+      <c r="I573" s="29" t="inlineStr">
         <is>
           <t>営業状況を確かめられないため（堀山の家の火災は登山者の記録のみ）</t>
         </is>
       </c>
-      <c r="J573" t="inlineStr">
+      <c r="J573" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr">
+      <c r="K573" s="29" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="n">
+      <c r="A574" s="29" t="n">
         <v>573</v>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B574" s="29" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="C574" t="inlineStr">
+      <c r="C574" s="29" t="inlineStr">
         <is>
           <t>20山</t>
         </is>
       </c>
-      <c r="D574" t="inlineStr">
+      <c r="D574" s="29" t="inlineStr">
         <is>
           <t>電車で行ける日帰り登山まとめ</t>
         </is>
       </c>
-      <c r="E574" t="inlineStr">
+      <c r="E574" s="29" t="inlineStr">
         <is>
           <t>ページを作り直し</t>
         </is>
       </c>
-      <c r="F574" t="inlineStr">
+      <c r="F574" s="29" t="inlineStr">
         <is>
           <t>search/train-daytrip（gen_train_daytrip.py）</t>
         </is>
       </c>
-      <c r="G574" t="inlineStr">
+      <c r="G574" s="29" t="inlineStr">
         <is>
           <t>42選・車の時間・{n}座・FAQの数字の誤り・日帰り不可6山</t>
         </is>
       </c>
-      <c r="H574" t="inlineStr">
+      <c r="H574" s="29" t="inlineStr">
         <is>
           <t>20選（電車の時間・運賃・乗り継ぎ・帰りの最終バス）＋ほか16山の一覧</t>
         </is>
       </c>
-      <c r="I574" t="inlineStr">
+      <c r="I574" s="29" t="inlineStr">
         <is>
           <t>mountains.json・西東京バス公式時刻表（2026-04-01改正）</t>
         </is>
       </c>
-      <c r="J574" t="inlineStr">
+      <c r="J574" s="29" t="inlineStr">
         <is>
           <t>生成スクリプトとcheck_pages</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr">
+      <c r="K574" s="29" t="inlineStr">
         <is>
           <t>高（最終バスは13山が確認中）</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="29" t="n">
+        <v>574</v>
+      </c>
+      <c r="B575" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C575" s="29" t="inlineStr">
+        <is>
+          <t>18軒</t>
+        </is>
+      </c>
+      <c r="D575" s="29" t="inlineStr">
+        <is>
+          <t>山の茶屋・山小屋グルメ（記事）</t>
+        </is>
+      </c>
+      <c r="E575" s="29" t="inlineStr">
+        <is>
+          <t>写真の取り込みツールを追加</t>
+        </is>
+      </c>
+      <c r="F575" s="29" t="inlineStr">
+        <is>
+          <t>scripts/gourmet_commons.py・gen_gourmet_article.py・mountain_gourmet.json（commonsQueries）</t>
+        </is>
+      </c>
+      <c r="G575" s="29" t="inlineStr">
+        <is>
+          <t>写真は手で置くだけ</t>
+        </is>
+      </c>
+      <c r="H575" s="29" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons の候補（商用で使えるライセンスのみ）から人が選んで取り込み、作者・ライセンス・元ページを表示</t>
+        </is>
+      </c>
+      <c r="I575" s="29" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons API</t>
+        </is>
+      </c>
+      <c r="J575" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K575" s="29" t="inlineStr">
+        <is>
+          <t>低（写真はまだ0枚）</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>575</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>18軒</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>山の茶屋・山小屋グルメ（記事）</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>写真の選択を管理画面から行えるようにした</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>admin/gourmet/・gourmet-article.yml・import_repo_images.py・admin/index.html</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>手元のスクリプトだけ</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>管理画面で Commons の候補から選んで GitHub に反映 → 記事を自動で作り直し → 作業フォルダへ取り込み</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons API</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0・画面で検索と画像変換を確認（GitHubへの書き込みは未試験）</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K576"/>
+  <dimension ref="A1:K578"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -55876,57 +55876,167 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="n">
+      <c r="A576" s="29" t="n">
         <v>575</v>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B576" s="29" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C576" t="inlineStr">
+      <c r="C576" s="29" t="inlineStr">
         <is>
           <t>18軒</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr">
+      <c r="D576" s="29" t="inlineStr">
         <is>
           <t>山の茶屋・山小屋グルメ（記事）</t>
         </is>
       </c>
-      <c r="E576" t="inlineStr">
+      <c r="E576" s="29" t="inlineStr">
         <is>
           <t>写真の選択を管理画面から行えるようにした</t>
         </is>
       </c>
-      <c r="F576" t="inlineStr">
+      <c r="F576" s="29" t="inlineStr">
         <is>
           <t>admin/gourmet/・gourmet-article.yml・import_repo_images.py・admin/index.html</t>
         </is>
       </c>
-      <c r="G576" t="inlineStr">
+      <c r="G576" s="29" t="inlineStr">
         <is>
           <t>手元のスクリプトだけ</t>
         </is>
       </c>
-      <c r="H576" t="inlineStr">
+      <c r="H576" s="29" t="inlineStr">
         <is>
           <t>管理画面で Commons の候補から選んで GitHub に反映 → 記事を自動で作り直し → 作業フォルダへ取り込み</t>
         </is>
       </c>
-      <c r="I576" t="inlineStr">
+      <c r="I576" s="29" t="inlineStr">
         <is>
           <t>Wikimedia Commons API</t>
         </is>
       </c>
-      <c r="J576" t="inlineStr">
+      <c r="J576" s="29" t="inlineStr">
         <is>
           <t>check_pages 終了コード0・画面で検索と画像変換を確認（GitHubへの書き込みは未試験）</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr">
+      <c r="K576" s="29" t="inlineStr">
         <is>
           <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="29" t="n">
+        <v>576</v>
+      </c>
+      <c r="B577" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C577" s="29" t="inlineStr">
+        <is>
+          <t>11軒</t>
+        </is>
+      </c>
+      <c r="D577" s="29" t="inlineStr">
+        <is>
+          <t>山の茶屋・山小屋グルメ（記事）</t>
+        </is>
+      </c>
+      <c r="E577" s="29" t="inlineStr">
+        <is>
+          <t>決まった名物の無い場所を外した</t>
+        </is>
+      </c>
+      <c r="F577" s="29" t="inlineStr">
+        <is>
+          <t>data/mountain_gourmet.json（removedItems）・gen_gourmet_article.py（FAQ）・articles/index.html・sitemap.xml</t>
+        </is>
+      </c>
+      <c r="G577" s="29" t="inlineStr">
+        <is>
+          <t>18選</t>
+        </is>
+      </c>
+      <c r="H577" s="29" t="inlineStr">
+        <is>
+          <t>7選（鍋割山荘・かげ信小屋・城山茶屋/青天狗・みくりが池温泉・ヒュッテみさやま・涸沢小屋・槍平小屋）</t>
+        </is>
+      </c>
+      <c r="I577" s="29" t="inlineStr">
+        <is>
+          <t>運営者の指示</t>
+        </is>
+      </c>
+      <c r="J577" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K577" s="29" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>577</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>hotaka・otenshoudake</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>山の茶屋・山小屋グルメ（記事）</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>カレーの山小屋を追加</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>data/mountain_gourmet.json・articles/index.html</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>7選</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>9選（穂高岳山荘の特製手作りカレー・牛すじカレー／大天荘のインディアン・ランチ）</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>穂高岳山荘 公式（/stay/store）・大天荘 公式（2025年度の昼食メニュー）</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>低（大天荘は2025年度のメニュー）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K578"/>
+  <dimension ref="A1:K579"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -55986,57 +55986,112 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="n">
+      <c r="A578" s="29" t="n">
         <v>577</v>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B578" s="29" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr">
+      <c r="C578" s="29" t="inlineStr">
         <is>
           <t>hotaka・otenshoudake</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr">
+      <c r="D578" s="29" t="inlineStr">
         <is>
           <t>山の茶屋・山小屋グルメ（記事）</t>
         </is>
       </c>
-      <c r="E578" t="inlineStr">
+      <c r="E578" s="29" t="inlineStr">
         <is>
           <t>カレーの山小屋を追加</t>
         </is>
       </c>
-      <c r="F578" t="inlineStr">
+      <c r="F578" s="29" t="inlineStr">
         <is>
           <t>data/mountain_gourmet.json・articles/index.html</t>
         </is>
       </c>
-      <c r="G578" t="inlineStr">
+      <c r="G578" s="29" t="inlineStr">
         <is>
           <t>7選</t>
         </is>
       </c>
-      <c r="H578" t="inlineStr">
+      <c r="H578" s="29" t="inlineStr">
         <is>
           <t>9選（穂高岳山荘の特製手作りカレー・牛すじカレー／大天荘のインディアン・ランチ）</t>
         </is>
       </c>
-      <c r="I578" t="inlineStr">
+      <c r="I578" s="29" t="inlineStr">
         <is>
           <t>穂高岳山荘 公式（/stay/store）・大天荘 公式（2025年度の昼食メニュー）</t>
         </is>
       </c>
-      <c r="J578" t="inlineStr">
+      <c r="J578" s="29" t="inlineStr">
         <is>
           <t>check_pages 終了コード0</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr">
+      <c r="K578" s="29" t="inlineStr">
         <is>
           <t>低（大天荘は2025年度のメニュー）</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="29" t="n">
+        <v>578</v>
+      </c>
+      <c r="B579" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C579" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D579" s="29" t="inlineStr">
+        <is>
+          <t>記事一覧</t>
+        </is>
+      </c>
+      <c r="E579" s="29" t="inlineStr">
+        <is>
+          <t>グルメ記事のカードに見出し画像</t>
+        </is>
+      </c>
+      <c r="F579" s="29" t="inlineStr">
+        <is>
+          <t>articles/index.html・articles/images/hero_mountain_gourmet.jpg</t>
+        </is>
+      </c>
+      <c r="G579" s="29" t="inlineStr">
+        <is>
+          <t>文字だけのカード</t>
+        </is>
+      </c>
+      <c r="H579" s="29" t="inlineStr">
+        <is>
+          <t>運営者の用意した画像（960px）</t>
+        </is>
+      </c>
+      <c r="I579" s="29" t="inlineStr">
+        <is>
+          <t>運営者の指示</t>
+        </is>
+      </c>
+      <c r="J579" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K579" s="29" t="inlineStr">
+        <is>
+          <t>低（9選の画像に差し替え済み）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K579"/>
+  <dimension ref="A1:K580"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -56092,6 +56092,61 @@
       <c r="K579" s="29" t="inlineStr">
         <is>
           <t>低（9選の画像に差し替え済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>579</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>69山</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>持ち物・服装のチェックリスト</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>新機能</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>data/packing.json・assets/js/packing.js・gen_huts_page.py・gen_mountain_pages.py・mypage/index.html</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>山小屋泊の持ち物の案内なし（登山計画は固定のひな形）</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>山小屋ページ（69山）にチェックリスト、山ページからリンク、登山計画は山と日付に合わせたひな形</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>長野県「登山準備・ルール確認票」・「登山計画書を届出しましょう」</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0・ブラウザで北岳（8月・10月）と赤岳を確認</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>中（服装・山小屋泊の項目は一般的な内容。山小屋ごとの決まりは書いていない）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K580"/>
+  <dimension ref="A1:K581"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -56096,57 +56096,112 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="n">
+      <c r="A580" s="29" t="n">
         <v>579</v>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B580" s="29" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C580" t="inlineStr">
+      <c r="C580" s="29" t="inlineStr">
         <is>
           <t>69山</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr">
+      <c r="D580" s="29" t="inlineStr">
         <is>
           <t>持ち物・服装のチェックリスト</t>
         </is>
       </c>
-      <c r="E580" t="inlineStr">
+      <c r="E580" s="29" t="inlineStr">
         <is>
           <t>新機能</t>
         </is>
       </c>
-      <c r="F580" t="inlineStr">
+      <c r="F580" s="29" t="inlineStr">
         <is>
           <t>data/packing.json・assets/js/packing.js・gen_huts_page.py・gen_mountain_pages.py・mypage/index.html</t>
         </is>
       </c>
-      <c r="G580" t="inlineStr">
+      <c r="G580" s="29" t="inlineStr">
         <is>
           <t>山小屋泊の持ち物の案内なし（登山計画は固定のひな形）</t>
         </is>
       </c>
-      <c r="H580" t="inlineStr">
+      <c r="H580" s="29" t="inlineStr">
         <is>
           <t>山小屋ページ（69山）にチェックリスト、山ページからリンク、登山計画は山と日付に合わせたひな形</t>
         </is>
       </c>
-      <c r="I580" t="inlineStr">
+      <c r="I580" s="29" t="inlineStr">
         <is>
           <t>長野県「登山準備・ルール確認票」・「登山計画書を届出しましょう」</t>
         </is>
       </c>
-      <c r="J580" t="inlineStr">
+      <c r="J580" s="29" t="inlineStr">
         <is>
           <t>check_pages 終了コード0・ブラウザで北岳（8月・10月）と赤岳を確認</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr">
+      <c r="K580" s="29" t="inlineStr">
         <is>
           <t>中（服装・山小屋泊の項目は一般的な内容。山小屋ごとの決まりは書いていない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>580</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>69山</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>持ち物・服装のチェックリスト</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>商品リンクを Amazon に変更</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>assets/js/packing.js・mypage/index.html</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>楽天の検索リンク</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Amazon の検索リンク（amazonafdaiki-22）</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>運営者の指示</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24234,7 +24234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K581"/>
+  <dimension ref="A1:K586"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -56151,55 +56151,330 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" t="n">
+      <c r="A581" s="29" t="n">
         <v>580</v>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B581" s="29" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C581" t="inlineStr">
+      <c r="C581" s="29" t="inlineStr">
         <is>
           <t>69山</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr">
+      <c r="D581" s="29" t="inlineStr">
         <is>
           <t>持ち物・服装のチェックリスト</t>
         </is>
       </c>
-      <c r="E581" t="inlineStr">
+      <c r="E581" s="29" t="inlineStr">
         <is>
           <t>商品リンクを Amazon に変更</t>
         </is>
       </c>
-      <c r="F581" t="inlineStr">
+      <c r="F581" s="29" t="inlineStr">
         <is>
           <t>assets/js/packing.js・mypage/index.html</t>
         </is>
       </c>
-      <c r="G581" t="inlineStr">
+      <c r="G581" s="29" t="inlineStr">
         <is>
           <t>楽天の検索リンク</t>
         </is>
       </c>
-      <c r="H581" t="inlineStr">
+      <c r="H581" s="29" t="inlineStr">
         <is>
           <t>Amazon の検索リンク（amazonafdaiki-22）</t>
         </is>
       </c>
-      <c r="I581" t="inlineStr">
+      <c r="I581" s="29" t="inlineStr">
         <is>
           <t>運営者の指示</t>
         </is>
       </c>
-      <c r="J581" t="inlineStr">
+      <c r="J581" s="29" t="inlineStr">
         <is>
           <t>check_pages 終了コード0</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr">
+      <c r="K581" s="29" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="29" t="n">
+        <v>581</v>
+      </c>
+      <c r="B582" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C582" s="29" t="inlineStr">
+        <is>
+          <t>全山</t>
+        </is>
+      </c>
+      <c r="D582" s="29" t="inlineStr">
+        <is>
+          <t>装備カード・持ち物チェックリスト</t>
+        </is>
+      </c>
+      <c r="E582" s="29" t="inlineStr">
+        <is>
+          <t>Amazonで売っていない商品を差し替え</t>
+        </is>
+      </c>
+      <c r="F582" s="29" t="inlineStr">
+        <is>
+          <t>data/gear-data.json・data/packing.json・山ページ156・検索/記事15ページ</t>
+        </is>
+      </c>
+      <c r="G582" s="29" t="inlineStr">
+        <is>
+          <t>トランゴ タワー GTX／トランゴ トレック GTX／ノースフェイス インナーダウン（Amazonに無い）・チェックリストの型番の曖昧な8商品</t>
+        </is>
+      </c>
+      <c r="H582" s="29" t="inlineStr">
+        <is>
+          <t>トランゴ テック GTX／ライトヒートジャケット／型番を特定した商品名（イーチップグローブ・リアクターライナーなど）</t>
+        </is>
+      </c>
+      <c r="I582" s="29" t="inlineStr">
+        <is>
+          <t>Amazon.co.jp の検索結果（2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J582" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K582" s="29" t="inlineStr">
+        <is>
+          <t>中（装備カードの商品も変わった）</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="29" t="n">
+        <v>582</v>
+      </c>
+      <c r="B583" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C583" s="29" t="inlineStr">
+        <is>
+          <t>kitadake・2500m以上の山</t>
+        </is>
+      </c>
+      <c r="D583" s="29" t="inlineStr">
+        <is>
+          <t>持ち物・服装のチェックリスト</t>
+        </is>
+      </c>
+      <c r="E583" s="29" t="inlineStr">
+        <is>
+          <t>運営者の体験を反映</t>
+        </is>
+      </c>
+      <c r="F583" s="29" t="inlineStr">
+        <is>
+          <t>data/packing.json（experiences・nightwarm）・assets/js/packing.js・gen_huts_page.py</t>
+        </is>
+      </c>
+      <c r="G583" s="29" t="inlineStr">
+        <is>
+          <t>夜の下半身の防寒の項目なし</t>
+        </is>
+      </c>
+      <c r="H583" s="29" t="inlineStr">
+        <is>
+          <t>標高2500m以上の山小屋泊・テント泊に「夜・早朝の下半身の防寒」。北岳に泊まった人の服装の例（2026-10-17 北岳肩の小屋）</t>
+        </is>
+      </c>
+      <c r="I583" s="29" t="inlineStr">
+        <is>
+          <t>運営者の体験</t>
+        </is>
+      </c>
+      <c r="J583" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K583" s="29" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="29" t="n">
+        <v>583</v>
+      </c>
+      <c r="B584" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C584" s="29" t="inlineStr">
+        <is>
+          <t>fuji・2500m以上の山</t>
+        </is>
+      </c>
+      <c r="D584" s="29" t="inlineStr">
+        <is>
+          <t>持ち物・服装のチェックリスト</t>
+        </is>
+      </c>
+      <c r="E584" s="29" t="inlineStr">
+        <is>
+          <t>運営者の友人の体験を反映</t>
+        </is>
+      </c>
+      <c r="F584" s="29" t="inlineStr">
+        <is>
+          <t>data/packing.json（experiences・sleepwarm）・assets/js/packing.js</t>
+        </is>
+      </c>
+      <c r="G584" s="29" t="inlineStr">
+        <is>
+          <t>寝るときの防寒の項目なし</t>
+        </is>
+      </c>
+      <c r="H584" s="29" t="inlineStr">
+        <is>
+          <t>標高2500m以上の山小屋泊に「寝るときの防寒」。富士山に泊まった人の服装の例（夏・友人）</t>
+        </is>
+      </c>
+      <c r="I584" s="29" t="inlineStr">
+        <is>
+          <t>運営者の友人の体験（運営者から聞いた内容）</t>
+        </is>
+      </c>
+      <c r="J584" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K584" s="29" t="inlineStr">
+        <is>
+          <t>低（時期は「夏」・小屋名は不明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="29" t="n">
+        <v>584</v>
+      </c>
+      <c r="B585" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C585" s="29" t="inlineStr">
+        <is>
+          <t>2500m以上の山</t>
+        </is>
+      </c>
+      <c r="D585" s="29" t="inlineStr">
+        <is>
+          <t>持ち物・服装のチェックリスト</t>
+        </is>
+      </c>
+      <c r="E585" s="29" t="inlineStr">
+        <is>
+          <t>防寒の見直し（2つの実例から）</t>
+        </is>
+      </c>
+      <c r="F585" s="29" t="inlineStr">
+        <is>
+          <t>data/packing.json・assets/js/packing.js</t>
+        </is>
+      </c>
+      <c r="G585" s="29" t="inlineStr">
+        <is>
+          <t>薄手のダウン・フリースまで（2500m以上も夏は同じ）</t>
+        </is>
+      </c>
+      <c r="H585" s="29" t="inlineStr">
+        <is>
+          <t>2500m以上の泊まりに厚手のダウン・下半身の防寒・寝るときの防寒・カイロ、手袋・帽子・寝袋に注意、実例を2500m以上の山すべてに参考表示</t>
+        </is>
+      </c>
+      <c r="I585" s="29" t="inlineStr">
+        <is>
+          <t>運営者（北岳肩の小屋 2026-10-17）・運営者の友人（富士山 夏）の体験</t>
+        </is>
+      </c>
+      <c r="J585" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0・雲取山／富士山／北岳で表示確認</t>
+        </is>
+      </c>
+      <c r="K585" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>585</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2500m以上の山・泊まり</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>持ち物・服装のチェックリスト</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>防寒の書き方を見直し</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>data/packing.json・assets/js/packing.js・gen_huts_page.py</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>厚手のダウンジャケット（1商品）</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>夜の防寒をもう1枚（厚手のダウンか中わた。重ね着でも可、綿は避ける。2商品）・乾いた肌着・靴下の着替え（ヒートテック可）</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>運営者の指示</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
         <is>
           <t>低</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K590"/>
+  <dimension ref="A1:K591"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -56665,55 +56665,110 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" t="n">
+      <c r="A590" s="29" t="n">
         <v>589</v>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B590" s="29" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C590" s="29" t="inlineStr">
         <is>
           <t>185軒</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr">
+      <c r="D590" s="29" t="inlineStr">
         <is>
           <t>管理表「山小屋情報」</t>
         </is>
       </c>
-      <c r="E590" t="inlineStr">
+      <c r="E590" s="29" t="inlineStr">
         <is>
           <t>予約開始日の監視の列を追加・説明を訂正</t>
         </is>
       </c>
-      <c r="F590" t="inlineStr">
+      <c r="F590" s="29" t="inlineStr">
         <is>
           <t>scripts/huts_excel.py</t>
         </is>
       </c>
-      <c r="G590" t="inlineStr">
+      <c r="G590" s="29" t="inlineStr">
         <is>
           <t>「自動では書き換えない：予約の開始…（報告だけ）」と一律に記載（自動で反映される小屋があるのに誤り）</t>
         </is>
       </c>
-      <c r="H590" t="inlineStr">
+      <c r="H590" s="29" t="inlineStr">
         <is>
           <t>小屋ごとに「自動で反映（レシピ／やまたんのお知らせ／型で読む）・報告だけ・監視なし」を記載。手で書いた値は書き換えないが、確認を通った自動の値は表示で優先</t>
         </is>
       </c>
-      <c r="I590" t="inlineStr">
+      <c r="I590" s="29" t="inlineStr">
         <is>
           <t>scripts/huts_auto.py の条件</t>
         </is>
       </c>
-      <c r="J590" t="inlineStr">
+      <c r="J590" s="29" t="inlineStr">
         <is>
           <t>自動で反映がある小屋 73軒</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr">
+      <c r="K590" s="29" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>590</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>全山</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>お気に入り数・登頂数の集計</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Firebase を設定して有効にした</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>assets/js/counts-config.js・ASSET_VER 20261020a（山ページ156・index・mypage）・scripts/firebase_rules.json</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>集計先なし（表示なし）</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Firebase Realtime Database（yamatch-35abd）に集計</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>運営者が作成したデータベース</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>ルールの読み書き制限を確認・check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
         <is>
           <t>低</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K591"/>
+  <dimension ref="A1:K592"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -56720,57 +56720,112 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" t="n">
+      <c r="A591" s="29" t="n">
         <v>590</v>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B591" s="29" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C591" s="29" t="inlineStr">
         <is>
           <t>全山</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr">
+      <c r="D591" s="29" t="inlineStr">
         <is>
           <t>お気に入り数・登頂数の集計</t>
         </is>
       </c>
-      <c r="E591" t="inlineStr">
+      <c r="E591" s="29" t="inlineStr">
         <is>
           <t>Firebase を設定して有効にした</t>
         </is>
       </c>
-      <c r="F591" t="inlineStr">
+      <c r="F591" s="29" t="inlineStr">
         <is>
           <t>assets/js/counts-config.js・ASSET_VER 20261020a（山ページ156・index・mypage）・scripts/firebase_rules.json</t>
         </is>
       </c>
-      <c r="G591" t="inlineStr">
+      <c r="G591" s="29" t="inlineStr">
         <is>
           <t>集計先なし（表示なし）</t>
         </is>
       </c>
-      <c r="H591" t="inlineStr">
+      <c r="H591" s="29" t="inlineStr">
         <is>
           <t>Firebase Realtime Database（yamatch-35abd）に集計</t>
         </is>
       </c>
-      <c r="I591" t="inlineStr">
+      <c r="I591" s="29" t="inlineStr">
         <is>
           <t>運営者が作成したデータベース</t>
         </is>
       </c>
-      <c r="J591" t="inlineStr">
+      <c r="J591" s="29" t="inlineStr">
         <is>
           <t>ルールの読み書き制限を確認・check_pages 終了コード0</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr">
+      <c r="K591" s="29" t="inlineStr">
         <is>
           <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>591</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>山小屋185軒</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>予約開始のお知らせ（プッシュ通知）</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>通知の設定を入れた（テスト前）</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>assets/js/huts-alert.js（PUSH）・privacy/index.html・MAP_VER 20261020b・index・mypage</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>休止中</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>登録した端末の宛先を Firebase に預ける。送信は GitHub の Secrets が揃うと毎朝7時</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>運営者が作成したデータベース・VAPID 公開鍵</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0（実機のテスト通知は未確認）</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K592"/>
+  <dimension ref="A1:K594"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -56775,57 +56775,167 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" t="n">
+      <c r="A592" s="29" t="n">
         <v>591</v>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B592" s="29" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
+      <c r="C592" s="29" t="inlineStr">
         <is>
           <t>山小屋185軒</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr">
+      <c r="D592" s="29" t="inlineStr">
         <is>
           <t>予約開始のお知らせ（プッシュ通知）</t>
         </is>
       </c>
-      <c r="E592" t="inlineStr">
+      <c r="E592" s="29" t="inlineStr">
         <is>
           <t>通知の設定を入れた（テスト前）</t>
         </is>
       </c>
-      <c r="F592" t="inlineStr">
+      <c r="F592" s="29" t="inlineStr">
         <is>
           <t>assets/js/huts-alert.js（PUSH）・privacy/index.html・MAP_VER 20261020b・index・mypage</t>
         </is>
       </c>
-      <c r="G592" t="inlineStr">
+      <c r="G592" s="29" t="inlineStr">
         <is>
           <t>休止中</t>
         </is>
       </c>
-      <c r="H592" t="inlineStr">
+      <c r="H592" s="29" t="inlineStr">
         <is>
           <t>登録した端末の宛先を Firebase に預ける。送信は GitHub の Secrets が揃うと毎朝7時</t>
         </is>
       </c>
-      <c r="I592" t="inlineStr">
+      <c r="I592" s="29" t="inlineStr">
         <is>
           <t>運営者が作成したデータベース・VAPID 公開鍵</t>
         </is>
       </c>
-      <c r="J592" t="inlineStr">
+      <c r="J592" s="29" t="inlineStr">
         <is>
           <t>check_pages 終了コード0（実機のテスト通知は未確認）</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr">
+      <c r="K592" s="29" t="inlineStr">
         <is>
           <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="29" t="n">
+        <v>592</v>
+      </c>
+      <c r="B593" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C593" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D593" s="29" t="inlineStr">
+        <is>
+          <t>予約開始のお知らせ（プッシュ通知）</t>
+        </is>
+      </c>
+      <c r="E593" s="29" t="inlineStr">
+        <is>
+          <t>管理者の印の送り直し</t>
+        </is>
+      </c>
+      <c r="F593" s="29" t="inlineStr">
+        <is>
+          <t>assets/js/huts-alert.js・MAP_VER 20261020c</t>
+        </is>
+      </c>
+      <c r="G593" s="29" t="inlineStr">
+        <is>
+          <t>お知らせの登録のあとに管理者表示をオンにすると、その日は管理者の印が送られない（テスト通知が届かない）</t>
+        </is>
+      </c>
+      <c r="H593" s="29" t="inlineStr">
+        <is>
+          <t>管理者表示の切り替えでも登録を送り直す</t>
+        </is>
+      </c>
+      <c r="I593" s="29" t="inlineStr">
+        <is>
+          <t>テスト通知が届かなかった調査</t>
+        </is>
+      </c>
+      <c r="J593" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K593" s="29" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>593</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>予約開始のお知らせ（プッシュ通知）</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>管理者向けに登録の状態を表示</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>assets/js/huts-alert.js・MAP_VER 20261020d</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>端末の登録の成否が分からない（テストで登録0台）</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>管理者表示の端末のマイページに、登録済み／登録できない理由／失敗の内容を出す</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>テスト通知が届かなかった調査（データベースは登録を受け付けることを確認）</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K594"/>
+  <dimension ref="A1:K597"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -56885,57 +56885,222 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" t="n">
+      <c r="A594" s="29" t="n">
         <v>593</v>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B594" s="29" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
+      <c r="C594" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr">
+      <c r="D594" s="29" t="inlineStr">
         <is>
           <t>予約開始のお知らせ（プッシュ通知）</t>
         </is>
       </c>
-      <c r="E594" t="inlineStr">
+      <c r="E594" s="29" t="inlineStr">
         <is>
           <t>管理者向けに登録の状態を表示</t>
         </is>
       </c>
-      <c r="F594" t="inlineStr">
+      <c r="F594" s="29" t="inlineStr">
         <is>
           <t>assets/js/huts-alert.js・MAP_VER 20261020d</t>
         </is>
       </c>
-      <c r="G594" t="inlineStr">
+      <c r="G594" s="29" t="inlineStr">
         <is>
           <t>端末の登録の成否が分からない（テストで登録0台）</t>
         </is>
       </c>
-      <c r="H594" t="inlineStr">
+      <c r="H594" s="29" t="inlineStr">
         <is>
           <t>管理者表示の端末のマイページに、登録済み／登録できない理由／失敗の内容を出す</t>
         </is>
       </c>
-      <c r="I594" t="inlineStr">
+      <c r="I594" s="29" t="inlineStr">
         <is>
           <t>テスト通知が届かなかった調査（データベースは登録を受け付けることを確認）</t>
         </is>
       </c>
-      <c r="J594" t="inlineStr">
+      <c r="J594" s="29" t="inlineStr">
         <is>
           <t>check_pages 終了コード0</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr">
+      <c r="K594" s="29" t="inlineStr">
         <is>
           <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="29" t="n">
+        <v>594</v>
+      </c>
+      <c r="B595" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C595" s="29" t="inlineStr">
+        <is>
+          <t>山小屋185軒</t>
+        </is>
+      </c>
+      <c r="D595" s="29" t="inlineStr">
+        <is>
+          <t>予約開始のお知らせ（プッシュ通知）</t>
+        </is>
+      </c>
+      <c r="E595" s="29" t="inlineStr">
+        <is>
+          <t>公開（説明・見本を実際の動きに合わせた）</t>
+        </is>
+      </c>
+      <c r="F595" s="29" t="inlineStr">
+        <is>
+          <t>gen_huts_page.py（PROMO）・assets/js/huts-alert.js（見本の文）・MAP_VER 20261020e</t>
+        </is>
+      </c>
+      <c r="G595" s="29" t="inlineStr">
+        <is>
+          <t>「Yamatch を開いたときにお知らせ（開いていないときには届きません）」</t>
+        </is>
+      </c>
+      <c r="H595" s="29" t="inlineStr">
+        <is>
+          <t>「通知を許可すると、開いていなくても朝7時ごろに届く。許可しないときは開いたときだけ」</t>
+        </is>
+      </c>
+      <c r="I595" s="29" t="inlineStr">
+        <is>
+          <t>管理者端末へのテスト通知が届いた（2026-10-20 20:22）</t>
+        </is>
+      </c>
+      <c r="J595" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0</t>
+        </is>
+      </c>
+      <c r="K595" s="29" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="29" t="n">
+        <v>595</v>
+      </c>
+      <c r="B596" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C596" s="29" t="inlineStr">
+        <is>
+          <t>全山（156ページ）</t>
+        </is>
+      </c>
+      <c r="D596" s="29" t="inlineStr">
+        <is>
+          <t>お気に入り数・登頂数の表示</t>
+        </is>
+      </c>
+      <c r="E596" s="29" t="inlineStr">
+        <is>
+          <t>表示の場所を移した</t>
+        </is>
+      </c>
+      <c r="F596" s="29" t="inlineStr">
+        <is>
+          <t>gen_mountain_pages.py・_base_mountain_style.css</t>
+        </is>
+      </c>
+      <c r="G596" s="29" t="inlineStr">
+        <is>
+          <t>ヒーローの中（山名の上）に丸い枠つき</t>
+        </is>
+      </c>
+      <c r="H596" s="29" t="inlineStr">
+        <is>
+          <t>タブとヒーローのあいだの行の左（最終更新と同じ行）に枠なし</t>
+        </is>
+      </c>
+      <c r="I596" s="29" t="inlineStr">
+        <is>
+          <t>運営者の指示</t>
+        </is>
+      </c>
+      <c r="J596" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0・写真あり／なしの山で表示確認</t>
+        </is>
+      </c>
+      <c r="K596" s="29" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>596</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>山小屋185軒</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>予約開始のお知らせ（プッシュ通知）</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>お試しを追加・早朝開始の小屋の見出し</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>assets/js/huts-alert.js・scripts/huts_push_send.js・gen_huts_page.py・scripts/firebase_rules.json（hutPushTrial）・privacy/index.html・MAP_VER 20261020g</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>お試しは画面の中だけ／0:00〜7:00開始の小屋も当日7時に「きょう予約開始」</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>「通知をお試しする」：すぐ見本の通知＋翌朝7時に本物を1回（送ったら宛先を消す）／前日「あした0:00から予約開始」・当日「予約の受付が始まっています」</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>運営者の指示</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>送信の手元の試し（--dry-run）・check_pages 終了コード0。ルールの貼り直しは運営者</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K599"/>
+  <dimension ref="A1:K600"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57211,6 +57211,61 @@
       <c r="K599" s="29" t="inlineStr">
         <is>
           <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="29" t="n">
+        <v>599</v>
+      </c>
+      <c r="B600" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C600" s="29" t="inlineStr">
+        <is>
+          <t>79軒</t>
+        </is>
+      </c>
+      <c r="D600" s="29" t="inlineStr">
+        <is>
+          <t>山小屋まとめ</t>
+        </is>
+      </c>
+      <c r="E600" s="29" t="inlineStr">
+        <is>
+          <t>ChatGPT の全件監査の指摘を一次情報で確認して修正</t>
+        </is>
+      </c>
+      <c r="F600" s="29" t="inlineStr">
+        <is>
+          <t>huts_checked.py（営業期間31・定員30）・huts_booking_extra.py・huts_rules.py・huts_extra.py・huts_official_urls.json・huts_recipes.json・build_huts_from_nagano.py・update_huts.py・gen_huts_page.py・data/huts.json</t>
+        </is>
+      </c>
+      <c r="G600" s="29" t="inlineStr">
+        <is>
+          <t>東海フォレストの電話予約「6月16日から」（実際は問い合わせ窓口の開設日）、赤石岳避難小屋「予約不要」、定員の古い値（山と溪谷）、2025年や例年の営業期間、槍ヶ岳グループの予約方法・電話、大滝山荘「1か月前」など</t>
+        </is>
+      </c>
+      <c r="H600" s="29" t="inlineStr">
+        <is>
+          <t>公式・自治体の原文どおりに修正（詳細は山小屋情報シート）。指摘のうち、原文と合わないもの（飯豊切合の常駐期間を2021年とする説など）は採らず、確かめられない3サイト（赤岳頂上山荘・雨飾山荘・青木鉱泉）は変更なし</t>
+        </is>
+      </c>
+      <c r="I600" s="29" t="inlineStr">
+        <is>
+          <t>各小屋・自治体・観光協会の公式ページ（2026-10-20〜21 取得）</t>
+        </is>
+      </c>
+      <c r="J600" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0・お知らせの型の前後比較（外れた2軒を戻した）</t>
+        </is>
+      </c>
+      <c r="K600" s="29" t="inlineStr">
+        <is>
+          <t>中（2つのセッションで並行して作業。こちらで統合）</t>
         </is>
       </c>
     </row>
@@ -58630,7 +58685,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0263-35-7200</t>
+          <t>090-2641-1911（営業期間中の現地。期間外は松本事務所 0263-35-7200）</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -58646,7 +58701,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>宿泊日の1か月前から</t>
+          <t>宿泊日の1か月前の朝9:00から（例：8月15日の宿泊は7月15日9:00から）</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -58656,7 +58711,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web・電話（山小屋の現地）</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -58696,7 +58751,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -58802,7 +58857,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>96人</t>
+          <t>96人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -58832,7 +58887,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -58900,7 +58955,11 @@
           <t>https://www.yarigatake.co.jp/sesshou/</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>080-8108-0361（営業期間中の現地。期間外は松本事務所 0263-35-7200）</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>2026/6/6～10/11、1か月前予約制 ＊開始日と終了日は降雪状況次第で変更あり</t>
@@ -58914,7 +58973,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>宿泊日の1か月前から</t>
+          <t>宿泊日の1か月前の朝9:00から（例：8月15日の宿泊は7月15日9:00から）</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -58924,7 +58983,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Web・電話</t>
+          <t>Web・電話（山小屋の現地）</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -58960,7 +59019,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -59030,7 +59089,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0263-35-7200</t>
+          <t>090-8250-2297（営業期間中の現地。期間外は松本事務所 0263-35-7200）</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -59046,7 +59105,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>宿泊日の1か月前から</t>
+          <t>宿泊日の1か月前の朝9:00から（例：8月15日の宿泊は7月15日9:00から）</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -59056,7 +59115,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web・電話（山小屋の現地）</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -59096,7 +59155,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -59342,7 +59401,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>約100人（山と溪谷オンライン）</t>
+          <t>80人程度（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -59372,7 +59431,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -59443,18 +59502,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026年4月27日〜11月3日</t>
+          <t>4/27～5/10、6/1～11/3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>自動（公式・予約サイト）</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5/11～5/31は改修工事のため休業（公式の2026年度営業スケジュール）</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>宿泊日の1か月前から（5名以上は電話のみで、前月同日の朝8:00から）</t>
+          <t>宿泊日の1か月前の同じ日の朝8:00から（Webは前々日18:00、電話は前日18:00まで。2026年の4/27〜5/27泊の電話予約は4月20日8:00から）</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -59504,7 +59567,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -59587,15 +59650,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026年4月26日〜11月3日の宿泊まで</t>
+          <t>4/27～5/31、7/1～11/3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>自動（公式・予約サイト）</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>11/3の宿泊まで。6月は修繕工事のため宿泊と外来食堂が休み（売店とテント場は利用可）</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>電話は宿泊日の1か月前（前月の同じ日）7:00から（Web（やまたん）は7/1〜10/25泊の限定数だけ、2か月前から）</t>
@@ -59648,7 +59715,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -59994,7 +60061,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0263-35-7200</t>
+          <t>090-2546-2100（営業期間中の現地。期間外は松本事務所 0263-35-7200）</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -60010,7 +60077,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>宿泊日の1か月前から</t>
+          <t>宿泊日の1か月前の朝9:00から（例：8月15日の宿泊は7月15日9:00から）</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -60020,7 +60087,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web・電話（山小屋の現地）</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -60060,7 +60127,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -60403,15 +60470,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026年4月25日〜11月23日</t>
+          <t>4/27～11/23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>自動（公式・予約サイト）</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>宿泊の開始は4/27（日帰り入浴などは4/24から。公式4月16日のお知らせ）。終わりは長野県のポータル・予約サイトの記載</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Webは宿泊日の90日前 0:00から（出典の記載は「2か月前予約制」）</t>
@@ -60464,7 +60535,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -60818,7 +60889,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>150人</t>
+          <t>150人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -60848,7 +60919,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -60918,7 +60989,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0263-35-7200</t>
+          <t>090-1401-7884・050-1726-5030（営業期間中の現地。期間外は松本事務所 0263-35-7200）</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -60934,7 +61005,7 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>宿泊日の1か月前の朝9:00から</t>
+          <t>宿泊日の1か月前の朝9:00から（例：8月15日の宿泊は7月15日9:00から）</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -60944,7 +61015,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Web・電話</t>
+          <t>Web・電話（山小屋の現地）</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -60984,7 +61055,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -61094,7 +61165,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>約300人（山と溪谷オンライン）</t>
+          <t>186人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -61124,7 +61195,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -61210,7 +61281,7 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Webは宿泊日の6週前の同じ曜日 0:00から（電話は日程が異なる。出典の記載は「1か月前予約制」）</t>
+          <t>やまたんは4月1日10:00から（5/14以降の宿泊分は宿泊日の6週前の同じ曜日0:00から）、モンベルの予約サイトは宿泊日の1か月前の同じ日0:00から、電話（松本事務所）は宿泊日が月〜木曜なら3週間前の月曜、金〜日曜なら3週間前の金曜の各10:00から（6/29以降の宿泊分）（2026年）</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -61220,7 +61291,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Web（やまたん）・電話</t>
+          <t>Web（やまたん）・Web（モンベル）・電話（松本事務所 0263-58-2210）</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -61230,7 +61301,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>約200人（山と溪谷オンライン）</t>
+          <t>30人～最大150人程度（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -61260,7 +61331,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -61350,7 +61421,7 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>宿泊日の1か月前から</t>
+          <t>電話のみで、宿泊日が月〜木曜なら3週間前の月曜、金〜日曜なら3週間前の金曜の各10:00から（蝶ヶ岳ヒュッテの電話予約と同じ決まり。2026年）</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -61358,7 +61429,11 @@
           <t>手入力（公式サイト・出典を読んで確認）</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>電話のみ（蝶ヶ岳ヒュッテ松本事務所 0263-58-2210）</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>はい</t>
@@ -61371,7 +61446,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>何日前・何か月前</t>
+          <t>非対応</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -61396,7 +61471,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -61418,12 +61493,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>報告だけ：「◯か月前」の数字の変化と、一斉解放の書き方が出てきたか</t>
+          <t>報告だけ：予約の開始らしい記載が見つかったら候補として報告（未登録の小屋）</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>決まりが変わっていないか（12〜6月は週1回、それ以外は毎月1日）</t>
+          <t>毎月1日に公式ページを見る（変わると「変更あり」）</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -61484,7 +61559,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Web・電話</t>
+          <t>Web（宿泊の3日前より前はWebのみ）・電話（前日・当日の予約）</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -61520,7 +61595,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -61999,20 +62074,24 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026/6/6～10/25、栂池自然園の開園は6/6～10/25 ＊春の大型連休中は営業なし</t>
+          <t>6/6～10/25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>宿泊は10/24が最終日（公式）</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>電話</t>
+          <t>Web（公式サイト）・電話（090-7708-6341）</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -62048,7 +62127,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -63051,15 +63130,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026/6/20～10/12 ＊5/20（水）7：00～Webで予約受付開始、テント場も完全予約制</t>
+          <t>4/25～5/5、6/20～10/12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>公式の2026年営業期間（残雪期を含む）</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>残雪期の宿泊分は4月1日 9:00から、夏季（6/20〜）の宿泊分は5月20日 7:00から（2026年）</t>
@@ -63112,7 +63195,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -63350,7 +63433,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>約200人（山と溪谷オンライン）</t>
+          <t>約120人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -63380,7 +63463,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -63711,15 +63794,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>例年：7月上旬～9月下旬</t>
+          <t>2026年の営業は終了</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>8月17日のお知らせ「今シーズンの大沢小屋の営業は終了いたしました」。例年は7月上旬～9月下旬</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -63756,7 +63843,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -64920,7 +65007,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>電話（1週間前まで）</t>
+          <t>電話（できる限り1週間前までに）</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -64928,7 +65015,11 @@
           <t>はい</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>18人（公式・自治体の案内で確認）</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>一斉（決まった日）</t>
@@ -64956,7 +65047,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -65031,15 +65122,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026/7月上旬～９月下旬 （予定） ＊Web予約のみ ＊営業期間の変更など要確認 ＊テント場あり</t>
+          <t>7/11～9/30</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>9/30の宿泊まで（公式の予約ページ）</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>6月22日 9:00から</t>
@@ -65062,7 +65157,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>20人</t>
+          <t>20人（小屋泊）（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -65092,7 +65187,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -65330,7 +65425,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>約100人（山と溪谷オンライン）</t>
+          <t>約50人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -65360,7 +65455,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -65582,7 +65677,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>約200人（山と溪谷オンライン）</t>
+          <t>約100人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -65612,7 +65707,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -65826,7 +65921,11 @@
           <t>手入力（公式サイト・出典を読んで確認）</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>メール（宿泊予約メール）</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>はい</t>
@@ -65864,7 +65963,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -65931,15 +66030,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026年は休業予定、要確認のこと</t>
+          <t>営業休止（2026年度から。再開は未定）</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>越百避難小屋は利用できる（長野県の観光サイト）</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
@@ -65976,7 +66079,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -66043,20 +66146,24 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4月下旬から11月中旬</t>
+          <t>4/29～11/24</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>自動（公式・予約サイト）</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>事前予約制（長野県の山小屋のページの2026年の記載）</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Web（予約フォーム）・電話</t>
+          <t>電話・メール</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -66096,7 +66203,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -66179,7 +66286,11 @@
           <t>自動（公式・予約サイト）</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026～27年の年末年始（12/31・1/1泊）に特別営業（公式）</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>宿泊の2日前まで（開始日の定めは記載なし）</t>
@@ -66228,7 +66339,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -66462,7 +66573,7 @@
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>約200人（山と溪谷オンライン）</t>
+          <t>80人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -66492,7 +66603,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -66699,7 +66810,11 @@
           <t>出典の記載</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026年の営業期間は公式サイトに記載がない（表示は長野県のポータルの2025年の記載）</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
@@ -66714,7 +66829,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>約200人（山と溪谷オンライン）</t>
+          <t>138人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -66744,7 +66859,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -67195,7 +67310,11 @@
           <t>出典の記載</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026年の営業期間は公式サイトに記載がない（表示は長野県のポータルの2025年の記載）</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
@@ -67210,7 +67329,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>約100人（山と溪谷オンライン）</t>
+          <t>61人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -67240,7 +67359,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -67431,17 +67550,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026/6/1～10/25 ＊完全予約制（電話）</t>
+          <t>6/1～10/18</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>出典の記載</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>営業期間は令和8年6月1日〜10月18日（予約制）</t>
+          <t>営業期間は令和8年6月1日〜10月18日（予約制）／完全予約制（電話）。栄村秋山郷観光協会の2026年の案内</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -67484,7 +67603,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -68079,10 +68198,18 @@
           <t>出典の記載</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>冬季営業は2026年11月6日～2027年3月7日（金土日の予約が基本。1～2月は平日も相談可）</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Web（公式サイトの予約）</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>はい</t>
@@ -68105,7 +68232,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>いいえ（noindex）</t>
+          <t>はい</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -68120,7 +68247,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -68459,15 +68586,19 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>例年4月下旬～11月下旬（3月～4月中旬は休休業）</t>
+          <t>4/下～11/下</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>冬季は週末と年末年始のみ。3月～4月中旬は休み（公式）</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
@@ -68508,7 +68639,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -68602,7 +68733,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>約50人（山と溪谷オンライン）</t>
+          <t>30人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -68632,7 +68763,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -68943,17 +69074,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026/4/29～5/5、7/1～9/30 ＊営業日を確認のこと ＊完全予約制（電話のみ）</t>
+          <t>7/1～10/11</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>出典の記載</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>令和8年は7月1日から10月11日まで営業</t>
+          <t>令和8年は7月1日から10月11日まで営業／公式「令和８年は７月１日より、１０月１１日まで営業」</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -69000,7 +69131,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -69191,23 +69322,27 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>GW、6/13～11/3、 年末年始 （予定）</t>
+          <t>4/25～5/5、6/13～11/3</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>GWは素泊まりのみ。11/2の泊まりまで（公式2026年3月26日のお知らせ）</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>4月1日から（2026年）</t>
+          <t>4月1日から（2026年。小屋泊は完全予約制で電話。テント泊は予約不要）</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>自動（公式ページのレシピ）</t>
+          <t>手入力（公式サイト・出典を読んで確認）</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -69215,7 +69350,11 @@
           <t>電話</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>27人</t>
@@ -69244,7 +69383,7 @@
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -69255,7 +69394,7 @@
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr">
         <is>
-          <t>bookingStart</t>
+          <t>bookingStartDate</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -69466,7 +69605,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>約30人（山と溪谷オンライン）</t>
+          <t>20人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -69492,7 +69631,7 @@
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -69578,7 +69717,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>約30人（山と溪谷オンライン）</t>
+          <t>25人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -69604,7 +69743,7 @@
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -69678,11 +69817,19 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>電話（055-288-2402）</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>約20人（山と溪谷オンライン）</t>
+          <t>15人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -69697,7 +69844,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>いいえ（noindex）</t>
+          <t>はい</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -69708,7 +69855,7 @@
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -70410,7 +70557,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>約47人（山と溪谷オンライン）</t>
+          <t>61人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -70436,7 +70583,7 @@
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -70511,15 +70658,19 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>6/26～10/25 （予定）</t>
+          <t>6/26～10/25</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>10/24の宿泊まで（公式）</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
@@ -70556,7 +70707,7 @@
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -71015,18 +71166,22 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4/26～11/3</t>
+          <t>4/26～11/15</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>予定。東海フォレストの施設案内</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>7/11〜9/22の宿泊分は6月15日 17:00から順次（Web。電話は6月16日から。2026年）</t>
+          <t>4/26〜7/10の宿泊分は4月6日から電話。7/11〜9/22の宿泊分は、泊まる月ごとに Web で6月15日・19日・23日の17:00から、電話で6月29日・7月3日・7月8日の10:00から（2026年）。9/23以降は宿泊日の30日前から電話</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -71044,10 +71199,14 @@
           <t>はい</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>80人（公式・自治体の案内で確認）</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>一斉（決まった日）</t>
+          <t>期間区切り</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -71068,7 +71227,7 @@
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -71086,7 +71245,7 @@
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
+          <t>報告だけ：期間区切りは自動では替えない（公式の記載が変わると「変更あり」）</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
@@ -71146,7 +71305,7 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>7/11〜9/22の宿泊分は6月15日 17:00から順次（Web。電話は6月16日から。2026年）</t>
+          <t>7/11〜9/22の宿泊分は、泊まる月ごとに Web で6月15日・19日・23日の17:00から、電話で6月29日・7月3日・7月8日の10:00から（2026年）。9/23以降は予約制ではなく当日受付（10/10・11泊だけ10月1日から電話で予約）</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -71171,7 +71330,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>一斉（決まった日）</t>
+          <t>期間区切り</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -71192,7 +71351,7 @@
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -71210,7 +71369,7 @@
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
+          <t>報告だけ：期間区切りは自動では替えない（公式の記載が変わると「変更あり」）</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
@@ -71286,7 +71445,7 @@
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>約10人（山と溪谷オンライン）</t>
+          <t>5人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -71312,7 +71471,7 @@
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -71390,7 +71549,7 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>7/11〜9/22の宿泊分は6月15日 17:00から順次（Web。電話は6月16日から。2026年）</t>
+          <t>7/11〜9/22の宿泊分は、泊まる月ごとに Web で6月15日・19日・23日の17:00から、電話で6月29日・7月3日・7月8日の10:00から（2026年）。9/23以降は予約制ではなく当日受付（10/10・11泊だけ10月1日から電話で予約）</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -71415,7 +71574,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>一斉（決まった日）</t>
+          <t>期間区切り</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -71436,7 +71595,7 @@
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -71454,7 +71613,7 @@
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
+          <t>報告だけ：期間区切りは自動では替えない（公式の記載が変わると「変更あり」）</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
@@ -71514,28 +71673,32 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>予約不要</t>
+          <t>7/11〜9/22の宿泊分は、泊まる月ごとに Web で6月15日・19日・23日の17:00から、電話で6月29日・7月3日・7月8日の10:00から（2026年）</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>手入力</t>
+          <t>手入力（公式サイト・出典を読んで確認）</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>予約なし</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
+          <t>Web・電話</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>約20人（山と溪谷オンライン）</t>
+          <t>10人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>非対応</t>
+          <t>期間区切り</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -71556,7 +71719,7 @@
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -71574,12 +71737,12 @@
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>対象外（予約不要）</t>
+          <t>報告だけ：期間区切りは自動では替えない（公式の記載が変わると「変更あり」）</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>毎月1日に公式ページを見る（変わると「変更あり」）</t>
+          <t>来季の予約開始日（発表が出そうな期間は3日に1回、それ以外は毎月1日）</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -71634,7 +71797,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>7/11〜9/22の宿泊分は6月15日 17:00から順次（Web。電話は6月16日から。2026年）</t>
+          <t>7/11〜9/22の宿泊分は、泊まる月ごとに Web で6月15日・19日・23日の17:00から、電話で6月29日・7月3日・7月8日の10:00から（2026年）。9/23以降は予約制ではなく当日受付（10/10・11泊だけ10月1日から電話で予約）</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -71659,7 +71822,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>一斉（決まった日）</t>
+          <t>期間区切り</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -71680,7 +71843,7 @@
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -71698,7 +71861,7 @@
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
+          <t>報告だけ：期間区切りは自動では替えない（公式の記載が変わると「変更あり」）</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
@@ -72126,17 +72289,17 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>5月1日 12:00から（2026年度）</t>
+          <t>Web（やまたん）は5月1日 12:00から（2026年度の全期間分）、電話（山小屋直通）は宿泊日の1か月前（前月の同じ日）の10:00から</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>自動（公式ページのレシピ）</t>
+          <t>手入力（公式サイト・出典を読んで確認）</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Web（やまたん）</t>
+          <t>Web（やまたん）・電話（山小屋直通。予約金2,000円の振込が必要）</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -72172,7 +72335,7 @@
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -72187,7 +72350,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>bookingStart</t>
+          <t>bookingStartDate</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -72879,18 +73042,22 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4/15～11/下 （宿泊は 8/30まで）</t>
+          <t>宿泊は2026年8月31日で終了</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>宿泊サービス部門は8月31日の営業で終了。飲食・売店は営業を続けている（公式）</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026年度分は2025年12月1日から（宿泊事業は2026年8月31日で終了）</t>
+          <t>宿泊サービスは2026年8月31日で終了（飲食・売店は営業）</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -72928,7 +73095,7 @@
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -73751,15 +73918,19 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4/28～10/18</t>
+          <t>4/28～10/17</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>10/17の宿泊まで。10/18は昼の売店だけ（公式）</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
@@ -73796,7 +73967,7 @@
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -74239,15 +74410,19 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>夏期：4月下旬～11月中旬  　冬期：12月下旬～1月上旬</t>
+          <t>5/上～11/中</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>自動（公式・予約サイト）</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>冬期は12月下旬～1月上旬。水曜定休（2026年は7/18～9/29は休まず営業）。予約サイトの小屋の案内</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
@@ -74288,7 +74463,7 @@
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -74739,15 +74914,19 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>通年（12月～4月中旬は土・日曜と年末年始の営業。その他の日は要確認）</t>
+          <t>通年</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>12月～4月中旬は完全予約（公式）</t>
+        </is>
+      </c>
       <c r="K128" t="inlineStr">
         <is>
           <t>記載なし</t>
@@ -74766,7 +74945,7 @@
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>約25人（山と溪谷オンライン）</t>
+          <t>23人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -74792,7 +74971,7 @@
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -74998,11 +75177,15 @@
           <t>手入力（公式サイトに記載が無いと確認）</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>電話</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
-          <t>約40人（山と溪谷オンライン）</t>
+          <t>2人部屋4室・3人部屋6室（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -75017,7 +75200,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>いいえ（noindex）</t>
+          <t>はい</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -75028,7 +75211,7 @@
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -75330,17 +75513,17 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>宿泊の2日前までに電話で予約</t>
+          <t>記載なし</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>手入力（公式サイト・出典を読んで確認）</t>
+          <t>手入力（公式サイトに記載が無いと確認）</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>電話・FAX（2週間以上先のみ）</t>
+          <t>電話（基本的に2日前まで）・FAX（2週間以上先のみ）</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -75376,7 +75559,7 @@
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
@@ -76515,15 +76698,19 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>例年 7/上～10/初（変動あり）</t>
+          <t>2026年の営業は終了</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>公式9月10日のお知らせ。公式の営業期間の記載は「6月下旬～9月下旬」「7月上旬～9月上旬」の2通りある</t>
+        </is>
+      </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
@@ -76534,7 +76721,7 @@
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
-          <t>約70人（山と溪谷オンライン）</t>
+          <t>60人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -76560,7 +76747,7 @@
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
@@ -76619,7 +76806,11 @@
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>http://www.goraikousansou.com/</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
@@ -76634,11 +76825,15 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Web（予約サイト）</t>
+        </is>
+      </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
-          <t>約180人（山と溪谷オンライン）</t>
+          <t>140人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -76653,7 +76848,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>いいえ（noindex）</t>
+          <t>はい</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -76664,7 +76859,7 @@
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
@@ -76676,16 +76871,20 @@
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>監視なし（公式サイトのURLが無い）</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr"/>
+          <t>報告だけ：予約の開始らしい記載が見つかったら候補として報告（未登録の小屋）</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>毎月1日に公式ページを見る（変わると「変更あり」）</t>
+        </is>
+      </c>
       <c r="AC144" t="inlineStr">
         <is>
           <t>書き換えない（予約の開始・方法・定員は人が確かめて直す）。自動で読めた値が確認を通れば、ページではそちらを優先して表示する</t>
@@ -76967,7 +77166,11 @@
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://mannnennyuki.wixsite.com/mannennyuki</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
@@ -77024,7 +77227,7 @@
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
@@ -77040,13 +77243,13 @@
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr"/>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>自動で反映：やまたんの予約開始のお知らせ（手の値より新しい年のとき）</t>
+          <t>自動で反映：やまたんの予約開始のお知らせ（手の値より新しい年のとき）／自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
@@ -77250,7 +77453,7 @@
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
-          <t>約150人（山と溪谷オンライン）</t>
+          <t>120人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -77276,7 +77479,7 @@
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
@@ -77587,7 +77790,11 @@
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>http://www2.tbb.t-com.ne.jp/hanagoya/</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
@@ -77632,7 +77839,7 @@
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
@@ -77644,16 +77851,20 @@
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr"/>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>監視なし（公式サイトのURLが無い）</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr"/>
+          <t>報告だけ：予約の開始らしい記載が見つかったら候補として報告（未登録の小屋）</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>毎月1日に公式ページを見る（変わると「変更あり」）</t>
+        </is>
+      </c>
       <c r="AC152" t="inlineStr">
         <is>
           <t>書き換えない（予約の開始・方法・定員は人が確かめて直す）。自動で読めた値が確認を通れば、ページではそちらを優先して表示する</t>
@@ -77687,7 +77898,11 @@
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://www.hinodekan-fujiyoshida.com/</t>
+        </is>
+      </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
@@ -77744,7 +77959,7 @@
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
@@ -77760,13 +77975,13 @@
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr"/>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>自動で反映：やまたんの予約開始のお知らせ（手の値より新しい年のとき）</t>
+          <t>自動で反映：やまたんの予約開始のお知らせ（手の値より新しい年のとき）／自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
@@ -77950,7 +78165,7 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>5月8日 10:00から（2026年）</t>
+          <t>2027年分はゴールデンウィーク明けにWeb予約開始の予定（電話は7月1日から。2026年は5月8日 10:00から）</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -77960,7 +78175,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Webのみ</t>
+          <t>Web・電話（7月1日から）</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -77992,7 +78207,7 @@
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
@@ -78063,15 +78278,19 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>例年 7/1～9/初</t>
+          <t>7/1～9/10</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>公式の全営業期間。2026年の営業は終了</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr">
         <is>
           <t>5月17日 10:00から（2026年。2027年分は5月中旬の予定）</t>
@@ -78116,7 +78335,7 @@
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
@@ -78307,15 +78526,19 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>例年 6/30～9/10</t>
+          <t>7/1～9/9</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>9/9の宿泊まで。2027年は7/1～9/8の宿泊の予定（公式）</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
           <t>2027年分は5月中旬ごろ（2026年は5月26日 10:00から）</t>
@@ -78360,7 +78583,7 @@
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
@@ -78431,15 +78654,19 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>例年 6/下～9/上</t>
+          <t>6/30～9/9</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>宿泊日の期間（公式の予約受付の案内）</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr">
         <is>
           <t>宿泊時期ごとに5月11日〜14日の各日 9:00から（2026年）</t>
@@ -78484,7 +78711,7 @@
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V159" t="inlineStr">
@@ -78694,17 +78921,17 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>5月1日から（2026年）</t>
+          <t>5月1日 9:30から（2026年。オンラインのみ）</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>自動（公式ページの日付）</t>
+          <t>手入力（公式サイト・出典を読んで確認）</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Web（やまたん）</t>
+          <t>Webのみ（2026年から電話予約なし）</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -78740,7 +78967,7 @@
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
@@ -79419,7 +79646,11 @@
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://hakusan-guide.or.jp/hakusan_stay/murodou/</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
@@ -79447,10 +79678,14 @@
           <t>電話のみ（予約センター）</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>約200人（山と溪谷オンライン）</t>
+          <t>収容750人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -79476,7 +79711,7 @@
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
@@ -79488,13 +79723,13 @@
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr"/>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>監視なし（公式サイトのURLが無い）</t>
+          <t>自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
@@ -79564,7 +79799,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>電話（予約センター）</t>
+          <t>電話（予約センター）・FAX</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -79596,7 +79831,7 @@
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
@@ -79891,7 +80126,11 @@
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://www.city.kitakata.fukushima.jp/soshiki/sangyo-y/43737.html</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
@@ -79903,7 +80142,11 @@
           <t>出典の記載</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>管理人の滞在は2026年7月3日～10月11日（喜多方市）。それ以外は無人の避難小屋</t>
+        </is>
+      </c>
       <c r="K171" t="inlineStr">
         <is>
           <t>予約不要</t>
@@ -79948,7 +80191,7 @@
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
@@ -79960,7 +80203,7 @@
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr"/>
@@ -79969,7 +80212,11 @@
           <t>対象外（予約不要）</t>
         </is>
       </c>
-      <c r="AB171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>毎月1日に公式ページを見る（変わると「変更あり」）</t>
+        </is>
+      </c>
       <c r="AC171" t="inlineStr">
         <is>
           <t>書き換えない（予約の開始・方法・定員は人が確かめて直す）。自動で読めた値が確認を通れば、ページではそちらを優先して表示する</t>
@@ -80003,21 +80250,37 @@
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://iide.3gaku.jp/</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>7月1日〜10月9日（不定休/ 要電話確認）</t>
+          <t>7/1～10/12</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>自動（公式・予約サイト）</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>管理人の2026年度の案内では、常駐は7/1～9/30、10月は2～4日・9～12日、10/12に小屋閉め（喜多方市の案内では管理人の滞在は7/3～10/12）。それ以外は無人の避難小屋</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>1年中いつでも予約できる（管理人の案内「山小屋の宿泊予約は、1年中受け付けております」）</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>手入力（公式サイト・出典を読んで確認）</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>電話・Web（予約フォーム）</t>
@@ -80056,7 +80319,7 @@
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
@@ -80072,16 +80335,20 @@
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr"/>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>監視なし（公式サイトのURLが無い）</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr"/>
+          <t>報告だけ：予約の開始らしい記載が見つかったら候補として報告（未登録の小屋）</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>毎月1日に公式ページを見る（変わると「変更あり」）</t>
+        </is>
+      </c>
       <c r="AC172" t="inlineStr">
         <is>
           <t>書き換えない（予約の開始・方法・定員は人が確かめて直す）。自動で読めた値が確認を通れば、ページではそちらを優先して表示する</t>
@@ -80115,7 +80382,11 @@
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://www.city.kitakata.fukushima.jp/soshiki/sangyo-y/43737.html</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
@@ -80127,7 +80398,11 @@
           <t>出典の記載</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>管理人の滞在は2026年7月3日～10月12日（喜多方市）。それ以外は無人の避難小屋</t>
+        </is>
+      </c>
       <c r="K173" t="inlineStr">
         <is>
           <t>予約不要</t>
@@ -80172,7 +80447,7 @@
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
@@ -80184,7 +80459,7 @@
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr"/>
@@ -80193,7 +80468,11 @@
           <t>対象外（予約不要）</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr"/>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>毎月1日に公式ページを見る（変わると「変更あり」）</t>
+        </is>
+      </c>
       <c r="AC173" t="inlineStr">
         <is>
           <t>書き換えない（予約の開始・方法・定員は人が確かめて直す）。自動で読めた値が確認を通れば、ページではそちらを優先して表示する</t>
@@ -80235,15 +80514,19 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>例年 4/下旬～10/下旬</t>
+          <t>4/29～10/24</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>公式の2026年の営業期間</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr">
         <is>
           <t>宿泊日の1年前から</t>
@@ -80284,7 +80567,7 @@
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V174" t="inlineStr">
@@ -80366,7 +80649,11 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Web・電話（予約受付日程表あり）</t>
+        </is>
+      </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
@@ -80385,7 +80672,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>いいえ（noindex）</t>
+          <t>はい</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -80396,7 +80683,7 @@
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
@@ -80583,7 +80870,11 @@
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://www.oze-info.jp/ozh_stay/miikelodge/</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
@@ -80598,7 +80889,7 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>3月9日から（Webは0:00、電話は8:30から。2026年）</t>
+          <t>3月9日から（Webは0:00から。電話の受付開始は、同じお知らせの中に8:00と8:30の両方の記載がある。2026年）</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -80614,7 +80905,7 @@
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
-          <t>約65人（山と溪谷オンライン）</t>
+          <t>60人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -80640,7 +80931,7 @@
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
@@ -80652,13 +80943,13 @@
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>監視なし（公式サイトのURLが無い）</t>
+          <t>自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
@@ -80842,7 +81133,7 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>3月9日から（Webは0:00、電話は8:30から。2026年）</t>
+          <t>3月9日から（Webは0:00から。電話の受付開始は、同じお知らせの中に8:00と8:30の両方の記載がある。2026年）</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -80858,7 +81149,7 @@
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
-          <t>約150人（山と溪谷オンライン）</t>
+          <t>112人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -80884,7 +81175,7 @@
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
@@ -80943,7 +81234,11 @@
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://www.city.uonuma.lg.jp/page/1013581.html</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
@@ -81000,7 +81295,7 @@
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V180" t="inlineStr">
@@ -81012,7 +81307,7 @@
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr"/>
@@ -81021,7 +81316,11 @@
           <t>対象外（予約不要）</t>
         </is>
       </c>
-      <c r="AB180" t="inlineStr"/>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>毎月1日に公式ページを見る（変わると「変更あり」）</t>
+        </is>
+      </c>
       <c r="AC180" t="inlineStr">
         <is>
           <t>書き換えない（予約の開始・方法・定員は人が確かめて直す）。自動で読めた値が確認を通れば、ページではそちらを優先して表示する</t>
@@ -81167,7 +81466,11 @@
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://www.enjoy-minakami.jp/news/471/</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
@@ -81228,7 +81531,7 @@
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
@@ -81240,13 +81543,13 @@
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr"/>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>監視なし（公式サイトのURLが無い）</t>
+          <t>自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
@@ -81287,7 +81590,11 @@
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://tairappyouyama.wixsite.com/yamanoie</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
@@ -81322,7 +81629,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>約25人（山と溪谷オンライン）</t>
+          <t>12人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -81348,7 +81655,7 @@
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
@@ -81360,13 +81667,13 @@
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr"/>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>監視なし（公式サイトのURLが無い）</t>
+          <t>自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr">
@@ -81407,7 +81714,11 @@
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://www.city.nikko.lg.jp/kanko_bunka_sports/activity/1/4/6167.html</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
@@ -81464,7 +81775,7 @@
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V184" t="inlineStr">
@@ -81476,7 +81787,7 @@
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr"/>
@@ -81485,7 +81796,11 @@
           <t>対象外（予約不要）</t>
         </is>
       </c>
-      <c r="AB184" t="inlineStr"/>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>毎月1日に公式ページを見る（変わると「変更あり」）</t>
+        </is>
+      </c>
       <c r="AC184" t="inlineStr">
         <is>
           <t>書き換えない（予約の開始・方法・定員は人が確かめて直す）。自動で読めた値が確認を通れば、ページではそちらを優先して表示する</t>
@@ -81619,7 +81934,11 @@
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>http://komanokoya.com/</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
@@ -81680,7 +81999,7 @@
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V186" t="inlineStr">
@@ -81696,13 +82015,13 @@
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr"/>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>監視なし（公式サイトのURLが無い）</t>
+          <t>自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K600"/>
+  <dimension ref="A1:K601"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57266,6 +57266,61 @@
       <c r="K600" s="29" t="inlineStr">
         <is>
           <t>中（2つのセッションで並行して作業。こちらで統合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="29" t="n">
+        <v>600</v>
+      </c>
+      <c r="B601" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C601" s="29" t="inlineStr">
+        <is>
+          <t>17軒</t>
+        </is>
+      </c>
+      <c r="D601" s="29" t="inlineStr">
+        <is>
+          <t>山小屋まとめ</t>
+        </is>
+      </c>
+      <c r="E601" s="29" t="inlineStr">
+        <is>
+          <t>「確認不能829項目の再調査」の指摘を一次情報で確認して修正</t>
+        </is>
+      </c>
+      <c r="F601" s="29" t="inlineStr">
+        <is>
+          <t>huts_checked.py（営業期間3・定員10、確認日を項目ごとに）・huts_booking_extra.py・huts_rules.py（蓼科山荘）・build_huts_from_nagano.py（常念小屋の注記）・data/huts.json</t>
+        </is>
+      </c>
+      <c r="G601" s="29" t="inlineStr">
+        <is>
+          <t>白馬村営3軒・鷲が峰ひゅって・女人堂・山口山荘の定員（山と溪谷の古い値）、八方池山荘の予約方法・電話、蓼科山荘の予約（メール可・初回日だけ）、トモエ館2軒の営業期間（例年）、日の出館の営業期間、常念小屋の注記など</t>
+        </is>
+      </c>
+      <c r="H601" s="29" t="inlineStr">
+        <is>
+          <t>公式の原文どおり（穂高岳山荘・燕山荘は公称と現在の制限を併記、赤岳鉱泉・行者小屋は人数の記載なし、日の出館は公式サイトの7/1〜9/7と予約サイトの食い違いを併記）。蛭ヶ岳山荘は公式ページを読み取れず変更なし。尾瀬沼ヒュッテの旧URLは今も開くため変更なし</t>
+        </is>
+      </c>
+      <c r="I601" s="29" t="inlineStr">
+        <is>
+          <t>各小屋・村の公式ページ（2026-10-21 取得）</t>
+        </is>
+      </c>
+      <c r="J601" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0・お知らせの型の前後比較</t>
+        </is>
+      </c>
+      <c r="K601" s="29" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -59261,7 +59316,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>約250人（山と溪谷オンライン）</t>
+          <t>約250人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -59291,7 +59346,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -59507,7 +59562,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -60641,7 +60696,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>約650人（山と溪谷オンライン）</t>
+          <t>650人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -60671,7 +60726,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -61140,7 +61195,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>通常営業期間は4月27日〜11月4日</t>
+          <t>公式の予約のページは「通常営業期間：4月25日～11月3日（積雪状況により変動）」、施設紹介のページは「4月27日～11月3日」と、公式の中で記載が分かれている</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -62079,7 +62134,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -62637,7 +62692,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>約200人（山と溪谷オンライン）</t>
+          <t>280人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -62667,7 +62722,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -62765,7 +62820,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>約63人（山と溪谷オンライン）</t>
+          <t>90人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -62795,7 +62850,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -62997,7 +63052,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0261-75-3788 白馬村振興公社</t>
+          <t>0261-72-2855（八方池山荘）</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -63023,13 +63078,13 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Web（予約フォーム）</t>
+          <t>電話（八方池山荘へ直接）</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>約40人（山と溪谷オンライン）</t>
+          <t>50人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -63059,7 +63114,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -63135,7 +63190,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -65897,7 +65952,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>宿泊専用E-mail alpees@outlook.jp</t>
+          <t>電話番号の記載なし（宿泊の予約はメール alpees@outlook.jp）</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -66151,7 +66206,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -66293,17 +66348,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>宿泊の2日前まで（開始日の定めは記載なし）</t>
+          <t>記載なし</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>手入力（公式サイト・出典を読んで確認）</t>
+          <t>手入力（公式サイトに記載が無いと確認）</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Web（予約フォーム）・電話</t>
+          <t>Web（予約フォーム。宿泊の2日前まで）・電話</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -66429,17 +66484,17 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>4月2日 10:00から（2026年。Web予約）</t>
+          <t>宿泊日の2か月前の同じ日の7:00から（2026年度の受付開始は4月2日10:00）</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>自動（やまたんのお知らせ）</t>
+          <t>手入力（公式サイト・出典を読んで確認）</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Web（やまたん）・メール（1週間前まで）</t>
+          <t>Web（やまたん）のみ（メール・電話の予約は受け付けない）</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -66450,7 +66505,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>一斉（決まった日）</t>
+          <t>何日前・何か月前</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -66475,7 +66530,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -66501,12 +66556,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>自動で反映：やまたんの予約開始のお知らせ（手の値より新しい年のとき）／自動で反映：型で読む（年が今年か来年・前の年の日付から45日以内・候補が1つのときだけ。それ以外は報告）</t>
+          <t>自動で反映：やまたんの予約開始のお知らせ（手の値より新しい年のとき）／報告だけ：「◯か月前」の数字の変化と、一斉解放の書き方が出てきたか</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>来季の予約開始日（発表が出そうな期間は3日に1回、それ以外は毎月1日）</t>
+          <t>決まりが変わっていないか（12〜6月は週1回、それ以外は毎月1日）</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -66957,7 +67012,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>約100人（山と溪谷オンライン）</t>
+          <t>定員を減らして完全予約制（人数の記載なし）（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -66987,7 +67042,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -67089,7 +67144,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>約200人（山と溪谷オンライン）</t>
+          <t>定員を減らして完全予約制（人数の記載なし）（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -67119,7 +67174,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -68089,7 +68144,7 @@
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2組6人</t>
+          <t>1日2組4人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -68119,7 +68174,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -68591,7 +68646,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -68857,7 +68912,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>約80人（山と溪谷オンライン）</t>
+          <t>40人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -68887,7 +68942,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -69079,7 +69134,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -69327,7 +69382,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -70663,7 +70718,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -73923,7 +73978,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -74415,7 +74470,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -74919,7 +74974,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -76953,7 +77008,7 @@
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
-          <t>約180人（山と溪谷オンライン）</t>
+          <t>100人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -76979,7 +77034,7 @@
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
@@ -77906,15 +77961,19 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026年7月1日〜8月31日</t>
+          <t>7/1～9/7</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>自動（公式・予約サイト）</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>公式サイトの記載。予約サイトでは、お知らせは7/1～9/10、上部の表示は7/1～8/31と、記載が一致しない</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr">
         <is>
           <t>4月11日 10:00から（2026年。Web予約）</t>
@@ -78030,18 +78089,22 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>例年 6/下～9/10</t>
+          <t>7/1～9/10</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>公式2026年1月3日のお知らせ「2026年の営業期間は、7月1日～9月10日の予定」</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>5月11日から（2026年）</t>
+          <t>5月11日 0:00ごろから（2026年。ネット予約のみ）</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -78083,7 +78146,7 @@
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
@@ -78283,7 +78346,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -78659,7 +78722,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -79274,18 +79337,22 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>例年 6/30～9/10ごろ</t>
+          <t>7/1～9/10</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>公式2026年1月3日のお知らせ「2026年の営業期間は、7月1日～9月10日の予定」</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>5月11日から（2026年）</t>
+          <t>5月11日 0:00ごろから（2026年。ネット予約のみ）</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -79327,7 +79394,7 @@
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
@@ -80519,7 +80586,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>手入力（公式・自治体の案内で確認 2026-10-20）</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K601"/>
+  <dimension ref="A1:K602"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57321,6 +57321,61 @@
       <c r="K601" s="29" t="inlineStr">
         <is>
           <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="29" t="n">
+        <v>601</v>
+      </c>
+      <c r="B602" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C602" s="29" t="inlineStr">
+        <is>
+          <t>17軒</t>
+        </is>
+      </c>
+      <c r="D602" s="29" t="inlineStr">
+        <is>
+          <t>山小屋まとめ</t>
+        </is>
+      </c>
+      <c r="E602" s="29" t="inlineStr">
+        <is>
+          <t>前の2回で確かめられなかった指摘・追加の3件を再確認して修正</t>
+        </is>
+      </c>
+      <c r="F602" s="29" t="inlineStr">
+        <is>
+          <t>huts_checked.py（営業期間6・定員7）・huts_booking_extra.py・huts_official_urls.json・data/huts.json</t>
+        </is>
+      </c>
+      <c r="G602" s="29" t="inlineStr">
+        <is>
+          <t>雨飾山荘・唐松岳頂上山荘・清四郎小屋・鎌岩館・南御室小屋・薬師岳小屋の営業期間（例年・2025年など）、白馬館3軒の予約必須・方法、鳳凰小屋のテントの予約、高谷池ヒュッテ・将監小屋ほか定員</t>
+        </is>
+      </c>
+      <c r="H602" s="29" t="inlineStr">
+        <is>
+          <t>公式の原文どおり。つながらないサイトは Wayback Machine の2026年の写しで確認。公称と予約サイトの定員が違う5軒は公式の数を出し予約サイトの数を併記</t>
+        </is>
+      </c>
+      <c r="I602" s="29" t="inlineStr">
+        <is>
+          <t>公式サイト（アーカイブ含む）・予約サイト（やまたん・モンベル）・白馬館のよくある質問</t>
+        </is>
+      </c>
+      <c r="J602" s="29" t="inlineStr">
+        <is>
+          <t>check_pages 終了コード0・お知らせの型の前後比較</t>
+        </is>
+      </c>
+      <c r="K602" s="29" t="inlineStr">
+        <is>
+          <t>中（赤岳頂上山荘の6/19開始・青木鉱泉の2026年日程・赤岳天望荘/美濃戸山荘の2026年期間・至仏山荘の予約開始・蛭ヶ岳山荘のメール予約は今回も確認できず変更なし）</t>
         </is>
       </c>
     </row>
@@ -62418,10 +62473,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>Webのみ（電話の予約枠なし）</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>約30人（山と溪谷オンライン）</t>
@@ -62454,7 +62513,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -62550,10 +62609,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>Webのみ（電話の予約枠なし）</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>800人</t>
@@ -62586,7 +62649,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -62921,17 +62984,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2025/4/26～5/5、6/21～10/14</t>
+          <t>6/27～10/12</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>出典の記載</t>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026年の営業は10月12日宿泊分で終了</t>
+          <t>2026年の営業は10月12日宿泊分で終了／夏季。公式2026年6月28日の案内「6月27日（土）より夏季の営業を開始」「10月12日（月・祝）宿泊分まで」（アーカイブで確認）。春の営業の有無は記載なし</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -62982,7 +63045,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -63346,10 +63409,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>Webのみ（電話の予約枠なし）</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -63378,7 +63445,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -64260,7 +64327,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>68人</t>
+          <t>67人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -64290,7 +64357,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -66500,7 +66567,7 @@
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>20人</t>
+          <t>大部屋18人（通常時の半数以下に減らしている）（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -69973,15 +70040,19 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>6/上～11/2 （予定）</t>
+          <t>4/29～5/6、6/上～11/2</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>公式の2026年の案内：GW（4/29〜5/6）のあとは金・土曜の営業、常駐は6月初旬から（ヘリの荷上げ次第）。終わりは山と溪谷の一覧の記載（予定）</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>宿泊日の1か月前から（GW営業分は例年4月1日から）</t>
@@ -70026,7 +70097,7 @@
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -70093,15 +70164,19 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>6/上～11/2 （予定）</t>
+          <t>4/29～5/6、6/上～11/2</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>公式の2026年の案内：GW（4/29〜5/6）のあとは金・土曜の営業、常駐は6月初旬から（ヘリの荷上げ次第）。終わりは山と溪谷の一覧の記載（予定）</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>宿泊日の1か月前から（GW営業分は例年4月1日から）</t>
@@ -70146,7 +70221,7 @@
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -70224,7 +70299,7 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>4月1日から（2026年。夏の営業分・電話で受付。宿泊は完全予約制で、テント泊は指定日だけ予約制）</t>
+          <t>4月1日から（2026年。夏の営業分・電話で受付。宿泊は完全予約制。テント泊は指定日だけ予約制で、8名以上のグループは日程にかかわらず予約が必要）</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -70270,7 +70345,7 @@
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -71120,7 +71195,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>65人</t>
+          <t>100人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -71146,7 +71221,7 @@
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -73628,7 +73703,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>120人</t>
+          <t>250人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -73654,7 +73729,7 @@
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -75932,7 +76007,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>約70人（山と溪谷オンライン）</t>
+          <t>最大70人（テント50張を設営した場合を含む）（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -75958,7 +76033,7 @@
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
@@ -77132,7 +77207,7 @@
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
-          <t>150人</t>
+          <t>180人（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -77158,7 +77233,7 @@
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
@@ -78217,15 +78292,19 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>例年 6/下～9/中</t>
+          <t>7/1～9/10</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>公式「7月1日～営業終了日までは不休」（電話は7/1〜9/10開通）。2026年度の営業終了のお知らせは9月11日。2027年度も7月1日開始の予定</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr">
         <is>
           <t>2027年分はゴールデンウィーク明けにWeb予約開始の予定（電話は7月1日から。2026年は5月8日 10:00から）</t>
@@ -79996,7 +80075,7 @@
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
-          <t>約50人（山と溪谷オンライン）</t>
+          <t>40人（大部屋34人・個室2室は各3人）（公式・自治体の案内で確認）</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -80022,7 +80101,7 @@
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
@@ -81429,15 +81508,19 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
-          <t>例年 6/1～10/20</t>
+          <t>6/上～10/下</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>公式「営業期間 6月上旬～10月末」。2025年は変則営業だった（公式）。営業日は電話で確認</t>
+        </is>
+      </c>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
@@ -81474,7 +81557,7 @@
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V181" t="inlineStr">
@@ -81901,22 +81984,34 @@
           <t>雨飾山（新潟県側・雨飾温泉からのルート）</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://amakazarisanso.com/</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>例年 5/中～11/上</t>
+          <t>5/16～11/15</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>出典の記載</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr"/>
+          <t>手入力（公式・自治体の案内で確認 2026-10-21）</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>公式2026年5月7日のお知らせ「5月16日（土）より営業を開始」。公式の案内「冬期休業:11-16~」（2026年6月10日のアーカイブで確認）</t>
+        </is>
+      </c>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Web（公式サイトの予約）・電話</t>
+        </is>
+      </c>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr">
         <is>
@@ -81935,7 +82030,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>いいえ（noindex）</t>
+          <t>はい</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
@@ -81946,7 +82041,7 @@
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
@@ -81958,16 +82053,20 @@
       <c r="X185" t="inlineStr"/>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>なし（公式サイトのURLなし）</t>
+          <t>あり（公式サイトの予約・お知らせのページ）</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr"/>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>監視なし（公式サイトのURLが無い）</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr"/>
+          <t>報告だけ：予約の開始らしい記載が見つかったら候補として報告（未登録の小屋）</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>毎月1日に公式ページを見る（変わると「変更あり」）</t>
+        </is>
+      </c>
       <c r="AC185" t="inlineStr">
         <is>
           <t>書き換えない（予約の開始・方法・定員は人が確かめて直す）。自動で読めた値が確認を通れば、ページではそちらを優先して表示する</t>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K605"/>
+  <dimension ref="A1:K606"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57480,47 +57480,92 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" t="n">
+      <c r="A605" s="29" t="n">
         <v>604</v>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B605" s="29" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
+      <c r="C605" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D605" t="inlineStr">
+      <c r="D605" s="29" t="inlineStr">
         <is>
           <t>海外登山ギア（/gear/）</t>
         </is>
       </c>
-      <c r="E605" t="inlineStr">
+      <c r="E605" s="29" t="inlineStr">
         <is>
           <t>楽天に無い商品を同じブランドの楽天にある商品に入れ替え</t>
         </is>
       </c>
-      <c r="F605" t="inlineStr">
+      <c r="F605" s="29" t="inlineStr">
         <is>
           <t>gear/ の15ページ・data/gear-items.json・CLAUDE.md</t>
         </is>
       </c>
-      <c r="G605" t="inlineStr">
+      <c r="G605" s="29" t="inlineStr">
         <is>
           <t>楽天に同じ商品が無い12点に、別ブランドを含む「似た商品」の写真を出していた</t>
         </is>
       </c>
-      <c r="H605" t="inlineStr">
+      <c r="H605" s="29" t="inlineStr">
         <is>
           <t>同じブランド・同じカテゴリーで入れ替え：Daybreak Jacket→Pace Wind Jacket（224g）、Renegade GT MID→Renegade X GT MID（575g・29,700円）、MOAB 3 MID GORE-TEX→MOAB 3 SYNTHETIC MID GORE-TEX（470g・23,100円）。同じ商品と分かった3点（Junction 40・Windrider 40・lofoten）は「似た商品」の表示を外した。入れ替え先の無い6点（Pa'lante 3点・BLACKYAK Public Climbing・CAYL 2点）は写真なし（アイコン）</t>
         </is>
       </c>
-      <c r="I605" t="inlineStr">
+      <c r="I605" s="29" t="inlineStr">
         <is>
           <t>houdinisportswear.com の商品ページ、merrell.jp の商品ページ、楽天市場 登山専門店 遊岳人（LOWA 正規代理店商品 L510807）、楽天ウェブサービス 商品検索API</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>605</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>adatara ほか19山</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>安達太良山・川苔山・唐松岳・北岳・槍ヶ岳・御嶽山・筑波山・塔ノ岳・大菩薩嶺・奥穂高岳・谷川岳・那須岳・苗場山・立山・赤城山・白馬岳・瑞牆山・至仏山・乗鞍岳・日光白根山</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>代表的な登山ルートを定番3コースに見直し（1回目）</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>山ページ20・data/mountains.json・trailheads.json・accesses.json・sitemap.xml</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>コース1〜3（多くは出典なし・概数）</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>定番3コース（立山・至仏山は2コース）。時間・距離・累積標高差は YAMAP モデルコースの値、通行止め・決まりは公式で確認。日帰り区分：白馬岳が日帰り不可に。よくある質問・紹介文・難易度の理由の時間も合わせた</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>YAMAP モデルコース（各ルートの sourceUrl）・尾瀬保護財団（至仏山の登り専用）・白馬館（大雪渓の通行止め）・御嶽山の規制緩和（既存の出典）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K606"/>
+  <dimension ref="A1:K607"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57525,47 +57525,92 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" t="n">
+      <c r="A606" s="29" t="n">
         <v>605</v>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B606" s="29" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C606" s="29" t="inlineStr">
         <is>
           <t>adatara ほか19山</t>
         </is>
       </c>
-      <c r="D606" t="inlineStr">
+      <c r="D606" s="29" t="inlineStr">
         <is>
           <t>安達太良山・川苔山・唐松岳・北岳・槍ヶ岳・御嶽山・筑波山・塔ノ岳・大菩薩嶺・奥穂高岳・谷川岳・那須岳・苗場山・立山・赤城山・白馬岳・瑞牆山・至仏山・乗鞍岳・日光白根山</t>
         </is>
       </c>
-      <c r="E606" t="inlineStr">
+      <c r="E606" s="29" t="inlineStr">
         <is>
           <t>代表的な登山ルートを定番3コースに見直し（1回目）</t>
         </is>
       </c>
-      <c r="F606" t="inlineStr">
+      <c r="F606" s="29" t="inlineStr">
         <is>
           <t>山ページ20・data/mountains.json・trailheads.json・accesses.json・sitemap.xml</t>
         </is>
       </c>
-      <c r="G606" t="inlineStr">
+      <c r="G606" s="29" t="inlineStr">
         <is>
           <t>コース1〜3（多くは出典なし・概数）</t>
         </is>
       </c>
-      <c r="H606" t="inlineStr">
+      <c r="H606" s="29" t="inlineStr">
         <is>
           <t>定番3コース（立山・至仏山は2コース）。時間・距離・累積標高差は YAMAP モデルコースの値、通行止め・決まりは公式で確認。日帰り区分：白馬岳が日帰り不可に。よくある質問・紹介文・難易度の理由の時間も合わせた</t>
         </is>
       </c>
-      <c r="I606" t="inlineStr">
+      <c r="I606" s="29" t="inlineStr">
         <is>
           <t>YAMAP モデルコース（各ルートの sourceUrl）・尾瀬保護財団（至仏山の登り専用）・白馬館（大雪渓の通行止め）・御嶽山の規制緩和（既存の出典）</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>606</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>takao ほか19山</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>高尾山・甲斐駒ヶ岳・雲取山・金時山・巻機山・鋸山・金峰山・平標山・景信山・浅間山・燧ヶ岳・伊豆ヶ岳・伊予ヶ岳・会津駒ヶ岳・大天井岳・武甲山・鹿島槍ヶ岳・妙高山・御岳山・木曽駒ヶ岳</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>代表的な登山ルートを定番3コースに見直し（2回目）</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>山ページ20・data/mountains.json・trailheads.json・accesses.json・sitemap.xml</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>コース1〜3（多くは出典なし・概数）</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>定番3コース（甲斐駒ヶ岳・鋸山・木曽駒ヶ岳は2コース）。値は YAMAP モデルコース。日帰り区分：雲取山が日帰り不可に（鴨沢往復9時間56分）。浅間山の前掛山コースに噴火警戒レベル1の注記、伊豆ヶ岳に男坂・女坂の注記、大天井岳の一ノ沢下山に林道通行止めの注記</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>YAMAP モデルコース（各ルートの sourceUrl）・長野県佐久地域振興局（浅間山登山情報）・安曇野市（一ノ沢林道）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K607"/>
+  <dimension ref="A1:K608"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57570,47 +57570,92 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" t="n">
+      <c r="A607" s="29" t="n">
         <v>606</v>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B607" s="29" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C607" s="29" t="inlineStr">
         <is>
           <t>takao ほか19山</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr">
+      <c r="D607" s="29" t="inlineStr">
         <is>
           <t>高尾山・甲斐駒ヶ岳・雲取山・金時山・巻機山・鋸山・金峰山・平標山・景信山・浅間山・燧ヶ岳・伊豆ヶ岳・伊予ヶ岳・会津駒ヶ岳・大天井岳・武甲山・鹿島槍ヶ岳・妙高山・御岳山・木曽駒ヶ岳</t>
         </is>
       </c>
-      <c r="E607" t="inlineStr">
+      <c r="E607" s="29" t="inlineStr">
         <is>
           <t>代表的な登山ルートを定番3コースに見直し（2回目）</t>
         </is>
       </c>
-      <c r="F607" t="inlineStr">
+      <c r="F607" s="29" t="inlineStr">
         <is>
           <t>山ページ20・data/mountains.json・trailheads.json・accesses.json・sitemap.xml</t>
         </is>
       </c>
-      <c r="G607" t="inlineStr">
+      <c r="G607" s="29" t="inlineStr">
         <is>
           <t>コース1〜3（多くは出典なし・概数）</t>
         </is>
       </c>
-      <c r="H607" t="inlineStr">
+      <c r="H607" s="29" t="inlineStr">
         <is>
           <t>定番3コース（甲斐駒ヶ岳・鋸山・木曽駒ヶ岳は2コース）。値は YAMAP モデルコース。日帰り区分：雲取山が日帰り不可に（鴨沢往復9時間56分）。浅間山の前掛山コースに噴火警戒レベル1の注記、伊豆ヶ岳に男坂・女坂の注記、大天井岳の一ノ沢下山に林道通行止めの注記</t>
         </is>
       </c>
-      <c r="I607" t="inlineStr">
+      <c r="I607" s="29" t="inlineStr">
         <is>
           <t>YAMAP モデルコース（各ルートの sourceUrl）・長野県佐久地域振興局（浅間山登山情報）・安曇野市（一ノ沢林道）</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>607</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>iide ほか19山</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>飯豊山・鷹ノ巣山・天城山・蛭ヶ岳・白山・鍋割山・空木岳・蔵王山・磐梯山・古賀志山・焼岳・三頭山・針ノ木岳・七面山・黒姫山・乾徳山・笠ヶ岳・火打山・大岳山・蝶ヶ岳（ほかに御岳山・妙高山の一部）</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>代表的な登山ルートを定番3コースに見直し（3回目）</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>山ページ22・data/mountains.json・sitemap.xml</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>コース1〜3（多くは出典なし・概数）。鷹ノ巣山は通行止めの稲村岩尾根を代表コースに掲載</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>定番3コース（笠ヶ岳・火打山は2コース）。値は YAMAP モデルコース。日帰り区分：蛭ヶ岳が日帰り可に（青根往復8時間58分）、白山・針ノ木岳が日帰り不可に。白山に砂防新道・観光新道の工事通行止めの注記、焼岳・蔵王山に活火山の注記。鷹ノ巣山は稲村岩尾根の通行止めを本文・注記に反映（経路の行き先は未修正）</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>YAMAP モデルコース（各ルートの sourceUrl）・石川県（白山の登山道の状況）・奥多摩観光協会（稲村岩尾根 復旧未定）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K608"/>
+  <dimension ref="A1:K609"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57615,47 +57615,92 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" t="n">
+      <c r="A608" s="29" t="n">
         <v>607</v>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B608" s="29" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
+      <c r="C608" s="29" t="inlineStr">
         <is>
           <t>iide ほか19山</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr">
+      <c r="D608" s="29" t="inlineStr">
         <is>
           <t>飯豊山・鷹ノ巣山・天城山・蛭ヶ岳・白山・鍋割山・空木岳・蔵王山・磐梯山・古賀志山・焼岳・三頭山・針ノ木岳・七面山・黒姫山・乾徳山・笠ヶ岳・火打山・大岳山・蝶ヶ岳（ほかに御岳山・妙高山の一部）</t>
         </is>
       </c>
-      <c r="E608" t="inlineStr">
+      <c r="E608" s="29" t="inlineStr">
         <is>
           <t>代表的な登山ルートを定番3コースに見直し（3回目）</t>
         </is>
       </c>
-      <c r="F608" t="inlineStr">
+      <c r="F608" s="29" t="inlineStr">
         <is>
           <t>山ページ22・data/mountains.json・sitemap.xml</t>
         </is>
       </c>
-      <c r="G608" t="inlineStr">
+      <c r="G608" s="29" t="inlineStr">
         <is>
           <t>コース1〜3（多くは出典なし・概数）。鷹ノ巣山は通行止めの稲村岩尾根を代表コースに掲載</t>
         </is>
       </c>
-      <c r="H608" t="inlineStr">
+      <c r="H608" s="29" t="inlineStr">
         <is>
           <t>定番3コース（笠ヶ岳・火打山は2コース）。値は YAMAP モデルコース。日帰り区分：蛭ヶ岳が日帰り可に（青根往復8時間58分）、白山・針ノ木岳が日帰り不可に。白山に砂防新道・観光新道の工事通行止めの注記、焼岳・蔵王山に活火山の注記。鷹ノ巣山は稲村岩尾根の通行止めを本文・注記に反映（経路の行き先は未修正）</t>
         </is>
       </c>
-      <c r="I608" t="inlineStr">
+      <c r="I608" s="29" t="inlineStr">
         <is>
           <t>YAMAP モデルコース（各ルートの sourceUrl）・石川県（白山の登山道の状況）・奥多摩観光協会（稲村岩尾根 復旧未定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>608</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>iizunasan ほか19山</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>飯縄山・天覧山・富士山・常念岳・日向山・仙丈ヶ岳・四阿山・間ノ岳・陣馬山・丹沢山・美ヶ原・光岳・雨飾山・塩見岳・赤石岳・棒ノ折山・明神ヶ岳・矢倉岳・日の出山・茅ヶ岳</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>代表的な登山ルートを定番3コースに見直し（4回目）</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>山ページ20・data/mountains.json・trailheads.json・accesses.json・sitemap.xml</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>コース1〜3（多くは出典なし・概数）</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>定番3コース（仙丈ヶ岳・光岳・雨飾山・塩見岳・赤石岳は2コース）。値は YAMAP モデルコース。富士山に須走ルートを追加（登山口は座標未確認）。常念岳の一ノ沢往復は前の値のまま（YAMAP のモデルコースが取り下げ）。日向山の文章から通行禁止の錦滝経由の案内を外した</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>YAMAP モデルコース（各ルートの sourceUrl）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K609"/>
+  <dimension ref="A1:K610"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57660,45 +57660,90 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" t="n">
+      <c r="A609" s="29" t="n">
         <v>608</v>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B609" s="29" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C609" s="29" t="inlineStr">
         <is>
           <t>iizunasan ほか19山</t>
         </is>
       </c>
-      <c r="D609" t="inlineStr">
+      <c r="D609" s="29" t="inlineStr">
         <is>
           <t>飯縄山・天覧山・富士山・常念岳・日向山・仙丈ヶ岳・四阿山・間ノ岳・陣馬山・丹沢山・美ヶ原・光岳・雨飾山・塩見岳・赤石岳・棒ノ折山・明神ヶ岳・矢倉岳・日の出山・茅ヶ岳</t>
         </is>
       </c>
-      <c r="E609" t="inlineStr">
+      <c r="E609" s="29" t="inlineStr">
         <is>
           <t>代表的な登山ルートを定番3コースに見直し（4回目）</t>
         </is>
       </c>
-      <c r="F609" t="inlineStr">
+      <c r="F609" s="29" t="inlineStr">
         <is>
           <t>山ページ20・data/mountains.json・trailheads.json・accesses.json・sitemap.xml</t>
         </is>
       </c>
-      <c r="G609" t="inlineStr">
+      <c r="G609" s="29" t="inlineStr">
         <is>
           <t>コース1〜3（多くは出典なし・概数）</t>
         </is>
       </c>
-      <c r="H609" t="inlineStr">
+      <c r="H609" s="29" t="inlineStr">
         <is>
           <t>定番3コース（仙丈ヶ岳・光岳・雨飾山・塩見岳・赤石岳は2コース）。値は YAMAP モデルコース。富士山に須走ルートを追加（登山口は座標未確認）。常念岳の一ノ沢往復は前の値のまま（YAMAP のモデルコースが取り下げ）。日向山の文章から通行禁止の錦滝経由の案内を外した</t>
         </is>
       </c>
-      <c r="I609" t="inlineStr">
+      <c r="I609" s="29" t="inlineStr">
+        <is>
+          <t>YAMAP モデルコース（各ルートの sourceUrl）</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>609</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>ogiyama ほか19山</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>扇山・平ヶ岳・八ヶ岳（赤岳）・蓼科山・武尊山・日和田山・高妻山・十二ヶ岳・鎌倉アルプス・丸山（奥武蔵）・高川山・甲武信ヶ岳・石老山・毛無山・西吾妻山・大山（丹沢）・嵐山・三ノ塔・岩菅山・荒船山</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>代表的な登山ルートを定番3コースに見直し（5回目）</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>山ページ20・data/mountains.json・sitemap.xml</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>コース1〜3（多くは出典なし・概数）</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>定番3コース（平ヶ岳・嵐山は2コース）。値は YAMAP モデルコース。日帰り区分：八ヶ岳（赤岳）（美濃戸周回8時間43分）・高妻山（弥勒尾根往復8時間56分）が日帰り可に。毛無山の麓往復は YAMAP に無く前の値のまま（要確認）</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
         <is>
           <t>YAMAP モデルコース（各ルートの sourceUrl）</t>
         </is>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K610"/>
+  <dimension ref="A1:K613"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57705,47 +57705,182 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" t="n">
+      <c r="A610" s="29" t="n">
         <v>609</v>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B610" s="29" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr">
+      <c r="C610" s="29" t="inlineStr">
         <is>
           <t>ogiyama ほか19山</t>
         </is>
       </c>
-      <c r="D610" t="inlineStr">
+      <c r="D610" s="29" t="inlineStr">
         <is>
           <t>扇山・平ヶ岳・八ヶ岳（赤岳）・蓼科山・武尊山・日和田山・高妻山・十二ヶ岳・鎌倉アルプス・丸山（奥武蔵）・高川山・甲武信ヶ岳・石老山・毛無山・西吾妻山・大山（丹沢）・嵐山・三ノ塔・岩菅山・荒船山</t>
         </is>
       </c>
-      <c r="E610" t="inlineStr">
+      <c r="E610" s="29" t="inlineStr">
         <is>
           <t>代表的な登山ルートを定番3コースに見直し（5回目）</t>
         </is>
       </c>
-      <c r="F610" t="inlineStr">
+      <c r="F610" s="29" t="inlineStr">
         <is>
           <t>山ページ20・data/mountains.json・sitemap.xml</t>
         </is>
       </c>
-      <c r="G610" t="inlineStr">
+      <c r="G610" s="29" t="inlineStr">
         <is>
           <t>コース1〜3（多くは出典なし・概数）</t>
         </is>
       </c>
-      <c r="H610" t="inlineStr">
+      <c r="H610" s="29" t="inlineStr">
         <is>
           <t>定番3コース（平ヶ岳・嵐山は2コース）。値は YAMAP モデルコース。日帰り区分：八ヶ岳（赤岳）（美濃戸周回8時間43分）・高妻山（弥勒尾根往復8時間56分）が日帰り可に。毛無山の麓往復は YAMAP に無く前の値のまま（要確認）</t>
         </is>
       </c>
-      <c r="I610" t="inlineStr">
+      <c r="I610" s="29" t="inlineStr">
         <is>
           <t>YAMAP モデルコース（各ルートの sourceUrl）</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="29" t="n">
+        <v>610</v>
+      </c>
+      <c r="B611" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C611" s="29" t="inlineStr">
+        <is>
+          <t>iwadonoyama ほか19山</t>
+        </is>
+      </c>
+      <c r="D611" s="29" t="inlineStr">
+        <is>
+          <t>岩殿山・荒沢岳・高水三山・百蔵山・草戸山・石割山・太平山・吾妻山（二宮）・鳳凰山・九鬼山・白砂山・本仁田山・霧ヶ峰・弘法山・聖岳・小仏城山・官ノ倉山・恵那山・二子山（奥武蔵）・経ヶ岳</t>
+        </is>
+      </c>
+      <c r="E611" s="29" t="inlineStr">
+        <is>
+          <t>代表的な登山ルートを定番3コースに見直し（6回目）</t>
+        </is>
+      </c>
+      <c r="F611" s="29" t="inlineStr">
+        <is>
+          <t>山ページ20・data/mountains.json・sitemap.xml</t>
+        </is>
+      </c>
+      <c r="G611" s="29" t="inlineStr">
+        <is>
+          <t>コース1〜3（多くは出典なし・概数）</t>
+        </is>
+      </c>
+      <c r="H611" s="29" t="inlineStr">
+        <is>
+          <t>定番3コース（荒沢岳は2コース）。値は YAMAP モデルコース。日帰り区分の変更なし。聖岳は通行止めの便ヶ島ルートを外し、聖沢往復は YAMA HACK の値のまま（累積標高差なし）。岩殿山は畑倉登山口から（強瀬ルートの再開は公式未確認）</t>
+        </is>
+      </c>
+      <c r="I611" s="29" t="inlineStr">
+        <is>
+          <t>YAMAP モデルコース（各ルートの sourceUrl）・長野県 入山注意情報（2025-11-26）</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="29" t="n">
+        <v>611</v>
+      </c>
+      <c r="B612" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C612" s="29" t="inlineStr">
+        <is>
+          <t>登山タイプ診断</t>
+        </is>
+      </c>
+      <c r="D612" s="29" t="inlineStr">
+        <is>
+          <t>/recommend/・/type/ の16ページ・/recommend/&lt;記号&gt;/ の16ページ</t>
+        </is>
+      </c>
+      <c r="E612" s="29" t="inlineStr">
+        <is>
+          <t>診断結果の共有URLと共有の文を変更</t>
+        </is>
+      </c>
+      <c r="F612" s="29" t="inlineStr">
+        <is>
+          <t>recommend/index.html・type/*/index.html・recommend/*/index.html</t>
+        </is>
+      </c>
+      <c r="G612" s="29" t="inlineStr">
+        <is>
+          <t>共有URLは /recommend/&lt;記号&gt;/（noindex で結果画面へ転送）。共有の文は結果のURLだけ。説明文に「9つの質問」「9問」</t>
+        </is>
+      </c>
+      <c r="H612" s="29" t="inlineStr">
+        <is>
+          <t>共有URLを検索に出るタイプのページ /type/&lt;スラッグ&gt;/?スコア にし、開くと結果画面へ切り替える。共有の文に診断の最初の画面のURLと #登山タイプ診断 を追加。「9問」を「12問」に統一</t>
+        </is>
+      </c>
+      <c r="I612" s="29" t="inlineStr">
+        <is>
+          <t>運営者の指示（2026-10-25）</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>612</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>登山タイプ診断</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>/recommend/・/type/</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>12問目を出発地から計画/自由の質問に変更、おすすめの山を出発地に関係なく選ぶ</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>recommend/index.html・type/index.html</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>12問目は出発地（大船・横浜／新宿・渋谷／大宮・浦和）。おすすめの山は出発地からの近さで最大約120点を加点。計画/自由は2問（主質問2点で実質1問で決まる）</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>12問目「週末の天気予報が微妙。どうする？」（計画/自由）。計画/自由は3問を各1点。近さの点をやめ、カードは車の時間の代わりにエリア・難易度を表示。共有URLから出発地を外した</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>運営者の指示（2026-10-25）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K613"/>
+  <dimension ref="A1:K615"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57840,47 +57840,137 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" t="n">
+      <c r="A613" s="29" t="n">
         <v>612</v>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B613" s="29" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C613" s="29" t="inlineStr">
         <is>
           <t>登山タイプ診断</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr">
+      <c r="D613" s="29" t="inlineStr">
         <is>
           <t>/recommend/・/type/</t>
         </is>
       </c>
-      <c r="E613" t="inlineStr">
+      <c r="E613" s="29" t="inlineStr">
         <is>
           <t>12問目を出発地から計画/自由の質問に変更、おすすめの山を出発地に関係なく選ぶ</t>
         </is>
       </c>
-      <c r="F613" t="inlineStr">
+      <c r="F613" s="29" t="inlineStr">
         <is>
           <t>recommend/index.html・type/index.html</t>
         </is>
       </c>
-      <c r="G613" t="inlineStr">
+      <c r="G613" s="29" t="inlineStr">
         <is>
           <t>12問目は出発地（大船・横浜／新宿・渋谷／大宮・浦和）。おすすめの山は出発地からの近さで最大約120点を加点。計画/自由は2問（主質問2点で実質1問で決まる）</t>
         </is>
       </c>
-      <c r="H613" t="inlineStr">
+      <c r="H613" s="29" t="inlineStr">
         <is>
           <t>12問目「週末の天気予報が微妙。どうする？」（計画/自由）。計画/自由は3問を各1点。近さの点をやめ、カードは車の時間の代わりにエリア・難易度を表示。共有URLから出発地を外した</t>
         </is>
       </c>
-      <c r="I613" t="inlineStr">
+      <c r="I613" s="29" t="inlineStr">
         <is>
           <t>運営者の指示（2026-10-25）</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="29" t="n">
+        <v>613</v>
+      </c>
+      <c r="B614" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C614" s="29" t="inlineStr">
+        <is>
+          <t>トップページ</t>
+        </is>
+      </c>
+      <c r="D614" s="29" t="inlineStr">
+        <is>
+          <t>index.html の「16タイプ診断」ボタン</t>
+        </is>
+      </c>
+      <c r="E614" s="29" t="inlineStr">
+        <is>
+          <t>ボタンの背景にキャラクターの絵を入れた</t>
+        </is>
+      </c>
+      <c r="F614" s="29" t="inlineStr">
+        <is>
+          <t>index.html・recommend/images/top-type-banner.jpg</t>
+        </is>
+      </c>
+      <c r="G614" s="29" t="inlineStr">
+        <is>
+          <t>無地（#c8d4b8）＋方位磁針のアイコン＋「›」</t>
+        </is>
+      </c>
+      <c r="H614" s="29" t="inlineStr">
+        <is>
+          <t>カワウソ3匹の絵（右寄せ）＋左からのグラデーション。大きさは変えていない（168×49.5px／スマホ）</t>
+        </is>
+      </c>
+      <c r="I614" s="29" t="inlineStr">
+        <is>
+          <t>運営者の指示（2026-10-25）。絵は運営者が ChatGPT で作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>614</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>トップページ</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>index.html の「16タイプ診断」ボタン</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>背景の緑のグラデーションをやめ、絵だけにした</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>左から緑（#c8d4b8）のグラデーション＋右に絵</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>絵をボタン全体に敷く（cover）。文字は白いふちどり</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>運営者の指摘（緑と絵が混ざって不自然）</t>
         </is>
       </c>
     </row>

--- a/yamatch_kensho_kanri (3).xlsx
+++ b/yamatch_kensho_kanri (3).xlsx
@@ -24253,7 +24253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K615"/>
+  <dimension ref="A1:K618"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="29" min="1" max="1"/>
@@ -57930,47 +57930,182 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" t="n">
+      <c r="A615" s="29" t="n">
         <v>614</v>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B615" s="29" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C615" s="29" t="inlineStr">
         <is>
           <t>トップページ</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr">
+      <c r="D615" s="29" t="inlineStr">
         <is>
           <t>index.html の「16タイプ診断」ボタン</t>
         </is>
       </c>
-      <c r="E615" t="inlineStr">
+      <c r="E615" s="29" t="inlineStr">
         <is>
           <t>背景の緑のグラデーションをやめ、絵だけにした</t>
         </is>
       </c>
-      <c r="F615" t="inlineStr">
+      <c r="F615" s="29" t="inlineStr">
         <is>
           <t>index.html</t>
         </is>
       </c>
-      <c r="G615" t="inlineStr">
+      <c r="G615" s="29" t="inlineStr">
         <is>
           <t>左から緑（#c8d4b8）のグラデーション＋右に絵</t>
         </is>
       </c>
-      <c r="H615" t="inlineStr">
+      <c r="H615" s="29" t="inlineStr">
         <is>
           <t>絵をボタン全体に敷く（cover）。文字は白いふちどり</t>
         </is>
       </c>
-      <c r="I615" t="inlineStr">
+      <c r="I615" s="29" t="inlineStr">
         <is>
           <t>運営者の指摘（緑と絵が混ざって不自然）</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="29" t="n">
+        <v>615</v>
+      </c>
+      <c r="B616" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C616" s="29" t="inlineStr">
+        <is>
+          <t>トップページ</t>
+        </is>
+      </c>
+      <c r="D616" s="29" t="inlineStr">
+        <is>
+          <t>index.html の「山選び診断」ボタン</t>
+        </is>
+      </c>
+      <c r="E616" s="29" t="inlineStr">
+        <is>
+          <t>ボタンの背景に景色の絵を入れた（16タイプ診断と同じ形）</t>
+        </is>
+      </c>
+      <c r="F616" s="29" t="inlineStr">
+        <is>
+          <t>index.html・recommend/images/top-find-banner.jpg</t>
+        </is>
+      </c>
+      <c r="G616" s="29" t="inlineStr">
+        <is>
+          <t>無地（#c8d4b8）＋山のアイコン＋「›」</t>
+        </is>
+      </c>
+      <c r="H616" s="29" t="inlineStr">
+        <is>
+          <t>道しるべと山の景色の絵をボタン全体に敷く。文字は白いふちどり。大きさは変えていない</t>
+        </is>
+      </c>
+      <c r="I616" s="29" t="inlineStr">
+        <is>
+          <t>運営者の指示（2026-10-25）。絵は運営者が ChatGPT で作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="29" t="n">
+        <v>616</v>
+      </c>
+      <c r="B617" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C617" s="29" t="inlineStr">
+        <is>
+          <t>トップページ</t>
+        </is>
+      </c>
+      <c r="D617" s="29" t="inlineStr">
+        <is>
+          <t>index.html の「16タイプ診断」ボタン</t>
+        </is>
+      </c>
+      <c r="E617" s="29" t="inlineStr">
+        <is>
+          <t>PCでカワウソの頭・顔が切れるのを直した</t>
+        </is>
+      </c>
+      <c r="F617" s="29" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="G617" s="29" t="inlineStr">
+        <is>
+          <t>絵をボタン全体に cover で敷く（PCで上下が切れる）</t>
+        </is>
+      </c>
+      <c r="H617" s="29" t="inlineStr">
+        <is>
+          <t>右端に絵の全体を高さに合わせて重ね、左は同じ絵の空と山並みの部分をぼかしてつなぐ。スマホの見た目は変わらない</t>
+        </is>
+      </c>
+      <c r="I617" s="29" t="inlineStr">
+        <is>
+          <t>運営者の指摘</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>617</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>全156山</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>山ページの「関連するまとめ」</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>登山タイプ診断へのリンクを全山に入れ、文をそろえた</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>data/mountains.json（relatedLinksHtml）・山ページ156</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>152山にリンクあり（文は4種類。123山が「出発地から」「AIが提案」）、4山はリンクなし、平標山は2つ</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>全156山で最後に1つ。「12問・約2分。16タイプのどれかと、そのタイプに合う山がわかる」</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>運営者の指示（2026-10-25）</t>
         </is>
       </c>
     </row>
